--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -561,7 +561,7 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01086772807397862</v>
+        <v>0.01143971376208275</v>
       </c>
       <c r="H2" t="n">
         <v>185.8333489727328</v>
@@ -570,14 +570,14 @@
         <v>200</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01114740663604194</v>
+        <v>0.008980106835938563</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>0.525</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="N2" t="n">
         <v>197.8088169752323</v>
@@ -586,14 +586,14 @@
         <v>200</v>
       </c>
       <c r="P2" t="n">
-        <v>0.525</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="Q2" t="n">
         <v>199.5572761277739</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -604,7 +604,7 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE 2026</t>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -634,7 +634,7 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00951068472871661</v>
+        <v>0.009067953039092178</v>
       </c>
       <c r="H3" t="n">
         <v>157.2321783542833</v>
@@ -643,14 +643,14 @@
         <v>200</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01243217591218257</v>
+        <v>0.01223255052547364</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
         <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>0.15</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="N3" t="n">
         <v>197.8854209931308</v>
@@ -659,7 +659,7 @@
         <v>200</v>
       </c>
       <c r="P3" t="n">
-        <v>0.15</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="Q3" t="n">
         <v>199.636475467609</v>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01339726082426194</v>
+        <v>0.01410237981501257</v>
       </c>
       <c r="H4" t="n">
         <v>158.5580779411727</v>
@@ -716,14 +716,14 @@
         <v>200</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08812743593513031</v>
+        <v>0.07902433993532074</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
         <v>200</v>
       </c>
       <c r="M4" t="n">
-        <v>0.375</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="N4" t="n">
         <v>197.7265973322816</v>
@@ -732,7 +732,7 @@
         <v>200</v>
       </c>
       <c r="P4" t="n">
-        <v>0.375</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="Q4" t="n">
         <v>199.5859359679221</v>
@@ -771,32 +771,32 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>199.7281696340077</v>
+        <v>199.0125831330724</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1048593991352036</v>
+        <v>0.1083988208702625</v>
       </c>
       <c r="H5" t="n">
         <v>175.1088701866436</v>
       </c>
       <c r="I5" t="n">
-        <v>199.3809783512508</v>
+        <v>199.3234195740198</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1119793431599173</v>
+        <v>0.1167777980905749</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
         <v>200</v>
       </c>
       <c r="M5" t="n">
-        <v>0.25</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N5" t="n">
         <v>187.2707284786031</v>
@@ -805,7 +805,7 @@
         <v>200</v>
       </c>
       <c r="P5" t="n">
-        <v>0.25</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="Q5" t="n">
         <v>193.7972259177366</v>
@@ -844,32 +844,32 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>199.6777733312251</v>
+        <v>199.5227768499908</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0602663955212074</v>
+        <v>0.06224017002961615</v>
       </c>
       <c r="H6" t="n">
         <v>191.646475967384</v>
       </c>
       <c r="I6" t="n">
-        <v>199.9843425299454</v>
+        <v>199.9904719366027</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05069113209634211</v>
+        <v>0.05344732191053987</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>200</v>
       </c>
       <c r="M6" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="N6" t="n">
         <v>192.53013744135</v>
@@ -878,7 +878,7 @@
         <v>200</v>
       </c>
       <c r="P6" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="Q6" t="n">
         <v>193.2139428195562</v>
@@ -917,32 +917,32 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>199.4138707719809</v>
+        <v>199.0827646374914</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07495987243786448</v>
+        <v>0.07542585392837421</v>
       </c>
       <c r="H7" t="n">
         <v>186.9197740801393</v>
       </c>
       <c r="I7" t="n">
-        <v>199.9778427942358</v>
+        <v>199.9920711524921</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05037771214012601</v>
+        <v>0.05301641570428982</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
         <v>200</v>
       </c>
       <c r="M7" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="N7" t="n">
         <v>185.3187572725189</v>
@@ -951,7 +951,7 @@
         <v>200</v>
       </c>
       <c r="P7" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="Q7" t="n">
         <v>190.8625800946274</v>
@@ -990,41 +990,41 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>142</v>
       </c>
       <c r="F8" t="n">
-        <v>109.7901638305704</v>
+        <v>101.1620929265983</v>
       </c>
       <c r="G8" t="n">
-        <v>5.394850249006375</v>
+        <v>5.212131266542356</v>
       </c>
       <c r="H8" t="n">
         <v>154.5040916050135</v>
       </c>
       <c r="I8" t="n">
-        <v>69.8183715712405</v>
+        <v>49.448315629151</v>
       </c>
       <c r="J8" t="n">
-        <v>4.324731014871479</v>
+        <v>3.415782015598385</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>97.3035593631158</v>
+        <v>95.80329746013628</v>
       </c>
       <c r="M8" t="n">
-        <v>15.475</v>
+        <v>15.18421052631579</v>
       </c>
       <c r="N8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="O8" t="n">
-        <v>97.3035593631158</v>
+        <v>95.80329746013628</v>
       </c>
       <c r="P8" t="n">
-        <v>15.475</v>
+        <v>15.18421052631579</v>
       </c>
       <c r="Q8" t="n">
         <v>172.894287988784</v>
@@ -1040,11 +1040,11 @@
         </is>
       </c>
       <c r="T8" t="n">
-        <v>69.8183715712405</v>
+        <v>49.448315629151</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=69.82% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=49.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1065,41 +1065,41 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
         <v>62</v>
       </c>
       <c r="F9" t="n">
-        <v>104.6693301380919</v>
+        <v>96.50000967408079</v>
       </c>
       <c r="G9" t="n">
-        <v>2.436405846945536</v>
+        <v>2.364058607609518</v>
       </c>
       <c r="H9" t="n">
         <v>164.086229256472</v>
       </c>
       <c r="I9" t="n">
-        <v>85.10601083112711</v>
+        <v>76.1592104766909</v>
       </c>
       <c r="J9" t="n">
-        <v>2.505385476676286</v>
+        <v>3.688325335653582</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>122.8188164483355</v>
+        <v>111.3394980759131</v>
       </c>
       <c r="M9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.631578947368421</v>
       </c>
       <c r="N9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="O9" t="n">
-        <v>122.8188164483355</v>
+        <v>111.3394980759131</v>
       </c>
       <c r="P9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.631578947368421</v>
       </c>
       <c r="Q9" t="n">
         <v>176.8647517474977</v>
@@ -1115,11 +1115,11 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>85.10601083112711</v>
+        <v>76.1592104766909</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=85.11% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=76.16% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1140,41 +1140,41 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
         <v>75</v>
       </c>
       <c r="F10" t="n">
-        <v>103.493304515511</v>
+        <v>94.84727283752737</v>
       </c>
       <c r="G10" t="n">
-        <v>2.781134605152803</v>
+        <v>2.632141656550983</v>
       </c>
       <c r="H10" t="n">
         <v>164.4874496413386</v>
       </c>
       <c r="I10" t="n">
-        <v>55.28951766255922</v>
+        <v>42.29469737291846</v>
       </c>
       <c r="J10" t="n">
-        <v>1.907720220549621</v>
+        <v>1.605336268698746</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>97.33649275709165</v>
+        <v>95.95074714452349</v>
       </c>
       <c r="M10" t="n">
-        <v>8.5</v>
+        <v>8.342105263157896</v>
       </c>
       <c r="N10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="O10" t="n">
-        <v>97.33649275709165</v>
+        <v>95.95074714452349</v>
       </c>
       <c r="P10" t="n">
-        <v>8.5</v>
+        <v>8.342105263157896</v>
       </c>
       <c r="Q10" t="n">
         <v>168.5443712458804</v>
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="T10" t="n">
-        <v>55.28951766255922</v>
+        <v>42.29469737291846</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=55.29% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=42.29% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1215,41 +1215,41 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
         <v>11</v>
       </c>
       <c r="F11" t="n">
-        <v>180.7337616565848</v>
+        <v>177.1662152513658</v>
       </c>
       <c r="G11" t="n">
-        <v>0.569434947554077</v>
+        <v>0.5816049116984011</v>
       </c>
       <c r="H11" t="n">
         <v>123.2554563734294</v>
       </c>
       <c r="I11" t="n">
-        <v>197.1010495257472</v>
+        <v>198.0872324051026</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5451272211304005</v>
+        <v>0.5883275269435004</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>191.0553731226729</v>
+        <v>192.4219018577286</v>
       </c>
       <c r="M11" t="n">
-        <v>28.65760328107719</v>
+        <v>29.69221398008126</v>
       </c>
       <c r="N11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="O11" t="n">
-        <v>157.8123172919869</v>
+        <v>156.945040560381</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9766427395591288</v>
+        <v>1.094459499402622</v>
       </c>
       <c r="Q11" t="n">
         <v>177.781032308345</v>
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="T11" t="n">
-        <v>180.7337616565848</v>
+        <v>177.1662152513658</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=180.73% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=177.17% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1290,41 +1290,41 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>193.8206202873477</v>
+        <v>191.8552562166053</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3617742632242628</v>
+        <v>0.3754643963600293</v>
       </c>
       <c r="H12" t="n">
         <v>147.3485671696691</v>
       </c>
       <c r="I12" t="n">
-        <v>199.5008953099487</v>
+        <v>199.5587784261111</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3524421653432469</v>
+        <v>0.3711322500993692</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>190.3536693647058</v>
+        <v>191.5362391585139</v>
       </c>
       <c r="M12" t="n">
-        <v>13.07354649830269</v>
+        <v>13.60373315610809</v>
       </c>
       <c r="N12" t="n">
         <v>191.4723960783834</v>
       </c>
       <c r="O12" t="n">
-        <v>190.307934378463</v>
+        <v>190.3614367008003</v>
       </c>
       <c r="P12" t="n">
-        <v>12.20253848204103</v>
+        <v>12.74459711503017</v>
       </c>
       <c r="Q12" t="n">
         <v>189.6908701459495</v>
@@ -1363,41 +1363,41 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>196.2274689180362</v>
+        <v>195.3735385790647</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2080582827589973</v>
+        <v>0.2165418703011477</v>
       </c>
       <c r="H13" t="n">
         <v>157.1522264328246</v>
       </c>
       <c r="I13" t="n">
-        <v>199.8421435724525</v>
+        <v>199.8393822352099</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2012342970231166</v>
+        <v>0.2121195042665527</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>193.3911027555972</v>
+        <v>194.1951423424674</v>
       </c>
       <c r="M13" t="n">
-        <v>15.41703159304306</v>
+        <v>15.91266483478217</v>
       </c>
       <c r="N13" t="n">
         <v>193.9340304002594</v>
       </c>
       <c r="O13" t="n">
-        <v>186.5917227749233</v>
+        <v>191.6897112957606</v>
       </c>
       <c r="P13" t="n">
-        <v>6.356524478761369</v>
+        <v>6.691078398696177</v>
       </c>
       <c r="Q13" t="n">
         <v>188.2053733911598</v>
@@ -1436,41 +1436,41 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
         <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>77.02940775429907</v>
+        <v>70.98011798172448</v>
       </c>
       <c r="G14" t="n">
-        <v>2.125116516871372</v>
+        <v>2.050209983850287</v>
       </c>
       <c r="H14" t="n">
         <v>66.61025297793201</v>
       </c>
       <c r="I14" t="n">
-        <v>91.8371059240401</v>
+        <v>84.9403327767854</v>
       </c>
       <c r="J14" t="n">
-        <v>3.101125429382205</v>
+        <v>2.624469817249901</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>170.2897028541543</v>
+        <v>168.2605793498451</v>
       </c>
       <c r="M14" t="n">
-        <v>33.88968371128689</v>
+        <v>33.4179335827928</v>
       </c>
       <c r="N14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="O14" t="n">
-        <v>181.9574498115498</v>
+        <v>180.3554903048052</v>
       </c>
       <c r="P14" t="n">
-        <v>62.675</v>
+        <v>59.6578947368421</v>
       </c>
       <c r="Q14" t="n">
         <v>186.0423288913966</v>
@@ -1486,11 +1486,11 @@
         </is>
       </c>
       <c r="T14" t="n">
-        <v>77.02940775429907</v>
+        <v>70.98011798172448</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=77.03% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=70.98% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1511,41 +1511,41 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
         <v>32</v>
       </c>
       <c r="F15" t="n">
-        <v>72.94225095080226</v>
+        <v>65.87044566451193</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9518265365471958</v>
+        <v>0.897248034177942</v>
       </c>
       <c r="H15" t="n">
         <v>82.6747998505866</v>
       </c>
       <c r="I15" t="n">
-        <v>93.24077319858718</v>
+        <v>90.82996398527685</v>
       </c>
       <c r="J15" t="n">
-        <v>1.212095214356139</v>
+        <v>1.202745696995517</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>175.9595610619057</v>
+        <v>172.9250609621144</v>
       </c>
       <c r="M15" t="n">
-        <v>22.44172919513397</v>
+        <v>22.15212661391847</v>
       </c>
       <c r="N15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="O15" t="n">
-        <v>179.9575083336535</v>
+        <v>176.3509089864839</v>
       </c>
       <c r="P15" t="n">
-        <v>29.75</v>
+        <v>28.47368421052632</v>
       </c>
       <c r="Q15" t="n">
         <v>186.4460938550808</v>
@@ -1561,11 +1561,11 @@
         </is>
       </c>
       <c r="T15" t="n">
-        <v>72.94225095080226</v>
+        <v>65.87044566451193</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=72.94% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=65.87% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1586,41 +1586,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
         <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>126.3567261342521</v>
+        <v>122.3179070028762</v>
       </c>
       <c r="G16" t="n">
-        <v>1.57965760327544</v>
+        <v>1.567952396243824</v>
       </c>
       <c r="H16" t="n">
         <v>90.20708978859948</v>
       </c>
       <c r="I16" t="n">
-        <v>136.1130968920736</v>
+        <v>142.1698014999685</v>
       </c>
       <c r="J16" t="n">
-        <v>1.592405092313915</v>
+        <v>1.461545414911759</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>179.4519087081363</v>
+        <v>177.5562163584148</v>
       </c>
       <c r="M16" t="n">
-        <v>23.40775602863392</v>
+        <v>23.00017792905756</v>
       </c>
       <c r="N16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="O16" t="n">
-        <v>185.0954791209864</v>
+        <v>182.3405142567343</v>
       </c>
       <c r="P16" t="n">
-        <v>33</v>
+        <v>31.26315789473684</v>
       </c>
       <c r="Q16" t="n">
         <v>186.1307414343702</v>
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>126.3567261342521</v>
+        <v>122.3179070028762</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=126.36% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=122.32% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>198.5183393661399</v>
+        <v>198.7352626872857</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1079118607902545</v>
+        <v>0.1117349335808297</v>
       </c>
       <c r="H17" t="n">
         <v>194.5446671655584</v>
       </c>
       <c r="I17" t="n">
-        <v>199.9471499975226</v>
+        <v>199.9347630529597</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05224131729022295</v>
+        <v>0.05500281057855451</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
         <v>200</v>
       </c>
       <c r="M17" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="N17" t="n">
         <v>196.7571923388938</v>
@@ -1695,7 +1695,7 @@
         <v>200</v>
       </c>
       <c r="P17" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="Q17" t="n">
         <v>197.0125798901019</v>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02453038060506788</v>
+        <v>0.02565291991697691</v>
       </c>
       <c r="H18" t="n">
         <v>199.6410247115898</v>
@@ -1752,7 +1752,7 @@
         <v>200</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0005921926693516549</v>
+        <v>0.000582446063573821</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1803,32 +1803,32 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>198.7612995065168</v>
+        <v>199.0372771487083</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09456513103887375</v>
+        <v>0.09944267109328039</v>
       </c>
       <c r="H19" t="n">
         <v>196.278530387405</v>
       </c>
       <c r="I19" t="n">
-        <v>199.8936071413619</v>
+        <v>199.9010828640821</v>
       </c>
       <c r="J19" t="n">
-        <v>0.05502945256332609</v>
+        <v>0.05750655344769912</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
         <v>200</v>
       </c>
       <c r="M19" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="N19" t="n">
         <v>196.7189002085085</v>
@@ -1837,7 +1837,7 @@
         <v>200</v>
       </c>
       <c r="P19" t="n">
-        <v>0.125</v>
+        <v>0.131578947368421</v>
       </c>
       <c r="Q19" t="n">
         <v>196.7488584326798</v>
@@ -1876,7 +1876,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07059010458825815</v>
+        <v>0.07047412404518942</v>
       </c>
       <c r="H20" t="n">
         <v>200</v>
@@ -1894,7 +1894,7 @@
         <v>200</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001388806193927645</v>
+        <v>0.001262668041030563</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1954,7 +1954,7 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05681577275851089</v>
+        <v>0.05672395709071366</v>
       </c>
       <c r="H21" t="n">
         <v>200</v>
@@ -1963,7 +1963,7 @@
         <v>200</v>
       </c>
       <c r="J21" t="n">
-        <v>0.006064804826459731</v>
+        <v>0.006155900490740383</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06360909203296403</v>
+        <v>0.06350447684539688</v>
       </c>
       <c r="H22" t="n">
         <v>200</v>
@@ -2032,7 +2032,7 @@
         <v>200</v>
       </c>
       <c r="J22" t="n">
-        <v>0.00042055881785232</v>
+        <v>0.0004386668824289527</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -2083,41 +2083,41 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>192.4620300351746</v>
+        <v>179.1739130190571</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1389783454021599</v>
+        <v>0.1271859159213902</v>
       </c>
       <c r="H23" t="n">
         <v>149.2565324185079</v>
       </c>
       <c r="I23" t="n">
-        <v>199.5908287140417</v>
+        <v>199.2048177791976</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1178408816709046</v>
+        <v>0.118578293258006</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>180</v>
+        <v>192.8571428571429</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="N23" t="n">
         <v>169.6992056798271</v>
       </c>
       <c r="O23" t="n">
-        <v>180</v>
+        <v>192.8571428571429</v>
       </c>
       <c r="P23" t="n">
-        <v>1.05</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="Q23" t="n">
         <v>186.3774873978808</v>
@@ -2156,48 +2156,48 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>197.1773995200509</v>
+        <v>182.221104530061</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07568306474485209</v>
+        <v>0.06574743966708289</v>
       </c>
       <c r="H24" t="n">
         <v>156.2502876793226</v>
       </c>
       <c r="I24" t="n">
-        <v>199.6675259601643</v>
+        <v>198.7364217540033</v>
       </c>
       <c r="J24" t="n">
-        <v>0.06859437203958388</v>
+        <v>0.07131395163685894</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>200</v>
+        <v>138.2549574812263</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2360291182994843</v>
+        <v>0.1431885455784045</v>
       </c>
       <c r="N24" t="n">
         <v>159.6122718089852</v>
       </c>
       <c r="O24" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="P24" t="n">
-        <v>0.575</v>
+        <v>0.5</v>
       </c>
       <c r="Q24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2208,7 +2208,7 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE 2026</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -2238,23 +2238,23 @@
         <v>200</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06991408417631947</v>
+        <v>0.0735937728171784</v>
       </c>
       <c r="H25" t="n">
         <v>155.3955473497874</v>
       </c>
       <c r="I25" t="n">
-        <v>199.9138281155518</v>
+        <v>199.9219951890681</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05559037673579727</v>
+        <v>0.05804041841012747</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>200</v>
       </c>
       <c r="M25" t="n">
-        <v>0.575</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="N25" t="n">
         <v>177.0659734750362</v>
@@ -2263,7 +2263,7 @@
         <v>200</v>
       </c>
       <c r="P25" t="n">
-        <v>0.575</v>
+        <v>0.6052631578947368</v>
       </c>
       <c r="Q25" t="n">
         <v>183.340259481936</v>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>200</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02641044271870376</v>
+        <v>0.02780046601968817</v>
       </c>
       <c r="H26" t="n">
         <v>97.19414576199205</v>
@@ -2320,14 +2320,14 @@
         <v>200</v>
       </c>
       <c r="J26" t="n">
-        <v>0.09281281657628805</v>
+        <v>0.09487158631641658</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
         <v>200</v>
       </c>
       <c r="M26" t="n">
-        <v>67.34999999999999</v>
+        <v>66.31578947368421</v>
       </c>
       <c r="N26" t="n">
         <v>198.3074653131699</v>
@@ -2336,7 +2336,7 @@
         <v>200</v>
       </c>
       <c r="P26" t="n">
-        <v>67.34999999999999</v>
+        <v>66.31578947368421</v>
       </c>
       <c r="Q26" t="n">
         <v>199.6509594119097</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2384,7 +2384,7 @@
         <v>200</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01849258866482504</v>
+        <v>0.01946588280507898</v>
       </c>
       <c r="H27" t="n">
         <v>129.0985231723771</v>
@@ -2393,14 +2393,14 @@
         <v>200</v>
       </c>
       <c r="J27" t="n">
-        <v>0.01147797890503303</v>
+        <v>0.01217744203193361</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
         <v>200</v>
       </c>
       <c r="M27" t="n">
-        <v>33.3</v>
+        <v>32.76315789473684</v>
       </c>
       <c r="N27" t="n">
         <v>198.6114841856233</v>
@@ -2409,7 +2409,7 @@
         <v>200</v>
       </c>
       <c r="P27" t="n">
-        <v>33.3</v>
+        <v>32.76315789473684</v>
       </c>
       <c r="Q27" t="n">
         <v>199.779644487174</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>200</v>
       </c>
       <c r="G28" t="n">
-        <v>0.01865813865375408</v>
+        <v>0.01964014595132009</v>
       </c>
       <c r="H28" t="n">
         <v>127.1718885128103</v>
@@ -2466,14 +2466,14 @@
         <v>200</v>
       </c>
       <c r="J28" t="n">
-        <v>0.004010341489567011</v>
+        <v>0.004357350598142374</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>200</v>
       </c>
       <c r="M28" t="n">
-        <v>34.05</v>
+        <v>33.55263157894737</v>
       </c>
       <c r="N28" t="n">
         <v>197.4940180993655</v>
@@ -2482,7 +2482,7 @@
         <v>200</v>
       </c>
       <c r="P28" t="n">
-        <v>34.05</v>
+        <v>33.55263157894737</v>
       </c>
       <c r="Q28" t="n">
         <v>199.5411797194807</v>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>200</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0976447329447092</v>
+        <v>0.09615446603845537</v>
       </c>
       <c r="H29" t="n">
         <v>191.5075017030775</v>
@@ -2539,14 +2539,14 @@
         <v>200</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02555652266465764</v>
+        <v>0.02400026013487088</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
         <v>200</v>
       </c>
       <c r="M29" t="n">
-        <v>0.45</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="N29" t="n">
         <v>198.5277121400952</v>
@@ -2555,7 +2555,7 @@
         <v>200</v>
       </c>
       <c r="P29" t="n">
-        <v>0.45</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="Q29" t="n">
         <v>199.9388941772115</v>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>200</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08282712908855035</v>
+        <v>0.08151387564442503</v>
       </c>
       <c r="H30" t="n">
         <v>196.0386411854094</v>
@@ -2612,14 +2612,14 @@
         <v>200</v>
       </c>
       <c r="J30" t="n">
-        <v>0.005820292236854531</v>
+        <v>0.005648859496855605</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
         <v>200</v>
       </c>
       <c r="M30" t="n">
-        <v>0.3</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="N30" t="n">
         <v>198.9477887234591</v>
@@ -2628,7 +2628,7 @@
         <v>200</v>
       </c>
       <c r="P30" t="n">
-        <v>0.3</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="Q30" t="n">
         <v>199.7754683359127</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
         <v>200</v>
       </c>
       <c r="G31" t="n">
-        <v>0.09492014033457305</v>
+        <v>0.09432961679395827</v>
       </c>
       <c r="H31" t="n">
         <v>194.2466814459454</v>
@@ -2685,14 +2685,14 @@
         <v>200</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00568686155435202</v>
+        <v>0.006504246045091579</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
         <v>200</v>
       </c>
       <c r="M31" t="n">
-        <v>0.15</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="N31" t="n">
         <v>199.0633013569061</v>
@@ -2701,7 +2701,7 @@
         <v>200</v>
       </c>
       <c r="P31" t="n">
-        <v>0.15</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="Q31" t="n">
         <v>199.9196066031173</v>
@@ -2740,41 +2740,41 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
         <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>173.0746205196547</v>
+        <v>167.192582466706</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4486583812338132</v>
+        <v>0.3731776944879054</v>
       </c>
       <c r="H32" t="n">
         <v>164.6748490827784</v>
       </c>
       <c r="I32" t="n">
-        <v>183.64447418154</v>
+        <v>187.7116605365616</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4039481296888282</v>
+        <v>0.35590860162829</v>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
-        <v>176.2406015037594</v>
+        <v>152.3809523809524</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>2.684210526315789</v>
       </c>
       <c r="N32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="O32" t="n">
-        <v>176.2406015037594</v>
+        <v>152.3809523809524</v>
       </c>
       <c r="P32" t="n">
-        <v>3.5</v>
+        <v>2.684210526315789</v>
       </c>
       <c r="Q32" t="n">
         <v>195.3761640213164</v>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -2822,23 +2822,23 @@
         <v>200</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1968837263275579</v>
+        <v>0.156967795367359</v>
       </c>
       <c r="H33" t="n">
         <v>170.4028696730483</v>
       </c>
       <c r="I33" t="n">
-        <v>197.7638774899579</v>
+        <v>197.7160600542925</v>
       </c>
       <c r="J33" t="n">
-        <v>0.182372380761035</v>
+        <v>0.1629487095041507</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
         <v>200</v>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1.789473684210526</v>
       </c>
       <c r="N33" t="n">
         <v>180.7526372107734</v>
@@ -2847,14 +2847,14 @@
         <v>200</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>1.789473684210526</v>
       </c>
       <c r="Q33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -2865,7 +2865,7 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE 2026</t>
         </is>
       </c>
     </row>
@@ -2886,41 +2886,41 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
         <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>175.9945967189597</v>
+        <v>175.6265418068303</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3223675186368475</v>
+        <v>0.3116447449667569</v>
       </c>
       <c r="H34" t="n">
         <v>169.6571057340244</v>
       </c>
       <c r="I34" t="n">
-        <v>175.3943735076782</v>
+        <v>172.2289143480554</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8323823094453979</v>
+        <v>0.4078312226593602</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>169.9487179487179</v>
+        <v>163.9888682745826</v>
       </c>
       <c r="M34" t="n">
-        <v>1.9</v>
+        <v>1.421052631578947</v>
       </c>
       <c r="N34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="O34" t="n">
-        <v>169.9487179487179</v>
+        <v>163.9888682745826</v>
       </c>
       <c r="P34" t="n">
-        <v>1.9</v>
+        <v>1.421052631578947</v>
       </c>
       <c r="Q34" t="n">
         <v>195.2398047728465</v>
@@ -2959,41 +2959,41 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
         <v>15</v>
       </c>
       <c r="F35" t="n">
-        <v>110.9396023575286</v>
+        <v>105.0282170767762</v>
       </c>
       <c r="G35" t="n">
-        <v>0.6977929268663463</v>
+        <v>0.6403055072847207</v>
       </c>
       <c r="H35" t="n">
         <v>48.55849570822402</v>
       </c>
       <c r="I35" t="n">
-        <v>128.5001447457965</v>
+        <v>128.6317087128079</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7017147666963096</v>
+        <v>0.8248307660368517</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
-        <v>190.870534578779</v>
+        <v>190.1370507886782</v>
       </c>
       <c r="M35" t="n">
-        <v>30.81911507859925</v>
+        <v>30.60377691036805</v>
       </c>
       <c r="N35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="O35" t="n">
-        <v>198.0316539985731</v>
+        <v>198.0246068743259</v>
       </c>
       <c r="P35" t="n">
-        <v>175.5469425492444</v>
+        <v>177.049413209731</v>
       </c>
       <c r="Q35" t="n">
         <v>185.853149170162</v>
@@ -3009,11 +3009,11 @@
         </is>
       </c>
       <c r="T35" t="n">
-        <v>110.9396023575286</v>
+        <v>105.0282170767762</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=110.94% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=105.03% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3034,41 +3034,41 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>166.3307051563135</v>
+        <v>161.9953762443956</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4268639197313808</v>
+        <v>0.4122286060260453</v>
       </c>
       <c r="H36" t="n">
         <v>58.86670393327421</v>
       </c>
       <c r="I36" t="n">
-        <v>180.2790006592498</v>
+        <v>171.3518767659004</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7522362272049626</v>
+        <v>0.649354005833872</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>187.3245280383966</v>
+        <v>187.6511691920828</v>
       </c>
       <c r="M36" t="n">
-        <v>9.207451865461026</v>
+        <v>9.022437799031088</v>
       </c>
       <c r="N36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="O36" t="n">
-        <v>198.5900892692148</v>
+        <v>198.7712512880413</v>
       </c>
       <c r="P36" t="n">
-        <v>85.50262813801223</v>
+        <v>86.37118751369708</v>
       </c>
       <c r="Q36" t="n">
         <v>187.2910306593169</v>
@@ -3107,41 +3107,41 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" t="n">
         <v>9</v>
       </c>
       <c r="F37" t="n">
-        <v>153.5008255177833</v>
+        <v>149.3030044507669</v>
       </c>
       <c r="G37" t="n">
-        <v>0.6468039735914667</v>
+        <v>0.6340439810854436</v>
       </c>
       <c r="H37" t="n">
         <v>60.32903496111531</v>
       </c>
       <c r="I37" t="n">
-        <v>154.5807831928902</v>
+        <v>163.1188236017408</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7104140658343583</v>
+        <v>0.8129319453662752</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>184.7445794523662</v>
+        <v>180.650285245381</v>
       </c>
       <c r="M37" t="n">
-        <v>9.383893129980439</v>
+        <v>9.231672364614226</v>
       </c>
       <c r="N37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="O37" t="n">
-        <v>197.3323511722214</v>
+        <v>197.3169566187356</v>
       </c>
       <c r="P37" t="n">
-        <v>91.25143798078706</v>
+        <v>91.948882085039</v>
       </c>
       <c r="Q37" t="n">
         <v>185.3862117422507</v>
@@ -3180,41 +3180,41 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E38" t="n">
         <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>191.3745717133044</v>
+        <v>191.9919619009012</v>
       </c>
       <c r="G38" t="n">
-        <v>0.453731659430479</v>
+        <v>0.4533242349898883</v>
       </c>
       <c r="H38" t="n">
         <v>164.4263244057969</v>
       </c>
       <c r="I38" t="n">
-        <v>194.7715279449446</v>
+        <v>194.5679991577052</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3716267464447413</v>
+        <v>0.3264860329740122</v>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>183.3636363636363</v>
+        <v>182.488038277512</v>
       </c>
       <c r="M38" t="n">
-        <v>7.9</v>
+        <v>7.368421052631579</v>
       </c>
       <c r="N38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="O38" t="n">
-        <v>183.3636363636363</v>
+        <v>182.488038277512</v>
       </c>
       <c r="P38" t="n">
-        <v>7.9</v>
+        <v>7.368421052631579</v>
       </c>
       <c r="Q38" t="n">
         <v>199.036270909302</v>
@@ -3253,41 +3253,41 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>198.5290703658214</v>
+        <v>198.5118901369247</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1721657792703782</v>
+        <v>0.1737669757217708</v>
       </c>
       <c r="H39" t="n">
         <v>170.2041702191862</v>
       </c>
       <c r="I39" t="n">
-        <v>199.1752360806499</v>
+        <v>199.3242543587107</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1182796072569811</v>
+        <v>0.1236912055260483</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
-        <v>189.4736842105263</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>3.447368421052631</v>
       </c>
       <c r="N39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="O39" t="n">
-        <v>189.4736842105263</v>
+        <v>182.2222222222222</v>
       </c>
       <c r="P39" t="n">
-        <v>3.8</v>
+        <v>3.447368421052631</v>
       </c>
       <c r="Q39" t="n">
         <v>199.0467638312102</v>
@@ -3326,41 +3326,41 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>196.9678749346641</v>
+        <v>197.8503046852848</v>
       </c>
       <c r="G40" t="n">
-        <v>0.213976235579023</v>
+        <v>0.2175630299201529</v>
       </c>
       <c r="H40" t="n">
         <v>165.7522199768573</v>
       </c>
       <c r="I40" t="n">
-        <v>199.6722780317213</v>
+        <v>199.6624849301809</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1101820487614344</v>
+        <v>0.1145922745262008</v>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>187</v>
+        <v>186.3157894736842</v>
       </c>
       <c r="M40" t="n">
-        <v>4.475</v>
+        <v>4.157894736842105</v>
       </c>
       <c r="N40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="O40" t="n">
-        <v>187</v>
+        <v>186.3157894736842</v>
       </c>
       <c r="P40" t="n">
-        <v>4.475</v>
+        <v>4.157894736842105</v>
       </c>
       <c r="Q40" t="n">
         <v>198.942356787496</v>
@@ -3399,41 +3399,41 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E41" t="n">
         <v>47</v>
       </c>
       <c r="F41" t="n">
-        <v>90.99235921750122</v>
+        <v>87.77044360060759</v>
       </c>
       <c r="G41" t="n">
-        <v>1.911676943434404</v>
+        <v>1.856873350730323</v>
       </c>
       <c r="H41" t="n">
         <v>127.4617865350128</v>
       </c>
       <c r="I41" t="n">
-        <v>104.5433766898648</v>
+        <v>91.89362526827718</v>
       </c>
       <c r="J41" t="n">
-        <v>1.709978353473075</v>
+        <v>1.511609206255772</v>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
-        <v>186.1504278089485</v>
+        <v>183.507499093661</v>
       </c>
       <c r="M41" t="n">
-        <v>60.05</v>
+        <v>54.92105263157895</v>
       </c>
       <c r="N41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="O41" t="n">
-        <v>186.1504278089485</v>
+        <v>183.507499093661</v>
       </c>
       <c r="P41" t="n">
-        <v>60.05</v>
+        <v>54.92105263157895</v>
       </c>
       <c r="Q41" t="n">
         <v>198.8825072752037</v>
@@ -3449,11 +3449,11 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>90.99235921750122</v>
+        <v>87.77044360060759</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=90.99% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=87.77% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3474,41 +3474,41 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E42" t="n">
         <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>116.0005077227006</v>
+        <v>113.7548643964564</v>
       </c>
       <c r="G42" t="n">
-        <v>1.240061939285104</v>
+        <v>1.223731755047448</v>
       </c>
       <c r="H42" t="n">
         <v>139.5371944473096</v>
       </c>
       <c r="I42" t="n">
-        <v>160.850427080628</v>
+        <v>155.8038714031126</v>
       </c>
       <c r="J42" t="n">
-        <v>1.230393263384364</v>
+        <v>1.261630135771666</v>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>183.8727900665802</v>
+        <v>181.2887708376975</v>
       </c>
       <c r="M42" t="n">
-        <v>27.625</v>
+        <v>24.97368421052632</v>
       </c>
       <c r="N42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="O42" t="n">
-        <v>183.8727900665802</v>
+        <v>181.2887708376975</v>
       </c>
       <c r="P42" t="n">
-        <v>27.625</v>
+        <v>24.97368421052632</v>
       </c>
       <c r="Q42" t="n">
         <v>198.6803521667581</v>
@@ -3524,11 +3524,11 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>116.0005077227006</v>
+        <v>113.7548643964564</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=116.00% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=113.75% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3549,41 +3549,41 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" t="n">
         <v>22</v>
       </c>
       <c r="F43" t="n">
-        <v>93.02139516879888</v>
+        <v>91.31975786598234</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9787505353883297</v>
+        <v>0.9782084518115962</v>
       </c>
       <c r="H43" t="n">
         <v>137.8269504556986</v>
       </c>
       <c r="I43" t="n">
-        <v>149.577522292609</v>
+        <v>129.0846217162649</v>
       </c>
       <c r="J43" t="n">
-        <v>1.095110705951826</v>
+        <v>0.8697344172166692</v>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
-        <v>188.6580027480691</v>
+        <v>186.9457477180321</v>
       </c>
       <c r="M43" t="n">
-        <v>34.075</v>
+        <v>31.68421052631579</v>
       </c>
       <c r="N43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="O43" t="n">
-        <v>188.6580027480691</v>
+        <v>186.9457477180321</v>
       </c>
       <c r="P43" t="n">
-        <v>34.075</v>
+        <v>31.68421052631579</v>
       </c>
       <c r="Q43" t="n">
         <v>198.9631246433146</v>
@@ -3599,11 +3599,11 @@
         </is>
       </c>
       <c r="T43" t="n">
-        <v>93.02139516879888</v>
+        <v>91.31975786598234</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=93.02% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=91.32% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3624,48 +3624,48 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
         <v>44</v>
       </c>
       <c r="F44" t="n">
-        <v>105.9365018332815</v>
+        <v>101.541216978027</v>
       </c>
       <c r="G44" t="n">
-        <v>3.456152875980131</v>
+        <v>3.270011438578409</v>
       </c>
       <c r="H44" t="n">
         <v>101.902133963665</v>
       </c>
       <c r="I44" t="n">
-        <v>105.6649301630763</v>
+        <v>113.9440981841071</v>
       </c>
       <c r="J44" t="n">
-        <v>1.445600904280817</v>
+        <v>1.94968755914931</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>186.6809141419736</v>
+        <v>185.0623623920618</v>
       </c>
       <c r="M44" t="n">
-        <v>70.47499999999999</v>
+        <v>69.28947368421052</v>
       </c>
       <c r="N44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="O44" t="n">
-        <v>186.6809141419736</v>
+        <v>185.0623623920618</v>
       </c>
       <c r="P44" t="n">
-        <v>70.47499999999999</v>
+        <v>69.28947368421052</v>
       </c>
       <c r="Q44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -3674,11 +3674,11 @@
         </is>
       </c>
       <c r="T44" t="n">
-        <v>105.6649301630763</v>
+        <v>101.541216978027</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=105.66% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=101.54% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3699,41 +3699,41 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
         <v>27</v>
       </c>
       <c r="F45" t="n">
-        <v>119.8318410788939</v>
+        <v>116.1460451702141</v>
       </c>
       <c r="G45" t="n">
-        <v>2.75931531555593</v>
+        <v>2.564017877299051</v>
       </c>
       <c r="H45" t="n">
         <v>133.2410714461222</v>
       </c>
       <c r="I45" t="n">
-        <v>132.1667107637251</v>
+        <v>138.7678816808106</v>
       </c>
       <c r="J45" t="n">
-        <v>1.272873950465782</v>
+        <v>1.468288778039868</v>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
-        <v>184.5081657232018</v>
+        <v>181.9877754532652</v>
       </c>
       <c r="M45" t="n">
-        <v>34.425</v>
+        <v>33.71052631578947</v>
       </c>
       <c r="N45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="O45" t="n">
-        <v>184.5081657232018</v>
+        <v>181.9877754532652</v>
       </c>
       <c r="P45" t="n">
-        <v>34.425</v>
+        <v>33.71052631578947</v>
       </c>
       <c r="Q45" t="n">
         <v>195.8311934408034</v>
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="T45" t="n">
-        <v>119.8318410788939</v>
+        <v>116.1460451702141</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=119.83% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=116.15% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3774,41 +3774,41 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46" t="n">
         <v>17</v>
       </c>
       <c r="F46" t="n">
-        <v>142.6834424411061</v>
+        <v>140.3897249540533</v>
       </c>
       <c r="G46" t="n">
-        <v>2.621771849552344</v>
+        <v>2.53501087439491</v>
       </c>
       <c r="H46" t="n">
         <v>129.1401202444324</v>
       </c>
       <c r="I46" t="n">
-        <v>162.176218108374</v>
+        <v>154.2493653257513</v>
       </c>
       <c r="J46" t="n">
-        <v>1.144557900774781</v>
+        <v>1.085230101094652</v>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
-        <v>187.5350995212476</v>
+        <v>187.2242110784918</v>
       </c>
       <c r="M46" t="n">
-        <v>36.05</v>
+        <v>35.57894736842105</v>
       </c>
       <c r="N46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="O46" t="n">
-        <v>187.5350995212476</v>
+        <v>187.2242110784918</v>
       </c>
       <c r="P46" t="n">
-        <v>36.05</v>
+        <v>35.57894736842105</v>
       </c>
       <c r="Q46" t="n">
         <v>196.1388328305384</v>
@@ -3824,11 +3824,11 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>142.6834424411061</v>
+        <v>140.3897249540533</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=142.68% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=140.39% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3849,41 +3849,41 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
         <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>196.6332359904158</v>
+        <v>195.9411133670229</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1606957213958789</v>
+        <v>0.1636167997295013</v>
       </c>
       <c r="H47" t="n">
         <v>52.02932925897922</v>
       </c>
       <c r="I47" t="n">
-        <v>198.1890928333171</v>
+        <v>195.6050915352664</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8695993149214983</v>
+        <v>0.6016355901040529</v>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
-        <v>198.5529878177032</v>
+        <v>198.4000634090768</v>
       </c>
       <c r="M47" t="n">
-        <v>26.58475087988627</v>
+        <v>25.60542579982614</v>
       </c>
       <c r="N47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="O47" t="n">
-        <v>199.0588235294118</v>
+        <v>198.8919667590028</v>
       </c>
       <c r="P47" t="n">
-        <v>43.475</v>
+        <v>40.1578947368421</v>
       </c>
       <c r="Q47" t="n">
         <v>193.8459595711977</v>
@@ -3922,41 +3922,41 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
         <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>197.9898874099946</v>
+        <v>197.4116289114259</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1205707578610449</v>
+        <v>0.1238703056407061</v>
       </c>
       <c r="H48" t="n">
         <v>75.82494372432545</v>
       </c>
       <c r="I48" t="n">
-        <v>198.5556588877688</v>
+        <v>198.5785629334108</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2486462814662605</v>
+        <v>0.208424441549574</v>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>197.4193548387097</v>
+        <v>197.2179224008849</v>
       </c>
       <c r="M48" t="n">
-        <v>12.94475919137651</v>
+        <v>12.65568768239685</v>
       </c>
       <c r="N48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="O48" t="n">
-        <v>197.4193548387097</v>
+        <v>197.6749026522867</v>
       </c>
       <c r="P48" t="n">
-        <v>19.15545161903231</v>
+        <v>17.71626486213928</v>
       </c>
       <c r="Q48" t="n">
         <v>192.3368460426438</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -4004,7 +4004,7 @@
         <v>200</v>
       </c>
       <c r="G49" t="n">
-        <v>0.02383801724012116</v>
+        <v>0.02509264972644333</v>
       </c>
       <c r="H49" t="n">
         <v>67.54170898302603</v>
@@ -4013,14 +4013,14 @@
         <v>200</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5800193533569574</v>
+        <v>0.3455497331267909</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
         <v>200</v>
       </c>
       <c r="M49" t="n">
-        <v>14.88420482866237</v>
+        <v>14.3506723441126</v>
       </c>
       <c r="N49" t="n">
         <v>179.6516960231333</v>
@@ -4029,7 +4029,7 @@
         <v>200</v>
       </c>
       <c r="P49" t="n">
-        <v>24.225</v>
+        <v>22.34210526315789</v>
       </c>
       <c r="Q49" t="n">
         <v>193.5695579772771</v>
@@ -4068,41 +4068,41 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" t="n">
         <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>193.7601776599972</v>
+        <v>194.3911602673957</v>
       </c>
       <c r="G50" t="n">
-        <v>1.943155674242012</v>
+        <v>1.518323311321763</v>
       </c>
       <c r="H50" t="n">
         <v>162.6912701840232</v>
       </c>
       <c r="I50" t="n">
-        <v>199.5255943639819</v>
+        <v>199.5122170374651</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1541396705658501</v>
+        <v>0.1641351663989946</v>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
         <v>200</v>
       </c>
       <c r="M50" t="n">
-        <v>2.473166561126709</v>
+        <v>1.354595385099712</v>
       </c>
       <c r="N50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="O50" t="n">
-        <v>193.8461538461539</v>
+        <v>196.6315789473684</v>
       </c>
       <c r="P50" t="n">
-        <v>10.75452228268771</v>
+        <v>10.46776771225995</v>
       </c>
       <c r="Q50" t="n">
         <v>160.5521309789579</v>
@@ -4141,41 +4141,41 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>194.0305425949256</v>
+        <v>194.7647831852421</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9109693245837992</v>
+        <v>0.7618632865622107</v>
       </c>
       <c r="H51" t="n">
         <v>169.9274838481079</v>
       </c>
       <c r="I51" t="n">
-        <v>199.2991603098328</v>
+        <v>199.569745356571</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1961689987007831</v>
+        <v>0.1221110404092794</v>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
-        <v>194.7368421052632</v>
+        <v>195.959595959596</v>
       </c>
       <c r="M51" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="N51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="O51" t="n">
-        <v>194.7368421052632</v>
+        <v>195.959595959596</v>
       </c>
       <c r="P51" t="n">
-        <v>3.688259689213548</v>
+        <v>3.561613668896306</v>
       </c>
       <c r="Q51" t="n">
         <v>165.5121650610737</v>
@@ -4214,41 +4214,41 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>192.885446614732</v>
+        <v>193.9165959732693</v>
       </c>
       <c r="G52" t="n">
-        <v>1.086715710934221</v>
+        <v>0.8615909360317315</v>
       </c>
       <c r="H52" t="n">
         <v>174.432365021141</v>
       </c>
       <c r="I52" t="n">
-        <v>199.5854243277648</v>
+        <v>199.8419507455721</v>
       </c>
       <c r="J52" t="n">
-        <v>0.05809685265835972</v>
+        <v>0.06365527772305327</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>194.4444444444444</v>
+        <v>196.6386554621849</v>
       </c>
       <c r="M52" t="n">
-        <v>11.575</v>
+        <v>8.552631578947368</v>
       </c>
       <c r="N52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="O52" t="n">
-        <v>194.4444444444444</v>
+        <v>196.6386554621849</v>
       </c>
       <c r="P52" t="n">
-        <v>5.705039689690354</v>
+        <v>5.611034800763306</v>
       </c>
       <c r="Q52" t="n">
         <v>154.7555469695623</v>
@@ -4287,41 +4287,41 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E53" t="n">
-        <v>2144</v>
+        <v>2128</v>
       </c>
       <c r="F53" t="n">
-        <v>26.85289068969008</v>
+        <v>20.26471065115279</v>
       </c>
       <c r="G53" t="n">
-        <v>27.19133176908635</v>
+        <v>23.59328463933557</v>
       </c>
       <c r="H53" t="n">
         <v>35.23746831954708</v>
       </c>
       <c r="I53" t="n">
-        <v>31.39818801810289</v>
+        <v>20.3485721220649</v>
       </c>
       <c r="J53" t="n">
-        <v>34.43192883982927</v>
+        <v>22.35766299143393</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
-        <v>163.3128180579777</v>
+        <v>162.1656348846054</v>
       </c>
       <c r="M53" t="n">
-        <v>967.175</v>
+        <v>960.578947368421</v>
       </c>
       <c r="N53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="O53" t="n">
-        <v>163.3128180579777</v>
+        <v>162.1656348846054</v>
       </c>
       <c r="P53" t="n">
-        <v>967.175</v>
+        <v>960.578947368421</v>
       </c>
       <c r="Q53" t="n">
         <v>188.2648408233968</v>
@@ -4337,11 +4337,11 @@
         </is>
       </c>
       <c r="T53" t="n">
-        <v>26.85289068969008</v>
+        <v>20.26471065115279</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=26.85% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=20.26% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4362,48 +4362,48 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="F54" t="n">
-        <v>26.49214062138509</v>
+        <v>21.78990331830676</v>
       </c>
       <c r="G54" t="n">
-        <v>12.7967918961113</v>
+        <v>12.18529853018219</v>
       </c>
       <c r="H54" t="n">
         <v>38.4591918317379</v>
       </c>
       <c r="I54" t="n">
-        <v>34.00706164062667</v>
+        <v>21.4311848091815</v>
       </c>
       <c r="J54" t="n">
-        <v>17.58349204788859</v>
+        <v>11.31461757696774</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
-        <v>163.8723200739284</v>
+        <v>162.6260942449485</v>
       </c>
       <c r="M54" t="n">
-        <v>457.6</v>
+        <v>456.2631578947368</v>
       </c>
       <c r="N54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="O54" t="n">
-        <v>163.8723200739284</v>
+        <v>162.6260942449485</v>
       </c>
       <c r="P54" t="n">
-        <v>457.6</v>
+        <v>456.2631578947368</v>
       </c>
       <c r="Q54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -4412,11 +4412,11 @@
         </is>
       </c>
       <c r="T54" t="n">
-        <v>26.49214062138509</v>
+        <v>21.4311848091815</v>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=26.49% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=21.43% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4437,48 +4437,48 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E55" t="n">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="F55" t="n">
-        <v>29.12359835648128</v>
+        <v>25.35547688070321</v>
       </c>
       <c r="G55" t="n">
-        <v>15.13124703896282</v>
+        <v>14.64653986540293</v>
       </c>
       <c r="H55" t="n">
         <v>38.25160771522186</v>
       </c>
       <c r="I55" t="n">
-        <v>31.68070990779176</v>
+        <v>23.44652230037202</v>
       </c>
       <c r="J55" t="n">
-        <v>17.71735368082924</v>
+        <v>13.31096246619567</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
-        <v>163.1488662914134</v>
+        <v>161.9773827308954</v>
       </c>
       <c r="M55" t="n">
-        <v>509.875</v>
+        <v>504.6315789473684</v>
       </c>
       <c r="N55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="O55" t="n">
-        <v>163.1488662914134</v>
+        <v>161.9773827308954</v>
       </c>
       <c r="P55" t="n">
-        <v>509.875</v>
+        <v>504.6315789473684</v>
       </c>
       <c r="Q55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -4487,11 +4487,11 @@
         </is>
       </c>
       <c r="T55" t="n">
-        <v>29.12359835648128</v>
+        <v>23.44652230037202</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=29.12% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=23.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4512,41 +4512,41 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E56" t="n">
         <v>64</v>
       </c>
       <c r="F56" t="n">
-        <v>81.47198116921597</v>
+        <v>74.37701734933476</v>
       </c>
       <c r="G56" t="n">
-        <v>3.135008075900632</v>
+        <v>2.979831085540594</v>
       </c>
       <c r="H56" t="n">
         <v>154.1439500713238</v>
       </c>
       <c r="I56" t="n">
-        <v>72.91870364656441</v>
+        <v>60.29125449784342</v>
       </c>
       <c r="J56" t="n">
-        <v>2.290586220935821</v>
+        <v>2.058542600183989</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>169.4065905844108</v>
+        <v>165.3708526408925</v>
       </c>
       <c r="M56" t="n">
-        <v>44.05</v>
+        <v>41.23684210526316</v>
       </c>
       <c r="N56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="O56" t="n">
-        <v>169.4065905844108</v>
+        <v>165.3708526408925</v>
       </c>
       <c r="P56" t="n">
-        <v>44.05</v>
+        <v>41.23684210526316</v>
       </c>
       <c r="Q56" t="n">
         <v>197.7368060568652</v>
@@ -4562,11 +4562,11 @@
         </is>
       </c>
       <c r="T56" t="n">
-        <v>72.91870364656441</v>
+        <v>60.29125449784342</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=72.92% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=60.29% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4587,41 +4587,41 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
         <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>102.7703103191185</v>
+        <v>99.24117228272365</v>
       </c>
       <c r="G57" t="n">
-        <v>1.664503146496795</v>
+        <v>1.645033028339421</v>
       </c>
       <c r="H57" t="n">
         <v>164.0555422208552</v>
       </c>
       <c r="I57" t="n">
-        <v>116.2778304889234</v>
+        <v>116.297575094597</v>
       </c>
       <c r="J57" t="n">
-        <v>1.680530218532175</v>
+        <v>1.527704620497148</v>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>168.3630694067963</v>
+        <v>163.4899500853628</v>
       </c>
       <c r="M57" t="n">
-        <v>19.35</v>
+        <v>18.31578947368421</v>
       </c>
       <c r="N57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="O57" t="n">
-        <v>168.3630694067963</v>
+        <v>163.4899500853628</v>
       </c>
       <c r="P57" t="n">
-        <v>19.35</v>
+        <v>18.31578947368421</v>
       </c>
       <c r="Q57" t="n">
         <v>197.2831175654684</v>
@@ -4637,11 +4637,11 @@
         </is>
       </c>
       <c r="T57" t="n">
-        <v>102.7703103191185</v>
+        <v>99.24117228272365</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=102.77% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=99.24% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4662,41 +4662,41 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
         <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>100.3500865647419</v>
+        <v>94.48969926947952</v>
       </c>
       <c r="G58" t="n">
-        <v>1.789229797592463</v>
+        <v>1.696695370092706</v>
       </c>
       <c r="H58" t="n">
         <v>158.4722608607674</v>
       </c>
       <c r="I58" t="n">
-        <v>107.3749575202978</v>
+        <v>108.3078562554235</v>
       </c>
       <c r="J58" t="n">
-        <v>1.551502533438682</v>
+        <v>1.695960225704595</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
-        <v>176.1983412751029</v>
+        <v>167.6753221837887</v>
       </c>
       <c r="M58" t="n">
-        <v>25.225</v>
+        <v>23.47368421052632</v>
       </c>
       <c r="N58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="O58" t="n">
-        <v>176.1983412751029</v>
+        <v>167.6753221837887</v>
       </c>
       <c r="P58" t="n">
-        <v>25.225</v>
+        <v>23.47368421052632</v>
       </c>
       <c r="Q58" t="n">
         <v>197.6615055783608</v>
@@ -4712,11 +4712,11 @@
         </is>
       </c>
       <c r="T58" t="n">
-        <v>100.3500865647419</v>
+        <v>94.48969926947952</v>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=100.35% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=94.49% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4737,48 +4737,48 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E59" t="n">
         <v>4</v>
       </c>
       <c r="F59" t="n">
-        <v>199.1515784552851</v>
+        <v>199.4821021973625</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2171935952862423</v>
+        <v>0.2298717867783556</v>
       </c>
       <c r="H59" t="n">
         <v>163.442478475025</v>
       </c>
       <c r="I59" t="n">
-        <v>198.8529854712564</v>
+        <v>192.0282448335926</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2523520159748225</v>
+        <v>0.2176559100684902</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
-        <v>187.1468144044321</v>
+        <v>171.7647058823529</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>2.710526315789474</v>
       </c>
       <c r="N59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="O59" t="n">
-        <v>187.1468144044321</v>
+        <v>171.7647058823529</v>
       </c>
       <c r="P59" t="n">
-        <v>3.05</v>
+        <v>2.710526315789474</v>
       </c>
       <c r="Q59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4789,7 +4789,7 @@
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 4 casos), menor MAE 2026</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE 2026</t>
         </is>
       </c>
     </row>
@@ -4810,41 +4810,41 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>197.1153685005927</v>
+        <v>197.7007515643313</v>
       </c>
       <c r="G60" t="n">
-        <v>0.16111705568712</v>
+        <v>0.1727165705253666</v>
       </c>
       <c r="H60" t="n">
         <v>179.6544870721095</v>
       </c>
       <c r="I60" t="n">
-        <v>198.510642801256</v>
+        <v>198.0983117983889</v>
       </c>
       <c r="J60" t="n">
-        <v>0.160475536467807</v>
+        <v>0.1643773387814032</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>185.5238095238095</v>
+        <v>163.0769230769231</v>
       </c>
       <c r="M60" t="n">
-        <v>2.05</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="N60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="O60" t="n">
-        <v>185.5238095238095</v>
+        <v>163.0769230769231</v>
       </c>
       <c r="P60" t="n">
-        <v>2.05</v>
+        <v>1.736842105263158</v>
       </c>
       <c r="Q60" t="n">
         <v>199.0965028052728</v>
@@ -4883,41 +4883,41 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>200</v>
+        <v>199.9502411083014</v>
       </c>
       <c r="G61" t="n">
-        <v>0.07106020839271786</v>
+        <v>0.0745902904045261</v>
       </c>
       <c r="H61" t="n">
         <v>178.3754768379913</v>
       </c>
       <c r="I61" t="n">
-        <v>198.3766852235132</v>
+        <v>198.6805210475813</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1311728987511709</v>
+        <v>0.1343820781330749</v>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
-        <v>186.6666666666667</v>
+        <v>185.4545454545454</v>
       </c>
       <c r="M61" t="n">
-        <v>1.225</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="N61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="O61" t="n">
-        <v>186.6666666666667</v>
+        <v>185.4545454545454</v>
       </c>
       <c r="P61" t="n">
-        <v>1.225</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="Q61" t="n">
         <v>199.3694289811982</v>
@@ -4956,41 +4956,41 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E62" t="n">
         <v>14</v>
       </c>
       <c r="F62" t="n">
-        <v>134.1009750112287</v>
+        <v>128.8719310283875</v>
       </c>
       <c r="G62" t="n">
-        <v>0.8293360287630058</v>
+        <v>0.7572694217418114</v>
       </c>
       <c r="H62" t="n">
         <v>51.86246745886869</v>
       </c>
       <c r="I62" t="n">
-        <v>136.0358785386255</v>
+        <v>130.9571266908071</v>
       </c>
       <c r="J62" t="n">
-        <v>2.476712250312984</v>
+        <v>1.758318531644439</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>176.8247135995747</v>
+        <v>175.5235927343014</v>
       </c>
       <c r="M62" t="n">
-        <v>20.75</v>
+        <v>17.10526315789474</v>
       </c>
       <c r="N62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="O62" t="n">
-        <v>176.8247135995747</v>
+        <v>175.5235927343014</v>
       </c>
       <c r="P62" t="n">
-        <v>20.75</v>
+        <v>17.10526315789474</v>
       </c>
       <c r="Q62" t="n">
         <v>188.4656733609786</v>
@@ -5006,11 +5006,11 @@
         </is>
       </c>
       <c r="T62" t="n">
-        <v>134.1009750112287</v>
+        <v>128.8719310283875</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=134.10% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=128.87% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5031,41 +5031,41 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E63" t="n">
         <v>7</v>
       </c>
       <c r="F63" t="n">
-        <v>157.6514297417157</v>
+        <v>154.6663812011903</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5093959694788122</v>
+        <v>0.4837828153102234</v>
       </c>
       <c r="H63" t="n">
         <v>69.84803023883232</v>
       </c>
       <c r="I63" t="n">
-        <v>152.7091013397381</v>
+        <v>160.7230440211508</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3118686490352386</v>
+        <v>0.4234746267679511</v>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
-        <v>178.5053309861494</v>
+        <v>176.4842587752804</v>
       </c>
       <c r="M63" t="n">
-        <v>8.503647849212859</v>
+        <v>7.368421052631579</v>
       </c>
       <c r="N63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="O63" t="n">
-        <v>178.5053309861494</v>
+        <v>176.4842587752804</v>
       </c>
       <c r="P63" t="n">
-        <v>8.800000000000001</v>
+        <v>7.368421052631579</v>
       </c>
       <c r="Q63" t="n">
         <v>186.3893216158546</v>
@@ -5104,48 +5104,48 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E64" t="n">
         <v>7</v>
       </c>
       <c r="F64" t="n">
-        <v>160.8965611868375</v>
+        <v>156.9060988936143</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7092713576905778</v>
+        <v>0.6365528514939038</v>
       </c>
       <c r="H64" t="n">
         <v>72.92360982323459</v>
       </c>
       <c r="I64" t="n">
-        <v>181.8965716953074</v>
+        <v>166.1274744316233</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9087576588590295</v>
+        <v>0.5598670879556945</v>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
-        <v>179.8759603567788</v>
+        <v>176.5775401069519</v>
       </c>
       <c r="M64" t="n">
-        <v>12.55</v>
+        <v>10.36842105263158</v>
       </c>
       <c r="N64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="O64" t="n">
-        <v>179.8759603567788</v>
+        <v>176.5775401069519</v>
       </c>
       <c r="P64" t="n">
-        <v>12.55</v>
+        <v>10.36842105263158</v>
       </c>
       <c r="Q64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -5156,7 +5156,7 @@
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 7 casos), menor MAE 2026</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE 2026</t>
         </is>
       </c>
     </row>
@@ -5177,43 +5177,43 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E65" t="n">
         <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>173.0643059224137</v>
+        <v>172.7342912125195</v>
       </c>
       <c r="G65" t="n">
-        <v>0.5361878126087376</v>
+        <v>0.5281176484570876</v>
       </c>
       <c r="H65" t="n">
         <v>124.1398173354868</v>
       </c>
       <c r="I65" t="n">
-        <v>189.2205045949596</v>
+        <v>189.1042820076799</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3995701755466284</v>
+        <v>0.3797058234358746</v>
       </c>
       <c r="K65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="L65" t="n">
-        <v>191.2608242821009</v>
+        <v>190.5411382191568</v>
       </c>
       <c r="M65" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="N65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="O65" t="n">
-        <v>191.2608242821009</v>
+        <v>190.5411382191568</v>
       </c>
       <c r="P65" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="Q65" t="n">
         <v>191.9303948964172</v>
@@ -5252,48 +5252,48 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>193.5457671029587</v>
+        <v>193.5182683795834</v>
       </c>
       <c r="G66" t="n">
-        <v>0.24546033812741</v>
+        <v>0.2457881406423402</v>
       </c>
       <c r="H66" t="n">
         <v>146.9871894171194</v>
       </c>
       <c r="I66" t="n">
-        <v>191.2133843615084</v>
+        <v>193.2101731341945</v>
       </c>
       <c r="J66" t="n">
-        <v>0.2125712751581715</v>
+        <v>0.2751233810656595</v>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
-        <v>190.9473684210526</v>
+        <v>193.7098844672657</v>
       </c>
       <c r="M66" t="n">
-        <v>9.35</v>
+        <v>8.894736842105264</v>
       </c>
       <c r="N66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="O66" t="n">
-        <v>190.9473684210526</v>
+        <v>193.7098844672657</v>
       </c>
       <c r="P66" t="n">
-        <v>9.35</v>
+        <v>8.894736842105264</v>
       </c>
       <c r="Q66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -5304,7 +5304,7 @@
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE 2026</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE 2026</t>
         </is>
       </c>
     </row>
@@ -5325,43 +5325,43 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E67" t="n">
         <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>192.0205915791879</v>
+        <v>191.7047398007156</v>
       </c>
       <c r="G67" t="n">
-        <v>0.3476040132777366</v>
+        <v>0.3384995990865677</v>
       </c>
       <c r="H67" t="n">
         <v>137.6516466078508</v>
       </c>
       <c r="I67" t="n">
-        <v>199.6866744737965</v>
+        <v>199.4595197986712</v>
       </c>
       <c r="J67" t="n">
-        <v>0.3028728210109919</v>
+        <v>0.2938794965819146</v>
       </c>
       <c r="K67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="L67" t="n">
-        <v>193.2608695652174</v>
+        <v>193.7098844672657</v>
       </c>
       <c r="M67" t="n">
-        <v>9.65</v>
+        <v>9.052631578947368</v>
       </c>
       <c r="N67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="O67" t="n">
-        <v>193.2608695652174</v>
+        <v>193.7098844672657</v>
       </c>
       <c r="P67" t="n">
-        <v>9.65</v>
+        <v>9.052631578947368</v>
       </c>
       <c r="Q67" t="n">
         <v>191.2393501485975</v>
@@ -5400,43 +5400,43 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>199.8281972817772</v>
+        <v>199.988140539529</v>
       </c>
       <c r="G68" t="n">
-        <v>0.057836630298039</v>
+        <v>0.06134600670915952</v>
       </c>
       <c r="H68" t="n">
         <v>183.5383709430125</v>
       </c>
       <c r="I68" t="n">
-        <v>199.7592380298397</v>
+        <v>199.8261929576067</v>
       </c>
       <c r="J68" t="n">
-        <v>0.06351670235828508</v>
+        <v>0.0661948246945351</v>
       </c>
       <c r="K68" t="n">
         <v>198.3312090033645</v>
       </c>
       <c r="L68" t="n">
-        <v>192.3076923076923</v>
+        <v>200</v>
       </c>
       <c r="M68" t="n">
-        <v>4.804497894862807</v>
+        <v>4.925787257750323</v>
       </c>
       <c r="N68" t="n">
         <v>188.2784643365136</v>
       </c>
       <c r="O68" t="n">
-        <v>192.3076923076923</v>
+        <v>200</v>
       </c>
       <c r="P68" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="Q68" t="n">
         <v>199.7672857698158</v>
@@ -5475,43 +5475,43 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>197.741714817379</v>
+        <v>198.1317768745953</v>
       </c>
       <c r="G69" t="n">
-        <v>0.07582063176123836</v>
+        <v>0.08121093263600343</v>
       </c>
       <c r="H69" t="n">
         <v>171.5447439761989</v>
       </c>
       <c r="I69" t="n">
-        <v>199.3595592321182</v>
+        <v>199.4593995691129</v>
       </c>
       <c r="J69" t="n">
-        <v>0.07547060842913393</v>
+        <v>0.07715776683387024</v>
       </c>
       <c r="K69" t="n">
         <v>194.4182830751776</v>
       </c>
       <c r="L69" t="n">
-        <v>185.4545454545454</v>
+        <v>200</v>
       </c>
       <c r="M69" t="n">
-        <v>2.425</v>
+        <v>2.421052631578947</v>
       </c>
       <c r="N69" t="n">
         <v>190.8574288418282</v>
       </c>
       <c r="O69" t="n">
-        <v>185.4545454545454</v>
+        <v>200</v>
       </c>
       <c r="P69" t="n">
-        <v>2.425</v>
+        <v>2.421052631578947</v>
       </c>
       <c r="Q69" t="n">
         <v>199.6130972886749</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -5559,7 +5559,7 @@
         <v>200</v>
       </c>
       <c r="G70" t="n">
-        <v>0.01690032095695999</v>
+        <v>0.01778981153364209</v>
       </c>
       <c r="H70" t="n">
         <v>188.453973372859</v>
@@ -5568,7 +5568,7 @@
         <v>200</v>
       </c>
       <c r="J70" t="n">
-        <v>0.01671858960669646</v>
+        <v>0.01701156060708355</v>
       </c>
       <c r="K70" t="n">
         <v>198.9765474653765</v>
@@ -5577,7 +5577,7 @@
         <v>200</v>
       </c>
       <c r="M70" t="n">
-        <v>2.850376030036672</v>
+        <v>3.000395821091233</v>
       </c>
       <c r="N70" t="n">
         <v>192.937344462188</v>
@@ -5586,7 +5586,7 @@
         <v>200</v>
       </c>
       <c r="P70" t="n">
-        <v>3.075</v>
+        <v>3.236842105263158</v>
       </c>
       <c r="Q70" t="n">
         <v>199.6974055100667</v>
@@ -5625,43 +5625,43 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E71" t="n">
         <v>84</v>
       </c>
       <c r="F71" t="n">
-        <v>64.56727502609267</v>
+        <v>57.37693578719302</v>
       </c>
       <c r="G71" t="n">
-        <v>2.941023707713654</v>
+        <v>2.825184477639819</v>
       </c>
       <c r="H71" t="n">
         <v>143.4057585362926</v>
       </c>
       <c r="I71" t="n">
-        <v>186.8912037129941</v>
+        <v>181.7289735216879</v>
       </c>
       <c r="J71" t="n">
-        <v>4.090041097183013</v>
+        <v>4.204953221303974</v>
       </c>
       <c r="K71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="L71" t="n">
-        <v>78.06937976371803</v>
+        <v>76.44148826641481</v>
       </c>
       <c r="M71" t="n">
-        <v>4.468310669191593</v>
+        <v>4.461687547631855</v>
       </c>
       <c r="N71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="O71" t="n">
-        <v>190.0346257603482</v>
+        <v>187.5628945654752</v>
       </c>
       <c r="P71" t="n">
-        <v>4.110173940924571</v>
+        <v>4.2884948607661</v>
       </c>
       <c r="Q71" t="n">
         <v>185.267595267154</v>
@@ -5677,11 +5677,11 @@
         </is>
       </c>
       <c r="T71" t="n">
-        <v>64.56727502609267</v>
+        <v>57.37693578719302</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=64.57% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=57.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5702,43 +5702,43 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E72" t="n">
         <v>35</v>
       </c>
       <c r="F72" t="n">
-        <v>93.10127722110948</v>
+        <v>91.0942949438804</v>
       </c>
       <c r="G72" t="n">
-        <v>1.524188672790535</v>
+        <v>1.574592744679023</v>
       </c>
       <c r="H72" t="n">
         <v>151.0433307550491</v>
       </c>
       <c r="I72" t="n">
-        <v>97.67313610158818</v>
+        <v>96.98750299847268</v>
       </c>
       <c r="J72" t="n">
-        <v>1.182501047033742</v>
+        <v>1.305697114865129</v>
       </c>
       <c r="K72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="L72" t="n">
-        <v>105.5723674611543</v>
+        <v>96.43718470396682</v>
       </c>
       <c r="M72" t="n">
-        <v>2.609542489206892</v>
+        <v>2.321839312638196</v>
       </c>
       <c r="N72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="O72" t="n">
-        <v>166.5100181083366</v>
+        <v>157.7563524619638</v>
       </c>
       <c r="P72" t="n">
-        <v>1.583036859339645</v>
+        <v>1.77161774667331</v>
       </c>
       <c r="Q72" t="n">
         <v>161.2927483340683</v>
@@ -5754,11 +5754,11 @@
         </is>
       </c>
       <c r="T72" t="n">
-        <v>93.10127722110948</v>
+        <v>91.0942949438804</v>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=93.10% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=91.09% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5779,43 +5779,43 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E73" t="n">
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>74.95528952368508</v>
+        <v>66.88932169454627</v>
       </c>
       <c r="G73" t="n">
-        <v>1.90198713878477</v>
+        <v>1.833647952485144</v>
       </c>
       <c r="H73" t="n">
         <v>148.5993365374143</v>
       </c>
       <c r="I73" t="n">
-        <v>180.4238358004238</v>
+        <v>167.6095784999177</v>
       </c>
       <c r="J73" t="n">
-        <v>2.504576588772987</v>
+        <v>2.325709697108638</v>
       </c>
       <c r="K73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="L73" t="n">
-        <v>120.5578166004785</v>
+        <v>99.42587142276584</v>
       </c>
       <c r="M73" t="n">
-        <v>2.512697660923004</v>
+        <v>2.018178237111945</v>
       </c>
       <c r="N73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="O73" t="n">
-        <v>181.1782806418032</v>
+        <v>164.8485968348066</v>
       </c>
       <c r="P73" t="n">
-        <v>2.473506868861743</v>
+        <v>2.220180862656712</v>
       </c>
       <c r="Q73" t="n">
         <v>173.6314937555617</v>
@@ -5831,11 +5831,11 @@
         </is>
       </c>
       <c r="T73" t="n">
-        <v>74.95528952368508</v>
+        <v>66.88932169454627</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=74.96% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=66.89% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5856,43 +5856,43 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E74" t="n">
         <v>9</v>
       </c>
       <c r="F74" t="n">
-        <v>170.6471179889325</v>
+        <v>168.5747304100348</v>
       </c>
       <c r="G74" t="n">
-        <v>3.172840474495327</v>
+        <v>2.582846452563731</v>
       </c>
       <c r="H74" t="n">
         <v>148.9425712788151</v>
       </c>
       <c r="I74" t="n">
-        <v>195.2038090910398</v>
+        <v>186.9126864191641</v>
       </c>
       <c r="J74" t="n">
-        <v>0.5001355446108131</v>
+        <v>0.4401064702641599</v>
       </c>
       <c r="K74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="L74" t="n">
-        <v>192.2858577223263</v>
+        <v>189.6448066714631</v>
       </c>
       <c r="M74" t="n">
-        <v>28.85799004315229</v>
+        <v>26.4294632033182</v>
       </c>
       <c r="N74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="O74" t="n">
-        <v>192.2974081025833</v>
+        <v>189.6448066714631</v>
       </c>
       <c r="P74" t="n">
-        <v>29.1</v>
+        <v>26.68421052631579</v>
       </c>
       <c r="Q74" t="n">
         <v>193.1141809259393</v>
@@ -5931,43 +5931,43 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E75" t="n">
         <v>5</v>
       </c>
       <c r="F75" t="n">
-        <v>171.4891813486573</v>
+        <v>168.2545421044971</v>
       </c>
       <c r="G75" t="n">
-        <v>1.329282647279138</v>
+        <v>1.16053340835048</v>
       </c>
       <c r="H75" t="n">
         <v>157.2380343536269</v>
       </c>
       <c r="I75" t="n">
-        <v>199.1471890121935</v>
+        <v>196.6279104486694</v>
       </c>
       <c r="J75" t="n">
-        <v>0.3086337287710494</v>
+        <v>0.3034072430596306</v>
       </c>
       <c r="K75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="L75" t="n">
-        <v>190.8035178062165</v>
+        <v>189.0211955227435</v>
       </c>
       <c r="M75" t="n">
-        <v>12.64906613744525</v>
+        <v>11.89375382888973</v>
       </c>
       <c r="N75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="O75" t="n">
-        <v>190.8792150652616</v>
+        <v>189.0211955227435</v>
       </c>
       <c r="P75" t="n">
-        <v>12.95</v>
+        <v>12.21052631578947</v>
       </c>
       <c r="Q75" t="n">
         <v>193.2892416279341</v>
@@ -6006,43 +6006,43 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E76" t="n">
         <v>4</v>
       </c>
       <c r="F76" t="n">
-        <v>175.1327941667306</v>
+        <v>175.6880157321164</v>
       </c>
       <c r="G76" t="n">
-        <v>1.882140965046261</v>
+        <v>1.531534735446058</v>
       </c>
       <c r="H76" t="n">
         <v>154.9841830576604</v>
       </c>
       <c r="I76" t="n">
-        <v>197.6103123259165</v>
+        <v>195.3413856273902</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2052184789848701</v>
+        <v>0.2057436508728052</v>
       </c>
       <c r="K76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="L76" t="n">
-        <v>191.7894736842105</v>
+        <v>189.1729323308271</v>
       </c>
       <c r="M76" t="n">
-        <v>15.31640743688422</v>
+        <v>14.08949935771264</v>
       </c>
       <c r="N76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="O76" t="n">
-        <v>191.7894736842105</v>
+        <v>189.1729323308271</v>
       </c>
       <c r="P76" t="n">
-        <v>16.375</v>
+        <v>14.71052631578947</v>
       </c>
       <c r="Q76" t="n">
         <v>192.8448970866968</v>
@@ -6081,43 +6081,43 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E77" t="n">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F77" t="n">
-        <v>54.28104028785678</v>
+        <v>46.69234462013655</v>
       </c>
       <c r="G77" t="n">
-        <v>7.915376878388163</v>
+        <v>6.788620896340505</v>
       </c>
       <c r="H77" t="n">
         <v>77.76772218573589</v>
       </c>
       <c r="I77" t="n">
-        <v>47.89131057290163</v>
+        <v>36.79734774047761</v>
       </c>
       <c r="J77" t="n">
-        <v>8.901034436271191</v>
+        <v>6.708211027185509</v>
       </c>
       <c r="K77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="L77" t="n">
-        <v>58.40706578245533</v>
+        <v>47.8895378952934</v>
       </c>
       <c r="M77" t="n">
-        <v>12.95</v>
+        <v>11.02631578947368</v>
       </c>
       <c r="N77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="O77" t="n">
-        <v>58.40706578245533</v>
+        <v>47.8895378952934</v>
       </c>
       <c r="P77" t="n">
-        <v>12.95</v>
+        <v>11.02631578947368</v>
       </c>
       <c r="Q77" t="n">
         <v>138.4032392925817</v>
@@ -6133,11 +6133,11 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>47.89131057290163</v>
+        <v>36.79734774047761</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=47.89% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=36.80% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6158,50 +6158,50 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E78" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F78" t="n">
-        <v>54.87840941086982</v>
+        <v>48.26514541284195</v>
       </c>
       <c r="G78" t="n">
-        <v>4.041673828677729</v>
+        <v>3.613344121230134</v>
       </c>
       <c r="H78" t="n">
         <v>103.5437500854655</v>
       </c>
       <c r="I78" t="n">
-        <v>51.58018674540056</v>
+        <v>51.10941098137504</v>
       </c>
       <c r="J78" t="n">
-        <v>4.367809224698335</v>
+        <v>4.074518054301315</v>
       </c>
       <c r="K78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="L78" t="n">
-        <v>147.2612966993405</v>
+        <v>132.8108105037542</v>
       </c>
       <c r="M78" t="n">
-        <v>8.459246600046754</v>
+        <v>6.46116481368479</v>
       </c>
       <c r="N78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="O78" t="n">
-        <v>50.44907786885641</v>
+        <v>47.39415663274317</v>
       </c>
       <c r="P78" t="n">
-        <v>4.171118839567049</v>
+        <v>4.42813360747103</v>
       </c>
       <c r="Q78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="T78" t="n">
-        <v>51.58018674540056</v>
+        <v>48.26514541284195</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=51.58% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=48.27% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6235,43 +6235,43 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E79" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F79" t="n">
-        <v>63.74394073718654</v>
+        <v>52.91222566319724</v>
       </c>
       <c r="G79" t="n">
-        <v>4.670608051404793</v>
+        <v>3.864661196179704</v>
       </c>
       <c r="H79" t="n">
         <v>102.5016657415887</v>
       </c>
       <c r="I79" t="n">
-        <v>45.5350977396655</v>
+        <v>36.92725458042533</v>
       </c>
       <c r="J79" t="n">
-        <v>4.106487143074899</v>
+        <v>3.302047854258936</v>
       </c>
       <c r="K79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="L79" t="n">
-        <v>62.83637639610319</v>
+        <v>53.13626166171554</v>
       </c>
       <c r="M79" t="n">
-        <v>7.5</v>
+        <v>6.657894736842105</v>
       </c>
       <c r="N79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="O79" t="n">
-        <v>62.83637639610319</v>
+        <v>53.13626166171554</v>
       </c>
       <c r="P79" t="n">
-        <v>7.5</v>
+        <v>6.657894736842105</v>
       </c>
       <c r="Q79" t="n">
         <v>148.0195847609927</v>
@@ -6287,11 +6287,11 @@
         </is>
       </c>
       <c r="T79" t="n">
-        <v>45.5350977396655</v>
+        <v>36.92725458042533</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE 2026 real=45.54% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=36.93% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6312,43 +6312,43 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E80" t="n">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="F80" t="n">
-        <v>136.2646821700044</v>
+        <v>142.0473293234183</v>
       </c>
       <c r="G80" t="n">
-        <v>23.68708579528359</v>
+        <v>24.73559830907586</v>
       </c>
       <c r="H80" t="n">
         <v>180.9937478063148</v>
       </c>
       <c r="I80" t="n">
-        <v>154.1270973615223</v>
+        <v>149.3522092224518</v>
       </c>
       <c r="J80" t="n">
-        <v>24.69003173630983</v>
+        <v>23.38961870508665</v>
       </c>
       <c r="K80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="L80" t="n">
-        <v>130.7177767334969</v>
+        <v>124.7515030309418</v>
       </c>
       <c r="M80" t="n">
-        <v>23.11005077362061</v>
+        <v>18.48013024581106</v>
       </c>
       <c r="N80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="O80" t="n">
-        <v>148.8342581507796</v>
+        <v>150.2710602240091</v>
       </c>
       <c r="P80" t="n">
-        <v>24.74206305431543</v>
+        <v>25.62322426770046</v>
       </c>
       <c r="Q80" t="n">
         <v>172.7461511452186</v>
@@ -6364,11 +6364,11 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>136.2646821700044</v>
+        <v>142.0473293234183</v>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=136.26% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=142.05% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6389,43 +6389,43 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E81" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F81" t="n">
-        <v>129.4093328784592</v>
+        <v>127.6155198807104</v>
       </c>
       <c r="G81" t="n">
-        <v>10.66910844146288</v>
+        <v>10.89448015320569</v>
       </c>
       <c r="H81" t="n">
         <v>185.5191244575439</v>
       </c>
       <c r="I81" t="n">
-        <v>140.5285620286041</v>
+        <v>135.1025520610708</v>
       </c>
       <c r="J81" t="n">
-        <v>9.66921833172178</v>
+        <v>8.567143251050577</v>
       </c>
       <c r="K81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="L81" t="n">
-        <v>182.6334976500069</v>
+        <v>176.0140030425413</v>
       </c>
       <c r="M81" t="n">
-        <v>14.29371314048767</v>
+        <v>12.30917172682913</v>
       </c>
       <c r="N81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="O81" t="n">
-        <v>139.4963708043945</v>
+        <v>137.4824606386474</v>
       </c>
       <c r="P81" t="n">
-        <v>11.07514696474235</v>
+        <v>11.41040295945036</v>
       </c>
       <c r="Q81" t="n">
         <v>163.1536185700502</v>
@@ -6441,11 +6441,11 @@
         </is>
       </c>
       <c r="T81" t="n">
-        <v>129.4093328784592</v>
+        <v>127.6155198807104</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=129.41% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=127.62% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6466,43 +6466,43 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E82" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="F82" t="n">
-        <v>120.8167820086724</v>
+        <v>124.3198054769538</v>
       </c>
       <c r="G82" t="n">
-        <v>12.23730403092784</v>
+        <v>12.65118418611661</v>
       </c>
       <c r="H82" t="n">
         <v>186.2973802760101</v>
       </c>
       <c r="I82" t="n">
-        <v>154.006947388668</v>
+        <v>143.6520875442592</v>
       </c>
       <c r="J82" t="n">
-        <v>12.98927439700293</v>
+        <v>12.94659064734331</v>
       </c>
       <c r="K82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="L82" t="n">
-        <v>163.3315662482434</v>
+        <v>159.6233471388631</v>
       </c>
       <c r="M82" t="n">
-        <v>12.51910437941551</v>
+        <v>12.05820103068101</v>
       </c>
       <c r="N82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="O82" t="n">
-        <v>138.7428822756705</v>
+        <v>139.5299674281279</v>
       </c>
       <c r="P82" t="n">
-        <v>13.14374712248669</v>
+        <v>13.52804288888773</v>
       </c>
       <c r="Q82" t="n">
         <v>166.6060177059153</v>
@@ -6518,11 +6518,11 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>120.8167820086724</v>
+        <v>124.3198054769538</v>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=120.82% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=124.32% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6543,43 +6543,43 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E83" t="n">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F83" t="n">
-        <v>38.03298100569638</v>
+        <v>35.45935764754714</v>
       </c>
       <c r="G83" t="n">
-        <v>6.202676391359164</v>
+        <v>6.299557206056292</v>
       </c>
       <c r="H83" t="n">
         <v>88.04980557911651</v>
       </c>
       <c r="I83" t="n">
-        <v>44.45364790933983</v>
+        <v>46.42585692650886</v>
       </c>
       <c r="J83" t="n">
-        <v>8.419454332980155</v>
+        <v>8.37710047108553</v>
       </c>
       <c r="K83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="L83" t="n">
-        <v>105.9678120321614</v>
+        <v>101.142689215435</v>
       </c>
       <c r="M83" t="n">
-        <v>37.72667374384968</v>
+        <v>37.65965657247335</v>
       </c>
       <c r="N83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="O83" t="n">
-        <v>85.57892620328377</v>
+        <v>82.87727882274899</v>
       </c>
       <c r="P83" t="n">
-        <v>29.31259478594988</v>
+        <v>30.05086433793102</v>
       </c>
       <c r="Q83" t="n">
         <v>103.1343264142703</v>
@@ -6595,11 +6595,11 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>38.03298100569638</v>
+        <v>35.45935764754714</v>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=38.03% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=35.46% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6620,43 +6620,43 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E84" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F84" t="n">
-        <v>36.2355963489991</v>
+        <v>32.38454879714672</v>
       </c>
       <c r="G84" t="n">
-        <v>2.596461743108535</v>
+        <v>2.590604588219051</v>
       </c>
       <c r="H84" t="n">
         <v>100.4914466151705</v>
       </c>
       <c r="I84" t="n">
-        <v>42.95228490250207</v>
+        <v>45.96231344597865</v>
       </c>
       <c r="J84" t="n">
-        <v>3.125356274497688</v>
+        <v>3.449044160724878</v>
       </c>
       <c r="K84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="L84" t="n">
-        <v>75.40218493641794</v>
+        <v>73.35136326793538</v>
       </c>
       <c r="M84" t="n">
-        <v>8.560851826875428</v>
+        <v>8.912867338922181</v>
       </c>
       <c r="N84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="O84" t="n">
-        <v>88.57681853269659</v>
+        <v>85.36326949733061</v>
       </c>
       <c r="P84" t="n">
-        <v>13.56201420137435</v>
+        <v>13.84714075997255</v>
       </c>
       <c r="Q84" t="n">
         <v>98.74789164115032</v>
@@ -6672,11 +6672,11 @@
         </is>
       </c>
       <c r="T84" t="n">
-        <v>36.2355963489991</v>
+        <v>32.38454879714672</v>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=36.24% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=32.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6697,43 +6697,43 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F85" t="n">
-        <v>46.54094187387292</v>
+        <v>45.66073922769827</v>
       </c>
       <c r="G85" t="n">
-        <v>4.157766553206945</v>
+        <v>4.349422253201568</v>
       </c>
       <c r="H85" t="n">
         <v>109.9471447641292</v>
       </c>
       <c r="I85" t="n">
-        <v>57.98519225800165</v>
+        <v>57.43339810358206</v>
       </c>
       <c r="J85" t="n">
-        <v>4.861116293420031</v>
+        <v>5.058339965311367</v>
       </c>
       <c r="K85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="L85" t="n">
-        <v>101.326550308803</v>
+        <v>96.11293749099474</v>
       </c>
       <c r="M85" t="n">
-        <v>18.39708375199444</v>
+        <v>18.23089364942659</v>
       </c>
       <c r="N85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="O85" t="n">
-        <v>91.70139914931504</v>
+        <v>90.05124321306785</v>
       </c>
       <c r="P85" t="n">
-        <v>17.45590217879477</v>
+        <v>17.93448716547004</v>
       </c>
       <c r="Q85" t="n">
         <v>106.9882513320439</v>
@@ -6749,11 +6749,11 @@
         </is>
       </c>
       <c r="T85" t="n">
-        <v>46.54094187387292</v>
+        <v>45.66073922769827</v>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=46.54% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=45.66% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6774,43 +6774,43 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E86" t="n">
         <v>33</v>
       </c>
       <c r="F86" t="n">
-        <v>109.0024078053168</v>
+        <v>107.0051144969647</v>
       </c>
       <c r="G86" t="n">
-        <v>3.060463463015666</v>
+        <v>2.888610677610906</v>
       </c>
       <c r="H86" t="n">
         <v>160.3842205944857</v>
       </c>
       <c r="I86" t="n">
-        <v>114.79439618021</v>
+        <v>118.5283012694314</v>
       </c>
       <c r="J86" t="n">
-        <v>1.895000924030766</v>
+        <v>1.511365094958628</v>
       </c>
       <c r="K86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="L86" t="n">
-        <v>145.3475644944138</v>
+        <v>131.5868440407407</v>
       </c>
       <c r="M86" t="n">
-        <v>2.718259353935719</v>
+        <v>2.046955790958906</v>
       </c>
       <c r="N86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="O86" t="n">
-        <v>170.1936995709836</v>
+        <v>170.6286794329426</v>
       </c>
       <c r="P86" t="n">
-        <v>22.275</v>
+        <v>21.39473684210526</v>
       </c>
       <c r="Q86" t="n">
         <v>188.4995472315167</v>
@@ -6826,11 +6826,11 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>109.0024078053168</v>
+        <v>107.0051144969647</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=109.00% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=107.01% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6851,43 +6851,43 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E87" t="n">
         <v>17</v>
       </c>
       <c r="F87" t="n">
-        <v>117.898962241331</v>
+        <v>113.1870478943641</v>
       </c>
       <c r="G87" t="n">
-        <v>1.239381168964092</v>
+        <v>1.165451077594584</v>
       </c>
       <c r="H87" t="n">
         <v>171.410316416684</v>
       </c>
       <c r="I87" t="n">
-        <v>163.3553613245868</v>
+        <v>143.5835389914779</v>
       </c>
       <c r="J87" t="n">
-        <v>1.234120915993784</v>
+        <v>0.9800779156337266</v>
       </c>
       <c r="K87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="L87" t="n">
-        <v>165.2788742697465</v>
+        <v>162.2316347756723</v>
       </c>
       <c r="M87" t="n">
-        <v>9.5</v>
+        <v>9.131578947368421</v>
       </c>
       <c r="N87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="O87" t="n">
-        <v>165.2788742697465</v>
+        <v>162.2316347756723</v>
       </c>
       <c r="P87" t="n">
-        <v>9.5</v>
+        <v>9.131578947368421</v>
       </c>
       <c r="Q87" t="n">
         <v>191.241827101395</v>
@@ -6903,11 +6903,11 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>117.898962241331</v>
+        <v>113.1870478943641</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=117.90% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=113.19% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6928,43 +6928,43 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
         <v>15</v>
       </c>
       <c r="F88" t="n">
-        <v>133.4688897628219</v>
+        <v>131.8021709096804</v>
       </c>
       <c r="G88" t="n">
-        <v>1.817614819626053</v>
+        <v>1.686097704619301</v>
       </c>
       <c r="H88" t="n">
         <v>169.0038464611843</v>
       </c>
       <c r="I88" t="n">
-        <v>171.5496435106509</v>
+        <v>173.8296114884862</v>
       </c>
       <c r="J88" t="n">
-        <v>1.096284929625645</v>
+        <v>1.003422029570916</v>
       </c>
       <c r="K88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="L88" t="n">
-        <v>196.6914558761517</v>
+        <v>172.6013331685172</v>
       </c>
       <c r="M88" t="n">
-        <v>2.517072343826294</v>
+        <v>1.919249045221429</v>
       </c>
       <c r="N88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="O88" t="n">
-        <v>180.1433048370754</v>
+        <v>180.73123264338</v>
       </c>
       <c r="P88" t="n">
-        <v>13.275</v>
+        <v>12.78947368421053</v>
       </c>
       <c r="Q88" t="n">
         <v>190.1751472740156</v>
@@ -6980,11 +6980,11 @@
         </is>
       </c>
       <c r="T88" t="n">
-        <v>133.4688897628219</v>
+        <v>131.8021709096804</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=133.47% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=131.80% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7005,7 +7005,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -7014,7 +7014,7 @@
         <v>200</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1029068012743253</v>
+        <v>0.1027285104502795</v>
       </c>
       <c r="H89" t="n">
         <v>200</v>
@@ -7023,7 +7023,7 @@
         <v>200</v>
       </c>
       <c r="J89" t="n">
-        <v>0.007655356111661534</v>
+        <v>0.007380532391221194</v>
       </c>
       <c r="K89" t="n">
         <v>200</v>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -7085,7 +7085,7 @@
         <v>200</v>
       </c>
       <c r="G90" t="n">
-        <v>0.09043378427001174</v>
+        <v>0.09027970940358052</v>
       </c>
       <c r="H90" t="n">
         <v>200</v>
@@ -7094,7 +7094,7 @@
         <v>200</v>
       </c>
       <c r="J90" t="n">
-        <v>0.003652499672644729</v>
+        <v>0.003657128813195968</v>
       </c>
       <c r="K90" t="n">
         <v>200</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -7156,7 +7156,7 @@
         <v>200</v>
       </c>
       <c r="G91" t="n">
-        <v>0.09289234583735555</v>
+        <v>0.09273934624974439</v>
       </c>
       <c r="H91" t="n">
         <v>200</v>
@@ -7165,7 +7165,7 @@
         <v>200</v>
       </c>
       <c r="J91" t="n">
-        <v>0.01408613662291505</v>
+        <v>0.01455603600441123</v>
       </c>
       <c r="K91" t="n">
         <v>200</v>
@@ -7218,43 +7218,43 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F92" t="n">
-        <v>58.00668116259605</v>
+        <v>52.49086450360068</v>
       </c>
       <c r="G92" t="n">
-        <v>7.828910977530427</v>
+        <v>7.632350894424847</v>
       </c>
       <c r="H92" t="n">
         <v>49.15109590531281</v>
       </c>
       <c r="I92" t="n">
-        <v>66.16055645135989</v>
+        <v>53.35077005079972</v>
       </c>
       <c r="J92" t="n">
-        <v>8.560172805104227</v>
+        <v>7.637694966892938</v>
       </c>
       <c r="K92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="L92" t="n">
-        <v>153.1421348380639</v>
+        <v>149.619457716756</v>
       </c>
       <c r="M92" t="n">
-        <v>90.83391578324411</v>
+        <v>92.43043766657274</v>
       </c>
       <c r="N92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="O92" t="n">
-        <v>110.1308965565349</v>
+        <v>108.5913919239667</v>
       </c>
       <c r="P92" t="n">
-        <v>39.37327812264689</v>
+        <v>39.96055378451477</v>
       </c>
       <c r="Q92" t="n">
         <v>92.01416331532587</v>
@@ -7270,11 +7270,11 @@
         </is>
       </c>
       <c r="T92" t="n">
-        <v>58.00668116259605</v>
+        <v>52.49086450360068</v>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=58.01% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=52.49% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7295,43 +7295,43 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F93" t="n">
-        <v>55.33481612761542</v>
+        <v>49.38424923276131</v>
       </c>
       <c r="G93" t="n">
-        <v>3.668000397334629</v>
+        <v>3.469072830113385</v>
       </c>
       <c r="H93" t="n">
         <v>60.93105560683724</v>
       </c>
       <c r="I93" t="n">
-        <v>71.82251129006953</v>
+        <v>60.1026346278737</v>
       </c>
       <c r="J93" t="n">
-        <v>5.433656621522725</v>
+        <v>4.939438714442002</v>
       </c>
       <c r="K93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="L93" t="n">
-        <v>150.8428584017242</v>
+        <v>146.0245283061174</v>
       </c>
       <c r="M93" t="n">
-        <v>40.53434849539032</v>
+        <v>41.69405104777928</v>
       </c>
       <c r="N93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="O93" t="n">
-        <v>118.5592043579543</v>
+        <v>114.1212768688539</v>
       </c>
       <c r="P93" t="n">
-        <v>20.73408918824621</v>
+        <v>20.99274142876214</v>
       </c>
       <c r="Q93" t="n">
         <v>96.01849856237216</v>
@@ -7347,11 +7347,11 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>55.33481612761542</v>
+        <v>49.38424923276131</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=55.33% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=49.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7372,50 +7372,50 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E94" t="n">
         <v>153</v>
       </c>
       <c r="F94" t="n">
-        <v>64.52569325776591</v>
+        <v>57.56739705044136</v>
       </c>
       <c r="G94" t="n">
-        <v>4.496225705286984</v>
+        <v>4.31128253527494</v>
       </c>
       <c r="H94" t="n">
         <v>64.07712599234655</v>
       </c>
       <c r="I94" t="n">
-        <v>67.13939243552699</v>
+        <v>52.98096764410323</v>
       </c>
       <c r="J94" t="n">
-        <v>4.534242139516957</v>
+        <v>3.790476368256205</v>
       </c>
       <c r="K94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="L94" t="n">
-        <v>152.1672609092015</v>
+        <v>149.6998267702992</v>
       </c>
       <c r="M94" t="n">
-        <v>45.4697162962926</v>
+        <v>45.6523329434659</v>
       </c>
       <c r="N94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="O94" t="n">
-        <v>114.6763908393289</v>
+        <v>112.5398372966676</v>
       </c>
       <c r="P94" t="n">
-        <v>22.27536611716415</v>
+        <v>22.36505768071156</v>
       </c>
       <c r="Q94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -7424,11 +7424,11 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>64.52569325776591</v>
+        <v>52.98096764410323</v>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=64.53% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE 2026 real=52.98% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7449,25 +7449,25 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E95" t="n">
         <v>10</v>
       </c>
       <c r="F95" t="n">
-        <v>150.1933170450354</v>
+        <v>147.5935778029153</v>
       </c>
       <c r="G95" t="n">
-        <v>0.6826243516899143</v>
+        <v>0.662334516860426</v>
       </c>
       <c r="H95" t="n">
         <v>152.3875262412586</v>
       </c>
       <c r="I95" t="n">
-        <v>199.4590255884752</v>
+        <v>198.9660683083715</v>
       </c>
       <c r="J95" t="n">
-        <v>0.501676095021948</v>
+        <v>0.5239013555859853</v>
       </c>
       <c r="K95" t="n">
         <v>128.1095321097334</v>
@@ -7476,16 +7476,16 @@
         <v>200</v>
       </c>
       <c r="M95" t="n">
-        <v>0.5</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="N95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="O95" t="n">
-        <v>171.1924021274927</v>
+        <v>168.4130957965686</v>
       </c>
       <c r="P95" t="n">
-        <v>3.597150788765764</v>
+        <v>3.712348962717789</v>
       </c>
       <c r="Q95" t="n">
         <v>118.2821915164861</v>
@@ -7501,11 +7501,11 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>150.1933170450354</v>
+        <v>147.5935778029153</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE 2026 real=150.19% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE 2026 real=147.59% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7526,43 +7526,43 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E96" t="n">
         <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>183.380146231257</v>
+        <v>181.6843142825061</v>
       </c>
       <c r="G96" t="n">
-        <v>0.32651713808835</v>
+        <v>0.3291270790645512</v>
       </c>
       <c r="H96" t="n">
         <v>158.9896824444987</v>
       </c>
       <c r="I96" t="n">
-        <v>199.4098775195</v>
+        <v>199.2150951603351</v>
       </c>
       <c r="J96" t="n">
-        <v>0.150369989321378</v>
+        <v>0.1584986195278356</v>
       </c>
       <c r="K96" t="n">
         <v>189.1617640516506</v>
       </c>
       <c r="L96" t="n">
-        <v>136.8432713806183</v>
+        <v>200</v>
       </c>
       <c r="M96" t="n">
-        <v>0.5742715794367811</v>
+        <v>0.8016990005837641</v>
       </c>
       <c r="N96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="O96" t="n">
-        <v>187.8588218129753</v>
+        <v>186.7228903978403</v>
       </c>
       <c r="P96" t="n">
-        <v>3.531501344803482</v>
+        <v>3.622631913077714</v>
       </c>
       <c r="Q96" t="n">
         <v>124.4459476108536</v>
@@ -7601,43 +7601,43 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
         <v>7</v>
       </c>
       <c r="F97" t="n">
-        <v>170.552227801555</v>
+        <v>166.6950640152984</v>
       </c>
       <c r="G97" t="n">
-        <v>0.4125145317110643</v>
+        <v>0.3995569831044574</v>
       </c>
       <c r="H97" t="n">
         <v>157.2976315063829</v>
       </c>
       <c r="I97" t="n">
-        <v>199.4332611980511</v>
+        <v>199.3927310976356</v>
       </c>
       <c r="J97" t="n">
-        <v>0.3530453433151393</v>
+        <v>0.3716897725749284</v>
       </c>
       <c r="K97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="L97" t="n">
-        <v>178.0949782047029</v>
+        <v>162.4241916567453</v>
       </c>
       <c r="M97" t="n">
-        <v>1.925684887170792</v>
+        <v>1.583574840897008</v>
       </c>
       <c r="N97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="O97" t="n">
-        <v>169.221498560424</v>
+        <v>168.6261496195838</v>
       </c>
       <c r="P97" t="n">
-        <v>2.226707747619145</v>
+        <v>2.339267854845288</v>
       </c>
       <c r="Q97" t="n">
         <v>128.4785456608675</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
         <v>200</v>
       </c>
       <c r="G98" t="n">
-        <v>0.07260366378937935</v>
+        <v>0.07575033617870201</v>
       </c>
       <c r="H98" t="n">
         <v>198.585723184526</v>
@@ -7694,16 +7694,14 @@
         <v>200</v>
       </c>
       <c r="J98" t="n">
-        <v>0.0005319163465056801</v>
+        <v>0.0005744433579079894</v>
       </c>
       <c r="K98" t="n">
         <v>199.9898962083731</v>
       </c>
-      <c r="L98" t="n">
-        <v>200</v>
-      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
         <v>199.2030987655621</v>
@@ -7749,7 +7747,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -7758,7 +7756,7 @@
         <v>200</v>
       </c>
       <c r="G99" t="n">
-        <v>0.04183094421640433</v>
+        <v>0.04403257285937298</v>
       </c>
       <c r="H99" t="n">
         <v>198.7380283178126</v>
@@ -7767,16 +7765,14 @@
         <v>200</v>
       </c>
       <c r="J99" t="n">
-        <v>0.001558341390311445</v>
+        <v>0.001595394861881958</v>
       </c>
       <c r="K99" t="n">
         <v>199.9983019911245</v>
       </c>
-      <c r="L99" t="n">
-        <v>200</v>
-      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="M99" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
         <v>198.5022493653877</v>
@@ -7822,7 +7818,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -7831,7 +7827,7 @@
         <v>200</v>
       </c>
       <c r="G100" t="n">
-        <v>0.05751753432389537</v>
+        <v>0.0598529225883256</v>
       </c>
       <c r="H100" t="n">
         <v>200</v>
@@ -7840,7 +7836,7 @@
         <v>200</v>
       </c>
       <c r="J100" t="n">
-        <v>0.002328931288167165</v>
+        <v>0.00240448959164621</v>
       </c>
       <c r="K100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,90 +446,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>n_semanas_real_2026</t>
+          <t>anio_eval</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>total_real_2026</t>
+          <t>n_semanas_real</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>smape_2026_prophet</t>
+          <t>total_real</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>mae_2026_prophet</t>
+          <t>smape_real_prophet</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>mae_real_prophet</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>cv_smape_prophet</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>smape_2026_deepar</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>mae_2026_deepar</t>
+          <t>smape_real_deepar</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>mae_real_deepar</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>cv_smape_deepar</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>smape_2026_ensemble</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>mae_2026_ensemble</t>
+          <t>smape_real_ensemble</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mae_real_ensemble</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>cv_smape_ensemble</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>smape_2026_stacking</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mae_2026_stacking</t>
+          <t>smape_real_stacking</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>mae_real_stacking</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>cv_smape_stacking</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>motor_productivo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>criterio_seleccion</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>smape_ganador</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>justificacion</t>
         </is>
@@ -552,59 +557,62 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>200</v>
-      </c>
       <c r="G2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.01143971376208275</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>185.8333489727328</v>
       </c>
-      <c r="I2" t="n">
-        <v>200</v>
-      </c>
       <c r="J2" t="n">
+        <v>200</v>
+      </c>
+      <c r="K2" t="n">
         <v>0.008980106835938563</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>200</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
+        <v>200</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.5526315789473685</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>197.8088169752323</v>
       </c>
-      <c r="O2" t="n">
-        <v>200</v>
-      </c>
       <c r="P2" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.5526315789473685</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>199.5572761277739</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -625,59 +633,62 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>200</v>
-      </c>
       <c r="G3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H3" t="n">
         <v>0.009067953039092178</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>157.2321783542833</v>
       </c>
-      <c r="I3" t="n">
-        <v>200</v>
-      </c>
       <c r="J3" t="n">
+        <v>200</v>
+      </c>
+      <c r="K3" t="n">
         <v>0.01223255052547364</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>200</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
+        <v>200</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.1578947368421053</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>197.8854209931308</v>
       </c>
-      <c r="O3" t="n">
-        <v>200</v>
-      </c>
       <c r="P3" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.1578947368421053</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>199.636475467609</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -698,59 +709,62 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>200</v>
-      </c>
       <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.01410237981501257</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>158.5580779411727</v>
       </c>
-      <c r="I4" t="n">
-        <v>200</v>
-      </c>
       <c r="J4" t="n">
+        <v>200</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.07902433993532074</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>200</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
+        <v>200</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.3947368421052632</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>197.7265973322816</v>
       </c>
-      <c r="O4" t="n">
-        <v>200</v>
-      </c>
       <c r="P4" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.3947368421052632</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>199.5859359679221</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -771,59 +785,62 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>199.0125831330724</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>0.1083988208702625</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>175.1088701866436</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>199.3234195740198</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.1167777980905749</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
-        <v>200</v>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
+        <v>200</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>187.2707284786031</v>
       </c>
-      <c r="O5" t="n">
-        <v>200</v>
-      </c>
       <c r="P5" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>193.7972259177366</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -844,59 +861,62 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>199.5227768499908</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.06224017002961615</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>191.646475967384</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>199.9904719366027</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.05344732191053987</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>200</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
+        <v>200</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>192.53013744135</v>
       </c>
-      <c r="O6" t="n">
-        <v>200</v>
-      </c>
       <c r="P6" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>193.2139428195562</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -917,59 +937,62 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>199.0827646374914</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.07542585392837421</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>186.9197740801393</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>199.9920711524921</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.05301641570428982</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
-        <v>200</v>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>185.3187572725189</v>
       </c>
-      <c r="O7" t="n">
-        <v>200</v>
-      </c>
       <c r="P7" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>190.8625800946274</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -990,61 +1013,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F8" t="n">
         <v>142</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>101.1620929265983</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5.212131266542356</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>154.5040916050135</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>49.448315629151</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>3.415782015598385</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>95.80329746013628</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>15.18421052631579</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>165.4966466258163</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>95.80329746013628</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>15.18421052631579</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>172.894287988784</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
         <v>49.448315629151</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=49.45% sobre 19 sem</t>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=49.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1065,61 +1091,64 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F9" t="n">
         <v>62</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>96.50000967408079</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2.364058607609518</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>164.086229256472</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>76.1592104766909</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>3.688325335653582</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>111.3394980759131</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>7.631578947368421</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>169.8771678897395</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>111.3394980759131</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>7.631578947368421</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>176.8647517474977</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
         <v>76.1592104766909</v>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=76.16% sobre 19 sem</t>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=76.16% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1140,61 +1169,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
         <v>75</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>94.84727283752737</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>2.632141656550983</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>164.4874496413386</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>42.29469737291846</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>1.605336268698746</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>95.95074714452349</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>8.342105263157896</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>162.692005533007</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>95.95074714452349</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>8.342105263157896</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>168.5443712458804</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T10" t="n">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
         <v>42.29469737291846</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=42.29% sobre 19 sem</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=42.29% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1215,61 +1247,64 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E11" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" t="n">
         <v>11</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>177.1662152513658</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>0.5816049116984011</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>123.2554563734294</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>198.0872324051026</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.5883275269435004</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>192.4219018577286</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>29.69221398008126</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>192.5936095855003</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>156.945040560381</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>1.094459499402622</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>177.781032308345</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
         <v>177.1662152513658</v>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=177.17% sobre 19 sem</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=177.17% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1290,59 +1325,62 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>191.8552562166053</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.3754643963600293</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>147.3485671696691</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>199.5587784261111</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.3711322500993692</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>191.5362391585139</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>13.60373315610809</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>191.4723960783834</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>190.3614367008003</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>12.74459711503017</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>189.6908701459495</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE 2026</t>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1363,59 +1401,62 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E13" t="n">
+        <v>19</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>195.3735385790647</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.2165418703011477</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>157.1522264328246</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>199.8393822352099</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.2121195042665527</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>194.1951423424674</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>15.91266483478217</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>193.9340304002594</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>191.6897112957606</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>6.691078398696177</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>188.2053733911598</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE 2026</t>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1436,61 +1477,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E14" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" t="n">
         <v>62</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>70.98011798172448</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2.050209983850287</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>66.61025297793201</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>84.9403327767854</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>2.624469817249901</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>168.2605793498451</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>33.4179335827928</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>128.1619574474296</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>180.3554903048052</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>59.6578947368421</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>186.0423288913966</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T14" t="n">
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>70.98011798172448</v>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=70.98% sobre 19 sem</t>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=70.98% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1511,61 +1555,64 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E15" t="n">
+        <v>19</v>
+      </c>
+      <c r="F15" t="n">
         <v>32</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>65.87044566451193</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>0.897248034177942</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>82.6747998505866</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>90.82996398527685</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>1.202745696995517</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>172.9250609621144</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>22.15212661391847</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>129.025548034421</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>176.3509089864839</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>28.47368421052632</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>186.4460938550808</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U15" t="n">
         <v>65.87044566451193</v>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=65.87% sobre 19 sem</t>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=65.87% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1586,61 +1633,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E16" t="n">
+        <v>19</v>
+      </c>
+      <c r="F16" t="n">
         <v>30</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>122.3179070028762</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>1.567952396243824</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>90.20708978859948</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>142.1698014999685</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>1.461545414911759</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>177.5562163584148</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>23.00017792905756</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>142.9387914444607</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>182.3405142567343</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>31.26315789473684</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>186.1307414343702</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U16" t="n">
         <v>122.3179070028762</v>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=122.32% sobre 19 sem</t>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=122.32% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1661,59 +1711,62 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E17" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>198.7352626872857</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.1117349335808297</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>194.5446671655584</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>199.9347630529597</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>0.05500281057855451</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
-        <v>200</v>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
+        <v>200</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>196.7571923388938</v>
       </c>
-      <c r="O17" t="n">
-        <v>200</v>
-      </c>
       <c r="P17" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>197.0125798901019</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1734,55 +1787,58 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E18" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" t="n">
         <v>0</v>
       </c>
-      <c r="F18" t="n">
-        <v>200</v>
-      </c>
       <c r="G18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.02565291991697691</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>199.6410247115898</v>
       </c>
-      <c r="I18" t="n">
-        <v>200</v>
-      </c>
       <c r="J18" t="n">
+        <v>200</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.000582446063573821</v>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>196.9959839919002</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>196.686324272832</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1803,59 +1859,62 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E19" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" t="n">
         <v>1</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>199.0372771487083</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>0.09944267109328039</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>196.278530387405</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>199.9010828640821</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>0.05750655344769912</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
-        <v>200</v>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
+        <v>200</v>
+      </c>
+      <c r="N19" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>196.7189002085085</v>
       </c>
-      <c r="O19" t="n">
-        <v>200</v>
-      </c>
       <c r="P19" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0.131578947368421</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>196.7488584326798</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1876,55 +1935,58 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E20" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="n">
-        <v>200</v>
-      </c>
       <c r="G20" t="n">
+        <v>200</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.07047412404518942</v>
       </c>
-      <c r="H20" t="n">
-        <v>200</v>
-      </c>
       <c r="I20" t="n">
         <v>200</v>
       </c>
       <c r="J20" t="n">
+        <v>200</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.001262668041030563</v>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>200</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
+      <c r="O20" t="n">
+        <v>200</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>200</v>
-      </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="n">
+        <v>200</v>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1945,55 +2007,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="n">
-        <v>200</v>
-      </c>
       <c r="G21" t="n">
+        <v>200</v>
+      </c>
+      <c r="H21" t="n">
         <v>0.05672395709071366</v>
       </c>
-      <c r="H21" t="n">
-        <v>200</v>
-      </c>
       <c r="I21" t="n">
         <v>200</v>
       </c>
       <c r="J21" t="n">
+        <v>200</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.006155900490740383</v>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
-      <c r="N21" t="n">
-        <v>200</v>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+      <c r="O21" t="n">
+        <v>200</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2014,55 +2079,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
-        <v>200</v>
-      </c>
       <c r="G22" t="n">
+        <v>200</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.06350447684539688</v>
       </c>
-      <c r="H22" t="n">
-        <v>200</v>
-      </c>
       <c r="I22" t="n">
         <v>200</v>
       </c>
       <c r="J22" t="n">
+        <v>200</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.0004386668824289527</v>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>200</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
+      <c r="O22" t="n">
+        <v>200</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>200</v>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" t="n">
+        <v>200</v>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2083,59 +2151,62 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E23" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" t="n">
         <v>2</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>179.1739130190571</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>0.1271859159213902</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>149.2565324185079</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>199.2048177791976</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>0.118578293258006</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>192.8571428571429</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>1.105263157894737</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>169.6992056798271</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>192.8571428571429</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>1.105263157894737</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>186.3774873978808</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2156,59 +2227,62 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E24" t="n">
+        <v>19</v>
+      </c>
+      <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>182.221104530061</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>0.06574743966708289</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>156.2502876793226</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>198.7364217540033</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>0.07131395163685894</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>138.2549574812263</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0.1431885455784045</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>159.6122718089852</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>175</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>185.3144083651474</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2229,59 +2303,62 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E25" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="F25" t="n">
-        <v>200</v>
-      </c>
       <c r="G25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.0735937728171784</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>155.3955473497874</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>199.9219951890681</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>0.05804041841012747</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
-        <v>200</v>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
+        <v>200</v>
+      </c>
+      <c r="N25" t="n">
         <v>0.6052631578947368</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>177.0659734750362</v>
       </c>
-      <c r="O25" t="n">
-        <v>200</v>
-      </c>
       <c r="P25" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0.6052631578947368</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>183.340259481936</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2302,59 +2379,62 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E26" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>200</v>
-      </c>
       <c r="G26" t="n">
+        <v>200</v>
+      </c>
+      <c r="H26" t="n">
         <v>0.02780046601968817</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>97.19414576199205</v>
       </c>
-      <c r="I26" t="n">
-        <v>200</v>
-      </c>
       <c r="J26" t="n">
+        <v>200</v>
+      </c>
+      <c r="K26" t="n">
         <v>0.09487158631641658</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
-        <v>200</v>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
+        <v>200</v>
+      </c>
+      <c r="N26" t="n">
         <v>66.31578947368421</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>198.3074653131699</v>
       </c>
-      <c r="O26" t="n">
-        <v>200</v>
-      </c>
       <c r="P26" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q26" t="n">
         <v>66.31578947368421</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>199.6509594119097</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2375,59 +2455,62 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E27" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" t="n">
-        <v>200</v>
-      </c>
       <c r="G27" t="n">
+        <v>200</v>
+      </c>
+      <c r="H27" t="n">
         <v>0.01946588280507898</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>129.0985231723771</v>
       </c>
-      <c r="I27" t="n">
-        <v>200</v>
-      </c>
       <c r="J27" t="n">
+        <v>200</v>
+      </c>
+      <c r="K27" t="n">
         <v>0.01217744203193361</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
-        <v>200</v>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
+        <v>200</v>
+      </c>
+      <c r="N27" t="n">
         <v>32.76315789473684</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>198.6114841856233</v>
       </c>
-      <c r="O27" t="n">
-        <v>200</v>
-      </c>
       <c r="P27" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q27" t="n">
         <v>32.76315789473684</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>199.779644487174</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2448,59 +2531,62 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E28" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
-        <v>200</v>
-      </c>
       <c r="G28" t="n">
+        <v>200</v>
+      </c>
+      <c r="H28" t="n">
         <v>0.01964014595132009</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>127.1718885128103</v>
       </c>
-      <c r="I28" t="n">
-        <v>200</v>
-      </c>
       <c r="J28" t="n">
+        <v>200</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.004357350598142374</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
-        <v>200</v>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
+        <v>200</v>
+      </c>
+      <c r="N28" t="n">
         <v>33.55263157894737</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>197.4940180993655</v>
       </c>
-      <c r="O28" t="n">
-        <v>200</v>
-      </c>
       <c r="P28" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q28" t="n">
         <v>33.55263157894737</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>199.5411797194807</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2521,59 +2607,62 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E29" t="n">
+        <v>19</v>
+      </c>
+      <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
-        <v>200</v>
-      </c>
       <c r="G29" t="n">
+        <v>200</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.09615446603845537</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>191.5075017030775</v>
       </c>
-      <c r="I29" t="n">
-        <v>200</v>
-      </c>
       <c r="J29" t="n">
+        <v>200</v>
+      </c>
+      <c r="K29" t="n">
         <v>0.02400026013487088</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
-        <v>200</v>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
+        <v>200</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.4736842105263158</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>198.5277121400952</v>
       </c>
-      <c r="O29" t="n">
-        <v>200</v>
-      </c>
       <c r="P29" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0.4736842105263158</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>199.9388941772115</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2594,59 +2683,62 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E30" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" t="n">
-        <v>200</v>
-      </c>
       <c r="G30" t="n">
+        <v>200</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.08151387564442503</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>196.0386411854094</v>
       </c>
-      <c r="I30" t="n">
-        <v>200</v>
-      </c>
       <c r="J30" t="n">
+        <v>200</v>
+      </c>
+      <c r="K30" t="n">
         <v>0.005648859496855605</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
-        <v>200</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
+        <v>200</v>
+      </c>
+      <c r="N30" t="n">
         <v>0.3157894736842105</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>198.9477887234591</v>
       </c>
-      <c r="O30" t="n">
-        <v>200</v>
-      </c>
       <c r="P30" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.3157894736842105</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>199.7754683359127</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2667,59 +2759,62 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E31" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="n">
-        <v>200</v>
-      </c>
       <c r="G31" t="n">
+        <v>200</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.09432961679395827</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>194.2466814459454</v>
       </c>
-      <c r="I31" t="n">
-        <v>200</v>
-      </c>
       <c r="J31" t="n">
+        <v>200</v>
+      </c>
+      <c r="K31" t="n">
         <v>0.006504246045091579</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
-        <v>200</v>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
+        <v>200</v>
+      </c>
+      <c r="N31" t="n">
         <v>0.1578947368421053</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>199.0633013569061</v>
       </c>
-      <c r="O31" t="n">
-        <v>200</v>
-      </c>
       <c r="P31" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0.1578947368421053</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>199.9196066031173</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2740,59 +2835,62 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E32" t="n">
+        <v>19</v>
+      </c>
+      <c r="F32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>167.192582466706</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>0.3731776944879054</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>164.6748490827784</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>187.7116605365616</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>0.35590860162829</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>152.3809523809524</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2.684210526315789</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>170.2678863343212</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>152.3809523809524</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>2.684210526315789</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>195.3761640213164</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE 2026</t>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2813,59 +2911,62 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E33" t="n">
+        <v>19</v>
+      </c>
+      <c r="F33" t="n">
         <v>1</v>
       </c>
-      <c r="F33" t="n">
-        <v>200</v>
-      </c>
       <c r="G33" t="n">
+        <v>200</v>
+      </c>
+      <c r="H33" t="n">
         <v>0.156967795367359</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>170.4028696730483</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>197.7160600542925</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>0.1629487095041507</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>200</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
+        <v>200</v>
+      </c>
+      <c r="N33" t="n">
         <v>1.789473684210526</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>180.7526372107734</v>
       </c>
-      <c r="O33" t="n">
-        <v>200</v>
-      </c>
       <c r="P33" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1.789473684210526</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>196.5601753860276</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2886,59 +2987,62 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E34" t="n">
+        <v>19</v>
+      </c>
+      <c r="F34" t="n">
         <v>6</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>175.6265418068303</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>0.3116447449667569</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>169.6571057340244</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>172.2289143480554</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>0.4078312226593602</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>163.9888682745826</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>1.421052631578947</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>184.4689912561869</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>163.9888682745826</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
         <v>1.421052631578947</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>195.2398047728465</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 6 casos), menor MAE 2026</t>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2959,61 +3063,64 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E35" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" t="n">
         <v>15</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>105.0282170767762</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>0.6403055072847207</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>48.55849570822402</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>128.6317087128079</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>0.8248307660368517</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>190.1370507886782</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>30.60377691036805</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>189.0070522024178</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>198.0246068743259</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>177.049413209731</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>185.853149170162</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T35" t="n">
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
         <v>105.0282170767762</v>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=105.03% sobre 19 sem</t>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=105.03% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3034,59 +3141,62 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E36" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" t="n">
         <v>6</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>161.9953762443956</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>0.4122286060260453</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>58.86670393327421</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>171.3518767659004</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>0.649354005833872</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>187.6511691920828</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>9.022437799031088</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>185.6171222178218</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>198.7712512880413</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>86.37118751369708</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>187.2910306593169</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 6 casos), menor MAE 2026</t>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3107,59 +3217,62 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E37" t="n">
+        <v>19</v>
+      </c>
+      <c r="F37" t="n">
         <v>9</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>149.3030044507669</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>0.6340439810854436</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>60.32903496111531</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>163.1188236017408</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>0.8129319453662752</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
         <v>180.650285245381</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>9.231672364614226</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>181.1462848359585</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>197.3169566187356</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>91.948882085039</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>185.3862117422507</v>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 9 casos), menor MAE 2026</t>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3180,59 +3293,62 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E38" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" t="n">
         <v>4</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>191.9919619009012</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>0.4533242349898883</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>164.4263244057969</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>194.5679991577052</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>0.3264860329740122</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
         <v>182.488038277512</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>7.368421052631579</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>190.3086393348001</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>182.488038277512</v>
       </c>
-      <c r="P38" t="n">
+      <c r="Q38" t="n">
         <v>7.368421052631579</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>199.036270909302</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE 2026</t>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3253,59 +3369,62 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E39" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" t="n">
         <v>2</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>198.5118901369247</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>0.1737669757217708</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>170.2041702191862</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>199.3242543587107</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>0.1236912055260483</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
         <v>182.2222222222222</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>3.447368421052631</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>190.9487472471646</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>182.2222222222222</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>3.447368421052631</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>199.0467638312102</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3326,59 +3445,62 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E40" t="n">
+        <v>19</v>
+      </c>
+      <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>197.8503046852848</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>0.2175630299201529</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>165.7522199768573</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>199.6624849301809</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>0.1145922745262008</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
         <v>186.3157894736842</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>4.157894736842105</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>189.6576328974018</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>186.3157894736842</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>4.157894736842105</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>198.942356787496</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3399,61 +3521,64 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E41" t="n">
+        <v>19</v>
+      </c>
+      <c r="F41" t="n">
         <v>47</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>87.77044360060759</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>1.856873350730323</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>127.4617865350128</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>91.89362526827718</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>1.511609206255772</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="n">
         <v>183.507499093661</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>54.92105263157895</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>183.1586103963582</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>183.507499093661</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>54.92105263157895</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>198.8825072752037</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T41" t="n">
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
         <v>87.77044360060759</v>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=87.77% sobre 19 sem</t>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=87.77% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3474,61 +3599,64 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E42" t="n">
+        <v>19</v>
+      </c>
+      <c r="F42" t="n">
         <v>25</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>113.7548643964564</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>1.223731755047448</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>139.5371944473096</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>155.8038714031126</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>1.261630135771666</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="n">
         <v>181.2887708376975</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>24.97368421052632</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>178.6003071053324</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>181.2887708376975</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>24.97368421052632</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>198.6803521667581</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T42" t="n">
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
         <v>113.7548643964564</v>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=113.75% sobre 19 sem</t>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=113.75% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3549,61 +3677,64 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E43" t="n">
+        <v>19</v>
+      </c>
+      <c r="F43" t="n">
         <v>22</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>91.31975786598234</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>0.9782084518115962</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>137.8269504556986</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>129.0846217162649</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>0.8697344172166692</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="n">
         <v>186.9457477180321</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>31.68421052631579</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>183.3878591635464</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>186.9457477180321</v>
       </c>
-      <c r="P43" t="n">
+      <c r="Q43" t="n">
         <v>31.68421052631579</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>198.9631246433146</v>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T43" t="n">
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
         <v>91.31975786598234</v>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=91.32% sobre 19 sem</t>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=91.32% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3624,61 +3755,64 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E44" t="n">
+        <v>19</v>
+      </c>
+      <c r="F44" t="n">
         <v>44</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>101.541216978027</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>3.270011438578409</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>101.902133963665</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>113.9440981841071</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>1.94968755914931</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="n">
         <v>185.0623623920618</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>69.28947368421052</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>175.3243009167544</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>185.0623623920618</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>69.28947368421052</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>196.0447922196767</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T44" t="n">
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
         <v>101.541216978027</v>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=101.54% sobre 19 sem</t>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=101.54% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3699,61 +3833,64 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E45" t="n">
+        <v>19</v>
+      </c>
+      <c r="F45" t="n">
         <v>27</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>116.1460451702141</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>2.564017877299051</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>133.2410714461222</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>138.7678816808106</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>1.468288778039868</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="n">
         <v>181.9877754532652</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>33.71052631578947</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>177.4357058560748</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>181.9877754532652</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>33.71052631578947</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>195.8311934408034</v>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T45" t="n">
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
         <v>116.1460451702141</v>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=116.15% sobre 19 sem</t>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=116.15% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3774,61 +3911,64 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E46" t="n">
+        <v>19</v>
+      </c>
+      <c r="F46" t="n">
         <v>17</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>140.3897249540533</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>2.53501087439491</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>129.1401202444324</v>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>154.2493653257513</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>1.085230101094652</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="n">
         <v>187.2242110784918</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>35.57894736842105</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>173.6962919474645</v>
       </c>
-      <c r="O46" t="n">
+      <c r="P46" t="n">
         <v>187.2242110784918</v>
       </c>
-      <c r="P46" t="n">
+      <c r="Q46" t="n">
         <v>35.57894736842105</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="R46" t="n">
         <v>196.1388328305384</v>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T46" t="n">
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
         <v>140.3897249540533</v>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=140.39% sobre 19 sem</t>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=140.39% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3849,59 +3989,62 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E47" t="n">
+        <v>19</v>
+      </c>
+      <c r="F47" t="n">
         <v>2</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>195.9411133670229</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>0.1636167997295013</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>52.02932925897922</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>195.6050915352664</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>0.6016355901040529</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="n">
         <v>198.4000634090768</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>25.60542579982614</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>176.1972572849119</v>
       </c>
-      <c r="O47" t="n">
+      <c r="P47" t="n">
         <v>198.8919667590028</v>
       </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
         <v>40.1578947368421</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="R47" t="n">
         <v>193.8459595711977</v>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3922,59 +4065,62 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E48" t="n">
+        <v>19</v>
+      </c>
+      <c r="F48" t="n">
         <v>2</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>197.4116289114259</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>0.1238703056407061</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>75.82494372432545</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>198.5785629334108</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>0.208424441549574</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="n">
         <v>197.2179224008849</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>12.65568768239685</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>183.163735304357</v>
       </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
         <v>197.6749026522867</v>
       </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
         <v>17.71626486213928</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="R48" t="n">
         <v>192.3368460426438</v>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3995,59 +4141,62 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E49" t="n">
+        <v>19</v>
+      </c>
+      <c r="F49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="n">
-        <v>200</v>
-      </c>
       <c r="G49" t="n">
+        <v>200</v>
+      </c>
+      <c r="H49" t="n">
         <v>0.02509264972644333</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>67.54170898302603</v>
       </c>
-      <c r="I49" t="n">
-        <v>200</v>
-      </c>
       <c r="J49" t="n">
+        <v>200</v>
+      </c>
+      <c r="K49" t="n">
         <v>0.3455497331267909</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
-        <v>200</v>
-      </c>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="n">
+        <v>200</v>
+      </c>
+      <c r="N49" t="n">
         <v>14.3506723441126</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>179.6516960231333</v>
       </c>
-      <c r="O49" t="n">
-        <v>200</v>
-      </c>
       <c r="P49" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q49" t="n">
         <v>22.34210526315789</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="R49" t="n">
         <v>193.5695579772771</v>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4068,59 +4217,62 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E50" t="n">
+        <v>19</v>
+      </c>
+      <c r="F50" t="n">
         <v>2</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>194.3911602673957</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>1.518323311321763</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>162.6912701840232</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>199.5122170374651</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>0.1641351663989946</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
-        <v>200</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
+        <v>200</v>
+      </c>
+      <c r="N50" t="n">
         <v>1.354595385099712</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>176.9763205357646</v>
       </c>
-      <c r="O50" t="n">
+      <c r="P50" t="n">
         <v>196.6315789473684</v>
       </c>
-      <c r="P50" t="n">
+      <c r="Q50" t="n">
         <v>10.46776771225995</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="R50" t="n">
         <v>160.5521309789579</v>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4141,59 +4293,62 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E51" t="n">
+        <v>19</v>
+      </c>
+      <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="F51" t="n">
+      <c r="G51" t="n">
         <v>194.7647831852421</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>0.7618632865622107</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>169.9274838481079</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>199.569745356571</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>0.1221110404092794</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="n">
         <v>195.959595959596</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>6.5</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>191.5443980495646</v>
       </c>
-      <c r="O51" t="n">
+      <c r="P51" t="n">
         <v>195.959595959596</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
         <v>3.561613668896306</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="R51" t="n">
         <v>165.5121650610737</v>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4214,59 +4369,62 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E52" t="n">
+        <v>19</v>
+      </c>
+      <c r="F52" t="n">
         <v>1</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>193.9165959732693</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>0.8615909360317315</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>174.432365021141</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>199.8419507455721</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>0.06365527772305327</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="n">
         <v>196.6386554621849</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>8.552631578947368</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>190.0491824654319</v>
       </c>
-      <c r="O52" t="n">
+      <c r="P52" t="n">
         <v>196.6386554621849</v>
       </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
         <v>5.611034800763306</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="R52" t="n">
         <v>154.7555469695623</v>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4287,61 +4445,64 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E53" t="n">
+        <v>19</v>
+      </c>
+      <c r="F53" t="n">
         <v>2128</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>20.26471065115279</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>23.59328463933557</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>35.23746831954708</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>20.3485721220649</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>22.35766299143393</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="n">
         <v>162.1656348846054</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>960.578947368421</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>169.178554981669</v>
       </c>
-      <c r="O53" t="n">
+      <c r="P53" t="n">
         <v>162.1656348846054</v>
       </c>
-      <c r="P53" t="n">
+      <c r="Q53" t="n">
         <v>960.578947368421</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="R53" t="n">
         <v>188.2648408233968</v>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T53" t="n">
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
         <v>20.26471065115279</v>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=20.26% sobre 19 sem</t>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=20.26% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4362,61 +4523,64 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E54" t="n">
+        <v>19</v>
+      </c>
+      <c r="F54" t="n">
         <v>1000</v>
       </c>
-      <c r="F54" t="n">
+      <c r="G54" t="n">
         <v>21.78990331830676</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>12.18529853018219</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>38.4591918317379</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>21.4311848091815</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>11.31461757696774</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="n">
         <v>162.6260942449485</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>456.2631578947368</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>163.7593826553296</v>
       </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
         <v>162.6260942449485</v>
       </c>
-      <c r="P54" t="n">
+      <c r="Q54" t="n">
         <v>456.2631578947368</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="R54" t="n">
         <v>187.9362468841497</v>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T54" t="n">
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
         <v>21.4311848091815</v>
       </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=21.43% sobre 19 sem</t>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=21.43% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4437,61 +4601,64 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E55" t="n">
+        <v>19</v>
+      </c>
+      <c r="F55" t="n">
         <v>1122</v>
       </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>25.35547688070321</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>14.64653986540293</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>38.25160771522186</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>23.44652230037202</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>13.31096246619567</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="n">
         <v>161.9773827308954</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>504.6315789473684</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>170.8273891473021</v>
       </c>
-      <c r="O55" t="n">
+      <c r="P55" t="n">
         <v>161.9773827308954</v>
       </c>
-      <c r="P55" t="n">
+      <c r="Q55" t="n">
         <v>504.6315789473684</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="R55" t="n">
         <v>188.8384134033935</v>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T55" t="n">
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
         <v>23.44652230037202</v>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=23.45% sobre 19 sem</t>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=23.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4512,61 +4679,64 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E56" t="n">
+        <v>19</v>
+      </c>
+      <c r="F56" t="n">
         <v>64</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>74.37701734933476</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>2.979831085540594</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>154.1439500713238</v>
       </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
         <v>60.29125449784342</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>2.058542600183989</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="n">
         <v>165.3708526408925</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>41.23684210526316</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>179.6737627262154</v>
       </c>
-      <c r="O56" t="n">
+      <c r="P56" t="n">
         <v>165.3708526408925</v>
       </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
         <v>41.23684210526316</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="R56" t="n">
         <v>197.7368060568652</v>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T56" t="n">
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
         <v>60.29125449784342</v>
       </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=60.29% sobre 19 sem</t>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=60.29% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4587,61 +4757,64 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E57" t="n">
+        <v>19</v>
+      </c>
+      <c r="F57" t="n">
         <v>30</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>99.24117228272365</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>1.645033028339421</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>164.0555422208552</v>
       </c>
-      <c r="I57" t="n">
+      <c r="J57" t="n">
         <v>116.297575094597</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>1.527704620497148</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="n">
         <v>163.4899500853628</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>18.31578947368421</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>187.7358722188936</v>
       </c>
-      <c r="O57" t="n">
+      <c r="P57" t="n">
         <v>163.4899500853628</v>
       </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
         <v>18.31578947368421</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="R57" t="n">
         <v>197.2831175654684</v>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T57" t="n">
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
         <v>99.24117228272365</v>
       </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=99.24% sobre 19 sem</t>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=99.24% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4662,61 +4835,64 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E58" t="n">
+        <v>19</v>
+      </c>
+      <c r="F58" t="n">
         <v>34</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>94.48969926947952</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>1.696695370092706</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>158.4722608607674</v>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>108.3078562554235</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>1.695960225704595</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="n">
         <v>167.6753221837887</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>23.47368421052632</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>183.1273067581348</v>
       </c>
-      <c r="O58" t="n">
+      <c r="P58" t="n">
         <v>167.6753221837887</v>
       </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
         <v>23.47368421052632</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="R58" t="n">
         <v>197.6615055783608</v>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T58" t="n">
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
         <v>94.48969926947952</v>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=94.49% sobre 19 sem</t>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=94.49% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4737,59 +4913,62 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E59" t="n">
+        <v>19</v>
+      </c>
+      <c r="F59" t="n">
         <v>4</v>
       </c>
-      <c r="F59" t="n">
+      <c r="G59" t="n">
         <v>199.4821021973625</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>0.2298717867783556</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>163.442478475025</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>192.0282448335926</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>0.2176559100684902</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="n">
         <v>171.7647058823529</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>2.710526315789474</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>198.2516520479188</v>
       </c>
-      <c r="O59" t="n">
+      <c r="P59" t="n">
         <v>171.7647058823529</v>
       </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
         <v>2.710526315789474</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="R59" t="n">
         <v>199.2894660635261</v>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE 2026</t>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4810,59 +4989,62 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E60" t="n">
+        <v>19</v>
+      </c>
+      <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>197.7007515643313</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>0.1727165705253666</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>179.6544870721095</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>198.0983117983889</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>0.1643773387814032</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="n">
         <v>163.0769230769231</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>1.736842105263158</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>197.6157031839507</v>
       </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
         <v>163.0769230769231</v>
       </c>
-      <c r="P60" t="n">
+      <c r="Q60" t="n">
         <v>1.736842105263158</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="R60" t="n">
         <v>199.0965028052728</v>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE 2026</t>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4883,59 +5065,62 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E61" t="n">
+        <v>19</v>
+      </c>
+      <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>199.9502411083014</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>0.0745902904045261</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>178.3754768379913</v>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>198.6805210475813</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>0.1343820781330749</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="n">
         <v>185.4545454545454</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>1.210526315789474</v>
       </c>
-      <c r="N61" t="n">
+      <c r="O61" t="n">
         <v>198.3770115307477</v>
       </c>
-      <c r="O61" t="n">
+      <c r="P61" t="n">
         <v>185.4545454545454</v>
       </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
         <v>1.210526315789474</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
         <v>199.3694289811982</v>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4956,61 +5141,64 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E62" t="n">
+        <v>19</v>
+      </c>
+      <c r="F62" t="n">
         <v>14</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>128.8719310283875</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>0.7572694217418114</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>51.86246745886869</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>130.9571266908071</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>1.758318531644439</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="n">
         <v>175.5235927343014</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>17.10526315789474</v>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>187.6026725565334</v>
       </c>
-      <c r="O62" t="n">
+      <c r="P62" t="n">
         <v>175.5235927343014</v>
       </c>
-      <c r="P62" t="n">
+      <c r="Q62" t="n">
         <v>17.10526315789474</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="R62" t="n">
         <v>188.4656733609786</v>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T62" t="n">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
         <v>128.8719310283875</v>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=128.87% sobre 19 sem</t>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=128.87% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5031,59 +5219,62 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E63" t="n">
+        <v>19</v>
+      </c>
+      <c r="F63" t="n">
         <v>7</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>154.6663812011903</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>0.4837828153102234</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>69.84803023883232</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>160.7230440211508</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>0.4234746267679511</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="n">
         <v>176.4842587752804</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>7.368421052631579</v>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>179.6068984245533</v>
       </c>
-      <c r="O63" t="n">
+      <c r="P63" t="n">
         <v>176.4842587752804</v>
       </c>
-      <c r="P63" t="n">
+      <c r="Q63" t="n">
         <v>7.368421052631579</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="R63" t="n">
         <v>186.3893216158546</v>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE 2026</t>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5104,59 +5295,62 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E64" t="n">
+        <v>19</v>
+      </c>
+      <c r="F64" t="n">
         <v>7</v>
       </c>
-      <c r="F64" t="n">
+      <c r="G64" t="n">
         <v>156.9060988936143</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>0.6365528514939038</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>72.92360982323459</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>166.1274744316233</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>0.5598670879556945</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="n">
         <v>176.5775401069519</v>
       </c>
-      <c r="M64" t="n">
+      <c r="N64" t="n">
         <v>10.36842105263158</v>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>188.9515900641726</v>
       </c>
-      <c r="O64" t="n">
+      <c r="P64" t="n">
         <v>176.5775401069519</v>
       </c>
-      <c r="P64" t="n">
+      <c r="Q64" t="n">
         <v>10.36842105263158</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="R64" t="n">
         <v>191.0006997623111</v>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE 2026</t>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5177,61 +5371,64 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E65" t="n">
+        <v>19</v>
+      </c>
+      <c r="F65" t="n">
         <v>4</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>172.7342912125195</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>0.5281176484570876</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>124.1398173354868</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>189.1042820076799</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>0.3797058234358746</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>137.6406301580537</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>190.5411382191568</v>
       </c>
-      <c r="M65" t="n">
+      <c r="N65" t="n">
         <v>17</v>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>183.1533465531335</v>
       </c>
-      <c r="O65" t="n">
+      <c r="P65" t="n">
         <v>190.5411382191568</v>
       </c>
-      <c r="P65" t="n">
+      <c r="Q65" t="n">
         <v>17</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="R65" t="n">
         <v>191.9303948964172</v>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE 2026</t>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5252,59 +5449,62 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E66" t="n">
+        <v>19</v>
+      </c>
+      <c r="F66" t="n">
         <v>2</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>193.5182683795834</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>0.2457881406423402</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>146.9871894171194</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>193.2101731341945</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>0.2751233810656595</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="n">
         <v>193.7098844672657</v>
       </c>
-      <c r="M66" t="n">
+      <c r="N66" t="n">
         <v>8.894736842105264</v>
       </c>
-      <c r="N66" t="n">
+      <c r="O66" t="n">
         <v>185.4205866195275</v>
       </c>
-      <c r="O66" t="n">
+      <c r="P66" t="n">
         <v>193.7098844672657</v>
       </c>
-      <c r="P66" t="n">
+      <c r="Q66" t="n">
         <v>8.894736842105264</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="R66" t="n">
         <v>192.190104304547</v>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5325,61 +5525,64 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" t="n">
         <v>2</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>191.7047398007156</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>0.3384995990865677</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>137.6516466078508</v>
       </c>
-      <c r="I67" t="n">
+      <c r="J67" t="n">
         <v>199.4595197986712</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>0.2938794965819146</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>151.2037021887013</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>193.7098844672657</v>
       </c>
-      <c r="M67" t="n">
+      <c r="N67" t="n">
         <v>9.052631578947368</v>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>175.6951253506204</v>
       </c>
-      <c r="O67" t="n">
+      <c r="P67" t="n">
         <v>193.7098844672657</v>
       </c>
-      <c r="P67" t="n">
+      <c r="Q67" t="n">
         <v>9.052631578947368</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="R67" t="n">
         <v>191.2393501485975</v>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE 2026</t>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5400,61 +5603,64 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E68" t="n">
+        <v>19</v>
+      </c>
+      <c r="F68" t="n">
         <v>1</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>199.988140539529</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>0.06134600670915952</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>183.5383709430125</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>199.8261929576067</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>0.0661948246945351</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>198.3312090033645</v>
       </c>
-      <c r="L68" t="n">
-        <v>200</v>
-      </c>
       <c r="M68" t="n">
+        <v>200</v>
+      </c>
+      <c r="N68" t="n">
         <v>4.925787257750323</v>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>188.2784643365136</v>
       </c>
-      <c r="O68" t="n">
-        <v>200</v>
-      </c>
       <c r="P68" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q68" t="n">
         <v>5.5</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="R68" t="n">
         <v>199.7672857698158</v>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5475,61 +5681,64 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E69" t="n">
+        <v>19</v>
+      </c>
+      <c r="F69" t="n">
         <v>1</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>198.1317768745953</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>0.08121093263600343</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>171.5447439761989</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>199.4593995691129</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>0.07715776683387024</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>194.4182830751776</v>
       </c>
-      <c r="L69" t="n">
-        <v>200</v>
-      </c>
       <c r="M69" t="n">
+        <v>200</v>
+      </c>
+      <c r="N69" t="n">
         <v>2.421052631578947</v>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>190.8574288418282</v>
       </c>
-      <c r="O69" t="n">
-        <v>200</v>
-      </c>
       <c r="P69" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q69" t="n">
         <v>2.421052631578947</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="R69" t="n">
         <v>199.6130972886749</v>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE 2026</t>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5550,61 +5759,64 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E70" t="n">
+        <v>19</v>
+      </c>
+      <c r="F70" t="n">
         <v>0</v>
       </c>
-      <c r="F70" t="n">
-        <v>200</v>
-      </c>
       <c r="G70" t="n">
+        <v>200</v>
+      </c>
+      <c r="H70" t="n">
         <v>0.01778981153364209</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>188.453973372859</v>
       </c>
-      <c r="I70" t="n">
-        <v>200</v>
-      </c>
       <c r="J70" t="n">
+        <v>200</v>
+      </c>
+      <c r="K70" t="n">
         <v>0.01701156060708355</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>198.9765474653765</v>
       </c>
-      <c r="L70" t="n">
-        <v>200</v>
-      </c>
       <c r="M70" t="n">
+        <v>200</v>
+      </c>
+      <c r="N70" t="n">
         <v>3.000395821091233</v>
       </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
         <v>192.937344462188</v>
       </c>
-      <c r="O70" t="n">
-        <v>200</v>
-      </c>
       <c r="P70" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q70" t="n">
         <v>3.236842105263158</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="R70" t="n">
         <v>199.6974055100667</v>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5625,63 +5837,66 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E71" t="n">
+        <v>19</v>
+      </c>
+      <c r="F71" t="n">
         <v>84</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>57.37693578719302</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>2.825184477639819</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>143.4057585362926</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>181.7289735216879</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>4.204953221303974</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>171.2174826415851</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>76.44148826641481</v>
       </c>
-      <c r="M71" t="n">
+      <c r="N71" t="n">
         <v>4.461687547631855</v>
       </c>
-      <c r="N71" t="n">
+      <c r="O71" t="n">
         <v>65.78436567943845</v>
       </c>
-      <c r="O71" t="n">
+      <c r="P71" t="n">
         <v>187.5628945654752</v>
       </c>
-      <c r="P71" t="n">
+      <c r="Q71" t="n">
         <v>4.2884948607661</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="R71" t="n">
         <v>185.267595267154</v>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T71" t="n">
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
         <v>57.37693578719302</v>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=57.38% sobre 19 sem</t>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=57.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5702,63 +5917,66 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E72" t="n">
+        <v>19</v>
+      </c>
+      <c r="F72" t="n">
         <v>35</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>91.0942949438804</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>1.574592744679023</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>151.0433307550491</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>96.98750299847268</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>1.305697114865129</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>171.9287045593839</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>96.43718470396682</v>
       </c>
-      <c r="M72" t="n">
+      <c r="N72" t="n">
         <v>2.321839312638196</v>
       </c>
-      <c r="N72" t="n">
+      <c r="O72" t="n">
         <v>96.15548417978732</v>
       </c>
-      <c r="O72" t="n">
+      <c r="P72" t="n">
         <v>157.7563524619638</v>
       </c>
-      <c r="P72" t="n">
+      <c r="Q72" t="n">
         <v>1.77161774667331</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="R72" t="n">
         <v>161.2927483340683</v>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T72" t="n">
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
         <v>91.0942949438804</v>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=91.09% sobre 19 sem</t>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=91.09% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5779,63 +5997,66 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E73" t="n">
+        <v>19</v>
+      </c>
+      <c r="F73" t="n">
         <v>50</v>
       </c>
-      <c r="F73" t="n">
+      <c r="G73" t="n">
         <v>66.88932169454627</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>1.833647952485144</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>148.5993365374143</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>167.6095784999177</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>2.325709697108638</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>191.7880460732582</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>99.42587142276584</v>
       </c>
-      <c r="M73" t="n">
+      <c r="N73" t="n">
         <v>2.018178237111945</v>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>105.84208545642</v>
       </c>
-      <c r="O73" t="n">
+      <c r="P73" t="n">
         <v>164.8485968348066</v>
       </c>
-      <c r="P73" t="n">
+      <c r="Q73" t="n">
         <v>2.220180862656712</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="R73" t="n">
         <v>173.6314937555617</v>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T73" t="n">
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
         <v>66.88932169454627</v>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=66.89% sobre 19 sem</t>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=66.89% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5856,61 +6077,64 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E74" t="n">
+        <v>19</v>
+      </c>
+      <c r="F74" t="n">
         <v>9</v>
       </c>
-      <c r="F74" t="n">
+      <c r="G74" t="n">
         <v>168.5747304100348</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>2.582846452563731</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>148.9425712788151</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>186.9126864191641</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>0.4401064702641599</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>144.0733541161664</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>189.6448066714631</v>
       </c>
-      <c r="M74" t="n">
+      <c r="N74" t="n">
         <v>26.4294632033182</v>
       </c>
-      <c r="N74" t="n">
+      <c r="O74" t="n">
         <v>166.1309749781026</v>
       </c>
-      <c r="O74" t="n">
+      <c r="P74" t="n">
         <v>189.6448066714631</v>
       </c>
-      <c r="P74" t="n">
+      <c r="Q74" t="n">
         <v>26.68421052631579</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="R74" t="n">
         <v>193.1141809259393</v>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE 2026</t>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5931,61 +6155,64 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E75" t="n">
+        <v>19</v>
+      </c>
+      <c r="F75" t="n">
         <v>5</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>168.2545421044971</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>1.16053340835048</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>157.2380343536269</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>196.6279104486694</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>0.3034072430596306</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>158.6014909691414</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>189.0211955227435</v>
       </c>
-      <c r="M75" t="n">
+      <c r="N75" t="n">
         <v>11.89375382888973</v>
       </c>
-      <c r="N75" t="n">
+      <c r="O75" t="n">
         <v>163.9609846286252</v>
       </c>
-      <c r="O75" t="n">
+      <c r="P75" t="n">
         <v>189.0211955227435</v>
       </c>
-      <c r="P75" t="n">
+      <c r="Q75" t="n">
         <v>12.21052631578947</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="R75" t="n">
         <v>193.2892416279341</v>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE 2026</t>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6006,61 +6233,64 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E76" t="n">
+        <v>19</v>
+      </c>
+      <c r="F76" t="n">
         <v>4</v>
       </c>
-      <c r="F76" t="n">
+      <c r="G76" t="n">
         <v>175.6880157321164</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>1.531534735446058</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>154.9841830576604</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>195.3413856273902</v>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
         <v>0.2057436508728052</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>166.7038660732646</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
         <v>189.1729323308271</v>
       </c>
-      <c r="M76" t="n">
+      <c r="N76" t="n">
         <v>14.08949935771264</v>
       </c>
-      <c r="N76" t="n">
+      <c r="O76" t="n">
         <v>168.5329779328607</v>
       </c>
-      <c r="O76" t="n">
+      <c r="P76" t="n">
         <v>189.1729323308271</v>
       </c>
-      <c r="P76" t="n">
+      <c r="Q76" t="n">
         <v>14.71052631578947</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="R76" t="n">
         <v>192.8448970866968</v>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE 2026</t>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6081,63 +6311,66 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E77" t="n">
+        <v>19</v>
+      </c>
+      <c r="F77" t="n">
         <v>361</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>46.69234462013655</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>6.788620896340505</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>77.76772218573589</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>36.79734774047761</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>6.708211027185509</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>110.3330967959057</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>47.8895378952934</v>
       </c>
-      <c r="M77" t="n">
+      <c r="N77" t="n">
         <v>11.02631578947368</v>
       </c>
-      <c r="N77" t="n">
+      <c r="O77" t="n">
         <v>117.4841503463031</v>
       </c>
-      <c r="O77" t="n">
+      <c r="P77" t="n">
         <v>47.8895378952934</v>
       </c>
-      <c r="P77" t="n">
+      <c r="Q77" t="n">
         <v>11.02631578947368</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="R77" t="n">
         <v>138.4032392925817</v>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T77" t="n">
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U77" t="n">
         <v>36.79734774047761</v>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=36.80% sobre 19 sem</t>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=36.80% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6158,63 +6391,66 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E78" t="n">
+        <v>19</v>
+      </c>
+      <c r="F78" t="n">
         <v>173</v>
       </c>
-      <c r="F78" t="n">
+      <c r="G78" t="n">
         <v>48.26514541284195</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>3.613344121230134</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>103.5437500854655</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>51.10941098137504</v>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
         <v>4.074518054301315</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>115.3631910942854</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>132.8108105037542</v>
       </c>
-      <c r="M78" t="n">
+      <c r="N78" t="n">
         <v>6.46116481368479</v>
       </c>
-      <c r="N78" t="n">
+      <c r="O78" t="n">
         <v>128.5059105773902</v>
       </c>
-      <c r="O78" t="n">
+      <c r="P78" t="n">
         <v>47.39415663274317</v>
       </c>
-      <c r="P78" t="n">
+      <c r="Q78" t="n">
         <v>4.42813360747103</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="R78" t="n">
         <v>82.9912432467173</v>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T78" t="n">
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U78" t="n">
         <v>48.26514541284195</v>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=48.27% sobre 19 sem</t>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=48.27% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6235,63 +6471,66 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E79" t="n">
+        <v>19</v>
+      </c>
+      <c r="F79" t="n">
         <v>188</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>52.91222566319724</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>3.864661196179704</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>102.5016657415887</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>36.92725458042533</v>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>3.302047854258936</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>114.5134591086363</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
         <v>53.13626166171554</v>
       </c>
-      <c r="M79" t="n">
+      <c r="N79" t="n">
         <v>6.657894736842105</v>
       </c>
-      <c r="N79" t="n">
+      <c r="O79" t="n">
         <v>131.5261264594907</v>
       </c>
-      <c r="O79" t="n">
+      <c r="P79" t="n">
         <v>53.13626166171554</v>
       </c>
-      <c r="P79" t="n">
+      <c r="Q79" t="n">
         <v>6.657894736842105</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="R79" t="n">
         <v>148.0195847609927</v>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T79" t="n">
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U79" t="n">
         <v>36.92725458042533</v>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=36.93% sobre 19 sem</t>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=36.93% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6312,63 +6551,66 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E80" t="n">
+        <v>19</v>
+      </c>
+      <c r="F80" t="n">
         <v>548</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>142.0473293234183</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>24.73559830907586</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>180.9937478063148</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>149.3522092224518</v>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
         <v>23.38961870508665</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>195.3549053278383</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
         <v>124.7515030309418</v>
       </c>
-      <c r="M80" t="n">
+      <c r="N80" t="n">
         <v>18.48013024581106</v>
       </c>
-      <c r="N80" t="n">
+      <c r="O80" t="n">
         <v>171.1146914183623</v>
       </c>
-      <c r="O80" t="n">
+      <c r="P80" t="n">
         <v>150.2710602240091</v>
       </c>
-      <c r="P80" t="n">
+      <c r="Q80" t="n">
         <v>25.62322426770046</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="R80" t="n">
         <v>172.7461511452186</v>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T80" t="n">
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U80" t="n">
         <v>142.0473293234183</v>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=142.05% sobre 19 sem</t>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=142.05% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6389,63 +6631,66 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E81" t="n">
+        <v>19</v>
+      </c>
+      <c r="F81" t="n">
         <v>255</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>127.6155198807104</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>10.89448015320569</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>185.5191244575439</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>135.1025520610708</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>8.567143251050577</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>199.4307199889832</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>176.0140030425413</v>
       </c>
-      <c r="M81" t="n">
+      <c r="N81" t="n">
         <v>12.30917172682913</v>
       </c>
-      <c r="N81" t="n">
+      <c r="O81" t="n">
         <v>169.7911563334158</v>
       </c>
-      <c r="O81" t="n">
+      <c r="P81" t="n">
         <v>137.4824606386474</v>
       </c>
-      <c r="P81" t="n">
+      <c r="Q81" t="n">
         <v>11.41040295945036</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="R81" t="n">
         <v>163.1536185700502</v>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T81" t="n">
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U81" t="n">
         <v>127.6155198807104</v>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=127.62% sobre 19 sem</t>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=127.62% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6466,63 +6711,66 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E82" t="n">
+        <v>19</v>
+      </c>
+      <c r="F82" t="n">
         <v>293</v>
       </c>
-      <c r="F82" t="n">
+      <c r="G82" t="n">
         <v>124.3198054769538</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>12.65118418611661</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>186.2973802760101</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>143.6520875442592</v>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>12.94659064734331</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>183.0162368876618</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>159.6233471388631</v>
       </c>
-      <c r="M82" t="n">
+      <c r="N82" t="n">
         <v>12.05820103068101</v>
       </c>
-      <c r="N82" t="n">
+      <c r="O82" t="n">
         <v>164.8878431370165</v>
       </c>
-      <c r="O82" t="n">
+      <c r="P82" t="n">
         <v>139.5299674281279</v>
       </c>
-      <c r="P82" t="n">
+      <c r="Q82" t="n">
         <v>13.52804288888773</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="R82" t="n">
         <v>166.6060177059153</v>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T82" t="n">
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U82" t="n">
         <v>124.3198054769538</v>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=124.32% sobre 19 sem</t>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=124.32% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6543,63 +6791,66 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E83" t="n">
+        <v>19</v>
+      </c>
+      <c r="F83" t="n">
         <v>362</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>35.45935764754714</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>6.299557206056292</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>88.04980557911651</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>46.42585692650886</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>8.37710047108553</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>194.0620340843763</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>101.142689215435</v>
       </c>
-      <c r="M83" t="n">
+      <c r="N83" t="n">
         <v>37.65965657247335</v>
       </c>
-      <c r="N83" t="n">
+      <c r="O83" t="n">
         <v>149.7627223031833</v>
       </c>
-      <c r="O83" t="n">
+      <c r="P83" t="n">
         <v>82.87727882274899</v>
       </c>
-      <c r="P83" t="n">
+      <c r="Q83" t="n">
         <v>30.05086433793102</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="R83" t="n">
         <v>103.1343264142703</v>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T83" t="n">
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U83" t="n">
         <v>35.45935764754714</v>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=35.46% sobre 19 sem</t>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=35.46% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6620,63 +6871,66 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E84" t="n">
+        <v>19</v>
+      </c>
+      <c r="F84" t="n">
         <v>162</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>32.38454879714672</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>2.590604588219051</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>100.4914466151705</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>45.96231344597865</v>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
         <v>3.449044160724878</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>161.0256208848398</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>73.35136326793538</v>
       </c>
-      <c r="M84" t="n">
+      <c r="N84" t="n">
         <v>8.912867338922181</v>
       </c>
-      <c r="N84" t="n">
+      <c r="O84" t="n">
         <v>93.7212443502728</v>
       </c>
-      <c r="O84" t="n">
+      <c r="P84" t="n">
         <v>85.36326949733061</v>
       </c>
-      <c r="P84" t="n">
+      <c r="Q84" t="n">
         <v>13.84714075997255</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="R84" t="n">
         <v>98.74789164115032</v>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T84" t="n">
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U84" t="n">
         <v>32.38454879714672</v>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=32.38% sobre 19 sem</t>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=32.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6697,63 +6951,66 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E85" t="n">
+        <v>19</v>
+      </c>
+      <c r="F85" t="n">
         <v>199</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>45.66073922769827</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>4.349422253201568</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>109.9471447641292</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>57.43339810358206</v>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>5.058339965311367</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>191.126671844217</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>96.11293749099474</v>
       </c>
-      <c r="M85" t="n">
+      <c r="N85" t="n">
         <v>18.23089364942659</v>
       </c>
-      <c r="N85" t="n">
+      <c r="O85" t="n">
         <v>122.1180851534335</v>
       </c>
-      <c r="O85" t="n">
+      <c r="P85" t="n">
         <v>90.05124321306785</v>
       </c>
-      <c r="P85" t="n">
+      <c r="Q85" t="n">
         <v>17.93448716547004</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="R85" t="n">
         <v>106.9882513320439</v>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T85" t="n">
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U85" t="n">
         <v>45.66073922769827</v>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=45.66% sobre 19 sem</t>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=45.66% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6774,63 +7031,66 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E86" t="n">
+        <v>19</v>
+      </c>
+      <c r="F86" t="n">
         <v>33</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>107.0051144969647</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>2.888610677610906</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>160.3842205944857</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>118.5283012694314</v>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>1.511365094958628</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>143.9950818237897</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>131.5868440407407</v>
       </c>
-      <c r="M86" t="n">
+      <c r="N86" t="n">
         <v>2.046955790958906</v>
       </c>
-      <c r="N86" t="n">
+      <c r="O86" t="n">
         <v>178.0725595254285</v>
       </c>
-      <c r="O86" t="n">
+      <c r="P86" t="n">
         <v>170.6286794329426</v>
       </c>
-      <c r="P86" t="n">
+      <c r="Q86" t="n">
         <v>21.39473684210526</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="R86" t="n">
         <v>188.4995472315167</v>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T86" t="n">
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U86" t="n">
         <v>107.0051144969647</v>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=107.01% sobre 19 sem</t>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=107.01% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6851,63 +7111,66 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E87" t="n">
+        <v>19</v>
+      </c>
+      <c r="F87" t="n">
         <v>17</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>113.1870478943641</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>1.165451077594584</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>171.410316416684</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>143.5835389914779</v>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" t="n">
         <v>0.9800779156337266</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" t="n">
         <v>150.2517475184781</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
         <v>162.2316347756723</v>
       </c>
-      <c r="M87" t="n">
+      <c r="N87" t="n">
         <v>9.131578947368421</v>
       </c>
-      <c r="N87" t="n">
+      <c r="O87" t="n">
         <v>166.9678403273574</v>
       </c>
-      <c r="O87" t="n">
+      <c r="P87" t="n">
         <v>162.2316347756723</v>
       </c>
-      <c r="P87" t="n">
+      <c r="Q87" t="n">
         <v>9.131578947368421</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="R87" t="n">
         <v>191.241827101395</v>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T87" t="n">
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U87" t="n">
         <v>113.1870478943641</v>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=113.19% sobre 19 sem</t>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=113.19% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6928,63 +7191,66 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E88" t="n">
+        <v>19</v>
+      </c>
+      <c r="F88" t="n">
         <v>15</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>131.8021709096804</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>1.686097704619301</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>169.0038464611843</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>173.8296114884862</v>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>1.003422029570916</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>118.6804789630648</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
         <v>172.6013331685172</v>
       </c>
-      <c r="M88" t="n">
+      <c r="N88" t="n">
         <v>1.919249045221429</v>
       </c>
-      <c r="N88" t="n">
+      <c r="O88" t="n">
         <v>181.2811328411623</v>
       </c>
-      <c r="O88" t="n">
+      <c r="P88" t="n">
         <v>180.73123264338</v>
       </c>
-      <c r="P88" t="n">
+      <c r="Q88" t="n">
         <v>12.78947368421053</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="R88" t="n">
         <v>190.1751472740156</v>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T88" t="n">
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U88" t="n">
         <v>131.8021709096804</v>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=131.80% sobre 19 sem</t>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=131.80% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7005,57 +7271,60 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E89" t="n">
+        <v>19</v>
+      </c>
+      <c r="F89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" t="n">
-        <v>200</v>
-      </c>
       <c r="G89" t="n">
+        <v>200</v>
+      </c>
+      <c r="H89" t="n">
         <v>0.1027285104502795</v>
       </c>
-      <c r="H89" t="n">
-        <v>200</v>
-      </c>
       <c r="I89" t="n">
         <v>200</v>
       </c>
       <c r="J89" t="n">
+        <v>200</v>
+      </c>
+      <c r="K89" t="n">
         <v>0.007380532391221194</v>
       </c>
-      <c r="K89" t="n">
-        <v>200</v>
-      </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="n">
+      <c r="L89" t="n">
+        <v>200</v>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>200</v>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="n">
+      <c r="O89" t="n">
+        <v>200</v>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>200</v>
-      </c>
-      <c r="R89" t="inlineStr">
+      <c r="R89" t="n">
+        <v>200</v>
+      </c>
+      <c r="S89" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7076,57 +7345,60 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E90" t="n">
+        <v>19</v>
+      </c>
+      <c r="F90" t="n">
         <v>0</v>
       </c>
-      <c r="F90" t="n">
-        <v>200</v>
-      </c>
       <c r="G90" t="n">
+        <v>200</v>
+      </c>
+      <c r="H90" t="n">
         <v>0.09027970940358052</v>
       </c>
-      <c r="H90" t="n">
-        <v>200</v>
-      </c>
       <c r="I90" t="n">
         <v>200</v>
       </c>
       <c r="J90" t="n">
+        <v>200</v>
+      </c>
+      <c r="K90" t="n">
         <v>0.003657128813195968</v>
       </c>
-      <c r="K90" t="n">
-        <v>200</v>
-      </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="n">
+      <c r="L90" t="n">
+        <v>200</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="n">
         <v>0</v>
       </c>
-      <c r="N90" t="n">
-        <v>200</v>
-      </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="n">
+      <c r="O90" t="n">
+        <v>200</v>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>200</v>
-      </c>
-      <c r="R90" t="inlineStr">
+      <c r="R90" t="n">
+        <v>200</v>
+      </c>
+      <c r="S90" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7147,57 +7419,60 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E91" t="n">
+        <v>19</v>
+      </c>
+      <c r="F91" t="n">
         <v>0</v>
       </c>
-      <c r="F91" t="n">
-        <v>200</v>
-      </c>
       <c r="G91" t="n">
+        <v>200</v>
+      </c>
+      <c r="H91" t="n">
         <v>0.09273934624974439</v>
       </c>
-      <c r="H91" t="n">
-        <v>200</v>
-      </c>
       <c r="I91" t="n">
         <v>200</v>
       </c>
       <c r="J91" t="n">
+        <v>200</v>
+      </c>
+      <c r="K91" t="n">
         <v>0.01455603600441123</v>
       </c>
-      <c r="K91" t="n">
-        <v>200</v>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="n">
+      <c r="L91" t="n">
+        <v>200</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>200</v>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="n">
+      <c r="O91" t="n">
+        <v>200</v>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>200</v>
-      </c>
-      <c r="R91" t="inlineStr">
+      <c r="R91" t="n">
+        <v>200</v>
+      </c>
+      <c r="S91" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7218,63 +7493,66 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E92" t="n">
+        <v>19</v>
+      </c>
+      <c r="F92" t="n">
         <v>293</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>52.49086450360068</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>7.632350894424847</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>49.15109590531281</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>53.35077005079972</v>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>7.637694966892938</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>104.6459551741298</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
         <v>149.619457716756</v>
       </c>
-      <c r="M92" t="n">
+      <c r="N92" t="n">
         <v>92.43043766657274</v>
       </c>
-      <c r="N92" t="n">
+      <c r="O92" t="n">
         <v>118.9713689353267</v>
       </c>
-      <c r="O92" t="n">
+      <c r="P92" t="n">
         <v>108.5913919239667</v>
       </c>
-      <c r="P92" t="n">
+      <c r="Q92" t="n">
         <v>39.96055378451477</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="R92" t="n">
         <v>92.01416331532587</v>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T92" t="n">
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U92" t="n">
         <v>52.49086450360068</v>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=52.49% sobre 19 sem</t>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=52.49% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7295,63 +7573,66 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E93" t="n">
+        <v>19</v>
+      </c>
+      <c r="F93" t="n">
         <v>140</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>49.38424923276131</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>3.469072830113385</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>60.93105560683724</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>60.1026346278737</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
         <v>4.939438714442002</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" t="n">
         <v>89.5280086489867</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
         <v>146.0245283061174</v>
       </c>
-      <c r="M93" t="n">
+      <c r="N93" t="n">
         <v>41.69405104777928</v>
       </c>
-      <c r="N93" t="n">
+      <c r="O93" t="n">
         <v>121.8694023763068</v>
       </c>
-      <c r="O93" t="n">
+      <c r="P93" t="n">
         <v>114.1212768688539</v>
       </c>
-      <c r="P93" t="n">
+      <c r="Q93" t="n">
         <v>20.99274142876214</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="R93" t="n">
         <v>96.01849856237216</v>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T93" t="n">
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U93" t="n">
         <v>49.38424923276131</v>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=49.38% sobre 19 sem</t>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=49.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7372,63 +7653,66 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E94" t="n">
+        <v>19</v>
+      </c>
+      <c r="F94" t="n">
         <v>153</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>57.56739705044136</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>4.31128253527494</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>64.07712599234655</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>52.98096764410323</v>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>3.790476368256205</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>91.94886769427217</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
         <v>149.6998267702992</v>
       </c>
-      <c r="M94" t="n">
+      <c r="N94" t="n">
         <v>45.6523329434659</v>
       </c>
-      <c r="N94" t="n">
+      <c r="O94" t="n">
         <v>120.3184691119026</v>
       </c>
-      <c r="O94" t="n">
+      <c r="P94" t="n">
         <v>112.5398372966676</v>
       </c>
-      <c r="P94" t="n">
+      <c r="Q94" t="n">
         <v>22.36505768071156</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="R94" t="n">
         <v>95.82311990464228</v>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T94" t="n">
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U94" t="n">
         <v>52.98096764410323</v>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE 2026 real=52.98% sobre 19 sem</t>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>DeepAR: menor SMAPE real=52.98% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7449,63 +7733,66 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E95" t="n">
+        <v>19</v>
+      </c>
+      <c r="F95" t="n">
         <v>10</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>147.5935778029153</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>0.662334516860426</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>152.3875262412586</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>198.9660683083715</v>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" t="n">
         <v>0.5239013555859853</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" t="n">
         <v>128.1095321097334</v>
       </c>
-      <c r="L95" t="n">
-        <v>200</v>
-      </c>
       <c r="M95" t="n">
+        <v>200</v>
+      </c>
+      <c r="N95" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
         <v>189.619699057401</v>
       </c>
-      <c r="O95" t="n">
+      <c r="P95" t="n">
         <v>168.4130957965686</v>
       </c>
-      <c r="P95" t="n">
+      <c r="Q95" t="n">
         <v>3.712348962717789</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="R95" t="n">
         <v>118.2821915164861</v>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>smape_real_2026</t>
-        </is>
-      </c>
-      <c r="T95" t="n">
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="U95" t="n">
         <v>147.5935778029153</v>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE 2026 real=147.59% sobre 19 sem</t>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Prophet: menor SMAPE real=147.59% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7526,61 +7813,64 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E96" t="n">
+        <v>19</v>
+      </c>
+      <c r="F96" t="n">
         <v>3</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>181.6843142825061</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>0.3291270790645512</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>158.9896824444987</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>199.2150951603351</v>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>0.1584986195278356</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>189.1617640516506</v>
       </c>
-      <c r="L96" t="n">
-        <v>200</v>
-      </c>
       <c r="M96" t="n">
+        <v>200</v>
+      </c>
+      <c r="N96" t="n">
         <v>0.8016990005837641</v>
       </c>
-      <c r="N96" t="n">
+      <c r="O96" t="n">
         <v>127.6499599586913</v>
       </c>
-      <c r="O96" t="n">
+      <c r="P96" t="n">
         <v>186.7228903978403</v>
       </c>
-      <c r="P96" t="n">
+      <c r="Q96" t="n">
         <v>3.622631913077714</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="R96" t="n">
         <v>124.4459476108536</v>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE 2026</t>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7601,61 +7891,64 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E97" t="n">
+        <v>19</v>
+      </c>
+      <c r="F97" t="n">
         <v>7</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>166.6950640152984</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>0.3995569831044574</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>157.2976315063829</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>199.3927310976356</v>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
         <v>0.3716897725749284</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
         <v>187.1093440450062</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
         <v>162.4241916567453</v>
       </c>
-      <c r="M97" t="n">
+      <c r="N97" t="n">
         <v>1.583574840897008</v>
       </c>
-      <c r="N97" t="n">
+      <c r="O97" t="n">
         <v>126.5693936023772</v>
       </c>
-      <c r="O97" t="n">
+      <c r="P97" t="n">
         <v>168.6261496195838</v>
       </c>
-      <c r="P97" t="n">
+      <c r="Q97" t="n">
         <v>2.339267854845288</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="R97" t="n">
         <v>128.4785456608675</v>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE 2026</t>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7676,57 +7969,60 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E98" t="n">
+        <v>19</v>
+      </c>
+      <c r="F98" t="n">
         <v>0</v>
       </c>
-      <c r="F98" t="n">
-        <v>200</v>
-      </c>
       <c r="G98" t="n">
+        <v>200</v>
+      </c>
+      <c r="H98" t="n">
         <v>0.07575033617870201</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>198.585723184526</v>
       </c>
-      <c r="I98" t="n">
-        <v>200</v>
-      </c>
       <c r="J98" t="n">
+        <v>200</v>
+      </c>
+      <c r="K98" t="n">
         <v>0.0005744433579079894</v>
       </c>
-      <c r="K98" t="n">
+      <c r="L98" t="n">
         <v>199.9898962083731</v>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="n">
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
         <v>0</v>
       </c>
-      <c r="N98" t="n">
+      <c r="O98" t="n">
         <v>199.2030987655621</v>
       </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="n">
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>200</v>
-      </c>
-      <c r="R98" t="inlineStr">
+      <c r="R98" t="n">
+        <v>200</v>
+      </c>
+      <c r="S98" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7747,57 +8043,60 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E99" t="n">
+        <v>19</v>
+      </c>
+      <c r="F99" t="n">
         <v>0</v>
       </c>
-      <c r="F99" t="n">
-        <v>200</v>
-      </c>
       <c r="G99" t="n">
+        <v>200</v>
+      </c>
+      <c r="H99" t="n">
         <v>0.04403257285937298</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>198.7380283178126</v>
       </c>
-      <c r="I99" t="n">
-        <v>200</v>
-      </c>
       <c r="J99" t="n">
+        <v>200</v>
+      </c>
+      <c r="K99" t="n">
         <v>0.001595394861881958</v>
       </c>
-      <c r="K99" t="n">
+      <c r="L99" t="n">
         <v>199.9983019911245</v>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="n">
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="n">
         <v>0</v>
       </c>
-      <c r="N99" t="n">
+      <c r="O99" t="n">
         <v>198.5022493653877</v>
       </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="n">
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>200</v>
-      </c>
-      <c r="R99" t="inlineStr">
+      <c r="R99" t="n">
+        <v>200</v>
+      </c>
+      <c r="S99" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7818,57 +8117,60 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>19</v>
+        <v>2026</v>
       </c>
       <c r="E100" t="n">
+        <v>19</v>
+      </c>
+      <c r="F100" t="n">
         <v>0</v>
       </c>
-      <c r="F100" t="n">
-        <v>200</v>
-      </c>
       <c r="G100" t="n">
+        <v>200</v>
+      </c>
+      <c r="H100" t="n">
         <v>0.0598529225883256</v>
       </c>
-      <c r="H100" t="n">
-        <v>200</v>
-      </c>
       <c r="I100" t="n">
         <v>200</v>
       </c>
       <c r="J100" t="n">
+        <v>200</v>
+      </c>
+      <c r="K100" t="n">
         <v>0.00240448959164621</v>
       </c>
-      <c r="K100" t="n">
-        <v>200</v>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="n">
+      <c r="L100" t="n">
+        <v>200</v>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="n">
         <v>0</v>
       </c>
-      <c r="N100" t="n">
-        <v>200</v>
-      </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="n">
-        <v>0</v>
-      </c>
+      <c r="O100" t="n">
+        <v>200</v>
+      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>mae_real_2026_casi_cero</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE 2026</t>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>mae_real_casi_cero</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -578,9 +578,11 @@
         <v>200</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008980106835938563</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>0.008620340954539604</v>
+      </c>
+      <c r="L2" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M2" t="n">
         <v>200</v>
       </c>
@@ -654,9 +656,11 @@
         <v>200</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01223255052547364</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>0.01293774852062258</v>
+      </c>
+      <c r="L3" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M3" t="n">
         <v>200</v>
       </c>
@@ -730,9 +734,11 @@
         <v>200</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07902433993532074</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>0.07625688786245192</v>
+      </c>
+      <c r="L4" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M4" t="n">
         <v>200</v>
       </c>
@@ -803,12 +809,14 @@
         <v>175.1088701866436</v>
       </c>
       <c r="J5" t="n">
-        <v>199.3234195740198</v>
+        <v>199.2843630995856</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1167777980905749</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>0.1172378734304398</v>
+      </c>
+      <c r="L5" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M5" t="n">
         <v>200</v>
       </c>
@@ -879,12 +887,14 @@
         <v>191.646475967384</v>
       </c>
       <c r="J6" t="n">
-        <v>199.9904719366027</v>
+        <v>199.9861671147559</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05344732191053987</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>0.05340157993507275</v>
+      </c>
+      <c r="L6" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M6" t="n">
         <v>200</v>
       </c>
@@ -955,12 +965,14 @@
         <v>186.9197740801393</v>
       </c>
       <c r="J7" t="n">
-        <v>199.9920711524921</v>
+        <v>199.9884309380623</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05301641570428982</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>0.05308000538193182</v>
+      </c>
+      <c r="L7" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M7" t="n">
         <v>200</v>
       </c>
@@ -1031,12 +1043,14 @@
         <v>154.5040916050135</v>
       </c>
       <c r="J8" t="n">
-        <v>49.448315629151</v>
+        <v>48.2035225269852</v>
       </c>
       <c r="K8" t="n">
-        <v>3.415782015598385</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>3.314891306805234</v>
+      </c>
+      <c r="L8" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M8" t="n">
         <v>95.80329746013628</v>
       </c>
@@ -1066,11 +1080,11 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>49.448315629151</v>
+        <v>48.2035225269852</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=49.45% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=48.20% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1123,14 @@
         <v>164.086229256472</v>
       </c>
       <c r="J9" t="n">
-        <v>76.1592104766909</v>
+        <v>69.98966250353146</v>
       </c>
       <c r="K9" t="n">
-        <v>3.688325335653582</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>2.063113567141357</v>
+      </c>
+      <c r="L9" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M9" t="n">
         <v>111.3394980759131</v>
       </c>
@@ -1144,11 +1160,11 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>76.1592104766909</v>
+        <v>69.98966250353146</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=76.16% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=69.99% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1203,14 @@
         <v>164.4874496413386</v>
       </c>
       <c r="J10" t="n">
-        <v>42.29469737291846</v>
+        <v>45.23277359273659</v>
       </c>
       <c r="K10" t="n">
-        <v>1.605336268698746</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>1.634276789548177</v>
+      </c>
+      <c r="L10" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M10" t="n">
         <v>95.95074714452349</v>
       </c>
@@ -1222,11 +1240,11 @@
         </is>
       </c>
       <c r="U10" t="n">
-        <v>42.29469737291846</v>
+        <v>45.23277359273659</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=42.29% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=45.23% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1283,14 @@
         <v>123.2554563734294</v>
       </c>
       <c r="J11" t="n">
-        <v>198.0872324051026</v>
+        <v>198.0164154965292</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5883275269435004</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>0.5887372433414818</v>
+      </c>
+      <c r="L11" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M11" t="n">
         <v>192.4219018577286</v>
       </c>
@@ -1343,12 +1363,14 @@
         <v>147.3485671696691</v>
       </c>
       <c r="J12" t="n">
-        <v>199.5587784261111</v>
+        <v>199.523179310629</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3711322500993692</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>0.3712791089096222</v>
+      </c>
+      <c r="L12" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M12" t="n">
         <v>191.5362391585139</v>
       </c>
@@ -1419,12 +1441,14 @@
         <v>157.1522264328246</v>
       </c>
       <c r="J13" t="n">
-        <v>199.8393822352099</v>
+        <v>199.8262982460481</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2121195042665527</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>0.2119254300762861</v>
+      </c>
+      <c r="L13" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M13" t="n">
         <v>194.1951423424674</v>
       </c>
@@ -1495,12 +1519,14 @@
         <v>66.61025297793201</v>
       </c>
       <c r="J14" t="n">
-        <v>84.9403327767854</v>
+        <v>85.47396170872173</v>
       </c>
       <c r="K14" t="n">
-        <v>2.624469817249901</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>2.660604966823898</v>
+      </c>
+      <c r="L14" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M14" t="n">
         <v>168.2605793498451</v>
       </c>
@@ -1573,12 +1599,14 @@
         <v>82.6747998505866</v>
       </c>
       <c r="J15" t="n">
-        <v>90.82996398527685</v>
+        <v>89.8785759618037</v>
       </c>
       <c r="K15" t="n">
-        <v>1.202745696995517</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>1.189208099884046</v>
+      </c>
+      <c r="L15" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M15" t="n">
         <v>172.9250609621144</v>
       </c>
@@ -1651,12 +1679,14 @@
         <v>90.20708978859948</v>
       </c>
       <c r="J16" t="n">
-        <v>142.1698014999685</v>
+        <v>142.02923967689</v>
       </c>
       <c r="K16" t="n">
-        <v>1.461545414911759</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>1.457101397264992</v>
+      </c>
+      <c r="L16" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M16" t="n">
         <v>177.5562163584148</v>
       </c>
@@ -1729,12 +1759,14 @@
         <v>194.5446671655584</v>
       </c>
       <c r="J17" t="n">
-        <v>199.9347630529597</v>
+        <v>199.943152462609</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05500281057855451</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>0.0548479375829464</v>
+      </c>
+      <c r="L17" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M17" t="n">
         <v>200</v>
       </c>
@@ -1808,9 +1840,11 @@
         <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>0.000582446063573821</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>0.0005657554175379</v>
+      </c>
+      <c r="L18" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>0</v>
@@ -1877,12 +1911,14 @@
         <v>196.278530387405</v>
       </c>
       <c r="J19" t="n">
-        <v>199.9010828640821</v>
+        <v>199.8695191024682</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05750655344769912</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>0.05725188032739883</v>
+      </c>
+      <c r="L19" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M19" t="n">
         <v>200</v>
       </c>
@@ -1956,9 +1992,11 @@
         <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001262668041030563</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>0.001370789179767052</v>
+      </c>
+      <c r="L20" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>0</v>
@@ -2028,9 +2066,11 @@
         <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>0.006155900490740383</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>0.005994552645078885</v>
+      </c>
+      <c r="L21" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>0</v>
@@ -2100,9 +2140,11 @@
         <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0004386668824289527</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>0.000365936301039679</v>
+      </c>
+      <c r="L22" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0</v>
@@ -2169,12 +2211,14 @@
         <v>149.2565324185079</v>
       </c>
       <c r="J23" t="n">
-        <v>199.2048177791976</v>
+        <v>199.2619412956352</v>
       </c>
       <c r="K23" t="n">
-        <v>0.118578293258006</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>0.1191078773049664</v>
+      </c>
+      <c r="L23" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M23" t="n">
         <v>192.8571428571429</v>
       </c>
@@ -2245,12 +2289,14 @@
         <v>156.2502876793226</v>
       </c>
       <c r="J24" t="n">
-        <v>198.7364217540033</v>
+        <v>198.5231057940479</v>
       </c>
       <c r="K24" t="n">
-        <v>0.07131395163685894</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>0.0644576519532402</v>
+      </c>
+      <c r="L24" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M24" t="n">
         <v>138.2549574812263</v>
       </c>
@@ -2271,7 +2317,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2282,7 +2328,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2367,14 @@
         <v>155.3955473497874</v>
       </c>
       <c r="J25" t="n">
-        <v>199.9219951890681</v>
+        <v>199.9139299449369</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05804041841012747</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>0.0576600837228529</v>
+      </c>
+      <c r="L25" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M25" t="n">
         <v>200</v>
       </c>
@@ -2400,9 +2448,11 @@
         <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>0.09487158631641658</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
+        <v>0.09259454194778965</v>
+      </c>
+      <c r="L26" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M26" t="n">
         <v>200</v>
       </c>
@@ -2476,9 +2526,11 @@
         <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01217744203193361</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>0.01173072176237696</v>
+      </c>
+      <c r="L27" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M27" t="n">
         <v>200</v>
       </c>
@@ -2552,9 +2604,11 @@
         <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>0.004357350598142374</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>0.004403138451811863</v>
+      </c>
+      <c r="L28" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M28" t="n">
         <v>200</v>
       </c>
@@ -2628,9 +2682,11 @@
         <v>200</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02400026013487088</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>0.02627149302176331</v>
+      </c>
+      <c r="L29" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M29" t="n">
         <v>200</v>
       </c>
@@ -2704,9 +2760,11 @@
         <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>0.005648859496855605</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>0.005751018203588878</v>
+      </c>
+      <c r="L30" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M30" t="n">
         <v>200</v>
       </c>
@@ -2780,9 +2838,11 @@
         <v>200</v>
       </c>
       <c r="K31" t="n">
-        <v>0.006504246045091579</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>0.005810557376236404</v>
+      </c>
+      <c r="L31" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M31" t="n">
         <v>200</v>
       </c>
@@ -2853,12 +2913,14 @@
         <v>164.6748490827784</v>
       </c>
       <c r="J32" t="n">
-        <v>187.7116605365616</v>
+        <v>188.3994774916149</v>
       </c>
       <c r="K32" t="n">
-        <v>0.35590860162829</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>0.3600397467700314</v>
+      </c>
+      <c r="L32" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M32" t="n">
         <v>152.3809523809524</v>
       </c>
@@ -2929,12 +2991,14 @@
         <v>170.4028696730483</v>
       </c>
       <c r="J33" t="n">
-        <v>197.7160600542925</v>
+        <v>197.5602748361831</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1629487095041507</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>0.3071348444317514</v>
+      </c>
+      <c r="L33" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M33" t="n">
         <v>200</v>
       </c>
@@ -3005,12 +3069,14 @@
         <v>169.6571057340244</v>
       </c>
       <c r="J34" t="n">
-        <v>172.2289143480554</v>
+        <v>171.6084043022315</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4078312226593602</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
+        <v>0.4006139541700345</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M34" t="n">
         <v>163.9888682745826</v>
       </c>
@@ -3081,12 +3147,14 @@
         <v>48.55849570822402</v>
       </c>
       <c r="J35" t="n">
-        <v>128.6317087128079</v>
+        <v>128.6246318422078</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8248307660368517</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>0.8253314883004678</v>
+      </c>
+      <c r="L35" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M35" t="n">
         <v>190.1370507886782</v>
       </c>
@@ -3159,12 +3227,14 @@
         <v>58.86670393327421</v>
       </c>
       <c r="J36" t="n">
-        <v>171.3518767659004</v>
+        <v>170.6440396621451</v>
       </c>
       <c r="K36" t="n">
-        <v>0.649354005833872</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+        <v>0.6600202651972441</v>
+      </c>
+      <c r="L36" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M36" t="n">
         <v>187.6511691920828</v>
       </c>
@@ -3235,12 +3305,14 @@
         <v>60.32903496111531</v>
       </c>
       <c r="J37" t="n">
-        <v>163.1188236017408</v>
+        <v>162.0004203901676</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8129319453662752</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
+        <v>0.8181360894281809</v>
+      </c>
+      <c r="L37" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M37" t="n">
         <v>180.650285245381</v>
       </c>
@@ -3311,12 +3383,14 @@
         <v>164.4263244057969</v>
       </c>
       <c r="J38" t="n">
-        <v>194.5679991577052</v>
+        <v>193.5392151146532</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3264860329740122</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>0.3365288969477717</v>
+      </c>
+      <c r="L38" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M38" t="n">
         <v>182.488038277512</v>
       </c>
@@ -3387,12 +3461,14 @@
         <v>170.2041702191862</v>
       </c>
       <c r="J39" t="n">
-        <v>199.3242543587107</v>
+        <v>199.1462918111721</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1236912055260483</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>0.1211556611899457</v>
+      </c>
+      <c r="L39" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M39" t="n">
         <v>182.2222222222222</v>
       </c>
@@ -3463,12 +3539,14 @@
         <v>165.7522199768573</v>
       </c>
       <c r="J40" t="n">
-        <v>199.6624849301809</v>
+        <v>199.5885882473661</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1145922745262008</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
+        <v>0.1159126568736139</v>
+      </c>
+      <c r="L40" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M40" t="n">
         <v>186.3157894736842</v>
       </c>
@@ -3539,12 +3617,14 @@
         <v>127.4617865350128</v>
       </c>
       <c r="J41" t="n">
-        <v>91.89362526827718</v>
+        <v>91.67853884817875</v>
       </c>
       <c r="K41" t="n">
-        <v>1.511609206255772</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+        <v>1.501031372391154</v>
+      </c>
+      <c r="L41" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M41" t="n">
         <v>183.507499093661</v>
       </c>
@@ -3617,12 +3697,14 @@
         <v>139.5371944473096</v>
       </c>
       <c r="J42" t="n">
-        <v>155.8038714031126</v>
+        <v>154.5839114750662</v>
       </c>
       <c r="K42" t="n">
-        <v>1.261630135771666</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
+        <v>1.253514010486913</v>
+      </c>
+      <c r="L42" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M42" t="n">
         <v>181.2887708376975</v>
       </c>
@@ -3695,12 +3777,14 @@
         <v>137.8269504556986</v>
       </c>
       <c r="J43" t="n">
-        <v>129.0846217162649</v>
+        <v>129.2210590644231</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8697344172166692</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>0.8683344472736246</v>
+      </c>
+      <c r="L43" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M43" t="n">
         <v>186.9457477180321</v>
       </c>
@@ -3773,12 +3857,14 @@
         <v>101.902133963665</v>
       </c>
       <c r="J44" t="n">
-        <v>113.9440981841071</v>
+        <v>113.6529259973059</v>
       </c>
       <c r="K44" t="n">
-        <v>1.94968755914931</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
+        <v>1.94118931811028</v>
+      </c>
+      <c r="L44" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M44" t="n">
         <v>185.0623623920618</v>
       </c>
@@ -3851,12 +3937,14 @@
         <v>133.2410714461222</v>
       </c>
       <c r="J45" t="n">
-        <v>138.7678816808106</v>
+        <v>138.8865780666307</v>
       </c>
       <c r="K45" t="n">
-        <v>1.468288778039868</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>1.465205468677794</v>
+      </c>
+      <c r="L45" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M45" t="n">
         <v>181.9877754532652</v>
       </c>
@@ -3929,12 +4017,14 @@
         <v>129.1401202444324</v>
       </c>
       <c r="J46" t="n">
-        <v>154.2493653257513</v>
+        <v>155.5388593759895</v>
       </c>
       <c r="K46" t="n">
-        <v>1.085230101094652</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
+        <v>1.100678491829755</v>
+      </c>
+      <c r="L46" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M46" t="n">
         <v>187.2242110784918</v>
       </c>
@@ -4007,12 +4097,14 @@
         <v>52.02932925897922</v>
       </c>
       <c r="J47" t="n">
-        <v>195.6050915352664</v>
+        <v>195.5685574757462</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6016355901040529</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>0.5965869982198665</v>
+      </c>
+      <c r="L47" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M47" t="n">
         <v>198.4000634090768</v>
       </c>
@@ -4083,12 +4175,14 @@
         <v>75.82494372432545</v>
       </c>
       <c r="J48" t="n">
-        <v>198.5785629334108</v>
+        <v>198.5330491254405</v>
       </c>
       <c r="K48" t="n">
-        <v>0.208424441549574</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
+        <v>0.2077539489681783</v>
+      </c>
+      <c r="L48" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M48" t="n">
         <v>197.2179224008849</v>
       </c>
@@ -4162,9 +4256,11 @@
         <v>200</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3455497331267909</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>0.3437848424462895</v>
+      </c>
+      <c r="L49" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M49" t="n">
         <v>200</v>
       </c>
@@ -4235,12 +4331,14 @@
         <v>162.6912701840232</v>
       </c>
       <c r="J50" t="n">
-        <v>199.5122170374651</v>
+        <v>199.5486379903699</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1641351663989946</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
+        <v>0.1629152076573967</v>
+      </c>
+      <c r="L50" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M50" t="n">
         <v>200</v>
       </c>
@@ -4311,12 +4409,14 @@
         <v>169.9274838481079</v>
       </c>
       <c r="J51" t="n">
-        <v>199.569745356571</v>
+        <v>199.4865823478398</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1221110404092794</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>0.1279910504674757</v>
+      </c>
+      <c r="L51" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M51" t="n">
         <v>195.959595959596</v>
       </c>
@@ -4387,12 +4487,14 @@
         <v>174.432365021141</v>
       </c>
       <c r="J52" t="n">
-        <v>199.8419507455721</v>
+        <v>199.8575276644268</v>
       </c>
       <c r="K52" t="n">
-        <v>0.06365527772305327</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
+        <v>0.06289546852160235</v>
+      </c>
+      <c r="L52" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M52" t="n">
         <v>196.6386554621849</v>
       </c>
@@ -4463,12 +4565,14 @@
         <v>35.23746831954708</v>
       </c>
       <c r="J53" t="n">
-        <v>20.3485721220649</v>
+        <v>20.44901503425639</v>
       </c>
       <c r="K53" t="n">
-        <v>22.35766299143393</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
+        <v>22.53472728636974</v>
+      </c>
+      <c r="L53" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M53" t="n">
         <v>162.1656348846054</v>
       </c>
@@ -4541,12 +4645,14 @@
         <v>38.4591918317379</v>
       </c>
       <c r="J54" t="n">
-        <v>21.4311848091815</v>
+        <v>21.5307402945977</v>
       </c>
       <c r="K54" t="n">
-        <v>11.31461757696774</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
+        <v>11.37805163170186</v>
+      </c>
+      <c r="L54" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M54" t="n">
         <v>162.6260942449485</v>
       </c>
@@ -4576,11 +4682,11 @@
         </is>
       </c>
       <c r="U54" t="n">
-        <v>21.4311848091815</v>
+        <v>21.5307402945977</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=21.43% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=21.53% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4619,12 +4725,14 @@
         <v>38.25160771522186</v>
       </c>
       <c r="J55" t="n">
-        <v>23.44652230037202</v>
+        <v>23.26637498008379</v>
       </c>
       <c r="K55" t="n">
-        <v>13.31096246619567</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>13.17654509709004</v>
+      </c>
+      <c r="L55" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M55" t="n">
         <v>161.9773827308954</v>
       </c>
@@ -4654,11 +4762,11 @@
         </is>
       </c>
       <c r="U55" t="n">
-        <v>23.44652230037202</v>
+        <v>23.26637498008379</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=23.45% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=23.27% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4805,14 @@
         <v>154.1439500713238</v>
       </c>
       <c r="J56" t="n">
-        <v>60.29125449784342</v>
+        <v>60.38041763078138</v>
       </c>
       <c r="K56" t="n">
-        <v>2.058542600183989</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>2.065272317818089</v>
+      </c>
+      <c r="L56" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M56" t="n">
         <v>165.3708526408925</v>
       </c>
@@ -4732,11 +4842,11 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>60.29125449784342</v>
+        <v>60.38041763078138</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=60.29% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=60.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4775,12 +4885,14 @@
         <v>164.0555422208552</v>
       </c>
       <c r="J57" t="n">
-        <v>116.297575094597</v>
+        <v>114.7616231997743</v>
       </c>
       <c r="K57" t="n">
-        <v>1.527704620497148</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>1.488718622791548</v>
+      </c>
+      <c r="L57" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M57" t="n">
         <v>163.4899500853628</v>
       </c>
@@ -4853,12 +4965,14 @@
         <v>158.4722608607674</v>
       </c>
       <c r="J58" t="n">
-        <v>108.3078562554235</v>
+        <v>105.6303668976963</v>
       </c>
       <c r="K58" t="n">
-        <v>1.695960225704595</v>
-      </c>
-      <c r="L58" t="inlineStr"/>
+        <v>1.579491473670759</v>
+      </c>
+      <c r="L58" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M58" t="n">
         <v>167.6753221837887</v>
       </c>
@@ -4931,12 +5045,14 @@
         <v>163.442478475025</v>
       </c>
       <c r="J59" t="n">
-        <v>192.0282448335926</v>
+        <v>192.5368174319365</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2176559100684902</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
+        <v>0.2214133618233808</v>
+      </c>
+      <c r="L59" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M59" t="n">
         <v>171.7647058823529</v>
       </c>
@@ -5007,12 +5123,14 @@
         <v>179.6544870721095</v>
       </c>
       <c r="J60" t="n">
-        <v>198.0983117983889</v>
+        <v>198.6597355840884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1643773387814032</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
+        <v>0.1659645822432419</v>
+      </c>
+      <c r="L60" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M60" t="n">
         <v>163.0769230769231</v>
       </c>
@@ -5083,12 +5201,14 @@
         <v>178.3754768379913</v>
       </c>
       <c r="J61" t="n">
-        <v>198.6805210475813</v>
+        <v>198.3975506268872</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1343820781330749</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
+        <v>0.137526459316728</v>
+      </c>
+      <c r="L61" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M61" t="n">
         <v>185.4545454545454</v>
       </c>
@@ -5159,12 +5279,14 @@
         <v>51.86246745886869</v>
       </c>
       <c r="J62" t="n">
-        <v>130.9571266908071</v>
+        <v>131.2644356700371</v>
       </c>
       <c r="K62" t="n">
-        <v>1.758318531644439</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>1.792143665152412</v>
+      </c>
+      <c r="L62" t="n">
+        <v>109.609711216533</v>
+      </c>
       <c r="M62" t="n">
         <v>175.5235927343014</v>
       </c>
@@ -5237,12 +5359,14 @@
         <v>69.84803023883232</v>
       </c>
       <c r="J63" t="n">
-        <v>160.7230440211508</v>
+        <v>160.5762472922584</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4234746267679511</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
+        <v>0.4223166429292686</v>
+      </c>
+      <c r="L63" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M63" t="n">
         <v>176.4842587752804</v>
       </c>
@@ -5313,12 +5437,14 @@
         <v>72.92360982323459</v>
       </c>
       <c r="J64" t="n">
-        <v>166.1274744316233</v>
+        <v>165.4971729021378</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5598670879556945</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>0.5568628189725624</v>
+      </c>
+      <c r="L64" t="n">
+        <v>109.7635513825217</v>
+      </c>
       <c r="M64" t="n">
         <v>176.5775401069519</v>
       </c>
@@ -5389,10 +5515,10 @@
         <v>124.1398173354868</v>
       </c>
       <c r="J65" t="n">
-        <v>189.1042820076799</v>
+        <v>188.6285607672464</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3797058234358746</v>
+        <v>0.3784678200407356</v>
       </c>
       <c r="L65" t="n">
         <v>137.6406301580537</v>
@@ -5467,12 +5593,14 @@
         <v>146.9871894171194</v>
       </c>
       <c r="J66" t="n">
-        <v>193.2101731341945</v>
+        <v>193.2466259789231</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2751233810656595</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
+        <v>0.2704853797460072</v>
+      </c>
+      <c r="L66" t="n">
+        <v>79.54507935933471</v>
+      </c>
       <c r="M66" t="n">
         <v>193.7098844672657</v>
       </c>
@@ -5543,10 +5671,10 @@
         <v>137.6516466078508</v>
       </c>
       <c r="J67" t="n">
-        <v>199.4595197986712</v>
+        <v>199.3097191502</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2938794965819146</v>
+        <v>0.2915347690590922</v>
       </c>
       <c r="L67" t="n">
         <v>151.2037021887013</v>
@@ -5621,10 +5749,10 @@
         <v>183.5383709430125</v>
       </c>
       <c r="J68" t="n">
-        <v>199.8261929576067</v>
+        <v>199.7828034264477</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0661948246945351</v>
+        <v>0.06645011343186964</v>
       </c>
       <c r="L68" t="n">
         <v>198.3312090033645</v>
@@ -5699,10 +5827,10 @@
         <v>171.5447439761989</v>
       </c>
       <c r="J69" t="n">
-        <v>199.4593995691129</v>
+        <v>199.3873217860459</v>
       </c>
       <c r="K69" t="n">
-        <v>0.07715776683387024</v>
+        <v>0.07890491428071096</v>
       </c>
       <c r="L69" t="n">
         <v>194.4182830751776</v>
@@ -5780,7 +5908,7 @@
         <v>200</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01701156060708355</v>
+        <v>0.01611044537267105</v>
       </c>
       <c r="L70" t="n">
         <v>198.9765474653765</v>
@@ -5855,10 +5983,10 @@
         <v>143.4057585362926</v>
       </c>
       <c r="J71" t="n">
-        <v>181.7289735216879</v>
+        <v>181.9880034485936</v>
       </c>
       <c r="K71" t="n">
-        <v>4.204953221303974</v>
+        <v>4.205103676707298</v>
       </c>
       <c r="L71" t="n">
         <v>171.2174826415851</v>
@@ -5935,10 +6063,10 @@
         <v>151.0433307550491</v>
       </c>
       <c r="J72" t="n">
-        <v>96.98750299847268</v>
+        <v>97.00281078314966</v>
       </c>
       <c r="K72" t="n">
-        <v>1.305697114865129</v>
+        <v>1.286265630916457</v>
       </c>
       <c r="L72" t="n">
         <v>171.9287045593839</v>
@@ -6015,10 +6143,10 @@
         <v>148.5993365374143</v>
       </c>
       <c r="J73" t="n">
-        <v>167.6095784999177</v>
+        <v>167.6451026349307</v>
       </c>
       <c r="K73" t="n">
-        <v>2.325709697108638</v>
+        <v>2.318164934182062</v>
       </c>
       <c r="L73" t="n">
         <v>191.7880460732582</v>
@@ -6095,10 +6223,10 @@
         <v>148.9425712788151</v>
       </c>
       <c r="J74" t="n">
-        <v>186.9126864191641</v>
+        <v>187.0298527328072</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4401064702641599</v>
+        <v>0.4419976246736432</v>
       </c>
       <c r="L74" t="n">
         <v>144.0733541161664</v>
@@ -6173,10 +6301,10 @@
         <v>157.2380343536269</v>
       </c>
       <c r="J75" t="n">
-        <v>196.6279104486694</v>
+        <v>196.6160780833582</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3034072430596306</v>
+        <v>0.3031989103336238</v>
       </c>
       <c r="L75" t="n">
         <v>158.6014909691414</v>
@@ -6251,10 +6379,10 @@
         <v>154.9841830576604</v>
       </c>
       <c r="J76" t="n">
-        <v>195.3413856273902</v>
+        <v>195.1948412340681</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2057436508728052</v>
+        <v>0.2055997108742528</v>
       </c>
       <c r="L76" t="n">
         <v>166.7038660732646</v>
@@ -6329,10 +6457,10 @@
         <v>77.76772218573589</v>
       </c>
       <c r="J77" t="n">
-        <v>36.79734774047761</v>
+        <v>37.10004537508804</v>
       </c>
       <c r="K77" t="n">
-        <v>6.708211027185509</v>
+        <v>6.776254930868525</v>
       </c>
       <c r="L77" t="n">
         <v>110.3330967959057</v>
@@ -6366,11 +6494,11 @@
         </is>
       </c>
       <c r="U77" t="n">
-        <v>36.79734774047761</v>
+        <v>37.10004537508804</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=36.80% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=37.10% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6409,10 +6537,10 @@
         <v>103.5437500854655</v>
       </c>
       <c r="J78" t="n">
-        <v>51.10941098137504</v>
+        <v>49.13942155356582</v>
       </c>
       <c r="K78" t="n">
-        <v>4.074518054301315</v>
+        <v>3.932447908708014</v>
       </c>
       <c r="L78" t="n">
         <v>115.3631910942854</v>
@@ -6489,10 +6617,10 @@
         <v>102.5016657415887</v>
       </c>
       <c r="J79" t="n">
-        <v>36.92725458042533</v>
+        <v>36.89186308680129</v>
       </c>
       <c r="K79" t="n">
-        <v>3.302047854258936</v>
+        <v>3.304314077057211</v>
       </c>
       <c r="L79" t="n">
         <v>114.5134591086363</v>
@@ -6526,11 +6654,11 @@
         </is>
       </c>
       <c r="U79" t="n">
-        <v>36.92725458042533</v>
+        <v>36.89186308680129</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=36.93% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=36.89% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6569,10 +6697,10 @@
         <v>180.9937478063148</v>
       </c>
       <c r="J80" t="n">
-        <v>149.3522092224518</v>
+        <v>148.3561506538706</v>
       </c>
       <c r="K80" t="n">
-        <v>23.38961870508665</v>
+        <v>23.31756395053142</v>
       </c>
       <c r="L80" t="n">
         <v>195.3549053278383</v>
@@ -6649,10 +6777,10 @@
         <v>185.5191244575439</v>
       </c>
       <c r="J81" t="n">
-        <v>135.1025520610708</v>
+        <v>137.2064188235088</v>
       </c>
       <c r="K81" t="n">
-        <v>8.567143251050577</v>
+        <v>8.59187932191203</v>
       </c>
       <c r="L81" t="n">
         <v>199.4307199889832</v>
@@ -6729,10 +6857,10 @@
         <v>186.2973802760101</v>
       </c>
       <c r="J82" t="n">
-        <v>143.6520875442592</v>
+        <v>145.1472793964314</v>
       </c>
       <c r="K82" t="n">
-        <v>12.94659064734331</v>
+        <v>12.99796069573456</v>
       </c>
       <c r="L82" t="n">
         <v>183.0162368876618</v>
@@ -6809,10 +6937,10 @@
         <v>88.04980557911651</v>
       </c>
       <c r="J83" t="n">
-        <v>46.42585692650886</v>
+        <v>47.56092545874292</v>
       </c>
       <c r="K83" t="n">
-        <v>8.37710047108553</v>
+        <v>8.665217789405114</v>
       </c>
       <c r="L83" t="n">
         <v>194.0620340843763</v>
@@ -6889,10 +7017,10 @@
         <v>100.4914466151705</v>
       </c>
       <c r="J84" t="n">
-        <v>45.96231344597865</v>
+        <v>46.15812962490158</v>
       </c>
       <c r="K84" t="n">
-        <v>3.449044160724878</v>
+        <v>3.475128502119654</v>
       </c>
       <c r="L84" t="n">
         <v>161.0256208848398</v>
@@ -6969,10 +7097,10 @@
         <v>109.9471447641292</v>
       </c>
       <c r="J85" t="n">
-        <v>57.43339810358206</v>
+        <v>55.36256686407579</v>
       </c>
       <c r="K85" t="n">
-        <v>5.058339965311367</v>
+        <v>4.933087742300096</v>
       </c>
       <c r="L85" t="n">
         <v>191.126671844217</v>
@@ -7049,10 +7177,10 @@
         <v>160.3842205944857</v>
       </c>
       <c r="J86" t="n">
-        <v>118.5283012694314</v>
+        <v>119.2256744546712</v>
       </c>
       <c r="K86" t="n">
-        <v>1.511365094958628</v>
+        <v>1.526445464584329</v>
       </c>
       <c r="L86" t="n">
         <v>143.9950818237897</v>
@@ -7129,10 +7257,10 @@
         <v>171.410316416684</v>
       </c>
       <c r="J87" t="n">
-        <v>143.5835389914779</v>
+        <v>143.560216889931</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9800779156337266</v>
+        <v>0.9883869165511783</v>
       </c>
       <c r="L87" t="n">
         <v>150.2517475184781</v>
@@ -7209,10 +7337,10 @@
         <v>169.0038464611843</v>
       </c>
       <c r="J88" t="n">
-        <v>173.8296114884862</v>
+        <v>173.3382025272879</v>
       </c>
       <c r="K88" t="n">
-        <v>1.003422029570916</v>
+        <v>1.000072263696867</v>
       </c>
       <c r="L88" t="n">
         <v>118.6804789630648</v>
@@ -7292,7 +7420,7 @@
         <v>200</v>
       </c>
       <c r="K89" t="n">
-        <v>0.007380532391221194</v>
+        <v>0.007270478566362362</v>
       </c>
       <c r="L89" t="n">
         <v>200</v>
@@ -7366,7 +7494,7 @@
         <v>200</v>
       </c>
       <c r="K90" t="n">
-        <v>0.003657128813195968</v>
+        <v>0.003415887464000547</v>
       </c>
       <c r="L90" t="n">
         <v>200</v>
@@ -7440,7 +7568,7 @@
         <v>200</v>
       </c>
       <c r="K91" t="n">
-        <v>0.01455603600441123</v>
+        <v>0.01376589551061007</v>
       </c>
       <c r="L91" t="n">
         <v>200</v>
@@ -7511,10 +7639,10 @@
         <v>49.15109590531281</v>
       </c>
       <c r="J92" t="n">
-        <v>53.35077005079972</v>
+        <v>53.86994196900773</v>
       </c>
       <c r="K92" t="n">
-        <v>7.637694966892938</v>
+        <v>7.694847947284689</v>
       </c>
       <c r="L92" t="n">
         <v>104.6459551741298</v>
@@ -7591,10 +7719,10 @@
         <v>60.93105560683724</v>
       </c>
       <c r="J93" t="n">
-        <v>60.1026346278737</v>
+        <v>59.78155232420327</v>
       </c>
       <c r="K93" t="n">
-        <v>4.939438714442002</v>
+        <v>4.925424425520819</v>
       </c>
       <c r="L93" t="n">
         <v>89.5280086489867</v>
@@ -7671,10 +7799,10 @@
         <v>64.07712599234655</v>
       </c>
       <c r="J94" t="n">
-        <v>52.98096764410323</v>
+        <v>52.69581648158714</v>
       </c>
       <c r="K94" t="n">
-        <v>3.790476368256205</v>
+        <v>3.740125253417435</v>
       </c>
       <c r="L94" t="n">
         <v>91.94886769427217</v>
@@ -7708,11 +7836,11 @@
         </is>
       </c>
       <c r="U94" t="n">
-        <v>52.98096764410323</v>
+        <v>52.69581648158714</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=52.98% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=52.70% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7751,10 +7879,10 @@
         <v>152.3875262412586</v>
       </c>
       <c r="J95" t="n">
-        <v>198.9660683083715</v>
+        <v>199.1922050178509</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5239013555859853</v>
+        <v>0.5243681068222776</v>
       </c>
       <c r="L95" t="n">
         <v>128.1095321097334</v>
@@ -7831,10 +7959,10 @@
         <v>158.9896824444987</v>
       </c>
       <c r="J96" t="n">
-        <v>199.2150951603351</v>
+        <v>199.2513153043118</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1584986195278356</v>
+        <v>0.158291047634362</v>
       </c>
       <c r="L96" t="n">
         <v>189.1617640516506</v>
@@ -7909,10 +8037,10 @@
         <v>157.2976315063829</v>
       </c>
       <c r="J97" t="n">
-        <v>199.3927310976356</v>
+        <v>199.3614643125625</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3716897725749284</v>
+        <v>0.3712739720909262</v>
       </c>
       <c r="L97" t="n">
         <v>187.1093440450062</v>
@@ -7990,7 +8118,7 @@
         <v>200</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0005744433579079894</v>
+        <v>0.000548695229506579</v>
       </c>
       <c r="L98" t="n">
         <v>199.9898962083731</v>
@@ -8064,7 +8192,7 @@
         <v>200</v>
       </c>
       <c r="K99" t="n">
-        <v>0.001595394861881958</v>
+        <v>0.001607453320843158</v>
       </c>
       <c r="L99" t="n">
         <v>199.9983019911245</v>
@@ -8138,7 +8266,7 @@
         <v>200</v>
       </c>
       <c r="K100" t="n">
-        <v>0.00240448959164621</v>
+        <v>0.002433839398527311</v>
       </c>
       <c r="L100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -569,10 +569,10 @@
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01143971376208275</v>
+        <v>0.01909339069720435</v>
       </c>
       <c r="I2" t="n">
-        <v>185.8333489727328</v>
+        <v>181.8875746538405</v>
       </c>
       <c r="J2" t="n">
         <v>200</v>
@@ -647,10 +647,10 @@
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009067953039092178</v>
+        <v>0.0120984434586246</v>
       </c>
       <c r="I3" t="n">
-        <v>157.2321783542833</v>
+        <v>157.3839857426704</v>
       </c>
       <c r="J3" t="n">
         <v>200</v>
@@ -725,10 +725,10 @@
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01410237981501257</v>
+        <v>0.02123577474837053</v>
       </c>
       <c r="I4" t="n">
-        <v>158.5580779411727</v>
+        <v>158.8438418444702</v>
       </c>
       <c r="J4" t="n">
         <v>200</v>
@@ -800,13 +800,13 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>199.0125831330724</v>
+        <v>199.863029343531</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1083988208702625</v>
+        <v>0.1060038941382352</v>
       </c>
       <c r="I5" t="n">
-        <v>175.1088701866436</v>
+        <v>175.5400786038201</v>
       </c>
       <c r="J5" t="n">
         <v>199.2843630995856</v>
@@ -878,13 +878,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>199.5227768499908</v>
+        <v>199.6986714004902</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06224017002961615</v>
+        <v>0.05880289809912526</v>
       </c>
       <c r="I6" t="n">
-        <v>191.646475967384</v>
+        <v>191.737797552366</v>
       </c>
       <c r="J6" t="n">
         <v>199.9861671147559</v>
@@ -956,13 +956,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>199.0827646374914</v>
+        <v>199.158331088558</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07542585392837421</v>
+        <v>0.06346581821336009</v>
       </c>
       <c r="I7" t="n">
-        <v>186.9197740801393</v>
+        <v>187.2671055681853</v>
       </c>
       <c r="J7" t="n">
         <v>199.9884309380623</v>
@@ -1034,13 +1034,13 @@
         <v>142</v>
       </c>
       <c r="G8" t="n">
-        <v>101.1620929265983</v>
+        <v>124.2408629147414</v>
       </c>
       <c r="H8" t="n">
-        <v>5.212131266542356</v>
+        <v>5.858449498066894</v>
       </c>
       <c r="I8" t="n">
-        <v>154.5040916050135</v>
+        <v>146.1852288200182</v>
       </c>
       <c r="J8" t="n">
         <v>48.2035225269852</v>
@@ -1114,13 +1114,13 @@
         <v>62</v>
       </c>
       <c r="G9" t="n">
-        <v>96.50000967408079</v>
+        <v>133.862958905723</v>
       </c>
       <c r="H9" t="n">
-        <v>2.364058607609518</v>
+        <v>2.745953184050532</v>
       </c>
       <c r="I9" t="n">
-        <v>164.086229256472</v>
+        <v>155.2184985113495</v>
       </c>
       <c r="J9" t="n">
         <v>69.98966250353146</v>
@@ -1194,13 +1194,13 @@
         <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>94.84727283752737</v>
+        <v>124.9117102132738</v>
       </c>
       <c r="H10" t="n">
-        <v>2.632141656550983</v>
+        <v>3.060920355992553</v>
       </c>
       <c r="I10" t="n">
-        <v>164.4874496413386</v>
+        <v>152.9918981156764</v>
       </c>
       <c r="J10" t="n">
         <v>45.23277359273659</v>
@@ -1274,13 +1274,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>177.1662152513658</v>
+        <v>169.256431894795</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5816049116984011</v>
+        <v>0.5989329700208699</v>
       </c>
       <c r="I11" t="n">
-        <v>123.2554563734294</v>
+        <v>129.9250091591691</v>
       </c>
       <c r="J11" t="n">
         <v>198.0164154965292</v>
@@ -1320,11 +1320,11 @@
         </is>
       </c>
       <c r="U11" t="n">
-        <v>177.1662152513658</v>
+        <v>169.256431894795</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=177.17% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=169.26% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1354,13 +1354,13 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>191.8552562166053</v>
+        <v>194.4159379304537</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3754643963600293</v>
+        <v>0.3858136158142387</v>
       </c>
       <c r="I12" t="n">
-        <v>147.3485671696691</v>
+        <v>140.9543563511172</v>
       </c>
       <c r="J12" t="n">
         <v>199.523179310629</v>
@@ -1432,13 +1432,13 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>195.3735385790647</v>
+        <v>194.7808770000501</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2165418703011477</v>
+        <v>0.2470576173028503</v>
       </c>
       <c r="I13" t="n">
-        <v>157.1522264328246</v>
+        <v>143.0465384202982</v>
       </c>
       <c r="J13" t="n">
         <v>199.8262982460481</v>
@@ -1510,13 +1510,13 @@
         <v>62</v>
       </c>
       <c r="G14" t="n">
-        <v>70.98011798172448</v>
+        <v>68.18440924623016</v>
       </c>
       <c r="H14" t="n">
-        <v>2.050209983850287</v>
+        <v>1.965115005649187</v>
       </c>
       <c r="I14" t="n">
-        <v>66.61025297793201</v>
+        <v>74.93132855047638</v>
       </c>
       <c r="J14" t="n">
         <v>85.47396170872173</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="U14" t="n">
-        <v>70.98011798172448</v>
+        <v>68.18440924623016</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=70.98% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=68.18% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1590,13 +1590,13 @@
         <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>65.87044566451193</v>
+        <v>68.63649638136945</v>
       </c>
       <c r="H15" t="n">
-        <v>0.897248034177942</v>
+        <v>0.9654501657857059</v>
       </c>
       <c r="I15" t="n">
-        <v>82.6747998505866</v>
+        <v>83.26703869122109</v>
       </c>
       <c r="J15" t="n">
         <v>89.8785759618037</v>
@@ -1636,11 +1636,11 @@
         </is>
       </c>
       <c r="U15" t="n">
-        <v>65.87044566451193</v>
+        <v>68.63649638136945</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=65.87% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=68.64% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1670,13 +1670,13 @@
         <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>122.3179070028762</v>
+        <v>121.4424954946124</v>
       </c>
       <c r="H16" t="n">
-        <v>1.567952396243824</v>
+        <v>1.534736430505168</v>
       </c>
       <c r="I16" t="n">
-        <v>90.20708978859948</v>
+        <v>88.28301425252694</v>
       </c>
       <c r="J16" t="n">
         <v>142.02923967689</v>
@@ -1716,11 +1716,11 @@
         </is>
       </c>
       <c r="U16" t="n">
-        <v>122.3179070028762</v>
+        <v>121.4424954946124</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=122.32% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=121.44% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1750,13 +1750,13 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>198.7352626872857</v>
+        <v>199.1102341795934</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1117349335808297</v>
+        <v>0.09613834946315496</v>
       </c>
       <c r="I17" t="n">
-        <v>194.5446671655584</v>
+        <v>194.6710344353644</v>
       </c>
       <c r="J17" t="n">
         <v>199.943152462609</v>
@@ -1831,10 +1831,10 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02565291991697691</v>
+        <v>0.03136352411444188</v>
       </c>
       <c r="I18" t="n">
-        <v>199.6410247115898</v>
+        <v>199.5917940260522</v>
       </c>
       <c r="J18" t="n">
         <v>200</v>
@@ -1902,13 +1902,13 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.0372771487083</v>
+        <v>199.4476600573335</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09944267109328039</v>
+        <v>0.08682774457069804</v>
       </c>
       <c r="I19" t="n">
-        <v>196.278530387405</v>
+        <v>196.3668815794815</v>
       </c>
       <c r="J19" t="n">
         <v>199.8695191024682</v>
@@ -1983,7 +1983,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07047412404518942</v>
+        <v>0.01308918116114505</v>
       </c>
       <c r="I20" t="n">
         <v>200</v>
@@ -2057,7 +2057,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05672395709071366</v>
+        <v>0.05679447572271468</v>
       </c>
       <c r="I21" t="n">
         <v>200</v>
@@ -2131,7 +2131,7 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06350447684539688</v>
+        <v>0.06271867433330723</v>
       </c>
       <c r="I22" t="n">
         <v>200</v>
@@ -2202,13 +2202,13 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>179.1739130190571</v>
+        <v>179.9337722008812</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1271859159213902</v>
+        <v>0.1264170913622294</v>
       </c>
       <c r="I23" t="n">
-        <v>149.2565324185079</v>
+        <v>148.7957871310144</v>
       </c>
       <c r="J23" t="n">
         <v>199.2619412956352</v>
@@ -2280,13 +2280,13 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>182.221104530061</v>
+        <v>182.6845580141106</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06574743966708289</v>
+        <v>0.06542854972043259</v>
       </c>
       <c r="I24" t="n">
-        <v>156.2502876793226</v>
+        <v>155.1760639717555</v>
       </c>
       <c r="J24" t="n">
         <v>198.5231057940479</v>
@@ -2361,10 +2361,10 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0735937728171784</v>
+        <v>0.07054487750177577</v>
       </c>
       <c r="I25" t="n">
-        <v>155.3955473497874</v>
+        <v>155.0685899856278</v>
       </c>
       <c r="J25" t="n">
         <v>199.9139299449369</v>
@@ -2439,10 +2439,10 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02780046601968817</v>
+        <v>0.0832718885486983</v>
       </c>
       <c r="I26" t="n">
-        <v>97.19414576199205</v>
+        <v>109.9617469881321</v>
       </c>
       <c r="J26" t="n">
         <v>200</v>
@@ -2517,10 +2517,10 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01946588280507898</v>
+        <v>0.004602625390390047</v>
       </c>
       <c r="I27" t="n">
-        <v>129.0985231723771</v>
+        <v>128.3332125535668</v>
       </c>
       <c r="J27" t="n">
         <v>200</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -2562,7 +2562,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2595,10 +2595,10 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01964014595132009</v>
+        <v>0.02779200000818176</v>
       </c>
       <c r="I28" t="n">
-        <v>127.1718885128103</v>
+        <v>134.8536674445885</v>
       </c>
       <c r="J28" t="n">
         <v>200</v>
@@ -2673,10 +2673,10 @@
         <v>200</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09615446603845537</v>
+        <v>0.1866389784049496</v>
       </c>
       <c r="I29" t="n">
-        <v>191.5075017030775</v>
+        <v>192.4134519048118</v>
       </c>
       <c r="J29" t="n">
         <v>200</v>
@@ -2751,10 +2751,10 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08151387564442503</v>
+        <v>0.1380433323432018</v>
       </c>
       <c r="I30" t="n">
-        <v>196.0386411854094</v>
+        <v>196.3947851007668</v>
       </c>
       <c r="J30" t="n">
         <v>200</v>
@@ -2829,10 +2829,10 @@
         <v>200</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09432961679395827</v>
+        <v>0.1477795792688235</v>
       </c>
       <c r="I31" t="n">
-        <v>194.2466814459454</v>
+        <v>194.2709642910985</v>
       </c>
       <c r="J31" t="n">
         <v>200</v>
@@ -2904,13 +2904,13 @@
         <v>7</v>
       </c>
       <c r="G32" t="n">
-        <v>167.192582466706</v>
+        <v>165.7546148305496</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3731776944879054</v>
+        <v>0.38785922921792</v>
       </c>
       <c r="I32" t="n">
-        <v>164.6748490827784</v>
+        <v>164.8758692530674</v>
       </c>
       <c r="J32" t="n">
         <v>188.3994774916149</v>
@@ -2985,10 +2985,10 @@
         <v>200</v>
       </c>
       <c r="H33" t="n">
-        <v>0.156967795367359</v>
+        <v>0.1535755243341698</v>
       </c>
       <c r="I33" t="n">
-        <v>170.4028696730483</v>
+        <v>170.1482256075269</v>
       </c>
       <c r="J33" t="n">
         <v>197.5602748361831</v>
@@ -3060,13 +3060,13 @@
         <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>175.6265418068303</v>
+        <v>174.6879222141001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3116447449667569</v>
+        <v>0.3296184931025303</v>
       </c>
       <c r="I34" t="n">
-        <v>169.6571057340244</v>
+        <v>171.4397998821392</v>
       </c>
       <c r="J34" t="n">
         <v>171.6084043022315</v>
@@ -3138,13 +3138,13 @@
         <v>15</v>
       </c>
       <c r="G35" t="n">
-        <v>105.0282170767762</v>
+        <v>108.3601558982242</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6403055072847207</v>
+        <v>0.9926778426100719</v>
       </c>
       <c r="I35" t="n">
-        <v>48.55849570822402</v>
+        <v>62.42552765573187</v>
       </c>
       <c r="J35" t="n">
         <v>128.6246318422078</v>
@@ -3184,11 +3184,11 @@
         </is>
       </c>
       <c r="U35" t="n">
-        <v>105.0282170767762</v>
+        <v>108.3601558982242</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=105.03% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=108.36% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3218,13 +3218,13 @@
         <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>161.9953762443956</v>
+        <v>156.7844328162785</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4122286060260453</v>
+        <v>0.6980743927875586</v>
       </c>
       <c r="I36" t="n">
-        <v>58.86670393327421</v>
+        <v>70.10918162979605</v>
       </c>
       <c r="J36" t="n">
         <v>170.6440396621451</v>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3296,13 +3296,13 @@
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>149.3030044507669</v>
+        <v>142.6549908394647</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6340439810854436</v>
+        <v>0.7294146855502518</v>
       </c>
       <c r="I37" t="n">
-        <v>60.32903496111531</v>
+        <v>69.25953978081323</v>
       </c>
       <c r="J37" t="n">
         <v>162.0004203901676</v>
@@ -3374,13 +3374,13 @@
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>191.9919619009012</v>
+        <v>199.6217616830302</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4533242349898883</v>
+        <v>0.3370447620534833</v>
       </c>
       <c r="I38" t="n">
-        <v>164.4263244057969</v>
+        <v>162.149087371204</v>
       </c>
       <c r="J38" t="n">
         <v>193.5392151146532</v>
@@ -3452,13 +3452,13 @@
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>198.5118901369247</v>
+        <v>200</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1737669757217708</v>
+        <v>0.1285627026425347</v>
       </c>
       <c r="I39" t="n">
-        <v>170.2041702191862</v>
+        <v>165.7621571068165</v>
       </c>
       <c r="J39" t="n">
         <v>199.1462918111721</v>
@@ -3530,13 +3530,13 @@
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>197.8503046852848</v>
+        <v>200</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2175630299201529</v>
+        <v>0.1607786834568675</v>
       </c>
       <c r="I40" t="n">
-        <v>165.7522199768573</v>
+        <v>163.618905219222</v>
       </c>
       <c r="J40" t="n">
         <v>199.5885882473661</v>
@@ -3608,13 +3608,13 @@
         <v>47</v>
       </c>
       <c r="G41" t="n">
-        <v>87.77044360060759</v>
+        <v>82.11866101265029</v>
       </c>
       <c r="H41" t="n">
-        <v>1.856873350730323</v>
+        <v>1.598833157227979</v>
       </c>
       <c r="I41" t="n">
-        <v>127.4617865350128</v>
+        <v>132.9108801179189</v>
       </c>
       <c r="J41" t="n">
         <v>91.67853884817875</v>
@@ -3654,11 +3654,11 @@
         </is>
       </c>
       <c r="U41" t="n">
-        <v>87.77044360060759</v>
+        <v>82.11866101265029</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=87.77% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=82.12% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3688,13 +3688,13 @@
         <v>25</v>
       </c>
       <c r="G42" t="n">
-        <v>113.7548643964564</v>
+        <v>109.6033369316858</v>
       </c>
       <c r="H42" t="n">
-        <v>1.223731755047448</v>
+        <v>1.06863407789476</v>
       </c>
       <c r="I42" t="n">
-        <v>139.5371944473096</v>
+        <v>144.2379256407503</v>
       </c>
       <c r="J42" t="n">
         <v>154.5839114750662</v>
@@ -3734,11 +3734,11 @@
         </is>
       </c>
       <c r="U42" t="n">
-        <v>113.7548643964564</v>
+        <v>109.6033369316858</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=113.75% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=109.60% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3768,13 +3768,13 @@
         <v>22</v>
       </c>
       <c r="G43" t="n">
-        <v>91.31975786598234</v>
+        <v>87.61246286752178</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9782084518115962</v>
+        <v>0.8606773829398876</v>
       </c>
       <c r="I43" t="n">
-        <v>137.8269504556986</v>
+        <v>143.2356557138082</v>
       </c>
       <c r="J43" t="n">
         <v>129.2210590644231</v>
@@ -3814,11 +3814,11 @@
         </is>
       </c>
       <c r="U43" t="n">
-        <v>91.31975786598234</v>
+        <v>87.61246286752178</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=91.32% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=87.61% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3848,13 +3848,13 @@
         <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>101.541216978027</v>
+        <v>96.02426038457011</v>
       </c>
       <c r="H44" t="n">
-        <v>3.270011438578409</v>
+        <v>2.811469877005802</v>
       </c>
       <c r="I44" t="n">
-        <v>101.902133963665</v>
+        <v>90.69108260489389</v>
       </c>
       <c r="J44" t="n">
         <v>113.6529259973059</v>
@@ -3894,11 +3894,11 @@
         </is>
       </c>
       <c r="U44" t="n">
-        <v>101.541216978027</v>
+        <v>96.02426038457011</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=101.54% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=96.02% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3928,13 +3928,13 @@
         <v>27</v>
       </c>
       <c r="G45" t="n">
-        <v>116.1460451702141</v>
+        <v>102.4367406023931</v>
       </c>
       <c r="H45" t="n">
-        <v>2.564017877299051</v>
+        <v>1.47241398353088</v>
       </c>
       <c r="I45" t="n">
-        <v>133.2410714461222</v>
+        <v>133.3421874706413</v>
       </c>
       <c r="J45" t="n">
         <v>138.8865780666307</v>
@@ -3974,11 +3974,11 @@
         </is>
       </c>
       <c r="U45" t="n">
-        <v>116.1460451702141</v>
+        <v>102.4367406023931</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=116.15% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=102.44% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4008,13 +4008,13 @@
         <v>17</v>
       </c>
       <c r="G46" t="n">
-        <v>140.3897249540533</v>
+        <v>134.8495847933821</v>
       </c>
       <c r="H46" t="n">
-        <v>2.53501087439491</v>
+        <v>1.94188163307336</v>
       </c>
       <c r="I46" t="n">
-        <v>129.1401202444324</v>
+        <v>124.5635906347636</v>
       </c>
       <c r="J46" t="n">
         <v>155.5388593759895</v>
@@ -4054,11 +4054,11 @@
         </is>
       </c>
       <c r="U46" t="n">
-        <v>140.3897249540533</v>
+        <v>134.8495847933821</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=140.39% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=134.85% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4088,13 +4088,13 @@
         <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>195.9411133670229</v>
+        <v>197.1734011497229</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1636167997295013</v>
+        <v>0.1529803815317455</v>
       </c>
       <c r="I47" t="n">
-        <v>52.02932925897922</v>
+        <v>68.7708518238762</v>
       </c>
       <c r="J47" t="n">
         <v>195.5685574757462</v>
@@ -4166,13 +4166,13 @@
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>197.4116289114259</v>
+        <v>198.4050298288979</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1238703056407061</v>
+        <v>0.1142571312560468</v>
       </c>
       <c r="I48" t="n">
-        <v>75.82494372432545</v>
+        <v>86.09499988689549</v>
       </c>
       <c r="J48" t="n">
         <v>198.5330491254405</v>
@@ -4247,10 +4247,10 @@
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02509264972644333</v>
+        <v>0.03928420848952716</v>
       </c>
       <c r="I49" t="n">
-        <v>67.54170898302603</v>
+        <v>78.24471458494588</v>
       </c>
       <c r="J49" t="n">
         <v>200</v>
@@ -4322,13 +4322,13 @@
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>194.3911602673957</v>
+        <v>195.8965903086375</v>
       </c>
       <c r="H50" t="n">
-        <v>1.518323311321763</v>
+        <v>1.219447449788111</v>
       </c>
       <c r="I50" t="n">
-        <v>162.6912701840232</v>
+        <v>165.7288014065556</v>
       </c>
       <c r="J50" t="n">
         <v>199.5486379903699</v>
@@ -4400,13 +4400,13 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>194.7647831852421</v>
+        <v>197.4072044927651</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7618632865622107</v>
+        <v>0.5937166551583655</v>
       </c>
       <c r="I51" t="n">
-        <v>169.9274838481079</v>
+        <v>167.1930514137077</v>
       </c>
       <c r="J51" t="n">
         <v>199.4865823478398</v>
@@ -4478,13 +4478,13 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>193.9165959732693</v>
+        <v>194.825835107561</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8615909360317315</v>
+        <v>0.7787430331267305</v>
       </c>
       <c r="I52" t="n">
-        <v>174.432365021141</v>
+        <v>169.1638840881747</v>
       </c>
       <c r="J52" t="n">
         <v>199.8575276644268</v>
@@ -4556,13 +4556,13 @@
         <v>2128</v>
       </c>
       <c r="G53" t="n">
-        <v>20.26471065115279</v>
+        <v>23.24265921886086</v>
       </c>
       <c r="H53" t="n">
-        <v>23.59328463933557</v>
+        <v>27.60851280394742</v>
       </c>
       <c r="I53" t="n">
-        <v>35.23746831954708</v>
+        <v>27.58321985589428</v>
       </c>
       <c r="J53" t="n">
         <v>20.44901503425639</v>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -4602,11 +4602,11 @@
         </is>
       </c>
       <c r="U53" t="n">
-        <v>20.26471065115279</v>
+        <v>20.44901503425639</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=20.26% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=20.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4636,13 +4636,13 @@
         <v>1000</v>
       </c>
       <c r="G54" t="n">
-        <v>21.78990331830676</v>
+        <v>21.83206715412024</v>
       </c>
       <c r="H54" t="n">
-        <v>12.18529853018219</v>
+        <v>12.4738250460123</v>
       </c>
       <c r="I54" t="n">
-        <v>38.4591918317379</v>
+        <v>30.20609014595014</v>
       </c>
       <c r="J54" t="n">
         <v>21.5307402945977</v>
@@ -4716,13 +4716,13 @@
         <v>1122</v>
       </c>
       <c r="G55" t="n">
-        <v>25.35547688070321</v>
+        <v>24.56807003457765</v>
       </c>
       <c r="H55" t="n">
-        <v>14.64653986540293</v>
+        <v>14.35624950110909</v>
       </c>
       <c r="I55" t="n">
-        <v>38.25160771522186</v>
+        <v>31.0709119837712</v>
       </c>
       <c r="J55" t="n">
         <v>23.26637498008379</v>
@@ -4796,13 +4796,13 @@
         <v>64</v>
       </c>
       <c r="G56" t="n">
-        <v>74.37701734933476</v>
+        <v>50.87017832092096</v>
       </c>
       <c r="H56" t="n">
-        <v>2.979831085540594</v>
+        <v>1.721520255055763</v>
       </c>
       <c r="I56" t="n">
-        <v>154.1439500713238</v>
+        <v>158.6050847963975</v>
       </c>
       <c r="J56" t="n">
         <v>60.38041763078138</v>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -4842,11 +4842,11 @@
         </is>
       </c>
       <c r="U56" t="n">
-        <v>60.38041763078138</v>
+        <v>50.87017832092096</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=60.38% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=50.87% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4876,13 +4876,13 @@
         <v>30</v>
       </c>
       <c r="G57" t="n">
-        <v>99.24117228272365</v>
+        <v>89.45073653074309</v>
       </c>
       <c r="H57" t="n">
-        <v>1.645033028339421</v>
+        <v>1.046812585803582</v>
       </c>
       <c r="I57" t="n">
-        <v>164.0555422208552</v>
+        <v>161.5065017675632</v>
       </c>
       <c r="J57" t="n">
         <v>114.7616231997743</v>
@@ -4922,11 +4922,11 @@
         </is>
       </c>
       <c r="U57" t="n">
-        <v>99.24117228272365</v>
+        <v>89.45073653074309</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=99.24% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=89.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4956,13 +4956,13 @@
         <v>34</v>
       </c>
       <c r="G58" t="n">
-        <v>94.48969926947952</v>
+        <v>101.1230093879027</v>
       </c>
       <c r="H58" t="n">
-        <v>1.696695370092706</v>
+        <v>1.313375448207419</v>
       </c>
       <c r="I58" t="n">
-        <v>158.4722608607674</v>
+        <v>161.0349167497434</v>
       </c>
       <c r="J58" t="n">
         <v>105.6303668976963</v>
@@ -5002,11 +5002,11 @@
         </is>
       </c>
       <c r="U58" t="n">
-        <v>94.48969926947952</v>
+        <v>101.1230093879027</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=94.49% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=101.12% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5036,13 +5036,13 @@
         <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>199.4821021973625</v>
+        <v>198.4585215841297</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2298717867783556</v>
+        <v>0.2287940483799308</v>
       </c>
       <c r="I59" t="n">
-        <v>163.442478475025</v>
+        <v>165.3309864977213</v>
       </c>
       <c r="J59" t="n">
         <v>192.5368174319365</v>
@@ -5114,13 +5114,13 @@
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>197.7007515643313</v>
+        <v>194.2894579019483</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1727165705253666</v>
+        <v>0.192270851063556</v>
       </c>
       <c r="I60" t="n">
-        <v>179.6544870721095</v>
+        <v>178.4437449361936</v>
       </c>
       <c r="J60" t="n">
         <v>198.6597355840884</v>
@@ -5192,13 +5192,13 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>199.9502411083014</v>
+        <v>198.4172888733546</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0745902904045261</v>
+        <v>0.1103024224920047</v>
       </c>
       <c r="I61" t="n">
-        <v>178.3754768379913</v>
+        <v>177.7053649160375</v>
       </c>
       <c r="J61" t="n">
         <v>198.3975506268872</v>
@@ -5270,13 +5270,13 @@
         <v>14</v>
       </c>
       <c r="G62" t="n">
-        <v>128.8719310283875</v>
+        <v>131.3991370717231</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7572694217418114</v>
+        <v>0.8216753045727233</v>
       </c>
       <c r="I62" t="n">
-        <v>51.86246745886869</v>
+        <v>66.55440226622002</v>
       </c>
       <c r="J62" t="n">
         <v>131.2644356700371</v>
@@ -5307,7 +5307,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -5316,11 +5316,11 @@
         </is>
       </c>
       <c r="U62" t="n">
-        <v>128.8719310283875</v>
+        <v>131.2644356700371</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=128.87% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=131.26% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5350,13 +5350,13 @@
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>154.6663812011903</v>
+        <v>162.6051633809513</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4837828153102234</v>
+        <v>0.4814538317421231</v>
       </c>
       <c r="I63" t="n">
-        <v>69.84803023883232</v>
+        <v>81.74557255773445</v>
       </c>
       <c r="J63" t="n">
         <v>160.5762472922584</v>
@@ -5428,13 +5428,13 @@
         <v>7</v>
       </c>
       <c r="G64" t="n">
-        <v>156.9060988936143</v>
+        <v>169.1165828986423</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6365528514939038</v>
+        <v>0.5602471188428393</v>
       </c>
       <c r="I64" t="n">
-        <v>72.92360982323459</v>
+        <v>78.0870900496615</v>
       </c>
       <c r="J64" t="n">
         <v>165.4971729021378</v>
@@ -5506,13 +5506,13 @@
         <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>172.7342912125195</v>
+        <v>174.9621849565533</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5281176484570876</v>
+        <v>0.6906981302002645</v>
       </c>
       <c r="I65" t="n">
-        <v>124.1398173354868</v>
+        <v>130.2538165104266</v>
       </c>
       <c r="J65" t="n">
         <v>188.6285607672464</v>
@@ -5584,13 +5584,13 @@
         <v>2</v>
       </c>
       <c r="G66" t="n">
-        <v>193.5182683795834</v>
+        <v>189.1575825432529</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2457881406423402</v>
+        <v>0.2719073590086947</v>
       </c>
       <c r="I66" t="n">
-        <v>146.9871894171194</v>
+        <v>146.8781158240608</v>
       </c>
       <c r="J66" t="n">
         <v>193.2466259789231</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -5632,7 +5632,7 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5662,13 +5662,13 @@
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>191.7047398007156</v>
+        <v>195.2253355795644</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3384995990865677</v>
+        <v>0.3983883461880737</v>
       </c>
       <c r="I67" t="n">
-        <v>137.6516466078508</v>
+        <v>145.9438817861322</v>
       </c>
       <c r="J67" t="n">
         <v>199.3097191502</v>
@@ -5740,13 +5740,13 @@
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>199.988140539529</v>
+        <v>200</v>
       </c>
       <c r="H68" t="n">
-        <v>0.06134600670915952</v>
+        <v>0.06428887613126047</v>
       </c>
       <c r="I68" t="n">
-        <v>183.5383709430125</v>
+        <v>185.5263813670961</v>
       </c>
       <c r="J68" t="n">
         <v>199.7828034264477</v>
@@ -5818,13 +5818,13 @@
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>198.1317768745953</v>
+        <v>197.3456030435345</v>
       </c>
       <c r="H69" t="n">
-        <v>0.08121093263600343</v>
+        <v>0.1573124460660443</v>
       </c>
       <c r="I69" t="n">
-        <v>171.5447439761989</v>
+        <v>176.5523739818266</v>
       </c>
       <c r="J69" t="n">
         <v>199.3873217860459</v>
@@ -5899,10 +5899,10 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01778981153364209</v>
+        <v>0.1072454671372258</v>
       </c>
       <c r="I70" t="n">
-        <v>188.453973372859</v>
+        <v>188.7537432880503</v>
       </c>
       <c r="J70" t="n">
         <v>200</v>
@@ -5974,13 +5974,13 @@
         <v>84</v>
       </c>
       <c r="G71" t="n">
-        <v>57.37693578719302</v>
+        <v>45.82204069402005</v>
       </c>
       <c r="H71" t="n">
-        <v>2.825184477639819</v>
+        <v>2.038774642227337</v>
       </c>
       <c r="I71" t="n">
-        <v>143.4057585362926</v>
+        <v>129.9990806504396</v>
       </c>
       <c r="J71" t="n">
         <v>181.9880034485936</v>
@@ -6020,11 +6020,11 @@
         </is>
       </c>
       <c r="U71" t="n">
-        <v>57.37693578719302</v>
+        <v>45.82204069402005</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=57.38% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=45.82% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6054,13 +6054,13 @@
         <v>35</v>
       </c>
       <c r="G72" t="n">
-        <v>91.0942949438804</v>
+        <v>88.75328127330114</v>
       </c>
       <c r="H72" t="n">
-        <v>1.574592744679023</v>
+        <v>1.273751500298519</v>
       </c>
       <c r="I72" t="n">
-        <v>151.0433307550491</v>
+        <v>135.1163038802778</v>
       </c>
       <c r="J72" t="n">
         <v>97.00281078314966</v>
@@ -6100,11 +6100,11 @@
         </is>
       </c>
       <c r="U72" t="n">
-        <v>91.0942949438804</v>
+        <v>88.75328127330114</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=91.09% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=88.75% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6134,13 +6134,13 @@
         <v>50</v>
       </c>
       <c r="G73" t="n">
-        <v>66.88932169454627</v>
+        <v>60.37376690297306</v>
       </c>
       <c r="H73" t="n">
-        <v>1.833647952485144</v>
+        <v>1.423320526030519</v>
       </c>
       <c r="I73" t="n">
-        <v>148.5993365374143</v>
+        <v>144.4569542682877</v>
       </c>
       <c r="J73" t="n">
         <v>167.6451026349307</v>
@@ -6180,11 +6180,11 @@
         </is>
       </c>
       <c r="U73" t="n">
-        <v>66.88932169454627</v>
+        <v>60.37376690297306</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=66.89% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=60.37% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6214,13 +6214,13 @@
         <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>168.5747304100348</v>
+        <v>170.8932475762028</v>
       </c>
       <c r="H74" t="n">
-        <v>2.582846452563731</v>
+        <v>1.090117710506654</v>
       </c>
       <c r="I74" t="n">
-        <v>148.9425712788151</v>
+        <v>150.4930337580551</v>
       </c>
       <c r="J74" t="n">
         <v>187.0298527328072</v>
@@ -6292,13 +6292,13 @@
         <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>168.2545421044971</v>
+        <v>178.8783298006462</v>
       </c>
       <c r="H75" t="n">
-        <v>1.16053340835048</v>
+        <v>0.5510931143417461</v>
       </c>
       <c r="I75" t="n">
-        <v>157.2380343536269</v>
+        <v>156.7678944986594</v>
       </c>
       <c r="J75" t="n">
         <v>196.6160780833582</v>
@@ -6370,13 +6370,13 @@
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>175.6880157321164</v>
+        <v>184.7079129050776</v>
       </c>
       <c r="H76" t="n">
-        <v>1.531534735446058</v>
+        <v>0.6694985058293008</v>
       </c>
       <c r="I76" t="n">
-        <v>154.9841830576604</v>
+        <v>155.145394665424</v>
       </c>
       <c r="J76" t="n">
         <v>195.1948412340681</v>
@@ -6448,13 +6448,13 @@
         <v>361</v>
       </c>
       <c r="G77" t="n">
-        <v>46.69234462013655</v>
+        <v>50.23937633796256</v>
       </c>
       <c r="H77" t="n">
-        <v>6.788620896340505</v>
+        <v>7.13896712350043</v>
       </c>
       <c r="I77" t="n">
-        <v>77.76772218573589</v>
+        <v>88.01776519136712</v>
       </c>
       <c r="J77" t="n">
         <v>37.10004537508804</v>
@@ -6528,13 +6528,13 @@
         <v>173</v>
       </c>
       <c r="G78" t="n">
-        <v>48.26514541284195</v>
+        <v>48.17126433890939</v>
       </c>
       <c r="H78" t="n">
-        <v>3.613344121230134</v>
+        <v>3.606407033882522</v>
       </c>
       <c r="I78" t="n">
-        <v>103.5437500854655</v>
+        <v>111.0836198476808</v>
       </c>
       <c r="J78" t="n">
         <v>49.13942155356582</v>
@@ -6574,11 +6574,11 @@
         </is>
       </c>
       <c r="U78" t="n">
-        <v>48.26514541284195</v>
+        <v>48.17126433890939</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=48.27% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=48.17% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6608,13 +6608,13 @@
         <v>188</v>
       </c>
       <c r="G79" t="n">
-        <v>52.91222566319724</v>
+        <v>54.83559803209809</v>
       </c>
       <c r="H79" t="n">
-        <v>3.864661196179704</v>
+        <v>4.029387121230872</v>
       </c>
       <c r="I79" t="n">
-        <v>102.5016657415887</v>
+        <v>108.761990389384</v>
       </c>
       <c r="J79" t="n">
         <v>36.89186308680129</v>
@@ -6688,13 +6688,13 @@
         <v>548</v>
       </c>
       <c r="G80" t="n">
-        <v>142.0473293234183</v>
+        <v>123.0231711982555</v>
       </c>
       <c r="H80" t="n">
-        <v>24.73559830907586</v>
+        <v>23.17411216716189</v>
       </c>
       <c r="I80" t="n">
-        <v>180.9937478063148</v>
+        <v>178.6234719835765</v>
       </c>
       <c r="J80" t="n">
         <v>148.3561506538706</v>
@@ -6734,11 +6734,11 @@
         </is>
       </c>
       <c r="U80" t="n">
-        <v>142.0473293234183</v>
+        <v>123.0231711982555</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=142.05% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=123.02% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6768,13 +6768,13 @@
         <v>255</v>
       </c>
       <c r="G81" t="n">
-        <v>127.6155198807104</v>
+        <v>105.9164731762228</v>
       </c>
       <c r="H81" t="n">
-        <v>10.89448015320569</v>
+        <v>9.934381053416464</v>
       </c>
       <c r="I81" t="n">
-        <v>185.5191244575439</v>
+        <v>184.0754328470002</v>
       </c>
       <c r="J81" t="n">
         <v>137.2064188235088</v>
@@ -6814,11 +6814,11 @@
         </is>
       </c>
       <c r="U81" t="n">
-        <v>127.6155198807104</v>
+        <v>105.9164731762228</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=127.62% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=105.92% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6848,13 +6848,13 @@
         <v>293</v>
       </c>
       <c r="G82" t="n">
-        <v>124.3198054769538</v>
+        <v>100.966746296182</v>
       </c>
       <c r="H82" t="n">
-        <v>12.65118418611661</v>
+        <v>11.50285758326346</v>
       </c>
       <c r="I82" t="n">
-        <v>186.2973802760101</v>
+        <v>184.4099560122273</v>
       </c>
       <c r="J82" t="n">
         <v>145.1472793964314</v>
@@ -6894,11 +6894,11 @@
         </is>
       </c>
       <c r="U82" t="n">
-        <v>124.3198054769538</v>
+        <v>100.966746296182</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=124.32% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=100.97% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6928,13 +6928,13 @@
         <v>362</v>
       </c>
       <c r="G83" t="n">
-        <v>35.45935764754714</v>
+        <v>39.45432954365923</v>
       </c>
       <c r="H83" t="n">
-        <v>6.299557206056292</v>
+        <v>6.859210293533699</v>
       </c>
       <c r="I83" t="n">
-        <v>88.04980557911651</v>
+        <v>90.64868701686645</v>
       </c>
       <c r="J83" t="n">
         <v>47.56092545874292</v>
@@ -6974,11 +6974,11 @@
         </is>
       </c>
       <c r="U83" t="n">
-        <v>35.45935764754714</v>
+        <v>39.45432954365923</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=35.46% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=39.45% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7008,13 +7008,13 @@
         <v>162</v>
       </c>
       <c r="G84" t="n">
-        <v>32.38454879714672</v>
+        <v>35.95489773850942</v>
       </c>
       <c r="H84" t="n">
-        <v>2.590604588219051</v>
+        <v>2.811982073726269</v>
       </c>
       <c r="I84" t="n">
-        <v>100.4914466151705</v>
+        <v>101.7188700792664</v>
       </c>
       <c r="J84" t="n">
         <v>46.15812962490158</v>
@@ -7054,11 +7054,11 @@
         </is>
       </c>
       <c r="U84" t="n">
-        <v>32.38454879714672</v>
+        <v>35.95489773850942</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=32.38% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=35.95% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7088,13 +7088,13 @@
         <v>199</v>
       </c>
       <c r="G85" t="n">
-        <v>45.66073922769827</v>
+        <v>51.40282038299348</v>
       </c>
       <c r="H85" t="n">
-        <v>4.349422253201568</v>
+        <v>4.813353122630911</v>
       </c>
       <c r="I85" t="n">
-        <v>109.9471447641292</v>
+        <v>104.3279851349203</v>
       </c>
       <c r="J85" t="n">
         <v>55.36256686407579</v>
@@ -7134,11 +7134,11 @@
         </is>
       </c>
       <c r="U85" t="n">
-        <v>45.66073922769827</v>
+        <v>51.40282038299348</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=45.66% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=51.40% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7168,13 +7168,13 @@
         <v>33</v>
       </c>
       <c r="G86" t="n">
-        <v>107.0051144969647</v>
+        <v>86.35855519846304</v>
       </c>
       <c r="H86" t="n">
-        <v>2.888610677610906</v>
+        <v>1.4945681015993</v>
       </c>
       <c r="I86" t="n">
-        <v>160.3842205944857</v>
+        <v>160.8111516104922</v>
       </c>
       <c r="J86" t="n">
         <v>119.2256744546712</v>
@@ -7214,11 +7214,11 @@
         </is>
       </c>
       <c r="U86" t="n">
-        <v>107.0051144969647</v>
+        <v>86.35855519846304</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=107.01% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=86.36% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7248,13 +7248,13 @@
         <v>17</v>
       </c>
       <c r="G87" t="n">
-        <v>113.1870478943641</v>
+        <v>118.3586643671639</v>
       </c>
       <c r="H87" t="n">
-        <v>1.165451077594584</v>
+        <v>0.8662622173625955</v>
       </c>
       <c r="I87" t="n">
-        <v>171.410316416684</v>
+        <v>169.6404464361343</v>
       </c>
       <c r="J87" t="n">
         <v>143.560216889931</v>
@@ -7294,11 +7294,11 @@
         </is>
       </c>
       <c r="U87" t="n">
-        <v>113.1870478943641</v>
+        <v>118.3586643671639</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=113.19% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=118.36% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7328,13 +7328,13 @@
         <v>15</v>
       </c>
       <c r="G88" t="n">
-        <v>131.8021709096804</v>
+        <v>127.0449845668104</v>
       </c>
       <c r="H88" t="n">
-        <v>1.686097704619301</v>
+        <v>1.143604954623066</v>
       </c>
       <c r="I88" t="n">
-        <v>169.0038464611843</v>
+        <v>167.2799949967896</v>
       </c>
       <c r="J88" t="n">
         <v>173.3382025272879</v>
@@ -7374,11 +7374,11 @@
         </is>
       </c>
       <c r="U88" t="n">
-        <v>131.8021709096804</v>
+        <v>127.0449845668104</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=131.80% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=127.04% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7411,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1027285104502795</v>
+        <v>0.1023614579503202</v>
       </c>
       <c r="I89" t="n">
         <v>200</v>
@@ -7485,7 +7485,7 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09027970940358052</v>
+        <v>0.02746008333061261</v>
       </c>
       <c r="I90" t="n">
         <v>200</v>
@@ -7559,7 +7559,7 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09273934624974439</v>
+        <v>0.09301406003964986</v>
       </c>
       <c r="I91" t="n">
         <v>200</v>
@@ -7630,13 +7630,13 @@
         <v>293</v>
       </c>
       <c r="G92" t="n">
-        <v>52.49086450360068</v>
+        <v>52.03867931340183</v>
       </c>
       <c r="H92" t="n">
-        <v>7.632350894424847</v>
+        <v>7.648850237162665</v>
       </c>
       <c r="I92" t="n">
-        <v>49.15109590531281</v>
+        <v>47.19125246366296</v>
       </c>
       <c r="J92" t="n">
         <v>53.86994196900773</v>
@@ -7676,11 +7676,11 @@
         </is>
       </c>
       <c r="U92" t="n">
-        <v>52.49086450360068</v>
+        <v>52.03867931340183</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=52.49% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=52.04% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7710,13 +7710,13 @@
         <v>140</v>
       </c>
       <c r="G93" t="n">
-        <v>49.38424923276131</v>
+        <v>52.79532864649887</v>
       </c>
       <c r="H93" t="n">
-        <v>3.469072830113385</v>
+        <v>3.654843053741769</v>
       </c>
       <c r="I93" t="n">
-        <v>60.93105560683724</v>
+        <v>56.67057405294103</v>
       </c>
       <c r="J93" t="n">
         <v>59.78155232420327</v>
@@ -7756,11 +7756,11 @@
         </is>
       </c>
       <c r="U93" t="n">
-        <v>49.38424923276131</v>
+        <v>52.79532864649887</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=49.38% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=52.80% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7790,13 +7790,13 @@
         <v>153</v>
       </c>
       <c r="G94" t="n">
-        <v>57.56739705044136</v>
+        <v>57.10510659288411</v>
       </c>
       <c r="H94" t="n">
-        <v>4.31128253527494</v>
+        <v>4.268456060466995</v>
       </c>
       <c r="I94" t="n">
-        <v>64.07712599234655</v>
+        <v>60.36683825363948</v>
       </c>
       <c r="J94" t="n">
         <v>52.69581648158714</v>
@@ -7870,13 +7870,13 @@
         <v>10</v>
       </c>
       <c r="G95" t="n">
-        <v>147.5935778029153</v>
+        <v>145.2656870067181</v>
       </c>
       <c r="H95" t="n">
-        <v>0.662334516860426</v>
+        <v>0.7158306497479658</v>
       </c>
       <c r="I95" t="n">
-        <v>152.3875262412586</v>
+        <v>152.0304599151261</v>
       </c>
       <c r="J95" t="n">
         <v>199.1922050178509</v>
@@ -7916,11 +7916,11 @@
         </is>
       </c>
       <c r="U95" t="n">
-        <v>147.5935778029153</v>
+        <v>145.2656870067181</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=147.59% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=145.27% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7950,13 +7950,13 @@
         <v>3</v>
       </c>
       <c r="G96" t="n">
-        <v>181.6843142825061</v>
+        <v>176.1932878216295</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3291270790645512</v>
+        <v>0.4196308764354335</v>
       </c>
       <c r="I96" t="n">
-        <v>158.9896824444987</v>
+        <v>155.4020478126902</v>
       </c>
       <c r="J96" t="n">
         <v>199.2513153043118</v>
@@ -8028,13 +8028,13 @@
         <v>7</v>
       </c>
       <c r="G97" t="n">
-        <v>166.6950640152984</v>
+        <v>161.5895969579176</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3995569831044574</v>
+        <v>0.432991156776099</v>
       </c>
       <c r="I97" t="n">
-        <v>157.2976315063829</v>
+        <v>159.5809636910691</v>
       </c>
       <c r="J97" t="n">
         <v>199.3614643125625</v>
@@ -8109,10 +8109,10 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.07575033617870201</v>
+        <v>0.1434930256603092</v>
       </c>
       <c r="I98" t="n">
-        <v>198.585723184526</v>
+        <v>198.561344495255</v>
       </c>
       <c r="J98" t="n">
         <v>200</v>
@@ -8183,10 +8183,10 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.04403257285937298</v>
+        <v>0.08714727738012426</v>
       </c>
       <c r="I99" t="n">
-        <v>198.7380283178126</v>
+        <v>198.6789577214581</v>
       </c>
       <c r="J99" t="n">
         <v>200</v>
@@ -8257,7 +8257,7 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0598529225883256</v>
+        <v>0.1272160571401307</v>
       </c>
       <c r="I100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:Y100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,20 +521,35 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>smape_real_nbglm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mae_real_nbglm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cv_smape_nbglm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>motor_productivo</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>criterio_seleccion</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>smape_ganador</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>justificacion</t>
         </is>
@@ -601,18 +616,27 @@
       <c r="R2" t="n">
         <v>199.5572761277739</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>200</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.047666304710546</v>
+      </c>
+      <c r="U2" t="n">
+        <v>194.9779461019607</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -679,18 +703,27 @@
       <c r="R3" t="n">
         <v>199.636475467609</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>200</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.0352297925787751</v>
+      </c>
+      <c r="U3" t="n">
+        <v>198.5158836242873</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -757,18 +790,27 @@
       <c r="R4" t="n">
         <v>199.5859359679221</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>200</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.03741817105613721</v>
+      </c>
+      <c r="U4" t="n">
+        <v>196.9436529554095</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -835,18 +877,27 @@
       <c r="R5" t="n">
         <v>193.7972259177366</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>199.2254908035844</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.1198320484669285</v>
+      </c>
+      <c r="U5" t="n">
+        <v>187.0400639517023</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -913,18 +964,27 @@
       <c r="R6" t="n">
         <v>193.2139428195562</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>198.400971319978</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.05977949533771661</v>
+      </c>
+      <c r="U6" t="n">
+        <v>198.9985835834048</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -991,18 +1051,27 @@
       <c r="R7" t="n">
         <v>190.8625800946274</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>199.7727927228824</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.06973172505380154</v>
+      </c>
+      <c r="U7" t="n">
+        <v>197.3279694158802</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -1069,20 +1138,29 @@
       <c r="R8" t="n">
         <v>172.894287988784</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>59.01081768196027</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.383893621127577</v>
+      </c>
+      <c r="U8" t="n">
+        <v>111.5676388698673</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>48.2035225269852</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=48.20% sobre 19 sem</t>
         </is>
@@ -1149,22 +1227,31 @@
       <c r="R9" t="n">
         <v>176.8647517474977</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>62.45968067597241</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.515713649482301</v>
+      </c>
+      <c r="U9" t="n">
+        <v>121.2492629006552</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U9" t="n">
-        <v>69.98966250353146</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE real=69.99% sobre 19 sem</t>
+      <c r="X9" t="n">
+        <v>62.45968067597241</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=62.46% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1229,20 +1316,29 @@
       <c r="R10" t="n">
         <v>168.5443712458804</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S10" t="n">
+        <v>60.49265913259512</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.901026720535735</v>
+      </c>
+      <c r="U10" t="n">
+        <v>114.746491150853</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>45.23277359273659</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=45.23% sobre 19 sem</t>
         </is>
@@ -1309,22 +1405,31 @@
       <c r="R11" t="n">
         <v>177.781032308345</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>127.3834750149388</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.5559937455885269</v>
+      </c>
+      <c r="U11" t="n">
+        <v>147.9725418621825</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U11" t="n">
-        <v>169.256431894795</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=169.26% sobre 19 sem</t>
+      <c r="X11" t="n">
+        <v>127.3834750149388</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=127.38% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1389,18 +1494,27 @@
       <c r="R12" t="n">
         <v>189.6908701459495</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>155.8692201644686</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4690080929408374</v>
+      </c>
+      <c r="U12" t="n">
+        <v>169.7722333133142</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -1467,18 +1581,27 @@
       <c r="R13" t="n">
         <v>188.2053733911598</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>166.1429368437917</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.3680900410091594</v>
+      </c>
+      <c r="U13" t="n">
+        <v>173.7069303697712</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -1545,20 +1668,29 @@
       <c r="R14" t="n">
         <v>186.0423288913966</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>75.78189336067067</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.656705421919318</v>
+      </c>
+      <c r="U14" t="n">
+        <v>130.2296761771863</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>68.18440924623016</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=68.18% sobre 19 sem</t>
         </is>
@@ -1625,20 +1757,29 @@
       <c r="R15" t="n">
         <v>186.4460938550808</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>76.52604808710842</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.336950864427592</v>
+      </c>
+      <c r="U15" t="n">
+        <v>131.9030800529592</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>68.63649638136945</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=68.64% sobre 19 sem</t>
         </is>
@@ -1705,22 +1846,31 @@
       <c r="R16" t="n">
         <v>186.1307414343702</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>108.4709234228671</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.318227811058774</v>
+      </c>
+      <c r="U16" t="n">
+        <v>133.2708900338696</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U16" t="n">
-        <v>121.4424954946124</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=121.44% sobre 19 sem</t>
+      <c r="X16" t="n">
+        <v>108.4709234228671</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=108.47% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -1785,18 +1935,27 @@
       <c r="R17" t="n">
         <v>197.0125798901019</v>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>198.6980564595817</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.06060324451992004</v>
+      </c>
+      <c r="U17" t="n">
+        <v>192.256373806382</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -1859,20 +2018,29 @@
       <c r="R18" t="n">
         <v>196.686324272832</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
+      <c r="S18" t="n">
+        <v>200</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5.358559373428652e-263</v>
+      </c>
+      <c r="U18" t="n">
+        <v>196.0211023092105</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1937,18 +2105,27 @@
       <c r="R19" t="n">
         <v>196.7488584326798</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>198.82015746588</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.06151385363938022</v>
+      </c>
+      <c r="U19" t="n">
+        <v>197.8046914283761</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -2011,18 +2188,27 @@
       <c r="R20" t="n">
         <v>200</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>200</v>
+      </c>
+      <c r="T20" t="n">
+        <v>7894.736842105263</v>
+      </c>
+      <c r="U20" t="n">
+        <v>200</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2085,18 +2271,27 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>200</v>
+      </c>
+      <c r="T21" t="n">
+        <v>18421.05263167506</v>
+      </c>
+      <c r="U21" t="n">
+        <v>200</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2159,20 +2354,29 @@
       <c r="R22" t="n">
         <v>200</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="n">
+        <v>200</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.38469284411295e-17</v>
+      </c>
+      <c r="U22" t="n">
+        <v>200</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2237,18 +2441,27 @@
       <c r="R23" t="n">
         <v>186.3774873978808</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>189.1502269944299</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.214788356206763</v>
+      </c>
+      <c r="U23" t="n">
+        <v>159.9263814945425</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -2315,18 +2528,27 @@
       <c r="R24" t="n">
         <v>185.3144083651474</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>192.5705904110226</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.127246183659518</v>
+      </c>
+      <c r="U24" t="n">
+        <v>166.4426133688291</v>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -2393,18 +2615,27 @@
       <c r="R25" t="n">
         <v>183.340259481936</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>199.5482494364765</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.142533101613901</v>
+      </c>
+      <c r="U25" t="n">
+        <v>180.6321027113416</v>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -2471,18 +2702,27 @@
       <c r="R26" t="n">
         <v>199.6509594119097</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>200</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.9017867897851561</v>
+      </c>
+      <c r="U26" t="n">
+        <v>183.6686755299509</v>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2549,18 +2789,27 @@
       <c r="R27" t="n">
         <v>199.779644487174</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>200</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.5530458220041397</v>
+      </c>
+      <c r="U27" t="n">
+        <v>192.722098187243</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2627,18 +2876,27 @@
       <c r="R28" t="n">
         <v>199.5411797194807</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S28" t="n">
+        <v>200</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.7508665704125755</v>
+      </c>
+      <c r="U28" t="n">
+        <v>184.9627687949149</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2705,18 +2963,27 @@
       <c r="R29" t="n">
         <v>199.9388941772115</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>200</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.03951542031433585</v>
+      </c>
+      <c r="U29" t="n">
+        <v>192.5799615112869</v>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2783,18 +3050,27 @@
       <c r="R30" t="n">
         <v>199.7754683359127</v>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S30" t="n">
+        <v>200</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.02591903960978625</v>
+      </c>
+      <c r="U30" t="n">
+        <v>198.9226798174336</v>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2861,18 +3137,27 @@
       <c r="R31" t="n">
         <v>199.9196066031173</v>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>200</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.01648866579845337</v>
+      </c>
+      <c r="U31" t="n">
+        <v>194.1597056483905</v>
+      </c>
+      <c r="V31" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2939,18 +3224,27 @@
       <c r="R32" t="n">
         <v>195.3761640213164</v>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S32" t="n">
+        <v>156.6987413005241</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.5793442316552549</v>
+      </c>
+      <c r="U32" t="n">
+        <v>173.3959783787531</v>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -3017,18 +3311,27 @@
       <c r="R33" t="n">
         <v>196.5601753860276</v>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S33" t="n">
+        <v>196.413504078234</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.3150697423847014</v>
+      </c>
+      <c r="U33" t="n">
+        <v>182.3083787234438</v>
+      </c>
+      <c r="V33" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -3095,18 +3398,27 @@
       <c r="R34" t="n">
         <v>195.2398047728465</v>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S34" t="n">
+        <v>166.4757146467686</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.3409276249292862</v>
+      </c>
+      <c r="U34" t="n">
+        <v>176.7243686471345</v>
+      </c>
+      <c r="V34" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
@@ -3173,20 +3485,29 @@
       <c r="R35" t="n">
         <v>185.853149170162</v>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S35" t="n">
+        <v>131.3760966488024</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.79261396959873</v>
+      </c>
+      <c r="U35" t="n">
+        <v>110.5529101365675</v>
+      </c>
+      <c r="V35" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U35" t="n">
+      <c r="X35" t="n">
         <v>108.3601558982242</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=108.36% sobre 19 sem</t>
         </is>
@@ -3253,18 +3574,27 @@
       <c r="R36" t="n">
         <v>187.2910306593169</v>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S36" t="n">
+        <v>163.8685222925315</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.141618918264861</v>
+      </c>
+      <c r="U36" t="n">
+        <v>118.8153464644226</v>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
@@ -3331,18 +3661,27 @@
       <c r="R37" t="n">
         <v>185.3862117422507</v>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S37" t="n">
+        <v>145.3573454334758</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.9968067490053601</v>
+      </c>
+      <c r="U37" t="n">
+        <v>110.8838400280787</v>
+      </c>
+      <c r="V37" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
@@ -3409,18 +3748,27 @@
       <c r="R38" t="n">
         <v>199.036270909302</v>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S38" t="n">
+        <v>184.4692848329074</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.3966684884236398</v>
+      </c>
+      <c r="U38" t="n">
+        <v>129.2920232398837</v>
+      </c>
+      <c r="V38" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -3487,18 +3835,27 @@
       <c r="R39" t="n">
         <v>199.0467638312102</v>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S39" t="n">
+        <v>194.1806375349233</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.2104870711844742</v>
+      </c>
+      <c r="U39" t="n">
+        <v>146.152525200624</v>
+      </c>
+      <c r="V39" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -3565,18 +3922,27 @@
       <c r="R40" t="n">
         <v>198.942356787496</v>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S40" t="n">
+        <v>194.3759123473405</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.2298943768714146</v>
+      </c>
+      <c r="U40" t="n">
+        <v>124.2002492905602</v>
+      </c>
+      <c r="V40" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -3643,22 +4009,31 @@
       <c r="R41" t="n">
         <v>198.8825072752037</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="n">
+        <v>73.34661585373087</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.068779849915095</v>
+      </c>
+      <c r="U41" t="n">
+        <v>124.7888620818299</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U41" t="n">
-        <v>82.11866101265029</v>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=82.12% sobre 19 sem</t>
+      <c r="X41" t="n">
+        <v>73.34661585373087</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=73.35% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3723,22 +4098,31 @@
       <c r="R42" t="n">
         <v>198.6803521667581</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="n">
+        <v>97.36275957055524</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0.5729920972582702</v>
+      </c>
+      <c r="U42" t="n">
+        <v>125.9010082864909</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U42" t="n">
-        <v>109.6033369316858</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=109.60% sobre 19 sem</t>
+      <c r="X42" t="n">
+        <v>97.36275957055524</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=97.36% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3803,22 +4187,31 @@
       <c r="R43" t="n">
         <v>198.9631246433146</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="n">
+        <v>82.93059261895746</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0.5788359418048948</v>
+      </c>
+      <c r="U43" t="n">
+        <v>126.6160396504699</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U43" t="n">
-        <v>87.61246286752178</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=87.61% sobre 19 sem</t>
+      <c r="X43" t="n">
+        <v>82.93059261895746</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=82.93% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3883,22 +4276,31 @@
       <c r="R44" t="n">
         <v>196.0447922196767</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="n">
+        <v>83.11287910207426</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.632134160643226</v>
+      </c>
+      <c r="U44" t="n">
+        <v>121.0188473841644</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U44" t="n">
-        <v>96.02426038457011</v>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=96.02% sobre 19 sem</t>
+      <c r="X44" t="n">
+        <v>83.11287910207426</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=83.11% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -3963,22 +4365,31 @@
       <c r="R45" t="n">
         <v>195.8311934408034</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="n">
+        <v>91.40918563383063</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0.7550130518360472</v>
+      </c>
+      <c r="U45" t="n">
+        <v>112.5504951429215</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U45" t="n">
-        <v>102.4367406023931</v>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=102.44% sobre 19 sem</t>
+      <c r="X45" t="n">
+        <v>91.40918563383063</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=91.41% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4043,22 +4454,31 @@
       <c r="R46" t="n">
         <v>196.1388328305384</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="n">
+        <v>126.0852506031915</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.09258897362871</v>
+      </c>
+      <c r="U46" t="n">
+        <v>125.7491255686458</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U46" t="n">
-        <v>134.8495847933821</v>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=134.85% sobre 19 sem</t>
+      <c r="X46" t="n">
+        <v>126.0852506031915</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=126.09% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4123,18 +4543,27 @@
       <c r="R47" t="n">
         <v>193.8459595711977</v>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S47" t="n">
+        <v>189.8391468171731</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0.8622159058568275</v>
+      </c>
+      <c r="U47" t="n">
+        <v>130.8486591703272</v>
+      </c>
+      <c r="V47" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -4201,18 +4630,27 @@
       <c r="R48" t="n">
         <v>192.3368460426438</v>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S48" t="n">
+        <v>191.1080046745255</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0.6834732548192755</v>
+      </c>
+      <c r="U48" t="n">
+        <v>148.2729860112375</v>
+      </c>
+      <c r="V48" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -4279,18 +4717,27 @@
       <c r="R49" t="n">
         <v>193.5695579772771</v>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S49" t="n">
+        <v>200</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.5964682706506903</v>
+      </c>
+      <c r="U49" t="n">
+        <v>141.2583029624075</v>
+      </c>
+      <c r="V49" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -4357,18 +4804,27 @@
       <c r="R50" t="n">
         <v>160.5521309789579</v>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S50" t="n">
+        <v>191.0159083039045</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.171392989508968</v>
+      </c>
+      <c r="U50" t="n">
+        <v>135.4400555181058</v>
+      </c>
+      <c r="V50" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -4435,18 +4891,27 @@
       <c r="R51" t="n">
         <v>165.5121650610737</v>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S51" t="n">
+        <v>189.9461906748481</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.461458145853869</v>
+      </c>
+      <c r="U51" t="n">
+        <v>151.1230387281904</v>
+      </c>
+      <c r="V51" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -4513,18 +4978,27 @@
       <c r="R52" t="n">
         <v>154.7555469695623</v>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S52" t="n">
+        <v>191.551320846184</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.141472433852223</v>
+      </c>
+      <c r="U52" t="n">
+        <v>133.8716916594558</v>
+      </c>
+      <c r="V52" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -4591,20 +5065,29 @@
       <c r="R53" t="n">
         <v>188.2648408233968</v>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S53" t="n">
+        <v>33.35473458934206</v>
+      </c>
+      <c r="T53" t="n">
+        <v>46.1343206529984</v>
+      </c>
+      <c r="U53" t="n">
+        <v>92.2349408254034</v>
+      </c>
+      <c r="V53" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U53" t="n">
+      <c r="X53" t="n">
         <v>20.44901503425639</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=20.45% sobre 19 sem</t>
         </is>
@@ -4671,20 +5154,29 @@
       <c r="R54" t="n">
         <v>187.9362468841497</v>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S54" t="n">
+        <v>34.11324738386026</v>
+      </c>
+      <c r="T54" t="n">
+        <v>22.26762956087289</v>
+      </c>
+      <c r="U54" t="n">
+        <v>91.67135817890519</v>
+      </c>
+      <c r="V54" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U54" t="n">
+      <c r="X54" t="n">
         <v>21.5307402945977</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=21.53% sobre 19 sem</t>
         </is>
@@ -4751,20 +5243,29 @@
       <c r="R55" t="n">
         <v>188.8384134033935</v>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S55" t="n">
+        <v>30.31248068057727</v>
+      </c>
+      <c r="T55" t="n">
+        <v>21.75927235930101</v>
+      </c>
+      <c r="U55" t="n">
+        <v>92.1901984902002</v>
+      </c>
+      <c r="V55" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U55" t="n">
+      <c r="X55" t="n">
         <v>23.26637498008379</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=23.27% sobre 19 sem</t>
         </is>
@@ -4831,22 +5332,31 @@
       <c r="R56" t="n">
         <v>197.7368060568652</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="n">
+        <v>44.67504455982316</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1.380595680498687</v>
+      </c>
+      <c r="U56" t="n">
+        <v>104.7066447751141</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U56" t="n">
-        <v>50.87017832092096</v>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=50.87% sobre 19 sem</t>
+      <c r="X56" t="n">
+        <v>44.67504455982316</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=44.68% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -4911,20 +5421,29 @@
       <c r="R57" t="n">
         <v>197.2831175654684</v>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S57" t="n">
+        <v>93.38885700918117</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0.8391190891061855</v>
+      </c>
+      <c r="U57" t="n">
+        <v>124.2225772452616</v>
+      </c>
+      <c r="V57" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U57" t="n">
+      <c r="X57" t="n">
         <v>89.45073653074309</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=89.45% sobre 19 sem</t>
         </is>
@@ -4991,22 +5510,31 @@
       <c r="R58" t="n">
         <v>197.6615055783608</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
+      <c r="S58" t="n">
+        <v>88.19208161899802</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.9554666528117263</v>
+      </c>
+      <c r="U58" t="n">
+        <v>111.9755139895278</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U58" t="n">
-        <v>101.1230093879027</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=101.12% sobre 19 sem</t>
+      <c r="X58" t="n">
+        <v>88.19208161899802</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=88.19% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5071,18 +5599,27 @@
       <c r="R59" t="n">
         <v>199.2894660635261</v>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S59" t="n">
+        <v>185.7921678432019</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.3605131591993669</v>
+      </c>
+      <c r="U59" t="n">
+        <v>167.6265476269683</v>
+      </c>
+      <c r="V59" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr">
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -5149,18 +5686,27 @@
       <c r="R60" t="n">
         <v>199.0965028052728</v>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S60" t="n">
+        <v>188.9577766873559</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0.2514451322102222</v>
+      </c>
+      <c r="U60" t="n">
+        <v>167.0169829765832</v>
+      </c>
+      <c r="V60" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr">
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
@@ -5227,18 +5773,27 @@
       <c r="R61" t="n">
         <v>199.3694289811982</v>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S61" t="n">
+        <v>194.4610071616202</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.1374148461663683</v>
+      </c>
+      <c r="U61" t="n">
+        <v>167.1297521794813</v>
+      </c>
+      <c r="V61" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr">
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -5305,22 +5860,31 @@
       <c r="R62" t="n">
         <v>188.4656733609786</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
+      <c r="S62" t="n">
+        <v>118.4075208684841</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0.9147199969677026</v>
+      </c>
+      <c r="U62" t="n">
+        <v>127.8730185036105</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U62" t="n">
-        <v>131.2644356700371</v>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE real=131.26% sobre 19 sem</t>
+      <c r="X62" t="n">
+        <v>118.4075208684841</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=118.41% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -5385,18 +5949,27 @@
       <c r="R63" t="n">
         <v>186.3893216158546</v>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S63" t="n">
+        <v>131.1240426073105</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0.5257290190575565</v>
+      </c>
+      <c r="U63" t="n">
+        <v>131.8859677830883</v>
+      </c>
+      <c r="V63" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr">
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -5463,18 +6036,27 @@
       <c r="R64" t="n">
         <v>191.0006997623111</v>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S64" t="n">
+        <v>144.1050038899509</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0.6735217199073611</v>
+      </c>
+      <c r="U64" t="n">
+        <v>132.574641557417</v>
+      </c>
+      <c r="V64" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr">
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -5541,18 +6123,27 @@
       <c r="R65" t="n">
         <v>191.9303948964172</v>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S65" t="n">
+        <v>163.1457219188228</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0.8506428596457795</v>
+      </c>
+      <c r="U65" t="n">
+        <v>113.9712651292745</v>
+      </c>
+      <c r="V65" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr">
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -5619,18 +6210,27 @@
       <c r="R66" t="n">
         <v>192.190104304547</v>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S66" t="n">
+        <v>183.0260032855074</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0.4989162885551428</v>
+      </c>
+      <c r="U66" t="n">
+        <v>118.44057480835</v>
+      </c>
+      <c r="V66" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="W66" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -5697,18 +6297,27 @@
       <c r="R67" t="n">
         <v>191.2393501485975</v>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S67" t="n">
+        <v>182.9206543630087</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.5825659356753343</v>
+      </c>
+      <c r="U67" t="n">
+        <v>116.630186356802</v>
+      </c>
+      <c r="V67" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="W67" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr">
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -5775,18 +6384,27 @@
       <c r="R68" t="n">
         <v>199.7672857698158</v>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S68" t="n">
+        <v>196.6829640048581</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0.2368618284134104</v>
+      </c>
+      <c r="U68" t="n">
+        <v>177.2448922419183</v>
+      </c>
+      <c r="V68" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="W68" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -5853,18 +6471,27 @@
       <c r="R69" t="n">
         <v>199.6130972886749</v>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S69" t="n">
+        <v>198.3286558355248</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0.1482711720901729</v>
+      </c>
+      <c r="U69" t="n">
+        <v>185.6695408532579</v>
+      </c>
+      <c r="V69" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="W69" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -5931,18 +6558,27 @@
       <c r="R70" t="n">
         <v>199.6974055100667</v>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S70" t="n">
+        <v>200</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0.1224972249654891</v>
+      </c>
+      <c r="U70" t="n">
+        <v>184.4638384017739</v>
+      </c>
+      <c r="V70" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="W70" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -6009,20 +6645,29 @@
       <c r="R71" t="n">
         <v>185.267595267154</v>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S71" t="n">
+        <v>56.26253696619978</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4.953444167374145</v>
+      </c>
+      <c r="U71" t="n">
+        <v>93.16202342284906</v>
+      </c>
+      <c r="V71" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="W71" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U71" t="n">
+      <c r="X71" t="n">
         <v>45.82204069402005</v>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=45.82% sobre 19 sem</t>
         </is>
@@ -6089,20 +6734,29 @@
       <c r="R72" t="n">
         <v>161.2927483340683</v>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S72" t="n">
+        <v>90.31026369645171</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2.188836707072257</v>
+      </c>
+      <c r="U72" t="n">
+        <v>104.036396201453</v>
+      </c>
+      <c r="V72" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr">
+      <c r="W72" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U72" t="n">
+      <c r="X72" t="n">
         <v>88.75328127330114</v>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=88.75% sobre 19 sem</t>
         </is>
@@ -6169,22 +6823,31 @@
       <c r="R73" t="n">
         <v>173.6314937555617</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
+      <c r="S73" t="n">
+        <v>60.23654364119692</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2.077975064835356</v>
+      </c>
+      <c r="U73" t="n">
+        <v>104.3951484726403</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U73" t="n">
-        <v>60.37376690297306</v>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=60.37% sobre 19 sem</t>
+      <c r="X73" t="n">
+        <v>60.23654364119692</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=60.24% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6249,18 +6912,27 @@
       <c r="R74" t="n">
         <v>193.1141809259393</v>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S74" t="n">
+        <v>158.6719930560306</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0.6877511468803854</v>
+      </c>
+      <c r="U74" t="n">
+        <v>113.155914904339</v>
+      </c>
+      <c r="V74" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr">
+      <c r="W74" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr">
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
@@ -6327,18 +6999,27 @@
       <c r="R75" t="n">
         <v>193.2892416279341</v>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S75" t="n">
+        <v>166.46519558855</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0.4770796541136497</v>
+      </c>
+      <c r="U75" t="n">
+        <v>110.9447640026735</v>
+      </c>
+      <c r="V75" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="W75" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr">
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
@@ -6405,18 +7086,27 @@
       <c r="R76" t="n">
         <v>192.8448970866968</v>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S76" t="n">
+        <v>173.9560715580791</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0.4352548070728992</v>
+      </c>
+      <c r="U76" t="n">
+        <v>118.0223455785753</v>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="W76" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr">
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -6483,22 +7173,31 @@
       <c r="R77" t="n">
         <v>138.4032392925817</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
+      <c r="S77" t="n">
+        <v>27.81798992196951</v>
+      </c>
+      <c r="T77" t="n">
+        <v>6.159508178917418</v>
+      </c>
+      <c r="U77" t="n">
+        <v>118.3894561520081</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U77" t="n">
-        <v>37.10004537508804</v>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE real=37.10% sobre 19 sem</t>
+      <c r="X77" t="n">
+        <v>27.81798992196951</v>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=27.82% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6563,22 +7262,31 @@
       <c r="R78" t="n">
         <v>82.9912432467173</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
+      <c r="S78" t="n">
+        <v>26.49401781885958</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.984444425214001</v>
+      </c>
+      <c r="U78" t="n">
+        <v>124.390269119479</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U78" t="n">
-        <v>48.17126433890939</v>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=48.17% sobre 19 sem</t>
+      <c r="X78" t="n">
+        <v>26.49401781885958</v>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=26.49% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6643,22 +7351,31 @@
       <c r="R79" t="n">
         <v>148.0195847609927</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
+      <c r="S79" t="n">
+        <v>29.65147043752832</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3.333330867224542</v>
+      </c>
+      <c r="U79" t="n">
+        <v>120.3982350383182</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U79" t="n">
-        <v>36.89186308680129</v>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE real=36.89% sobre 19 sem</t>
+      <c r="X79" t="n">
+        <v>29.65147043752832</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=29.65% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6723,22 +7440,31 @@
       <c r="R80" t="n">
         <v>172.7461511452186</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
+      <c r="S80" t="n">
+        <v>57.96095518018842</v>
+      </c>
+      <c r="T80" t="n">
+        <v>32.31025324996108</v>
+      </c>
+      <c r="U80" t="n">
+        <v>175.912448276349</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U80" t="n">
-        <v>123.0231711982555</v>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=123.02% sobre 19 sem</t>
+      <c r="X80" t="n">
+        <v>57.96095518018842</v>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=57.96% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6803,22 +7529,31 @@
       <c r="R81" t="n">
         <v>163.1536185700502</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
+      <c r="S81" t="n">
+        <v>54.90681100609219</v>
+      </c>
+      <c r="T81" t="n">
+        <v>8.290467964049277</v>
+      </c>
+      <c r="U81" t="n">
+        <v>172.1596497720207</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U81" t="n">
-        <v>105.9164731762228</v>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=105.92% sobre 19 sem</t>
+      <c r="X81" t="n">
+        <v>54.90681100609219</v>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=54.91% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6883,22 +7618,31 @@
       <c r="R82" t="n">
         <v>166.6060177059153</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
+      <c r="S82" t="n">
+        <v>42.97019417453158</v>
+      </c>
+      <c r="T82" t="n">
+        <v>10.49981439198042</v>
+      </c>
+      <c r="U82" t="n">
+        <v>176.1888335684919</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U82" t="n">
-        <v>100.966746296182</v>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=100.97% sobre 19 sem</t>
+      <c r="X82" t="n">
+        <v>42.97019417453158</v>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=42.97% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -6963,20 +7707,29 @@
       <c r="R83" t="n">
         <v>103.1343264142703</v>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S83" t="n">
+        <v>49.1159143607714</v>
+      </c>
+      <c r="T83" t="n">
+        <v>11.98994874908024</v>
+      </c>
+      <c r="U83" t="n">
+        <v>103.3034448942146</v>
+      </c>
+      <c r="V83" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr">
+      <c r="W83" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U83" t="n">
+      <c r="X83" t="n">
         <v>39.45432954365923</v>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=39.45% sobre 19 sem</t>
         </is>
@@ -7043,20 +7796,29 @@
       <c r="R84" t="n">
         <v>98.74789164115032</v>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S84" t="n">
+        <v>47.26168944743522</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4.879463558855073</v>
+      </c>
+      <c r="U84" t="n">
+        <v>110.607240444147</v>
+      </c>
+      <c r="V84" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr">
+      <c r="W84" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U84" t="n">
+      <c r="X84" t="n">
         <v>35.95489773850942</v>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=35.95% sobre 19 sem</t>
         </is>
@@ -7123,22 +7885,31 @@
       <c r="R85" t="n">
         <v>106.9882513320439</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
+      <c r="S85" t="n">
+        <v>40.47455651444805</v>
+      </c>
+      <c r="T85" t="n">
+        <v>4.521045170692717</v>
+      </c>
+      <c r="U85" t="n">
+        <v>107.8756984639591</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U85" t="n">
-        <v>51.40282038299348</v>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=51.40% sobre 19 sem</t>
+      <c r="X85" t="n">
+        <v>40.47455651444805</v>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=40.47% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7203,22 +7974,31 @@
       <c r="R86" t="n">
         <v>188.4995472315167</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
+      <c r="S86" t="n">
+        <v>70.26626119828747</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0.6349999969654554</v>
+      </c>
+      <c r="U86" t="n">
+        <v>113.2748521774272</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U86" t="n">
-        <v>86.35855519846304</v>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=86.36% sobre 19 sem</t>
+      <c r="X86" t="n">
+        <v>70.26626119828747</v>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=70.27% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7283,22 +8063,31 @@
       <c r="R87" t="n">
         <v>191.241827101395</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T87" t="inlineStr">
+      <c r="S87" t="n">
+        <v>103.835751536259</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0.4254498060582186</v>
+      </c>
+      <c r="U87" t="n">
+        <v>108.9238350712686</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U87" t="n">
-        <v>118.3586643671639</v>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=118.36% sobre 19 sem</t>
+      <c r="X87" t="n">
+        <v>103.835751536259</v>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=103.84% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7363,22 +8152,31 @@
       <c r="R88" t="n">
         <v>190.1751472740156</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
+      <c r="S88" t="n">
+        <v>117.9134080625519</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0.4788652747549516</v>
+      </c>
+      <c r="U88" t="n">
+        <v>121.3094122928426</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U88" t="n">
-        <v>127.0449845668104</v>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=127.04% sobre 19 sem</t>
+      <c r="X88" t="n">
+        <v>117.9134080625519</v>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=117.91% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7439,18 +8237,27 @@
       <c r="R89" t="n">
         <v>200</v>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S89" t="n">
+        <v>200</v>
+      </c>
+      <c r="T89" t="n">
+        <v>7.21227621483376</v>
+      </c>
+      <c r="U89" t="n">
+        <v>200</v>
+      </c>
+      <c r="V89" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T89" t="inlineStr">
+      <c r="W89" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr">
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -7513,18 +8320,27 @@
       <c r="R90" t="n">
         <v>200</v>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="S90" t="n">
+        <v>200</v>
+      </c>
+      <c r="T90" t="n">
+        <v>3.199488491048593</v>
+      </c>
+      <c r="U90" t="n">
+        <v>200</v>
+      </c>
+      <c r="V90" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T90" t="inlineStr">
+      <c r="W90" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr">
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -7587,20 +8403,29 @@
       <c r="R91" t="n">
         <v>200</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
+      <c r="S91" t="n">
+        <v>200</v>
+      </c>
+      <c r="T91" t="n">
+        <v>3.424141759816033e-17</v>
+      </c>
+      <c r="U91" t="n">
+        <v>200</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7665,22 +8490,31 @@
       <c r="R92" t="n">
         <v>92.01416331532587</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T92" t="inlineStr">
+      <c r="S92" t="n">
+        <v>36.61799934689352</v>
+      </c>
+      <c r="T92" t="n">
+        <v>4.898603469004812</v>
+      </c>
+      <c r="U92" t="n">
+        <v>95.83480509856771</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U92" t="n">
-        <v>52.03867931340183</v>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=52.04% sobre 19 sem</t>
+      <c r="X92" t="n">
+        <v>36.61799934689352</v>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=36.62% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7745,22 +8579,31 @@
       <c r="R93" t="n">
         <v>96.01849856237216</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
+      <c r="S93" t="n">
+        <v>36.9770007869263</v>
+      </c>
+      <c r="T93" t="n">
+        <v>2.207257357329876</v>
+      </c>
+      <c r="U93" t="n">
+        <v>99.35850993844542</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U93" t="n">
-        <v>52.79532864649887</v>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Prophet: menor SMAPE real=52.80% sobre 19 sem</t>
+      <c r="X93" t="n">
+        <v>36.9770007869263</v>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=36.98% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7825,22 +8668,31 @@
       <c r="R94" t="n">
         <v>95.82311990464228</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
+      <c r="S94" t="n">
+        <v>38.9841638923733</v>
+      </c>
+      <c r="T94" t="n">
+        <v>2.654681877562788</v>
+      </c>
+      <c r="U94" t="n">
+        <v>93.11495456228404</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U94" t="n">
-        <v>52.69581648158714</v>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>DeepAR: menor SMAPE real=52.70% sobre 19 sem</t>
+      <c r="X94" t="n">
+        <v>38.9841638923733</v>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>NBGLM: menor SMAPE real=38.98% sobre 19 sem</t>
         </is>
       </c>
     </row>
@@ -7905,20 +8757,29 @@
       <c r="R95" t="n">
         <v>118.2821915164861</v>
       </c>
-      <c r="S95" t="inlineStr">
+      <c r="S95" t="n">
+        <v>160.6233741719039</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1.630178425302371</v>
+      </c>
+      <c r="U95" t="n">
+        <v>128.8999217807187</v>
+      </c>
+      <c r="V95" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="W95" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="U95" t="n">
+      <c r="X95" t="n">
         <v>145.2656870067181</v>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=145.27% sobre 19 sem</t>
         </is>
@@ -7985,18 +8846,27 @@
       <c r="R96" t="n">
         <v>124.4459476108536</v>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="S96" t="n">
+        <v>180.9761017902954</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0.9242610827578899</v>
+      </c>
+      <c r="U96" t="n">
+        <v>151.8363274594118</v>
+      </c>
+      <c r="V96" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
+      <c r="W96" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr">
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
@@ -8063,18 +8933,27 @@
       <c r="R97" t="n">
         <v>128.4785456608675</v>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="S97" t="n">
+        <v>163.2961637414761</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0.8241713784572454</v>
+      </c>
+      <c r="U97" t="n">
+        <v>136.0400571203446</v>
+      </c>
+      <c r="V97" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T97" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr">
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -8137,18 +9016,27 @@
       <c r="R98" t="n">
         <v>200</v>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S98" t="n">
+        <v>200</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0.0009204004093562376</v>
+      </c>
+      <c r="U98" t="n">
+        <v>199.9999998548883</v>
+      </c>
+      <c r="V98" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="W98" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr">
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -8211,20 +9099,29 @@
       <c r="R99" t="n">
         <v>200</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
+      <c r="S99" t="n">
+        <v>200</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0.0004808773835790487</v>
+      </c>
+      <c r="U99" t="n">
+        <v>200</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -8285,20 +9182,29 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>DeepAR</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
+      <c r="S100" t="n">
+        <v>200</v>
+      </c>
+      <c r="T100" t="n">
+        <v>1.76736659311027e-06</v>
+      </c>
+      <c r="U100" t="n">
+        <v>200</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>NBGLM</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -575,7 +575,7 @@
         <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -584,16 +584,16 @@
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01909339069720435</v>
+        <v>0.01086772807397862</v>
       </c>
       <c r="I2" t="n">
-        <v>181.8875746538405</v>
+        <v>185.8333489727328</v>
       </c>
       <c r="J2" t="n">
         <v>200</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008620340954539604</v>
+        <v>0.009038219012261</v>
       </c>
       <c r="L2" t="n">
         <v>109.609711216533</v>
@@ -602,7 +602,7 @@
         <v>200</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.525</v>
       </c>
       <c r="O2" t="n">
         <v>197.8088169752323</v>
@@ -611,7 +611,7 @@
         <v>200</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.525</v>
       </c>
       <c r="R2" t="n">
         <v>199.5572761277739</v>
@@ -620,7 +620,7 @@
         <v>200</v>
       </c>
       <c r="T2" t="n">
-        <v>0.047666304710546</v>
+        <v>0.04831761745957867</v>
       </c>
       <c r="U2" t="n">
         <v>194.9779461019607</v>
@@ -662,7 +662,7 @@
         <v>2026</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -671,16 +671,16 @@
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0120984434586246</v>
+        <v>0.00951068472871661</v>
       </c>
       <c r="I3" t="n">
-        <v>157.3839857426704</v>
+        <v>157.2321783542833</v>
       </c>
       <c r="J3" t="n">
         <v>200</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01293774852062258</v>
+        <v>0.01291920560802575</v>
       </c>
       <c r="L3" t="n">
         <v>79.54507935933471</v>
@@ -689,7 +689,7 @@
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.15</v>
       </c>
       <c r="O3" t="n">
         <v>197.8854209931308</v>
@@ -698,7 +698,7 @@
         <v>200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.15</v>
       </c>
       <c r="R3" t="n">
         <v>199.636475467609</v>
@@ -707,7 +707,7 @@
         <v>200</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0352297925787751</v>
+        <v>0.03380843033181492</v>
       </c>
       <c r="U3" t="n">
         <v>198.5158836242873</v>
@@ -749,7 +749,7 @@
         <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -758,16 +758,16 @@
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02123577474837053</v>
+        <v>0.01339726082426194</v>
       </c>
       <c r="I4" t="n">
-        <v>158.8438418444702</v>
+        <v>158.5580779411727</v>
       </c>
       <c r="J4" t="n">
         <v>200</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07625688786245192</v>
+        <v>0.08872090040442157</v>
       </c>
       <c r="L4" t="n">
         <v>109.7635513825217</v>
@@ -776,7 +776,7 @@
         <v>200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.375</v>
       </c>
       <c r="O4" t="n">
         <v>197.7265973322816</v>
@@ -785,7 +785,7 @@
         <v>200</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.375</v>
       </c>
       <c r="R4" t="n">
         <v>199.5859359679221</v>
@@ -794,7 +794,7 @@
         <v>200</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03741817105613721</v>
+        <v>0.03815314787819993</v>
       </c>
       <c r="U4" t="n">
         <v>196.9436529554095</v>
@@ -836,25 +836,25 @@
         <v>2026</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>199.863029343531</v>
+        <v>199.1222961182866</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1060038941382352</v>
+        <v>0.103539670713508</v>
       </c>
       <c r="I5" t="n">
-        <v>175.5400786038201</v>
+        <v>175.1088701866436</v>
       </c>
       <c r="J5" t="n">
-        <v>199.2843630995856</v>
+        <v>199.3201449446063</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1172378734304398</v>
+        <v>0.1119777478183459</v>
       </c>
       <c r="L5" t="n">
         <v>109.609711216533</v>
@@ -863,7 +863,7 @@
         <v>200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
         <v>187.2707284786031</v>
@@ -872,16 +872,16 @@
         <v>200</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.25</v>
       </c>
       <c r="R5" t="n">
         <v>193.7972259177366</v>
       </c>
       <c r="S5" t="n">
-        <v>199.2254908035844</v>
+        <v>199.2642162634052</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1198320484669285</v>
+        <v>0.113840446043582</v>
       </c>
       <c r="U5" t="n">
         <v>187.0400639517023</v>
@@ -923,25 +923,25 @@
         <v>2026</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>199.6986714004902</v>
+        <v>199.5466380074913</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05880289809912526</v>
+        <v>0.05958452539361416</v>
       </c>
       <c r="I6" t="n">
-        <v>191.737797552366</v>
+        <v>191.646475967384</v>
       </c>
       <c r="J6" t="n">
-        <v>199.9861671147559</v>
+        <v>199.9868587590181</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05340157993507275</v>
+        <v>0.05077332858287904</v>
       </c>
       <c r="L6" t="n">
         <v>79.54507935933471</v>
@@ -950,7 +950,7 @@
         <v>200</v>
       </c>
       <c r="N6" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="O6" t="n">
         <v>192.53013744135</v>
@@ -959,7 +959,7 @@
         <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="R6" t="n">
         <v>193.2139428195562</v>
@@ -968,7 +968,7 @@
         <v>198.400971319978</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05977949533771661</v>
+        <v>0.05679052057083078</v>
       </c>
       <c r="U6" t="n">
         <v>198.9985835834048</v>
@@ -1010,25 +1010,25 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>199.158331088558</v>
+        <v>199.1310401828866</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06346581821336009</v>
+        <v>0.07351845768099691</v>
       </c>
       <c r="I7" t="n">
-        <v>187.2671055681853</v>
+        <v>186.9197740801393</v>
       </c>
       <c r="J7" t="n">
-        <v>199.9884309380623</v>
+        <v>199.9890093911592</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05308000538193182</v>
+        <v>0.05044767351613336</v>
       </c>
       <c r="L7" t="n">
         <v>109.7635513825217</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="N7" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="O7" t="n">
         <v>185.3187572725189</v>
@@ -1046,16 +1046,16 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="R7" t="n">
         <v>190.8625800946274</v>
       </c>
       <c r="S7" t="n">
-        <v>199.7727927228824</v>
+        <v>199.7841530867383</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06973172505380154</v>
+        <v>0.06624513880111146</v>
       </c>
       <c r="U7" t="n">
         <v>197.3279694158802</v>
@@ -1097,52 +1097,52 @@
         <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G8" t="n">
-        <v>124.2408629147414</v>
+        <v>102.939746329922</v>
       </c>
       <c r="H8" t="n">
-        <v>5.858449498066894</v>
+        <v>5.316948239627654</v>
       </c>
       <c r="I8" t="n">
-        <v>146.1852288200182</v>
+        <v>154.5040916050135</v>
       </c>
       <c r="J8" t="n">
-        <v>48.2035225269852</v>
+        <v>48.43958717347449</v>
       </c>
       <c r="K8" t="n">
-        <v>3.314891306805234</v>
+        <v>3.473010580623329</v>
       </c>
       <c r="L8" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M8" t="n">
-        <v>95.80329746013628</v>
+        <v>91.01313258712945</v>
       </c>
       <c r="N8" t="n">
-        <v>15.18421052631579</v>
+        <v>14.425</v>
       </c>
       <c r="O8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="P8" t="n">
-        <v>95.80329746013628</v>
+        <v>91.01313258712945</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.18421052631579</v>
+        <v>14.425</v>
       </c>
       <c r="R8" t="n">
         <v>172.894287988784</v>
       </c>
       <c r="S8" t="n">
-        <v>59.01081768196027</v>
+        <v>60.56045746576052</v>
       </c>
       <c r="T8" t="n">
-        <v>3.383893621127577</v>
+        <v>3.494017018505561</v>
       </c>
       <c r="U8" t="n">
         <v>111.5676388698673</v>
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>48.2035225269852</v>
+        <v>48.43958717347449</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=48.20% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=48.44% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1186,52 +1186,52 @@
         <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>133.862958905723</v>
+        <v>96.84936542770946</v>
       </c>
       <c r="H9" t="n">
-        <v>2.745953184050532</v>
+        <v>2.348153715242724</v>
       </c>
       <c r="I9" t="n">
-        <v>155.2184985113495</v>
+        <v>164.086229256472</v>
       </c>
       <c r="J9" t="n">
-        <v>69.98966250353146</v>
+        <v>70.37750705227454</v>
       </c>
       <c r="K9" t="n">
-        <v>2.063113567141357</v>
+        <v>2.150741598423064</v>
       </c>
       <c r="L9" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M9" t="n">
-        <v>111.3394980759131</v>
+        <v>105.7725231721175</v>
       </c>
       <c r="N9" t="n">
-        <v>7.631578947368421</v>
+        <v>7.25</v>
       </c>
       <c r="O9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="P9" t="n">
-        <v>111.3394980759131</v>
+        <v>105.7725231721175</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.631578947368421</v>
+        <v>7.25</v>
       </c>
       <c r="R9" t="n">
         <v>176.8647517474977</v>
       </c>
       <c r="S9" t="n">
-        <v>62.45968067597241</v>
+        <v>60.63470926628591</v>
       </c>
       <c r="T9" t="n">
-        <v>1.515713649482301</v>
+        <v>1.474394540926025</v>
       </c>
       <c r="U9" t="n">
         <v>121.2492629006552</v>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>62.45968067597241</v>
+        <v>60.63470926628591</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=62.46% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=60.63% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1275,52 +1275,52 @@
         <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G10" t="n">
-        <v>124.9117102132738</v>
+        <v>97.69809429310973</v>
       </c>
       <c r="H10" t="n">
-        <v>3.060920355992553</v>
+        <v>2.759493428145611</v>
       </c>
       <c r="I10" t="n">
-        <v>152.9918981156764</v>
+        <v>164.4874496413386</v>
       </c>
       <c r="J10" t="n">
-        <v>45.23277359273659</v>
+        <v>50.53504307263596</v>
       </c>
       <c r="K10" t="n">
-        <v>1.634276789548177</v>
+        <v>1.810953329620644</v>
       </c>
       <c r="L10" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M10" t="n">
-        <v>95.95074714452349</v>
+        <v>92.26432089840841</v>
       </c>
       <c r="N10" t="n">
-        <v>8.342105263157896</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="P10" t="n">
-        <v>95.95074714452349</v>
+        <v>92.26432089840841</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.342105263157896</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
         <v>168.5443712458804</v>
       </c>
       <c r="S10" t="n">
-        <v>60.49265913259512</v>
+        <v>64.3948423725101</v>
       </c>
       <c r="T10" t="n">
-        <v>1.901026720535735</v>
+        <v>2.051508251981994</v>
       </c>
       <c r="U10" t="n">
         <v>114.746491150853</v>
@@ -1336,11 +1336,11 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>45.23277359273659</v>
+        <v>50.53504307263596</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=45.23% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=50.54% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1364,52 +1364,52 @@
         <v>2026</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11" t="n">
-        <v>169.256431894795</v>
+        <v>178.4347588485121</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5989329700208699</v>
+        <v>0.602524666113481</v>
       </c>
       <c r="I11" t="n">
-        <v>129.9250091591691</v>
+        <v>123.2554563734294</v>
       </c>
       <c r="J11" t="n">
-        <v>198.0164154965292</v>
+        <v>198.0925893582057</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5887372433414818</v>
+        <v>0.6092428015336366</v>
       </c>
       <c r="L11" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M11" t="n">
-        <v>192.4219018577286</v>
+        <v>190.8008067648422</v>
       </c>
       <c r="N11" t="n">
-        <v>29.69221398008126</v>
+        <v>28.6076032810772</v>
       </c>
       <c r="O11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="P11" t="n">
-        <v>156.945040560381</v>
+        <v>159.6359755253572</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.094459499402622</v>
+        <v>1.089736524432491</v>
       </c>
       <c r="R11" t="n">
         <v>177.781032308345</v>
       </c>
       <c r="S11" t="n">
-        <v>127.3834750149388</v>
+        <v>122.7920619307176</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5559937455885269</v>
+        <v>0.5498154268247075</v>
       </c>
       <c r="U11" t="n">
         <v>147.9725418621825</v>
@@ -1425,11 +1425,11 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>127.3834750149388</v>
+        <v>122.7920619307176</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=127.38% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=122.79% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1453,52 +1453,52 @@
         <v>2026</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>194.4159379304537</v>
+        <v>191.8552562166053</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3858136158142387</v>
+        <v>0.3566911765420278</v>
       </c>
       <c r="I12" t="n">
-        <v>140.9543563511172</v>
+        <v>147.3485671696691</v>
       </c>
       <c r="J12" t="n">
-        <v>199.523179310629</v>
+        <v>199.5470203450976</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3712791089096222</v>
+        <v>0.352847024244512</v>
       </c>
       <c r="L12" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M12" t="n">
-        <v>191.5362391585139</v>
+        <v>191.9594272005882</v>
       </c>
       <c r="N12" t="n">
-        <v>13.60373315610809</v>
+        <v>13.07354649830269</v>
       </c>
       <c r="O12" t="n">
         <v>191.4723960783834</v>
       </c>
       <c r="P12" t="n">
-        <v>190.3614367008003</v>
+        <v>190.8433648657603</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.74459711503017</v>
+        <v>12.20253848204103</v>
       </c>
       <c r="R12" t="n">
         <v>189.6908701459495</v>
       </c>
       <c r="S12" t="n">
-        <v>155.8692201644686</v>
+        <v>158.0757591562452</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4690080929408374</v>
+        <v>0.4759576117403433</v>
       </c>
       <c r="U12" t="n">
         <v>169.7722333133142</v>
@@ -1540,52 +1540,52 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>194.7808770000501</v>
+        <v>195.8361847211582</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2470576173028503</v>
+        <v>0.2557147767860903</v>
       </c>
       <c r="I13" t="n">
-        <v>143.0465384202982</v>
+        <v>157.1522264328246</v>
       </c>
       <c r="J13" t="n">
-        <v>199.8262982460481</v>
+        <v>199.8165244396315</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2119254300762861</v>
+        <v>0.251282968706494</v>
       </c>
       <c r="L13" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M13" t="n">
-        <v>194.1951423424674</v>
+        <v>191.6282423682011</v>
       </c>
       <c r="N13" t="n">
-        <v>15.91266483478217</v>
+        <v>15.36703159304306</v>
       </c>
       <c r="O13" t="n">
         <v>193.9340304002594</v>
       </c>
       <c r="P13" t="n">
-        <v>191.6897112957606</v>
+        <v>192.1270949117732</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.691078398696177</v>
+        <v>6.406524478761369</v>
       </c>
       <c r="R13" t="n">
         <v>188.2053733911598</v>
       </c>
       <c r="S13" t="n">
-        <v>166.1429368437917</v>
+        <v>160.1046040574139</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3680900410091594</v>
+        <v>0.3681780684362106</v>
       </c>
       <c r="U13" t="n">
         <v>173.7069303697712</v>
@@ -1603,7 +1603,7 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1627,52 +1627,52 @@
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G14" t="n">
-        <v>68.18440924623016</v>
+        <v>68.80570985590298</v>
       </c>
       <c r="H14" t="n">
-        <v>1.965115005649187</v>
+        <v>2.008123501430287</v>
       </c>
       <c r="I14" t="n">
-        <v>74.93132855047638</v>
+        <v>66.61025297793201</v>
       </c>
       <c r="J14" t="n">
-        <v>85.47396170872173</v>
+        <v>84.31915847426973</v>
       </c>
       <c r="K14" t="n">
-        <v>2.660604966823898</v>
+        <v>2.754202184815645</v>
       </c>
       <c r="L14" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M14" t="n">
-        <v>168.2605793498451</v>
+        <v>167.7578144530684</v>
       </c>
       <c r="N14" t="n">
-        <v>33.4179335827928</v>
+        <v>33.63968371128689</v>
       </c>
       <c r="O14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="P14" t="n">
-        <v>180.3554903048052</v>
+        <v>180.5377157895649</v>
       </c>
       <c r="Q14" t="n">
-        <v>59.6578947368421</v>
+        <v>62.425</v>
       </c>
       <c r="R14" t="n">
         <v>186.0423288913966</v>
       </c>
       <c r="S14" t="n">
-        <v>75.78189336067067</v>
+        <v>76.61476888162572</v>
       </c>
       <c r="T14" t="n">
-        <v>2.656705421919318</v>
+        <v>2.953578645514585</v>
       </c>
       <c r="U14" t="n">
         <v>130.2296761771863</v>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>68.18440924623016</v>
+        <v>68.80570985590298</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=68.18% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=68.81% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1716,52 +1716,52 @@
         <v>2026</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>68.63649638136945</v>
+        <v>65.36323213379569</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9654501657857059</v>
+        <v>0.8910109167640803</v>
       </c>
       <c r="I15" t="n">
-        <v>83.26703869122109</v>
+        <v>82.6747998505866</v>
       </c>
       <c r="J15" t="n">
-        <v>89.8785759618037</v>
+        <v>90.57517357326512</v>
       </c>
       <c r="K15" t="n">
-        <v>1.189208099884046</v>
+        <v>1.23767065801537</v>
       </c>
       <c r="L15" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M15" t="n">
-        <v>172.9250609621144</v>
+        <v>173.5878226721619</v>
       </c>
       <c r="N15" t="n">
-        <v>22.15212661391847</v>
+        <v>22.39172919513397</v>
       </c>
       <c r="O15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="P15" t="n">
-        <v>176.3509089864839</v>
+        <v>177.1697271735234</v>
       </c>
       <c r="Q15" t="n">
-        <v>28.47368421052632</v>
+        <v>29.7</v>
       </c>
       <c r="R15" t="n">
         <v>186.4460938550808</v>
       </c>
       <c r="S15" t="n">
-        <v>76.52604808710842</v>
+        <v>79.85510675984227</v>
       </c>
       <c r="T15" t="n">
-        <v>1.336950864427592</v>
+        <v>1.521641786051784</v>
       </c>
       <c r="U15" t="n">
         <v>131.9030800529592</v>
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>68.63649638136945</v>
+        <v>65.36323213379569</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=68.64% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=65.36% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1805,52 +1805,52 @@
         <v>2026</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>121.4424954946124</v>
+        <v>120.1868578325129</v>
       </c>
       <c r="H16" t="n">
-        <v>1.534736430505168</v>
+        <v>1.603530893967823</v>
       </c>
       <c r="I16" t="n">
-        <v>88.28301425252694</v>
+        <v>90.20708978859948</v>
       </c>
       <c r="J16" t="n">
-        <v>142.02923967689</v>
+        <v>135.5839928652588</v>
       </c>
       <c r="K16" t="n">
-        <v>1.457101397264992</v>
+        <v>1.412338377221286</v>
       </c>
       <c r="L16" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M16" t="n">
-        <v>177.5562163584148</v>
+        <v>176.4025580239632</v>
       </c>
       <c r="N16" t="n">
-        <v>23.00017792905756</v>
+        <v>23.20775602863392</v>
       </c>
       <c r="O16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="P16" t="n">
-        <v>182.3405142567343</v>
+        <v>182.0806314010404</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.26315789473684</v>
+        <v>32.8</v>
       </c>
       <c r="R16" t="n">
         <v>186.1307414343702</v>
       </c>
       <c r="S16" t="n">
-        <v>108.4709234228671</v>
+        <v>105.9453658902282</v>
       </c>
       <c r="T16" t="n">
-        <v>1.318227811058774</v>
+        <v>1.415537147198349</v>
       </c>
       <c r="U16" t="n">
         <v>133.2708900338696</v>
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>108.4709234228671</v>
+        <v>105.9453658902282</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=108.47% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=105.95% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -1894,25 +1894,25 @@
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>199.1102341795934</v>
+        <v>198.7984995529214</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09613834946315496</v>
+        <v>0.1095214356824465</v>
       </c>
       <c r="I17" t="n">
-        <v>194.6710344353644</v>
+        <v>194.5446671655584</v>
       </c>
       <c r="J17" t="n">
-        <v>199.943152462609</v>
+        <v>199.9459948394786</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0548479375829464</v>
+        <v>0.05222732714755758</v>
       </c>
       <c r="L17" t="n">
         <v>109.609711216533</v>
@@ -1921,7 +1921,7 @@
         <v>200</v>
       </c>
       <c r="N17" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="O17" t="n">
         <v>196.7571923388938</v>
@@ -1930,16 +1930,16 @@
         <v>200</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="R17" t="n">
         <v>197.0125798901019</v>
       </c>
       <c r="S17" t="n">
-        <v>198.6980564595817</v>
+        <v>198.7631536366026</v>
       </c>
       <c r="T17" t="n">
-        <v>0.06060324451992004</v>
+        <v>0.05757308229392404</v>
       </c>
       <c r="U17" t="n">
         <v>192.256373806382</v>
@@ -1981,7 +1981,7 @@
         <v>2026</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1990,16 +1990,16 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03136352411444188</v>
+        <v>0.02453038060506788</v>
       </c>
       <c r="I18" t="n">
-        <v>199.5917940260522</v>
+        <v>199.6410247115898</v>
       </c>
       <c r="J18" t="n">
         <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0005657554175379</v>
+        <v>0.0005626091125968551</v>
       </c>
       <c r="L18" t="n">
         <v>79.54507935933471</v>
@@ -2022,7 +2022,7 @@
         <v>200</v>
       </c>
       <c r="T18" t="n">
-        <v>5.358559373428652e-263</v>
+        <v>5.090631404757219e-263</v>
       </c>
       <c r="U18" t="n">
         <v>196.0211023092105</v>
@@ -2064,25 +2064,25 @@
         <v>2026</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.4476600573335</v>
+        <v>199.0879467724605</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08682774457069804</v>
+        <v>0.09628835939416915</v>
       </c>
       <c r="I19" t="n">
-        <v>196.3668815794815</v>
+        <v>196.278530387405</v>
       </c>
       <c r="J19" t="n">
-        <v>199.8695191024682</v>
+        <v>199.8760431473448</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05725188032739883</v>
+        <v>0.05466784212850494</v>
       </c>
       <c r="L19" t="n">
         <v>109.7635513825217</v>
@@ -2091,7 +2091,7 @@
         <v>200</v>
       </c>
       <c r="N19" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="O19" t="n">
         <v>196.7189002085085</v>
@@ -2100,16 +2100,16 @@
         <v>200</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.131578947368421</v>
+        <v>0.125</v>
       </c>
       <c r="R19" t="n">
         <v>196.7488584326798</v>
       </c>
       <c r="S19" t="n">
-        <v>198.82015746588</v>
+        <v>198.879149592586</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06151385363938022</v>
+        <v>0.05843816095741121</v>
       </c>
       <c r="U19" t="n">
         <v>197.8046914283761</v>
@@ -2151,7 +2151,7 @@
         <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01308918116114505</v>
+        <v>0.07059010458825815</v>
       </c>
       <c r="I20" t="n">
         <v>200</v>
@@ -2169,7 +2169,7 @@
         <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001370789179767052</v>
+        <v>0.00140240633767629</v>
       </c>
       <c r="L20" t="n">
         <v>109.609711216533</v>
@@ -2192,7 +2192,7 @@
         <v>200</v>
       </c>
       <c r="T20" t="n">
-        <v>7894.736842105263</v>
+        <v>7500</v>
       </c>
       <c r="U20" t="n">
         <v>200</v>
@@ -2234,7 +2234,7 @@
         <v>2026</v>
       </c>
       <c r="E21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05679447572271468</v>
+        <v>0.05681577275851089</v>
       </c>
       <c r="I21" t="n">
         <v>200</v>
@@ -2252,7 +2252,7 @@
         <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>0.005994552645078885</v>
+        <v>0.006011293468559891</v>
       </c>
       <c r="L21" t="n">
         <v>79.54507935933471</v>
@@ -2275,7 +2275,7 @@
         <v>200</v>
       </c>
       <c r="T21" t="n">
-        <v>18421.05263167506</v>
+        <v>17500.00000009131</v>
       </c>
       <c r="U21" t="n">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>2026</v>
       </c>
       <c r="E22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06271867433330723</v>
+        <v>0.06360909203296403</v>
       </c>
       <c r="I22" t="n">
         <v>200</v>
@@ -2335,7 +2335,7 @@
         <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000365936301039679</v>
+        <v>0.000365317727903835</v>
       </c>
       <c r="L22" t="n">
         <v>109.7635513825217</v>
@@ -2358,7 +2358,7 @@
         <v>200</v>
       </c>
       <c r="T22" t="n">
-        <v>3.38469284411295e-17</v>
+        <v>3.215458201907303e-17</v>
       </c>
       <c r="U22" t="n">
         <v>200</v>
@@ -2400,25 +2400,25 @@
         <v>2026</v>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>179.9337722008812</v>
+        <v>179.1739130190571</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1264170913622294</v>
+        <v>0.1208266201253207</v>
       </c>
       <c r="I23" t="n">
-        <v>148.7957871310144</v>
+        <v>149.2565324185079</v>
       </c>
       <c r="J23" t="n">
-        <v>199.2619412956352</v>
+        <v>199.2988442308534</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1191078773049664</v>
+        <v>0.1169462719000806</v>
       </c>
       <c r="L23" t="n">
         <v>109.609711216533</v>
@@ -2427,7 +2427,7 @@
         <v>192.8571428571429</v>
       </c>
       <c r="N23" t="n">
-        <v>1.105263157894737</v>
+        <v>1.05</v>
       </c>
       <c r="O23" t="n">
         <v>169.6992056798271</v>
@@ -2436,16 +2436,16 @@
         <v>192.8571428571429</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.105263157894737</v>
+        <v>1.05</v>
       </c>
       <c r="R23" t="n">
         <v>186.3774873978808</v>
       </c>
       <c r="S23" t="n">
-        <v>189.1502269944299</v>
+        <v>189.6927156447084</v>
       </c>
       <c r="T23" t="n">
-        <v>0.214788356206763</v>
+        <v>0.2113223124025828</v>
       </c>
       <c r="U23" t="n">
         <v>159.9263814945425</v>
@@ -2487,25 +2487,25 @@
         <v>2026</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>182.6845580141106</v>
+        <v>182.221104530061</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06542854972043259</v>
+        <v>0.06246006768372875</v>
       </c>
       <c r="I24" t="n">
-        <v>155.1760639717555</v>
+        <v>156.2502876793226</v>
       </c>
       <c r="J24" t="n">
-        <v>198.5231057940479</v>
+        <v>198.5969505043455</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0644576519532402</v>
+        <v>0.06201450118704753</v>
       </c>
       <c r="L24" t="n">
         <v>79.54507935933471</v>
@@ -2514,7 +2514,7 @@
         <v>138.2549574812263</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1431885455784045</v>
+        <v>0.1360291182994842</v>
       </c>
       <c r="O24" t="n">
         <v>159.6122718089852</v>
@@ -2523,16 +2523,16 @@
         <v>175</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5</v>
+        <v>0.475</v>
       </c>
       <c r="R24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="S24" t="n">
-        <v>192.5705904110226</v>
+        <v>192.9420608904714</v>
       </c>
       <c r="T24" t="n">
-        <v>0.127246183659518</v>
+        <v>0.1233272719333847</v>
       </c>
       <c r="U24" t="n">
         <v>166.4426133688291</v>
@@ -2574,7 +2574,7 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2583,16 +2583,16 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>0.07054487750177577</v>
+        <v>0.06991408417631947</v>
       </c>
       <c r="I25" t="n">
-        <v>155.0685899856278</v>
+        <v>155.3955473497874</v>
       </c>
       <c r="J25" t="n">
-        <v>199.9139299449369</v>
+        <v>199.91823344769</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0576600837228529</v>
+        <v>0.05538158754912472</v>
       </c>
       <c r="L25" t="n">
         <v>109.7635513825217</v>
@@ -2601,7 +2601,7 @@
         <v>200</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.575</v>
       </c>
       <c r="O25" t="n">
         <v>177.0659734750362</v>
@@ -2610,16 +2610,16 @@
         <v>200</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.575</v>
       </c>
       <c r="R25" t="n">
         <v>183.340259481936</v>
       </c>
       <c r="S25" t="n">
-        <v>199.5482494364765</v>
+        <v>199.5708369646526</v>
       </c>
       <c r="T25" t="n">
-        <v>0.142533101613901</v>
+        <v>0.1423984762855963</v>
       </c>
       <c r="U25" t="n">
         <v>180.6321027113416</v>
@@ -2661,7 +2661,7 @@
         <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2670,16 +2670,16 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0832718885486983</v>
+        <v>0.02641044271870376</v>
       </c>
       <c r="I26" t="n">
-        <v>109.9617469881321</v>
+        <v>97.19414576199205</v>
       </c>
       <c r="J26" t="n">
         <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>0.09259454194778965</v>
+        <v>0.0921510468117073</v>
       </c>
       <c r="L26" t="n">
         <v>109.609711216533</v>
@@ -2688,7 +2688,7 @@
         <v>200</v>
       </c>
       <c r="N26" t="n">
-        <v>66.31578947368421</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>198.3074653131699</v>
@@ -2697,7 +2697,7 @@
         <v>200</v>
       </c>
       <c r="Q26" t="n">
-        <v>66.31578947368421</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="R26" t="n">
         <v>199.6509594119097</v>
@@ -2706,7 +2706,7 @@
         <v>200</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9017867897851561</v>
+        <v>0.9201320418796755</v>
       </c>
       <c r="U26" t="n">
         <v>183.6686755299509</v>
@@ -2748,7 +2748,7 @@
         <v>2026</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2757,16 +2757,16 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.004602625390390047</v>
+        <v>0.01849258866482504</v>
       </c>
       <c r="I27" t="n">
-        <v>128.3332125535668</v>
+        <v>129.0985231723771</v>
       </c>
       <c r="J27" t="n">
         <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01173072176237696</v>
+        <v>0.01147627579690619</v>
       </c>
       <c r="L27" t="n">
         <v>79.54507935933471</v>
@@ -2775,7 +2775,7 @@
         <v>200</v>
       </c>
       <c r="N27" t="n">
-        <v>32.76315789473684</v>
+        <v>33.3</v>
       </c>
       <c r="O27" t="n">
         <v>198.6114841856233</v>
@@ -2784,7 +2784,7 @@
         <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>32.76315789473684</v>
+        <v>33.3</v>
       </c>
       <c r="R27" t="n">
         <v>199.779644487174</v>
@@ -2793,14 +2793,14 @@
         <v>200</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5530458220041397</v>
+        <v>0.5743908083603411</v>
       </c>
       <c r="U27" t="n">
         <v>192.722098187243</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2811,7 +2811,7 @@
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
         <v>2026</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2844,16 +2844,16 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.02779200000818176</v>
+        <v>0.01865813865375408</v>
       </c>
       <c r="I28" t="n">
-        <v>134.8536674445885</v>
+        <v>127.1718885128103</v>
       </c>
       <c r="J28" t="n">
         <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>0.004403138451811863</v>
+        <v>0.00451688792496775</v>
       </c>
       <c r="L28" t="n">
         <v>109.7635513825217</v>
@@ -2862,7 +2862,7 @@
         <v>200</v>
       </c>
       <c r="N28" t="n">
-        <v>33.55263157894737</v>
+        <v>34.05</v>
       </c>
       <c r="O28" t="n">
         <v>197.4940180993655</v>
@@ -2871,7 +2871,7 @@
         <v>200</v>
       </c>
       <c r="Q28" t="n">
-        <v>33.55263157894737</v>
+        <v>34.05</v>
       </c>
       <c r="R28" t="n">
         <v>199.5411797194807</v>
@@ -2880,7 +2880,7 @@
         <v>200</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7508665704125755</v>
+        <v>0.7538728996217575</v>
       </c>
       <c r="U28" t="n">
         <v>184.9627687949149</v>
@@ -2922,7 +2922,7 @@
         <v>2026</v>
       </c>
       <c r="E29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2931,16 +2931,16 @@
         <v>200</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1866389784049496</v>
+        <v>0.0976447329447092</v>
       </c>
       <c r="I29" t="n">
-        <v>192.4134519048118</v>
+        <v>191.5075017030775</v>
       </c>
       <c r="J29" t="n">
         <v>200</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02627149302176331</v>
+        <v>0.02601264090501351</v>
       </c>
       <c r="L29" t="n">
         <v>109.609711216533</v>
@@ -2949,7 +2949,7 @@
         <v>200</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.45</v>
       </c>
       <c r="O29" t="n">
         <v>198.5277121400952</v>
@@ -2958,7 +2958,7 @@
         <v>200</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.45</v>
       </c>
       <c r="R29" t="n">
         <v>199.9388941772115</v>
@@ -2967,7 +2967,7 @@
         <v>200</v>
       </c>
       <c r="T29" t="n">
-        <v>0.03951542031433585</v>
+        <v>0.03753968500489356</v>
       </c>
       <c r="U29" t="n">
         <v>192.5799615112869</v>
@@ -3009,7 +3009,7 @@
         <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3018,16 +3018,16 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1380433323432018</v>
+        <v>0.08282712908855035</v>
       </c>
       <c r="I30" t="n">
-        <v>196.3947851007668</v>
+        <v>196.0386411854094</v>
       </c>
       <c r="J30" t="n">
         <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>0.005751018203588878</v>
+        <v>0.00576525480302511</v>
       </c>
       <c r="L30" t="n">
         <v>79.54507935933471</v>
@@ -3036,7 +3036,7 @@
         <v>200</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3</v>
       </c>
       <c r="O30" t="n">
         <v>198.9477887234591</v>
@@ -3045,7 +3045,7 @@
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3</v>
       </c>
       <c r="R30" t="n">
         <v>199.7754683359127</v>
@@ -3054,7 +3054,7 @@
         <v>200</v>
       </c>
       <c r="T30" t="n">
-        <v>0.02591903960978625</v>
+        <v>0.02462361562998687</v>
       </c>
       <c r="U30" t="n">
         <v>198.9226798174336</v>
@@ -3096,7 +3096,7 @@
         <v>2026</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -3105,16 +3105,16 @@
         <v>200</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1477795792688235</v>
+        <v>0.09492014033457305</v>
       </c>
       <c r="I31" t="n">
-        <v>194.2709642910985</v>
+        <v>194.2466814459454</v>
       </c>
       <c r="J31" t="n">
         <v>200</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005810557376236404</v>
+        <v>0.005793890306590724</v>
       </c>
       <c r="L31" t="n">
         <v>109.7635513825217</v>
@@ -3123,7 +3123,7 @@
         <v>200</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.15</v>
       </c>
       <c r="O31" t="n">
         <v>199.0633013569061</v>
@@ -3132,7 +3132,7 @@
         <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.15</v>
       </c>
       <c r="R31" t="n">
         <v>199.9196066031173</v>
@@ -3141,7 +3141,7 @@
         <v>200</v>
       </c>
       <c r="T31" t="n">
-        <v>0.01648866579845337</v>
+        <v>0.0156642325101831</v>
       </c>
       <c r="U31" t="n">
         <v>194.1597056483905</v>
@@ -3183,59 +3183,59 @@
         <v>2026</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>165.7546148305496</v>
+        <v>162.0968926914251</v>
       </c>
       <c r="H32" t="n">
-        <v>0.38785922921792</v>
+        <v>0.4029735300622607</v>
       </c>
       <c r="I32" t="n">
-        <v>164.8758692530674</v>
+        <v>164.6748490827784</v>
       </c>
       <c r="J32" t="n">
-        <v>188.3994774916149</v>
+        <v>184.3450690318275</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3600397467700314</v>
+        <v>0.4578138118526899</v>
       </c>
       <c r="L32" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M32" t="n">
-        <v>152.3809523809524</v>
+        <v>154.0413533834586</v>
       </c>
       <c r="N32" t="n">
-        <v>2.684210526315789</v>
+        <v>3.4</v>
       </c>
       <c r="O32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="P32" t="n">
-        <v>152.3809523809524</v>
+        <v>154.0413533834586</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.684210526315789</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
         <v>195.3761640213164</v>
       </c>
       <c r="S32" t="n">
-        <v>156.6987413005241</v>
+        <v>152.9603523577473</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5793442316552549</v>
+        <v>0.6197694400850768</v>
       </c>
       <c r="U32" t="n">
         <v>173.3959783787531</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -3246,7 +3246,7 @@
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
         <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
@@ -3279,16 +3279,16 @@
         <v>200</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1535755243341698</v>
+        <v>0.1968837263275579</v>
       </c>
       <c r="I33" t="n">
-        <v>170.1482256075269</v>
+        <v>170.4028696730483</v>
       </c>
       <c r="J33" t="n">
-        <v>197.5602748361831</v>
+        <v>197.682261094374</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3071348444317514</v>
+        <v>0.3001168361263843</v>
       </c>
       <c r="L33" t="n">
         <v>79.54507935933471</v>
@@ -3297,7 +3297,7 @@
         <v>200</v>
       </c>
       <c r="N33" t="n">
-        <v>1.789473684210526</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>180.7526372107734</v>
@@ -3306,16 +3306,16 @@
         <v>200</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.789473684210526</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="S33" t="n">
-        <v>196.413504078234</v>
+        <v>196.5928288743223</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3150697423847014</v>
+        <v>0.3447896743772237</v>
       </c>
       <c r="U33" t="n">
         <v>182.3083787234438</v>
@@ -3357,52 +3357,52 @@
         <v>2026</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
-        <v>174.6879222141001</v>
+        <v>168.5254247214432</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3296184931025303</v>
+        <v>0.3162578492589506</v>
       </c>
       <c r="I34" t="n">
-        <v>171.4397998821392</v>
+        <v>169.6571057340244</v>
       </c>
       <c r="J34" t="n">
-        <v>171.6084043022315</v>
+        <v>171.6136216027415</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4006139541700345</v>
+        <v>0.9876155844856072</v>
       </c>
       <c r="L34" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M34" t="n">
-        <v>163.9888682745826</v>
+        <v>164.3383283383283</v>
       </c>
       <c r="N34" t="n">
-        <v>1.421052631578947</v>
+        <v>1.9</v>
       </c>
       <c r="O34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="P34" t="n">
-        <v>163.9888682745826</v>
+        <v>164.3383283383283</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.421052631578947</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
         <v>195.2398047728465</v>
       </c>
       <c r="S34" t="n">
-        <v>166.4757146467686</v>
+        <v>160.3353263613274</v>
       </c>
       <c r="T34" t="n">
-        <v>0.3409276249292862</v>
+        <v>0.3518140627313046</v>
       </c>
       <c r="U34" t="n">
         <v>176.7243686471345</v>
@@ -3420,7 +3420,7 @@
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3444,52 +3444,52 @@
         <v>2026</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F35" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>108.3601558982242</v>
+        <v>105.9281725311015</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9926778426100719</v>
+        <v>0.6844616986657439</v>
       </c>
       <c r="I35" t="n">
-        <v>62.42552765573187</v>
+        <v>48.55849570822402</v>
       </c>
       <c r="J35" t="n">
-        <v>128.6246318422078</v>
+        <v>123.1572115120545</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8253314883004678</v>
+        <v>0.8016465967314691</v>
       </c>
       <c r="L35" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M35" t="n">
-        <v>190.1370507886782</v>
+        <v>189.5464969622409</v>
       </c>
       <c r="N35" t="n">
-        <v>30.60377691036805</v>
+        <v>30.71911507859925</v>
       </c>
       <c r="O35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="P35" t="n">
-        <v>198.0246068743259</v>
+        <v>197.8549201547707</v>
       </c>
       <c r="Q35" t="n">
-        <v>177.049413209731</v>
+        <v>175.4469425492444</v>
       </c>
       <c r="R35" t="n">
         <v>185.853149170162</v>
       </c>
       <c r="S35" t="n">
-        <v>131.3760966488024</v>
+        <v>128.5818390703525</v>
       </c>
       <c r="T35" t="n">
-        <v>1.79261396959873</v>
+        <v>1.82424504622132</v>
       </c>
       <c r="U35" t="n">
         <v>110.5529101365675</v>
@@ -3505,11 +3505,11 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>108.3601558982242</v>
+        <v>105.9281725311015</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=108.36% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=105.93% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -3533,59 +3533,59 @@
         <v>2026</v>
       </c>
       <c r="E36" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>156.7844328162785</v>
+        <v>163.7264674232613</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6980743927875586</v>
+        <v>0.4907642625934389</v>
       </c>
       <c r="I36" t="n">
-        <v>70.10918162979605</v>
+        <v>58.86670393327421</v>
       </c>
       <c r="J36" t="n">
-        <v>170.6440396621451</v>
+        <v>169.2768130296432</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6600202651972441</v>
+        <v>0.7105029179987218</v>
       </c>
       <c r="L36" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M36" t="n">
-        <v>187.6511691920828</v>
+        <v>185.551721301033</v>
       </c>
       <c r="N36" t="n">
-        <v>9.022437799031088</v>
+        <v>9.107451865461025</v>
       </c>
       <c r="O36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="P36" t="n">
-        <v>198.7712512880413</v>
+        <v>198.2693084419491</v>
       </c>
       <c r="Q36" t="n">
-        <v>86.37118751369708</v>
+        <v>85.40262813801223</v>
       </c>
       <c r="R36" t="n">
         <v>187.2910306593169</v>
       </c>
       <c r="S36" t="n">
-        <v>163.8685222925315</v>
+        <v>157.1419251017288</v>
       </c>
       <c r="T36" t="n">
-        <v>1.141618918264861</v>
+        <v>1.118917428962281</v>
       </c>
       <c r="U36" t="n">
         <v>118.8153464644226</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -3596,7 +3596,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3620,52 +3620,52 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>142.6549908394647</v>
+        <v>151.8378542282286</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7294146855502518</v>
+        <v>0.6140177756242682</v>
       </c>
       <c r="I37" t="n">
-        <v>69.25953978081323</v>
+        <v>60.32903496111531</v>
       </c>
       <c r="J37" t="n">
-        <v>162.0004203901676</v>
+        <v>163.9003993706592</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8181360894281809</v>
+        <v>0.8983255976255238</v>
       </c>
       <c r="L37" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M37" t="n">
-        <v>180.650285245381</v>
+        <v>181.617770983112</v>
       </c>
       <c r="N37" t="n">
-        <v>9.231672364614226</v>
+        <v>9.383893129980439</v>
       </c>
       <c r="O37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="P37" t="n">
-        <v>197.3169566187356</v>
+        <v>197.4511087877988</v>
       </c>
       <c r="Q37" t="n">
-        <v>91.948882085039</v>
+        <v>91.25143798078706</v>
       </c>
       <c r="R37" t="n">
         <v>185.3862117422507</v>
       </c>
       <c r="S37" t="n">
-        <v>145.3573454334758</v>
+        <v>148.089478161802</v>
       </c>
       <c r="T37" t="n">
-        <v>0.9968067490053601</v>
+        <v>1.091784744323357</v>
       </c>
       <c r="U37" t="n">
         <v>110.8838400280787</v>
@@ -3707,52 +3707,52 @@
         <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>199.6217616830302</v>
+        <v>192.3923638058561</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3370447620534833</v>
+        <v>0.4625873314833769</v>
       </c>
       <c r="I38" t="n">
-        <v>162.149087371204</v>
+        <v>164.4263244057969</v>
       </c>
       <c r="J38" t="n">
-        <v>193.5392151146532</v>
+        <v>193.8622543589206</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3365288969477717</v>
+        <v>0.3699466801412142</v>
       </c>
       <c r="L38" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M38" t="n">
-        <v>182.488038277512</v>
+        <v>183.3636363636363</v>
       </c>
       <c r="N38" t="n">
-        <v>7.368421052631579</v>
+        <v>7.9</v>
       </c>
       <c r="O38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="P38" t="n">
-        <v>182.488038277512</v>
+        <v>183.3636363636363</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.368421052631579</v>
+        <v>7.9</v>
       </c>
       <c r="R38" t="n">
         <v>199.036270909302</v>
       </c>
       <c r="S38" t="n">
-        <v>184.4692848329074</v>
+        <v>185.245820591262</v>
       </c>
       <c r="T38" t="n">
-        <v>0.3966684884236398</v>
+        <v>0.4200888512268395</v>
       </c>
       <c r="U38" t="n">
         <v>129.2920232398837</v>
@@ -3794,52 +3794,52 @@
         <v>2026</v>
       </c>
       <c r="E39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>200</v>
+        <v>198.5862956300785</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1285627026425347</v>
+        <v>0.1724602873418419</v>
       </c>
       <c r="I39" t="n">
-        <v>165.7621571068165</v>
+        <v>170.2041702191862</v>
       </c>
       <c r="J39" t="n">
-        <v>199.1462918111721</v>
+        <v>199.1889772206135</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1211556611899457</v>
+        <v>0.1158998444099787</v>
       </c>
       <c r="L39" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M39" t="n">
-        <v>182.2222222222222</v>
+        <v>183.1578947368421</v>
       </c>
       <c r="N39" t="n">
-        <v>3.447368421052631</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="P39" t="n">
-        <v>182.2222222222222</v>
+        <v>183.1578947368421</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.447368421052631</v>
+        <v>3.8</v>
       </c>
       <c r="R39" t="n">
         <v>199.0467638312102</v>
       </c>
       <c r="S39" t="n">
-        <v>194.1806375349233</v>
+        <v>194.4716056581771</v>
       </c>
       <c r="T39" t="n">
-        <v>0.2104870711844742</v>
+        <v>0.2213114506864156</v>
       </c>
       <c r="U39" t="n">
         <v>146.152525200624</v>
@@ -3881,52 +3881,52 @@
         <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>200</v>
+        <v>197.9577894510206</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1607786834568675</v>
+        <v>0.2197660420449167</v>
       </c>
       <c r="I40" t="n">
-        <v>163.618905219222</v>
+        <v>165.7522199768573</v>
       </c>
       <c r="J40" t="n">
-        <v>199.5885882473661</v>
+        <v>199.6091588349978</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1159126568736139</v>
+        <v>0.1103781947572354</v>
       </c>
       <c r="L40" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M40" t="n">
-        <v>186.3157894736842</v>
+        <v>187</v>
       </c>
       <c r="N40" t="n">
-        <v>4.157894736842105</v>
+        <v>4.475</v>
       </c>
       <c r="O40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="P40" t="n">
-        <v>186.3157894736842</v>
+        <v>187</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.157894736842105</v>
+        <v>4.475</v>
       </c>
       <c r="R40" t="n">
         <v>198.942356787496</v>
       </c>
       <c r="S40" t="n">
-        <v>194.3759123473405</v>
+        <v>194.6571167299734</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2298943768714146</v>
+        <v>0.2431969099467668</v>
       </c>
       <c r="U40" t="n">
         <v>124.2002492905602</v>
@@ -3968,52 +3968,52 @@
         <v>2026</v>
       </c>
       <c r="E41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G41" t="n">
-        <v>82.11866101265029</v>
+        <v>87.58438501164028</v>
       </c>
       <c r="H41" t="n">
-        <v>1.598833157227979</v>
+        <v>2.030336807144944</v>
       </c>
       <c r="I41" t="n">
-        <v>132.9108801179189</v>
+        <v>127.4617865350128</v>
       </c>
       <c r="J41" t="n">
-        <v>91.67853884817875</v>
+        <v>88.16748667658304</v>
       </c>
       <c r="K41" t="n">
-        <v>1.501031372391154</v>
+        <v>1.513182749141943</v>
       </c>
       <c r="L41" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M41" t="n">
-        <v>183.507499093661</v>
+        <v>183.2510430578968</v>
       </c>
       <c r="N41" t="n">
-        <v>54.92105263157895</v>
+        <v>59.6</v>
       </c>
       <c r="O41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="P41" t="n">
-        <v>183.507499093661</v>
+        <v>183.2510430578968</v>
       </c>
       <c r="Q41" t="n">
-        <v>54.92105263157895</v>
+        <v>59.6</v>
       </c>
       <c r="R41" t="n">
         <v>198.8825072752037</v>
       </c>
       <c r="S41" t="n">
-        <v>73.34661585373087</v>
+        <v>70.80422175698777</v>
       </c>
       <c r="T41" t="n">
-        <v>1.068779849915095</v>
+        <v>1.129418131199049</v>
       </c>
       <c r="U41" t="n">
         <v>124.7888620818299</v>
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="X41" t="n">
-        <v>73.34661585373087</v>
+        <v>70.80422175698777</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=73.35% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=70.80% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -4057,52 +4057,52 @@
         <v>2026</v>
       </c>
       <c r="E42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G42" t="n">
-        <v>109.6033369316858</v>
+        <v>110.5832306135111</v>
       </c>
       <c r="H42" t="n">
-        <v>1.06863407789476</v>
+        <v>1.222854070382742</v>
       </c>
       <c r="I42" t="n">
-        <v>144.2379256407503</v>
+        <v>139.5371944473096</v>
       </c>
       <c r="J42" t="n">
-        <v>154.5839114750662</v>
+        <v>156.5471576898993</v>
       </c>
       <c r="K42" t="n">
-        <v>1.253514010486913</v>
+        <v>1.338495597351946</v>
       </c>
       <c r="L42" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M42" t="n">
-        <v>181.2887708376975</v>
+        <v>181.4835915550719</v>
       </c>
       <c r="N42" t="n">
-        <v>24.97368421052632</v>
+        <v>27.475</v>
       </c>
       <c r="O42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="P42" t="n">
-        <v>181.2887708376975</v>
+        <v>181.4835915550719</v>
       </c>
       <c r="Q42" t="n">
-        <v>24.97368421052632</v>
+        <v>27.475</v>
       </c>
       <c r="R42" t="n">
         <v>198.6803521667581</v>
       </c>
       <c r="S42" t="n">
-        <v>97.36275957055524</v>
+        <v>95.21274486565832</v>
       </c>
       <c r="T42" t="n">
-        <v>0.5729920972582702</v>
+        <v>0.656324198860722</v>
       </c>
       <c r="U42" t="n">
         <v>125.9010082864909</v>
@@ -4118,11 +4118,11 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>97.36275957055524</v>
+        <v>95.21274486565832</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=97.36% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=95.21% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -4146,52 +4146,52 @@
         <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G43" t="n">
-        <v>87.61246286752178</v>
+        <v>91.54776374116032</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8606773829398876</v>
+        <v>1.123728032782006</v>
       </c>
       <c r="I43" t="n">
-        <v>143.2356557138082</v>
+        <v>137.8269504556986</v>
       </c>
       <c r="J43" t="n">
-        <v>129.2210590644231</v>
+        <v>131.4560119700474</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8683344472736246</v>
+        <v>1.103993563605121</v>
       </c>
       <c r="L43" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M43" t="n">
-        <v>186.9457477180321</v>
+        <v>186.1949515602007</v>
       </c>
       <c r="N43" t="n">
-        <v>31.68421052631579</v>
+        <v>33.775</v>
       </c>
       <c r="O43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="P43" t="n">
-        <v>186.9457477180321</v>
+        <v>186.1949515602007</v>
       </c>
       <c r="Q43" t="n">
-        <v>31.68421052631579</v>
+        <v>33.775</v>
       </c>
       <c r="R43" t="n">
         <v>198.9631246433146</v>
       </c>
       <c r="S43" t="n">
-        <v>82.93059261895746</v>
+        <v>78.94820616457373</v>
       </c>
       <c r="T43" t="n">
-        <v>0.5788359418048948</v>
+        <v>0.5599070909893283</v>
       </c>
       <c r="U43" t="n">
         <v>126.6160396504699</v>
@@ -4207,11 +4207,11 @@
         </is>
       </c>
       <c r="X43" t="n">
-        <v>82.93059261895746</v>
+        <v>78.94820616457373</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=82.93% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=78.95% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -4235,52 +4235,52 @@
         <v>2026</v>
       </c>
       <c r="E44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G44" t="n">
-        <v>96.02426038457011</v>
+        <v>100.1760886061951</v>
       </c>
       <c r="H44" t="n">
-        <v>2.811469877005802</v>
+        <v>3.283604980073041</v>
       </c>
       <c r="I44" t="n">
-        <v>90.69108260489389</v>
+        <v>101.902133963665</v>
       </c>
       <c r="J44" t="n">
-        <v>113.6529259973059</v>
+        <v>108.540756260745</v>
       </c>
       <c r="K44" t="n">
-        <v>1.94118931811028</v>
+        <v>1.860320510021031</v>
       </c>
       <c r="L44" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M44" t="n">
-        <v>185.0623623920618</v>
+        <v>185.1842442724588</v>
       </c>
       <c r="N44" t="n">
-        <v>69.28947368421052</v>
+        <v>70.325</v>
       </c>
       <c r="O44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="P44" t="n">
-        <v>185.0623623920618</v>
+        <v>185.1842442724588</v>
       </c>
       <c r="Q44" t="n">
-        <v>69.28947368421052</v>
+        <v>70.325</v>
       </c>
       <c r="R44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="S44" t="n">
-        <v>83.11287910207426</v>
+        <v>82.67021880934045</v>
       </c>
       <c r="T44" t="n">
-        <v>1.632134160643226</v>
+        <v>1.727701335879652</v>
       </c>
       <c r="U44" t="n">
         <v>121.0188473841644</v>
@@ -4296,11 +4296,11 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>83.11287910207426</v>
+        <v>82.67021880934045</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=83.11% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=82.67% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -4324,52 +4324,52 @@
         <v>2026</v>
       </c>
       <c r="E45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G45" t="n">
-        <v>102.4367406023931</v>
+        <v>117.5693890290908</v>
       </c>
       <c r="H45" t="n">
-        <v>1.47241398353088</v>
+        <v>2.696912041121936</v>
       </c>
       <c r="I45" t="n">
-        <v>133.3421874706413</v>
+        <v>133.2410714461222</v>
       </c>
       <c r="J45" t="n">
-        <v>138.8865780666307</v>
+        <v>134.4149074996252</v>
       </c>
       <c r="K45" t="n">
-        <v>1.465205468677794</v>
+        <v>1.41176982500326</v>
       </c>
       <c r="L45" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M45" t="n">
-        <v>181.9877754532652</v>
+        <v>182.4802234152958</v>
       </c>
       <c r="N45" t="n">
-        <v>33.71052631578947</v>
+        <v>34.375</v>
       </c>
       <c r="O45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="P45" t="n">
-        <v>181.9877754532652</v>
+        <v>182.4802234152958</v>
       </c>
       <c r="Q45" t="n">
-        <v>33.71052631578947</v>
+        <v>34.375</v>
       </c>
       <c r="R45" t="n">
         <v>195.8311934408034</v>
       </c>
       <c r="S45" t="n">
-        <v>91.40918563383063</v>
+        <v>92.28450382596138</v>
       </c>
       <c r="T45" t="n">
-        <v>0.7550130518360472</v>
+        <v>0.8368388459927267</v>
       </c>
       <c r="U45" t="n">
         <v>112.5504951429215</v>
@@ -4385,11 +4385,11 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>91.40918563383063</v>
+        <v>92.28450382596138</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=91.41% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=92.28% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -4413,52 +4413,52 @@
         <v>2026</v>
       </c>
       <c r="E46" t="n">
+        <v>20</v>
+      </c>
+      <c r="F46" t="n">
         <v>19</v>
       </c>
-      <c r="F46" t="n">
-        <v>17</v>
-      </c>
       <c r="G46" t="n">
-        <v>134.8495847933821</v>
+        <v>136.8313047173424</v>
       </c>
       <c r="H46" t="n">
-        <v>1.94188163307336</v>
+        <v>2.514120583028526</v>
       </c>
       <c r="I46" t="n">
-        <v>124.5635906347636</v>
+        <v>129.1401202444324</v>
       </c>
       <c r="J46" t="n">
-        <v>155.5388593759895</v>
+        <v>151.6740223278146</v>
       </c>
       <c r="K46" t="n">
-        <v>1.100678491829755</v>
+        <v>1.101884879710657</v>
       </c>
       <c r="L46" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M46" t="n">
-        <v>187.2242110784918</v>
+        <v>187.01193669478</v>
       </c>
       <c r="N46" t="n">
-        <v>35.57894736842105</v>
+        <v>35.95</v>
       </c>
       <c r="O46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="P46" t="n">
-        <v>187.2242110784918</v>
+        <v>187.01193669478</v>
       </c>
       <c r="Q46" t="n">
-        <v>35.57894736842105</v>
+        <v>35.95</v>
       </c>
       <c r="R46" t="n">
         <v>196.1388328305384</v>
       </c>
       <c r="S46" t="n">
-        <v>126.0852506031915</v>
+        <v>121.5832947563951</v>
       </c>
       <c r="T46" t="n">
-        <v>1.09258897362871</v>
+        <v>1.081930593728427</v>
       </c>
       <c r="U46" t="n">
         <v>125.7491255686458</v>
@@ -4474,11 +4474,11 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>126.0852506031915</v>
+        <v>121.5832947563951</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=126.09% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=121.58% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -4502,52 +4502,52 @@
         <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>197.1734011497229</v>
+        <v>196.2533354157135</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1529803815317455</v>
+        <v>0.2054359597430263</v>
       </c>
       <c r="I47" t="n">
-        <v>68.7708518238762</v>
+        <v>52.02932925897922</v>
       </c>
       <c r="J47" t="n">
-        <v>195.5685574757462</v>
+        <v>191.5389692181939</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5965869982198665</v>
+        <v>0.7019875407916307</v>
       </c>
       <c r="L47" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M47" t="n">
-        <v>198.4000634090768</v>
+        <v>198.0470841511268</v>
       </c>
       <c r="N47" t="n">
-        <v>25.60542579982614</v>
+        <v>26.53475087988627</v>
       </c>
       <c r="O47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="P47" t="n">
-        <v>198.8919667590028</v>
+        <v>198.7613219094247</v>
       </c>
       <c r="Q47" t="n">
-        <v>40.1578947368421</v>
+        <v>43.425</v>
       </c>
       <c r="R47" t="n">
         <v>193.8459595711977</v>
       </c>
       <c r="S47" t="n">
-        <v>189.8391468171731</v>
+        <v>185.3898606257719</v>
       </c>
       <c r="T47" t="n">
-        <v>0.8622159058568275</v>
+        <v>0.9208266485431664</v>
       </c>
       <c r="U47" t="n">
         <v>130.8486591703272</v>
@@ -4565,7 +4565,7 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4589,52 +4589,52 @@
         <v>2026</v>
       </c>
       <c r="E48" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>198.4050298288979</v>
+        <v>197.4116289114259</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1142571312560468</v>
+        <v>0.1176767903586708</v>
       </c>
       <c r="I48" t="n">
-        <v>86.09499988689549</v>
+        <v>75.82494372432545</v>
       </c>
       <c r="J48" t="n">
-        <v>198.5330491254405</v>
+        <v>198.6063966691685</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2077539489681783</v>
+        <v>0.2362585533218085</v>
       </c>
       <c r="L48" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M48" t="n">
-        <v>197.2179224008849</v>
+        <v>197.3570262808407</v>
       </c>
       <c r="N48" t="n">
-        <v>12.65568768239685</v>
+        <v>12.94475919137651</v>
       </c>
       <c r="O48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="P48" t="n">
-        <v>197.6749026522867</v>
+        <v>197.7911575196724</v>
       </c>
       <c r="Q48" t="n">
-        <v>17.71626486213928</v>
+        <v>19.15545161903231</v>
       </c>
       <c r="R48" t="n">
         <v>192.3368460426438</v>
       </c>
       <c r="S48" t="n">
-        <v>191.1080046745255</v>
+        <v>191.5526044407993</v>
       </c>
       <c r="T48" t="n">
-        <v>0.6834732548192755</v>
+        <v>0.7809453426517626</v>
       </c>
       <c r="U48" t="n">
         <v>148.2729860112375</v>
@@ -4676,52 +4676,52 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.03928420848952716</v>
+        <v>0.07383801724012115</v>
       </c>
       <c r="I49" t="n">
-        <v>78.24471458494588</v>
+        <v>67.54170898302603</v>
       </c>
       <c r="J49" t="n">
-        <v>200</v>
+        <v>195.3168227111101</v>
       </c>
       <c r="K49" t="n">
-        <v>0.3437848424462895</v>
+        <v>0.440125846631825</v>
       </c>
       <c r="L49" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M49" t="n">
-        <v>200</v>
+        <v>199.2313995433047</v>
       </c>
       <c r="N49" t="n">
-        <v>14.3506723441126</v>
+        <v>14.83420482866237</v>
       </c>
       <c r="O49" t="n">
         <v>179.6516960231333</v>
       </c>
       <c r="P49" t="n">
-        <v>200</v>
+        <v>199.672131147541</v>
       </c>
       <c r="Q49" t="n">
-        <v>22.34210526315789</v>
+        <v>24.175</v>
       </c>
       <c r="R49" t="n">
         <v>193.5695579772771</v>
       </c>
       <c r="S49" t="n">
-        <v>200</v>
+        <v>193.2495431384828</v>
       </c>
       <c r="T49" t="n">
-        <v>0.5964682706506903</v>
+        <v>0.6147829788060031</v>
       </c>
       <c r="U49" t="n">
         <v>141.2583029624075</v>
@@ -4739,7 +4739,7 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4763,52 +4763,52 @@
         <v>2026</v>
       </c>
       <c r="E50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G50" t="n">
-        <v>195.8965903086375</v>
+        <v>190.1860027565376</v>
       </c>
       <c r="H50" t="n">
-        <v>1.219447449788111</v>
+        <v>1.811214069262746</v>
       </c>
       <c r="I50" t="n">
-        <v>165.7288014065556</v>
+        <v>162.6912701840232</v>
       </c>
       <c r="J50" t="n">
-        <v>199.5486379903699</v>
+        <v>199.1345096289146</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1629152076573967</v>
+        <v>0.3014211135351322</v>
       </c>
       <c r="L50" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M50" t="n">
-        <v>200</v>
+        <v>188.7749836195508</v>
       </c>
       <c r="N50" t="n">
-        <v>1.354595385099712</v>
+        <v>2.323166561126709</v>
       </c>
       <c r="O50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="P50" t="n">
-        <v>196.6315789473684</v>
+        <v>193.6754652824088</v>
       </c>
       <c r="Q50" t="n">
-        <v>10.46776771225995</v>
+        <v>10.60452228268771</v>
       </c>
       <c r="R50" t="n">
         <v>160.5521309789579</v>
       </c>
       <c r="S50" t="n">
-        <v>191.0159083039045</v>
+        <v>189.5889037134853</v>
       </c>
       <c r="T50" t="n">
-        <v>3.171392989508968</v>
+        <v>4.311792175500303</v>
       </c>
       <c r="U50" t="n">
         <v>135.4400555181058</v>
@@ -4826,7 +4826,7 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4850,52 +4850,52 @@
         <v>2026</v>
       </c>
       <c r="E51" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>197.4072044927651</v>
+        <v>190.9721759438794</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5937166551583655</v>
+        <v>0.8704176835186438</v>
       </c>
       <c r="I51" t="n">
-        <v>167.1930514137077</v>
+        <v>169.9274838481079</v>
       </c>
       <c r="J51" t="n">
-        <v>199.4865823478398</v>
+        <v>192.3028144606102</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1279910504674757</v>
+        <v>0.1434088457519661</v>
       </c>
       <c r="L51" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M51" t="n">
-        <v>195.959595959596</v>
+        <v>195.5244755244755</v>
       </c>
       <c r="N51" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="O51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="P51" t="n">
-        <v>195.959595959596</v>
+        <v>193.2048049441361</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.561613668896306</v>
+        <v>3.638259689213548</v>
       </c>
       <c r="R51" t="n">
         <v>165.5121650610737</v>
       </c>
       <c r="S51" t="n">
-        <v>189.9461906748481</v>
+        <v>188.6067148624402</v>
       </c>
       <c r="T51" t="n">
-        <v>1.461458145853869</v>
+        <v>1.831224401117342</v>
       </c>
       <c r="U51" t="n">
         <v>151.1230387281904</v>
@@ -4913,7 +4913,7 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4937,52 +4937,52 @@
         <v>2026</v>
       </c>
       <c r="E52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>194.825835107561</v>
+        <v>188.9958162828261</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7787430331267305</v>
+        <v>1.00129017973042</v>
       </c>
       <c r="I52" t="n">
-        <v>169.1638840881747</v>
+        <v>174.432365021141</v>
       </c>
       <c r="J52" t="n">
-        <v>199.8575276644268</v>
+        <v>199.6256320167606</v>
       </c>
       <c r="K52" t="n">
-        <v>0.06289546852160235</v>
+        <v>0.1585411434662608</v>
       </c>
       <c r="L52" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M52" t="n">
-        <v>196.6386554621849</v>
+        <v>196.19941873463</v>
       </c>
       <c r="N52" t="n">
-        <v>8.552631578947368</v>
+        <v>11.475</v>
       </c>
       <c r="O52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="P52" t="n">
-        <v>196.6386554621849</v>
+        <v>192.142663329359</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.611034800763306</v>
+        <v>5.605039689690354</v>
       </c>
       <c r="R52" t="n">
         <v>154.7555469695623</v>
       </c>
       <c r="S52" t="n">
-        <v>191.551320846184</v>
+        <v>190.2365743867556</v>
       </c>
       <c r="T52" t="n">
-        <v>2.141472433852223</v>
+        <v>2.985689708770413</v>
       </c>
       <c r="U52" t="n">
         <v>133.8716916594558</v>
@@ -5000,7 +5000,7 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5024,59 +5024,59 @@
         <v>2026</v>
       </c>
       <c r="E53" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F53" t="n">
-        <v>2128</v>
+        <v>2279</v>
       </c>
       <c r="G53" t="n">
-        <v>23.24265921886086</v>
+        <v>19.49960594346439</v>
       </c>
       <c r="H53" t="n">
-        <v>27.60851280394742</v>
+        <v>22.77922614753295</v>
       </c>
       <c r="I53" t="n">
-        <v>27.58321985589428</v>
+        <v>35.23746831954708</v>
       </c>
       <c r="J53" t="n">
-        <v>20.44901503425639</v>
+        <v>19.62979676942301</v>
       </c>
       <c r="K53" t="n">
-        <v>22.53472728636974</v>
+        <v>21.7087593849698</v>
       </c>
       <c r="L53" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M53" t="n">
-        <v>162.1656348846054</v>
+        <v>161.6595762447816</v>
       </c>
       <c r="N53" t="n">
-        <v>960.578947368421</v>
+        <v>960.425</v>
       </c>
       <c r="O53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="P53" t="n">
-        <v>162.1656348846054</v>
+        <v>161.6595762447816</v>
       </c>
       <c r="Q53" t="n">
-        <v>960.578947368421</v>
+        <v>960.425</v>
       </c>
       <c r="R53" t="n">
         <v>188.2648408233968</v>
       </c>
       <c r="S53" t="n">
-        <v>33.35473458934206</v>
+        <v>34.1856960792193</v>
       </c>
       <c r="T53" t="n">
-        <v>46.1343206529984</v>
+        <v>48.85744400228063</v>
       </c>
       <c r="U53" t="n">
         <v>92.2349408254034</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>20.44901503425639</v>
+        <v>19.49960594346439</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=20.45% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=19.50% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5113,52 +5113,52 @@
         <v>2026</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F54" t="n">
-        <v>1000</v>
+        <v>1069</v>
       </c>
       <c r="G54" t="n">
-        <v>21.83206715412024</v>
+        <v>22.0104914430118</v>
       </c>
       <c r="H54" t="n">
-        <v>12.4738250460123</v>
+        <v>12.37528277567318</v>
       </c>
       <c r="I54" t="n">
-        <v>30.20609014595014</v>
+        <v>38.4591918317379</v>
       </c>
       <c r="J54" t="n">
-        <v>21.5307402945977</v>
+        <v>20.86573678611043</v>
       </c>
       <c r="K54" t="n">
-        <v>11.37805163170186</v>
+        <v>11.10529454897445</v>
       </c>
       <c r="L54" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M54" t="n">
-        <v>162.6260942449485</v>
+        <v>162.0216712531311</v>
       </c>
       <c r="N54" t="n">
-        <v>456.2631578947368</v>
+        <v>454.45</v>
       </c>
       <c r="O54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="P54" t="n">
-        <v>162.6260942449485</v>
+        <v>162.0216712531311</v>
       </c>
       <c r="Q54" t="n">
-        <v>456.2631578947368</v>
+        <v>454.45</v>
       </c>
       <c r="R54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="S54" t="n">
-        <v>34.11324738386026</v>
+        <v>34.78772843329066</v>
       </c>
       <c r="T54" t="n">
-        <v>22.26762956087289</v>
+        <v>23.30953662574492</v>
       </c>
       <c r="U54" t="n">
         <v>91.67135817890519</v>
@@ -5174,11 +5174,11 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>21.5307402945977</v>
+        <v>20.86573678611043</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=21.53% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=20.87% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5202,52 +5202,52 @@
         <v>2026</v>
       </c>
       <c r="E55" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>1122</v>
+        <v>1204</v>
       </c>
       <c r="G55" t="n">
-        <v>24.56807003457765</v>
+        <v>25.14083857716377</v>
       </c>
       <c r="H55" t="n">
-        <v>14.35624950110909</v>
+        <v>14.69550352042221</v>
       </c>
       <c r="I55" t="n">
-        <v>31.0709119837712</v>
+        <v>38.25160771522186</v>
       </c>
       <c r="J55" t="n">
-        <v>23.26637498008379</v>
+        <v>23.2194777075171</v>
       </c>
       <c r="K55" t="n">
-        <v>13.17654509709004</v>
+        <v>13.34124330195221</v>
       </c>
       <c r="L55" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M55" t="n">
-        <v>161.9773827308954</v>
+        <v>161.5406661246429</v>
       </c>
       <c r="N55" t="n">
-        <v>504.6315789473684</v>
+        <v>506.275</v>
       </c>
       <c r="O55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="P55" t="n">
-        <v>161.9773827308954</v>
+        <v>161.5406661246429</v>
       </c>
       <c r="Q55" t="n">
-        <v>504.6315789473684</v>
+        <v>506.275</v>
       </c>
       <c r="R55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="S55" t="n">
-        <v>30.31248068057727</v>
+        <v>31.13756976946399</v>
       </c>
       <c r="T55" t="n">
-        <v>21.75927235930101</v>
+        <v>23.17726626922712</v>
       </c>
       <c r="U55" t="n">
         <v>92.1901984902002</v>
@@ -5263,11 +5263,11 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>23.26637498008379</v>
+        <v>23.2194777075171</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=23.27% sobre 19 sem</t>
+          <t>DeepAR: menor SMAPE real=23.22% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5291,52 +5291,52 @@
         <v>2026</v>
       </c>
       <c r="E56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F56" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G56" t="n">
-        <v>50.87017832092096</v>
+        <v>72.59780631431283</v>
       </c>
       <c r="H56" t="n">
-        <v>1.721520255055763</v>
+        <v>2.927095271311128</v>
       </c>
       <c r="I56" t="n">
-        <v>158.6050847963975</v>
+        <v>154.1439500713238</v>
       </c>
       <c r="J56" t="n">
-        <v>60.38041763078138</v>
+        <v>57.68251133907203</v>
       </c>
       <c r="K56" t="n">
-        <v>2.065272317818089</v>
+        <v>1.974453659767151</v>
       </c>
       <c r="L56" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M56" t="n">
-        <v>165.3708526408925</v>
+        <v>166.3141326689463</v>
       </c>
       <c r="N56" t="n">
-        <v>41.23684210526316</v>
+        <v>43.85</v>
       </c>
       <c r="O56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="P56" t="n">
-        <v>165.3708526408925</v>
+        <v>166.3141326689463</v>
       </c>
       <c r="Q56" t="n">
-        <v>41.23684210526316</v>
+        <v>43.85</v>
       </c>
       <c r="R56" t="n">
         <v>197.7368060568652</v>
       </c>
       <c r="S56" t="n">
-        <v>44.67504455982316</v>
+        <v>47.23705434251701</v>
       </c>
       <c r="T56" t="n">
-        <v>1.380595680498687</v>
+        <v>1.441218211973871</v>
       </c>
       <c r="U56" t="n">
         <v>104.7066447751141</v>
@@ -5352,11 +5352,11 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>44.67504455982316</v>
+        <v>47.23705434251701</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=44.68% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=47.24% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5380,59 +5380,59 @@
         <v>2026</v>
       </c>
       <c r="E57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F57" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G57" t="n">
-        <v>89.45073653074309</v>
+        <v>98.10399639077968</v>
       </c>
       <c r="H57" t="n">
-        <v>1.046812585803582</v>
+        <v>1.624721621133489</v>
       </c>
       <c r="I57" t="n">
-        <v>161.5065017675632</v>
+        <v>164.0555422208552</v>
       </c>
       <c r="J57" t="n">
-        <v>114.7616231997743</v>
+        <v>118.4808392854339</v>
       </c>
       <c r="K57" t="n">
-        <v>1.488718622791548</v>
+        <v>1.462888092115611</v>
       </c>
       <c r="L57" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M57" t="n">
-        <v>163.4899500853628</v>
+        <v>164.8154525810946</v>
       </c>
       <c r="N57" t="n">
-        <v>18.31578947368421</v>
+        <v>19.3</v>
       </c>
       <c r="O57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="P57" t="n">
-        <v>163.4899500853628</v>
+        <v>164.8154525810946</v>
       </c>
       <c r="Q57" t="n">
-        <v>18.31578947368421</v>
+        <v>19.3</v>
       </c>
       <c r="R57" t="n">
         <v>197.2831175654684</v>
       </c>
       <c r="S57" t="n">
-        <v>93.38885700918117</v>
+        <v>92.85103094933392</v>
       </c>
       <c r="T57" t="n">
-        <v>0.8391190891061855</v>
+        <v>0.8263998232182921</v>
       </c>
       <c r="U57" t="n">
         <v>124.2225772452616</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5441,11 +5441,11 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>89.45073653074309</v>
+        <v>92.85103094933392</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=89.45% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=92.85% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5469,52 +5469,52 @@
         <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F58" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G58" t="n">
-        <v>101.1230093879027</v>
+        <v>91.49378868818445</v>
       </c>
       <c r="H58" t="n">
-        <v>1.313375448207419</v>
+        <v>1.674555031619139</v>
       </c>
       <c r="I58" t="n">
-        <v>161.0349167497434</v>
+        <v>158.4722608607674</v>
       </c>
       <c r="J58" t="n">
-        <v>105.6303668976963</v>
+        <v>108.2980179309141</v>
       </c>
       <c r="K58" t="n">
-        <v>1.579491473670759</v>
+        <v>1.63337824655962</v>
       </c>
       <c r="L58" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M58" t="n">
-        <v>167.6753221837887</v>
+        <v>168.3159463185017</v>
       </c>
       <c r="N58" t="n">
-        <v>23.47368421052632</v>
+        <v>25.075</v>
       </c>
       <c r="O58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="P58" t="n">
-        <v>167.6753221837887</v>
+        <v>168.3159463185017</v>
       </c>
       <c r="Q58" t="n">
-        <v>23.47368421052632</v>
+        <v>25.075</v>
       </c>
       <c r="R58" t="n">
         <v>197.6615055783608</v>
       </c>
       <c r="S58" t="n">
-        <v>88.19208161899802</v>
+        <v>88.74442516281512</v>
       </c>
       <c r="T58" t="n">
-        <v>0.9554666528117263</v>
+        <v>1.007184664798359</v>
       </c>
       <c r="U58" t="n">
         <v>111.9755139895278</v>
@@ -5530,11 +5530,11 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>88.19208161899802</v>
+        <v>88.74442516281512</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=88.19% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=88.74% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5558,52 +5558,52 @@
         <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>198.4585215841297</v>
+        <v>199.4821021973625</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2287940483799308</v>
+        <v>0.2183781974394378</v>
       </c>
       <c r="I59" t="n">
-        <v>165.3309864977213</v>
+        <v>163.442478475025</v>
       </c>
       <c r="J59" t="n">
-        <v>192.5368174319365</v>
+        <v>192.9099765603397</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2214133618233808</v>
+        <v>0.2108791554023861</v>
       </c>
       <c r="L59" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M59" t="n">
-        <v>171.7647058823529</v>
+        <v>173.3333333333333</v>
       </c>
       <c r="N59" t="n">
-        <v>2.710526315789474</v>
+        <v>2.95</v>
       </c>
       <c r="O59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="P59" t="n">
-        <v>171.7647058823529</v>
+        <v>173.3333333333333</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.710526315789474</v>
+        <v>2.95</v>
       </c>
       <c r="R59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="S59" t="n">
-        <v>185.7921678432019</v>
+        <v>186.5025594510418</v>
       </c>
       <c r="T59" t="n">
-        <v>0.3605131591993669</v>
+        <v>0.3762815311939612</v>
       </c>
       <c r="U59" t="n">
         <v>167.6265476269683</v>
@@ -5645,52 +5645,52 @@
         <v>2026</v>
       </c>
       <c r="E60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F60" t="n">
         <v>3</v>
       </c>
       <c r="G60" t="n">
-        <v>194.2894579019483</v>
+        <v>197.7007515643313</v>
       </c>
       <c r="H60" t="n">
-        <v>0.192270851063556</v>
+        <v>0.1640807419990983</v>
       </c>
       <c r="I60" t="n">
-        <v>178.4437449361936</v>
+        <v>179.6544870721095</v>
       </c>
       <c r="J60" t="n">
-        <v>198.6597355840884</v>
+        <v>198.726748804884</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1659645822432419</v>
+        <v>0.1581502749256105</v>
       </c>
       <c r="L60" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M60" t="n">
-        <v>163.0769230769231</v>
+        <v>165.7142857142857</v>
       </c>
       <c r="N60" t="n">
-        <v>1.736842105263158</v>
+        <v>1.95</v>
       </c>
       <c r="O60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="P60" t="n">
-        <v>163.0769230769231</v>
+        <v>165.7142857142857</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.736842105263158</v>
+        <v>1.95</v>
       </c>
       <c r="R60" t="n">
         <v>199.0965028052728</v>
       </c>
       <c r="S60" t="n">
-        <v>188.9577766873559</v>
+        <v>189.5098878529882</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2514451322102222</v>
+        <v>0.2523929302587709</v>
       </c>
       <c r="U60" t="n">
         <v>167.0169829765832</v>
@@ -5732,52 +5732,52 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>198.4172888733546</v>
+        <v>199.9502411083014</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1103024224920047</v>
+        <v>0.0708607758842998</v>
       </c>
       <c r="I61" t="n">
-        <v>177.7053649160375</v>
+        <v>178.3754768379913</v>
       </c>
       <c r="J61" t="n">
-        <v>198.3975506268872</v>
+        <v>198.4776730955428</v>
       </c>
       <c r="K61" t="n">
-        <v>0.137526459316728</v>
+        <v>0.135473811856939</v>
       </c>
       <c r="L61" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M61" t="n">
-        <v>185.4545454545454</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>1.210526315789474</v>
+        <v>1.225</v>
       </c>
       <c r="O61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="P61" t="n">
-        <v>185.4545454545454</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.210526315789474</v>
+        <v>1.225</v>
       </c>
       <c r="R61" t="n">
         <v>199.3694289811982</v>
       </c>
       <c r="S61" t="n">
-        <v>194.4610071616202</v>
+        <v>194.7379568035392</v>
       </c>
       <c r="T61" t="n">
-        <v>0.1374148461663683</v>
+        <v>0.1461059149062048</v>
       </c>
       <c r="U61" t="n">
         <v>167.1297521794813</v>
@@ -5819,52 +5819,52 @@
         <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G62" t="n">
-        <v>131.3991370717231</v>
+        <v>123.8814038245265</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8216753045727233</v>
+        <v>0.7447802726545814</v>
       </c>
       <c r="I62" t="n">
-        <v>66.55440226622002</v>
+        <v>51.86246745886869</v>
       </c>
       <c r="J62" t="n">
-        <v>131.2644356700371</v>
+        <v>130.9495021586091</v>
       </c>
       <c r="K62" t="n">
-        <v>1.792143665152412</v>
+        <v>2.035626480551362</v>
       </c>
       <c r="L62" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M62" t="n">
-        <v>175.5235927343014</v>
+        <v>176.3126304888907</v>
       </c>
       <c r="N62" t="n">
-        <v>17.10526315789474</v>
+        <v>20.65</v>
       </c>
       <c r="O62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="P62" t="n">
-        <v>175.5235927343014</v>
+        <v>176.3126304888907</v>
       </c>
       <c r="Q62" t="n">
-        <v>17.10526315789474</v>
+        <v>20.65</v>
       </c>
       <c r="R62" t="n">
         <v>188.4656733609786</v>
       </c>
       <c r="S62" t="n">
-        <v>118.4075208684841</v>
+        <v>116.5089827846871</v>
       </c>
       <c r="T62" t="n">
-        <v>0.9147199969677026</v>
+        <v>1.003534982270476</v>
       </c>
       <c r="U62" t="n">
         <v>127.8730185036105</v>
@@ -5880,11 +5880,11 @@
         </is>
       </c>
       <c r="X62" t="n">
-        <v>118.4075208684841</v>
+        <v>116.5089827846871</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=118.41% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=116.51% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -5908,52 +5908,52 @@
         <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F63" t="n">
         <v>7</v>
       </c>
       <c r="G63" t="n">
-        <v>162.6051633809513</v>
+        <v>156.9330621411308</v>
       </c>
       <c r="H63" t="n">
-        <v>0.4814538317421231</v>
+        <v>0.501227868029037</v>
       </c>
       <c r="I63" t="n">
-        <v>81.74557255773445</v>
+        <v>69.84803023883232</v>
       </c>
       <c r="J63" t="n">
-        <v>160.5762472922584</v>
+        <v>162.5474349276456</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4223166429292686</v>
+        <v>0.4018922233822466</v>
       </c>
       <c r="L63" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M63" t="n">
-        <v>176.4842587752804</v>
+        <v>177.6600458365164</v>
       </c>
       <c r="N63" t="n">
-        <v>7.368421052631579</v>
+        <v>8.503647849212859</v>
       </c>
       <c r="O63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="P63" t="n">
-        <v>176.4842587752804</v>
+        <v>177.6600458365164</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.368421052631579</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R63" t="n">
         <v>186.3893216158546</v>
       </c>
       <c r="S63" t="n">
-        <v>131.1240426073105</v>
+        <v>134.567840476945</v>
       </c>
       <c r="T63" t="n">
-        <v>0.5257290190575565</v>
+        <v>0.6279944860502141</v>
       </c>
       <c r="U63" t="n">
         <v>131.8859677830883</v>
@@ -5995,52 +5995,52 @@
         <v>2026</v>
       </c>
       <c r="E64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>169.1165828986423</v>
+        <v>150.1672909984136</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5602471188428393</v>
+        <v>0.6246504300677056</v>
       </c>
       <c r="I64" t="n">
-        <v>78.0870900496615</v>
+        <v>72.92360982323459</v>
       </c>
       <c r="J64" t="n">
-        <v>165.4971729021378</v>
+        <v>158.2336582834401</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5568628189725624</v>
+        <v>0.5515223531598076</v>
       </c>
       <c r="L64" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M64" t="n">
-        <v>176.5775401069519</v>
+        <v>177.0343773873185</v>
       </c>
       <c r="N64" t="n">
-        <v>10.36842105263158</v>
+        <v>12.45</v>
       </c>
       <c r="O64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="P64" t="n">
-        <v>176.5775401069519</v>
+        <v>177.0343773873185</v>
       </c>
       <c r="Q64" t="n">
-        <v>10.36842105263158</v>
+        <v>12.45</v>
       </c>
       <c r="R64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="S64" t="n">
-        <v>144.1050038899509</v>
+        <v>139.4880097887306</v>
       </c>
       <c r="T64" t="n">
-        <v>0.6735217199073611</v>
+        <v>0.7096876609936263</v>
       </c>
       <c r="U64" t="n">
         <v>132.574641557417</v>
@@ -6058,7 +6058,7 @@
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6082,52 +6082,52 @@
         <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G65" t="n">
-        <v>174.9621849565533</v>
+        <v>164.2406054145438</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6906981302002645</v>
+        <v>0.5031218849050085</v>
       </c>
       <c r="I65" t="n">
-        <v>130.2538165104266</v>
+        <v>124.1398173354868</v>
       </c>
       <c r="J65" t="n">
-        <v>188.6285607672464</v>
+        <v>181.0791972107662</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3784678200407356</v>
+        <v>0.3753839700944796</v>
       </c>
       <c r="L65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="M65" t="n">
-        <v>190.5411382191568</v>
+        <v>190.5140813081989</v>
       </c>
       <c r="N65" t="n">
-        <v>17</v>
+        <v>18.05</v>
       </c>
       <c r="O65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="P65" t="n">
-        <v>190.5411382191568</v>
+        <v>190.5140813081989</v>
       </c>
       <c r="Q65" t="n">
-        <v>17</v>
+        <v>18.05</v>
       </c>
       <c r="R65" t="n">
         <v>191.9303948964172</v>
       </c>
       <c r="S65" t="n">
-        <v>163.1457219188228</v>
+        <v>161.9562297696662</v>
       </c>
       <c r="T65" t="n">
-        <v>0.8506428596457795</v>
+        <v>1.03790360753235</v>
       </c>
       <c r="U65" t="n">
         <v>113.9712651292745</v>
@@ -6145,7 +6145,7 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6169,59 +6169,59 @@
         <v>2026</v>
       </c>
       <c r="E66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
-        <v>189.1575825432529</v>
+        <v>189.4012658429347</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2719073590086947</v>
+        <v>0.2692268827356448</v>
       </c>
       <c r="I66" t="n">
-        <v>146.8781158240608</v>
+        <v>146.9871894171194</v>
       </c>
       <c r="J66" t="n">
-        <v>193.2466259789231</v>
+        <v>186.671418728838</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2704853797460072</v>
+        <v>0.2805501287685855</v>
       </c>
       <c r="L66" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M66" t="n">
-        <v>193.7098844672657</v>
+        <v>192.9717586649551</v>
       </c>
       <c r="N66" t="n">
-        <v>8.894736842105264</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="P66" t="n">
-        <v>193.7098844672657</v>
+        <v>192.9717586649551</v>
       </c>
       <c r="Q66" t="n">
-        <v>8.894736842105264</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="S66" t="n">
-        <v>183.0260032855074</v>
+        <v>178.5915885387897</v>
       </c>
       <c r="T66" t="n">
-        <v>0.4989162885551428</v>
+        <v>0.5632527591119588</v>
       </c>
       <c r="U66" t="n">
         <v>118.44057480835</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -6232,7 +6232,7 @@
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6256,52 +6256,52 @@
         <v>2026</v>
       </c>
       <c r="E67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F67" t="n">
         <v>2</v>
       </c>
       <c r="G67" t="n">
-        <v>195.2253355795644</v>
+        <v>192.1195028106798</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3983883461880737</v>
+        <v>0.3484548554492455</v>
       </c>
       <c r="I67" t="n">
-        <v>145.9438817861322</v>
+        <v>137.6516466078508</v>
       </c>
       <c r="J67" t="n">
-        <v>199.3097191502</v>
+        <v>199.34423319269</v>
       </c>
       <c r="K67" t="n">
-        <v>0.2915347690590922</v>
+        <v>0.3058159597885096</v>
       </c>
       <c r="L67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="M67" t="n">
-        <v>193.7098844672657</v>
+        <v>194.0243902439024</v>
       </c>
       <c r="N67" t="n">
-        <v>9.052631578947368</v>
+        <v>9.65</v>
       </c>
       <c r="O67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="P67" t="n">
-        <v>193.7098844672657</v>
+        <v>194.0243902439024</v>
       </c>
       <c r="Q67" t="n">
-        <v>9.052631578947368</v>
+        <v>9.65</v>
       </c>
       <c r="R67" t="n">
         <v>191.2393501485975</v>
       </c>
       <c r="S67" t="n">
-        <v>182.9206543630087</v>
+        <v>183.7746216448583</v>
       </c>
       <c r="T67" t="n">
-        <v>0.5825659356753343</v>
+        <v>0.7133704864658601</v>
       </c>
       <c r="U67" t="n">
         <v>116.630186356802</v>
@@ -6343,25 +6343,25 @@
         <v>2026</v>
       </c>
       <c r="E68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>200</v>
+        <v>199.988140539529</v>
       </c>
       <c r="H68" t="n">
-        <v>0.06428887613126047</v>
+        <v>0.05827870637370154</v>
       </c>
       <c r="I68" t="n">
-        <v>185.5263813670961</v>
+        <v>183.5383709430125</v>
       </c>
       <c r="J68" t="n">
-        <v>199.7828034264477</v>
+        <v>199.7936632551253</v>
       </c>
       <c r="K68" t="n">
-        <v>0.06645011343186964</v>
+        <v>0.06366529122400008</v>
       </c>
       <c r="L68" t="n">
         <v>198.3312090033645</v>
@@ -6370,7 +6370,7 @@
         <v>200</v>
       </c>
       <c r="N68" t="n">
-        <v>4.925787257750323</v>
+        <v>4.904497894862807</v>
       </c>
       <c r="O68" t="n">
         <v>188.2784643365136</v>
@@ -6379,16 +6379,16 @@
         <v>200</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="R68" t="n">
         <v>199.7672857698158</v>
       </c>
       <c r="S68" t="n">
-        <v>196.6829640048581</v>
+        <v>196.8488158046152</v>
       </c>
       <c r="T68" t="n">
-        <v>0.2368618284134104</v>
+        <v>0.3092824996220025</v>
       </c>
       <c r="U68" t="n">
         <v>177.2448922419183</v>
@@ -6430,25 +6430,25 @@
         <v>2026</v>
       </c>
       <c r="E69" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>197.3456030435345</v>
+        <v>198.1317768745953</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1573124460660443</v>
+        <v>0.07715038600420325</v>
       </c>
       <c r="I69" t="n">
-        <v>176.5523739818266</v>
+        <v>171.5447439761989</v>
       </c>
       <c r="J69" t="n">
-        <v>199.3873217860459</v>
+        <v>199.4179556967436</v>
       </c>
       <c r="K69" t="n">
-        <v>0.07890491428071096</v>
+        <v>0.07628203787767085</v>
       </c>
       <c r="L69" t="n">
         <v>194.4182830751776</v>
@@ -6457,7 +6457,7 @@
         <v>200</v>
       </c>
       <c r="N69" t="n">
-        <v>2.421052631578947</v>
+        <v>2.525</v>
       </c>
       <c r="O69" t="n">
         <v>190.8574288418282</v>
@@ -6466,16 +6466,16 @@
         <v>200</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.421052631578947</v>
+        <v>2.525</v>
       </c>
       <c r="R69" t="n">
         <v>199.6130972886749</v>
       </c>
       <c r="S69" t="n">
-        <v>198.3286558355248</v>
+        <v>198.4122230437486</v>
       </c>
       <c r="T69" t="n">
-        <v>0.1482711720901729</v>
+        <v>0.1830226391484761</v>
       </c>
       <c r="U69" t="n">
         <v>185.6695408532579</v>
@@ -6517,7 +6517,7 @@
         <v>2026</v>
       </c>
       <c r="E70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -6526,16 +6526,16 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1072454671372258</v>
+        <v>0.01690032095695999</v>
       </c>
       <c r="I70" t="n">
-        <v>188.7537432880503</v>
+        <v>188.453973372859</v>
       </c>
       <c r="J70" t="n">
         <v>200</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01611044537267105</v>
+        <v>0.01607239648951918</v>
       </c>
       <c r="L70" t="n">
         <v>198.9765474653765</v>
@@ -6544,7 +6544,7 @@
         <v>200</v>
       </c>
       <c r="N70" t="n">
-        <v>3.000395821091233</v>
+        <v>2.850376030036672</v>
       </c>
       <c r="O70" t="n">
         <v>192.937344462188</v>
@@ -6553,7 +6553,7 @@
         <v>200</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.236842105263158</v>
+        <v>3.075</v>
       </c>
       <c r="R70" t="n">
         <v>199.6974055100667</v>
@@ -6562,7 +6562,7 @@
         <v>200</v>
       </c>
       <c r="T70" t="n">
-        <v>0.1224972249654891</v>
+        <v>0.1600966959150359</v>
       </c>
       <c r="U70" t="n">
         <v>184.4638384017739</v>
@@ -6604,59 +6604,59 @@
         <v>2026</v>
       </c>
       <c r="E71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F71" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G71" t="n">
-        <v>45.82204069402005</v>
+        <v>59.39563859697882</v>
       </c>
       <c r="H71" t="n">
-        <v>2.038774642227337</v>
+        <v>3.012223041556701</v>
       </c>
       <c r="I71" t="n">
-        <v>129.9990806504396</v>
+        <v>143.4057585362926</v>
       </c>
       <c r="J71" t="n">
-        <v>181.9880034485936</v>
+        <v>182.3481421699075</v>
       </c>
       <c r="K71" t="n">
-        <v>4.205103676707298</v>
+        <v>4.480961701689276</v>
       </c>
       <c r="L71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="M71" t="n">
-        <v>76.44148826641481</v>
+        <v>73.55375808142874</v>
       </c>
       <c r="N71" t="n">
-        <v>4.461687547631855</v>
+        <v>4.341667333711549</v>
       </c>
       <c r="O71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="P71" t="n">
-        <v>187.5628945654752</v>
+        <v>188.1847498372014</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.2884948607661</v>
+        <v>4.574070117727795</v>
       </c>
       <c r="R71" t="n">
         <v>185.267595267154</v>
       </c>
       <c r="S71" t="n">
-        <v>56.26253696619978</v>
+        <v>54.83436778227493</v>
       </c>
       <c r="T71" t="n">
-        <v>4.953444167374145</v>
+        <v>4.827419988379988</v>
       </c>
       <c r="U71" t="n">
         <v>93.16202342284906</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -6665,11 +6665,11 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>45.82204069402005</v>
+        <v>54.83436778227493</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=45.82% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=54.83% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -6693,59 +6693,59 @@
         <v>2026</v>
       </c>
       <c r="E72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G72" t="n">
-        <v>88.75328127330114</v>
+        <v>91.56196775349026</v>
       </c>
       <c r="H72" t="n">
-        <v>1.273751500298519</v>
+        <v>1.663026533958095</v>
       </c>
       <c r="I72" t="n">
-        <v>135.1163038802778</v>
+        <v>151.0433307550491</v>
       </c>
       <c r="J72" t="n">
-        <v>97.00281078314966</v>
+        <v>96.85877469435373</v>
       </c>
       <c r="K72" t="n">
-        <v>1.286265630916457</v>
+        <v>1.381957484185444</v>
       </c>
       <c r="L72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="M72" t="n">
-        <v>96.43718470396682</v>
+        <v>93.27621259369054</v>
       </c>
       <c r="N72" t="n">
-        <v>2.321839312638196</v>
+        <v>2.276963503510039</v>
       </c>
       <c r="O72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="P72" t="n">
-        <v>157.7563524619638</v>
+        <v>160.3965804330911</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.77161774667331</v>
+        <v>1.933036859339645</v>
       </c>
       <c r="R72" t="n">
         <v>161.2927483340683</v>
       </c>
       <c r="S72" t="n">
-        <v>90.31026369645171</v>
+        <v>86.32696783685466</v>
       </c>
       <c r="T72" t="n">
-        <v>2.188836707072257</v>
+        <v>2.104661029299291</v>
       </c>
       <c r="U72" t="n">
         <v>104.036396201453</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -6754,11 +6754,11 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>88.75328127330114</v>
+        <v>86.32696783685466</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=88.75% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=86.33% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -6782,52 +6782,52 @@
         <v>2026</v>
       </c>
       <c r="E73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G73" t="n">
-        <v>60.37376690297306</v>
+        <v>68.94883353215404</v>
       </c>
       <c r="H73" t="n">
-        <v>1.423320526030519</v>
+        <v>1.91737407432194</v>
       </c>
       <c r="I73" t="n">
-        <v>144.4569542682877</v>
+        <v>148.5993365374143</v>
       </c>
       <c r="J73" t="n">
-        <v>167.6451026349307</v>
+        <v>169.220217719738</v>
       </c>
       <c r="K73" t="n">
-        <v>2.318164934182062</v>
+        <v>2.451722676942217</v>
       </c>
       <c r="L73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="M73" t="n">
-        <v>99.42587142276584</v>
+        <v>95.65853798886769</v>
       </c>
       <c r="N73" t="n">
-        <v>2.018178237111945</v>
+        <v>1.985706949234009</v>
       </c>
       <c r="O73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="P73" t="n">
-        <v>164.8485968348066</v>
+        <v>166.6061669930662</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.220180862656712</v>
+        <v>2.359171819523877</v>
       </c>
       <c r="R73" t="n">
         <v>173.6314937555617</v>
       </c>
       <c r="S73" t="n">
-        <v>60.23654364119692</v>
+        <v>58.6602811276452</v>
       </c>
       <c r="T73" t="n">
-        <v>2.077975064835356</v>
+        <v>2.036843857846089</v>
       </c>
       <c r="U73" t="n">
         <v>104.3951484726403</v>
@@ -6843,11 +6843,11 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>60.23654364119692</v>
+        <v>58.6602811276452</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=60.24% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=58.66% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -6871,52 +6871,52 @@
         <v>2026</v>
       </c>
       <c r="E74" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F74" t="n">
         <v>9</v>
       </c>
       <c r="G74" t="n">
-        <v>170.8932475762028</v>
+        <v>170.145993889533</v>
       </c>
       <c r="H74" t="n">
-        <v>1.090117710506654</v>
+        <v>3.149849585366976</v>
       </c>
       <c r="I74" t="n">
-        <v>150.4930337580551</v>
+        <v>148.9425712788151</v>
       </c>
       <c r="J74" t="n">
-        <v>187.0298527328072</v>
+        <v>187.6783600961669</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4419976246736432</v>
+        <v>0.4214485667936149</v>
       </c>
       <c r="L74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="M74" t="n">
-        <v>189.6448066714631</v>
+        <v>190.1625663378899</v>
       </c>
       <c r="N74" t="n">
-        <v>26.4294632033182</v>
+        <v>28.85799004315229</v>
       </c>
       <c r="O74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="P74" t="n">
-        <v>189.6448066714631</v>
+        <v>190.1625663378899</v>
       </c>
       <c r="Q74" t="n">
-        <v>26.68421052631579</v>
+        <v>29.1</v>
       </c>
       <c r="R74" t="n">
         <v>193.1141809259393</v>
       </c>
       <c r="S74" t="n">
-        <v>158.6719930560306</v>
+        <v>160.7383934032291</v>
       </c>
       <c r="T74" t="n">
-        <v>0.6877511468803854</v>
+        <v>0.7997630920275045</v>
       </c>
       <c r="U74" t="n">
         <v>113.155914904339</v>
@@ -6958,52 +6958,52 @@
         <v>2026</v>
       </c>
       <c r="E75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F75" t="n">
         <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>178.8783298006462</v>
+        <v>169.8418149992723</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5510931143417461</v>
+        <v>1.321079360199853</v>
       </c>
       <c r="I75" t="n">
-        <v>156.7678944986594</v>
+        <v>157.2380343536269</v>
       </c>
       <c r="J75" t="n">
-        <v>196.6160780833582</v>
+        <v>196.7852741791903</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3031989103336238</v>
+        <v>0.2880628842185335</v>
       </c>
       <c r="L75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="M75" t="n">
-        <v>189.0211955227435</v>
+        <v>189.5701357466064</v>
       </c>
       <c r="N75" t="n">
-        <v>11.89375382888973</v>
+        <v>12.64906613744525</v>
       </c>
       <c r="O75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="P75" t="n">
-        <v>189.0211955227435</v>
+        <v>189.5701357466064</v>
       </c>
       <c r="Q75" t="n">
-        <v>12.21052631578947</v>
+        <v>12.95</v>
       </c>
       <c r="R75" t="n">
         <v>193.2892416279341</v>
       </c>
       <c r="S75" t="n">
-        <v>166.46519558855</v>
+        <v>168.1419358091225</v>
       </c>
       <c r="T75" t="n">
-        <v>0.4770796541136497</v>
+        <v>0.5189411821855205</v>
       </c>
       <c r="U75" t="n">
         <v>110.9447640026735</v>
@@ -7045,52 +7045,52 @@
         <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F76" t="n">
         <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>184.7079129050776</v>
+        <v>176.9036149455106</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6694985058293008</v>
+        <v>1.878543571681752</v>
       </c>
       <c r="I76" t="n">
-        <v>155.145394665424</v>
+        <v>154.9841830576604</v>
       </c>
       <c r="J76" t="n">
-        <v>195.1948412340681</v>
+        <v>195.4350991723647</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2055997108742528</v>
+        <v>0.1957219736138898</v>
       </c>
       <c r="L76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="M76" t="n">
-        <v>189.1729323308271</v>
+        <v>189.7142857142857</v>
       </c>
       <c r="N76" t="n">
-        <v>14.08949935771264</v>
+        <v>15.31640743688422</v>
       </c>
       <c r="O76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="P76" t="n">
-        <v>189.1729323308271</v>
+        <v>189.7142857142857</v>
       </c>
       <c r="Q76" t="n">
-        <v>14.71052631578947</v>
+        <v>16.375</v>
       </c>
       <c r="R76" t="n">
         <v>192.8448970866968</v>
       </c>
       <c r="S76" t="n">
-        <v>173.9560715580791</v>
+        <v>175.2582679801752</v>
       </c>
       <c r="T76" t="n">
-        <v>0.4352548070728992</v>
+        <v>0.5172447171484865</v>
       </c>
       <c r="U76" t="n">
         <v>118.0223455785753</v>
@@ -7132,52 +7132,52 @@
         <v>2026</v>
       </c>
       <c r="E77" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F77" t="n">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="G77" t="n">
-        <v>50.23937633796256</v>
+        <v>48.13996557180829</v>
       </c>
       <c r="H77" t="n">
-        <v>7.13896712350043</v>
+        <v>6.80594682904123</v>
       </c>
       <c r="I77" t="n">
-        <v>88.01776519136712</v>
+        <v>77.76772218573589</v>
       </c>
       <c r="J77" t="n">
-        <v>37.10004537508804</v>
+        <v>35.7354676737036</v>
       </c>
       <c r="K77" t="n">
-        <v>6.776254930868525</v>
+        <v>6.504485339100792</v>
       </c>
       <c r="L77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="M77" t="n">
-        <v>47.8895378952934</v>
+        <v>46.55889078776278</v>
       </c>
       <c r="N77" t="n">
-        <v>11.02631578947368</v>
+        <v>10.6</v>
       </c>
       <c r="O77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="P77" t="n">
-        <v>47.8895378952934</v>
+        <v>46.55889078776278</v>
       </c>
       <c r="Q77" t="n">
-        <v>11.02631578947368</v>
+        <v>10.6</v>
       </c>
       <c r="R77" t="n">
         <v>138.4032392925817</v>
       </c>
       <c r="S77" t="n">
-        <v>27.81798992196951</v>
+        <v>26.75039048553721</v>
       </c>
       <c r="T77" t="n">
-        <v>6.159508178917418</v>
+        <v>5.892245533829699</v>
       </c>
       <c r="U77" t="n">
         <v>118.3894561520081</v>
@@ -7193,11 +7193,11 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>27.81798992196951</v>
+        <v>26.75039048553721</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=27.82% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=26.75% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7221,52 +7221,52 @@
         <v>2026</v>
       </c>
       <c r="E78" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F78" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G78" t="n">
-        <v>48.17126433890939</v>
+        <v>49.87175554871417</v>
       </c>
       <c r="H78" t="n">
-        <v>3.606407033882522</v>
+        <v>3.633385459905116</v>
       </c>
       <c r="I78" t="n">
-        <v>111.0836198476808</v>
+        <v>103.5437500854655</v>
       </c>
       <c r="J78" t="n">
-        <v>49.13942155356582</v>
+        <v>48.93253207042698</v>
       </c>
       <c r="K78" t="n">
-        <v>3.932447908708014</v>
+        <v>3.939060829281599</v>
       </c>
       <c r="L78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="M78" t="n">
-        <v>132.8108105037542</v>
+        <v>130.1702699785665</v>
       </c>
       <c r="N78" t="n">
-        <v>6.46116481368479</v>
+        <v>6.33810657300055</v>
       </c>
       <c r="O78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="P78" t="n">
-        <v>47.39415663274317</v>
+        <v>49.02444880110601</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.42813360747103</v>
+        <v>4.406726927097479</v>
       </c>
       <c r="R78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="S78" t="n">
-        <v>26.49401781885958</v>
+        <v>25.48398265391347</v>
       </c>
       <c r="T78" t="n">
-        <v>2.984444425214001</v>
+        <v>2.85796442450722</v>
       </c>
       <c r="U78" t="n">
         <v>124.390269119479</v>
@@ -7282,11 +7282,11 @@
         </is>
       </c>
       <c r="X78" t="n">
-        <v>26.49401781885958</v>
+        <v>25.48398265391347</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=26.49% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=25.48% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7310,52 +7310,52 @@
         <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F79" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="G79" t="n">
-        <v>54.83559803209809</v>
+        <v>54.13640532746658</v>
       </c>
       <c r="H79" t="n">
-        <v>4.029387121230872</v>
+        <v>3.83883329606333</v>
       </c>
       <c r="I79" t="n">
-        <v>108.761990389384</v>
+        <v>102.5016657415887</v>
       </c>
       <c r="J79" t="n">
-        <v>36.89186308680129</v>
+        <v>39.07835373096954</v>
       </c>
       <c r="K79" t="n">
-        <v>3.304314077057211</v>
+        <v>3.54430598501511</v>
       </c>
       <c r="L79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="M79" t="n">
-        <v>53.13626166171554</v>
+        <v>51.59055968974086</v>
       </c>
       <c r="N79" t="n">
-        <v>6.657894736842105</v>
+        <v>6.4</v>
       </c>
       <c r="O79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="P79" t="n">
-        <v>53.13626166171554</v>
+        <v>51.59055968974086</v>
       </c>
       <c r="Q79" t="n">
-        <v>6.657894736842105</v>
+        <v>6.4</v>
       </c>
       <c r="R79" t="n">
         <v>148.0195847609927</v>
       </c>
       <c r="S79" t="n">
-        <v>29.65147043752832</v>
+        <v>28.42761267530013</v>
       </c>
       <c r="T79" t="n">
-        <v>3.333330867224542</v>
+        <v>3.181795794451428</v>
       </c>
       <c r="U79" t="n">
         <v>120.3982350383182</v>
@@ -7371,11 +7371,11 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>29.65147043752832</v>
+        <v>28.42761267530013</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=29.65% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=28.43% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7399,52 +7399,52 @@
         <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F80" t="n">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="G80" t="n">
-        <v>123.0231711982555</v>
+        <v>143.4940966234259</v>
       </c>
       <c r="H80" t="n">
-        <v>23.17411216716189</v>
+        <v>26.07980948970724</v>
       </c>
       <c r="I80" t="n">
-        <v>178.6234719835765</v>
+        <v>180.9937478063148</v>
       </c>
       <c r="J80" t="n">
-        <v>148.3561506538706</v>
+        <v>148.1310218281596</v>
       </c>
       <c r="K80" t="n">
-        <v>23.31756395053142</v>
+        <v>24.4944853507629</v>
       </c>
       <c r="L80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="M80" t="n">
-        <v>124.7515030309418</v>
+        <v>127.0263245736096</v>
       </c>
       <c r="N80" t="n">
-        <v>18.48013024581106</v>
+        <v>20.13112373352051</v>
       </c>
       <c r="O80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="P80" t="n">
-        <v>150.2710602240091</v>
+        <v>152.7575072128086</v>
       </c>
       <c r="Q80" t="n">
-        <v>25.62322426770046</v>
+        <v>27.14206305431544</v>
       </c>
       <c r="R80" t="n">
         <v>172.7461511452186</v>
       </c>
       <c r="S80" t="n">
-        <v>57.96095518018842</v>
+        <v>57.58138393443687</v>
       </c>
       <c r="T80" t="n">
-        <v>32.31025324996108</v>
+        <v>31.8213527961697</v>
       </c>
       <c r="U80" t="n">
         <v>175.912448276349</v>
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="X80" t="n">
-        <v>57.96095518018842</v>
+        <v>57.58138393443687</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=57.96% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=57.58% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7488,52 +7488,52 @@
         <v>2026</v>
       </c>
       <c r="E81" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F81" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="G81" t="n">
-        <v>105.9164731762228</v>
+        <v>129.5473408072873</v>
       </c>
       <c r="H81" t="n">
-        <v>9.934381053416464</v>
+        <v>11.62075399902387</v>
       </c>
       <c r="I81" t="n">
-        <v>184.0754328470002</v>
+        <v>185.5191244575439</v>
       </c>
       <c r="J81" t="n">
-        <v>137.2064188235088</v>
+        <v>131.8378164529767</v>
       </c>
       <c r="K81" t="n">
-        <v>8.59187932191203</v>
+        <v>8.653196714647356</v>
       </c>
       <c r="L81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="M81" t="n">
-        <v>176.0140030425413</v>
+        <v>175.2778190194465</v>
       </c>
       <c r="N81" t="n">
-        <v>12.30917172682913</v>
+        <v>12.94371314048767</v>
       </c>
       <c r="O81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="P81" t="n">
-        <v>137.4824606386474</v>
+        <v>140.0036770211532</v>
       </c>
       <c r="Q81" t="n">
-        <v>11.41040295945036</v>
+        <v>12.19623702618386</v>
       </c>
       <c r="R81" t="n">
         <v>163.1536185700502</v>
       </c>
       <c r="S81" t="n">
-        <v>54.90681100609219</v>
+        <v>55.4369281065792</v>
       </c>
       <c r="T81" t="n">
-        <v>8.290467964049277</v>
+        <v>8.566789406263265</v>
       </c>
       <c r="U81" t="n">
         <v>172.1596497720207</v>
@@ -7549,11 +7549,11 @@
         </is>
       </c>
       <c r="X81" t="n">
-        <v>54.90681100609219</v>
+        <v>55.4369281065792</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=54.91% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=55.44% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7577,52 +7577,52 @@
         <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F82" t="n">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="G82" t="n">
-        <v>100.966746296182</v>
+        <v>126.3886823142627</v>
       </c>
       <c r="H82" t="n">
-        <v>11.50285758326346</v>
+        <v>13.28730403092784</v>
       </c>
       <c r="I82" t="n">
-        <v>184.4099560122273</v>
+        <v>186.2973802760101</v>
       </c>
       <c r="J82" t="n">
-        <v>145.1472793964314</v>
+        <v>145.6424824373007</v>
       </c>
       <c r="K82" t="n">
-        <v>12.99796069573456</v>
+        <v>13.57082597269097</v>
       </c>
       <c r="L82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="M82" t="n">
-        <v>159.6233471388631</v>
+        <v>160.6252306293776</v>
       </c>
       <c r="N82" t="n">
-        <v>12.05820103068101</v>
+        <v>12.78029097914696</v>
       </c>
       <c r="O82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="P82" t="n">
-        <v>139.5299674281279</v>
+        <v>142.2704254070456</v>
       </c>
       <c r="Q82" t="n">
-        <v>13.52804288888773</v>
+        <v>14.23154326578053</v>
       </c>
       <c r="R82" t="n">
         <v>166.6060177059153</v>
       </c>
       <c r="S82" t="n">
-        <v>42.97019417453158</v>
+        <v>41.14041794173689</v>
       </c>
       <c r="T82" t="n">
-        <v>10.49981439198042</v>
+        <v>10.06700724468474</v>
       </c>
       <c r="U82" t="n">
         <v>176.1888335684919</v>
@@ -7638,11 +7638,11 @@
         </is>
       </c>
       <c r="X82" t="n">
-        <v>42.97019417453158</v>
+        <v>41.14041794173689</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=42.97% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=41.14% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7666,52 +7666,52 @@
         <v>2026</v>
       </c>
       <c r="E83" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F83" t="n">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="G83" t="n">
-        <v>39.45432954365923</v>
+        <v>34.85754703895741</v>
       </c>
       <c r="H83" t="n">
-        <v>6.859210293533699</v>
+        <v>6.099900701419037</v>
       </c>
       <c r="I83" t="n">
-        <v>90.64868701686645</v>
+        <v>88.04980557911651</v>
       </c>
       <c r="J83" t="n">
-        <v>47.56092545874292</v>
+        <v>46.55927137251179</v>
       </c>
       <c r="K83" t="n">
-        <v>8.665217789405114</v>
+        <v>8.365042273621768</v>
       </c>
       <c r="L83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="M83" t="n">
-        <v>101.142689215435</v>
+        <v>101.9346113584368</v>
       </c>
       <c r="N83" t="n">
-        <v>37.65965657247335</v>
+        <v>37.32667374384968</v>
       </c>
       <c r="O83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="P83" t="n">
-        <v>82.87727882274899</v>
+        <v>81.22115794251302</v>
       </c>
       <c r="Q83" t="n">
-        <v>30.05086433793102</v>
+        <v>28.91259478594988</v>
       </c>
       <c r="R83" t="n">
         <v>103.1343264142703</v>
       </c>
       <c r="S83" t="n">
-        <v>49.1159143607714</v>
+        <v>49.58750519153977</v>
       </c>
       <c r="T83" t="n">
-        <v>11.98994874908024</v>
+        <v>11.84574626389659</v>
       </c>
       <c r="U83" t="n">
         <v>103.3034448942146</v>
@@ -7727,11 +7727,11 @@
         </is>
       </c>
       <c r="X83" t="n">
-        <v>39.45432954365923</v>
+        <v>34.85754703895741</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=39.45% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=34.86% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7755,52 +7755,52 @@
         <v>2026</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F84" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G84" t="n">
-        <v>35.95489773850942</v>
+        <v>31.58514004799532</v>
       </c>
       <c r="H84" t="n">
-        <v>2.811982073726269</v>
+        <v>2.498959406337137</v>
       </c>
       <c r="I84" t="n">
-        <v>101.7188700792664</v>
+        <v>100.4914466151705</v>
       </c>
       <c r="J84" t="n">
-        <v>46.15812962490158</v>
+        <v>47.98794929851191</v>
       </c>
       <c r="K84" t="n">
-        <v>3.475128502119654</v>
+        <v>3.654283444185853</v>
       </c>
       <c r="L84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="M84" t="n">
-        <v>73.35136326793538</v>
+        <v>73.96001404024166</v>
       </c>
       <c r="N84" t="n">
-        <v>8.912867338922181</v>
+        <v>8.840772408548593</v>
       </c>
       <c r="O84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="P84" t="n">
-        <v>85.36326949733061</v>
+        <v>84.02527497638295</v>
       </c>
       <c r="Q84" t="n">
-        <v>13.84714075997255</v>
+        <v>13.36201420137435</v>
       </c>
       <c r="R84" t="n">
         <v>98.74789164115032</v>
       </c>
       <c r="S84" t="n">
-        <v>47.26168944743522</v>
+        <v>48.65716653790398</v>
       </c>
       <c r="T84" t="n">
-        <v>4.879463558855073</v>
+        <v>4.936587764206472</v>
       </c>
       <c r="U84" t="n">
         <v>110.607240444147</v>
@@ -7816,11 +7816,11 @@
         </is>
       </c>
       <c r="X84" t="n">
-        <v>35.95489773850942</v>
+        <v>31.58514004799532</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=35.95% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=31.59% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7844,52 +7844,52 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F85" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G85" t="n">
-        <v>51.40282038299348</v>
+        <v>45.15610031900901</v>
       </c>
       <c r="H85" t="n">
-        <v>4.813353122630911</v>
+        <v>4.222544006128435</v>
       </c>
       <c r="I85" t="n">
-        <v>104.3279851349203</v>
+        <v>109.9471447641292</v>
       </c>
       <c r="J85" t="n">
-        <v>55.36256686407579</v>
+        <v>56.13119419402656</v>
       </c>
       <c r="K85" t="n">
-        <v>4.933087742300096</v>
+        <v>4.843195688430205</v>
       </c>
       <c r="L85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="M85" t="n">
-        <v>96.11293749099474</v>
+        <v>97.24702211580134</v>
       </c>
       <c r="N85" t="n">
-        <v>18.23089364942659</v>
+        <v>18.19708375199444</v>
       </c>
       <c r="O85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="P85" t="n">
-        <v>90.05124321306785</v>
+        <v>88.21496725218614</v>
       </c>
       <c r="Q85" t="n">
-        <v>17.93448716547004</v>
+        <v>17.25590217879476</v>
       </c>
       <c r="R85" t="n">
         <v>106.9882513320439</v>
       </c>
       <c r="S85" t="n">
-        <v>40.47455651444805</v>
+        <v>40.36683712377915</v>
       </c>
       <c r="T85" t="n">
-        <v>4.521045170692717</v>
+        <v>4.437200514899401</v>
       </c>
       <c r="U85" t="n">
         <v>107.8756984639591</v>
@@ -7905,11 +7905,11 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>40.47455651444805</v>
+        <v>40.36683712377915</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=40.47% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=40.37% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -7933,52 +7933,52 @@
         <v>2026</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F86" t="n">
         <v>33</v>
       </c>
       <c r="G86" t="n">
-        <v>86.35855519846304</v>
+        <v>111.6548587721165</v>
       </c>
       <c r="H86" t="n">
-        <v>1.4945681015993</v>
+        <v>3.143938514500572</v>
       </c>
       <c r="I86" t="n">
-        <v>160.8111516104922</v>
+        <v>160.3842205944857</v>
       </c>
       <c r="J86" t="n">
-        <v>119.2256744546712</v>
+        <v>123.2643907319376</v>
       </c>
       <c r="K86" t="n">
-        <v>1.526445464584329</v>
+        <v>1.613915950770248</v>
       </c>
       <c r="L86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="M86" t="n">
-        <v>131.5868440407407</v>
+        <v>135.0075018387036</v>
       </c>
       <c r="N86" t="n">
-        <v>2.046955790958906</v>
+        <v>2.191859988868237</v>
       </c>
       <c r="O86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="P86" t="n">
-        <v>170.6286794329426</v>
+        <v>172.0972454612955</v>
       </c>
       <c r="Q86" t="n">
-        <v>21.39473684210526</v>
+        <v>22.275</v>
       </c>
       <c r="R86" t="n">
         <v>188.4995472315167</v>
       </c>
       <c r="S86" t="n">
-        <v>70.26626119828747</v>
+        <v>76.7529481383731</v>
       </c>
       <c r="T86" t="n">
-        <v>0.6349999969654554</v>
+        <v>0.6764592464114857</v>
       </c>
       <c r="U86" t="n">
         <v>113.2748521774272</v>
@@ -7994,11 +7994,11 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>70.26626119828747</v>
+        <v>76.7529481383731</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=70.27% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=76.75% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8022,52 +8022,52 @@
         <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F87" t="n">
         <v>17</v>
       </c>
       <c r="G87" t="n">
-        <v>118.3586643671639</v>
+        <v>117.5276954996459</v>
       </c>
       <c r="H87" t="n">
-        <v>0.8662622173625955</v>
+        <v>1.216379534714496</v>
       </c>
       <c r="I87" t="n">
-        <v>169.6404464361343</v>
+        <v>171.410316416684</v>
       </c>
       <c r="J87" t="n">
-        <v>143.560216889931</v>
+        <v>146.3822060454345</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9883869165511783</v>
+        <v>0.9404386721636527</v>
       </c>
       <c r="L87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="M87" t="n">
-        <v>162.2316347756723</v>
+        <v>164.1200530368887</v>
       </c>
       <c r="N87" t="n">
-        <v>9.131578947368421</v>
+        <v>9.5</v>
       </c>
       <c r="O87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="P87" t="n">
-        <v>162.2316347756723</v>
+        <v>164.1200530368887</v>
       </c>
       <c r="Q87" t="n">
-        <v>9.131578947368421</v>
+        <v>9.5</v>
       </c>
       <c r="R87" t="n">
         <v>191.241827101395</v>
       </c>
       <c r="S87" t="n">
-        <v>103.835751536259</v>
+        <v>108.6439639594461</v>
       </c>
       <c r="T87" t="n">
-        <v>0.4254498060582186</v>
+        <v>0.4485334189074034</v>
       </c>
       <c r="U87" t="n">
         <v>108.9238350712686</v>
@@ -8083,11 +8083,11 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>103.835751536259</v>
+        <v>108.6439639594461</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=103.84% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=108.64% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8111,52 +8111,52 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F88" t="n">
         <v>15</v>
       </c>
       <c r="G88" t="n">
-        <v>127.0449845668104</v>
+        <v>135.2120623641964</v>
       </c>
       <c r="H88" t="n">
-        <v>1.143604954623066</v>
+        <v>1.812539916426184</v>
       </c>
       <c r="I88" t="n">
-        <v>167.2799949967896</v>
+        <v>169.0038464611843</v>
       </c>
       <c r="J88" t="n">
-        <v>173.3382025272879</v>
+        <v>174.6712924009235</v>
       </c>
       <c r="K88" t="n">
-        <v>1.000072263696867</v>
+        <v>0.9501939325037349</v>
       </c>
       <c r="L88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="M88" t="n">
-        <v>172.6013331685172</v>
+        <v>174.7089229247851</v>
       </c>
       <c r="N88" t="n">
-        <v>1.919249045221429</v>
+        <v>2.017072343826294</v>
       </c>
       <c r="O88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="P88" t="n">
-        <v>180.73123264338</v>
+        <v>181.694671011211</v>
       </c>
       <c r="Q88" t="n">
-        <v>12.78947368421053</v>
+        <v>13.275</v>
       </c>
       <c r="R88" t="n">
         <v>190.1751472740156</v>
       </c>
       <c r="S88" t="n">
-        <v>117.9134080625519</v>
+        <v>122.0177376594243</v>
       </c>
       <c r="T88" t="n">
-        <v>0.4788652747549516</v>
+        <v>0.5053271539442487</v>
       </c>
       <c r="U88" t="n">
         <v>121.3094122928426</v>
@@ -8172,11 +8172,11 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>117.9134080625519</v>
+        <v>122.0177376594243</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=117.91% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=122.02% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
         <v>2026</v>
       </c>
       <c r="E89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -8209,7 +8209,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1023614579503202</v>
+        <v>0.1029068012743253</v>
       </c>
       <c r="I89" t="n">
         <v>200</v>
@@ -8218,7 +8218,7 @@
         <v>200</v>
       </c>
       <c r="K89" t="n">
-        <v>0.007270478566362362</v>
+        <v>0.007222974619452209</v>
       </c>
       <c r="L89" t="n">
         <v>200</v>
@@ -8283,7 +8283,7 @@
         <v>2026</v>
       </c>
       <c r="E90" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.02746008333061261</v>
+        <v>0.09043378427001174</v>
       </c>
       <c r="I90" t="n">
         <v>200</v>
@@ -8301,7 +8301,7 @@
         <v>200</v>
       </c>
       <c r="K90" t="n">
-        <v>0.003415887464000547</v>
+        <v>0.00336885562718009</v>
       </c>
       <c r="L90" t="n">
         <v>200</v>
@@ -8366,7 +8366,7 @@
         <v>2026</v>
       </c>
       <c r="E91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8375,7 +8375,7 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09301406003964986</v>
+        <v>0.09289234583735555</v>
       </c>
       <c r="I91" t="n">
         <v>200</v>
@@ -8384,7 +8384,7 @@
         <v>200</v>
       </c>
       <c r="K91" t="n">
-        <v>0.01376589551061007</v>
+        <v>0.0136562216612037</v>
       </c>
       <c r="L91" t="n">
         <v>200</v>
@@ -8407,7 +8407,7 @@
         <v>200</v>
       </c>
       <c r="T91" t="n">
-        <v>3.424141759816033e-17</v>
+        <v>3.252934671825231e-17</v>
       </c>
       <c r="U91" t="n">
         <v>200</v>
@@ -8449,52 +8449,52 @@
         <v>2026</v>
       </c>
       <c r="E92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="G92" t="n">
-        <v>52.03867931340183</v>
+        <v>50.94360508394109</v>
       </c>
       <c r="H92" t="n">
-        <v>7.648850237162665</v>
+        <v>7.445236591551317</v>
       </c>
       <c r="I92" t="n">
-        <v>47.19125246366296</v>
+        <v>49.15109590531281</v>
       </c>
       <c r="J92" t="n">
-        <v>53.86994196900773</v>
+        <v>53.47394331476245</v>
       </c>
       <c r="K92" t="n">
-        <v>7.694847947284689</v>
+        <v>7.683758525707208</v>
       </c>
       <c r="L92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="M92" t="n">
-        <v>149.619457716756</v>
+        <v>147.2305093707955</v>
       </c>
       <c r="N92" t="n">
-        <v>92.43043766657274</v>
+        <v>89.88391578324411</v>
       </c>
       <c r="O92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="P92" t="n">
-        <v>108.5913919239667</v>
+        <v>105.1104064577516</v>
       </c>
       <c r="Q92" t="n">
-        <v>39.96055378451477</v>
+        <v>38.44656124176299</v>
       </c>
       <c r="R92" t="n">
         <v>92.01416331532587</v>
       </c>
       <c r="S92" t="n">
-        <v>36.61799934689352</v>
+        <v>35.73768986318822</v>
       </c>
       <c r="T92" t="n">
-        <v>4.898603469004812</v>
+        <v>4.82728776594493</v>
       </c>
       <c r="U92" t="n">
         <v>95.83480509856771</v>
@@ -8510,11 +8510,11 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>36.61799934689352</v>
+        <v>35.73768986318822</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=36.62% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=35.74% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8538,52 +8538,52 @@
         <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F93" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G93" t="n">
-        <v>52.79532864649887</v>
+        <v>48.32233224272152</v>
       </c>
       <c r="H93" t="n">
-        <v>3.654843053741769</v>
+        <v>3.431324012122839</v>
       </c>
       <c r="I93" t="n">
-        <v>56.67057405294103</v>
+        <v>60.93105560683724</v>
       </c>
       <c r="J93" t="n">
-        <v>59.78155232420327</v>
+        <v>58.08717966558936</v>
       </c>
       <c r="K93" t="n">
-        <v>4.925424425520819</v>
+        <v>4.805245515527159</v>
       </c>
       <c r="L93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="M93" t="n">
-        <v>146.0245283061174</v>
+        <v>141.5101871367132</v>
       </c>
       <c r="N93" t="n">
-        <v>41.69405104777928</v>
+        <v>40.03434849539031</v>
       </c>
       <c r="O93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="P93" t="n">
-        <v>114.1212768688539</v>
+        <v>110.5071469160868</v>
       </c>
       <c r="Q93" t="n">
-        <v>20.99274142876214</v>
+        <v>20.23408918824621</v>
       </c>
       <c r="R93" t="n">
         <v>96.01849856237216</v>
       </c>
       <c r="S93" t="n">
-        <v>36.9770007869263</v>
+        <v>37.36511806436712</v>
       </c>
       <c r="T93" t="n">
-        <v>2.207257357329876</v>
+        <v>2.297978956289589</v>
       </c>
       <c r="U93" t="n">
         <v>99.35850993844542</v>
@@ -8599,11 +8599,11 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>36.9770007869263</v>
+        <v>37.36511806436712</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=36.98% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=37.37% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8627,52 +8627,52 @@
         <v>2026</v>
       </c>
       <c r="E94" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F94" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G94" t="n">
-        <v>57.10510659288411</v>
+        <v>54.77044594910456</v>
       </c>
       <c r="H94" t="n">
-        <v>4.268456060466995</v>
+        <v>4.102986916830831</v>
       </c>
       <c r="I94" t="n">
-        <v>60.36683825363948</v>
+        <v>64.07712599234655</v>
       </c>
       <c r="J94" t="n">
-        <v>52.69581648158714</v>
+        <v>51.59798605665487</v>
       </c>
       <c r="K94" t="n">
-        <v>3.740125253417435</v>
+        <v>3.673017500525156</v>
       </c>
       <c r="L94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="M94" t="n">
-        <v>149.6998267702992</v>
+        <v>148.6854236670783</v>
       </c>
       <c r="N94" t="n">
-        <v>45.6523329434659</v>
+        <v>45.0197162962926</v>
       </c>
       <c r="O94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="P94" t="n">
-        <v>112.5398372966676</v>
+        <v>110.6095095898828</v>
       </c>
       <c r="Q94" t="n">
-        <v>22.36505768071156</v>
+        <v>21.77462019881609</v>
       </c>
       <c r="R94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="S94" t="n">
-        <v>38.9841638923733</v>
+        <v>37.14162886109072</v>
       </c>
       <c r="T94" t="n">
-        <v>2.654681877562788</v>
+        <v>2.531651885104475</v>
       </c>
       <c r="U94" t="n">
         <v>93.11495456228404</v>
@@ -8688,11 +8688,11 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>38.9841638923733</v>
+        <v>37.14162886109072</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=38.98% sobre 19 sem</t>
+          <t>NBGLM: menor SMAPE real=37.14% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8716,25 +8716,25 @@
         <v>2026</v>
       </c>
       <c r="E95" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F95" t="n">
         <v>10</v>
       </c>
       <c r="G95" t="n">
-        <v>145.2656870067181</v>
+        <v>150.2138989127696</v>
       </c>
       <c r="H95" t="n">
-        <v>0.7158306497479658</v>
+        <v>0.651952329193679</v>
       </c>
       <c r="I95" t="n">
-        <v>152.0304599151261</v>
+        <v>152.3875262412586</v>
       </c>
       <c r="J95" t="n">
-        <v>199.1922050178509</v>
+        <v>199.2325947669584</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5243681068222776</v>
+        <v>0.4981978432695418</v>
       </c>
       <c r="L95" t="n">
         <v>128.1095321097334</v>
@@ -8743,25 +8743,25 @@
         <v>200</v>
       </c>
       <c r="N95" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5</v>
       </c>
       <c r="O95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="P95" t="n">
-        <v>168.4130957965686</v>
+        <v>169.9924410067401</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.712348962717789</v>
+        <v>3.597150788765764</v>
       </c>
       <c r="R95" t="n">
         <v>118.2821915164861</v>
       </c>
       <c r="S95" t="n">
-        <v>160.6233741719039</v>
+        <v>162.5922054633087</v>
       </c>
       <c r="T95" t="n">
-        <v>1.630178425302371</v>
+        <v>1.59740887326649</v>
       </c>
       <c r="U95" t="n">
         <v>128.8999217807187</v>
@@ -8777,11 +8777,11 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>145.2656870067181</v>
+        <v>150.2138989127696</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=145.27% sobre 19 sem</t>
+          <t>Prophet: menor SMAPE real=150.21% sobre 20 sem</t>
         </is>
       </c>
     </row>
@@ -8805,25 +8805,25 @@
         <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F96" t="n">
         <v>3</v>
       </c>
       <c r="G96" t="n">
-        <v>176.1932878216295</v>
+        <v>182.6000985683808</v>
       </c>
       <c r="H96" t="n">
-        <v>0.4196308764354335</v>
+        <v>0.3181738069780032</v>
       </c>
       <c r="I96" t="n">
-        <v>155.4020478126902</v>
+        <v>158.9896824444987</v>
       </c>
       <c r="J96" t="n">
-        <v>199.2513153043118</v>
+        <v>199.2887495390962</v>
       </c>
       <c r="K96" t="n">
-        <v>0.158291047634362</v>
+        <v>0.1504088082893271</v>
       </c>
       <c r="L96" t="n">
         <v>189.1617640516506</v>
@@ -8832,25 +8832,25 @@
         <v>200</v>
       </c>
       <c r="N96" t="n">
-        <v>0.8016990005837641</v>
+        <v>0.8742715794367811</v>
       </c>
       <c r="O96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="P96" t="n">
-        <v>186.7228903978403</v>
+        <v>187.3867458779483</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.622631913077714</v>
+        <v>3.531501344803482</v>
       </c>
       <c r="R96" t="n">
         <v>124.4459476108536</v>
       </c>
       <c r="S96" t="n">
-        <v>180.9761017902954</v>
+        <v>181.9272967007806</v>
       </c>
       <c r="T96" t="n">
-        <v>0.9242610827578899</v>
+        <v>0.9157679185459064</v>
       </c>
       <c r="U96" t="n">
         <v>151.8363274594118</v>
@@ -8892,52 +8892,52 @@
         <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F97" t="n">
         <v>7</v>
       </c>
       <c r="G97" t="n">
-        <v>161.5895969579176</v>
+        <v>168.3603108145335</v>
       </c>
       <c r="H97" t="n">
-        <v>0.432991156776099</v>
+        <v>0.3854174982544045</v>
       </c>
       <c r="I97" t="n">
-        <v>159.5809636910691</v>
+        <v>157.2976315063829</v>
       </c>
       <c r="J97" t="n">
-        <v>199.3614643125625</v>
+        <v>199.3933910969344</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3712739720909262</v>
+        <v>0.3528828039641452</v>
       </c>
       <c r="L97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="M97" t="n">
-        <v>162.4241916567453</v>
+        <v>166.1817724910707</v>
       </c>
       <c r="N97" t="n">
-        <v>1.583574840897008</v>
+        <v>1.625684887170792</v>
       </c>
       <c r="O97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="P97" t="n">
-        <v>168.6261496195838</v>
+        <v>170.1948421386046</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.339267854845288</v>
+        <v>2.276168801400835</v>
       </c>
       <c r="R97" t="n">
         <v>128.4785456608675</v>
       </c>
       <c r="S97" t="n">
-        <v>163.2961637414761</v>
+        <v>165.1313555544023</v>
       </c>
       <c r="T97" t="n">
-        <v>0.8241713784572454</v>
+        <v>0.821790731875075</v>
       </c>
       <c r="U97" t="n">
         <v>136.0400571203446</v>
@@ -8979,7 +8979,7 @@
         <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8988,23 +8988,25 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1434930256603092</v>
+        <v>0.07260366378937935</v>
       </c>
       <c r="I98" t="n">
-        <v>198.561344495255</v>
+        <v>198.585723184526</v>
       </c>
       <c r="J98" t="n">
         <v>200</v>
       </c>
       <c r="K98" t="n">
-        <v>0.000548695229506579</v>
+        <v>0.00054404465349612</v>
       </c>
       <c r="L98" t="n">
         <v>199.9898962083731</v>
       </c>
-      <c r="M98" t="inlineStr"/>
+      <c r="M98" t="n">
+        <v>200</v>
+      </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="O98" t="n">
         <v>199.2030987655621</v>
@@ -9020,7 +9022,7 @@
         <v>200</v>
       </c>
       <c r="T98" t="n">
-        <v>0.0009204004093562376</v>
+        <v>0.005154196125645891</v>
       </c>
       <c r="U98" t="n">
         <v>199.9999998548883</v>
@@ -9062,7 +9064,7 @@
         <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -9071,23 +9073,25 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.08714727738012426</v>
+        <v>0.04183094421640433</v>
       </c>
       <c r="I99" t="n">
-        <v>198.6789577214581</v>
+        <v>198.7380283178126</v>
       </c>
       <c r="J99" t="n">
         <v>200</v>
       </c>
       <c r="K99" t="n">
-        <v>0.001607453320843158</v>
+        <v>0.00161789215811154</v>
       </c>
       <c r="L99" t="n">
         <v>199.9983019911245</v>
       </c>
-      <c r="M99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>200</v>
+      </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="O99" t="n">
         <v>198.5022493653877</v>
@@ -9103,14 +9107,14 @@
         <v>200</v>
       </c>
       <c r="T99" t="n">
-        <v>0.0004808773835790487</v>
+        <v>0.004032312519180891</v>
       </c>
       <c r="U99" t="n">
         <v>200</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
@@ -9121,7 +9125,7 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9149,7 @@
         <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -9154,7 +9158,7 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1272160571401307</v>
+        <v>0.05751753432389537</v>
       </c>
       <c r="I100" t="n">
         <v>200</v>
@@ -9163,7 +9167,7 @@
         <v>200</v>
       </c>
       <c r="K100" t="n">
-        <v>0.002433839398527311</v>
+        <v>0.002432684187964065</v>
       </c>
       <c r="L100" t="n">
         <v>200</v>
@@ -9186,7 +9190,7 @@
         <v>200</v>
       </c>
       <c r="T100" t="n">
-        <v>1.76736659311027e-06</v>
+        <v>0.0001924153076147698</v>
       </c>
       <c r="U100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -5076,7 +5076,7 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>19.49960594346439</v>
+        <v>19.62979676942301</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=19.50% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE real=19.63% sobre 20 sem</t>
         </is>
       </c>
     </row>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -575,52 +575,52 @@
         <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01086772807397862</v>
+        <v>0.09640672006432924</v>
       </c>
       <c r="I2" t="n">
         <v>185.8333489727328</v>
       </c>
       <c r="J2" t="n">
-        <v>200</v>
+        <v>199.2579644023037</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009038219012261</v>
+        <v>0.09418773272458057</v>
       </c>
       <c r="L2" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M2" t="n">
-        <v>200</v>
+        <v>177.1428571428572</v>
       </c>
       <c r="N2" t="n">
-        <v>0.525</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="O2" t="n">
         <v>197.8088169752323</v>
       </c>
       <c r="P2" t="n">
-        <v>200</v>
+        <v>177.1428571428572</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.525</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="R2" t="n">
         <v>199.5572761277739</v>
       </c>
       <c r="S2" t="n">
-        <v>200</v>
+        <v>194.1154745887209</v>
       </c>
       <c r="T2" t="n">
-        <v>0.04831761745957867</v>
+        <v>0.1155501944511648</v>
       </c>
       <c r="U2" t="n">
         <v>194.9779461019607</v>
@@ -638,7 +638,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -662,25 +662,25 @@
         <v>2026</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>199.7529419278686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00951068472871661</v>
+        <v>0.05207677763587828</v>
       </c>
       <c r="I3" t="n">
         <v>157.2321783542833</v>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>199.586521041329</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01291920560802575</v>
+        <v>0.05579806788954927</v>
       </c>
       <c r="L3" t="n">
         <v>79.54507935933471</v>
@@ -689,7 +689,7 @@
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>0.15</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="O3" t="n">
         <v>197.8854209931308</v>
@@ -698,16 +698,16 @@
         <v>200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.15</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="R3" t="n">
         <v>199.636475467609</v>
       </c>
       <c r="S3" t="n">
-        <v>200</v>
+        <v>199.4086924003466</v>
       </c>
       <c r="T3" t="n">
-        <v>0.03380843033181492</v>
+        <v>0.07575186921040457</v>
       </c>
       <c r="U3" t="n">
         <v>198.5158836242873</v>
@@ -725,7 +725,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -749,52 +749,52 @@
         <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01339726082426194</v>
+        <v>0.05512805289066256</v>
       </c>
       <c r="I4" t="n">
         <v>158.5580779411727</v>
       </c>
       <c r="J4" t="n">
-        <v>200</v>
+        <v>195.0043654828781</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08872090040442157</v>
+        <v>0.1312822637752856</v>
       </c>
       <c r="L4" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M4" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="N4" t="n">
-        <v>0.375</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="O4" t="n">
         <v>197.7265973322816</v>
       </c>
       <c r="P4" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.375</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="R4" t="n">
         <v>199.5859359679221</v>
       </c>
       <c r="S4" t="n">
-        <v>200</v>
+        <v>195.882373998402</v>
       </c>
       <c r="T4" t="n">
-        <v>0.03815314787819993</v>
+        <v>0.07941716176852767</v>
       </c>
       <c r="U4" t="n">
         <v>196.9436529554095</v>
@@ -812,7 +812,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         <v>2026</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>199.1222961182866</v>
+        <v>199.0479027213012</v>
       </c>
       <c r="H5" t="n">
-        <v>0.103539670713508</v>
+        <v>0.1766370530365091</v>
       </c>
       <c r="I5" t="n">
         <v>175.1088701866436</v>
       </c>
       <c r="J5" t="n">
-        <v>199.3201449446063</v>
+        <v>199.291615850557</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1119777478183459</v>
+        <v>0.1851306619209305</v>
       </c>
       <c r="L5" t="n">
         <v>109.609711216533</v>
@@ -863,7 +863,7 @@
         <v>200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="O5" t="n">
         <v>187.2707284786031</v>
@@ -872,16 +872,16 @@
         <v>200</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.25</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="R5" t="n">
         <v>193.7972259177366</v>
       </c>
       <c r="S5" t="n">
-        <v>199.2642162634052</v>
+        <v>199.360188055135</v>
       </c>
       <c r="T5" t="n">
-        <v>0.113840446043582</v>
+        <v>0.1859482139509409</v>
       </c>
       <c r="U5" t="n">
         <v>187.0400639517023</v>
@@ -899,7 +899,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
         <v>2026</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>199.5466380074913</v>
+        <v>199.4965556931469</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05958452539361416</v>
+        <v>0.09523652339086032</v>
       </c>
       <c r="I6" t="n">
         <v>191.646475967384</v>
       </c>
       <c r="J6" t="n">
-        <v>199.9868587590181</v>
+        <v>199.9769257249451</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05077332858287904</v>
+        <v>0.0876597108729765</v>
       </c>
       <c r="L6" t="n">
         <v>79.54507935933471</v>
@@ -950,7 +950,7 @@
         <v>200</v>
       </c>
       <c r="N6" t="n">
-        <v>0.125</v>
+        <v>0.1521739130434783</v>
       </c>
       <c r="O6" t="n">
         <v>192.53013744135</v>
@@ -959,16 +959,16 @@
         <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.125</v>
+        <v>0.1521739130434783</v>
       </c>
       <c r="R6" t="n">
         <v>193.2139428195562</v>
       </c>
       <c r="S6" t="n">
-        <v>198.400971319978</v>
+        <v>198.5786411733137</v>
       </c>
       <c r="T6" t="n">
-        <v>0.05679052057083078</v>
+        <v>0.09286132223550503</v>
       </c>
       <c r="U6" t="n">
         <v>198.9985835834048</v>
@@ -986,7 +986,7 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1010,25 +1010,25 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>199.1310401828866</v>
+        <v>198.7342969739748</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07351845768099691</v>
+        <v>0.1074898285321442</v>
       </c>
       <c r="I7" t="n">
         <v>186.9197740801393</v>
       </c>
       <c r="J7" t="n">
-        <v>199.9890093911592</v>
+        <v>199.9820249646312</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05044767351613336</v>
+        <v>0.08736130679163399</v>
       </c>
       <c r="L7" t="n">
         <v>109.7635513825217</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="N7" t="n">
-        <v>0.125</v>
+        <v>0.1521739130434783</v>
       </c>
       <c r="O7" t="n">
         <v>185.3187572725189</v>
@@ -1046,16 +1046,16 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.125</v>
+        <v>0.1521739130434783</v>
       </c>
       <c r="R7" t="n">
         <v>190.8625800946274</v>
       </c>
       <c r="S7" t="n">
-        <v>199.7841530867383</v>
+        <v>199.8123070319464</v>
       </c>
       <c r="T7" t="n">
-        <v>0.06624513880111146</v>
+        <v>0.1010827293922708</v>
       </c>
       <c r="U7" t="n">
         <v>197.3279694158802</v>
@@ -1073,7 +1073,7 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1097,59 +1097,59 @@
         <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="G8" t="n">
-        <v>102.939746329922</v>
+        <v>100.2669787630565</v>
       </c>
       <c r="H8" t="n">
-        <v>5.316948239627654</v>
+        <v>5.033323505655278</v>
       </c>
       <c r="I8" t="n">
         <v>154.5040916050135</v>
       </c>
       <c r="J8" t="n">
-        <v>48.43958717347449</v>
+        <v>57.1925436233631</v>
       </c>
       <c r="K8" t="n">
-        <v>3.473010580623329</v>
+        <v>4.901934090576742</v>
       </c>
       <c r="L8" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M8" t="n">
-        <v>91.01313258712945</v>
+        <v>90.13850994198548</v>
       </c>
       <c r="N8" t="n">
-        <v>14.425</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="P8" t="n">
-        <v>91.01313258712945</v>
+        <v>90.13850994198548</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.425</v>
+        <v>14</v>
       </c>
       <c r="R8" t="n">
         <v>172.894287988784</v>
       </c>
       <c r="S8" t="n">
-        <v>60.56045746576052</v>
+        <v>59.9679535293255</v>
       </c>
       <c r="T8" t="n">
-        <v>3.494017018505561</v>
+        <v>3.350774604290362</v>
       </c>
       <c r="U8" t="n">
         <v>111.5676388698673</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>48.43958717347449</v>
+        <v>59.9679535293255</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=48.44% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=59.97% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1186,52 +1186,52 @@
         <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>96.84936542770946</v>
+        <v>96.86242957945571</v>
       </c>
       <c r="H9" t="n">
-        <v>2.348153715242724</v>
+        <v>2.327612097079943</v>
       </c>
       <c r="I9" t="n">
         <v>164.086229256472</v>
       </c>
       <c r="J9" t="n">
-        <v>70.37750705227454</v>
+        <v>73.71026723278355</v>
       </c>
       <c r="K9" t="n">
-        <v>2.150741598423064</v>
+        <v>2.669844237566461</v>
       </c>
       <c r="L9" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M9" t="n">
-        <v>105.7725231721175</v>
+        <v>100.7484856228131</v>
       </c>
       <c r="N9" t="n">
-        <v>7.25</v>
+        <v>7.173913043478261</v>
       </c>
       <c r="O9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="P9" t="n">
-        <v>105.7725231721175</v>
+        <v>100.7484856228131</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.25</v>
+        <v>7.173913043478261</v>
       </c>
       <c r="R9" t="n">
         <v>176.8647517474977</v>
       </c>
       <c r="S9" t="n">
-        <v>60.63470926628591</v>
+        <v>59.18799158853509</v>
       </c>
       <c r="T9" t="n">
-        <v>1.474394540926025</v>
+        <v>1.457843465323946</v>
       </c>
       <c r="U9" t="n">
         <v>121.2492629006552</v>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>60.63470926628591</v>
+        <v>59.18799158853509</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=60.63% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=59.19% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1275,59 +1275,59 @@
         <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>97.69809429310973</v>
+        <v>89.49394177012995</v>
       </c>
       <c r="H10" t="n">
-        <v>2.759493428145611</v>
+        <v>2.491078366601676</v>
       </c>
       <c r="I10" t="n">
         <v>164.4874496413386</v>
       </c>
       <c r="J10" t="n">
-        <v>50.53504307263596</v>
+        <v>65.26079607571089</v>
       </c>
       <c r="K10" t="n">
-        <v>1.810953329620644</v>
+        <v>1.817841397374628</v>
       </c>
       <c r="L10" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M10" t="n">
-        <v>92.26432089840841</v>
+        <v>93.93884057717756</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>7.543478260869565</v>
       </c>
       <c r="O10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="P10" t="n">
-        <v>92.26432089840841</v>
+        <v>93.93884057717756</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>7.543478260869565</v>
       </c>
       <c r="R10" t="n">
         <v>168.5443712458804</v>
       </c>
       <c r="S10" t="n">
-        <v>64.3948423725101</v>
+        <v>61.39934805337054</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051508251981994</v>
+        <v>1.887811508963884</v>
       </c>
       <c r="U10" t="n">
         <v>114.746491150853</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1336,11 +1336,11 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>50.53504307263596</v>
+        <v>61.39934805337054</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=50.54% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=61.40% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1364,52 +1364,52 @@
         <v>2026</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>178.4347588485121</v>
+        <v>179.5697715406957</v>
       </c>
       <c r="H11" t="n">
-        <v>0.602524666113481</v>
+        <v>0.6108910140117226</v>
       </c>
       <c r="I11" t="n">
         <v>123.2554563734294</v>
       </c>
       <c r="J11" t="n">
-        <v>198.0925893582057</v>
+        <v>198.3252005482301</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6092428015336366</v>
+        <v>0.6167025165834394</v>
       </c>
       <c r="L11" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M11" t="n">
-        <v>190.8008067648422</v>
+        <v>187.6528754476888</v>
       </c>
       <c r="N11" t="n">
-        <v>28.6076032810772</v>
+        <v>25.83269850528452</v>
       </c>
       <c r="O11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="P11" t="n">
-        <v>159.6359755253572</v>
+        <v>162.0103299062185</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.089736524432491</v>
+        <v>1.034553499506514</v>
       </c>
       <c r="R11" t="n">
         <v>177.781032308345</v>
       </c>
       <c r="S11" t="n">
-        <v>122.7920619307176</v>
+        <v>125.3137009295347</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5498154268247075</v>
+        <v>0.6440559530907478</v>
       </c>
       <c r="U11" t="n">
         <v>147.9725418621825</v>
@@ -1425,11 +1425,11 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>122.7920619307176</v>
+        <v>125.3137009295347</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=122.79% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=125.31% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1453,59 +1453,59 @@
         <v>2026</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>191.8552562166053</v>
+        <v>192.5956874696411</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3566911765420278</v>
+        <v>0.3971227622104589</v>
       </c>
       <c r="I12" t="n">
         <v>147.3485671696691</v>
       </c>
       <c r="J12" t="n">
-        <v>199.5470203450976</v>
+        <v>199.5744872982048</v>
       </c>
       <c r="K12" t="n">
-        <v>0.352847024244512</v>
+        <v>0.401254753256975</v>
       </c>
       <c r="L12" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M12" t="n">
-        <v>191.9594272005882</v>
+        <v>186.0516758265984</v>
       </c>
       <c r="N12" t="n">
-        <v>13.07354649830269</v>
+        <v>11.80308391156755</v>
       </c>
       <c r="O12" t="n">
         <v>191.4723960783834</v>
       </c>
       <c r="P12" t="n">
-        <v>190.8433648657603</v>
+        <v>182.9634089977751</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.20253848204103</v>
+        <v>10.63861541995272</v>
       </c>
       <c r="R12" t="n">
         <v>189.6908701459495</v>
       </c>
       <c r="S12" t="n">
-        <v>158.0757591562452</v>
+        <v>159.1043792977246</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4759576117403433</v>
+        <v>0.5395046849004895</v>
       </c>
       <c r="U12" t="n">
         <v>169.7722333133142</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1516,7 +1516,7 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
@@ -1549,25 +1549,25 @@
         <v>195.8361847211582</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2557147767860903</v>
+        <v>0.2223606754661655</v>
       </c>
       <c r="I13" t="n">
         <v>157.1522264328246</v>
       </c>
       <c r="J13" t="n">
-        <v>199.8165244396315</v>
+        <v>199.8404560344622</v>
       </c>
       <c r="K13" t="n">
-        <v>0.251282968706494</v>
+        <v>0.2186316362277156</v>
       </c>
       <c r="L13" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M13" t="n">
-        <v>191.6282423682011</v>
+        <v>192.7202107549575</v>
       </c>
       <c r="N13" t="n">
-        <v>15.36703159304306</v>
+        <v>13.88437529829831</v>
       </c>
       <c r="O13" t="n">
         <v>193.9340304002594</v>
@@ -1576,16 +1576,16 @@
         <v>192.1270949117732</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.406524478761369</v>
+        <v>5.570890851096843</v>
       </c>
       <c r="R13" t="n">
         <v>188.2053733911598</v>
       </c>
       <c r="S13" t="n">
-        <v>160.1046040574139</v>
+        <v>165.3083513542729</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3681780684362106</v>
+        <v>0.407074069984613</v>
       </c>
       <c r="U13" t="n">
         <v>173.7069303697712</v>
@@ -1627,52 +1627,52 @@
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>68.80570985590298</v>
+        <v>69.39790860052938</v>
       </c>
       <c r="H14" t="n">
-        <v>2.008123501430287</v>
+        <v>2.372329349033962</v>
       </c>
       <c r="I14" t="n">
         <v>66.61025297793201</v>
       </c>
       <c r="J14" t="n">
-        <v>84.31915847426973</v>
+        <v>76.92207018141531</v>
       </c>
       <c r="K14" t="n">
-        <v>2.754202184815645</v>
+        <v>2.703067216152471</v>
       </c>
       <c r="L14" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M14" t="n">
-        <v>167.7578144530684</v>
+        <v>163.2388813787565</v>
       </c>
       <c r="N14" t="n">
-        <v>33.63968371128689</v>
+        <v>33.72268947014127</v>
       </c>
       <c r="O14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="P14" t="n">
-        <v>180.5377157895649</v>
+        <v>180.3952676159481</v>
       </c>
       <c r="Q14" t="n">
-        <v>62.425</v>
+        <v>74.73913043478261</v>
       </c>
       <c r="R14" t="n">
         <v>186.0423288913966</v>
       </c>
       <c r="S14" t="n">
-        <v>76.61476888162572</v>
+        <v>79.1706967455949</v>
       </c>
       <c r="T14" t="n">
-        <v>2.953578645514585</v>
+        <v>5.0374764945796</v>
       </c>
       <c r="U14" t="n">
         <v>130.2296761771863</v>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>68.80570985590298</v>
+        <v>69.39790860052938</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=68.81% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=69.40% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1716,52 +1716,52 @@
         <v>2026</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>65.36323213379569</v>
+        <v>66.60050454684506</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8910109167640803</v>
+        <v>1.065927405429038</v>
       </c>
       <c r="I15" t="n">
         <v>82.6747998505866</v>
       </c>
       <c r="J15" t="n">
-        <v>90.57517357326512</v>
+        <v>88.03721417177097</v>
       </c>
       <c r="K15" t="n">
-        <v>1.23767065801537</v>
+        <v>1.376838481255402</v>
       </c>
       <c r="L15" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M15" t="n">
-        <v>173.5878226721619</v>
+        <v>170.7138702810821</v>
       </c>
       <c r="N15" t="n">
-        <v>22.39172919513397</v>
+        <v>22.72205646810959</v>
       </c>
       <c r="O15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="P15" t="n">
-        <v>177.1697271735234</v>
+        <v>177.4115898461844</v>
       </c>
       <c r="Q15" t="n">
-        <v>29.7</v>
+        <v>35.28260869565217</v>
       </c>
       <c r="R15" t="n">
         <v>186.4460938550808</v>
       </c>
       <c r="S15" t="n">
-        <v>79.85510675984227</v>
+        <v>81.99553157655238</v>
       </c>
       <c r="T15" t="n">
-        <v>1.521641786051784</v>
+        <v>2.437640334943708</v>
       </c>
       <c r="U15" t="n">
         <v>131.9030800529592</v>
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>65.36323213379569</v>
+        <v>66.60050454684506</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=65.36% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=66.60% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1805,52 +1805,52 @@
         <v>2026</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>120.1868578325129</v>
+        <v>115.4195850524713</v>
       </c>
       <c r="H16" t="n">
-        <v>1.603530893967823</v>
+        <v>1.767846442013095</v>
       </c>
       <c r="I16" t="n">
         <v>90.20708978859948</v>
       </c>
       <c r="J16" t="n">
-        <v>135.5839928652588</v>
+        <v>123.8382033410324</v>
       </c>
       <c r="K16" t="n">
-        <v>1.412338377221286</v>
+        <v>1.481049571138128</v>
       </c>
       <c r="L16" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M16" t="n">
-        <v>176.4025580239632</v>
+        <v>172.8053037784588</v>
       </c>
       <c r="N16" t="n">
-        <v>23.20775602863392</v>
+        <v>23.70060744474833</v>
       </c>
       <c r="O16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="P16" t="n">
-        <v>182.0806314010404</v>
+        <v>181.7847259866078</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.8</v>
+        <v>39.52173913043478</v>
       </c>
       <c r="R16" t="n">
         <v>186.1307414343702</v>
       </c>
       <c r="S16" t="n">
-        <v>105.9453658902282</v>
+        <v>104.1603161324143</v>
       </c>
       <c r="T16" t="n">
-        <v>1.415537147198349</v>
+        <v>2.437815710078234</v>
       </c>
       <c r="U16" t="n">
         <v>133.2708900338696</v>
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>105.9453658902282</v>
+        <v>104.1603161324143</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=105.95% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=104.16% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -1894,25 +1894,25 @@
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>198.7984995529214</v>
+        <v>198.9552170025404</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1095214356824465</v>
+        <v>0.1084945518651706</v>
       </c>
       <c r="I17" t="n">
         <v>194.5446671655584</v>
       </c>
       <c r="J17" t="n">
-        <v>199.9459948394786</v>
+        <v>199.953038990851</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05222732714755758</v>
+        <v>0.0457257643045931</v>
       </c>
       <c r="L17" t="n">
         <v>109.609711216533</v>
@@ -1921,7 +1921,7 @@
         <v>200</v>
       </c>
       <c r="N17" t="n">
-        <v>0.125</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="O17" t="n">
         <v>196.7571923388938</v>
@@ -1930,16 +1930,16 @@
         <v>200</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.125</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="R17" t="n">
         <v>197.0125798901019</v>
       </c>
       <c r="S17" t="n">
-        <v>198.7631536366026</v>
+        <v>198.9244814231327</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05757308229392404</v>
+        <v>0.05006354982080351</v>
       </c>
       <c r="U17" t="n">
         <v>192.256373806382</v>
@@ -1981,7 +1981,7 @@
         <v>2026</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02453038060506788</v>
+        <v>0.02260952408321706</v>
       </c>
       <c r="I18" t="n">
         <v>199.6410247115898</v>
@@ -1999,7 +1999,7 @@
         <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0005626091125968551</v>
+        <v>0.0005588044341359392</v>
       </c>
       <c r="L18" t="n">
         <v>79.54507935933471</v>
@@ -2022,7 +2022,7 @@
         <v>200</v>
       </c>
       <c r="T18" t="n">
-        <v>5.090631404757219e-263</v>
+        <v>4.426636004136712e-263</v>
       </c>
       <c r="U18" t="n">
         <v>196.0211023092105</v>
@@ -2064,25 +2064,25 @@
         <v>2026</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.0879467724605</v>
+        <v>199.2123176671249</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09628835939416915</v>
+        <v>0.09310047787324048</v>
       </c>
       <c r="I19" t="n">
         <v>196.278530387405</v>
       </c>
       <c r="J19" t="n">
-        <v>199.8760431473448</v>
+        <v>199.8922114324738</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05466784212850494</v>
+        <v>0.0482601753578682</v>
       </c>
       <c r="L19" t="n">
         <v>109.7635513825217</v>
@@ -2091,7 +2091,7 @@
         <v>200</v>
       </c>
       <c r="N19" t="n">
-        <v>0.125</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="O19" t="n">
         <v>196.7189002085085</v>
@@ -2100,16 +2100,16 @@
         <v>200</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.125</v>
+        <v>0.108695652173913</v>
       </c>
       <c r="R19" t="n">
         <v>196.7488584326798</v>
       </c>
       <c r="S19" t="n">
-        <v>198.879149592586</v>
+        <v>199.0253474718139</v>
       </c>
       <c r="T19" t="n">
-        <v>0.05843816095741121</v>
+        <v>0.05081579213687931</v>
       </c>
       <c r="U19" t="n">
         <v>197.8046914283761</v>
@@ -2151,7 +2151,7 @@
         <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07059010458825815</v>
+        <v>0.07091308014421872</v>
       </c>
       <c r="I20" t="n">
         <v>200</v>
@@ -2169,7 +2169,7 @@
         <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00140240633767629</v>
+        <v>0.001364348782705161</v>
       </c>
       <c r="L20" t="n">
         <v>109.609711216533</v>
@@ -2192,7 +2192,7 @@
         <v>200</v>
       </c>
       <c r="T20" t="n">
-        <v>7500</v>
+        <v>6521.739130434783</v>
       </c>
       <c r="U20" t="n">
         <v>200</v>
@@ -2234,7 +2234,7 @@
         <v>2026</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05681577275851089</v>
+        <v>0.05707240016553016</v>
       </c>
       <c r="I21" t="n">
         <v>200</v>
@@ -2252,7 +2252,7 @@
         <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>0.006011293468559891</v>
+        <v>0.006024787974672279</v>
       </c>
       <c r="L21" t="n">
         <v>79.54507935933471</v>
@@ -2275,7 +2275,7 @@
         <v>200</v>
       </c>
       <c r="T21" t="n">
-        <v>17500.00000009131</v>
+        <v>15217.39130442722</v>
       </c>
       <c r="U21" t="n">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>2026</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06360909203296403</v>
+        <v>0.0639010226511763</v>
       </c>
       <c r="I22" t="n">
         <v>200</v>
@@ -2335,7 +2335,7 @@
         <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000365317727903835</v>
+        <v>0.0003876241781221087</v>
       </c>
       <c r="L22" t="n">
         <v>109.7635513825217</v>
@@ -2358,7 +2358,7 @@
         <v>200</v>
       </c>
       <c r="T22" t="n">
-        <v>3.215458201907303e-17</v>
+        <v>2.796050610354176e-17</v>
       </c>
       <c r="U22" t="n">
         <v>200</v>
@@ -2400,59 +2400,59 @@
         <v>2026</v>
       </c>
       <c r="E23" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>179.1739130190571</v>
+        <v>188.0993788680326</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1208266201253207</v>
+        <v>0.1191255336072813</v>
       </c>
       <c r="I23" t="n">
         <v>149.2565324185079</v>
       </c>
       <c r="J23" t="n">
-        <v>199.2988442308534</v>
+        <v>199.3902993311769</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1169462719000806</v>
+        <v>0.2144830638454611</v>
       </c>
       <c r="L23" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M23" t="n">
-        <v>192.8571428571429</v>
+        <v>193.6507936507937</v>
       </c>
       <c r="N23" t="n">
-        <v>1.05</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="O23" t="n">
         <v>169.6992056798271</v>
       </c>
       <c r="P23" t="n">
-        <v>192.8571428571429</v>
+        <v>193.6507936507937</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.05</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="R23" t="n">
         <v>186.3774873978808</v>
       </c>
       <c r="S23" t="n">
-        <v>189.6927156447084</v>
+        <v>191.0371440388769</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2113223124025828</v>
+        <v>0.2607550959162749</v>
       </c>
       <c r="U23" t="n">
         <v>159.9263814945425</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -2463,7 +2463,7 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2487,59 +2487,59 @@
         <v>2026</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>182.221104530061</v>
+        <v>189.3326627180366</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06246006768372875</v>
+        <v>0.05767232671072361</v>
       </c>
       <c r="I24" t="n">
         <v>156.2502876793226</v>
       </c>
       <c r="J24" t="n">
-        <v>198.5969505043455</v>
+        <v>198.7799569603005</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06201450118704753</v>
+        <v>0.07957654129197167</v>
       </c>
       <c r="L24" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M24" t="n">
-        <v>138.2549574812263</v>
+        <v>158.8366383208175</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1360291182994842</v>
+        <v>0.2487209724343341</v>
       </c>
       <c r="O24" t="n">
         <v>159.6122718089852</v>
       </c>
       <c r="P24" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.475</v>
+        <v>0.5434782608695652</v>
       </c>
       <c r="R24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="S24" t="n">
-        <v>192.9420608904714</v>
+        <v>193.8626616438882</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1233272719333847</v>
+        <v>0.1369834510173822</v>
       </c>
       <c r="U24" t="n">
         <v>166.4426133688291</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2583,16 +2583,16 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>0.06991408417631947</v>
+        <v>0.06665634897032278</v>
       </c>
       <c r="I25" t="n">
         <v>155.3955473497874</v>
       </c>
       <c r="J25" t="n">
-        <v>199.91823344769</v>
+        <v>199.9288986501652</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05538158754912472</v>
+        <v>0.05297273674255192</v>
       </c>
       <c r="L25" t="n">
         <v>109.7635513825217</v>
@@ -2601,7 +2601,7 @@
         <v>200</v>
       </c>
       <c r="N25" t="n">
-        <v>0.575</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="O25" t="n">
         <v>177.0659734750362</v>
@@ -2610,16 +2610,16 @@
         <v>200</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.575</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="R25" t="n">
         <v>183.340259481936</v>
       </c>
       <c r="S25" t="n">
-        <v>199.5708369646526</v>
+        <v>199.6268147518718</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1423984762855963</v>
+        <v>0.1883433489305086</v>
       </c>
       <c r="U25" t="n">
         <v>180.6321027113416</v>
@@ -2661,7 +2661,7 @@
         <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02641044271870376</v>
+        <v>0.02296560236409023</v>
       </c>
       <c r="I26" t="n">
         <v>97.19414576199205</v>
@@ -2679,7 +2679,7 @@
         <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0921510468117073</v>
+        <v>0.1038645319465069</v>
       </c>
       <c r="L26" t="n">
         <v>109.609711216533</v>
@@ -2688,7 +2688,7 @@
         <v>200</v>
       </c>
       <c r="N26" t="n">
-        <v>67.34999999999999</v>
+        <v>71.47826086956522</v>
       </c>
       <c r="O26" t="n">
         <v>198.3074653131699</v>
@@ -2697,7 +2697,7 @@
         <v>200</v>
       </c>
       <c r="Q26" t="n">
-        <v>67.34999999999999</v>
+        <v>71.47826086956522</v>
       </c>
       <c r="R26" t="n">
         <v>199.6509594119097</v>
@@ -2706,7 +2706,7 @@
         <v>200</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9201320418796755</v>
+        <v>1.069336825017407</v>
       </c>
       <c r="U26" t="n">
         <v>183.6686755299509</v>
@@ -2748,7 +2748,7 @@
         <v>2026</v>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01849258866482504</v>
+        <v>0.01608051188245655</v>
       </c>
       <c r="I27" t="n">
         <v>129.0985231723771</v>
@@ -2766,7 +2766,7 @@
         <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01147627579690619</v>
+        <v>0.01105918152281296</v>
       </c>
       <c r="L27" t="n">
         <v>79.54507935933471</v>
@@ -2775,7 +2775,7 @@
         <v>200</v>
       </c>
       <c r="N27" t="n">
-        <v>33.3</v>
+        <v>35.28260869565217</v>
       </c>
       <c r="O27" t="n">
         <v>198.6114841856233</v>
@@ -2784,7 +2784,7 @@
         <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>33.3</v>
+        <v>35.28260869565217</v>
       </c>
       <c r="R27" t="n">
         <v>199.779644487174</v>
@@ -2793,7 +2793,7 @@
         <v>200</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5743908083603411</v>
+        <v>0.7160689155560462</v>
       </c>
       <c r="U27" t="n">
         <v>192.722098187243</v>
@@ -2835,7 +2835,7 @@
         <v>2026</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01865813865375408</v>
+        <v>0.01622446839456877</v>
       </c>
       <c r="I28" t="n">
         <v>127.1718885128103</v>
@@ -2853,7 +2853,7 @@
         <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>0.00451688792496775</v>
+        <v>0.02541885056650545</v>
       </c>
       <c r="L28" t="n">
         <v>109.7635513825217</v>
@@ -2862,7 +2862,7 @@
         <v>200</v>
       </c>
       <c r="N28" t="n">
-        <v>34.05</v>
+        <v>36.19565217391305</v>
       </c>
       <c r="O28" t="n">
         <v>197.4940180993655</v>
@@ -2871,7 +2871,7 @@
         <v>200</v>
       </c>
       <c r="Q28" t="n">
-        <v>34.05</v>
+        <v>36.19565217391305</v>
       </c>
       <c r="R28" t="n">
         <v>199.5411797194807</v>
@@ -2880,14 +2880,14 @@
         <v>200</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7538728996217575</v>
+        <v>0.8041157552583883</v>
       </c>
       <c r="U28" t="n">
         <v>184.9627687949149</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2898,7 +2898,7 @@
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2922,25 +2922,25 @@
         <v>2026</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>200</v>
+        <v>196.886012865036</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0976447329447092</v>
+        <v>0.1381129309159472</v>
       </c>
       <c r="I29" t="n">
         <v>191.5075017030775</v>
       </c>
       <c r="J29" t="n">
-        <v>200</v>
+        <v>199.6430165552206</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02601264090501351</v>
+        <v>0.06743395785322541</v>
       </c>
       <c r="L29" t="n">
         <v>109.609711216533</v>
@@ -2949,7 +2949,7 @@
         <v>200</v>
       </c>
       <c r="N29" t="n">
-        <v>0.45</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="O29" t="n">
         <v>198.5277121400952</v>
@@ -2958,16 +2958,16 @@
         <v>200</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.45</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R29" t="n">
         <v>199.9388941772115</v>
       </c>
       <c r="S29" t="n">
-        <v>200</v>
+        <v>199.9999595883774</v>
       </c>
       <c r="T29" t="n">
-        <v>0.03753968500489356</v>
+        <v>0.07612185230396007</v>
       </c>
       <c r="U29" t="n">
         <v>192.5799615112869</v>
@@ -2985,7 +2985,7 @@
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
         <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08282712908855035</v>
+        <v>0.09271128771702397</v>
       </c>
       <c r="I30" t="n">
         <v>196.0386411854094</v>
@@ -3027,7 +3027,7 @@
         <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>0.00576525480302511</v>
+        <v>0.005792552333991318</v>
       </c>
       <c r="L30" t="n">
         <v>79.54507935933471</v>
@@ -3036,7 +3036,7 @@
         <v>200</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="O30" t="n">
         <v>198.9477887234591</v>
@@ -3045,7 +3045,7 @@
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="R30" t="n">
         <v>199.7754683359127</v>
@@ -3054,7 +3054,7 @@
         <v>200</v>
       </c>
       <c r="T30" t="n">
-        <v>0.02462361562998687</v>
+        <v>0.02141443680013175</v>
       </c>
       <c r="U30" t="n">
         <v>198.9226798174336</v>
@@ -3096,25 +3096,25 @@
         <v>2026</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>200</v>
+        <v>197.2154099320408</v>
       </c>
       <c r="H31" t="n">
-        <v>0.09492014033457305</v>
+        <v>0.1348741867312997</v>
       </c>
       <c r="I31" t="n">
         <v>194.2466814459454</v>
       </c>
       <c r="J31" t="n">
-        <v>200</v>
+        <v>199.8851341157176</v>
       </c>
       <c r="K31" t="n">
-        <v>0.005793890306590724</v>
+        <v>0.0488081467166611</v>
       </c>
       <c r="L31" t="n">
         <v>109.7635513825217</v>
@@ -3123,7 +3123,7 @@
         <v>200</v>
       </c>
       <c r="N31" t="n">
-        <v>0.15</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="O31" t="n">
         <v>199.0633013569061</v>
@@ -3132,16 +3132,16 @@
         <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.15</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="R31" t="n">
         <v>199.9196066031173</v>
       </c>
       <c r="S31" t="n">
-        <v>200</v>
+        <v>199.9999999913935</v>
       </c>
       <c r="T31" t="n">
-        <v>0.0156642325101831</v>
+        <v>0.05709933295456548</v>
       </c>
       <c r="U31" t="n">
         <v>194.1597056483905</v>
@@ -3159,7 +3159,7 @@
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3183,52 +3183,52 @@
         <v>2026</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G32" t="n">
-        <v>162.0968926914251</v>
+        <v>146.7319878793955</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4029735300622607</v>
+        <v>0.58739462129047</v>
       </c>
       <c r="I32" t="n">
         <v>164.6748490827784</v>
       </c>
       <c r="J32" t="n">
-        <v>184.3450690318275</v>
+        <v>168.6519714295135</v>
       </c>
       <c r="K32" t="n">
-        <v>0.4578138118526899</v>
+        <v>0.9526356847622569</v>
       </c>
       <c r="L32" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M32" t="n">
-        <v>154.0413533834586</v>
+        <v>157.0394148787501</v>
       </c>
       <c r="N32" t="n">
-        <v>3.4</v>
+        <v>8.652173913043478</v>
       </c>
       <c r="O32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="P32" t="n">
-        <v>154.0413533834586</v>
+        <v>157.0394148787501</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>8.652173913043478</v>
       </c>
       <c r="R32" t="n">
         <v>195.3761640213164</v>
       </c>
       <c r="S32" t="n">
-        <v>152.9603523577473</v>
+        <v>142.7163228269366</v>
       </c>
       <c r="T32" t="n">
-        <v>0.6197694400850768</v>
+        <v>1.241395123958266</v>
       </c>
       <c r="U32" t="n">
         <v>173.3959783787531</v>
@@ -3240,13 +3240,15 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>146.7319878793955</v>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=146.73% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -3270,52 +3272,52 @@
         <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G33" t="n">
-        <v>200</v>
+        <v>167.4517535775812</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1968837263275579</v>
+        <v>0.2884666033267993</v>
       </c>
       <c r="I33" t="n">
         <v>170.4028696730483</v>
       </c>
       <c r="J33" t="n">
-        <v>197.682261094374</v>
+        <v>188.377627252309</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3001168361263843</v>
+        <v>0.4644442591589993</v>
       </c>
       <c r="L33" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M33" t="n">
-        <v>200</v>
+        <v>189.7435897435898</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="O33" t="n">
         <v>180.7526372107734</v>
       </c>
       <c r="P33" t="n">
-        <v>200</v>
+        <v>189.7435897435898</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="R33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="S33" t="n">
-        <v>196.5928288743223</v>
+        <v>180.2510347941071</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3447896743772237</v>
+        <v>0.5087351181077601</v>
       </c>
       <c r="U33" t="n">
         <v>182.3083787234438</v>
@@ -3333,7 +3335,7 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3357,52 +3359,52 @@
         <v>2026</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>168.5254247214432</v>
+        <v>157.0880607143566</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3162578492589506</v>
+        <v>0.5151377343414262</v>
       </c>
       <c r="I34" t="n">
         <v>169.6571057340244</v>
       </c>
       <c r="J34" t="n">
-        <v>171.6136216027415</v>
+        <v>170.9330944059021</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9876155844856072</v>
+        <v>2.646025138296189</v>
       </c>
       <c r="L34" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M34" t="n">
-        <v>164.3383283383283</v>
+        <v>167.5100569928156</v>
       </c>
       <c r="N34" t="n">
-        <v>1.9</v>
+        <v>5.717391304347826</v>
       </c>
       <c r="O34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="P34" t="n">
-        <v>164.3383283383283</v>
+        <v>167.5100569928156</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>5.717391304347826</v>
       </c>
       <c r="R34" t="n">
         <v>195.2398047728465</v>
       </c>
       <c r="S34" t="n">
-        <v>160.3353263613274</v>
+        <v>152.4983711525398</v>
       </c>
       <c r="T34" t="n">
-        <v>0.3518140627313046</v>
+        <v>0.7121254488184438</v>
       </c>
       <c r="U34" t="n">
         <v>176.7243686471345</v>
@@ -3414,13 +3416,15 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>157.0880607143566</v>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=157.09% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -3444,52 +3448,52 @@
         <v>2026</v>
       </c>
       <c r="E35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" t="n">
-        <v>105.9281725311015</v>
+        <v>113.2848554010246</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6844616986657439</v>
+        <v>0.6558033861263876</v>
       </c>
       <c r="I35" t="n">
         <v>48.55849570822402</v>
       </c>
       <c r="J35" t="n">
-        <v>123.1572115120545</v>
+        <v>126.6760925192243</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8016465967314691</v>
+        <v>1.025372215368218</v>
       </c>
       <c r="L35" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M35" t="n">
-        <v>189.5464969622409</v>
+        <v>190.4538676034567</v>
       </c>
       <c r="N35" t="n">
-        <v>30.71911507859925</v>
+        <v>31.47006673612028</v>
       </c>
       <c r="O35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="P35" t="n">
-        <v>197.8549201547707</v>
+        <v>197.9608001345832</v>
       </c>
       <c r="Q35" t="n">
-        <v>175.4469425492444</v>
+        <v>170.9799005052389</v>
       </c>
       <c r="R35" t="n">
         <v>185.853149170162</v>
       </c>
       <c r="S35" t="n">
-        <v>128.5818390703525</v>
+        <v>135.8763646985932</v>
       </c>
       <c r="T35" t="n">
-        <v>1.82424504622132</v>
+        <v>2.572579880569255</v>
       </c>
       <c r="U35" t="n">
         <v>110.5529101365675</v>
@@ -3505,11 +3509,11 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>105.9281725311015</v>
+        <v>113.2848554010246</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=105.93% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=113.28% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -3533,52 +3537,52 @@
         <v>2026</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>163.7264674232613</v>
+        <v>165.4537784983441</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4907642625934389</v>
+        <v>0.4702297935595121</v>
       </c>
       <c r="I36" t="n">
         <v>58.86670393327421</v>
       </c>
       <c r="J36" t="n">
-        <v>169.2768130296432</v>
+        <v>164.9398927199169</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7105029179987218</v>
+        <v>0.7312362484139593</v>
       </c>
       <c r="L36" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M36" t="n">
-        <v>185.551721301033</v>
+        <v>186.1695209808159</v>
       </c>
       <c r="N36" t="n">
-        <v>9.107451865461025</v>
+        <v>9.555762135616817</v>
       </c>
       <c r="O36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="P36" t="n">
-        <v>198.2693084419491</v>
+        <v>198.1506685547728</v>
       </c>
       <c r="Q36" t="n">
-        <v>85.40262813801223</v>
+        <v>83.5338775666923</v>
       </c>
       <c r="R36" t="n">
         <v>187.2910306593169</v>
       </c>
       <c r="S36" t="n">
-        <v>157.1419251017288</v>
+        <v>159.5615302812286</v>
       </c>
       <c r="T36" t="n">
-        <v>1.118917428962281</v>
+        <v>1.513345438955633</v>
       </c>
       <c r="U36" t="n">
         <v>118.8153464644226</v>
@@ -3596,7 +3600,7 @@
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3620,52 +3624,52 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>151.8378542282286</v>
+        <v>158.1198732419379</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6140177756242682</v>
+        <v>0.5562682868815395</v>
       </c>
       <c r="I37" t="n">
         <v>60.32903496111531</v>
       </c>
       <c r="J37" t="n">
-        <v>163.9003993706592</v>
+        <v>168.609042931008</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8983255976255238</v>
+        <v>1.044320482672119</v>
       </c>
       <c r="L37" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M37" t="n">
-        <v>181.617770983112</v>
+        <v>184.015453028793</v>
       </c>
       <c r="N37" t="n">
-        <v>9.383893129980439</v>
+        <v>9.787898060304089</v>
       </c>
       <c r="O37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="P37" t="n">
-        <v>197.4511087877988</v>
+        <v>197.7835728589555</v>
       </c>
       <c r="Q37" t="n">
-        <v>91.25143798078706</v>
+        <v>88.89743836828053</v>
       </c>
       <c r="R37" t="n">
         <v>185.3862117422507</v>
       </c>
       <c r="S37" t="n">
-        <v>148.089478161802</v>
+        <v>154.8604157928713</v>
       </c>
       <c r="T37" t="n">
-        <v>1.091784744323357</v>
+        <v>1.553482650555693</v>
       </c>
       <c r="U37" t="n">
         <v>110.8838400280787</v>
@@ -3707,59 +3711,59 @@
         <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>192.3923638058561</v>
+        <v>193.3846641790053</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4625873314833769</v>
+        <v>0.5239297728687791</v>
       </c>
       <c r="I38" t="n">
         <v>164.4263244057969</v>
       </c>
       <c r="J38" t="n">
-        <v>193.8622543589206</v>
+        <v>194.6628298773223</v>
       </c>
       <c r="K38" t="n">
-        <v>0.3699466801412142</v>
+        <v>0.5992480163143454</v>
       </c>
       <c r="L38" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M38" t="n">
-        <v>183.3636363636363</v>
+        <v>185.5335968379447</v>
       </c>
       <c r="N38" t="n">
-        <v>7.9</v>
+        <v>10.84782608695652</v>
       </c>
       <c r="O38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="P38" t="n">
-        <v>183.3636363636363</v>
+        <v>185.5335968379447</v>
       </c>
       <c r="Q38" t="n">
-        <v>7.9</v>
+        <v>10.84782608695652</v>
       </c>
       <c r="R38" t="n">
         <v>199.036270909302</v>
       </c>
       <c r="S38" t="n">
-        <v>185.245820591262</v>
+        <v>187.1702787750105</v>
       </c>
       <c r="T38" t="n">
-        <v>0.4200888512268395</v>
+        <v>0.5776903847574255</v>
       </c>
       <c r="U38" t="n">
         <v>129.2920232398837</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -3770,7 +3774,7 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3794,52 +3798,52 @@
         <v>2026</v>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>198.5862956300785</v>
+        <v>198.7706918522422</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1724602873418419</v>
+        <v>0.1729726208837764</v>
       </c>
       <c r="I39" t="n">
         <v>170.2041702191862</v>
       </c>
       <c r="J39" t="n">
-        <v>199.1889772206135</v>
+        <v>199.2947628005335</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1158998444099787</v>
+        <v>0.1030238417183106</v>
       </c>
       <c r="L39" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M39" t="n">
-        <v>183.1578947368421</v>
+        <v>185.4545454545454</v>
       </c>
       <c r="N39" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="O39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="P39" t="n">
-        <v>183.1578947368421</v>
+        <v>185.4545454545454</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
         <v>199.0467638312102</v>
       </c>
       <c r="S39" t="n">
-        <v>194.4716056581771</v>
+        <v>195.192700572328</v>
       </c>
       <c r="T39" t="n">
-        <v>0.2213114506864156</v>
+        <v>0.2862166282653509</v>
       </c>
       <c r="U39" t="n">
         <v>146.152525200624</v>
@@ -3881,52 +3885,52 @@
         <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>197.9577894510206</v>
+        <v>198.2241647400179</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2197660420449167</v>
+        <v>0.2392891166621177</v>
       </c>
       <c r="I40" t="n">
         <v>165.7522199768573</v>
       </c>
       <c r="J40" t="n">
-        <v>199.6091588349978</v>
+        <v>199.6601381173894</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1103781947572354</v>
+        <v>0.09725505564008544</v>
       </c>
       <c r="L40" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M40" t="n">
-        <v>187</v>
+        <v>188.695652173913</v>
       </c>
       <c r="N40" t="n">
-        <v>4.475</v>
+        <v>6.239130434782608</v>
       </c>
       <c r="O40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="P40" t="n">
-        <v>187</v>
+        <v>188.695652173913</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.475</v>
+        <v>6.239130434782608</v>
       </c>
       <c r="R40" t="n">
         <v>198.942356787496</v>
       </c>
       <c r="S40" t="n">
-        <v>194.6571167299734</v>
+        <v>195.354014547803</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2431969099467668</v>
+        <v>0.3232036678554339</v>
       </c>
       <c r="U40" t="n">
         <v>124.2002492905602</v>
@@ -3968,52 +3972,52 @@
         <v>2026</v>
       </c>
       <c r="E41" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F41" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G41" t="n">
-        <v>87.58438501164028</v>
+        <v>82.72779030325239</v>
       </c>
       <c r="H41" t="n">
-        <v>2.030336807144944</v>
+        <v>2.205068090204341</v>
       </c>
       <c r="I41" t="n">
         <v>127.4617865350128</v>
       </c>
       <c r="J41" t="n">
-        <v>88.16748667658304</v>
+        <v>83.2708876044556</v>
       </c>
       <c r="K41" t="n">
-        <v>1.513182749141943</v>
+        <v>1.811546819726689</v>
       </c>
       <c r="L41" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M41" t="n">
-        <v>183.2510430578968</v>
+        <v>183.2704771757123</v>
       </c>
       <c r="N41" t="n">
-        <v>59.6</v>
+        <v>72.32608695652173</v>
       </c>
       <c r="O41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="P41" t="n">
-        <v>183.2510430578968</v>
+        <v>183.2704771757123</v>
       </c>
       <c r="Q41" t="n">
-        <v>59.6</v>
+        <v>72.32608695652173</v>
       </c>
       <c r="R41" t="n">
         <v>198.8825072752037</v>
       </c>
       <c r="S41" t="n">
-        <v>70.80422175698777</v>
+        <v>68.94662220594313</v>
       </c>
       <c r="T41" t="n">
-        <v>1.129418131199049</v>
+        <v>1.633128644014865</v>
       </c>
       <c r="U41" t="n">
         <v>124.7888620818299</v>
@@ -4029,11 +4033,11 @@
         </is>
       </c>
       <c r="X41" t="n">
-        <v>70.80422175698777</v>
+        <v>68.94662220594313</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=70.80% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=68.95% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -4057,52 +4061,52 @@
         <v>2026</v>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F42" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G42" t="n">
-        <v>110.5832306135111</v>
+        <v>104.1026920736107</v>
       </c>
       <c r="H42" t="n">
-        <v>1.222854070382742</v>
+        <v>1.296501311921143</v>
       </c>
       <c r="I42" t="n">
         <v>139.5371944473096</v>
       </c>
       <c r="J42" t="n">
-        <v>156.5471576898993</v>
+        <v>156.615136406059</v>
       </c>
       <c r="K42" t="n">
-        <v>1.338495597351946</v>
+        <v>1.590515636108311</v>
       </c>
       <c r="L42" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M42" t="n">
-        <v>181.4835915550719</v>
+        <v>181.2013484684743</v>
       </c>
       <c r="N42" t="n">
-        <v>27.475</v>
+        <v>32.21739130434783</v>
       </c>
       <c r="O42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="P42" t="n">
-        <v>181.4835915550719</v>
+        <v>181.2013484684743</v>
       </c>
       <c r="Q42" t="n">
-        <v>27.475</v>
+        <v>32.21739130434783</v>
       </c>
       <c r="R42" t="n">
         <v>198.6803521667581</v>
       </c>
       <c r="S42" t="n">
-        <v>95.21274486565832</v>
+        <v>87.18884383126479</v>
       </c>
       <c r="T42" t="n">
-        <v>0.656324198860722</v>
+        <v>0.747015619254191</v>
       </c>
       <c r="U42" t="n">
         <v>125.9010082864909</v>
@@ -4118,11 +4122,11 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>95.21274486565832</v>
+        <v>87.18884383126479</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=95.21% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=87.19% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -4146,52 +4150,52 @@
         <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F43" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G43" t="n">
-        <v>91.54776374116032</v>
+        <v>88.26598834050192</v>
       </c>
       <c r="H43" t="n">
-        <v>1.123728032782006</v>
+        <v>1.287595910820883</v>
       </c>
       <c r="I43" t="n">
         <v>137.8269504556986</v>
       </c>
       <c r="J43" t="n">
-        <v>131.4560119700474</v>
+        <v>127.4417016791812</v>
       </c>
       <c r="K43" t="n">
-        <v>1.103993563605121</v>
+        <v>1.34725603985074</v>
       </c>
       <c r="L43" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M43" t="n">
-        <v>186.1949515602007</v>
+        <v>186.2893573502836</v>
       </c>
       <c r="N43" t="n">
-        <v>33.775</v>
+        <v>41.54347826086956</v>
       </c>
       <c r="O43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="P43" t="n">
-        <v>186.1949515602007</v>
+        <v>186.2893573502836</v>
       </c>
       <c r="Q43" t="n">
-        <v>33.775</v>
+        <v>41.54347826086956</v>
       </c>
       <c r="R43" t="n">
         <v>198.9631246433146</v>
       </c>
       <c r="S43" t="n">
-        <v>78.94820616457373</v>
+        <v>80.11092782082243</v>
       </c>
       <c r="T43" t="n">
-        <v>0.5599070909893283</v>
+        <v>0.9713696197997124</v>
       </c>
       <c r="U43" t="n">
         <v>126.6160396504699</v>
@@ -4207,11 +4211,11 @@
         </is>
       </c>
       <c r="X43" t="n">
-        <v>78.94820616457373</v>
+        <v>80.11092782082243</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=78.95% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=80.11% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -4235,52 +4239,52 @@
         <v>2026</v>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G44" t="n">
-        <v>100.1760886061951</v>
+        <v>102.5913204693476</v>
       </c>
       <c r="H44" t="n">
-        <v>3.283604980073041</v>
+        <v>3.54781187482808</v>
       </c>
       <c r="I44" t="n">
         <v>101.902133963665</v>
       </c>
       <c r="J44" t="n">
-        <v>108.540756260745</v>
+        <v>106.7058072665996</v>
       </c>
       <c r="K44" t="n">
-        <v>1.860320510021031</v>
+        <v>1.77103799103927</v>
       </c>
       <c r="L44" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M44" t="n">
-        <v>185.1842442724588</v>
+        <v>185.942217792085</v>
       </c>
       <c r="N44" t="n">
-        <v>70.325</v>
+        <v>79.4301274678176</v>
       </c>
       <c r="O44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="P44" t="n">
-        <v>185.1842442724588</v>
+        <v>185.9779150045329</v>
       </c>
       <c r="Q44" t="n">
-        <v>70.325</v>
+        <v>82.95652173913044</v>
       </c>
       <c r="R44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="S44" t="n">
-        <v>82.67021880934045</v>
+        <v>91.20043864530405</v>
       </c>
       <c r="T44" t="n">
-        <v>1.727701335879652</v>
+        <v>3.522292112030377</v>
       </c>
       <c r="U44" t="n">
         <v>121.0188473841644</v>
@@ -4296,11 +4300,11 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>82.67021880934045</v>
+        <v>91.20043864530405</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=82.67% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=91.20% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -4324,52 +4328,52 @@
         <v>2026</v>
       </c>
       <c r="E45" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G45" t="n">
-        <v>117.5693890290908</v>
+        <v>122.3160069363318</v>
       </c>
       <c r="H45" t="n">
-        <v>2.696912041121936</v>
+        <v>3.149067529114105</v>
       </c>
       <c r="I45" t="n">
         <v>133.2410714461222</v>
       </c>
       <c r="J45" t="n">
-        <v>134.4149074996252</v>
+        <v>130.2208490932587</v>
       </c>
       <c r="K45" t="n">
-        <v>1.41176982500326</v>
+        <v>1.366357758115597</v>
       </c>
       <c r="L45" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M45" t="n">
-        <v>182.4802234152958</v>
+        <v>183.7309562954249</v>
       </c>
       <c r="N45" t="n">
-        <v>34.375</v>
+        <v>39.28260869565217</v>
       </c>
       <c r="O45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="P45" t="n">
-        <v>182.4802234152958</v>
+        <v>183.7309562954249</v>
       </c>
       <c r="Q45" t="n">
-        <v>34.375</v>
+        <v>39.28260869565217</v>
       </c>
       <c r="R45" t="n">
         <v>195.8311934408034</v>
       </c>
       <c r="S45" t="n">
-        <v>92.28450382596138</v>
+        <v>100.1711588658116</v>
       </c>
       <c r="T45" t="n">
-        <v>0.8368388459927267</v>
+        <v>1.634375800392914</v>
       </c>
       <c r="U45" t="n">
         <v>112.5504951429215</v>
@@ -4385,11 +4389,11 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>92.28450382596138</v>
+        <v>100.1711588658116</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=92.28% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=100.17% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -4413,52 +4417,52 @@
         <v>2026</v>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F46" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G46" t="n">
-        <v>136.8313047173424</v>
+        <v>135.7367315420406</v>
       </c>
       <c r="H46" t="n">
-        <v>2.514120583028526</v>
+        <v>2.70010287577914</v>
       </c>
       <c r="I46" t="n">
         <v>129.1401202444324</v>
       </c>
       <c r="J46" t="n">
-        <v>151.6740223278146</v>
+        <v>151.5660132383503</v>
       </c>
       <c r="K46" t="n">
-        <v>1.101884879710657</v>
+        <v>1.122142766855141</v>
       </c>
       <c r="L46" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M46" t="n">
-        <v>187.01193669478</v>
+        <v>187.4330170603259</v>
       </c>
       <c r="N46" t="n">
-        <v>35.95</v>
+        <v>42.72432800067003</v>
       </c>
       <c r="O46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="P46" t="n">
-        <v>187.01193669478</v>
+        <v>187.45470889511</v>
       </c>
       <c r="Q46" t="n">
-        <v>35.95</v>
+        <v>43.93478260869565</v>
       </c>
       <c r="R46" t="n">
         <v>196.1388328305384</v>
       </c>
       <c r="S46" t="n">
-        <v>121.5832947563951</v>
+        <v>123.8234213213976</v>
       </c>
       <c r="T46" t="n">
-        <v>1.081930593728427</v>
+        <v>1.908771523870075</v>
       </c>
       <c r="U46" t="n">
         <v>125.7491255686458</v>
@@ -4474,11 +4478,11 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>121.5832947563951</v>
+        <v>123.8234213213976</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=121.58% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=123.82% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -4502,52 +4506,52 @@
         <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>196.2533354157135</v>
+        <v>196.5209543145911</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2054359597430263</v>
+        <v>0.2221182258635011</v>
       </c>
       <c r="I47" t="n">
         <v>52.02932925897922</v>
       </c>
       <c r="J47" t="n">
-        <v>191.5389692181939</v>
+        <v>190.2559898730695</v>
       </c>
       <c r="K47" t="n">
-        <v>0.7019875407916307</v>
+        <v>1.130426493699136</v>
       </c>
       <c r="L47" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M47" t="n">
-        <v>198.0470841511268</v>
+        <v>197.9629028613394</v>
       </c>
       <c r="N47" t="n">
-        <v>26.53475087988627</v>
+        <v>29.27883831116923</v>
       </c>
       <c r="O47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="P47" t="n">
-        <v>198.7613219094247</v>
+        <v>198.7991070912838</v>
       </c>
       <c r="Q47" t="n">
-        <v>43.425</v>
+        <v>56.30434782608695</v>
       </c>
       <c r="R47" t="n">
         <v>193.8459595711977</v>
       </c>
       <c r="S47" t="n">
-        <v>185.3898606257719</v>
+        <v>185.1329876177941</v>
       </c>
       <c r="T47" t="n">
-        <v>0.9208266485431664</v>
+        <v>1.704194556920437</v>
       </c>
       <c r="U47" t="n">
         <v>130.8486591703272</v>
@@ -4565,7 +4569,7 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4593,7 @@
         <v>2026</v>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -4598,43 +4602,43 @@
         <v>197.4116289114259</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1176767903586708</v>
+        <v>0.1023276437901485</v>
       </c>
       <c r="I48" t="n">
         <v>75.82494372432545</v>
       </c>
       <c r="J48" t="n">
-        <v>198.6063966691685</v>
+        <v>198.7881710166683</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2362585533218085</v>
+        <v>0.3272215899392314</v>
       </c>
       <c r="L48" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M48" t="n">
-        <v>197.3570262808407</v>
+        <v>197.7017619833397</v>
       </c>
       <c r="N48" t="n">
-        <v>12.94475919137651</v>
+        <v>13.86763525488404</v>
       </c>
       <c r="O48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="P48" t="n">
-        <v>197.7911575196724</v>
+        <v>198.0792674084108</v>
       </c>
       <c r="Q48" t="n">
-        <v>19.15545161903231</v>
+        <v>23.84235614989821</v>
       </c>
       <c r="R48" t="n">
         <v>192.3368460426438</v>
       </c>
       <c r="S48" t="n">
-        <v>191.5526044407993</v>
+        <v>192.6544386441733</v>
       </c>
       <c r="T48" t="n">
-        <v>0.7809453426517626</v>
+        <v>1.487823412839192</v>
       </c>
       <c r="U48" t="n">
         <v>148.2729860112375</v>
@@ -4676,52 +4680,52 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.07383801724012115</v>
+        <v>0.107685232382714</v>
       </c>
       <c r="I49" t="n">
         <v>67.54170898302603</v>
       </c>
       <c r="J49" t="n">
-        <v>195.3168227111101</v>
+        <v>192.9933706852672</v>
       </c>
       <c r="K49" t="n">
-        <v>0.440125846631825</v>
+        <v>0.7616750114464241</v>
       </c>
       <c r="L49" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M49" t="n">
-        <v>199.2313995433047</v>
+        <v>198.7084920295648</v>
       </c>
       <c r="N49" t="n">
-        <v>14.83420482866237</v>
+        <v>16.33837133214592</v>
       </c>
       <c r="O49" t="n">
         <v>179.6516960231333</v>
       </c>
       <c r="P49" t="n">
-        <v>199.672131147541</v>
+        <v>199.5066175560497</v>
       </c>
       <c r="Q49" t="n">
-        <v>24.175</v>
+        <v>31.67391304347826</v>
       </c>
       <c r="R49" t="n">
         <v>193.5695579772771</v>
       </c>
       <c r="S49" t="n">
-        <v>193.2495431384828</v>
+        <v>190.7776968167292</v>
       </c>
       <c r="T49" t="n">
-        <v>0.6147829788060031</v>
+        <v>1.045974666730537</v>
       </c>
       <c r="U49" t="n">
         <v>141.2583029624075</v>
@@ -4739,7 +4743,7 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4763,52 +4767,52 @@
         <v>2026</v>
       </c>
       <c r="E50" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>190.1860027565376</v>
+        <v>189.7994969033458</v>
       </c>
       <c r="H50" t="n">
-        <v>1.811214069262746</v>
+        <v>3.869851488063552</v>
       </c>
       <c r="I50" t="n">
         <v>162.6912701840232</v>
       </c>
       <c r="J50" t="n">
-        <v>199.1345096289146</v>
+        <v>196.7614499456022</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3014211135351322</v>
+        <v>0.3455874680551403</v>
       </c>
       <c r="L50" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M50" t="n">
-        <v>188.7749836195508</v>
+        <v>191.147728062793</v>
       </c>
       <c r="N50" t="n">
-        <v>2.323166561126709</v>
+        <v>7.312309513921323</v>
       </c>
       <c r="O50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="P50" t="n">
-        <v>193.6754652824088</v>
+        <v>193.4135280554246</v>
       </c>
       <c r="Q50" t="n">
-        <v>10.60452228268771</v>
+        <v>13.03107782436076</v>
       </c>
       <c r="R50" t="n">
         <v>160.5521309789579</v>
       </c>
       <c r="S50" t="n">
-        <v>189.5889037134853</v>
+        <v>190.5537618513702</v>
       </c>
       <c r="T50" t="n">
-        <v>4.311792175500303</v>
+        <v>14.06025828632104</v>
       </c>
       <c r="U50" t="n">
         <v>135.4400555181058</v>
@@ -4826,7 +4830,7 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4850,52 +4854,52 @@
         <v>2026</v>
       </c>
       <c r="E51" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>190.9721759438794</v>
+        <v>189.7784228856569</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8704176835186438</v>
+        <v>1.466018721053983</v>
       </c>
       <c r="I51" t="n">
         <v>169.9274838481079</v>
       </c>
       <c r="J51" t="n">
-        <v>192.3028144606102</v>
+        <v>184.7710950335155</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1434088457519661</v>
+        <v>0.189051601077927</v>
       </c>
       <c r="L51" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M51" t="n">
-        <v>195.5244755244755</v>
+        <v>195.8955584201071</v>
       </c>
       <c r="N51" t="n">
-        <v>7.7</v>
+        <v>13.2393867157233</v>
       </c>
       <c r="O51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="P51" t="n">
-        <v>193.2048049441361</v>
+        <v>192.8527800555265</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.638259689213548</v>
+        <v>4.731702148524894</v>
       </c>
       <c r="R51" t="n">
         <v>165.5121650610737</v>
       </c>
       <c r="S51" t="n">
-        <v>188.6067148624402</v>
+        <v>189.680701432455</v>
       </c>
       <c r="T51" t="n">
-        <v>1.831224401117342</v>
+        <v>6.219254369252377</v>
       </c>
       <c r="U51" t="n">
         <v>151.1230387281904</v>
@@ -4913,7 +4917,7 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4937,52 +4941,52 @@
         <v>2026</v>
       </c>
       <c r="E52" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>188.9958162828261</v>
+        <v>188.9622851709017</v>
       </c>
       <c r="H52" t="n">
-        <v>1.00129017973042</v>
+        <v>2.19100280753381</v>
       </c>
       <c r="I52" t="n">
         <v>174.432365021141</v>
       </c>
       <c r="J52" t="n">
-        <v>199.6256320167606</v>
+        <v>199.1565596561415</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1585411434662608</v>
+        <v>0.1833099189597912</v>
       </c>
       <c r="L52" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M52" t="n">
-        <v>196.19941873463</v>
+        <v>196.5348518483145</v>
       </c>
       <c r="N52" t="n">
-        <v>11.475</v>
+        <v>20.20863496794401</v>
       </c>
       <c r="O52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="P52" t="n">
-        <v>192.142663329359</v>
+        <v>192.2138596845881</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.605039689690354</v>
+        <v>6.843596540696626</v>
       </c>
       <c r="R52" t="n">
         <v>154.7555469695623</v>
       </c>
       <c r="S52" t="n">
-        <v>190.2365743867556</v>
+        <v>191.2056469997896</v>
       </c>
       <c r="T52" t="n">
-        <v>2.985689708770413</v>
+        <v>10.57367013666008</v>
       </c>
       <c r="U52" t="n">
         <v>133.8716916594558</v>
@@ -5000,7 +5004,7 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5024,52 +5028,52 @@
         <v>2026</v>
       </c>
       <c r="E53" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F53" t="n">
-        <v>2279</v>
+        <v>2696</v>
       </c>
       <c r="G53" t="n">
-        <v>19.49960594346439</v>
+        <v>19.4402932458659</v>
       </c>
       <c r="H53" t="n">
-        <v>22.77922614753295</v>
+        <v>23.63699715423957</v>
       </c>
       <c r="I53" t="n">
         <v>35.23746831954708</v>
       </c>
       <c r="J53" t="n">
-        <v>19.62979676942301</v>
+        <v>17.8172358714134</v>
       </c>
       <c r="K53" t="n">
-        <v>21.7087593849698</v>
+        <v>19.90194493285133</v>
       </c>
       <c r="L53" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M53" t="n">
-        <v>161.6595762447816</v>
+        <v>162.8856277742575</v>
       </c>
       <c r="N53" t="n">
-        <v>960.425</v>
+        <v>1061.978260869565</v>
       </c>
       <c r="O53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="P53" t="n">
-        <v>161.6595762447816</v>
+        <v>162.8856277742575</v>
       </c>
       <c r="Q53" t="n">
-        <v>960.425</v>
+        <v>1061.978260869565</v>
       </c>
       <c r="R53" t="n">
         <v>188.2648408233968</v>
       </c>
       <c r="S53" t="n">
-        <v>34.1856960792193</v>
+        <v>42.50348384326168</v>
       </c>
       <c r="T53" t="n">
-        <v>48.85744400228063</v>
+        <v>78.57314109556394</v>
       </c>
       <c r="U53" t="n">
         <v>92.2349408254034</v>
@@ -5085,11 +5089,11 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>19.62979676942301</v>
+        <v>17.8172358714134</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=19.63% sobre 20 sem</t>
+          <t>DeepAR: menor SMAPE real=17.82% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5113,59 +5117,59 @@
         <v>2026</v>
       </c>
       <c r="E54" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F54" t="n">
-        <v>1069</v>
+        <v>1271</v>
       </c>
       <c r="G54" t="n">
-        <v>22.0104914430118</v>
+        <v>20.72754113641285</v>
       </c>
       <c r="H54" t="n">
-        <v>12.37528277567318</v>
+        <v>11.79391705998009</v>
       </c>
       <c r="I54" t="n">
         <v>38.4591918317379</v>
       </c>
       <c r="J54" t="n">
-        <v>20.86573678611043</v>
+        <v>22.70335561200558</v>
       </c>
       <c r="K54" t="n">
-        <v>11.10529454897445</v>
+        <v>13.49333944868383</v>
       </c>
       <c r="L54" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M54" t="n">
-        <v>162.0216712531311</v>
+        <v>162.7510613149525</v>
       </c>
       <c r="N54" t="n">
-        <v>454.45</v>
+        <v>490.0217391304348</v>
       </c>
       <c r="O54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="P54" t="n">
-        <v>162.0216712531311</v>
+        <v>162.7510613149525</v>
       </c>
       <c r="Q54" t="n">
-        <v>454.45</v>
+        <v>490.0217391304348</v>
       </c>
       <c r="R54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="S54" t="n">
-        <v>34.78772843329066</v>
+        <v>42.12132287974038</v>
       </c>
       <c r="T54" t="n">
-        <v>23.30953662574492</v>
+        <v>35.35053273428665</v>
       </c>
       <c r="U54" t="n">
         <v>91.67135817890519</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
@@ -5174,11 +5178,11 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>20.86573678611043</v>
+        <v>20.72754113641285</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=20.87% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=20.73% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5202,59 +5206,59 @@
         <v>2026</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F55" t="n">
-        <v>1204</v>
+        <v>1420</v>
       </c>
       <c r="G55" t="n">
-        <v>25.14083857716377</v>
+        <v>23.55506705210731</v>
       </c>
       <c r="H55" t="n">
-        <v>14.69550352042221</v>
+        <v>14.04258120989469</v>
       </c>
       <c r="I55" t="n">
         <v>38.25160771522186</v>
       </c>
       <c r="J55" t="n">
-        <v>23.2194777075171</v>
+        <v>24.82026751275703</v>
       </c>
       <c r="K55" t="n">
-        <v>13.34124330195221</v>
+        <v>15.62374331453546</v>
       </c>
       <c r="L55" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M55" t="n">
-        <v>161.5406661246429</v>
+        <v>163.1038272712023</v>
       </c>
       <c r="N55" t="n">
-        <v>506.275</v>
+        <v>572.1739130434783</v>
       </c>
       <c r="O55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="P55" t="n">
-        <v>161.5406661246429</v>
+        <v>163.1038272712023</v>
       </c>
       <c r="Q55" t="n">
-        <v>506.275</v>
+        <v>572.1739130434783</v>
       </c>
       <c r="R55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="S55" t="n">
-        <v>31.13756976946399</v>
+        <v>40.15519558781323</v>
       </c>
       <c r="T55" t="n">
-        <v>23.17726626922712</v>
+        <v>39.84661362628754</v>
       </c>
       <c r="U55" t="n">
         <v>92.1901984902002</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
@@ -5263,11 +5267,11 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>23.2194777075171</v>
+        <v>23.55506705210731</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=23.22% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=23.56% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5291,52 +5295,52 @@
         <v>2026</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G56" t="n">
-        <v>72.59780631431283</v>
+        <v>70.75000240776146</v>
       </c>
       <c r="H56" t="n">
-        <v>2.927095271311128</v>
+        <v>3.072888443060451</v>
       </c>
       <c r="I56" t="n">
         <v>154.1439500713238</v>
       </c>
       <c r="J56" t="n">
-        <v>57.68251133907203</v>
+        <v>68.35169810424058</v>
       </c>
       <c r="K56" t="n">
-        <v>1.974453659767151</v>
+        <v>2.256310476171245</v>
       </c>
       <c r="L56" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M56" t="n">
-        <v>166.3141326689463</v>
+        <v>168.6347902417901</v>
       </c>
       <c r="N56" t="n">
-        <v>43.85</v>
+        <v>53.86626925227143</v>
       </c>
       <c r="O56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="P56" t="n">
-        <v>166.3141326689463</v>
+        <v>168.6528173016046</v>
       </c>
       <c r="Q56" t="n">
-        <v>43.85</v>
+        <v>54.10869565217391</v>
       </c>
       <c r="R56" t="n">
         <v>197.7368060568652</v>
       </c>
       <c r="S56" t="n">
-        <v>47.23705434251701</v>
+        <v>55.95075362148568</v>
       </c>
       <c r="T56" t="n">
-        <v>1.441218211973871</v>
+        <v>1.736058086714748</v>
       </c>
       <c r="U56" t="n">
         <v>104.7066447751141</v>
@@ -5352,11 +5356,11 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>47.23705434251701</v>
+        <v>55.95075362148568</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=47.24% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=55.95% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5380,59 +5384,59 @@
         <v>2026</v>
       </c>
       <c r="E57" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F57" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G57" t="n">
-        <v>98.10399639077968</v>
+        <v>90.17983228652754</v>
       </c>
       <c r="H57" t="n">
-        <v>1.624721621133489</v>
+        <v>1.552291662272906</v>
       </c>
       <c r="I57" t="n">
         <v>164.0555422208552</v>
       </c>
       <c r="J57" t="n">
-        <v>118.4808392854339</v>
+        <v>127.8315821153468</v>
       </c>
       <c r="K57" t="n">
-        <v>1.462888092115611</v>
+        <v>1.568792435141413</v>
       </c>
       <c r="L57" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M57" t="n">
-        <v>164.8154525810946</v>
+        <v>166.9763237835721</v>
       </c>
       <c r="N57" t="n">
-        <v>19.3</v>
+        <v>23</v>
       </c>
       <c r="O57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="P57" t="n">
-        <v>164.8154525810946</v>
+        <v>166.9763237835721</v>
       </c>
       <c r="Q57" t="n">
-        <v>19.3</v>
+        <v>23</v>
       </c>
       <c r="R57" t="n">
         <v>197.2831175654684</v>
       </c>
       <c r="S57" t="n">
-        <v>92.85103094933392</v>
+        <v>97.4505612721191</v>
       </c>
       <c r="T57" t="n">
-        <v>0.8263998232182921</v>
+        <v>0.9584128892904199</v>
       </c>
       <c r="U57" t="n">
         <v>124.2225772452616</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -5441,11 +5445,11 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>92.85103094933392</v>
+        <v>90.17983228652754</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=92.85% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=90.18% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5469,52 +5473,52 @@
         <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F58" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G58" t="n">
-        <v>91.49378868818445</v>
+        <v>89.98534646608356</v>
       </c>
       <c r="H58" t="n">
-        <v>1.674555031619139</v>
+        <v>1.899959525298533</v>
       </c>
       <c r="I58" t="n">
         <v>158.4722608607674</v>
       </c>
       <c r="J58" t="n">
-        <v>108.2980179309141</v>
+        <v>117.5749584956436</v>
       </c>
       <c r="K58" t="n">
-        <v>1.63337824655962</v>
+        <v>1.751557513723373</v>
       </c>
       <c r="L58" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M58" t="n">
-        <v>168.3159463185017</v>
+        <v>170.5894451766619</v>
       </c>
       <c r="N58" t="n">
-        <v>25.075</v>
+        <v>31.56521739130435</v>
       </c>
       <c r="O58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="P58" t="n">
-        <v>168.3159463185017</v>
+        <v>170.5894451766619</v>
       </c>
       <c r="Q58" t="n">
-        <v>25.075</v>
+        <v>31.56521739130435</v>
       </c>
       <c r="R58" t="n">
         <v>197.6615055783608</v>
       </c>
       <c r="S58" t="n">
-        <v>88.74442516281512</v>
+        <v>88.93515152944408</v>
       </c>
       <c r="T58" t="n">
-        <v>1.007184664798359</v>
+        <v>1.101417340569095</v>
       </c>
       <c r="U58" t="n">
         <v>111.9755139895278</v>
@@ -5530,11 +5534,11 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>88.74442516281512</v>
+        <v>88.93515152944408</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=88.74% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=88.94% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5558,52 +5562,52 @@
         <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G59" t="n">
-        <v>199.4821021973625</v>
+        <v>199.5468394226922</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2183781974394378</v>
+        <v>0.2768506064690763</v>
       </c>
       <c r="I59" t="n">
         <v>163.442478475025</v>
       </c>
       <c r="J59" t="n">
-        <v>192.9099765603397</v>
+        <v>193.0444133653387</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2108791554023861</v>
+        <v>0.2692230842082216</v>
       </c>
       <c r="L59" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M59" t="n">
-        <v>173.3333333333333</v>
+        <v>173.7114845938375</v>
       </c>
       <c r="N59" t="n">
-        <v>2.95</v>
+        <v>4.956521739130435</v>
       </c>
       <c r="O59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="P59" t="n">
-        <v>173.3333333333333</v>
+        <v>173.7114845938375</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.95</v>
+        <v>4.956521739130435</v>
       </c>
       <c r="R59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="S59" t="n">
-        <v>186.5025594510418</v>
+        <v>172.5221446786796</v>
       </c>
       <c r="T59" t="n">
-        <v>0.3762815311939612</v>
+        <v>0.3958316615589348</v>
       </c>
       <c r="U59" t="n">
         <v>167.6265476269683</v>
@@ -5621,7 +5625,7 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5645,52 +5649,52 @@
         <v>2026</v>
       </c>
       <c r="E60" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>197.7007515643313</v>
+        <v>197.8217646398928</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1640807419990983</v>
+        <v>0.1861571669557376</v>
       </c>
       <c r="I60" t="n">
         <v>179.6544870721095</v>
       </c>
       <c r="J60" t="n">
-        <v>198.726748804884</v>
+        <v>198.6906461944827</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1581502749256105</v>
+        <v>0.1812997704605782</v>
       </c>
       <c r="L60" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M60" t="n">
-        <v>165.7142857142857</v>
+        <v>168.4033613445378</v>
       </c>
       <c r="N60" t="n">
-        <v>1.95</v>
+        <v>2.891304347826087</v>
       </c>
       <c r="O60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="P60" t="n">
-        <v>165.7142857142857</v>
+        <v>168.4033613445378</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.95</v>
+        <v>2.891304347826087</v>
       </c>
       <c r="R60" t="n">
         <v>199.0965028052728</v>
       </c>
       <c r="S60" t="n">
-        <v>189.5098878529882</v>
+        <v>186.0449066994106</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2523929302587709</v>
+        <v>0.2820691686391204</v>
       </c>
       <c r="U60" t="n">
         <v>167.0169829765832</v>
@@ -5708,7 +5712,7 @@
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5732,52 +5736,52 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
-        <v>199.9502411083014</v>
+        <v>199.9531681019307</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0708607758842998</v>
+        <v>0.1050963268559129</v>
       </c>
       <c r="I61" t="n">
         <v>178.3754768379913</v>
       </c>
       <c r="J61" t="n">
-        <v>198.4776730955428</v>
+        <v>197.1877208886168</v>
       </c>
       <c r="K61" t="n">
-        <v>0.135473811856939</v>
+        <v>0.1635155699790316</v>
       </c>
       <c r="L61" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M61" t="n">
-        <v>186.6666666666667</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="N61" t="n">
-        <v>1.225</v>
+        <v>2.260869565217391</v>
       </c>
       <c r="O61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="P61" t="n">
-        <v>186.6666666666667</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.225</v>
+        <v>2.260869565217391</v>
       </c>
       <c r="R61" t="n">
         <v>199.3694289811982</v>
       </c>
       <c r="S61" t="n">
-        <v>194.7379568035392</v>
+        <v>190.609444133645</v>
       </c>
       <c r="T61" t="n">
-        <v>0.1461059149062048</v>
+        <v>0.2084494288028756</v>
       </c>
       <c r="U61" t="n">
         <v>167.1297521794813</v>
@@ -5795,7 +5799,7 @@
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5819,59 +5823,59 @@
         <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G62" t="n">
-        <v>123.8814038245265</v>
+        <v>119.2277209283495</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7447802726545814</v>
+        <v>0.761352537839095</v>
       </c>
       <c r="I62" t="n">
         <v>51.86246745886869</v>
       </c>
       <c r="J62" t="n">
-        <v>130.9495021586091</v>
+        <v>133.5624336927553</v>
       </c>
       <c r="K62" t="n">
-        <v>2.035626480551362</v>
+        <v>2.994062352107012</v>
       </c>
       <c r="L62" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M62" t="n">
-        <v>176.3126304888907</v>
+        <v>179.0413583623338</v>
       </c>
       <c r="N62" t="n">
-        <v>20.65</v>
+        <v>37.16415571126796</v>
       </c>
       <c r="O62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="P62" t="n">
-        <v>176.3126304888907</v>
+        <v>179.1625326908875</v>
       </c>
       <c r="Q62" t="n">
-        <v>20.65</v>
+        <v>50.27871844864998</v>
       </c>
       <c r="R62" t="n">
         <v>188.4656733609786</v>
       </c>
       <c r="S62" t="n">
-        <v>116.5089827846871</v>
+        <v>122.3084475291242</v>
       </c>
       <c r="T62" t="n">
-        <v>1.003534982270476</v>
+        <v>2.05563889704695</v>
       </c>
       <c r="U62" t="n">
         <v>127.8730185036105</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -5880,11 +5884,11 @@
         </is>
       </c>
       <c r="X62" t="n">
-        <v>116.5089827846871</v>
+        <v>119.2277209283495</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=116.51% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=119.23% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -5908,52 +5912,52 @@
         <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G63" t="n">
-        <v>156.9330621411308</v>
+        <v>154.0090319989282</v>
       </c>
       <c r="H63" t="n">
-        <v>0.501227868029037</v>
+        <v>0.5195231974902645</v>
       </c>
       <c r="I63" t="n">
         <v>69.84803023883232</v>
       </c>
       <c r="J63" t="n">
-        <v>162.5474349276456</v>
+        <v>167.1118256355263</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4018922233822466</v>
+        <v>0.4428218214418847</v>
       </c>
       <c r="L63" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M63" t="n">
-        <v>177.6600458365164</v>
+        <v>180.1206671572637</v>
       </c>
       <c r="N63" t="n">
-        <v>8.503647849212859</v>
+        <v>12.15501876333826</v>
       </c>
       <c r="O63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="P63" t="n">
-        <v>177.6600458365164</v>
+        <v>180.3618638239061</v>
       </c>
       <c r="Q63" t="n">
-        <v>8.800000000000001</v>
+        <v>18.35260170399609</v>
       </c>
       <c r="R63" t="n">
         <v>186.3893216158546</v>
       </c>
       <c r="S63" t="n">
-        <v>134.567840476945</v>
+        <v>140.0878107146123</v>
       </c>
       <c r="T63" t="n">
-        <v>0.6279944860502141</v>
+        <v>1.139928270036557</v>
       </c>
       <c r="U63" t="n">
         <v>131.8859677830883</v>
@@ -5971,7 +5975,7 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5995,70 +5999,72 @@
         <v>2026</v>
       </c>
       <c r="E64" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F64" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G64" t="n">
-        <v>150.1672909984136</v>
+        <v>144.6640924290954</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6246504300677056</v>
+        <v>0.7123712842017973</v>
       </c>
       <c r="I64" t="n">
         <v>72.92360982323459</v>
       </c>
       <c r="J64" t="n">
-        <v>158.2336582834401</v>
+        <v>155.8241243354186</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5515223531598076</v>
+        <v>0.9337406050508241</v>
       </c>
       <c r="L64" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M64" t="n">
-        <v>177.0343773873185</v>
+        <v>179.6281987244426</v>
       </c>
       <c r="N64" t="n">
-        <v>12.45</v>
+        <v>22.62215745018642</v>
       </c>
       <c r="O64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="P64" t="n">
-        <v>177.0343773873185</v>
+        <v>179.7513301297856</v>
       </c>
       <c r="Q64" t="n">
-        <v>12.45</v>
+        <v>32</v>
       </c>
       <c r="R64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="S64" t="n">
-        <v>139.4880097887306</v>
+        <v>142.3844661408978</v>
       </c>
       <c r="T64" t="n">
-        <v>0.7096876609936263</v>
+        <v>1.466619050468889</v>
       </c>
       <c r="U64" t="n">
         <v>132.574641557417</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>144.6640924290954</v>
+      </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=144.66% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -6082,70 +6088,72 @@
         <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>164.2406054145438</v>
+        <v>157.2615659772668</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5031218849050085</v>
+        <v>0.6561727716521711</v>
       </c>
       <c r="I65" t="n">
         <v>124.1398173354868</v>
       </c>
       <c r="J65" t="n">
-        <v>181.0791972107662</v>
+        <v>171.3785789985182</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3753839700944796</v>
+        <v>0.559045196864532</v>
       </c>
       <c r="L65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="M65" t="n">
-        <v>190.5140813081989</v>
+        <v>190.7712059161261</v>
       </c>
       <c r="N65" t="n">
-        <v>18.05</v>
+        <v>28.28459385160271</v>
       </c>
       <c r="O65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="P65" t="n">
-        <v>190.5140813081989</v>
+        <v>190.8351421727835</v>
       </c>
       <c r="Q65" t="n">
-        <v>18.05</v>
+        <v>29.06521739130435</v>
       </c>
       <c r="R65" t="n">
         <v>191.9303948964172</v>
       </c>
       <c r="S65" t="n">
-        <v>161.9562297696662</v>
+        <v>162.49835435417</v>
       </c>
       <c r="T65" t="n">
-        <v>1.03790360753235</v>
+        <v>2.911749098649227</v>
       </c>
       <c r="U65" t="n">
         <v>113.9712651292745</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>157.2615659772668</v>
+      </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=157.26% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -6169,52 +6177,52 @@
         <v>2026</v>
       </c>
       <c r="E66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
-        <v>189.4012658429347</v>
+        <v>184.891199503253</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2692268827356448</v>
+        <v>0.3527404758689708</v>
       </c>
       <c r="I66" t="n">
         <v>146.9871894171194</v>
       </c>
       <c r="J66" t="n">
-        <v>186.671418728838</v>
+        <v>182.5534283094383</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2805501287685855</v>
+        <v>0.3899194867525623</v>
       </c>
       <c r="L66" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M66" t="n">
-        <v>192.9717586649551</v>
+        <v>192.1804112614516</v>
       </c>
       <c r="N66" t="n">
-        <v>9.300000000000001</v>
+        <v>12.91304347826087</v>
       </c>
       <c r="O66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="P66" t="n">
-        <v>192.9717586649551</v>
+        <v>192.1804112614516</v>
       </c>
       <c r="Q66" t="n">
-        <v>9.300000000000001</v>
+        <v>12.91304347826087</v>
       </c>
       <c r="R66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="S66" t="n">
-        <v>178.5915885387897</v>
+        <v>175.5600594590176</v>
       </c>
       <c r="T66" t="n">
-        <v>0.5632527591119588</v>
+        <v>1.343768581845118</v>
       </c>
       <c r="U66" t="n">
         <v>118.44057480835</v>
@@ -6232,7 +6240,7 @@
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6256,59 +6264,59 @@
         <v>2026</v>
       </c>
       <c r="E67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G67" t="n">
-        <v>192.1195028106798</v>
+        <v>190.1598108836026</v>
       </c>
       <c r="H67" t="n">
-        <v>0.3484548554492455</v>
+        <v>0.4585044062246966</v>
       </c>
       <c r="I67" t="n">
         <v>137.6516466078508</v>
       </c>
       <c r="J67" t="n">
-        <v>199.34423319269</v>
+        <v>198.5569003946447</v>
       </c>
       <c r="K67" t="n">
-        <v>0.3058159597885096</v>
+        <v>0.4636885009186891</v>
       </c>
       <c r="L67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="M67" t="n">
-        <v>194.0243902439024</v>
+        <v>193.6590588493686</v>
       </c>
       <c r="N67" t="n">
-        <v>9.65</v>
+        <v>13.1134702291736</v>
       </c>
       <c r="O67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="P67" t="n">
-        <v>194.0243902439024</v>
+        <v>194.3273435116722</v>
       </c>
       <c r="Q67" t="n">
-        <v>9.65</v>
+        <v>16.93478260869565</v>
       </c>
       <c r="R67" t="n">
         <v>191.2393501485975</v>
       </c>
       <c r="S67" t="n">
-        <v>183.7746216448583</v>
+        <v>182.6963314834599</v>
       </c>
       <c r="T67" t="n">
-        <v>0.7133704864658601</v>
+        <v>1.650403780856818</v>
       </c>
       <c r="U67" t="n">
         <v>116.630186356802</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -6319,7 +6327,7 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6351,7 @@
         <v>2026</v>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -6352,16 +6360,16 @@
         <v>199.988140539529</v>
       </c>
       <c r="H68" t="n">
-        <v>0.05827870637370154</v>
+        <v>0.05067713597713177</v>
       </c>
       <c r="I68" t="n">
         <v>183.5383709430125</v>
       </c>
       <c r="J68" t="n">
-        <v>199.7936632551253</v>
+        <v>199.8205767435873</v>
       </c>
       <c r="K68" t="n">
-        <v>0.06366529122400008</v>
+        <v>0.05766034586476899</v>
       </c>
       <c r="L68" t="n">
         <v>198.3312090033645</v>
@@ -6370,7 +6378,7 @@
         <v>200</v>
       </c>
       <c r="N68" t="n">
-        <v>4.904497894862807</v>
+        <v>6.351737299880702</v>
       </c>
       <c r="O68" t="n">
         <v>188.2784643365136</v>
@@ -6379,16 +6387,16 @@
         <v>200</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.45</v>
+        <v>6.826086956521739</v>
       </c>
       <c r="R68" t="n">
         <v>199.7672857698158</v>
       </c>
       <c r="S68" t="n">
-        <v>196.8488158046152</v>
+        <v>197.2598398301002</v>
       </c>
       <c r="T68" t="n">
-        <v>0.3092824996220025</v>
+        <v>0.58784095891447</v>
       </c>
       <c r="U68" t="n">
         <v>177.2448922419183</v>
@@ -6430,7 +6438,7 @@
         <v>2026</v>
       </c>
       <c r="E69" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -6439,16 +6447,16 @@
         <v>198.1317768745953</v>
       </c>
       <c r="H69" t="n">
-        <v>0.07715038600420325</v>
+        <v>0.06708729217756805</v>
       </c>
       <c r="I69" t="n">
         <v>171.5447439761989</v>
       </c>
       <c r="J69" t="n">
-        <v>199.4179556967436</v>
+        <v>199.4938745189075</v>
       </c>
       <c r="K69" t="n">
-        <v>0.07628203787767085</v>
+        <v>0.07028127604290697</v>
       </c>
       <c r="L69" t="n">
         <v>194.4182830751776</v>
@@ -6457,7 +6465,7 @@
         <v>200</v>
       </c>
       <c r="N69" t="n">
-        <v>2.525</v>
+        <v>3.108695652173913</v>
       </c>
       <c r="O69" t="n">
         <v>190.8574288418282</v>
@@ -6466,23 +6474,23 @@
         <v>200</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.525</v>
+        <v>3.108695652173913</v>
       </c>
       <c r="R69" t="n">
         <v>199.6130972886749</v>
       </c>
       <c r="S69" t="n">
-        <v>198.4122230437486</v>
+        <v>198.6193243858683</v>
       </c>
       <c r="T69" t="n">
-        <v>0.1830226391484761</v>
+        <v>0.2781863905030194</v>
       </c>
       <c r="U69" t="n">
         <v>185.6695408532579</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -6493,7 +6501,7 @@
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6525,7 @@
         <v>2026</v>
       </c>
       <c r="E70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -6526,7 +6534,7 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01690032095695999</v>
+        <v>0.01469593126692173</v>
       </c>
       <c r="I70" t="n">
         <v>188.453973372859</v>
@@ -6535,7 +6543,7 @@
         <v>200</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01607239648951918</v>
+        <v>0.01611177625948345</v>
       </c>
       <c r="L70" t="n">
         <v>198.9765474653765</v>
@@ -6544,7 +6552,7 @@
         <v>200</v>
       </c>
       <c r="N70" t="n">
-        <v>2.850376030036672</v>
+        <v>3.652500895684062</v>
       </c>
       <c r="O70" t="n">
         <v>192.937344462188</v>
@@ -6553,7 +6561,7 @@
         <v>200</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.075</v>
+        <v>3.847826086956522</v>
       </c>
       <c r="R70" t="n">
         <v>199.6974055100667</v>
@@ -6562,14 +6570,14 @@
         <v>200</v>
       </c>
       <c r="T70" t="n">
-        <v>0.1600966959150359</v>
+        <v>0.2883720663686506</v>
       </c>
       <c r="U70" t="n">
         <v>184.4638384017739</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -6580,7 +6588,7 @@
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6604,52 +6612,52 @@
         <v>2026</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F71" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="G71" t="n">
-        <v>59.39563859697882</v>
+        <v>60.84223256271035</v>
       </c>
       <c r="H71" t="n">
-        <v>3.012223041556701</v>
+        <v>3.078949151164985</v>
       </c>
       <c r="I71" t="n">
         <v>143.4057585362926</v>
       </c>
       <c r="J71" t="n">
-        <v>182.3481421699075</v>
+        <v>175.1755208750977</v>
       </c>
       <c r="K71" t="n">
-        <v>4.480961701689276</v>
+        <v>4.541592070852817</v>
       </c>
       <c r="L71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="M71" t="n">
-        <v>73.55375808142874</v>
+        <v>69.78785307192437</v>
       </c>
       <c r="N71" t="n">
-        <v>4.341667333711549</v>
+        <v>4.214327809702388</v>
       </c>
       <c r="O71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="P71" t="n">
-        <v>188.1847498372014</v>
+        <v>189.7258694236534</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.574070117727795</v>
+        <v>4.803539232806779</v>
       </c>
       <c r="R71" t="n">
         <v>185.267595267154</v>
       </c>
       <c r="S71" t="n">
-        <v>54.83436778227493</v>
+        <v>53.34049861321677</v>
       </c>
       <c r="T71" t="n">
-        <v>4.827419988379988</v>
+        <v>4.599205857701338</v>
       </c>
       <c r="U71" t="n">
         <v>93.16202342284906</v>
@@ -6665,11 +6673,11 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>54.83436778227493</v>
+        <v>53.34049861321677</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=54.83% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=53.34% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -6693,52 +6701,52 @@
         <v>2026</v>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F72" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G72" t="n">
-        <v>91.56196775349026</v>
+        <v>88.11716214288521</v>
       </c>
       <c r="H72" t="n">
-        <v>1.663026533958095</v>
+        <v>1.648898475053217</v>
       </c>
       <c r="I72" t="n">
         <v>151.0433307550491</v>
       </c>
       <c r="J72" t="n">
-        <v>96.85877469435373</v>
+        <v>89.97205653125231</v>
       </c>
       <c r="K72" t="n">
-        <v>1.381957484185444</v>
+        <v>1.347222829498326</v>
       </c>
       <c r="L72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="M72" t="n">
-        <v>93.27621259369054</v>
+        <v>90.61334304210067</v>
       </c>
       <c r="N72" t="n">
-        <v>2.276963503510039</v>
+        <v>2.297549201132918</v>
       </c>
       <c r="O72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="P72" t="n">
-        <v>160.3965804330911</v>
+        <v>166.6497519436556</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.933036859339645</v>
+        <v>2.072205964643169</v>
       </c>
       <c r="R72" t="n">
         <v>161.2927483340683</v>
       </c>
       <c r="S72" t="n">
-        <v>86.32696783685466</v>
+        <v>82.09163071455964</v>
       </c>
       <c r="T72" t="n">
-        <v>2.104661029299291</v>
+        <v>2.10242440504272</v>
       </c>
       <c r="U72" t="n">
         <v>104.036396201453</v>
@@ -6754,11 +6762,11 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>86.32696783685466</v>
+        <v>82.09163071455964</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=86.33% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=82.09% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -6782,52 +6790,52 @@
         <v>2026</v>
       </c>
       <c r="E73" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F73" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G73" t="n">
-        <v>68.94883353215404</v>
+        <v>71.14000991959982</v>
       </c>
       <c r="H73" t="n">
-        <v>1.91737407432194</v>
+        <v>1.945619104365378</v>
       </c>
       <c r="I73" t="n">
         <v>148.5993365374143</v>
       </c>
       <c r="J73" t="n">
-        <v>169.220217719738</v>
+        <v>158.7452752782929</v>
       </c>
       <c r="K73" t="n">
-        <v>2.451722676942217</v>
+        <v>2.402732410976158</v>
       </c>
       <c r="L73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="M73" t="n">
-        <v>95.65853798886769</v>
+        <v>90.14976892230113</v>
       </c>
       <c r="N73" t="n">
-        <v>1.985706949234009</v>
+        <v>2.027271146359651</v>
       </c>
       <c r="O73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="P73" t="n">
-        <v>166.6061669930662</v>
+        <v>170.9618843417967</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.359171819523877</v>
+        <v>2.486236364803371</v>
       </c>
       <c r="R73" t="n">
         <v>173.6314937555617</v>
       </c>
       <c r="S73" t="n">
-        <v>58.6602811276452</v>
+        <v>57.28942679324784</v>
       </c>
       <c r="T73" t="n">
-        <v>2.036843857846089</v>
+        <v>2.010197168566853</v>
       </c>
       <c r="U73" t="n">
         <v>104.3951484726403</v>
@@ -6843,11 +6851,11 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>58.6602811276452</v>
+        <v>57.28942679324784</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=58.66% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=57.29% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -6871,70 +6879,72 @@
         <v>2026</v>
       </c>
       <c r="E74" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G74" t="n">
-        <v>170.145993889533</v>
+        <v>172.1836151238099</v>
       </c>
       <c r="H74" t="n">
-        <v>3.149849585366976</v>
+        <v>5.008689584156971</v>
       </c>
       <c r="I74" t="n">
         <v>148.9425712788151</v>
       </c>
       <c r="J74" t="n">
-        <v>187.6783600961669</v>
+        <v>188.349608968092</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4214485667936149</v>
+        <v>0.4522304879555368</v>
       </c>
       <c r="L74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="M74" t="n">
-        <v>190.1625663378899</v>
+        <v>190.8244029995426</v>
       </c>
       <c r="N74" t="n">
-        <v>28.85799004315229</v>
+        <v>33.02868699404547</v>
       </c>
       <c r="O74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="P74" t="n">
-        <v>190.1625663378899</v>
+        <v>190.8244029995426</v>
       </c>
       <c r="Q74" t="n">
-        <v>29.1</v>
+        <v>33.23913043478261</v>
       </c>
       <c r="R74" t="n">
         <v>193.1141809259393</v>
       </c>
       <c r="S74" t="n">
-        <v>160.7383934032291</v>
+        <v>160.1021769444664</v>
       </c>
       <c r="T74" t="n">
-        <v>0.7997630920275045</v>
+        <v>1.284833000992501</v>
       </c>
       <c r="U74" t="n">
         <v>113.155914904339</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X74" t="n">
+        <v>160.1021769444664</v>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=160.10% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -6958,52 +6968,52 @@
         <v>2026</v>
       </c>
       <c r="E75" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>169.8418149992723</v>
+        <v>170.9138701345115</v>
       </c>
       <c r="H75" t="n">
-        <v>1.321079360199853</v>
+        <v>1.78909214966093</v>
       </c>
       <c r="I75" t="n">
         <v>157.2380343536269</v>
       </c>
       <c r="J75" t="n">
-        <v>196.7852741791903</v>
+        <v>197.1918545450863</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2880628842185335</v>
+        <v>0.2939822974793316</v>
       </c>
       <c r="L75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="M75" t="n">
-        <v>189.5701357466064</v>
+        <v>190.2742771873689</v>
       </c>
       <c r="N75" t="n">
-        <v>12.64906613744525</v>
+        <v>14.34588343629438</v>
       </c>
       <c r="O75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="P75" t="n">
-        <v>189.5701357466064</v>
+        <v>190.2742771873689</v>
       </c>
       <c r="Q75" t="n">
-        <v>12.95</v>
+        <v>14.60869565217391</v>
       </c>
       <c r="R75" t="n">
         <v>193.2892416279341</v>
       </c>
       <c r="S75" t="n">
-        <v>168.1419358091225</v>
+        <v>165.936670532348</v>
       </c>
       <c r="T75" t="n">
-        <v>0.5189411821855205</v>
+        <v>0.6901346666078548</v>
       </c>
       <c r="U75" t="n">
         <v>110.9447640026735</v>
@@ -7021,7 +7031,7 @@
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7045,52 +7055,52 @@
         <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>176.9036149455106</v>
+        <v>178.354973633617</v>
       </c>
       <c r="H76" t="n">
-        <v>1.878543571681752</v>
+        <v>2.928783987660015</v>
       </c>
       <c r="I76" t="n">
         <v>154.9841830576604</v>
       </c>
       <c r="J76" t="n">
-        <v>195.4350991723647</v>
+        <v>195.8787915029281</v>
       </c>
       <c r="K76" t="n">
-        <v>0.1957219736138898</v>
+        <v>0.2138249000719048</v>
       </c>
       <c r="L76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="M76" t="n">
-        <v>189.7142857142857</v>
+        <v>190.4663648805137</v>
       </c>
       <c r="N76" t="n">
-        <v>15.31640743688422</v>
+        <v>17.67981181273928</v>
       </c>
       <c r="O76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="P76" t="n">
-        <v>189.7142857142857</v>
+        <v>190.4663648805137</v>
       </c>
       <c r="Q76" t="n">
-        <v>16.375</v>
+        <v>18.82608695652174</v>
       </c>
       <c r="R76" t="n">
         <v>192.8448970866968</v>
       </c>
       <c r="S76" t="n">
-        <v>175.2582679801752</v>
+        <v>174.6501292534513</v>
       </c>
       <c r="T76" t="n">
-        <v>0.5172447171484865</v>
+        <v>0.7673414095887637</v>
       </c>
       <c r="U76" t="n">
         <v>118.0223455785753</v>
@@ -7108,7 +7118,7 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7132,52 +7142,52 @@
         <v>2026</v>
       </c>
       <c r="E77" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
-        <v>374</v>
+        <v>405</v>
       </c>
       <c r="G77" t="n">
-        <v>48.13996557180829</v>
+        <v>47.7742567812519</v>
       </c>
       <c r="H77" t="n">
-        <v>6.80594682904123</v>
+        <v>6.516607002343314</v>
       </c>
       <c r="I77" t="n">
         <v>77.76772218573589</v>
       </c>
       <c r="J77" t="n">
-        <v>35.7354676737036</v>
+        <v>40.82434585879298</v>
       </c>
       <c r="K77" t="n">
-        <v>6.504485339100792</v>
+        <v>7.055082554337187</v>
       </c>
       <c r="L77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="M77" t="n">
-        <v>46.55889078776278</v>
+        <v>50.96798626368885</v>
       </c>
       <c r="N77" t="n">
-        <v>10.6</v>
+        <v>10.93478260869565</v>
       </c>
       <c r="O77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="P77" t="n">
-        <v>46.55889078776278</v>
+        <v>50.96798626368885</v>
       </c>
       <c r="Q77" t="n">
-        <v>10.6</v>
+        <v>10.93478260869565</v>
       </c>
       <c r="R77" t="n">
         <v>138.4032392925817</v>
       </c>
       <c r="S77" t="n">
-        <v>26.75039048553721</v>
+        <v>29.91163125949122</v>
       </c>
       <c r="T77" t="n">
-        <v>5.892245533829699</v>
+        <v>5.863774255073022</v>
       </c>
       <c r="U77" t="n">
         <v>118.3894561520081</v>
@@ -7193,11 +7203,11 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>26.75039048553721</v>
+        <v>29.91163125949122</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=26.75% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=29.91% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7221,52 +7231,52 @@
         <v>2026</v>
       </c>
       <c r="E78" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F78" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="G78" t="n">
-        <v>49.87175554871417</v>
+        <v>50.32574451465677</v>
       </c>
       <c r="H78" t="n">
-        <v>3.633385459905116</v>
+        <v>3.521806610383386</v>
       </c>
       <c r="I78" t="n">
         <v>103.5437500854655</v>
       </c>
       <c r="J78" t="n">
-        <v>48.93253207042698</v>
+        <v>50.96377117821061</v>
       </c>
       <c r="K78" t="n">
-        <v>3.939060829281599</v>
+        <v>3.962567182278121</v>
       </c>
       <c r="L78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="M78" t="n">
-        <v>130.1702699785665</v>
+        <v>122.1481532087901</v>
       </c>
       <c r="N78" t="n">
-        <v>6.33810657300055</v>
+        <v>5.938200660697792</v>
       </c>
       <c r="O78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="P78" t="n">
-        <v>49.02444880110601</v>
+        <v>49.64483641563533</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.406726927097479</v>
+        <v>4.286161776429979</v>
       </c>
       <c r="R78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="S78" t="n">
-        <v>25.48398265391347</v>
+        <v>28.67701772125466</v>
       </c>
       <c r="T78" t="n">
-        <v>2.85796442450722</v>
+        <v>2.888506578911857</v>
       </c>
       <c r="U78" t="n">
         <v>124.390269119479</v>
@@ -7282,11 +7292,11 @@
         </is>
       </c>
       <c r="X78" t="n">
-        <v>25.48398265391347</v>
+        <v>28.67701772125466</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=25.48% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=28.68% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7310,52 +7320,52 @@
         <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F79" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="G79" t="n">
-        <v>54.13640532746658</v>
+        <v>52.24408238532585</v>
       </c>
       <c r="H79" t="n">
-        <v>3.83883329606333</v>
+        <v>3.593158205875207</v>
       </c>
       <c r="I79" t="n">
         <v>102.5016657415887</v>
       </c>
       <c r="J79" t="n">
-        <v>39.07835373096954</v>
+        <v>46.03484485015787</v>
       </c>
       <c r="K79" t="n">
-        <v>3.54430598501511</v>
+        <v>4.07569851818366</v>
       </c>
       <c r="L79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="M79" t="n">
-        <v>51.59055968974086</v>
+        <v>54.67502084822188</v>
       </c>
       <c r="N79" t="n">
-        <v>6.4</v>
+        <v>6.521739130434782</v>
       </c>
       <c r="O79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="P79" t="n">
-        <v>51.59055968974086</v>
+        <v>54.67502084822188</v>
       </c>
       <c r="Q79" t="n">
-        <v>6.4</v>
+        <v>6.521739130434782</v>
       </c>
       <c r="R79" t="n">
         <v>148.0195847609927</v>
       </c>
       <c r="S79" t="n">
-        <v>28.42761267530013</v>
+        <v>31.6420999173577</v>
       </c>
       <c r="T79" t="n">
-        <v>3.181795794451428</v>
+        <v>3.111168359319405</v>
       </c>
       <c r="U79" t="n">
         <v>120.3982350383182</v>
@@ -7371,11 +7381,11 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>28.42761267530013</v>
+        <v>31.6420999173577</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=28.43% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=31.64% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7399,52 +7409,52 @@
         <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F80" t="n">
-        <v>604</v>
+        <v>747</v>
       </c>
       <c r="G80" t="n">
-        <v>143.4940966234259</v>
+        <v>145.0705658071386</v>
       </c>
       <c r="H80" t="n">
-        <v>26.07980948970724</v>
+        <v>28.12110535809797</v>
       </c>
       <c r="I80" t="n">
         <v>180.9937478063148</v>
       </c>
       <c r="J80" t="n">
-        <v>148.1310218281596</v>
+        <v>151.809715025411</v>
       </c>
       <c r="K80" t="n">
-        <v>24.4944853507629</v>
+        <v>27.11125750867945</v>
       </c>
       <c r="L80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="M80" t="n">
-        <v>127.0263245736096</v>
+        <v>120.9418419406456</v>
       </c>
       <c r="N80" t="n">
-        <v>20.13112373352051</v>
+        <v>20.96910410342009</v>
       </c>
       <c r="O80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="P80" t="n">
-        <v>152.7575072128086</v>
+        <v>158.7876267559903</v>
       </c>
       <c r="Q80" t="n">
-        <v>27.14206305431544</v>
+        <v>29.80223370262615</v>
       </c>
       <c r="R80" t="n">
         <v>172.7461511452186</v>
       </c>
       <c r="S80" t="n">
-        <v>57.58138393443687</v>
+        <v>55.57865689849766</v>
       </c>
       <c r="T80" t="n">
-        <v>31.8213527961697</v>
+        <v>29.84619604790962</v>
       </c>
       <c r="U80" t="n">
         <v>175.912448276349</v>
@@ -7460,11 +7470,11 @@
         </is>
       </c>
       <c r="X80" t="n">
-        <v>57.58138393443687</v>
+        <v>55.57865689849766</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=57.58% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=55.58% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7488,52 +7498,52 @@
         <v>2026</v>
       </c>
       <c r="E81" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F81" t="n">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="G81" t="n">
-        <v>129.5473408072873</v>
+        <v>132.4867083561084</v>
       </c>
       <c r="H81" t="n">
-        <v>11.62075399902387</v>
+        <v>12.62685812777978</v>
       </c>
       <c r="I81" t="n">
         <v>185.5191244575439</v>
       </c>
       <c r="J81" t="n">
-        <v>131.8378164529767</v>
+        <v>118.7066549978501</v>
       </c>
       <c r="K81" t="n">
-        <v>8.653196714647356</v>
+        <v>8.635753424982873</v>
       </c>
       <c r="L81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="M81" t="n">
-        <v>175.2778190194465</v>
+        <v>163.9232010442408</v>
       </c>
       <c r="N81" t="n">
-        <v>12.94371314048767</v>
+        <v>13.06296597356382</v>
       </c>
       <c r="O81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="P81" t="n">
-        <v>140.0036770211532</v>
+        <v>145.6926430037564</v>
       </c>
       <c r="Q81" t="n">
-        <v>12.19623702618386</v>
+        <v>13.39475915977169</v>
       </c>
       <c r="R81" t="n">
         <v>163.1536185700502</v>
       </c>
       <c r="S81" t="n">
-        <v>55.4369281065792</v>
+        <v>56.08703951311051</v>
       </c>
       <c r="T81" t="n">
-        <v>8.566789406263265</v>
+        <v>8.829026597258693</v>
       </c>
       <c r="U81" t="n">
         <v>172.1596497720207</v>
@@ -7549,11 +7559,11 @@
         </is>
       </c>
       <c r="X81" t="n">
-        <v>55.4369281065792</v>
+        <v>56.08703951311051</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=55.44% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=56.09% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7577,52 +7587,52 @@
         <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
-        <v>321</v>
+        <v>397</v>
       </c>
       <c r="G82" t="n">
-        <v>126.3886823142627</v>
+        <v>129.9289044477184</v>
       </c>
       <c r="H82" t="n">
-        <v>13.28730403092784</v>
+        <v>14.44120356230335</v>
       </c>
       <c r="I82" t="n">
         <v>186.2973802760101</v>
       </c>
       <c r="J82" t="n">
-        <v>145.6424824373007</v>
+        <v>146.7946985204721</v>
       </c>
       <c r="K82" t="n">
-        <v>13.57082597269097</v>
+        <v>14.69457114501941</v>
       </c>
       <c r="L82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="M82" t="n">
-        <v>160.6252306293776</v>
+        <v>157.7438414402413</v>
       </c>
       <c r="N82" t="n">
-        <v>12.78029097914696</v>
+        <v>13.7715504726638</v>
       </c>
       <c r="O82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="P82" t="n">
-        <v>142.2704254070456</v>
+        <v>148.8478716529916</v>
       </c>
       <c r="Q82" t="n">
-        <v>14.23154326578053</v>
+        <v>15.62010462447254</v>
       </c>
       <c r="R82" t="n">
         <v>166.6060177059153</v>
       </c>
       <c r="S82" t="n">
-        <v>41.14041794173689</v>
+        <v>37.55860291656742</v>
       </c>
       <c r="T82" t="n">
-        <v>10.06700724468474</v>
+        <v>9.225247055395791</v>
       </c>
       <c r="U82" t="n">
         <v>176.1888335684919</v>
@@ -7638,11 +7648,11 @@
         </is>
       </c>
       <c r="X82" t="n">
-        <v>41.14041794173689</v>
+        <v>37.55860291656742</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=41.14% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=37.56% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7666,52 +7676,52 @@
         <v>2026</v>
       </c>
       <c r="E83" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F83" t="n">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="G83" t="n">
-        <v>34.85754703895741</v>
+        <v>35.82254323442039</v>
       </c>
       <c r="H83" t="n">
-        <v>6.099900701419037</v>
+        <v>5.694070255825614</v>
       </c>
       <c r="I83" t="n">
         <v>88.04980557911651</v>
       </c>
       <c r="J83" t="n">
-        <v>46.55927137251179</v>
+        <v>47.2904668050621</v>
       </c>
       <c r="K83" t="n">
-        <v>8.365042273621768</v>
+        <v>7.732049972518708</v>
       </c>
       <c r="L83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="M83" t="n">
-        <v>101.9346113584368</v>
+        <v>100.7175260153327</v>
       </c>
       <c r="N83" t="n">
-        <v>37.32667374384968</v>
+        <v>34.58841195117363</v>
       </c>
       <c r="O83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="P83" t="n">
-        <v>81.22115794251302</v>
+        <v>85.29903085503335</v>
       </c>
       <c r="Q83" t="n">
-        <v>28.91259478594988</v>
+        <v>26.30615167954335</v>
       </c>
       <c r="R83" t="n">
         <v>103.1343264142703</v>
       </c>
       <c r="S83" t="n">
-        <v>49.58750519153977</v>
+        <v>53.63666954731949</v>
       </c>
       <c r="T83" t="n">
-        <v>11.84574626389659</v>
+        <v>11.83305544347967</v>
       </c>
       <c r="U83" t="n">
         <v>103.3034448942146</v>
@@ -7727,11 +7737,11 @@
         </is>
       </c>
       <c r="X83" t="n">
-        <v>34.85754703895741</v>
+        <v>35.82254323442039</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=34.86% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=35.82% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7755,52 +7765,52 @@
         <v>2026</v>
       </c>
       <c r="E84" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F84" t="n">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="G84" t="n">
-        <v>31.58514004799532</v>
+        <v>33.73703538560333</v>
       </c>
       <c r="H84" t="n">
-        <v>2.498959406337137</v>
+        <v>2.409518881690106</v>
       </c>
       <c r="I84" t="n">
         <v>100.4914466151705</v>
       </c>
       <c r="J84" t="n">
-        <v>47.98794929851191</v>
+        <v>47.81622092646597</v>
       </c>
       <c r="K84" t="n">
-        <v>3.654283444185853</v>
+        <v>3.38359716330306</v>
       </c>
       <c r="L84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="M84" t="n">
-        <v>73.96001404024166</v>
+        <v>75.43474935161561</v>
       </c>
       <c r="N84" t="n">
-        <v>8.840772408548593</v>
+        <v>8.546227556774392</v>
       </c>
       <c r="O84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="P84" t="n">
-        <v>84.02527497638295</v>
+        <v>84.19084285065338</v>
       </c>
       <c r="Q84" t="n">
-        <v>13.36201420137435</v>
+        <v>12.11375428791303</v>
       </c>
       <c r="R84" t="n">
         <v>98.74789164115032</v>
       </c>
       <c r="S84" t="n">
-        <v>48.65716653790398</v>
+        <v>53.52479167646013</v>
       </c>
       <c r="T84" t="n">
-        <v>4.936587764206472</v>
+        <v>5.115119524303525</v>
       </c>
       <c r="U84" t="n">
         <v>110.607240444147</v>
@@ -7816,11 +7826,11 @@
         </is>
       </c>
       <c r="X84" t="n">
-        <v>31.58514004799532</v>
+        <v>33.73703538560333</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=31.59% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=33.74% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7844,59 +7854,59 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F85" t="n">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="G85" t="n">
-        <v>45.15610031900901</v>
+        <v>45.17291284242295</v>
       </c>
       <c r="H85" t="n">
-        <v>4.222544006128435</v>
+        <v>3.888797644604952</v>
       </c>
       <c r="I85" t="n">
         <v>109.9471447641292</v>
       </c>
       <c r="J85" t="n">
-        <v>56.13119419402656</v>
+        <v>52.94713432947248</v>
       </c>
       <c r="K85" t="n">
-        <v>4.843195688430205</v>
+        <v>4.410926643149813</v>
       </c>
       <c r="L85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="M85" t="n">
-        <v>97.24702211580134</v>
+        <v>95.14488454484602</v>
       </c>
       <c r="N85" t="n">
-        <v>18.19708375199444</v>
+        <v>16.82355108869082</v>
       </c>
       <c r="O85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="P85" t="n">
-        <v>88.21496725218614</v>
+        <v>92.95972573699466</v>
       </c>
       <c r="Q85" t="n">
-        <v>17.25590217879476</v>
+        <v>15.73936784729693</v>
       </c>
       <c r="R85" t="n">
         <v>106.9882513320439</v>
       </c>
       <c r="S85" t="n">
-        <v>40.36683712377915</v>
+        <v>44.59654253377675</v>
       </c>
       <c r="T85" t="n">
-        <v>4.437200514899401</v>
+        <v>4.491232479349994</v>
       </c>
       <c r="U85" t="n">
         <v>107.8756984639591</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -7905,11 +7915,11 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>40.36683712377915</v>
+        <v>45.17291284242295</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=40.37% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=45.17% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -7933,52 +7943,52 @@
         <v>2026</v>
       </c>
       <c r="E86" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F86" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G86" t="n">
-        <v>111.6548587721165</v>
+        <v>116.1258789295296</v>
       </c>
       <c r="H86" t="n">
-        <v>3.143938514500572</v>
+        <v>3.687717971647376</v>
       </c>
       <c r="I86" t="n">
         <v>160.3842205944857</v>
       </c>
       <c r="J86" t="n">
-        <v>123.2643907319376</v>
+        <v>128.3126990226881</v>
       </c>
       <c r="K86" t="n">
-        <v>1.613915950770248</v>
+        <v>1.586542376572479</v>
       </c>
       <c r="L86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="M86" t="n">
-        <v>135.0075018387036</v>
+        <v>141.5407491610016</v>
       </c>
       <c r="N86" t="n">
-        <v>2.191859988868237</v>
+        <v>2.642830396475999</v>
       </c>
       <c r="O86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="P86" t="n">
-        <v>172.0972454612955</v>
+        <v>173.1011636375044</v>
       </c>
       <c r="Q86" t="n">
-        <v>22.275</v>
+        <v>22.34782608695652</v>
       </c>
       <c r="R86" t="n">
         <v>188.4995472315167</v>
       </c>
       <c r="S86" t="n">
-        <v>76.7529481383731</v>
+        <v>81.8534709765423</v>
       </c>
       <c r="T86" t="n">
-        <v>0.6764592464114857</v>
+        <v>0.841383742441259</v>
       </c>
       <c r="U86" t="n">
         <v>113.2748521774272</v>
@@ -7994,11 +8004,11 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>76.7529481383731</v>
+        <v>81.8534709765423</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=76.75% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=81.85% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8022,52 +8032,52 @@
         <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G87" t="n">
-        <v>117.5276954996459</v>
+        <v>120.7737723997747</v>
       </c>
       <c r="H87" t="n">
-        <v>1.216379534714496</v>
+        <v>1.311565685642731</v>
       </c>
       <c r="I87" t="n">
         <v>171.410316416684</v>
       </c>
       <c r="J87" t="n">
-        <v>146.3822060454345</v>
+        <v>150.0373242641209</v>
       </c>
       <c r="K87" t="n">
-        <v>0.9404386721636527</v>
+        <v>0.8977096382759049</v>
       </c>
       <c r="L87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="M87" t="n">
-        <v>164.1200530368887</v>
+        <v>166.3155740693442</v>
       </c>
       <c r="N87" t="n">
-        <v>9.5</v>
+        <v>9.608695652173912</v>
       </c>
       <c r="O87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="P87" t="n">
-        <v>164.1200530368887</v>
+        <v>166.3155740693442</v>
       </c>
       <c r="Q87" t="n">
-        <v>9.5</v>
+        <v>9.608695652173912</v>
       </c>
       <c r="R87" t="n">
         <v>191.241827101395</v>
       </c>
       <c r="S87" t="n">
-        <v>108.6439639594461</v>
+        <v>113.4080778222351</v>
       </c>
       <c r="T87" t="n">
-        <v>0.4485334189074034</v>
+        <v>0.5430723172151088</v>
       </c>
       <c r="U87" t="n">
         <v>108.9238350712686</v>
@@ -8083,11 +8093,11 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>108.6439639594461</v>
+        <v>113.4080778222351</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=108.64% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=113.41% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8111,52 +8121,52 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F88" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G88" t="n">
-        <v>135.2120623641964</v>
+        <v>134.5501681717121</v>
       </c>
       <c r="H88" t="n">
-        <v>1.812539916426184</v>
+        <v>1.994443549360311</v>
       </c>
       <c r="I88" t="n">
         <v>169.0038464611843</v>
       </c>
       <c r="J88" t="n">
-        <v>174.6712924009235</v>
+        <v>177.9232806527804</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9501939325037349</v>
+        <v>0.9566053945677125</v>
       </c>
       <c r="L88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="M88" t="n">
-        <v>174.7089229247851</v>
+        <v>169.0174741238627</v>
       </c>
       <c r="N88" t="n">
-        <v>2.017072343826294</v>
+        <v>2.139778100925943</v>
       </c>
       <c r="O88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="P88" t="n">
-        <v>181.694671011211</v>
+        <v>181.2562356619226</v>
       </c>
       <c r="Q88" t="n">
-        <v>13.275</v>
+        <v>13.17391304347826</v>
       </c>
       <c r="R88" t="n">
         <v>190.1751472740156</v>
       </c>
       <c r="S88" t="n">
-        <v>122.0177376594243</v>
+        <v>119.265709752752</v>
       </c>
       <c r="T88" t="n">
-        <v>0.5053271539442487</v>
+        <v>0.590183809542804</v>
       </c>
       <c r="U88" t="n">
         <v>121.3094122928426</v>
@@ -8172,11 +8182,11 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>122.0177376594243</v>
+        <v>119.265709752752</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=122.02% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=119.27% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8210,7 @@
         <v>2026</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -8209,7 +8219,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1029068012743253</v>
+        <v>0.1034044395744402</v>
       </c>
       <c r="I89" t="n">
         <v>200</v>
@@ -8218,7 +8228,7 @@
         <v>200</v>
       </c>
       <c r="K89" t="n">
-        <v>0.007222974619452209</v>
+        <v>0.007181157493568859</v>
       </c>
       <c r="L89" t="n">
         <v>200</v>
@@ -8241,7 +8251,7 @@
         <v>200</v>
       </c>
       <c r="T89" t="n">
-        <v>7.21227621483376</v>
+        <v>7.212276214833761</v>
       </c>
       <c r="U89" t="n">
         <v>200</v>
@@ -8283,7 +8293,7 @@
         <v>2026</v>
       </c>
       <c r="E90" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -8292,7 +8302,7 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09043378427001174</v>
+        <v>0.09086107718308541</v>
       </c>
       <c r="I90" t="n">
         <v>200</v>
@@ -8301,7 +8311,7 @@
         <v>200</v>
       </c>
       <c r="K90" t="n">
-        <v>0.00336885562718009</v>
+        <v>0.003364990963457704</v>
       </c>
       <c r="L90" t="n">
         <v>200</v>
@@ -8366,7 +8376,7 @@
         <v>2026</v>
       </c>
       <c r="E91" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8375,7 +8385,7 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09289234583735555</v>
+        <v>0.09331921028752266</v>
       </c>
       <c r="I91" t="n">
         <v>200</v>
@@ -8384,7 +8394,7 @@
         <v>200</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0136562216612037</v>
+        <v>0.0136128956536169</v>
       </c>
       <c r="L91" t="n">
         <v>200</v>
@@ -8407,7 +8417,7 @@
         <v>200</v>
       </c>
       <c r="T91" t="n">
-        <v>3.252934671825231e-17</v>
+        <v>2.828638845065418e-17</v>
       </c>
       <c r="U91" t="n">
         <v>200</v>
@@ -8449,52 +8459,52 @@
         <v>2026</v>
       </c>
       <c r="E92" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F92" t="n">
-        <v>313</v>
+        <v>385</v>
       </c>
       <c r="G92" t="n">
-        <v>50.94360508394109</v>
+        <v>50.58915032524707</v>
       </c>
       <c r="H92" t="n">
-        <v>7.445236591551317</v>
+        <v>7.806418729797821</v>
       </c>
       <c r="I92" t="n">
         <v>49.15109590531281</v>
       </c>
       <c r="J92" t="n">
-        <v>53.47394331476245</v>
+        <v>53.65888694735421</v>
       </c>
       <c r="K92" t="n">
-        <v>7.683758525707208</v>
+        <v>8.187580257720475</v>
       </c>
       <c r="L92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="M92" t="n">
-        <v>147.2305093707955</v>
+        <v>146.3331867260178</v>
       </c>
       <c r="N92" t="n">
-        <v>89.88391578324411</v>
+        <v>92.65748173165527</v>
       </c>
       <c r="O92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="P92" t="n">
-        <v>105.1104064577516</v>
+        <v>96.80706086275286</v>
       </c>
       <c r="Q92" t="n">
-        <v>38.44656124176299</v>
+        <v>34.78598795298529</v>
       </c>
       <c r="R92" t="n">
         <v>92.01416331532587</v>
       </c>
       <c r="S92" t="n">
-        <v>35.73768986318822</v>
+        <v>36.56210345867902</v>
       </c>
       <c r="T92" t="n">
-        <v>4.82728776594493</v>
+        <v>5.468270849612063</v>
       </c>
       <c r="U92" t="n">
         <v>95.83480509856771</v>
@@ -8510,11 +8520,11 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>35.73768986318822</v>
+        <v>36.56210345867902</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=35.74% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=36.56% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8538,52 +8548,52 @@
         <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F93" t="n">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="G93" t="n">
-        <v>48.32233224272152</v>
+        <v>46.76699698834544</v>
       </c>
       <c r="H93" t="n">
-        <v>3.431324012122839</v>
+        <v>3.47279107812409</v>
       </c>
       <c r="I93" t="n">
         <v>60.93105560683724</v>
       </c>
       <c r="J93" t="n">
-        <v>58.08717966558936</v>
+        <v>55.8655753410899</v>
       </c>
       <c r="K93" t="n">
-        <v>4.805245515527159</v>
+        <v>4.805141230617503</v>
       </c>
       <c r="L93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="M93" t="n">
-        <v>141.5101871367132</v>
+        <v>141.0048742728754</v>
       </c>
       <c r="N93" t="n">
-        <v>40.03434849539031</v>
+        <v>41.14593888710504</v>
       </c>
       <c r="O93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="P93" t="n">
-        <v>110.5071469160868</v>
+        <v>103.7751115518001</v>
       </c>
       <c r="Q93" t="n">
-        <v>20.23408918824621</v>
+        <v>18.6749435732643</v>
       </c>
       <c r="R93" t="n">
         <v>96.01849856237216</v>
       </c>
       <c r="S93" t="n">
-        <v>37.36511806436712</v>
+        <v>36.12898636730212</v>
       </c>
       <c r="T93" t="n">
-        <v>2.297978956289589</v>
+        <v>2.351952779066206</v>
       </c>
       <c r="U93" t="n">
         <v>99.35850993844542</v>
@@ -8599,11 +8609,11 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>37.36511806436712</v>
+        <v>36.12898636730212</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=37.37% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=36.13% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8627,52 +8637,52 @@
         <v>2026</v>
       </c>
       <c r="E94" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F94" t="n">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="G94" t="n">
-        <v>54.77044594910456</v>
+        <v>53.92068970347205</v>
       </c>
       <c r="H94" t="n">
-        <v>4.102986916830831</v>
+        <v>4.303053183034618</v>
       </c>
       <c r="I94" t="n">
         <v>64.07712599234655</v>
       </c>
       <c r="J94" t="n">
-        <v>51.59798605665487</v>
+        <v>57.27144253283743</v>
       </c>
       <c r="K94" t="n">
-        <v>3.673017500525156</v>
+        <v>4.389300741472915</v>
       </c>
       <c r="L94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="M94" t="n">
-        <v>148.6854236670783</v>
+        <v>146.3738991083444</v>
       </c>
       <c r="N94" t="n">
-        <v>45.0197162962926</v>
+        <v>45.52523307304197</v>
       </c>
       <c r="O94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="P94" t="n">
-        <v>110.6095095898828</v>
+        <v>103.6028181092246</v>
       </c>
       <c r="Q94" t="n">
-        <v>21.77462019881609</v>
+        <v>20.14457404216937</v>
       </c>
       <c r="R94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="S94" t="n">
-        <v>37.14162886109072</v>
+        <v>38.51503931286526</v>
       </c>
       <c r="T94" t="n">
-        <v>2.531651885104475</v>
+        <v>3.020287649644401</v>
       </c>
       <c r="U94" t="n">
         <v>93.11495456228404</v>
@@ -8688,11 +8698,11 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>37.14162886109072</v>
+        <v>38.51503931286526</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=37.14% sobre 20 sem</t>
+          <t>NBGLM: menor SMAPE real=38.52% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8716,25 +8726,25 @@
         <v>2026</v>
       </c>
       <c r="E95" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G95" t="n">
-        <v>150.2138989127696</v>
+        <v>151.4967953183141</v>
       </c>
       <c r="H95" t="n">
-        <v>0.651952329193679</v>
+        <v>0.629440394355325</v>
       </c>
       <c r="I95" t="n">
         <v>152.3875262412586</v>
       </c>
       <c r="J95" t="n">
-        <v>199.2325947669584</v>
+        <v>199.295024811595</v>
       </c>
       <c r="K95" t="n">
-        <v>0.4981978432695418</v>
+        <v>0.4766873730414749</v>
       </c>
       <c r="L95" t="n">
         <v>128.1095321097334</v>
@@ -8743,25 +8753,25 @@
         <v>200</v>
       </c>
       <c r="N95" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="O95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="P95" t="n">
-        <v>169.9924410067401</v>
+        <v>166.8563216454057</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.597150788765764</v>
+        <v>3.264262189594318</v>
       </c>
       <c r="R95" t="n">
         <v>118.2821915164861</v>
       </c>
       <c r="S95" t="n">
-        <v>162.5922054633087</v>
+        <v>161.3096889825202</v>
       </c>
       <c r="T95" t="n">
-        <v>1.59740887326649</v>
+        <v>1.542967425701738</v>
       </c>
       <c r="U95" t="n">
         <v>128.8999217807187</v>
@@ -8777,11 +8787,11 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>150.2138989127696</v>
+        <v>151.4967953183141</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=150.21% sobre 20 sem</t>
+          <t>Prophet: menor SMAPE real=151.50% sobre 23 sem</t>
         </is>
       </c>
     </row>
@@ -8805,25 +8815,25 @@
         <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F96" t="n">
         <v>3</v>
       </c>
       <c r="G96" t="n">
-        <v>182.6000985683808</v>
+        <v>184.8696509290267</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3181738069780032</v>
+        <v>0.2894927597943328</v>
       </c>
       <c r="I96" t="n">
         <v>158.9896824444987</v>
       </c>
       <c r="J96" t="n">
-        <v>199.2887495390962</v>
+        <v>199.3815213383446</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1504088082893271</v>
+        <v>0.1308509358942739</v>
       </c>
       <c r="L96" t="n">
         <v>189.1617640516506</v>
@@ -8832,25 +8842,25 @@
         <v>200</v>
       </c>
       <c r="N96" t="n">
-        <v>0.8742715794367811</v>
+        <v>1.262135874822121</v>
       </c>
       <c r="O96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="P96" t="n">
-        <v>187.3867458779483</v>
+        <v>189.0319529373464</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.531501344803482</v>
+        <v>3.235419393944986</v>
       </c>
       <c r="R96" t="n">
         <v>124.4459476108536</v>
       </c>
       <c r="S96" t="n">
-        <v>181.9272967007806</v>
+        <v>184.2846058267657</v>
       </c>
       <c r="T96" t="n">
-        <v>0.9157679185459064</v>
+        <v>0.9281105864255196</v>
       </c>
       <c r="U96" t="n">
         <v>151.8363274594118</v>
@@ -8892,52 +8902,52 @@
         <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G97" t="n">
-        <v>168.3603108145335</v>
+        <v>170.805862174128</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3854174982544045</v>
+        <v>0.3835315886264866</v>
       </c>
       <c r="I97" t="n">
         <v>157.2976315063829</v>
       </c>
       <c r="J97" t="n">
-        <v>199.3933910969344</v>
+        <v>199.4284607259294</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3528828039641452</v>
+        <v>0.350494112217551</v>
       </c>
       <c r="L97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="M97" t="n">
-        <v>166.1817724910707</v>
+        <v>163.0662907379325</v>
       </c>
       <c r="N97" t="n">
-        <v>1.625684887170792</v>
+        <v>1.617831665536632</v>
       </c>
       <c r="O97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="P97" t="n">
-        <v>170.1948421386046</v>
+        <v>167.6797090282344</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.276168801400835</v>
+        <v>2.091098841382167</v>
       </c>
       <c r="R97" t="n">
         <v>128.4785456608675</v>
       </c>
       <c r="S97" t="n">
-        <v>165.1313555544023</v>
+        <v>162.5356126507977</v>
       </c>
       <c r="T97" t="n">
-        <v>0.821790731875075</v>
+        <v>0.8284550584071141</v>
       </c>
       <c r="U97" t="n">
         <v>136.0400571203446</v>
@@ -8955,7 +8965,7 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8989,7 @@
         <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8988,7 +8998,7 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.07260366378937935</v>
+        <v>0.06313362068641683</v>
       </c>
       <c r="I98" t="n">
         <v>198.585723184526</v>
@@ -8997,7 +9007,7 @@
         <v>200</v>
       </c>
       <c r="K98" t="n">
-        <v>0.00054404465349612</v>
+        <v>0.0005247004063138043</v>
       </c>
       <c r="L98" t="n">
         <v>199.9898962083731</v>
@@ -9006,7 +9016,7 @@
         <v>200</v>
       </c>
       <c r="N98" t="n">
-        <v>0.075</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="O98" t="n">
         <v>199.2030987655621</v>
@@ -9022,7 +9032,7 @@
         <v>200</v>
       </c>
       <c r="T98" t="n">
-        <v>0.005154196125645891</v>
+        <v>0.03609275218497298</v>
       </c>
       <c r="U98" t="n">
         <v>199.9999998548883</v>
@@ -9064,7 +9074,7 @@
         <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -9073,7 +9083,7 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.04183094421640433</v>
+        <v>0.03637473410122116</v>
       </c>
       <c r="I99" t="n">
         <v>198.7380283178126</v>
@@ -9082,7 +9092,7 @@
         <v>200</v>
       </c>
       <c r="K99" t="n">
-        <v>0.00161789215811154</v>
+        <v>0.001627731885337944</v>
       </c>
       <c r="L99" t="n">
         <v>199.9983019911245</v>
@@ -9091,7 +9101,7 @@
         <v>200</v>
       </c>
       <c r="N99" t="n">
-        <v>0.075</v>
+        <v>0.2304334210966156</v>
       </c>
       <c r="O99" t="n">
         <v>198.5022493653877</v>
@@ -9107,7 +9117,7 @@
         <v>200</v>
       </c>
       <c r="T99" t="n">
-        <v>0.004032312519180891</v>
+        <v>0.03038073171553119</v>
       </c>
       <c r="U99" t="n">
         <v>200</v>
@@ -9149,7 +9159,7 @@
         <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -9158,7 +9168,7 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.05751753432389537</v>
+        <v>0.05161836148268496</v>
       </c>
       <c r="I100" t="n">
         <v>200</v>
@@ -9167,14 +9177,16 @@
         <v>200</v>
       </c>
       <c r="K100" t="n">
-        <v>0.002432684187964065</v>
+        <v>0.002418710587654218</v>
       </c>
       <c r="L100" t="n">
         <v>200</v>
       </c>
-      <c r="M100" t="inlineStr"/>
+      <c r="M100" t="n">
+        <v>200</v>
+      </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>0.06521739130434782</v>
       </c>
       <c r="O100" t="n">
         <v>200</v>
@@ -9190,14 +9202,14 @@
         <v>200</v>
       </c>
       <c r="T100" t="n">
-        <v>0.0001924153076147698</v>
+        <v>0.01282877454675312</v>
       </c>
       <c r="U100" t="n">
         <v>200</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W100" t="inlineStr">
@@ -9208,7 +9220,7 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -575,7 +575,7 @@
         <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -584,50 +584,50 @@
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09640672006432924</v>
+        <v>0.09238977339498218</v>
       </c>
       <c r="I2" t="n">
         <v>185.8333489727328</v>
       </c>
       <c r="J2" t="n">
-        <v>199.2579644023037</v>
+        <v>199.2888825522077</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09418773272458057</v>
+        <v>0.0933538099404826</v>
       </c>
       <c r="L2" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M2" t="n">
-        <v>177.1428571428572</v>
+        <v>180</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.6875</v>
       </c>
       <c r="O2" t="n">
         <v>197.8088169752323</v>
       </c>
       <c r="P2" t="n">
-        <v>177.1428571428572</v>
+        <v>180</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.6875</v>
       </c>
       <c r="R2" t="n">
         <v>199.5572761277739</v>
       </c>
       <c r="S2" t="n">
-        <v>194.1154745887209</v>
+        <v>194.3606631475242</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1155501944511648</v>
+        <v>0.1270160811209012</v>
       </c>
       <c r="U2" t="n">
         <v>194.9779461019607</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -638,7 +638,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
         <v>2026</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -671,16 +671,16 @@
         <v>199.7529419278686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05207677763587828</v>
+        <v>0.04990691190105003</v>
       </c>
       <c r="I3" t="n">
         <v>157.2321783542833</v>
       </c>
       <c r="J3" t="n">
-        <v>199.586521041329</v>
+        <v>199.6037493312737</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05579806788954927</v>
+        <v>0.0552020374046991</v>
       </c>
       <c r="L3" t="n">
         <v>79.54507935933471</v>
@@ -689,7 +689,7 @@
         <v>200</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="O3" t="n">
         <v>197.8854209931308</v>
@@ -698,16 +698,16 @@
         <v>200</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.2291666666666667</v>
       </c>
       <c r="R3" t="n">
         <v>199.636475467609</v>
       </c>
       <c r="S3" t="n">
-        <v>199.4086924003466</v>
+        <v>199.4333302169988</v>
       </c>
       <c r="T3" t="n">
-        <v>0.07575186921040457</v>
+        <v>0.08128269129803049</v>
       </c>
       <c r="U3" t="n">
         <v>198.5158836242873</v>
@@ -749,7 +749,7 @@
         <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -758,43 +758,43 @@
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05512805289066256</v>
+        <v>0.05283105068688496</v>
       </c>
       <c r="I4" t="n">
         <v>158.5580779411727</v>
       </c>
       <c r="J4" t="n">
-        <v>195.0043654828781</v>
+        <v>195.2125169210915</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1312822637752856</v>
+        <v>0.1435042186988603</v>
       </c>
       <c r="L4" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M4" t="n">
-        <v>168</v>
+        <v>173.3333333333333</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="O4" t="n">
         <v>197.7265973322816</v>
       </c>
       <c r="P4" t="n">
-        <v>168</v>
+        <v>173.3333333333333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="R4" t="n">
         <v>199.5859359679221</v>
       </c>
       <c r="S4" t="n">
-        <v>195.882373998402</v>
+        <v>196.0539417484686</v>
       </c>
       <c r="T4" t="n">
-        <v>0.07941716176852767</v>
+        <v>0.09143706365799938</v>
       </c>
       <c r="U4" t="n">
         <v>196.9436529554095</v>
@@ -836,7 +836,7 @@
         <v>2026</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -845,16 +845,16 @@
         <v>199.0479027213012</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1766370530365091</v>
+        <v>0.1692771758266546</v>
       </c>
       <c r="I5" t="n">
         <v>175.1088701866436</v>
       </c>
       <c r="J5" t="n">
-        <v>199.291615850557</v>
+        <v>199.3211318567838</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1851306619209305</v>
+        <v>0.1779919650089362</v>
       </c>
       <c r="L5" t="n">
         <v>109.609711216533</v>
@@ -863,7 +863,7 @@
         <v>200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="O5" t="n">
         <v>187.2707284786031</v>
@@ -872,16 +872,16 @@
         <v>200</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="R5" t="n">
         <v>193.7972259177366</v>
       </c>
       <c r="S5" t="n">
-        <v>199.360188055135</v>
+        <v>199.386846886171</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1859482139509409</v>
+        <v>0.1782003717029851</v>
       </c>
       <c r="U5" t="n">
         <v>187.0400639517023</v>
@@ -923,25 +923,25 @@
         <v>2026</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>199.4965556931469</v>
+        <v>199.5175325392658</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09523652339086032</v>
+        <v>0.09131319804606282</v>
       </c>
       <c r="I6" t="n">
         <v>191.646475967384</v>
       </c>
       <c r="J6" t="n">
-        <v>199.9769257249451</v>
+        <v>199.9778871530725</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0876597108729765</v>
+        <v>0.08403767526253114</v>
       </c>
       <c r="L6" t="n">
         <v>79.54507935933471</v>
@@ -950,7 +950,7 @@
         <v>200</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1521739130434783</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="O6" t="n">
         <v>192.53013744135</v>
@@ -959,7 +959,7 @@
         <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1521739130434783</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="R6" t="n">
         <v>193.2139428195562</v>
@@ -968,7 +968,7 @@
         <v>198.5786411733137</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09286132223550503</v>
+        <v>0.08899210047569232</v>
       </c>
       <c r="U6" t="n">
         <v>198.9985835834048</v>
@@ -1010,25 +1010,25 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>198.7342969739748</v>
+        <v>198.7893275403238</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1074898285321442</v>
+        <v>0.1034173866230271</v>
       </c>
       <c r="I7" t="n">
         <v>186.9197740801393</v>
       </c>
       <c r="J7" t="n">
-        <v>199.9820249646312</v>
+        <v>199.9827739244382</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08736130679163399</v>
+        <v>0.08372825494511628</v>
       </c>
       <c r="L7" t="n">
         <v>109.7635513825217</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1521739130434783</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="O7" t="n">
         <v>185.3187572725189</v>
@@ -1046,16 +1046,16 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1521739130434783</v>
+        <v>0.1458333333333333</v>
       </c>
       <c r="R7" t="n">
         <v>190.8625800946274</v>
       </c>
       <c r="S7" t="n">
-        <v>199.8123070319464</v>
+        <v>199.8201275722819</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1010827293922708</v>
+        <v>0.09687094900092623</v>
       </c>
       <c r="U7" t="n">
         <v>197.3279694158802</v>
@@ -1097,52 +1097,52 @@
         <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G8" t="n">
-        <v>100.2669787630565</v>
+        <v>100.1124878587876</v>
       </c>
       <c r="H8" t="n">
-        <v>5.033323505655278</v>
+        <v>4.901391109923342</v>
       </c>
       <c r="I8" t="n">
         <v>154.5040916050135</v>
       </c>
       <c r="J8" t="n">
-        <v>57.1925436233631</v>
+        <v>62.34216615161932</v>
       </c>
       <c r="K8" t="n">
-        <v>4.901934090576742</v>
+        <v>5.481663005783507</v>
       </c>
       <c r="L8" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M8" t="n">
-        <v>90.13850994198548</v>
+        <v>94.17843761913393</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>14.625</v>
       </c>
       <c r="O8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="P8" t="n">
-        <v>90.13850994198548</v>
+        <v>94.17843761913393</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>14.625</v>
       </c>
       <c r="R8" t="n">
         <v>172.894287988784</v>
       </c>
       <c r="S8" t="n">
-        <v>59.9679535293255</v>
+        <v>62.28509479054119</v>
       </c>
       <c r="T8" t="n">
-        <v>3.350774604290362</v>
+        <v>3.325249698416485</v>
       </c>
       <c r="U8" t="n">
         <v>111.5676388698673</v>
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>59.9679535293255</v>
+        <v>62.28509479054119</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=59.97% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=62.29% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1186,52 +1186,52 @@
         <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>96.86242957945571</v>
+        <v>94.18208509883893</v>
       </c>
       <c r="H9" t="n">
-        <v>2.327612097079943</v>
+        <v>2.246817711851911</v>
       </c>
       <c r="I9" t="n">
         <v>164.086229256472</v>
       </c>
       <c r="J9" t="n">
-        <v>73.71026723278355</v>
+        <v>77.46126867626897</v>
       </c>
       <c r="K9" t="n">
-        <v>2.669844237566461</v>
+        <v>2.934838491239349</v>
       </c>
       <c r="L9" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M9" t="n">
-        <v>100.7484856228131</v>
+        <v>103.601914106478</v>
       </c>
       <c r="N9" t="n">
-        <v>7.173913043478261</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="O9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="P9" t="n">
-        <v>100.7484856228131</v>
+        <v>103.601914106478</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.173913043478261</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="R9" t="n">
         <v>176.8647517474977</v>
       </c>
       <c r="S9" t="n">
-        <v>59.18799158853509</v>
+        <v>60.38101971880621</v>
       </c>
       <c r="T9" t="n">
-        <v>1.457843465323946</v>
+        <v>1.462338286659661</v>
       </c>
       <c r="U9" t="n">
         <v>121.2492629006552</v>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>59.18799158853509</v>
+        <v>60.38101971880621</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=59.19% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=60.38% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1275,52 +1275,52 @@
         <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
         <v>87</v>
       </c>
       <c r="G10" t="n">
-        <v>89.49394177012995</v>
+        <v>94.09836086304119</v>
       </c>
       <c r="H10" t="n">
-        <v>2.491078366601676</v>
+        <v>2.469549318102043</v>
       </c>
       <c r="I10" t="n">
         <v>164.4874496413386</v>
       </c>
       <c r="J10" t="n">
-        <v>65.26079607571089</v>
+        <v>70.87492957255627</v>
       </c>
       <c r="K10" t="n">
-        <v>1.817841397374628</v>
+        <v>1.743550528453186</v>
       </c>
       <c r="L10" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M10" t="n">
-        <v>93.93884057717756</v>
+        <v>98.35805555312848</v>
       </c>
       <c r="N10" t="n">
-        <v>7.543478260869565</v>
+        <v>7.979166666666667</v>
       </c>
       <c r="O10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="P10" t="n">
-        <v>93.93884057717756</v>
+        <v>98.35805555312848</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.543478260869565</v>
+        <v>7.979166666666667</v>
       </c>
       <c r="R10" t="n">
         <v>168.5443712458804</v>
       </c>
       <c r="S10" t="n">
-        <v>61.39934805337054</v>
+        <v>67.17437521781342</v>
       </c>
       <c r="T10" t="n">
-        <v>1.887811508963884</v>
+        <v>1.888005259843791</v>
       </c>
       <c r="U10" t="n">
         <v>114.746491150853</v>
@@ -1336,11 +1336,11 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>61.39934805337054</v>
+        <v>67.17437521781342</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=61.40% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=67.17% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1364,52 +1364,52 @@
         <v>2026</v>
       </c>
       <c r="E11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>179.5697715406957</v>
+        <v>180.5912829636609</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6108910140117226</v>
+        <v>0.6271038884279009</v>
       </c>
       <c r="I11" t="n">
         <v>123.2554563734294</v>
       </c>
       <c r="J11" t="n">
-        <v>198.3252005482301</v>
+        <v>198.3768860507129</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6167025165834394</v>
+        <v>0.6326279513561061</v>
       </c>
       <c r="L11" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M11" t="n">
-        <v>187.6528754476888</v>
+        <v>184.0006723040351</v>
       </c>
       <c r="N11" t="n">
-        <v>25.83269850528452</v>
+        <v>24.83966940089766</v>
       </c>
       <c r="O11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="P11" t="n">
-        <v>162.0103299062185</v>
+        <v>164.1208671336508</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.034553499506514</v>
+        <v>1.033113770360409</v>
       </c>
       <c r="R11" t="n">
         <v>177.781032308345</v>
       </c>
       <c r="S11" t="n">
-        <v>125.3137009295347</v>
+        <v>122.8450781291039</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6440559530907478</v>
+        <v>0.6583270558379246</v>
       </c>
       <c r="U11" t="n">
         <v>147.9725418621825</v>
@@ -1425,11 +1425,11 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>125.3137009295347</v>
+        <v>122.8450781291039</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=125.31% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=122.85% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         <v>2026</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
@@ -1462,25 +1462,25 @@
         <v>192.5956874696411</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3971227622104589</v>
+        <v>0.3805759804516898</v>
       </c>
       <c r="I12" t="n">
         <v>147.3485671696691</v>
       </c>
       <c r="J12" t="n">
-        <v>199.5744872982048</v>
+        <v>199.592216994113</v>
       </c>
       <c r="K12" t="n">
-        <v>0.401254753256975</v>
+        <v>0.4024294311096615</v>
       </c>
       <c r="L12" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M12" t="n">
-        <v>186.0516758265984</v>
+        <v>186.6328560004902</v>
       </c>
       <c r="N12" t="n">
-        <v>11.80308391156755</v>
+        <v>11.43628874858557</v>
       </c>
       <c r="O12" t="n">
         <v>191.4723960783834</v>
@@ -1489,16 +1489,16 @@
         <v>182.9634089977751</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.63861541995272</v>
+        <v>10.19533977745468</v>
       </c>
       <c r="R12" t="n">
         <v>189.6908701459495</v>
       </c>
       <c r="S12" t="n">
-        <v>159.1043792977246</v>
+        <v>160.8083634936527</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5395046849004895</v>
+        <v>0.5588063692567461</v>
       </c>
       <c r="U12" t="n">
         <v>169.7722333133142</v>
@@ -1540,52 +1540,52 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
-        <v>195.8361847211582</v>
+        <v>196.2147133828711</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2223606754661655</v>
+        <v>0.2547623139884086</v>
       </c>
       <c r="I13" t="n">
         <v>157.1522264328246</v>
       </c>
       <c r="J13" t="n">
-        <v>199.8404560344622</v>
+        <v>199.8323997562024</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2186316362277156</v>
+        <v>0.2511518590666376</v>
       </c>
       <c r="L13" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M13" t="n">
-        <v>192.7202107549575</v>
+        <v>188.8568686401676</v>
       </c>
       <c r="N13" t="n">
-        <v>13.88437529829831</v>
+        <v>13.38919299420255</v>
       </c>
       <c r="O13" t="n">
         <v>193.9340304002594</v>
       </c>
       <c r="P13" t="n">
-        <v>192.1270949117732</v>
+        <v>192.5207401661846</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.570890851096843</v>
+        <v>5.380437065634474</v>
       </c>
       <c r="R13" t="n">
         <v>188.2053733911598</v>
       </c>
       <c r="S13" t="n">
-        <v>165.3083513542729</v>
+        <v>159.7205184268186</v>
       </c>
       <c r="T13" t="n">
-        <v>0.407074069984613</v>
+        <v>0.4013584377309827</v>
       </c>
       <c r="U13" t="n">
         <v>173.7069303697712</v>
@@ -1603,7 +1603,7 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1627,52 +1627,52 @@
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>69.39790860052938</v>
+        <v>68.78636566054853</v>
       </c>
       <c r="H14" t="n">
-        <v>2.372329349033962</v>
+        <v>2.398797942000959</v>
       </c>
       <c r="I14" t="n">
         <v>66.61025297793201</v>
       </c>
       <c r="J14" t="n">
-        <v>76.92207018141531</v>
+        <v>74.64024737042836</v>
       </c>
       <c r="K14" t="n">
-        <v>2.703067216152471</v>
+        <v>2.663120287868505</v>
       </c>
       <c r="L14" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M14" t="n">
-        <v>163.2388813787565</v>
+        <v>162.5696016821114</v>
       </c>
       <c r="N14" t="n">
-        <v>33.72268947014127</v>
+        <v>33.94284318140149</v>
       </c>
       <c r="O14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="P14" t="n">
-        <v>180.3952676159481</v>
+        <v>180.7124883532208</v>
       </c>
       <c r="Q14" t="n">
-        <v>74.73913043478261</v>
+        <v>80.77083333333333</v>
       </c>
       <c r="R14" t="n">
         <v>186.0423288913966</v>
       </c>
       <c r="S14" t="n">
-        <v>79.1706967455949</v>
+        <v>82.35502468392289</v>
       </c>
       <c r="T14" t="n">
-        <v>5.0374764945796</v>
+        <v>6.871554460679278</v>
       </c>
       <c r="U14" t="n">
         <v>130.2296761771863</v>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>69.39790860052938</v>
+        <v>68.78636566054853</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=69.40% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=68.79% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1716,52 +1716,52 @@
         <v>2026</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G15" t="n">
-        <v>66.60050454684506</v>
+        <v>66.98812300624824</v>
       </c>
       <c r="H15" t="n">
-        <v>1.065927405429038</v>
+        <v>1.113216586572249</v>
       </c>
       <c r="I15" t="n">
         <v>82.6747998505866</v>
       </c>
       <c r="J15" t="n">
-        <v>88.03721417177097</v>
+        <v>85.87658830892269</v>
       </c>
       <c r="K15" t="n">
-        <v>1.376838481255402</v>
+        <v>1.393093045066255</v>
       </c>
       <c r="L15" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M15" t="n">
-        <v>170.7138702810821</v>
+        <v>170.0041191689805</v>
       </c>
       <c r="N15" t="n">
-        <v>22.72205646810959</v>
+        <v>22.8812290192702</v>
       </c>
       <c r="O15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="P15" t="n">
-        <v>177.4115898461844</v>
+        <v>177.7948935468054</v>
       </c>
       <c r="Q15" t="n">
-        <v>35.28260869565217</v>
+        <v>38.45833333333334</v>
       </c>
       <c r="R15" t="n">
         <v>186.4460938550808</v>
       </c>
       <c r="S15" t="n">
-        <v>81.99553157655238</v>
+        <v>84.71438220335999</v>
       </c>
       <c r="T15" t="n">
-        <v>2.437640334943708</v>
+        <v>3.26651252462619</v>
       </c>
       <c r="U15" t="n">
         <v>131.9030800529592</v>
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>66.60050454684506</v>
+        <v>66.98812300624824</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=66.60% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=66.99% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1805,52 +1805,52 @@
         <v>2026</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>115.4195850524713</v>
+        <v>112.5264090609578</v>
       </c>
       <c r="H16" t="n">
-        <v>1.767846442013095</v>
+        <v>1.740920392753358</v>
       </c>
       <c r="I16" t="n">
         <v>90.20708978859948</v>
       </c>
       <c r="J16" t="n">
-        <v>123.8382033410324</v>
+        <v>120.0955416391536</v>
       </c>
       <c r="K16" t="n">
-        <v>1.481049571138128</v>
+        <v>1.470569981840985</v>
       </c>
       <c r="L16" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M16" t="n">
-        <v>172.8053037784588</v>
+        <v>172.5483151230665</v>
       </c>
       <c r="N16" t="n">
-        <v>23.70060744474833</v>
+        <v>23.96177419821775</v>
       </c>
       <c r="O16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="P16" t="n">
-        <v>181.7847259866078</v>
+        <v>182.1050992459377</v>
       </c>
       <c r="Q16" t="n">
-        <v>39.52173913043478</v>
+        <v>42.375</v>
       </c>
       <c r="R16" t="n">
         <v>186.1307414343702</v>
       </c>
       <c r="S16" t="n">
-        <v>104.1603161324143</v>
+        <v>106.5011998637745</v>
       </c>
       <c r="T16" t="n">
-        <v>2.437815710078234</v>
+        <v>3.347004642725491</v>
       </c>
       <c r="U16" t="n">
         <v>133.2708900338696</v>
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>104.1603161324143</v>
+        <v>106.5011998637745</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=104.16% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=106.50% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -1894,25 +1894,25 @@
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>198.9552170025404</v>
+        <v>198.9987496274345</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1084945518651706</v>
+        <v>0.1112527512550425</v>
       </c>
       <c r="I17" t="n">
         <v>194.5446671655584</v>
       </c>
       <c r="J17" t="n">
-        <v>199.953038990851</v>
+        <v>199.9549956995655</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0457257643045931</v>
+        <v>0.0439123054440127</v>
       </c>
       <c r="L17" t="n">
         <v>109.609711216533</v>
@@ -1921,7 +1921,7 @@
         <v>200</v>
       </c>
       <c r="N17" t="n">
-        <v>0.108695652173913</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="O17" t="n">
         <v>196.7571923388938</v>
@@ -1930,16 +1930,16 @@
         <v>200</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.108695652173913</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="R17" t="n">
         <v>197.0125798901019</v>
       </c>
       <c r="S17" t="n">
-        <v>198.9244814231327</v>
+        <v>198.9692946971688</v>
       </c>
       <c r="T17" t="n">
-        <v>0.05006354982080351</v>
+        <v>0.04797756857827003</v>
       </c>
       <c r="U17" t="n">
         <v>192.256373806382</v>
@@ -1981,7 +1981,7 @@
         <v>2026</v>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02260952408321706</v>
+        <v>0.02469487618589014</v>
       </c>
       <c r="I18" t="n">
         <v>199.6410247115898</v>
@@ -1999,7 +1999,7 @@
         <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0005588044341359392</v>
+        <v>0.0005610538594717875</v>
       </c>
       <c r="L18" t="n">
         <v>79.54507935933471</v>
@@ -2022,7 +2022,7 @@
         <v>200</v>
       </c>
       <c r="T18" t="n">
-        <v>4.426636004136712e-263</v>
+        <v>4.242192837297683e-263</v>
       </c>
       <c r="U18" t="n">
         <v>196.0211023092105</v>
@@ -2064,25 +2064,25 @@
         <v>2026</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.2123176671249</v>
+        <v>199.246564725076</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09310047787324048</v>
+        <v>0.09538539145820128</v>
       </c>
       <c r="I19" t="n">
         <v>196.278530387405</v>
       </c>
       <c r="J19" t="n">
-        <v>199.8922114324738</v>
+        <v>199.8967026227874</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0482601753578682</v>
+        <v>0.04645743202683102</v>
       </c>
       <c r="L19" t="n">
         <v>109.7635513825217</v>
@@ -2091,7 +2091,7 @@
         <v>200</v>
       </c>
       <c r="N19" t="n">
-        <v>0.108695652173913</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="O19" t="n">
         <v>196.7189002085085</v>
@@ -2100,16 +2100,16 @@
         <v>200</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.108695652173913</v>
+        <v>0.1041666666666667</v>
       </c>
       <c r="R19" t="n">
         <v>196.7488584326798</v>
       </c>
       <c r="S19" t="n">
-        <v>199.0253474718139</v>
+        <v>199.0659579938217</v>
       </c>
       <c r="T19" t="n">
-        <v>0.05081579213687931</v>
+        <v>0.04869846746450934</v>
       </c>
       <c r="U19" t="n">
         <v>197.8046914283761</v>
@@ -2151,7 +2151,7 @@
         <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07091308014421872</v>
+        <v>0.07101922894124693</v>
       </c>
       <c r="I20" t="n">
         <v>200</v>
@@ -2169,7 +2169,7 @@
         <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001364348782705161</v>
+        <v>0.00135199373175945</v>
       </c>
       <c r="L20" t="n">
         <v>109.609711216533</v>
@@ -2192,7 +2192,7 @@
         <v>200</v>
       </c>
       <c r="T20" t="n">
-        <v>6521.739130434783</v>
+        <v>6250</v>
       </c>
       <c r="U20" t="n">
         <v>200</v>
@@ -2234,7 +2234,7 @@
         <v>2026</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05707240016553016</v>
+        <v>0.05715685033181415</v>
       </c>
       <c r="I21" t="n">
         <v>200</v>
@@ -2252,7 +2252,7 @@
         <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>0.006024787974672279</v>
+        <v>0.006040243875664572</v>
       </c>
       <c r="L21" t="n">
         <v>79.54507935933471</v>
@@ -2275,7 +2275,7 @@
         <v>200</v>
       </c>
       <c r="T21" t="n">
-        <v>15217.39130442722</v>
+        <v>14583.33333340942</v>
       </c>
       <c r="U21" t="n">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>2026</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0639010226511763</v>
+        <v>0.0639970336351797</v>
       </c>
       <c r="I22" t="n">
         <v>200</v>
@@ -2335,7 +2335,7 @@
         <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0003876241781221087</v>
+        <v>0.000397037299094625</v>
       </c>
       <c r="L22" t="n">
         <v>109.7635513825217</v>
@@ -2358,7 +2358,7 @@
         <v>200</v>
       </c>
       <c r="T22" t="n">
-        <v>2.796050610354176e-17</v>
+        <v>2.679548501589419e-17</v>
       </c>
       <c r="U22" t="n">
         <v>200</v>
@@ -2400,52 +2400,52 @@
         <v>2026</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>188.0993788680326</v>
+        <v>189.5869565095285</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1191255336072813</v>
+        <v>0.1272192625621998</v>
       </c>
       <c r="I23" t="n">
         <v>149.2565324185079</v>
       </c>
       <c r="J23" t="n">
-        <v>199.3902993311769</v>
+        <v>199.4157035257112</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2144830638454611</v>
+        <v>0.3874155932337184</v>
       </c>
       <c r="L23" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M23" t="n">
-        <v>193.6507936507937</v>
+        <v>194.2857142857143</v>
       </c>
       <c r="N23" t="n">
-        <v>1.043478260869565</v>
+        <v>1.875</v>
       </c>
       <c r="O23" t="n">
         <v>169.6992056798271</v>
       </c>
       <c r="P23" t="n">
-        <v>193.6507936507937</v>
+        <v>194.2857142857143</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.043478260869565</v>
+        <v>1.875</v>
       </c>
       <c r="R23" t="n">
         <v>186.3774873978808</v>
       </c>
       <c r="S23" t="n">
-        <v>191.0371440388769</v>
+        <v>191.4105963705904</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2607550959162749</v>
+        <v>0.338078850963736</v>
       </c>
       <c r="U23" t="n">
         <v>159.9263814945425</v>
@@ -2487,52 +2487,52 @@
         <v>2026</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>189.3326627180366</v>
+        <v>191.1105522650305</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05767232671072361</v>
+        <v>0.06057232076800143</v>
       </c>
       <c r="I24" t="n">
         <v>156.2502876793226</v>
       </c>
       <c r="J24" t="n">
-        <v>198.7799569603005</v>
+        <v>198.8307920869546</v>
       </c>
       <c r="K24" t="n">
-        <v>0.07957654129197167</v>
+        <v>0.1836614891690675</v>
       </c>
       <c r="L24" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M24" t="n">
-        <v>158.8366383208175</v>
+        <v>169.1274787406131</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2487209724343341</v>
+        <v>0.4258575985829036</v>
       </c>
       <c r="O24" t="n">
         <v>159.6122718089852</v>
       </c>
       <c r="P24" t="n">
-        <v>180</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.5434782608695652</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="R24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="S24" t="n">
-        <v>193.8626616438882</v>
+        <v>194.1183840753929</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1369834510173822</v>
+        <v>0.168721598493243</v>
       </c>
       <c r="U24" t="n">
         <v>166.4426133688291</v>
@@ -2574,7 +2574,7 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2583,16 +2583,16 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>0.06665634897032278</v>
+        <v>0.07062044496379477</v>
       </c>
       <c r="I25" t="n">
         <v>155.3955473497874</v>
       </c>
       <c r="J25" t="n">
-        <v>199.9288986501652</v>
+        <v>199.9318612064084</v>
       </c>
       <c r="K25" t="n">
-        <v>0.05297273674255192</v>
+        <v>0.0701348939381</v>
       </c>
       <c r="L25" t="n">
         <v>109.7635513825217</v>
@@ -2601,7 +2601,7 @@
         <v>200</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5652173913043478</v>
+        <v>1.229166666666667</v>
       </c>
       <c r="O25" t="n">
         <v>177.0659734750362</v>
@@ -2610,16 +2610,16 @@
         <v>200</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5652173913043478</v>
+        <v>1.229166666666667</v>
       </c>
       <c r="R25" t="n">
         <v>183.340259481936</v>
       </c>
       <c r="S25" t="n">
-        <v>199.6268147518718</v>
+        <v>199.6423641372105</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1883433489305086</v>
+        <v>0.2384298444055527</v>
       </c>
       <c r="U25" t="n">
         <v>180.6321027113416</v>
@@ -2661,7 +2661,7 @@
         <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02296560236409023</v>
+        <v>0.02200870226558647</v>
       </c>
       <c r="I26" t="n">
         <v>97.19414576199205</v>
@@ -2679,7 +2679,7 @@
         <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1038645319465069</v>
+        <v>0.105833757744135</v>
       </c>
       <c r="L26" t="n">
         <v>109.609711216533</v>
@@ -2688,7 +2688,7 @@
         <v>200</v>
       </c>
       <c r="N26" t="n">
-        <v>71.47826086956522</v>
+        <v>70.3125</v>
       </c>
       <c r="O26" t="n">
         <v>198.3074653131699</v>
@@ -2697,7 +2697,7 @@
         <v>200</v>
       </c>
       <c r="Q26" t="n">
-        <v>71.47826086956522</v>
+        <v>70.3125</v>
       </c>
       <c r="R26" t="n">
         <v>199.6509594119097</v>
@@ -2706,7 +2706,7 @@
         <v>200</v>
       </c>
       <c r="T26" t="n">
-        <v>1.069336825017407</v>
+        <v>1.138951792336027</v>
       </c>
       <c r="U26" t="n">
         <v>183.6686755299509</v>
@@ -2748,7 +2748,7 @@
         <v>2026</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01608051188245655</v>
+        <v>0.01541049055402086</v>
       </c>
       <c r="I27" t="n">
         <v>129.0985231723771</v>
@@ -2766,7 +2766,7 @@
         <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01105918152281296</v>
+        <v>0.01137759494141414</v>
       </c>
       <c r="L27" t="n">
         <v>79.54507935933471</v>
@@ -2775,7 +2775,7 @@
         <v>200</v>
       </c>
       <c r="N27" t="n">
-        <v>35.28260869565217</v>
+        <v>34.4375</v>
       </c>
       <c r="O27" t="n">
         <v>198.6114841856233</v>
@@ -2784,7 +2784,7 @@
         <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>35.28260869565217</v>
+        <v>34.4375</v>
       </c>
       <c r="R27" t="n">
         <v>199.779644487174</v>
@@ -2793,7 +2793,7 @@
         <v>200</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7160689155560462</v>
+        <v>0.7753725409691095</v>
       </c>
       <c r="U27" t="n">
         <v>192.722098187243</v>
@@ -2835,7 +2835,7 @@
         <v>2026</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.01622446839456877</v>
+        <v>0.0155484488781284</v>
       </c>
       <c r="I28" t="n">
         <v>127.1718885128103</v>
@@ -2853,7 +2853,7 @@
         <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>0.02541885056650545</v>
+        <v>0.05058959153596346</v>
       </c>
       <c r="L28" t="n">
         <v>109.7635513825217</v>
@@ -2862,7 +2862,7 @@
         <v>200</v>
       </c>
       <c r="N28" t="n">
-        <v>36.19565217391305</v>
+        <v>35.875</v>
       </c>
       <c r="O28" t="n">
         <v>197.4940180993655</v>
@@ -2871,7 +2871,7 @@
         <v>200</v>
       </c>
       <c r="Q28" t="n">
-        <v>36.19565217391305</v>
+        <v>35.875</v>
       </c>
       <c r="R28" t="n">
         <v>199.5411797194807</v>
@@ -2880,7 +2880,7 @@
         <v>200</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8041157552583883</v>
+        <v>0.83269649664334</v>
       </c>
       <c r="U28" t="n">
         <v>184.9627687949149</v>
@@ -2922,25 +2922,25 @@
         <v>2026</v>
       </c>
       <c r="E29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>196.886012865036</v>
+        <v>197.0275577348071</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1381129309159472</v>
+        <v>0.1473758985359336</v>
       </c>
       <c r="I29" t="n">
         <v>191.5075017030775</v>
       </c>
       <c r="J29" t="n">
-        <v>199.6430165552206</v>
+        <v>199.6578908654198</v>
       </c>
       <c r="K29" t="n">
-        <v>0.06743395785322541</v>
+        <v>0.06570026843773663</v>
       </c>
       <c r="L29" t="n">
         <v>109.609711216533</v>
@@ -2949,7 +2949,7 @@
         <v>200</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="O29" t="n">
         <v>198.5277121400952</v>
@@ -2958,16 +2958,16 @@
         <v>200</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R29" t="n">
         <v>199.9388941772115</v>
       </c>
       <c r="S29" t="n">
-        <v>199.9999595883774</v>
+        <v>199.999961272195</v>
       </c>
       <c r="T29" t="n">
-        <v>0.07612185230396007</v>
+        <v>0.07295291457808649</v>
       </c>
       <c r="U29" t="n">
         <v>192.5799615112869</v>
@@ -3009,7 +3009,7 @@
         <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.09271128771702397</v>
+        <v>0.1007596403583528</v>
       </c>
       <c r="I30" t="n">
         <v>196.0386411854094</v>
@@ -3027,7 +3027,7 @@
         <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>0.005792552333991318</v>
+        <v>0.005811931459301625</v>
       </c>
       <c r="L30" t="n">
         <v>79.54507935933471</v>
@@ -3036,7 +3036,7 @@
         <v>200</v>
       </c>
       <c r="N30" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
       <c r="O30" t="n">
         <v>198.9477887234591</v>
@@ -3045,7 +3045,7 @@
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.25</v>
       </c>
       <c r="R30" t="n">
         <v>199.7754683359127</v>
@@ -3054,7 +3054,7 @@
         <v>200</v>
       </c>
       <c r="T30" t="n">
-        <v>0.02141443680013175</v>
+        <v>0.020527641695696</v>
       </c>
       <c r="U30" t="n">
         <v>198.9226798174336</v>
@@ -3096,25 +3096,25 @@
         <v>2026</v>
       </c>
       <c r="E31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>197.2154099320408</v>
+        <v>197.3364790654304</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1348741867312997</v>
+        <v>0.1431302305581424</v>
       </c>
       <c r="I31" t="n">
         <v>194.2466814459454</v>
       </c>
       <c r="J31" t="n">
-        <v>199.8851341157176</v>
+        <v>199.8899201942293</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0488081467166611</v>
+        <v>0.04713093038733673</v>
       </c>
       <c r="L31" t="n">
         <v>109.7635513825217</v>
@@ -3123,7 +3123,7 @@
         <v>200</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="O31" t="n">
         <v>199.0633013569061</v>
@@ -3132,16 +3132,16 @@
         <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="R31" t="n">
         <v>199.9196066031173</v>
       </c>
       <c r="S31" t="n">
-        <v>199.9999999913935</v>
+        <v>199.9999999917521</v>
       </c>
       <c r="T31" t="n">
-        <v>0.05709933295456548</v>
+        <v>0.05472020386558352</v>
       </c>
       <c r="U31" t="n">
         <v>194.1597056483905</v>
@@ -3183,52 +3183,52 @@
         <v>2026</v>
       </c>
       <c r="E32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F32" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G32" t="n">
-        <v>146.7319878793955</v>
+        <v>144.1198765122525</v>
       </c>
       <c r="H32" t="n">
-        <v>0.58739462129047</v>
+        <v>0.7441079019883944</v>
       </c>
       <c r="I32" t="n">
         <v>164.6748490827784</v>
       </c>
       <c r="J32" t="n">
-        <v>168.6519714295135</v>
+        <v>166.1972827302878</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9526356847622569</v>
+        <v>1.216894351016665</v>
       </c>
       <c r="L32" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M32" t="n">
-        <v>157.0394148787501</v>
+        <v>157.9374441348126</v>
       </c>
       <c r="N32" t="n">
-        <v>8.652173913043478</v>
+        <v>10.04166666666667</v>
       </c>
       <c r="O32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="P32" t="n">
-        <v>157.0394148787501</v>
+        <v>157.9374441348126</v>
       </c>
       <c r="Q32" t="n">
-        <v>8.652173913043478</v>
+        <v>10.04166666666667</v>
       </c>
       <c r="R32" t="n">
         <v>195.3761640213164</v>
       </c>
       <c r="S32" t="n">
-        <v>142.7163228269366</v>
+        <v>143.3697981039369</v>
       </c>
       <c r="T32" t="n">
-        <v>1.241395123958266</v>
+        <v>2.141585587987389</v>
       </c>
       <c r="U32" t="n">
         <v>173.3959783787531</v>
@@ -3244,11 +3244,11 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>146.7319878793955</v>
+        <v>144.1198765122525</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=146.73% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=144.12% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -3272,52 +3272,52 @@
         <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>167.4517535775812</v>
+        <v>158.0334561427051</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2884666033267993</v>
+        <v>0.301546770546361</v>
       </c>
       <c r="I33" t="n">
         <v>170.4028696730483</v>
       </c>
       <c r="J33" t="n">
-        <v>188.377627252309</v>
+        <v>181.5351440239996</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4644442591589993</v>
+        <v>0.4630544675113303</v>
       </c>
       <c r="L33" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M33" t="n">
-        <v>189.7435897435898</v>
+        <v>187.8183831672204</v>
       </c>
       <c r="N33" t="n">
-        <v>3.5</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="O33" t="n">
         <v>180.7526372107734</v>
       </c>
       <c r="P33" t="n">
-        <v>189.7435897435898</v>
+        <v>187.8183831672204</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.5</v>
+        <v>4.083333333333333</v>
       </c>
       <c r="R33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="S33" t="n">
-        <v>180.2510347941071</v>
+        <v>176.8750401881282</v>
       </c>
       <c r="T33" t="n">
-        <v>0.5087351181077601</v>
+        <v>0.6516481255066526</v>
       </c>
       <c r="U33" t="n">
         <v>182.3083787234438</v>
@@ -3335,7 +3335,7 @@
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3359,52 +3359,52 @@
         <v>2026</v>
       </c>
       <c r="E34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G34" t="n">
-        <v>157.0880607143566</v>
+        <v>156.0829422059128</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5151377343414262</v>
+        <v>0.6589674712418576</v>
       </c>
       <c r="I34" t="n">
         <v>169.6571057340244</v>
       </c>
       <c r="J34" t="n">
-        <v>170.9330944059021</v>
+        <v>171.1311227876345</v>
       </c>
       <c r="K34" t="n">
-        <v>2.646025138296189</v>
+        <v>3.137910561965469</v>
       </c>
       <c r="L34" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M34" t="n">
-        <v>167.5100569928156</v>
+        <v>168.4256150656863</v>
       </c>
       <c r="N34" t="n">
-        <v>5.717391304347826</v>
+        <v>6.5</v>
       </c>
       <c r="O34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="P34" t="n">
-        <v>167.5100569928156</v>
+        <v>168.4256150656863</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.717391304347826</v>
+        <v>6.5</v>
       </c>
       <c r="R34" t="n">
         <v>195.2398047728465</v>
       </c>
       <c r="S34" t="n">
-        <v>152.4983711525398</v>
+        <v>153.1386443458626</v>
       </c>
       <c r="T34" t="n">
-        <v>0.7121254488184438</v>
+        <v>1.117764354865418</v>
       </c>
       <c r="U34" t="n">
         <v>176.7243686471345</v>
@@ -3420,11 +3420,11 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>157.0880607143566</v>
+        <v>156.0829422059128</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=157.09% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=156.08% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -3448,52 +3448,52 @@
         <v>2026</v>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F35" t="n">
         <v>18</v>
       </c>
       <c r="G35" t="n">
-        <v>113.2848554010246</v>
+        <v>116.8979864259819</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6558033861263876</v>
+        <v>0.6414754500263838</v>
       </c>
       <c r="I35" t="n">
         <v>48.55849570822402</v>
       </c>
       <c r="J35" t="n">
-        <v>126.6760925192243</v>
+        <v>129.7312553309233</v>
       </c>
       <c r="K35" t="n">
-        <v>1.025372215368218</v>
+        <v>1.152761421673629</v>
       </c>
       <c r="L35" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M35" t="n">
-        <v>190.4538676034567</v>
+        <v>190.8516231199793</v>
       </c>
       <c r="N35" t="n">
-        <v>31.47006673612028</v>
+        <v>31.76489407303251</v>
       </c>
       <c r="O35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="P35" t="n">
-        <v>197.9608001345832</v>
+        <v>198.0457667956422</v>
       </c>
       <c r="Q35" t="n">
-        <v>170.9799005052389</v>
+        <v>170.9807379841873</v>
       </c>
       <c r="R35" t="n">
         <v>185.853149170162</v>
       </c>
       <c r="S35" t="n">
-        <v>135.8763646985932</v>
+        <v>138.5481828361519</v>
       </c>
       <c r="T35" t="n">
-        <v>2.572579880569255</v>
+        <v>2.967085931556756</v>
       </c>
       <c r="U35" t="n">
         <v>110.5529101365675</v>
@@ -3509,11 +3509,11 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>113.2848554010246</v>
+        <v>116.8979864259819</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=113.28% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=116.90% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
         <v>2026</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F36" t="n">
         <v>9</v>
@@ -3546,43 +3546,43 @@
         <v>165.4537784983441</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4702297935595121</v>
+        <v>0.4506368854945325</v>
       </c>
       <c r="I36" t="n">
         <v>58.86670393327421</v>
       </c>
       <c r="J36" t="n">
-        <v>164.9398927199169</v>
+        <v>166.4007305232537</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7312362484139593</v>
+        <v>0.7167570211664328</v>
       </c>
       <c r="L36" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M36" t="n">
-        <v>186.1695209808159</v>
+        <v>186.7457909399486</v>
       </c>
       <c r="N36" t="n">
-        <v>9.555762135616817</v>
+        <v>9.734355160027052</v>
       </c>
       <c r="O36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="P36" t="n">
-        <v>198.1506685547728</v>
+        <v>198.2277240316573</v>
       </c>
       <c r="Q36" t="n">
-        <v>83.5338775666923</v>
+        <v>83.80329933474678</v>
       </c>
       <c r="R36" t="n">
         <v>187.2910306593169</v>
       </c>
       <c r="S36" t="n">
-        <v>159.5615302812286</v>
+        <v>161.2464665195107</v>
       </c>
       <c r="T36" t="n">
-        <v>1.513345438955633</v>
+        <v>1.706659111411458</v>
       </c>
       <c r="U36" t="n">
         <v>118.8153464644226</v>
@@ -3624,52 +3624,52 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
         <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>158.1198732419379</v>
+        <v>159.8648785235238</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5562682868815395</v>
+        <v>0.5375794385995696</v>
       </c>
       <c r="I37" t="n">
         <v>60.32903496111531</v>
       </c>
       <c r="J37" t="n">
-        <v>168.609042931008</v>
+        <v>169.9169994755493</v>
       </c>
       <c r="K37" t="n">
-        <v>1.044320482672119</v>
+        <v>1.062051652510472</v>
       </c>
       <c r="L37" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M37" t="n">
-        <v>184.015453028793</v>
+        <v>184.68147581926</v>
       </c>
       <c r="N37" t="n">
-        <v>9.787898060304089</v>
+        <v>9.933022199180121</v>
       </c>
       <c r="O37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="P37" t="n">
-        <v>197.7835728589555</v>
+        <v>197.8759239898324</v>
       </c>
       <c r="Q37" t="n">
-        <v>88.89743836828053</v>
+        <v>88.56837843626886</v>
       </c>
       <c r="R37" t="n">
         <v>185.3862117422507</v>
       </c>
       <c r="S37" t="n">
-        <v>154.8604157928713</v>
+        <v>156.7412318015016</v>
       </c>
       <c r="T37" t="n">
-        <v>1.553482650555693</v>
+        <v>1.775045998738149</v>
       </c>
       <c r="U37" t="n">
         <v>110.8838400280787</v>
@@ -3711,52 +3711,52 @@
         <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F38" t="n">
         <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>193.3846641790053</v>
+        <v>193.6603031715468</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5239297728687791</v>
+        <v>0.5502117871569219</v>
       </c>
       <c r="I38" t="n">
         <v>164.4263244057969</v>
       </c>
       <c r="J38" t="n">
-        <v>194.6628298773223</v>
+        <v>194.8852119657672</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5992480163143454</v>
+        <v>0.7201488391456481</v>
       </c>
       <c r="L38" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M38" t="n">
-        <v>185.5335968379447</v>
+        <v>186.1363636363636</v>
       </c>
       <c r="N38" t="n">
-        <v>10.84782608695652</v>
+        <v>13.52083333333333</v>
       </c>
       <c r="O38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="P38" t="n">
-        <v>185.5335968379447</v>
+        <v>186.1363636363636</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.84782608695652</v>
+        <v>13.52083333333333</v>
       </c>
       <c r="R38" t="n">
         <v>199.036270909302</v>
       </c>
       <c r="S38" t="n">
-        <v>187.1702787750105</v>
+        <v>187.7048504927184</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5776903847574255</v>
+        <v>0.6418559263963389</v>
       </c>
       <c r="U38" t="n">
         <v>129.2920232398837</v>
@@ -3798,52 +3798,52 @@
         <v>2026</v>
       </c>
       <c r="E39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>198.7706918522422</v>
+        <v>198.8219130250654</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1729726208837764</v>
+        <v>0.1730604370946455</v>
       </c>
       <c r="I39" t="n">
         <v>170.2041702191862</v>
       </c>
       <c r="J39" t="n">
-        <v>199.2947628005335</v>
+        <v>199.3241476838446</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1030238417183106</v>
+        <v>0.09970820878019504</v>
       </c>
       <c r="L39" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M39" t="n">
-        <v>185.4545454545454</v>
+        <v>186.0869565217391</v>
       </c>
       <c r="N39" t="n">
-        <v>5</v>
+        <v>5.854166666666667</v>
       </c>
       <c r="O39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="P39" t="n">
-        <v>185.4545454545454</v>
+        <v>186.0869565217391</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>5.854166666666667</v>
       </c>
       <c r="R39" t="n">
         <v>199.0467638312102</v>
       </c>
       <c r="S39" t="n">
-        <v>195.192700572328</v>
+        <v>195.3930047151476</v>
       </c>
       <c r="T39" t="n">
-        <v>0.2862166282653509</v>
+        <v>0.3098871835001967</v>
       </c>
       <c r="U39" t="n">
         <v>146.152525200624</v>
@@ -3885,52 +3885,52 @@
         <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
         <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>198.2241647400179</v>
+        <v>198.2981578758505</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2392891166621177</v>
+        <v>0.2474889189401752</v>
       </c>
       <c r="I40" t="n">
         <v>165.7522199768573</v>
       </c>
       <c r="J40" t="n">
-        <v>199.6601381173894</v>
+        <v>199.6742990291648</v>
       </c>
       <c r="K40" t="n">
-        <v>0.09725505564008544</v>
+        <v>0.09354414265114504</v>
       </c>
       <c r="L40" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M40" t="n">
-        <v>188.695652173913</v>
+        <v>189.1666666666667</v>
       </c>
       <c r="N40" t="n">
-        <v>6.239130434782608</v>
+        <v>8.041666666666666</v>
       </c>
       <c r="O40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="P40" t="n">
-        <v>188.695652173913</v>
+        <v>189.1666666666667</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.239130434782608</v>
+        <v>8.041666666666666</v>
       </c>
       <c r="R40" t="n">
         <v>198.942356787496</v>
       </c>
       <c r="S40" t="n">
-        <v>195.354014547803</v>
+        <v>195.5475972749778</v>
       </c>
       <c r="T40" t="n">
-        <v>0.3232036678554339</v>
+        <v>0.360091758570227</v>
       </c>
       <c r="U40" t="n">
         <v>124.2002492905602</v>
@@ -3972,52 +3972,52 @@
         <v>2026</v>
       </c>
       <c r="E41" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F41" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G41" t="n">
-        <v>82.72779030325239</v>
+        <v>82.36181669230595</v>
       </c>
       <c r="H41" t="n">
-        <v>2.205068090204341</v>
+        <v>2.315633934912618</v>
       </c>
       <c r="I41" t="n">
         <v>127.4617865350128</v>
       </c>
       <c r="J41" t="n">
-        <v>83.2708876044556</v>
+        <v>80.67815950615892</v>
       </c>
       <c r="K41" t="n">
-        <v>1.811546819726689</v>
+        <v>1.807472114623043</v>
       </c>
       <c r="L41" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M41" t="n">
-        <v>183.2704771757123</v>
+        <v>183.2156609274762</v>
       </c>
       <c r="N41" t="n">
-        <v>72.32608695652173</v>
+        <v>76.875</v>
       </c>
       <c r="O41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="P41" t="n">
-        <v>183.2704771757123</v>
+        <v>183.2156609274762</v>
       </c>
       <c r="Q41" t="n">
-        <v>72.32608695652173</v>
+        <v>76.875</v>
       </c>
       <c r="R41" t="n">
         <v>198.8825072752037</v>
       </c>
       <c r="S41" t="n">
-        <v>68.94662220594313</v>
+        <v>67.99944625466701</v>
       </c>
       <c r="T41" t="n">
-        <v>1.633128644014865</v>
+        <v>1.790465524326272</v>
       </c>
       <c r="U41" t="n">
         <v>124.7888620818299</v>
@@ -4033,11 +4033,11 @@
         </is>
       </c>
       <c r="X41" t="n">
-        <v>68.94662220594313</v>
+        <v>67.99944625466701</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=68.95% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=68.00% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -4061,52 +4061,52 @@
         <v>2026</v>
       </c>
       <c r="E42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F42" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G42" t="n">
-        <v>104.1026920736107</v>
+        <v>102.7675015291024</v>
       </c>
       <c r="H42" t="n">
-        <v>1.296501311921143</v>
+        <v>1.330768077642003</v>
       </c>
       <c r="I42" t="n">
         <v>139.5371944473096</v>
       </c>
       <c r="J42" t="n">
-        <v>156.615136406059</v>
+        <v>156.8485070497925</v>
       </c>
       <c r="K42" t="n">
-        <v>1.590515636108311</v>
+        <v>1.673525259402368</v>
       </c>
       <c r="L42" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M42" t="n">
-        <v>181.2013484684743</v>
+        <v>181.200311890131</v>
       </c>
       <c r="N42" t="n">
-        <v>32.21739130434783</v>
+        <v>34.08333333333334</v>
       </c>
       <c r="O42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="P42" t="n">
-        <v>181.2013484684743</v>
+        <v>181.200311890131</v>
       </c>
       <c r="Q42" t="n">
-        <v>32.21739130434783</v>
+        <v>34.08333333333334</v>
       </c>
       <c r="R42" t="n">
         <v>198.6803521667581</v>
       </c>
       <c r="S42" t="n">
-        <v>87.18884383126479</v>
+        <v>84.50088578046086</v>
       </c>
       <c r="T42" t="n">
-        <v>0.747015619254191</v>
+        <v>0.7585201957721628</v>
       </c>
       <c r="U42" t="n">
         <v>125.9010082864909</v>
@@ -4122,11 +4122,11 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>87.18884383126479</v>
+        <v>84.50088578046086</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=87.19% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=84.50% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -4150,52 +4150,52 @@
         <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F43" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G43" t="n">
-        <v>88.26598834050192</v>
+        <v>87.28106962397432</v>
       </c>
       <c r="H43" t="n">
-        <v>1.287595910820883</v>
+        <v>1.335705207861408</v>
       </c>
       <c r="I43" t="n">
         <v>137.8269504556986</v>
       </c>
       <c r="J43" t="n">
-        <v>127.4417016791812</v>
+        <v>125.1681580974914</v>
       </c>
       <c r="K43" t="n">
-        <v>1.34725603985074</v>
+        <v>1.402398755290558</v>
       </c>
       <c r="L43" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M43" t="n">
-        <v>186.2893573502836</v>
+        <v>186.1328320895093</v>
       </c>
       <c r="N43" t="n">
-        <v>41.54347826086956</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="O43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="P43" t="n">
-        <v>186.2893573502836</v>
+        <v>186.1328320895093</v>
       </c>
       <c r="Q43" t="n">
-        <v>41.54347826086956</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="R43" t="n">
         <v>198.9631246433146</v>
       </c>
       <c r="S43" t="n">
-        <v>80.11092782082243</v>
+        <v>79.0378561004004</v>
       </c>
       <c r="T43" t="n">
-        <v>0.9713696197997124</v>
+        <v>1.086405372344756</v>
       </c>
       <c r="U43" t="n">
         <v>126.6160396504699</v>
@@ -4211,11 +4211,11 @@
         </is>
       </c>
       <c r="X43" t="n">
-        <v>80.11092782082243</v>
+        <v>79.0378561004004</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=80.11% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=79.04% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -4239,52 +4239,52 @@
         <v>2026</v>
       </c>
       <c r="E44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F44" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G44" t="n">
-        <v>102.5913204693476</v>
+        <v>101.4106959347236</v>
       </c>
       <c r="H44" t="n">
-        <v>3.54781187482808</v>
+        <v>3.596832160579731</v>
       </c>
       <c r="I44" t="n">
         <v>101.902133963665</v>
       </c>
       <c r="J44" t="n">
-        <v>106.7058072665996</v>
+        <v>102.2728260688832</v>
       </c>
       <c r="K44" t="n">
-        <v>1.77103799103927</v>
+        <v>1.69776768391928</v>
       </c>
       <c r="L44" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M44" t="n">
-        <v>185.942217792085</v>
+        <v>186.1511073484419</v>
       </c>
       <c r="N44" t="n">
-        <v>79.4301274678176</v>
+        <v>83.15822230584824</v>
       </c>
       <c r="O44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="P44" t="n">
-        <v>185.9779150045329</v>
+        <v>186.3314880385136</v>
       </c>
       <c r="Q44" t="n">
-        <v>82.95652173913044</v>
+        <v>91.20833333333333</v>
       </c>
       <c r="R44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="S44" t="n">
-        <v>91.20043864530405</v>
+        <v>94.32385183734597</v>
       </c>
       <c r="T44" t="n">
-        <v>3.522292112030377</v>
+        <v>5.012388893725952</v>
       </c>
       <c r="U44" t="n">
         <v>121.0188473841644</v>
@@ -4300,11 +4300,11 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>91.20043864530405</v>
+        <v>94.32385183734597</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=91.20% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=94.32% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -4328,52 +4328,52 @@
         <v>2026</v>
       </c>
       <c r="E45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F45" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G45" t="n">
-        <v>122.3160069363318</v>
+        <v>123.6540232660805</v>
       </c>
       <c r="H45" t="n">
-        <v>3.149067529114105</v>
+        <v>3.300247891535429</v>
       </c>
       <c r="I45" t="n">
         <v>133.2410714461222</v>
       </c>
       <c r="J45" t="n">
-        <v>130.2208490932587</v>
+        <v>127.8483953239954</v>
       </c>
       <c r="K45" t="n">
-        <v>1.366357758115597</v>
+        <v>1.331772445537866</v>
       </c>
       <c r="L45" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M45" t="n">
-        <v>183.7309562954249</v>
+        <v>184.2343130466408</v>
       </c>
       <c r="N45" t="n">
-        <v>39.28260869565217</v>
+        <v>41.54166666666666</v>
       </c>
       <c r="O45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="P45" t="n">
-        <v>183.7309562954249</v>
+        <v>184.2343130466408</v>
       </c>
       <c r="Q45" t="n">
-        <v>39.28260869565217</v>
+        <v>41.54166666666666</v>
       </c>
       <c r="R45" t="n">
         <v>195.8311934408034</v>
       </c>
       <c r="S45" t="n">
-        <v>100.1711588658116</v>
+        <v>103.3194889096851</v>
       </c>
       <c r="T45" t="n">
-        <v>1.634375800392914</v>
+        <v>2.169692890302565</v>
       </c>
       <c r="U45" t="n">
         <v>112.5504951429215</v>
@@ -4389,11 +4389,11 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>100.1711588658116</v>
+        <v>103.3194889096851</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=100.17% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=103.32% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -4417,52 +4417,52 @@
         <v>2026</v>
       </c>
       <c r="E46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F46" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G46" t="n">
-        <v>135.7367315420406</v>
+        <v>133.1211168205784</v>
       </c>
       <c r="H46" t="n">
-        <v>2.70010287577914</v>
+        <v>2.731181544234872</v>
       </c>
       <c r="I46" t="n">
         <v>129.1401202444324</v>
       </c>
       <c r="J46" t="n">
-        <v>151.5660132383503</v>
+        <v>146.232019798444</v>
       </c>
       <c r="K46" t="n">
-        <v>1.122142766855141</v>
+        <v>1.101723379072723</v>
       </c>
       <c r="L46" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M46" t="n">
-        <v>187.4330170603259</v>
+        <v>187.5288824711572</v>
       </c>
       <c r="N46" t="n">
-        <v>42.72432800067003</v>
+        <v>45.5644927119441</v>
       </c>
       <c r="O46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="P46" t="n">
-        <v>187.45470889511</v>
+        <v>187.7190314249972</v>
       </c>
       <c r="Q46" t="n">
-        <v>43.93478260869565</v>
+        <v>49.91666666666666</v>
       </c>
       <c r="R46" t="n">
         <v>196.1388328305384</v>
       </c>
       <c r="S46" t="n">
-        <v>123.8234213213976</v>
+        <v>125.2530483618128</v>
       </c>
       <c r="T46" t="n">
-        <v>1.908771523870075</v>
+        <v>2.773539326140427</v>
       </c>
       <c r="U46" t="n">
         <v>125.7491255686458</v>
@@ -4478,11 +4478,11 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>123.8234213213976</v>
+        <v>125.2530483618128</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=123.82% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=125.25% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4506,7 @@
         <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F47" t="n">
         <v>4</v>
@@ -4515,43 +4515,43 @@
         <v>196.5209543145911</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2221182258635011</v>
+        <v>0.2128632997858552</v>
       </c>
       <c r="I47" t="n">
         <v>52.02932925897922</v>
       </c>
       <c r="J47" t="n">
-        <v>190.2559898730695</v>
+        <v>190.661990295025</v>
       </c>
       <c r="K47" t="n">
-        <v>1.130426493699136</v>
+        <v>1.402523974264165</v>
       </c>
       <c r="L47" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M47" t="n">
-        <v>197.9629028613394</v>
+        <v>198.0477819087835</v>
       </c>
       <c r="N47" t="n">
-        <v>29.27883831116923</v>
+        <v>30.30731738479767</v>
       </c>
       <c r="O47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="P47" t="n">
-        <v>198.7991070912838</v>
+        <v>198.8491442958136</v>
       </c>
       <c r="Q47" t="n">
-        <v>56.30434782608695</v>
+        <v>63.56306315862759</v>
       </c>
       <c r="R47" t="n">
         <v>193.8459595711977</v>
       </c>
       <c r="S47" t="n">
-        <v>185.1329876177941</v>
+        <v>185.7524464670526</v>
       </c>
       <c r="T47" t="n">
-        <v>1.704194556920437</v>
+        <v>2.17706222844933</v>
       </c>
       <c r="U47" t="n">
         <v>130.8486591703272</v>
@@ -4593,7 +4593,7 @@
         <v>2026</v>
       </c>
       <c r="E48" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
@@ -4602,43 +4602,43 @@
         <v>197.4116289114259</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1023276437901485</v>
+        <v>0.09806399196555902</v>
       </c>
       <c r="I48" t="n">
         <v>75.82494372432545</v>
       </c>
       <c r="J48" t="n">
-        <v>198.7881710166683</v>
+        <v>198.8386638909737</v>
       </c>
       <c r="K48" t="n">
-        <v>0.3272215899392314</v>
+        <v>0.4766963579860826</v>
       </c>
       <c r="L48" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M48" t="n">
-        <v>197.7017619833397</v>
+        <v>197.7975219007006</v>
       </c>
       <c r="N48" t="n">
-        <v>13.86763525488404</v>
+        <v>14.21611750782219</v>
       </c>
       <c r="O48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="P48" t="n">
-        <v>198.0792674084108</v>
+        <v>198.1592979330603</v>
       </c>
       <c r="Q48" t="n">
-        <v>23.84235614989821</v>
+        <v>26.69742465512154</v>
       </c>
       <c r="R48" t="n">
         <v>192.3368460426438</v>
       </c>
       <c r="S48" t="n">
-        <v>192.6544386441733</v>
+        <v>192.960503700666</v>
       </c>
       <c r="T48" t="n">
-        <v>1.487823412839192</v>
+        <v>1.916144240073933</v>
       </c>
       <c r="U48" t="n">
         <v>148.2729860112375</v>
@@ -4680,7 +4680,7 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
@@ -4689,43 +4689,43 @@
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.107685232382714</v>
+        <v>0.103198347700101</v>
       </c>
       <c r="I49" t="n">
         <v>67.54170898302603</v>
       </c>
       <c r="J49" t="n">
-        <v>192.9933706852672</v>
+        <v>193.285313573381</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7616750114464241</v>
+        <v>0.9947434210124114</v>
       </c>
       <c r="L49" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M49" t="n">
-        <v>198.7084920295648</v>
+        <v>198.7623048616662</v>
       </c>
       <c r="N49" t="n">
-        <v>16.33837133214592</v>
+        <v>16.99260096397655</v>
       </c>
       <c r="O49" t="n">
         <v>179.6516960231333</v>
       </c>
       <c r="P49" t="n">
-        <v>199.5066175560497</v>
+        <v>199.527175157881</v>
       </c>
       <c r="Q49" t="n">
-        <v>31.67391304347826</v>
+        <v>34.85190379153376</v>
       </c>
       <c r="R49" t="n">
         <v>193.5695579772771</v>
       </c>
       <c r="S49" t="n">
-        <v>190.7776968167292</v>
+        <v>191.1619594493655</v>
       </c>
       <c r="T49" t="n">
-        <v>1.045974666730537</v>
+        <v>1.287354175399031</v>
       </c>
       <c r="U49" t="n">
         <v>141.2583029624075</v>
@@ -4767,52 +4767,52 @@
         <v>2026</v>
       </c>
       <c r="E50" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F50" t="n">
         <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>189.7994969033458</v>
+        <v>190.2245178657064</v>
       </c>
       <c r="H50" t="n">
-        <v>3.869851488063552</v>
+        <v>4.532822588444636</v>
       </c>
       <c r="I50" t="n">
         <v>162.6912701840232</v>
       </c>
       <c r="J50" t="n">
-        <v>196.7614499456022</v>
+        <v>196.8963895312021</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3455874680551403</v>
+        <v>0.3344503561427851</v>
       </c>
       <c r="L50" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M50" t="n">
-        <v>191.147728062793</v>
+        <v>192.2542620549439</v>
       </c>
       <c r="N50" t="n">
-        <v>7.312309513921323</v>
+        <v>9.146953662236532</v>
       </c>
       <c r="O50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="P50" t="n">
-        <v>193.4135280554246</v>
+        <v>193.6879643864485</v>
       </c>
       <c r="Q50" t="n">
-        <v>13.03107782436076</v>
+        <v>14.58561396653528</v>
       </c>
       <c r="R50" t="n">
         <v>160.5521309789579</v>
       </c>
       <c r="S50" t="n">
-        <v>190.5537618513702</v>
+        <v>190.9473551075631</v>
       </c>
       <c r="T50" t="n">
-        <v>14.06025828632104</v>
+        <v>17.2298443262551</v>
       </c>
       <c r="U50" t="n">
         <v>135.4400555181058</v>
@@ -4854,52 +4854,52 @@
         <v>2026</v>
       </c>
       <c r="E51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>189.7784228856569</v>
+        <v>190.2043219320878</v>
       </c>
       <c r="H51" t="n">
-        <v>1.466018721053983</v>
+        <v>1.662514124286943</v>
       </c>
       <c r="I51" t="n">
         <v>169.9274838481079</v>
       </c>
       <c r="J51" t="n">
-        <v>184.7710950335155</v>
+        <v>185.4056327404524</v>
       </c>
       <c r="K51" t="n">
-        <v>0.189051601077927</v>
+        <v>0.2217234068381974</v>
       </c>
       <c r="L51" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M51" t="n">
-        <v>195.8955584201071</v>
+        <v>196.0740124018415</v>
       </c>
       <c r="N51" t="n">
-        <v>13.2393867157233</v>
+        <v>13.87524560256816</v>
       </c>
       <c r="O51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="P51" t="n">
-        <v>192.8527800555265</v>
+        <v>193.1635287487645</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.731702148524894</v>
+        <v>5.310507974087312</v>
       </c>
       <c r="R51" t="n">
         <v>165.5121650610737</v>
       </c>
       <c r="S51" t="n">
-        <v>189.680701432455</v>
+        <v>190.1106722061027</v>
       </c>
       <c r="T51" t="n">
-        <v>6.219254369252377</v>
+        <v>7.645007009384247</v>
       </c>
       <c r="U51" t="n">
         <v>151.1230387281904</v>
@@ -4941,52 +4941,52 @@
         <v>2026</v>
       </c>
       <c r="E52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F52" t="n">
         <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>188.9622851709017</v>
+        <v>189.4221899554474</v>
       </c>
       <c r="H52" t="n">
-        <v>2.19100280753381</v>
+        <v>2.594455221952179</v>
       </c>
       <c r="I52" t="n">
         <v>174.432365021141</v>
       </c>
       <c r="J52" t="n">
-        <v>199.1565596561415</v>
+        <v>199.1917030038023</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1833099189597912</v>
+        <v>0.177983292756472</v>
       </c>
       <c r="L52" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M52" t="n">
-        <v>196.5348518483145</v>
+        <v>196.692358582482</v>
       </c>
       <c r="N52" t="n">
-        <v>20.20863496794401</v>
+        <v>21.74160851094635</v>
       </c>
       <c r="O52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="P52" t="n">
-        <v>192.2138596845881</v>
+        <v>192.5677751534704</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.843596540696626</v>
+        <v>7.788443947555142</v>
       </c>
       <c r="R52" t="n">
         <v>154.7555469695623</v>
       </c>
       <c r="S52" t="n">
-        <v>191.2056469997896</v>
+        <v>191.5720783747983</v>
       </c>
       <c r="T52" t="n">
-        <v>10.57367013666008</v>
+        <v>13.39175311243195</v>
       </c>
       <c r="U52" t="n">
         <v>133.8716916594558</v>
@@ -5028,52 +5028,52 @@
         <v>2026</v>
       </c>
       <c r="E53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F53" t="n">
-        <v>2696</v>
+        <v>2840</v>
       </c>
       <c r="G53" t="n">
-        <v>19.4402932458659</v>
+        <v>19.81317872296284</v>
       </c>
       <c r="H53" t="n">
-        <v>23.63699715423957</v>
+        <v>24.63728416607406</v>
       </c>
       <c r="I53" t="n">
         <v>35.23746831954708</v>
       </c>
       <c r="J53" t="n">
-        <v>17.8172358714134</v>
+        <v>18.21180301884046</v>
       </c>
       <c r="K53" t="n">
-        <v>19.90194493285133</v>
+        <v>20.51335326459974</v>
       </c>
       <c r="L53" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M53" t="n">
-        <v>162.8856277742575</v>
+        <v>163.498571035511</v>
       </c>
       <c r="N53" t="n">
-        <v>1061.978260869565</v>
+        <v>1112.854166666667</v>
       </c>
       <c r="O53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="P53" t="n">
-        <v>162.8856277742575</v>
+        <v>163.498571035511</v>
       </c>
       <c r="Q53" t="n">
-        <v>1061.978260869565</v>
+        <v>1112.854166666667</v>
       </c>
       <c r="R53" t="n">
         <v>188.2648408233968</v>
       </c>
       <c r="S53" t="n">
-        <v>42.50348384326168</v>
+        <v>45.99685526730337</v>
       </c>
       <c r="T53" t="n">
-        <v>78.57314109556394</v>
+        <v>95.88333984517892</v>
       </c>
       <c r="U53" t="n">
         <v>92.2349408254034</v>
@@ -5089,11 +5089,11 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>17.8172358714134</v>
+        <v>18.21180301884046</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=17.82% sobre 23 sem</t>
+          <t>DeepAR: menor SMAPE real=18.21% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5117,52 +5117,52 @@
         <v>2026</v>
       </c>
       <c r="E54" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F54" t="n">
-        <v>1271</v>
+        <v>1332</v>
       </c>
       <c r="G54" t="n">
-        <v>20.72754113641285</v>
+        <v>20.15918071164578</v>
       </c>
       <c r="H54" t="n">
-        <v>11.79391705998009</v>
+        <v>11.48924610389167</v>
       </c>
       <c r="I54" t="n">
         <v>38.4591918317379</v>
       </c>
       <c r="J54" t="n">
-        <v>22.70335561200558</v>
+        <v>23.61771749479679</v>
       </c>
       <c r="K54" t="n">
-        <v>13.49333944868383</v>
+        <v>14.39206329784811</v>
       </c>
       <c r="L54" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M54" t="n">
-        <v>162.7510613149525</v>
+        <v>163.381789446615</v>
       </c>
       <c r="N54" t="n">
-        <v>490.0217391304348</v>
+        <v>510.5</v>
       </c>
       <c r="O54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="P54" t="n">
-        <v>162.7510613149525</v>
+        <v>163.381789446615</v>
       </c>
       <c r="Q54" t="n">
-        <v>490.0217391304348</v>
+        <v>510.5</v>
       </c>
       <c r="R54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="S54" t="n">
-        <v>42.12132287974038</v>
+        <v>45.7020281333458</v>
       </c>
       <c r="T54" t="n">
-        <v>35.35053273428665</v>
+        <v>42.92606372582961</v>
       </c>
       <c r="U54" t="n">
         <v>91.67135817890519</v>
@@ -5178,11 +5178,11 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>20.72754113641285</v>
+        <v>20.15918071164578</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=20.73% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=20.16% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5206,52 +5206,52 @@
         <v>2026</v>
       </c>
       <c r="E55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F55" t="n">
-        <v>1420</v>
+        <v>1503</v>
       </c>
       <c r="G55" t="n">
-        <v>23.55506705210731</v>
+        <v>23.01187674672067</v>
       </c>
       <c r="H55" t="n">
-        <v>14.04258120989469</v>
+        <v>13.8414317572904</v>
       </c>
       <c r="I55" t="n">
         <v>38.25160771522186</v>
       </c>
       <c r="J55" t="n">
-        <v>24.82026751275703</v>
+        <v>26.02651666734207</v>
       </c>
       <c r="K55" t="n">
-        <v>15.62374331453546</v>
+        <v>17.51608646817878</v>
       </c>
       <c r="L55" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M55" t="n">
-        <v>163.1038272712023</v>
+        <v>163.6985215778323</v>
       </c>
       <c r="N55" t="n">
-        <v>572.1739130434783</v>
+        <v>602.5625</v>
       </c>
       <c r="O55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="P55" t="n">
-        <v>163.1038272712023</v>
+        <v>163.6985215778323</v>
       </c>
       <c r="Q55" t="n">
-        <v>572.1739130434783</v>
+        <v>602.5625</v>
       </c>
       <c r="R55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="S55" t="n">
-        <v>40.15519558781323</v>
+        <v>43.6062374418027</v>
       </c>
       <c r="T55" t="n">
-        <v>39.84661362628754</v>
+        <v>49.23042089827342</v>
       </c>
       <c r="U55" t="n">
         <v>92.1901984902002</v>
@@ -5267,11 +5267,11 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>23.55506705210731</v>
+        <v>23.01187674672067</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=23.56% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=23.01% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5295,52 +5295,52 @@
         <v>2026</v>
       </c>
       <c r="E56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="G56" t="n">
-        <v>70.75000240776146</v>
+        <v>72.02356238360656</v>
       </c>
       <c r="H56" t="n">
-        <v>3.072888443060451</v>
+        <v>3.287071266976904</v>
       </c>
       <c r="I56" t="n">
         <v>154.1439500713238</v>
       </c>
       <c r="J56" t="n">
-        <v>68.35169810424058</v>
+        <v>68.30227160802244</v>
       </c>
       <c r="K56" t="n">
-        <v>2.256310476171245</v>
+        <v>2.246097620761395</v>
       </c>
       <c r="L56" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M56" t="n">
-        <v>168.6347902417901</v>
+        <v>169.4835575273476</v>
       </c>
       <c r="N56" t="n">
-        <v>53.86626925227143</v>
+        <v>57.35198327273171</v>
       </c>
       <c r="O56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="P56" t="n">
-        <v>168.6528173016046</v>
+        <v>169.5174488102849</v>
       </c>
       <c r="Q56" t="n">
-        <v>54.10869565217391</v>
+        <v>57.8125</v>
       </c>
       <c r="R56" t="n">
         <v>197.7368060568652</v>
       </c>
       <c r="S56" t="n">
-        <v>55.95075362148568</v>
+        <v>57.20235627657991</v>
       </c>
       <c r="T56" t="n">
-        <v>1.736058086714748</v>
+        <v>1.76394664475274</v>
       </c>
       <c r="U56" t="n">
         <v>104.7066447751141</v>
@@ -5356,11 +5356,11 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>55.95075362148568</v>
+        <v>57.20235627657991</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=55.95% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=57.20% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5384,52 +5384,52 @@
         <v>2026</v>
       </c>
       <c r="E57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F57" t="n">
         <v>38</v>
       </c>
       <c r="G57" t="n">
-        <v>90.17983228652754</v>
+        <v>94.75567260792225</v>
       </c>
       <c r="H57" t="n">
-        <v>1.552291662272906</v>
+        <v>1.675103479712558</v>
       </c>
       <c r="I57" t="n">
         <v>164.0555422208552</v>
       </c>
       <c r="J57" t="n">
-        <v>127.8315821153468</v>
+        <v>130.8385995272074</v>
       </c>
       <c r="K57" t="n">
-        <v>1.568792435141413</v>
+        <v>1.519977565318321</v>
       </c>
       <c r="L57" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M57" t="n">
-        <v>166.9763237835721</v>
+        <v>168.3523102925899</v>
       </c>
       <c r="N57" t="n">
-        <v>23</v>
+        <v>24.60416666666667</v>
       </c>
       <c r="O57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="P57" t="n">
-        <v>166.9763237835721</v>
+        <v>168.3523102925899</v>
       </c>
       <c r="Q57" t="n">
-        <v>23</v>
+        <v>24.60416666666667</v>
       </c>
       <c r="R57" t="n">
         <v>197.2831175654684</v>
       </c>
       <c r="S57" t="n">
-        <v>97.4505612721191</v>
+        <v>101.7234545524474</v>
       </c>
       <c r="T57" t="n">
-        <v>0.9584128892904199</v>
+        <v>0.9429043330170425</v>
       </c>
       <c r="U57" t="n">
         <v>124.2225772452616</v>
@@ -5445,11 +5445,11 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>90.17983228652754</v>
+        <v>94.75567260792225</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=90.18% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=94.76% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5473,52 +5473,52 @@
         <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F58" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G58" t="n">
-        <v>89.98534646608356</v>
+        <v>88.8688213896983</v>
       </c>
       <c r="H58" t="n">
-        <v>1.899959525298533</v>
+        <v>1.97475055418743</v>
       </c>
       <c r="I58" t="n">
         <v>158.4722608607674</v>
       </c>
       <c r="J58" t="n">
-        <v>117.5749584956436</v>
+        <v>120.6941795478983</v>
       </c>
       <c r="K58" t="n">
-        <v>1.751557513723373</v>
+        <v>1.842030318086942</v>
       </c>
       <c r="L58" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M58" t="n">
-        <v>170.5894451766619</v>
+        <v>171.0700060037982</v>
       </c>
       <c r="N58" t="n">
-        <v>31.56521739130435</v>
+        <v>33.64583333333334</v>
       </c>
       <c r="O58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="P58" t="n">
-        <v>170.5894451766619</v>
+        <v>171.0700060037982</v>
       </c>
       <c r="Q58" t="n">
-        <v>31.56521739130435</v>
+        <v>33.64583333333334</v>
       </c>
       <c r="R58" t="n">
         <v>197.6615055783608</v>
       </c>
       <c r="S58" t="n">
-        <v>88.93515152944408</v>
+        <v>89.73059687062958</v>
       </c>
       <c r="T58" t="n">
-        <v>1.101417340569095</v>
+        <v>1.172426225870094</v>
       </c>
       <c r="U58" t="n">
         <v>111.9755139895278</v>
@@ -5534,11 +5534,11 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>88.93515152944408</v>
+        <v>89.73059687062958</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=88.94% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=89.73% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
         <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F59" t="n">
         <v>6</v>
@@ -5571,43 +5571,43 @@
         <v>199.5468394226922</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2768506064690763</v>
+        <v>0.2653151645328648</v>
       </c>
       <c r="I59" t="n">
         <v>163.442478475025</v>
       </c>
       <c r="J59" t="n">
-        <v>193.0444133653387</v>
+        <v>193.3342294751162</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2692230842082216</v>
+        <v>0.258391598481908</v>
       </c>
       <c r="L59" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M59" t="n">
-        <v>173.7114845938375</v>
+        <v>174.9064171122995</v>
       </c>
       <c r="N59" t="n">
-        <v>4.956521739130435</v>
+        <v>5.875</v>
       </c>
       <c r="O59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="P59" t="n">
-        <v>173.7114845938375</v>
+        <v>174.9064171122995</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.956521739130435</v>
+        <v>5.875</v>
       </c>
       <c r="R59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="S59" t="n">
-        <v>172.5221446786796</v>
+        <v>173.6670553170678</v>
       </c>
       <c r="T59" t="n">
-        <v>0.3958316615589348</v>
+        <v>0.450879453393054</v>
       </c>
       <c r="U59" t="n">
         <v>167.6265476269683</v>
@@ -5649,7 +5649,7 @@
         <v>2026</v>
       </c>
       <c r="E60" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -5658,43 +5658,43 @@
         <v>197.8217646398928</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1861571669557376</v>
+        <v>0.1784006183325819</v>
       </c>
       <c r="I60" t="n">
         <v>179.6544870721095</v>
       </c>
       <c r="J60" t="n">
-        <v>198.6906461944827</v>
+        <v>198.7452026030459</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1812997704605782</v>
+        <v>0.1741067871157174</v>
       </c>
       <c r="L60" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M60" t="n">
-        <v>168.4033613445378</v>
+        <v>170.1587301587302</v>
       </c>
       <c r="N60" t="n">
-        <v>2.891304347826087</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="O60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="P60" t="n">
-        <v>168.4033613445378</v>
+        <v>170.1587301587302</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.891304347826087</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R60" t="n">
         <v>199.0965028052728</v>
       </c>
       <c r="S60" t="n">
-        <v>186.0449066994106</v>
+        <v>186.6263689202685</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2820691686391204</v>
+        <v>0.2999967515724015</v>
       </c>
       <c r="U60" t="n">
         <v>167.0169829765832</v>
@@ -5736,7 +5736,7 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -5745,43 +5745,43 @@
         <v>199.9531681019307</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1050963268559129</v>
+        <v>0.1007173132369165</v>
       </c>
       <c r="I61" t="n">
         <v>178.3754768379913</v>
       </c>
       <c r="J61" t="n">
-        <v>197.1877208886168</v>
+        <v>197.3048991849245</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1635155699790316</v>
+        <v>0.1602251162734526</v>
       </c>
       <c r="L61" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M61" t="n">
-        <v>182.6666666666667</v>
+        <v>183.75</v>
       </c>
       <c r="N61" t="n">
-        <v>2.260869565217391</v>
+        <v>2.729166666666667</v>
       </c>
       <c r="O61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="P61" t="n">
-        <v>182.6666666666667</v>
+        <v>183.75</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.260869565217391</v>
+        <v>2.729166666666667</v>
       </c>
       <c r="R61" t="n">
         <v>199.3694289811982</v>
       </c>
       <c r="S61" t="n">
-        <v>190.609444133645</v>
+        <v>191.0007172947431</v>
       </c>
       <c r="T61" t="n">
-        <v>0.2084494288028756</v>
+        <v>0.2421981990418275</v>
       </c>
       <c r="U61" t="n">
         <v>167.1297521794813</v>
@@ -5823,52 +5823,52 @@
         <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F62" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G62" t="n">
-        <v>119.2277209283495</v>
+        <v>115.0714960980425</v>
       </c>
       <c r="H62" t="n">
-        <v>0.761352537839095</v>
+        <v>0.7444208963099056</v>
       </c>
       <c r="I62" t="n">
         <v>51.86246745886869</v>
       </c>
       <c r="J62" t="n">
-        <v>133.5624336927553</v>
+        <v>134.4105482127552</v>
       </c>
       <c r="K62" t="n">
-        <v>2.994062352107012</v>
+        <v>3.425978484552677</v>
       </c>
       <c r="L62" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M62" t="n">
-        <v>179.0413583623338</v>
+        <v>179.7158878848481</v>
       </c>
       <c r="N62" t="n">
-        <v>37.16415571126796</v>
+        <v>42.43720076707844</v>
       </c>
       <c r="O62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="P62" t="n">
-        <v>179.1625326908875</v>
+        <v>179.9230212454476</v>
       </c>
       <c r="Q62" t="n">
-        <v>50.27871844864998</v>
+        <v>60.90831139371448</v>
       </c>
       <c r="R62" t="n">
         <v>188.4656733609786</v>
       </c>
       <c r="S62" t="n">
-        <v>122.3084475291242</v>
+        <v>123.840234425149</v>
       </c>
       <c r="T62" t="n">
-        <v>2.05563889704695</v>
+        <v>2.617745701031933</v>
       </c>
       <c r="U62" t="n">
         <v>127.8730185036105</v>
@@ -5884,11 +5884,11 @@
         </is>
       </c>
       <c r="X62" t="n">
-        <v>119.2277209283495</v>
+        <v>115.0714960980425</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=119.23% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=115.07% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -5912,52 +5912,52 @@
         <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>154.0090319989282</v>
+        <v>147.8188112287161</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5195231974902645</v>
+        <v>0.5000845178023875</v>
       </c>
       <c r="I63" t="n">
         <v>69.84803023883232</v>
       </c>
       <c r="J63" t="n">
-        <v>167.1118256355263</v>
+        <v>164.0184235376574</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4428218214418847</v>
+        <v>0.4507962089061189</v>
       </c>
       <c r="L63" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M63" t="n">
-        <v>180.1206671572637</v>
+        <v>180.5376455904877</v>
       </c>
       <c r="N63" t="n">
-        <v>12.15501876333826</v>
+        <v>13.25352849882985</v>
       </c>
       <c r="O63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="P63" t="n">
-        <v>180.3618638239061</v>
+        <v>181.0126881707742</v>
       </c>
       <c r="Q63" t="n">
-        <v>18.35260170399609</v>
+        <v>21.65221409322612</v>
       </c>
       <c r="R63" t="n">
         <v>186.3893216158546</v>
       </c>
       <c r="S63" t="n">
-        <v>140.0878107146123</v>
+        <v>140.7102637875787</v>
       </c>
       <c r="T63" t="n">
-        <v>1.139928270036557</v>
+        <v>1.379688051367461</v>
       </c>
       <c r="U63" t="n">
         <v>131.8859677830883</v>
@@ -5975,7 +5975,7 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5999,52 +5999,52 @@
         <v>2026</v>
       </c>
       <c r="E64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>144.6640924290954</v>
+        <v>141.6564464705618</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7123712842017973</v>
+        <v>0.7300548706756037</v>
       </c>
       <c r="I64" t="n">
         <v>72.92360982323459</v>
       </c>
       <c r="J64" t="n">
-        <v>155.8241243354186</v>
+        <v>155.9307174498431</v>
       </c>
       <c r="K64" t="n">
-        <v>0.9337406050508241</v>
+        <v>1.211972614781416</v>
       </c>
       <c r="L64" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M64" t="n">
-        <v>179.6281987244426</v>
+        <v>180.3182275636854</v>
       </c>
       <c r="N64" t="n">
-        <v>22.62215745018642</v>
+        <v>25.96941433467142</v>
       </c>
       <c r="O64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="P64" t="n">
-        <v>179.7513301297856</v>
+        <v>180.521209708531</v>
       </c>
       <c r="Q64" t="n">
-        <v>32</v>
+        <v>39.99123758256633</v>
       </c>
       <c r="R64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="S64" t="n">
-        <v>142.3844661408978</v>
+        <v>143.5126733326317</v>
       </c>
       <c r="T64" t="n">
-        <v>1.466619050468889</v>
+        <v>1.867934673595985</v>
       </c>
       <c r="U64" t="n">
         <v>132.574641557417</v>
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="X64" t="n">
-        <v>144.6640924290954</v>
+        <v>141.6564464705618</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=144.66% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=141.66% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -6088,52 +6088,52 @@
         <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G65" t="n">
-        <v>157.2615659772668</v>
+        <v>155.480822424112</v>
       </c>
       <c r="H65" t="n">
-        <v>0.6561727716521711</v>
+        <v>0.7502048770932279</v>
       </c>
       <c r="I65" t="n">
         <v>124.1398173354868</v>
       </c>
       <c r="J65" t="n">
-        <v>171.3785789985182</v>
+        <v>170.5715077099328</v>
       </c>
       <c r="K65" t="n">
-        <v>0.559045196864532</v>
+        <v>0.6796958122893066</v>
       </c>
       <c r="L65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="M65" t="n">
-        <v>190.7712059161261</v>
+        <v>190.7006764318506</v>
       </c>
       <c r="N65" t="n">
-        <v>28.28459385160271</v>
+        <v>32.87690244111926</v>
       </c>
       <c r="O65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="P65" t="n">
-        <v>190.8351421727835</v>
+        <v>190.761948677814</v>
       </c>
       <c r="Q65" t="n">
-        <v>29.06521739130435</v>
+        <v>33.625</v>
       </c>
       <c r="R65" t="n">
         <v>191.9303948964172</v>
       </c>
       <c r="S65" t="n">
-        <v>162.49835435417</v>
+        <v>162.284479679222</v>
       </c>
       <c r="T65" t="n">
-        <v>2.911749098649227</v>
+        <v>4.020766697853392</v>
       </c>
       <c r="U65" t="n">
         <v>113.9712651292745</v>
@@ -6149,11 +6149,11 @@
         </is>
       </c>
       <c r="X65" t="n">
-        <v>157.2615659772668</v>
+        <v>155.480822424112</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=157.26% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=155.48% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -6177,52 +6177,52 @@
         <v>2026</v>
       </c>
       <c r="E66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
-        <v>184.891199503253</v>
+        <v>182.2476695665705</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3527404758689708</v>
+        <v>0.3695273264813482</v>
       </c>
       <c r="I66" t="n">
         <v>146.9871894171194</v>
       </c>
       <c r="J66" t="n">
-        <v>182.5534283094383</v>
+        <v>180.3459413036325</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3899194867525623</v>
+        <v>0.4064358027291891</v>
       </c>
       <c r="L66" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M66" t="n">
-        <v>192.1804112614516</v>
+        <v>192.2395607922245</v>
       </c>
       <c r="N66" t="n">
-        <v>12.91304347826087</v>
+        <v>14.89583333333333</v>
       </c>
       <c r="O66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="P66" t="n">
-        <v>192.1804112614516</v>
+        <v>192.2395607922245</v>
       </c>
       <c r="Q66" t="n">
-        <v>12.91304347826087</v>
+        <v>14.89583333333333</v>
       </c>
       <c r="R66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="S66" t="n">
-        <v>175.5600594590176</v>
+        <v>175.4247667889375</v>
       </c>
       <c r="T66" t="n">
-        <v>1.343768581845118</v>
+        <v>1.806412889004299</v>
       </c>
       <c r="U66" t="n">
         <v>118.44057480835</v>
@@ -6240,7 +6240,7 @@
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6264,52 +6264,52 @@
         <v>2026</v>
       </c>
       <c r="E67" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>190.1598108836026</v>
+        <v>187.7521498383148</v>
       </c>
       <c r="H67" t="n">
-        <v>0.4585044062246966</v>
+        <v>0.5389679906118942</v>
       </c>
       <c r="I67" t="n">
         <v>137.6516466078508</v>
       </c>
       <c r="J67" t="n">
-        <v>198.5569003946447</v>
+        <v>196.4080267258852</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4636885009186891</v>
+        <v>0.5502692552689088</v>
       </c>
       <c r="L67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="M67" t="n">
-        <v>193.6590588493686</v>
+        <v>192.8522685320083</v>
       </c>
       <c r="N67" t="n">
-        <v>13.1134702291736</v>
+        <v>14.26230507406671</v>
       </c>
       <c r="O67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="P67" t="n">
-        <v>194.3273435116722</v>
+        <v>194.0260697900837</v>
       </c>
       <c r="Q67" t="n">
-        <v>16.93478260869565</v>
+        <v>19.85416666666667</v>
       </c>
       <c r="R67" t="n">
         <v>191.2393501485975</v>
       </c>
       <c r="S67" t="n">
-        <v>182.6963314834599</v>
+        <v>181.0806839434517</v>
       </c>
       <c r="T67" t="n">
-        <v>1.650403780856818</v>
+        <v>2.223232977114444</v>
       </c>
       <c r="U67" t="n">
         <v>116.630186356802</v>
@@ -6327,7 +6327,7 @@
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
         <v>2026</v>
       </c>
       <c r="E68" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -6360,16 +6360,16 @@
         <v>199.988140539529</v>
       </c>
       <c r="H68" t="n">
-        <v>0.05067713597713177</v>
+        <v>0.04856558864475128</v>
       </c>
       <c r="I68" t="n">
         <v>183.5383709430125</v>
       </c>
       <c r="J68" t="n">
-        <v>199.8205767435873</v>
+        <v>199.8280527126044</v>
       </c>
       <c r="K68" t="n">
-        <v>0.05766034586476899</v>
+        <v>0.05587964844368295</v>
       </c>
       <c r="L68" t="n">
         <v>198.3312090033645</v>
@@ -6378,7 +6378,7 @@
         <v>200</v>
       </c>
       <c r="N68" t="n">
-        <v>6.351737299880702</v>
+        <v>6.712081579052339</v>
       </c>
       <c r="O68" t="n">
         <v>188.2784643365136</v>
@@ -6387,16 +6387,16 @@
         <v>200</v>
       </c>
       <c r="Q68" t="n">
-        <v>6.826086956521739</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="R68" t="n">
         <v>199.7672857698158</v>
       </c>
       <c r="S68" t="n">
-        <v>197.2598398301002</v>
+        <v>197.3740131705127</v>
       </c>
       <c r="T68" t="n">
-        <v>0.58784095891447</v>
+        <v>0.6442582695936658</v>
       </c>
       <c r="U68" t="n">
         <v>177.2448922419183</v>
@@ -6438,7 +6438,7 @@
         <v>2026</v>
       </c>
       <c r="E69" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -6447,16 +6447,16 @@
         <v>198.1317768745953</v>
       </c>
       <c r="H69" t="n">
-        <v>0.06708729217756805</v>
+        <v>0.06429198833683604</v>
       </c>
       <c r="I69" t="n">
         <v>171.5447439761989</v>
       </c>
       <c r="J69" t="n">
-        <v>199.4938745189075</v>
+        <v>199.5149630806197</v>
       </c>
       <c r="K69" t="n">
-        <v>0.07028127604290697</v>
+        <v>0.06857957821459099</v>
       </c>
       <c r="L69" t="n">
         <v>194.4182830751776</v>
@@ -6465,7 +6465,7 @@
         <v>200</v>
       </c>
       <c r="N69" t="n">
-        <v>3.108695652173913</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="O69" t="n">
         <v>190.8574288418282</v>
@@ -6474,16 +6474,16 @@
         <v>200</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.108695652173913</v>
+        <v>3.416666666666667</v>
       </c>
       <c r="R69" t="n">
         <v>199.6130972886749</v>
       </c>
       <c r="S69" t="n">
-        <v>198.6193243858683</v>
+        <v>198.6768525364572</v>
       </c>
       <c r="T69" t="n">
-        <v>0.2781863905030194</v>
+        <v>0.3002826763129219</v>
       </c>
       <c r="U69" t="n">
         <v>185.6695408532579</v>
@@ -6525,7 +6525,7 @@
         <v>2026</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -6534,7 +6534,7 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01469593126692173</v>
+        <v>0.01408360079746666</v>
       </c>
       <c r="I70" t="n">
         <v>188.453973372859</v>
@@ -6543,7 +6543,7 @@
         <v>200</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01611177625948345</v>
+        <v>0.01614480047598248</v>
       </c>
       <c r="L70" t="n">
         <v>198.9765474653765</v>
@@ -6552,7 +6552,7 @@
         <v>200</v>
       </c>
       <c r="N70" t="n">
-        <v>3.652500895684062</v>
+        <v>3.687813358363893</v>
       </c>
       <c r="O70" t="n">
         <v>192.937344462188</v>
@@ -6561,7 +6561,7 @@
         <v>200</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.847826086956522</v>
+        <v>3.875</v>
       </c>
       <c r="R70" t="n">
         <v>199.6974055100667</v>
@@ -6570,7 +6570,7 @@
         <v>200</v>
       </c>
       <c r="T70" t="n">
-        <v>0.2883720663686506</v>
+        <v>0.3188993582383924</v>
       </c>
       <c r="U70" t="n">
         <v>184.4638384017739</v>
@@ -6612,52 +6612,52 @@
         <v>2026</v>
       </c>
       <c r="E71" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F71" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G71" t="n">
-        <v>60.84223256271035</v>
+        <v>61.34695045948616</v>
       </c>
       <c r="H71" t="n">
-        <v>3.078949151164985</v>
+        <v>3.084299467974718</v>
       </c>
       <c r="I71" t="n">
         <v>143.4057585362926</v>
       </c>
       <c r="J71" t="n">
-        <v>175.1755208750977</v>
+        <v>173.5415322252807</v>
       </c>
       <c r="K71" t="n">
-        <v>4.541592070852817</v>
+        <v>4.554704402073362</v>
       </c>
       <c r="L71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="M71" t="n">
-        <v>69.78785307192437</v>
+        <v>69.44887372191104</v>
       </c>
       <c r="N71" t="n">
-        <v>4.214327809702388</v>
+        <v>4.261547569775879</v>
       </c>
       <c r="O71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="P71" t="n">
-        <v>189.7258694236534</v>
+        <v>190.1539581976679</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.803539232806779</v>
+        <v>4.853391764773163</v>
       </c>
       <c r="R71" t="n">
         <v>185.267595267154</v>
       </c>
       <c r="S71" t="n">
-        <v>53.34049861321677</v>
+        <v>54.91812707291811</v>
       </c>
       <c r="T71" t="n">
-        <v>4.599205857701338</v>
+        <v>4.826720185282983</v>
       </c>
       <c r="U71" t="n">
         <v>93.16202342284906</v>
@@ -6673,11 +6673,11 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>53.34049861321677</v>
+        <v>54.91812707291811</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=53.34% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=54.92% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -6701,52 +6701,52 @@
         <v>2026</v>
       </c>
       <c r="E72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F72" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G72" t="n">
-        <v>88.11716214288521</v>
+        <v>87.20988140011258</v>
       </c>
       <c r="H72" t="n">
-        <v>1.648898475053217</v>
+        <v>1.642466111479539</v>
       </c>
       <c r="I72" t="n">
         <v>151.0433307550491</v>
       </c>
       <c r="J72" t="n">
-        <v>89.97205653125231</v>
+        <v>86.79876133578003</v>
       </c>
       <c r="K72" t="n">
-        <v>1.347222829498326</v>
+        <v>1.307239309458101</v>
       </c>
       <c r="L72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="M72" t="n">
-        <v>90.61334304210067</v>
+        <v>90.88895020884301</v>
       </c>
       <c r="N72" t="n">
-        <v>2.297549201132918</v>
+        <v>2.438331418698073</v>
       </c>
       <c r="O72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="P72" t="n">
-        <v>166.6497519436556</v>
+        <v>168.3172643464729</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.072205964643169</v>
+        <v>2.110864049449704</v>
       </c>
       <c r="R72" t="n">
         <v>161.2927483340683</v>
       </c>
       <c r="S72" t="n">
-        <v>82.09163071455964</v>
+        <v>82.50956190575791</v>
       </c>
       <c r="T72" t="n">
-        <v>2.10242440504272</v>
+        <v>2.228309830326239</v>
       </c>
       <c r="U72" t="n">
         <v>104.036396201453</v>
@@ -6762,11 +6762,11 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>82.09163071455964</v>
+        <v>82.50956190575791</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=82.09% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=82.51% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -6790,52 +6790,52 @@
         <v>2026</v>
       </c>
       <c r="E73" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G73" t="n">
-        <v>71.14000991959982</v>
+        <v>71.70774255746809</v>
       </c>
       <c r="H73" t="n">
-        <v>1.945619104365378</v>
+        <v>1.938968631695724</v>
       </c>
       <c r="I73" t="n">
         <v>148.5993365374143</v>
       </c>
       <c r="J73" t="n">
-        <v>158.7452752782929</v>
+        <v>153.5954395736106</v>
       </c>
       <c r="K73" t="n">
-        <v>2.402732410976158</v>
+        <v>2.355923158194214</v>
       </c>
       <c r="L73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="M73" t="n">
-        <v>90.14976892230113</v>
+        <v>88.73030972106281</v>
       </c>
       <c r="N73" t="n">
-        <v>2.027271146359651</v>
+        <v>1.997552126646042</v>
       </c>
       <c r="O73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="P73" t="n">
-        <v>170.9618843417967</v>
+        <v>172.1718058275552</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.486236364803371</v>
+        <v>2.507643182936564</v>
       </c>
       <c r="R73" t="n">
         <v>173.6314937555617</v>
       </c>
       <c r="S73" t="n">
-        <v>57.28942679324784</v>
+        <v>58.77174837866832</v>
       </c>
       <c r="T73" t="n">
-        <v>2.010197168566853</v>
+        <v>2.143140475575205</v>
       </c>
       <c r="U73" t="n">
         <v>104.3951484726403</v>
@@ -6851,11 +6851,11 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>57.28942679324784</v>
+        <v>58.77174837866832</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=57.29% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=58.77% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -6879,52 +6879,52 @@
         <v>2026</v>
       </c>
       <c r="E74" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F74" t="n">
         <v>11</v>
       </c>
       <c r="G74" t="n">
-        <v>172.1836151238099</v>
+        <v>173.3426311603178</v>
       </c>
       <c r="H74" t="n">
-        <v>5.008689584156971</v>
+        <v>5.508267258971564</v>
       </c>
       <c r="I74" t="n">
         <v>148.9425712788151</v>
       </c>
       <c r="J74" t="n">
-        <v>188.349608968092</v>
+        <v>188.8350419277548</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4522304879555368</v>
+        <v>0.434158698718744</v>
       </c>
       <c r="L74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="M74" t="n">
-        <v>190.8244029995426</v>
+        <v>191.2067195412283</v>
       </c>
       <c r="N74" t="n">
-        <v>33.02868699404547</v>
+        <v>35.33999170262691</v>
       </c>
       <c r="O74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="P74" t="n">
-        <v>190.8244029995426</v>
+        <v>191.2067195412283</v>
       </c>
       <c r="Q74" t="n">
-        <v>33.23913043478261</v>
+        <v>35.54166666666666</v>
       </c>
       <c r="R74" t="n">
         <v>193.1141809259393</v>
       </c>
       <c r="S74" t="n">
-        <v>160.1021769444664</v>
+        <v>161.7645862384469</v>
       </c>
       <c r="T74" t="n">
-        <v>1.284833000992501</v>
+        <v>1.568910235668429</v>
       </c>
       <c r="U74" t="n">
         <v>113.155914904339</v>
@@ -6940,11 +6940,11 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>160.1021769444664</v>
+        <v>161.7645862384469</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=160.10% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=161.76% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -6968,52 +6968,52 @@
         <v>2026</v>
       </c>
       <c r="E75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F75" t="n">
         <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>170.9138701345115</v>
+        <v>172.1257922122402</v>
       </c>
       <c r="H75" t="n">
-        <v>1.78909214966093</v>
+        <v>1.922071693781937</v>
       </c>
       <c r="I75" t="n">
         <v>157.2380343536269</v>
       </c>
       <c r="J75" t="n">
-        <v>197.1918545450863</v>
+        <v>197.3088606057077</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2939822974793316</v>
+        <v>0.2817551987303564</v>
       </c>
       <c r="L75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="M75" t="n">
-        <v>190.2742771873689</v>
+        <v>190.6795156378952</v>
       </c>
       <c r="N75" t="n">
-        <v>14.34588343629438</v>
+        <v>15.24813829311545</v>
       </c>
       <c r="O75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="P75" t="n">
-        <v>190.2742771873689</v>
+        <v>190.6795156378952</v>
       </c>
       <c r="Q75" t="n">
-        <v>14.60869565217391</v>
+        <v>15.5</v>
       </c>
       <c r="R75" t="n">
         <v>193.2892416279341</v>
       </c>
       <c r="S75" t="n">
-        <v>165.936670532348</v>
+        <v>167.3559759268335</v>
       </c>
       <c r="T75" t="n">
-        <v>0.6901346666078548</v>
+        <v>0.7985252001300038</v>
       </c>
       <c r="U75" t="n">
         <v>110.9447640026735</v>
@@ -7055,52 +7055,52 @@
         <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F76" t="n">
         <v>5</v>
       </c>
       <c r="G76" t="n">
-        <v>178.354973633617</v>
+        <v>179.2568497322164</v>
       </c>
       <c r="H76" t="n">
-        <v>2.928783987660015</v>
+        <v>3.192081591173338</v>
       </c>
       <c r="I76" t="n">
         <v>154.9841830576604</v>
       </c>
       <c r="J76" t="n">
-        <v>195.8787915029281</v>
+        <v>196.0505085236394</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2138249000719048</v>
+        <v>0.2052074704385354</v>
       </c>
       <c r="L76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="M76" t="n">
-        <v>190.4663648805137</v>
+        <v>190.863599677159</v>
       </c>
       <c r="N76" t="n">
-        <v>17.67981181273928</v>
+        <v>18.71047097254399</v>
       </c>
       <c r="O76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="P76" t="n">
-        <v>190.4663648805137</v>
+        <v>190.863599677159</v>
       </c>
       <c r="Q76" t="n">
-        <v>18.82608695652174</v>
+        <v>20.85416666666667</v>
       </c>
       <c r="R76" t="n">
         <v>192.8448970866968</v>
       </c>
       <c r="S76" t="n">
-        <v>174.6501292534513</v>
+        <v>175.7063738678908</v>
       </c>
       <c r="T76" t="n">
-        <v>0.7673414095887637</v>
+        <v>0.877827446481018</v>
       </c>
       <c r="U76" t="n">
         <v>118.0223455785753</v>
@@ -7142,52 +7142,52 @@
         <v>2026</v>
       </c>
       <c r="E77" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F77" t="n">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="G77" t="n">
-        <v>47.7742567812519</v>
+        <v>46.47505719782153</v>
       </c>
       <c r="H77" t="n">
-        <v>6.516607002343314</v>
+        <v>6.28277908356672</v>
       </c>
       <c r="I77" t="n">
         <v>77.76772218573589</v>
       </c>
       <c r="J77" t="n">
-        <v>40.82434585879298</v>
+        <v>44.06413052616614</v>
       </c>
       <c r="K77" t="n">
-        <v>7.055082554337187</v>
+        <v>7.367943329729475</v>
       </c>
       <c r="L77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="M77" t="n">
-        <v>50.96798626368885</v>
+        <v>55.06794886135159</v>
       </c>
       <c r="N77" t="n">
-        <v>10.93478260869565</v>
+        <v>11.70833333333333</v>
       </c>
       <c r="O77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="P77" t="n">
-        <v>50.96798626368885</v>
+        <v>55.06794886135159</v>
       </c>
       <c r="Q77" t="n">
-        <v>10.93478260869565</v>
+        <v>11.70833333333333</v>
       </c>
       <c r="R77" t="n">
         <v>138.4032392925817</v>
       </c>
       <c r="S77" t="n">
-        <v>29.91163125949122</v>
+        <v>32.24270743084072</v>
       </c>
       <c r="T77" t="n">
-        <v>5.863774255073022</v>
+        <v>5.932864951354129</v>
       </c>
       <c r="U77" t="n">
         <v>118.3894561520081</v>
@@ -7203,11 +7203,11 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>29.91163125949122</v>
+        <v>32.24270743084072</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=29.91% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=32.24% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7231,52 +7231,52 @@
         <v>2026</v>
       </c>
       <c r="E78" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F78" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G78" t="n">
-        <v>50.32574451465677</v>
+        <v>49.66723387575536</v>
       </c>
       <c r="H78" t="n">
-        <v>3.521806610383386</v>
+        <v>3.409834025958952</v>
       </c>
       <c r="I78" t="n">
         <v>103.5437500854655</v>
       </c>
       <c r="J78" t="n">
-        <v>50.96377117821061</v>
+        <v>53.38814440168505</v>
       </c>
       <c r="K78" t="n">
-        <v>3.962567182278121</v>
+        <v>3.997693569883748</v>
       </c>
       <c r="L78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="M78" t="n">
-        <v>122.1481532087901</v>
+        <v>117.0607914055987</v>
       </c>
       <c r="N78" t="n">
-        <v>5.938200660697792</v>
+        <v>5.690818513743579</v>
       </c>
       <c r="O78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="P78" t="n">
-        <v>49.64483641563533</v>
+        <v>52.91358782520027</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.286161776429979</v>
+        <v>4.404478823137183</v>
       </c>
       <c r="R78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="S78" t="n">
-        <v>28.67701772125466</v>
+        <v>31.481531192365</v>
       </c>
       <c r="T78" t="n">
-        <v>2.888506578911857</v>
+        <v>2.921953121524437</v>
       </c>
       <c r="U78" t="n">
         <v>124.390269119479</v>
@@ -7292,11 +7292,11 @@
         </is>
       </c>
       <c r="X78" t="n">
-        <v>28.67701772125466</v>
+        <v>31.481531192365</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=28.68% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=31.48% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7320,52 +7320,52 @@
         <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F79" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G79" t="n">
-        <v>52.24408238532585</v>
+        <v>50.335930401087</v>
       </c>
       <c r="H79" t="n">
-        <v>3.593158205875207</v>
+        <v>3.4517723720998</v>
       </c>
       <c r="I79" t="n">
         <v>102.5016657415887</v>
       </c>
       <c r="J79" t="n">
-        <v>46.03484485015787</v>
+        <v>49.71125144661219</v>
       </c>
       <c r="K79" t="n">
-        <v>4.07569851818366</v>
+        <v>4.416549243131193</v>
       </c>
       <c r="L79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="M79" t="n">
-        <v>54.67502084822188</v>
+        <v>57.69992528257627</v>
       </c>
       <c r="N79" t="n">
-        <v>6.521739130434782</v>
+        <v>6.6875</v>
       </c>
       <c r="O79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="P79" t="n">
-        <v>54.67502084822188</v>
+        <v>57.69992528257627</v>
       </c>
       <c r="Q79" t="n">
-        <v>6.521739130434782</v>
+        <v>6.6875</v>
       </c>
       <c r="R79" t="n">
         <v>148.0195847609927</v>
       </c>
       <c r="S79" t="n">
-        <v>31.6420999173577</v>
+        <v>34.0863393255216</v>
       </c>
       <c r="T79" t="n">
-        <v>3.111168359319405</v>
+        <v>3.187340837450748</v>
       </c>
       <c r="U79" t="n">
         <v>120.3982350383182</v>
@@ -7381,11 +7381,11 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>31.6420999173577</v>
+        <v>34.0863393255216</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=31.64% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=34.09% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7409,52 +7409,52 @@
         <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F80" t="n">
-        <v>747</v>
+        <v>790</v>
       </c>
       <c r="G80" t="n">
-        <v>145.0705658071386</v>
+        <v>144.6360358455763</v>
       </c>
       <c r="H80" t="n">
-        <v>28.12110535809797</v>
+        <v>28.39113287792135</v>
       </c>
       <c r="I80" t="n">
         <v>180.9937478063148</v>
       </c>
       <c r="J80" t="n">
-        <v>151.809715025411</v>
+        <v>152.7039681099278</v>
       </c>
       <c r="K80" t="n">
-        <v>27.11125750867945</v>
+        <v>27.64499574860297</v>
       </c>
       <c r="L80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="M80" t="n">
-        <v>120.9418419406456</v>
+        <v>120.3882102704755</v>
       </c>
       <c r="N80" t="n">
-        <v>20.96910410342009</v>
+        <v>21.3492732445399</v>
       </c>
       <c r="O80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="P80" t="n">
-        <v>158.7876267559903</v>
+        <v>160.5027082559168</v>
       </c>
       <c r="Q80" t="n">
-        <v>29.80223370262615</v>
+        <v>30.35191477596914</v>
       </c>
       <c r="R80" t="n">
         <v>172.7461511452186</v>
       </c>
       <c r="S80" t="n">
-        <v>55.57865689849766</v>
+        <v>54.17209463992535</v>
       </c>
       <c r="T80" t="n">
-        <v>29.84619604790962</v>
+        <v>28.95510697940467</v>
       </c>
       <c r="U80" t="n">
         <v>175.912448276349</v>
@@ -7470,11 +7470,11 @@
         </is>
       </c>
       <c r="X80" t="n">
-        <v>55.57865689849766</v>
+        <v>54.17209463992535</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=55.58% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=54.17% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7498,52 +7498,52 @@
         <v>2026</v>
       </c>
       <c r="E81" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F81" t="n">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="G81" t="n">
-        <v>132.4867083561084</v>
+        <v>132.1254209199005</v>
       </c>
       <c r="H81" t="n">
-        <v>12.62685812777978</v>
+        <v>12.61055894746372</v>
       </c>
       <c r="I81" t="n">
         <v>185.5191244575439</v>
       </c>
       <c r="J81" t="n">
-        <v>118.7066549978501</v>
+        <v>117.5102746798739</v>
       </c>
       <c r="K81" t="n">
-        <v>8.635753424982873</v>
+        <v>9.366696817338918</v>
       </c>
       <c r="L81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="M81" t="n">
-        <v>163.9232010442408</v>
+        <v>162.1923398856764</v>
       </c>
       <c r="N81" t="n">
-        <v>13.06296597356382</v>
+        <v>13.02483438452085</v>
       </c>
       <c r="O81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="P81" t="n">
-        <v>145.6926430037564</v>
+        <v>146.8494116843916</v>
       </c>
       <c r="Q81" t="n">
-        <v>13.39475915977169</v>
+        <v>13.4559246932461</v>
       </c>
       <c r="R81" t="n">
         <v>163.1536185700502</v>
       </c>
       <c r="S81" t="n">
-        <v>56.08703951311051</v>
+        <v>55.18680741715015</v>
       </c>
       <c r="T81" t="n">
-        <v>8.829026597258693</v>
+        <v>8.657222666661834</v>
       </c>
       <c r="U81" t="n">
         <v>172.1596497720207</v>
@@ -7559,11 +7559,11 @@
         </is>
       </c>
       <c r="X81" t="n">
-        <v>56.08703951311051</v>
+        <v>55.18680741715015</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=56.09% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=55.19% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7587,52 +7587,52 @@
         <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F82" t="n">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="G82" t="n">
-        <v>129.9289044477184</v>
+        <v>130.4082911873624</v>
       </c>
       <c r="H82" t="n">
-        <v>14.44120356230335</v>
+        <v>14.77151678933826</v>
       </c>
       <c r="I82" t="n">
         <v>186.2973802760101</v>
       </c>
       <c r="J82" t="n">
-        <v>146.7946985204721</v>
+        <v>147.141676840363</v>
       </c>
       <c r="K82" t="n">
-        <v>14.69457114501941</v>
+        <v>15.06512782755899</v>
       </c>
       <c r="L82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="M82" t="n">
-        <v>157.7438414402413</v>
+        <v>158.9308837266639</v>
       </c>
       <c r="N82" t="n">
-        <v>13.7715504726638</v>
+        <v>14.28263561303417</v>
       </c>
       <c r="O82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="P82" t="n">
-        <v>148.8478716529916</v>
+        <v>150.7562222351752</v>
       </c>
       <c r="Q82" t="n">
-        <v>15.62010462447254</v>
+        <v>16.07901112328347</v>
       </c>
       <c r="R82" t="n">
         <v>166.6060177059153</v>
       </c>
       <c r="S82" t="n">
-        <v>37.55860291656742</v>
+        <v>37.63301310609035</v>
       </c>
       <c r="T82" t="n">
-        <v>9.225247055395791</v>
+        <v>9.210726229697036</v>
       </c>
       <c r="U82" t="n">
         <v>176.1888335684919</v>
@@ -7648,11 +7648,11 @@
         </is>
       </c>
       <c r="X82" t="n">
-        <v>37.55860291656742</v>
+        <v>37.63301310609035</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=37.56% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=37.63% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7676,52 +7676,52 @@
         <v>2026</v>
       </c>
       <c r="E83" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F83" t="n">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="G83" t="n">
-        <v>35.82254323442039</v>
+        <v>38.55088026874415</v>
       </c>
       <c r="H83" t="n">
-        <v>5.694070255825614</v>
+        <v>5.82105084784645</v>
       </c>
       <c r="I83" t="n">
         <v>88.04980557911651</v>
       </c>
       <c r="J83" t="n">
-        <v>47.2904668050621</v>
+        <v>48.81168296710427</v>
       </c>
       <c r="K83" t="n">
-        <v>7.732049972518708</v>
+        <v>7.729765190223816</v>
       </c>
       <c r="L83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="M83" t="n">
-        <v>100.7175260153327</v>
+        <v>98.48174674508603</v>
       </c>
       <c r="N83" t="n">
-        <v>34.58841195117363</v>
+        <v>33.48056145320806</v>
       </c>
       <c r="O83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="P83" t="n">
-        <v>85.29903085503335</v>
+        <v>90.07823790274031</v>
       </c>
       <c r="Q83" t="n">
-        <v>26.30615167954335</v>
+        <v>25.75172869289571</v>
       </c>
       <c r="R83" t="n">
         <v>103.1343264142703</v>
       </c>
       <c r="S83" t="n">
-        <v>53.63666954731949</v>
+        <v>52.87979117452389</v>
       </c>
       <c r="T83" t="n">
-        <v>11.83305544347967</v>
+        <v>11.57357328125053</v>
       </c>
       <c r="U83" t="n">
         <v>103.3034448942146</v>
@@ -7737,11 +7737,11 @@
         </is>
       </c>
       <c r="X83" t="n">
-        <v>35.82254323442039</v>
+        <v>38.55088026874415</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=35.82% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=38.55% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7765,52 +7765,52 @@
         <v>2026</v>
       </c>
       <c r="E84" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F84" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="G84" t="n">
-        <v>33.73703538560333</v>
+        <v>35.98096847304528</v>
       </c>
       <c r="H84" t="n">
-        <v>2.409518881690106</v>
+        <v>2.43602600495171</v>
       </c>
       <c r="I84" t="n">
         <v>100.4914466151705</v>
       </c>
       <c r="J84" t="n">
-        <v>47.81622092646597</v>
+        <v>48.13170036163415</v>
       </c>
       <c r="K84" t="n">
-        <v>3.38359716330306</v>
+        <v>3.402200816679951</v>
       </c>
       <c r="L84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="M84" t="n">
-        <v>75.43474935161561</v>
+        <v>75.24862404261012</v>
       </c>
       <c r="N84" t="n">
-        <v>8.546227556774392</v>
+        <v>8.419301408575459</v>
       </c>
       <c r="O84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="P84" t="n">
-        <v>84.19084285065338</v>
+        <v>86.62199055701288</v>
       </c>
       <c r="Q84" t="n">
-        <v>12.11375428791303</v>
+        <v>11.78239945745356</v>
       </c>
       <c r="R84" t="n">
         <v>98.74789164115032</v>
       </c>
       <c r="S84" t="n">
-        <v>53.52479167646013</v>
+        <v>53.84857939311091</v>
       </c>
       <c r="T84" t="n">
-        <v>5.115119524303525</v>
+        <v>5.086121349145057</v>
       </c>
       <c r="U84" t="n">
         <v>110.607240444147</v>
@@ -7826,11 +7826,11 @@
         </is>
       </c>
       <c r="X84" t="n">
-        <v>33.73703538560333</v>
+        <v>35.98096847304528</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=33.74% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=35.98% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7854,59 +7854,59 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G85" t="n">
-        <v>45.17291284242295</v>
+        <v>48.22410033751445</v>
       </c>
       <c r="H85" t="n">
-        <v>3.888797644604952</v>
+        <v>3.974672465078696</v>
       </c>
       <c r="I85" t="n">
         <v>109.9471447641292</v>
       </c>
       <c r="J85" t="n">
-        <v>52.94713432947248</v>
+        <v>51.89351382674426</v>
       </c>
       <c r="K85" t="n">
-        <v>4.410926643149813</v>
+        <v>4.30813663569926</v>
       </c>
       <c r="L85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="M85" t="n">
-        <v>95.14488454484602</v>
+        <v>92.30664048160357</v>
       </c>
       <c r="N85" t="n">
-        <v>16.82355108869082</v>
+        <v>16.22673645999537</v>
       </c>
       <c r="O85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="P85" t="n">
-        <v>92.95972573699466</v>
+        <v>97.41973716461989</v>
       </c>
       <c r="Q85" t="n">
-        <v>15.73936784729693</v>
+        <v>15.41689418699289</v>
       </c>
       <c r="R85" t="n">
         <v>106.9882513320439</v>
       </c>
       <c r="S85" t="n">
-        <v>44.59654253377675</v>
+        <v>43.15264064001872</v>
       </c>
       <c r="T85" t="n">
-        <v>4.491232479349994</v>
+        <v>4.338974668943958</v>
       </c>
       <c r="U85" t="n">
         <v>107.8756984639591</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -7915,11 +7915,11 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>45.17291284242295</v>
+        <v>43.15264064001872</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=45.17% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=43.15% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -7943,52 +7943,52 @@
         <v>2026</v>
       </c>
       <c r="E86" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F86" t="n">
         <v>38</v>
       </c>
       <c r="G86" t="n">
-        <v>116.1258789295296</v>
+        <v>119.6206339741325</v>
       </c>
       <c r="H86" t="n">
-        <v>3.687717971647376</v>
+        <v>3.890290018699859</v>
       </c>
       <c r="I86" t="n">
         <v>160.3842205944857</v>
       </c>
       <c r="J86" t="n">
-        <v>128.3126990226881</v>
+        <v>131.2996698967427</v>
       </c>
       <c r="K86" t="n">
-        <v>1.586542376572479</v>
+        <v>1.592519190019324</v>
       </c>
       <c r="L86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="M86" t="n">
-        <v>141.5407491610016</v>
+        <v>143.9765512792932</v>
       </c>
       <c r="N86" t="n">
-        <v>2.642830396475999</v>
+        <v>2.822131001700958</v>
       </c>
       <c r="O86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="P86" t="n">
-        <v>173.1011636375044</v>
+        <v>174.2219484859416</v>
       </c>
       <c r="Q86" t="n">
-        <v>22.34782608695652</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="R86" t="n">
         <v>188.4995472315167</v>
       </c>
       <c r="S86" t="n">
-        <v>81.8534709765423</v>
+        <v>86.77624301918637</v>
       </c>
       <c r="T86" t="n">
-        <v>0.841383742441259</v>
+        <v>1.001154152655852</v>
       </c>
       <c r="U86" t="n">
         <v>113.2748521774272</v>
@@ -8004,11 +8004,11 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>81.8534709765423</v>
+        <v>86.77624301918637</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=81.85% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=86.78% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8032,52 +8032,52 @@
         <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
         <v>19</v>
       </c>
       <c r="G87" t="n">
-        <v>120.7737723997747</v>
+        <v>124.0748652164507</v>
       </c>
       <c r="H87" t="n">
-        <v>1.311565685642731</v>
+        <v>1.378238515867345</v>
       </c>
       <c r="I87" t="n">
         <v>171.410316416684</v>
       </c>
       <c r="J87" t="n">
-        <v>150.0373242641209</v>
+        <v>152.1191024197826</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8977096382759049</v>
+        <v>0.8877626768742942</v>
       </c>
       <c r="L87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="M87" t="n">
-        <v>166.3155740693442</v>
+        <v>167.7190918164549</v>
       </c>
       <c r="N87" t="n">
-        <v>9.608695652173912</v>
+        <v>10.45833333333333</v>
       </c>
       <c r="O87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="P87" t="n">
-        <v>166.3155740693442</v>
+        <v>167.7190918164549</v>
       </c>
       <c r="Q87" t="n">
-        <v>9.608695652173912</v>
+        <v>10.45833333333333</v>
       </c>
       <c r="R87" t="n">
         <v>191.241827101395</v>
       </c>
       <c r="S87" t="n">
-        <v>113.4080778222351</v>
+        <v>117.016074579642</v>
       </c>
       <c r="T87" t="n">
-        <v>0.5430723172151088</v>
+        <v>0.6133114361700361</v>
       </c>
       <c r="U87" t="n">
         <v>108.9238350712686</v>
@@ -8093,11 +8093,11 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>113.4080778222351</v>
+        <v>117.016074579642</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=113.41% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=117.02% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8121,52 +8121,52 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
         <v>18</v>
       </c>
       <c r="G88" t="n">
-        <v>134.5501681717121</v>
+        <v>137.2772444978907</v>
       </c>
       <c r="H88" t="n">
-        <v>1.994443549360311</v>
+        <v>2.055451826229087</v>
       </c>
       <c r="I88" t="n">
         <v>169.0038464611843</v>
       </c>
       <c r="J88" t="n">
-        <v>177.9232806527804</v>
+        <v>178.8431439589145</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9566053945677125</v>
+        <v>0.9167893191839737</v>
       </c>
       <c r="L88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="M88" t="n">
-        <v>169.0174741238627</v>
+        <v>170.8399756459885</v>
       </c>
       <c r="N88" t="n">
-        <v>2.139778100925943</v>
+        <v>2.104949722687403</v>
       </c>
       <c r="O88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="P88" t="n">
-        <v>181.2562356619226</v>
+        <v>182.0372258426758</v>
       </c>
       <c r="Q88" t="n">
-        <v>13.17391304347826</v>
+        <v>14.125</v>
       </c>
       <c r="R88" t="n">
         <v>190.1751472740156</v>
       </c>
       <c r="S88" t="n">
-        <v>119.265709752752</v>
+        <v>122.629638513054</v>
       </c>
       <c r="T88" t="n">
-        <v>0.590183809542804</v>
+        <v>0.7384892654011512</v>
       </c>
       <c r="U88" t="n">
         <v>121.3094122928426</v>
@@ -8182,11 +8182,11 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>119.265709752752</v>
+        <v>122.629638513054</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=119.27% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=122.63% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
         <v>2026</v>
       </c>
       <c r="E89" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -8219,7 +8219,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1034044395744402</v>
+        <v>0.1035679512288425</v>
       </c>
       <c r="I89" t="n">
         <v>200</v>
@@ -8228,7 +8228,7 @@
         <v>200</v>
       </c>
       <c r="K89" t="n">
-        <v>0.007181157493568859</v>
+        <v>0.007116236184866621</v>
       </c>
       <c r="L89" t="n">
         <v>200</v>
@@ -8251,7 +8251,7 @@
         <v>200</v>
       </c>
       <c r="T89" t="n">
-        <v>7.212276214833761</v>
+        <v>7.21227621483376</v>
       </c>
       <c r="U89" t="n">
         <v>200</v>
@@ -8293,7 +8293,7 @@
         <v>2026</v>
       </c>
       <c r="E90" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -8302,7 +8302,7 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09086107718308541</v>
+        <v>0.09100131122582784</v>
       </c>
       <c r="I90" t="n">
         <v>200</v>
@@ -8311,7 +8311,7 @@
         <v>200</v>
       </c>
       <c r="K90" t="n">
-        <v>0.003364990963457704</v>
+        <v>0.003352477918869271</v>
       </c>
       <c r="L90" t="n">
         <v>200</v>
@@ -8376,7 +8376,7 @@
         <v>2026</v>
       </c>
       <c r="E91" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8385,7 +8385,7 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09331921028752266</v>
+        <v>0.09345947579812951</v>
       </c>
       <c r="I91" t="n">
         <v>200</v>
@@ -8394,7 +8394,7 @@
         <v>200</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0136128956536169</v>
+        <v>0.01358042405695121</v>
       </c>
       <c r="L91" t="n">
         <v>200</v>
@@ -8417,7 +8417,7 @@
         <v>200</v>
       </c>
       <c r="T91" t="n">
-        <v>2.828638845065418e-17</v>
+        <v>2.710778893187692e-17</v>
       </c>
       <c r="U91" t="n">
         <v>200</v>
@@ -8459,52 +8459,52 @@
         <v>2026</v>
       </c>
       <c r="E92" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F92" t="n">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="G92" t="n">
-        <v>50.58915032524707</v>
+        <v>50.81720714933605</v>
       </c>
       <c r="H92" t="n">
-        <v>7.806418729797821</v>
+        <v>8.229198781425604</v>
       </c>
       <c r="I92" t="n">
         <v>49.15109590531281</v>
       </c>
       <c r="J92" t="n">
-        <v>53.65888694735421</v>
+        <v>54.05813673509176</v>
       </c>
       <c r="K92" t="n">
-        <v>8.187580257720475</v>
+        <v>8.667249683706071</v>
       </c>
       <c r="L92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="M92" t="n">
-        <v>146.3331867260178</v>
+        <v>145.1299702704904</v>
       </c>
       <c r="N92" t="n">
-        <v>92.65748173165527</v>
+        <v>93.65849896561129</v>
       </c>
       <c r="O92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="P92" t="n">
-        <v>96.80706086275286</v>
+        <v>93.23088683705704</v>
       </c>
       <c r="Q92" t="n">
-        <v>34.78598795298529</v>
+        <v>33.51436772257085</v>
       </c>
       <c r="R92" t="n">
         <v>92.01416331532587</v>
       </c>
       <c r="S92" t="n">
-        <v>36.56210345867902</v>
+        <v>35.61339068746875</v>
       </c>
       <c r="T92" t="n">
-        <v>5.468270849612063</v>
+        <v>5.493510551764362</v>
       </c>
       <c r="U92" t="n">
         <v>95.83480509856771</v>
@@ -8520,11 +8520,11 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>36.56210345867902</v>
+        <v>35.61339068746875</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=36.56% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=35.61% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8548,52 +8548,52 @@
         <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F93" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="G93" t="n">
-        <v>46.76699698834544</v>
+        <v>47.29273134308652</v>
       </c>
       <c r="H93" t="n">
-        <v>3.47279107812409</v>
+        <v>3.728743913484136</v>
       </c>
       <c r="I93" t="n">
         <v>60.93105560683724</v>
       </c>
       <c r="J93" t="n">
-        <v>55.8655753410899</v>
+        <v>55.49201589625309</v>
       </c>
       <c r="K93" t="n">
-        <v>4.805141230617503</v>
+        <v>5.141016757035305</v>
       </c>
       <c r="L93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="M93" t="n">
-        <v>141.0048742728754</v>
+        <v>139.8022773934235</v>
       </c>
       <c r="N93" t="n">
-        <v>41.14593888710504</v>
+        <v>41.66525063954594</v>
       </c>
       <c r="O93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="P93" t="n">
-        <v>103.7751115518001</v>
+        <v>99.63567471335472</v>
       </c>
       <c r="Q93" t="n">
-        <v>18.6749435732643</v>
+        <v>17.93644890212915</v>
       </c>
       <c r="R93" t="n">
         <v>96.01849856237216</v>
       </c>
       <c r="S93" t="n">
-        <v>36.12898636730212</v>
+        <v>34.94100165608</v>
       </c>
       <c r="T93" t="n">
-        <v>2.351952779066206</v>
+        <v>2.318161172800703</v>
       </c>
       <c r="U93" t="n">
         <v>99.35850993844542</v>
@@ -8609,11 +8609,11 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>36.12898636730212</v>
+        <v>34.94100165608</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=36.13% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=34.94% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8637,52 +8637,52 @@
         <v>2026</v>
       </c>
       <c r="E94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F94" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="G94" t="n">
-        <v>53.92068970347205</v>
+        <v>53.25947624904145</v>
       </c>
       <c r="H94" t="n">
-        <v>4.303053183034618</v>
+        <v>4.3901691327336</v>
       </c>
       <c r="I94" t="n">
         <v>64.07712599234655</v>
       </c>
       <c r="J94" t="n">
-        <v>57.27144253283743</v>
+        <v>61.85939605120323</v>
       </c>
       <c r="K94" t="n">
-        <v>4.389300741472915</v>
+        <v>4.965759876091769</v>
       </c>
       <c r="L94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="M94" t="n">
-        <v>146.3738991083444</v>
+        <v>144.8736097808937</v>
       </c>
       <c r="N94" t="n">
-        <v>45.52523307304197</v>
+        <v>45.68054826102104</v>
       </c>
       <c r="O94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="P94" t="n">
-        <v>103.6028181092246</v>
+        <v>100.0062163492703</v>
       </c>
       <c r="Q94" t="n">
-        <v>20.14457404216937</v>
+        <v>19.46287869400934</v>
       </c>
       <c r="R94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="S94" t="n">
-        <v>38.51503931286526</v>
+        <v>38.00214671634703</v>
       </c>
       <c r="T94" t="n">
-        <v>3.020287649644401</v>
+        <v>3.145750961099421</v>
       </c>
       <c r="U94" t="n">
         <v>93.11495456228404</v>
@@ -8698,11 +8698,11 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>38.51503931286526</v>
+        <v>38.00214671634703</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=38.52% sobre 23 sem</t>
+          <t>NBGLM: menor SMAPE real=38.00% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8726,25 +8726,25 @@
         <v>2026</v>
       </c>
       <c r="E95" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G95" t="n">
-        <v>151.4967953183141</v>
+        <v>148.4660272027334</v>
       </c>
       <c r="H95" t="n">
-        <v>0.629440394355325</v>
+        <v>0.6267581054027628</v>
       </c>
       <c r="I95" t="n">
         <v>152.3875262412586</v>
       </c>
       <c r="J95" t="n">
-        <v>199.295024811595</v>
+        <v>199.301491897467</v>
       </c>
       <c r="K95" t="n">
-        <v>0.4766873730414749</v>
+        <v>0.4984347198135324</v>
       </c>
       <c r="L95" t="n">
         <v>128.1095321097334</v>
@@ -8753,25 +8753,25 @@
         <v>200</v>
       </c>
       <c r="N95" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5</v>
       </c>
       <c r="O95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="P95" t="n">
-        <v>166.8563216454057</v>
+        <v>168.2373082435138</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.264262189594318</v>
+        <v>3.169917931694554</v>
       </c>
       <c r="R95" t="n">
         <v>118.2821915164861</v>
       </c>
       <c r="S95" t="n">
-        <v>161.3096889825202</v>
+        <v>157.8434525212073</v>
       </c>
       <c r="T95" t="n">
-        <v>1.542967425701738</v>
+        <v>1.532090325210222</v>
       </c>
       <c r="U95" t="n">
         <v>128.8999217807187</v>
@@ -8787,11 +8787,11 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>151.4967953183141</v>
+        <v>148.4660272027334</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=151.50% sobre 23 sem</t>
+          <t>Prophet: menor SMAPE real=148.47% sobre 24 sem</t>
         </is>
       </c>
     </row>
@@ -8815,25 +8815,25 @@
         <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F96" t="n">
         <v>3</v>
       </c>
       <c r="G96" t="n">
-        <v>184.8696509290267</v>
+        <v>185.5000821403173</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2894927597943328</v>
+        <v>0.2811483352958202</v>
       </c>
       <c r="I96" t="n">
         <v>158.9896824444987</v>
       </c>
       <c r="J96" t="n">
-        <v>199.3815213383446</v>
+        <v>199.4072912825802</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1308509358942739</v>
+        <v>0.125414931048193</v>
       </c>
       <c r="L96" t="n">
         <v>189.1617640516506</v>
@@ -8842,25 +8842,25 @@
         <v>200</v>
       </c>
       <c r="N96" t="n">
-        <v>1.262135874822121</v>
+        <v>1.481632344945054</v>
       </c>
       <c r="O96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="P96" t="n">
-        <v>189.0319529373464</v>
+        <v>189.4889548982903</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.235419393944986</v>
+        <v>3.123775857105041</v>
       </c>
       <c r="R96" t="n">
         <v>124.4459476108536</v>
       </c>
       <c r="S96" t="n">
-        <v>184.2846058267657</v>
+        <v>184.9394139173172</v>
       </c>
       <c r="T96" t="n">
-        <v>0.9281105864255196</v>
+        <v>0.9436462249325906</v>
       </c>
       <c r="U96" t="n">
         <v>151.8363274594118</v>
@@ -8902,52 +8902,52 @@
         <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F97" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G97" t="n">
-        <v>170.805862174128</v>
+        <v>170.4249265108153</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3835315886264866</v>
+        <v>0.4048010743517452</v>
       </c>
       <c r="I97" t="n">
         <v>157.2976315063829</v>
       </c>
       <c r="J97" t="n">
-        <v>199.4284607259294</v>
+        <v>199.4090022955906</v>
       </c>
       <c r="K97" t="n">
-        <v>0.350494112217551</v>
+        <v>0.3774483945165135</v>
       </c>
       <c r="L97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="M97" t="n">
-        <v>163.0662907379325</v>
+        <v>154.6893586856203</v>
       </c>
       <c r="N97" t="n">
-        <v>1.617831665536632</v>
+        <v>1.575165877739588</v>
       </c>
       <c r="O97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="P97" t="n">
-        <v>167.6797090282344</v>
+        <v>169.0263878187246</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.091098841382167</v>
+        <v>2.04563638965791</v>
       </c>
       <c r="R97" t="n">
         <v>128.4785456608675</v>
       </c>
       <c r="S97" t="n">
-        <v>162.5356126507977</v>
+        <v>157.9595871373196</v>
       </c>
       <c r="T97" t="n">
-        <v>0.8284550584071141</v>
+        <v>0.8237589857741744</v>
       </c>
       <c r="U97" t="n">
         <v>136.0400571203446</v>
@@ -8965,7 +8965,7 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -8989,7 +8989,7 @@
         <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8998,7 +8998,7 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.06313362068641683</v>
+        <v>0.06050305315781612</v>
       </c>
       <c r="I98" t="n">
         <v>198.585723184526</v>
@@ -9007,7 +9007,7 @@
         <v>200</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0005247004063138043</v>
+        <v>0.0005236563068297292</v>
       </c>
       <c r="L98" t="n">
         <v>199.9898962083731</v>
@@ -9016,7 +9016,7 @@
         <v>200</v>
       </c>
       <c r="N98" t="n">
-        <v>0.3260869565217391</v>
+        <v>0.5</v>
       </c>
       <c r="O98" t="n">
         <v>199.2030987655621</v>
@@ -9032,7 +9032,7 @@
         <v>200</v>
       </c>
       <c r="T98" t="n">
-        <v>0.03609275218497298</v>
+        <v>0.042972898000321</v>
       </c>
       <c r="U98" t="n">
         <v>199.9999998548883</v>
@@ -9074,7 +9074,7 @@
         <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -9083,7 +9083,7 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.03637473410122116</v>
+        <v>0.03485912018033694</v>
       </c>
       <c r="I99" t="n">
         <v>198.7380283178126</v>
@@ -9092,7 +9092,7 @@
         <v>200</v>
       </c>
       <c r="K99" t="n">
-        <v>0.001627731885337944</v>
+        <v>0.0016373444565096</v>
       </c>
       <c r="L99" t="n">
         <v>199.9983019911245</v>
@@ -9101,7 +9101,7 @@
         <v>200</v>
       </c>
       <c r="N99" t="n">
-        <v>0.2304334210966156</v>
+        <v>0.3171048613027408</v>
       </c>
       <c r="O99" t="n">
         <v>198.5022493653877</v>
@@ -9117,7 +9117,7 @@
         <v>200</v>
       </c>
       <c r="T99" t="n">
-        <v>0.03038073171553119</v>
+        <v>0.03506900760664092</v>
       </c>
       <c r="U99" t="n">
         <v>200</v>
@@ -9159,7 +9159,7 @@
         <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -9168,7 +9168,7 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.05161836148268496</v>
+        <v>0.05177206683268074</v>
       </c>
       <c r="I100" t="n">
         <v>200</v>
@@ -9177,7 +9177,7 @@
         <v>200</v>
       </c>
       <c r="K100" t="n">
-        <v>0.002418710587654218</v>
+        <v>0.002396106685502108</v>
       </c>
       <c r="L100" t="n">
         <v>200</v>
@@ -9186,7 +9186,7 @@
         <v>200</v>
       </c>
       <c r="N100" t="n">
-        <v>0.06521739130434782</v>
+        <v>0.125</v>
       </c>
       <c r="O100" t="n">
         <v>200</v>
@@ -9202,7 +9202,7 @@
         <v>200</v>
       </c>
       <c r="T100" t="n">
-        <v>0.01282877454675312</v>
+        <v>0.01616425401782888</v>
       </c>
       <c r="U100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -575,59 +575,59 @@
         <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.09238977339498218</v>
+        <v>0.2006674831338297</v>
       </c>
       <c r="I2" t="n">
         <v>185.8333489727328</v>
       </c>
       <c r="J2" t="n">
-        <v>199.2888825522077</v>
+        <v>197.4073596888732</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0933538099404826</v>
+        <v>0.1951254343367843</v>
       </c>
       <c r="L2" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M2" t="n">
-        <v>180</v>
+        <v>155.6923076923077</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="O2" t="n">
         <v>197.8088169752323</v>
       </c>
       <c r="P2" t="n">
-        <v>180</v>
+        <v>155.6923076923077</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6875</v>
+        <v>0.75</v>
       </c>
       <c r="R2" t="n">
         <v>199.5572761277739</v>
       </c>
       <c r="S2" t="n">
-        <v>194.3606631475242</v>
+        <v>184.0794920386864</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1270160811209012</v>
+        <v>0.1760121898273306</v>
       </c>
       <c r="U2" t="n">
         <v>194.9779461019607</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -638,7 +638,7 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>NBGLM: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -662,59 +662,59 @@
         <v>2026</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>199.7529419278686</v>
+        <v>199.7803928247721</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04990691190105003</v>
+        <v>0.1229909956009693</v>
       </c>
       <c r="I3" t="n">
         <v>157.2321783542833</v>
       </c>
       <c r="J3" t="n">
-        <v>199.6037493312737</v>
+        <v>197.2796288638902</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0552020374046991</v>
+        <v>0.1214219715065594</v>
       </c>
       <c r="L3" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M3" t="n">
-        <v>200</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="O3" t="n">
         <v>197.8854209931308</v>
       </c>
       <c r="P3" t="n">
-        <v>200</v>
+        <v>183.3333333333333</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2291666666666667</v>
+        <v>0.3269230769230769</v>
       </c>
       <c r="R3" t="n">
         <v>199.636475467609</v>
       </c>
       <c r="S3" t="n">
-        <v>199.4333302169988</v>
+        <v>187.0830627946073</v>
       </c>
       <c r="T3" t="n">
-        <v>0.08128269129803049</v>
+        <v>0.09806476296935614</v>
       </c>
       <c r="U3" t="n">
         <v>198.5158836242873</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -725,7 +725,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>NBGLM: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -749,52 +749,52 @@
         <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05283105068688496</v>
+        <v>0.0872286621725092</v>
       </c>
       <c r="I4" t="n">
         <v>158.5580779411727</v>
       </c>
       <c r="J4" t="n">
-        <v>195.2125169210915</v>
+        <v>191.1760450805634</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1435042186988603</v>
+        <v>0.1792257312452026</v>
       </c>
       <c r="L4" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M4" t="n">
-        <v>173.3333333333333</v>
+        <v>160</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
         <v>197.7265973322816</v>
       </c>
       <c r="P4" t="n">
-        <v>173.3333333333333</v>
+        <v>160</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="R4" t="n">
         <v>199.5859359679221</v>
       </c>
       <c r="S4" t="n">
-        <v>196.0539417484686</v>
+        <v>192.0311816113775</v>
       </c>
       <c r="T4" t="n">
-        <v>0.09143706365799938</v>
+        <v>0.1242171289414107</v>
       </c>
       <c r="U4" t="n">
         <v>196.9436529554095</v>
@@ -812,7 +812,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -836,25 +836,25 @@
         <v>2026</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>199.0479027213012</v>
+        <v>199.1344570193647</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1692771758266546</v>
+        <v>0.194717393070758</v>
       </c>
       <c r="I5" t="n">
         <v>175.1088701866436</v>
       </c>
       <c r="J5" t="n">
-        <v>199.3211318567838</v>
+        <v>199.1789075403633</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1779919650089362</v>
+        <v>0.2029091662089284</v>
       </c>
       <c r="L5" t="n">
         <v>109.609711216533</v>
@@ -863,7 +863,7 @@
         <v>200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="O5" t="n">
         <v>187.2707284786031</v>
@@ -872,16 +872,16 @@
         <v>200</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="R5" t="n">
         <v>193.7972259177366</v>
       </c>
       <c r="S5" t="n">
-        <v>199.386846886171</v>
+        <v>199.4340125103117</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1782003717029851</v>
+        <v>0.2029541892643015</v>
       </c>
       <c r="U5" t="n">
         <v>187.0400639517023</v>
@@ -899,7 +899,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
         <v>2026</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>199.5175325392658</v>
+        <v>199.5546454208607</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09131319804606282</v>
+        <v>0.08444375875288576</v>
       </c>
       <c r="I6" t="n">
         <v>191.646475967384</v>
       </c>
       <c r="J6" t="n">
-        <v>199.9778871530725</v>
+        <v>199.9795881412977</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08403767526253114</v>
+        <v>0.0776408859315368</v>
       </c>
       <c r="L6" t="n">
         <v>79.54507935933471</v>
@@ -950,7 +950,7 @@
         <v>200</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.1346153846153846</v>
       </c>
       <c r="O6" t="n">
         <v>192.53013744135</v>
@@ -959,7 +959,7 @@
         <v>200</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.1346153846153846</v>
       </c>
       <c r="R6" t="n">
         <v>193.2139428195562</v>
@@ -968,7 +968,7 @@
         <v>198.5786411733137</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08899210047569232</v>
+        <v>0.08214655428525444</v>
       </c>
       <c r="U6" t="n">
         <v>198.9985835834048</v>
@@ -1010,25 +1010,25 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>198.7893275403238</v>
+        <v>198.6610533081308</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1034173866230271</v>
+        <v>0.134291957686018</v>
       </c>
       <c r="I7" t="n">
         <v>186.9197740801393</v>
       </c>
       <c r="J7" t="n">
-        <v>199.9827739244382</v>
+        <v>199.9807829565354</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08372825494511628</v>
+        <v>0.1157850864840191</v>
       </c>
       <c r="L7" t="n">
         <v>109.7635513825217</v>
@@ -1037,7 +1037,7 @@
         <v>200</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="O7" t="n">
         <v>185.3187572725189</v>
@@ -1046,16 +1046,16 @@
         <v>200</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1458333333333333</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="R7" t="n">
         <v>190.8625800946274</v>
       </c>
       <c r="S7" t="n">
-        <v>199.8201275722819</v>
+        <v>199.8339639128756</v>
       </c>
       <c r="T7" t="n">
-        <v>0.09687094900092623</v>
+        <v>0.127880876000855</v>
       </c>
       <c r="U7" t="n">
         <v>197.3279694158802</v>
@@ -1073,7 +1073,7 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1097,52 +1097,52 @@
         <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="G8" t="n">
-        <v>100.1124878587876</v>
+        <v>97.22491608385673</v>
       </c>
       <c r="H8" t="n">
-        <v>4.901391109923342</v>
+        <v>4.842719830400823</v>
       </c>
       <c r="I8" t="n">
         <v>154.5040916050135</v>
       </c>
       <c r="J8" t="n">
-        <v>62.34216615161932</v>
+        <v>66.09321580505865</v>
       </c>
       <c r="K8" t="n">
-        <v>5.481663005783507</v>
+        <v>6.379512625221059</v>
       </c>
       <c r="L8" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M8" t="n">
-        <v>94.17843761913393</v>
+        <v>94.35475689730009</v>
       </c>
       <c r="N8" t="n">
-        <v>14.625</v>
+        <v>14.71153846153846</v>
       </c>
       <c r="O8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="P8" t="n">
-        <v>94.17843761913393</v>
+        <v>94.35475689730009</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.625</v>
+        <v>14.71153846153846</v>
       </c>
       <c r="R8" t="n">
         <v>172.894287988784</v>
       </c>
       <c r="S8" t="n">
-        <v>62.28509479054119</v>
+        <v>60.16199655312483</v>
       </c>
       <c r="T8" t="n">
-        <v>3.325249698416485</v>
+        <v>3.27268470603121</v>
       </c>
       <c r="U8" t="n">
         <v>111.5676388698673</v>
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>62.28509479054119</v>
+        <v>60.16199655312483</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=62.29% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=60.16% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1186,52 +1186,52 @@
         <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G9" t="n">
-        <v>94.18208509883893</v>
+        <v>91.2579130376192</v>
       </c>
       <c r="H9" t="n">
-        <v>2.246817711851911</v>
+        <v>2.184156444835504</v>
       </c>
       <c r="I9" t="n">
         <v>164.086229256472</v>
       </c>
       <c r="J9" t="n">
-        <v>77.46126867626897</v>
+        <v>81.59982771449211</v>
       </c>
       <c r="K9" t="n">
-        <v>2.934838491239349</v>
+        <v>3.552656265560343</v>
       </c>
       <c r="L9" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M9" t="n">
-        <v>103.601914106478</v>
+        <v>103.0533505779254</v>
       </c>
       <c r="N9" t="n">
-        <v>7.333333333333333</v>
+        <v>7.346153846153846</v>
       </c>
       <c r="O9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="P9" t="n">
-        <v>103.601914106478</v>
+        <v>103.0533505779254</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.333333333333333</v>
+        <v>7.346153846153846</v>
       </c>
       <c r="R9" t="n">
         <v>176.8647517474977</v>
       </c>
       <c r="S9" t="n">
-        <v>60.38101971880621</v>
+        <v>57.53807472706776</v>
       </c>
       <c r="T9" t="n">
-        <v>1.462338286659661</v>
+        <v>1.39801286411231</v>
       </c>
       <c r="U9" t="n">
         <v>121.2492629006552</v>
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>60.38101971880621</v>
+        <v>57.53807472706776</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=60.38% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=57.54% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1275,52 +1275,52 @@
         <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>94.09836086304119</v>
+        <v>90.90668407086</v>
       </c>
       <c r="H10" t="n">
-        <v>2.469549318102043</v>
+        <v>2.459546181486654</v>
       </c>
       <c r="I10" t="n">
         <v>164.4874496413386</v>
       </c>
       <c r="J10" t="n">
-        <v>70.87492957255627</v>
+        <v>80.62136290545641</v>
       </c>
       <c r="K10" t="n">
-        <v>1.743550528453186</v>
+        <v>1.954195725687168</v>
       </c>
       <c r="L10" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M10" t="n">
-        <v>98.35805555312848</v>
+        <v>98.21286575944892</v>
       </c>
       <c r="N10" t="n">
-        <v>7.979166666666667</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="P10" t="n">
-        <v>98.35805555312848</v>
+        <v>98.21286575944892</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.979166666666667</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
         <v>168.5443712458804</v>
       </c>
       <c r="S10" t="n">
-        <v>67.17437521781342</v>
+        <v>65.3176995141846</v>
       </c>
       <c r="T10" t="n">
-        <v>1.888005259843791</v>
+        <v>1.888960773953696</v>
       </c>
       <c r="U10" t="n">
         <v>114.746491150853</v>
@@ -1336,11 +1336,11 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>67.17437521781342</v>
+        <v>65.3176995141846</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=67.17% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=65.32% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1364,52 +1364,52 @@
         <v>2026</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>180.5912829636609</v>
+        <v>181.515507584439</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6271038884279009</v>
+        <v>0.6173266662411392</v>
       </c>
       <c r="I11" t="n">
         <v>123.2554563734294</v>
       </c>
       <c r="J11" t="n">
-        <v>198.3768860507129</v>
+        <v>198.496465086452</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6326279513561061</v>
+        <v>0.6359759888102187</v>
       </c>
       <c r="L11" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M11" t="n">
-        <v>184.0006723040351</v>
+        <v>181.3852359729555</v>
       </c>
       <c r="N11" t="n">
-        <v>24.83966940089766</v>
+        <v>23.063540985444</v>
       </c>
       <c r="O11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="P11" t="n">
-        <v>164.1208671336508</v>
+        <v>166.0092425476692</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.033113770360409</v>
+        <v>0.9921050187942237</v>
       </c>
       <c r="R11" t="n">
         <v>177.781032308345</v>
       </c>
       <c r="S11" t="n">
-        <v>122.8450781291039</v>
+        <v>123.5450259718557</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6583270558379246</v>
+        <v>0.7176289557794688</v>
       </c>
       <c r="U11" t="n">
         <v>147.9725418621825</v>
@@ -1425,11 +1425,11 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>122.8450781291039</v>
+        <v>123.5450259718557</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=122.85% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=123.55% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         <v>2026</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" t="n">
         <v>9</v>
@@ -1462,43 +1462,43 @@
         <v>192.5956874696411</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3805759804516898</v>
+        <v>0.351300905032329</v>
       </c>
       <c r="I12" t="n">
         <v>147.3485671696691</v>
       </c>
       <c r="J12" t="n">
-        <v>199.592216994113</v>
+        <v>199.6235849176428</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4024294311096615</v>
+        <v>0.4164095901696</v>
       </c>
       <c r="L12" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M12" t="n">
-        <v>186.6328560004902</v>
+        <v>187.6610978466063</v>
       </c>
       <c r="N12" t="n">
-        <v>11.43628874858557</v>
+        <v>10.67195884484822</v>
       </c>
       <c r="O12" t="n">
         <v>191.4723960783834</v>
       </c>
       <c r="P12" t="n">
-        <v>182.9634089977751</v>
+        <v>183.7041303456979</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.19533977745468</v>
+        <v>9.46877517918894</v>
       </c>
       <c r="R12" t="n">
         <v>189.6908701459495</v>
       </c>
       <c r="S12" t="n">
-        <v>160.8083634936527</v>
+        <v>163.8231047633718</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5588063692567461</v>
+        <v>0.5920824067350805</v>
       </c>
       <c r="U12" t="n">
         <v>169.7722333133142</v>
@@ -1540,52 +1540,52 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>196.2147133828711</v>
+        <v>196.5301539342985</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2547623139884086</v>
+        <v>0.2736267513739156</v>
       </c>
       <c r="I13" t="n">
         <v>157.1522264328246</v>
       </c>
       <c r="J13" t="n">
-        <v>199.8323997562024</v>
+        <v>199.8277670092382</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2511518590666376</v>
+        <v>0.2703163975234029</v>
       </c>
       <c r="L13" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M13" t="n">
-        <v>188.8568686401676</v>
+        <v>183.5601864370778</v>
       </c>
       <c r="N13" t="n">
-        <v>13.38919299420255</v>
+        <v>12.43617814849466</v>
       </c>
       <c r="O13" t="n">
         <v>193.9340304002594</v>
       </c>
       <c r="P13" t="n">
-        <v>192.5207401661846</v>
+        <v>192.8768953963663</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.380437065634474</v>
+        <v>5.005018829816438</v>
       </c>
       <c r="R13" t="n">
         <v>188.2053733911598</v>
       </c>
       <c r="S13" t="n">
-        <v>159.7205184268186</v>
+        <v>156.1223227898773</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4013584377309827</v>
+        <v>0.4111642329034779</v>
       </c>
       <c r="U13" t="n">
         <v>173.7069303697712</v>
@@ -1603,7 +1603,7 @@
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1627,52 +1627,52 @@
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="G14" t="n">
-        <v>68.78636566054853</v>
+        <v>70.1958408791165</v>
       </c>
       <c r="H14" t="n">
-        <v>2.398797942000959</v>
+        <v>2.736183592451876</v>
       </c>
       <c r="I14" t="n">
         <v>66.61025297793201</v>
       </c>
       <c r="J14" t="n">
-        <v>74.64024737042836</v>
+        <v>72.37581760472351</v>
       </c>
       <c r="K14" t="n">
-        <v>2.663120287868505</v>
+        <v>3.007663214842723</v>
       </c>
       <c r="L14" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M14" t="n">
-        <v>162.5696016821114</v>
+        <v>159.5399375746496</v>
       </c>
       <c r="N14" t="n">
-        <v>33.94284318140149</v>
+        <v>34.0281274780627</v>
       </c>
       <c r="O14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="P14" t="n">
-        <v>180.7124883532208</v>
+        <v>180.7733847934277</v>
       </c>
       <c r="Q14" t="n">
-        <v>80.77083333333333</v>
+        <v>91.01923076923077</v>
       </c>
       <c r="R14" t="n">
         <v>186.0423288913966</v>
       </c>
       <c r="S14" t="n">
-        <v>82.35502468392289</v>
+        <v>87.66138746028537</v>
       </c>
       <c r="T14" t="n">
-        <v>6.871554460679278</v>
+        <v>11.71729553707351</v>
       </c>
       <c r="U14" t="n">
         <v>130.2296761771863</v>
@@ -1688,11 +1688,11 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>68.78636566054853</v>
+        <v>70.1958408791165</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=68.79% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=70.20% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1716,52 +1716,52 @@
         <v>2026</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F15" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
-        <v>66.98812300624824</v>
+        <v>68.83481220671345</v>
       </c>
       <c r="H15" t="n">
-        <v>1.113216586572249</v>
+        <v>1.268116397136053</v>
       </c>
       <c r="I15" t="n">
         <v>82.6747998505866</v>
       </c>
       <c r="J15" t="n">
-        <v>85.87658830892269</v>
+        <v>81.22456724195349</v>
       </c>
       <c r="K15" t="n">
-        <v>1.393093045066255</v>
+        <v>1.379338892325262</v>
       </c>
       <c r="L15" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M15" t="n">
-        <v>170.0041191689805</v>
+        <v>168.0571596557481</v>
       </c>
       <c r="N15" t="n">
-        <v>22.8812290192702</v>
+        <v>23.13369034589022</v>
       </c>
       <c r="O15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="P15" t="n">
-        <v>177.7948935468054</v>
+        <v>178.2169897626607</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.45833333333334</v>
+        <v>43.94230769230769</v>
       </c>
       <c r="R15" t="n">
         <v>186.4460938550808</v>
       </c>
       <c r="S15" t="n">
-        <v>84.71438220335999</v>
+        <v>89.94521924807745</v>
       </c>
       <c r="T15" t="n">
-        <v>3.26651252462619</v>
+        <v>5.524349859202757</v>
       </c>
       <c r="U15" t="n">
         <v>131.9030800529592</v>
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>66.98812300624824</v>
+        <v>68.83481220671345</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=66.99% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=68.83% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1805,59 +1805,59 @@
         <v>2026</v>
       </c>
       <c r="E16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>112.5264090609578</v>
+        <v>111.1712374987075</v>
       </c>
       <c r="H16" t="n">
-        <v>1.740920392753358</v>
+        <v>1.918207186286123</v>
       </c>
       <c r="I16" t="n">
         <v>90.20708978859948</v>
       </c>
       <c r="J16" t="n">
-        <v>120.0955416391536</v>
+        <v>115.8528555849145</v>
       </c>
       <c r="K16" t="n">
-        <v>1.470569981840985</v>
+        <v>1.837330136736047</v>
       </c>
       <c r="L16" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M16" t="n">
-        <v>172.5483151230665</v>
+        <v>170.0377875017184</v>
       </c>
       <c r="N16" t="n">
-        <v>23.96177419821775</v>
+        <v>24.2248835744896</v>
       </c>
       <c r="O16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="P16" t="n">
-        <v>182.1050992459377</v>
+        <v>181.9337683311368</v>
       </c>
       <c r="Q16" t="n">
-        <v>42.375</v>
+        <v>47.13461538461539</v>
       </c>
       <c r="R16" t="n">
         <v>186.1307414343702</v>
       </c>
       <c r="S16" t="n">
-        <v>106.5011998637745</v>
+        <v>109.723969075079</v>
       </c>
       <c r="T16" t="n">
-        <v>3.347004642725491</v>
+        <v>5.827568191103187</v>
       </c>
       <c r="U16" t="n">
         <v>133.2708900338696</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>106.5011998637745</v>
+        <v>111.1712374987075</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=106.50% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=111.17% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -1894,25 +1894,25 @@
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>198.9987496274345</v>
+        <v>199.0757688868626</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1112527512550425</v>
+        <v>0.1178858876047085</v>
       </c>
       <c r="I17" t="n">
         <v>194.5446671655584</v>
       </c>
       <c r="J17" t="n">
-        <v>199.9549956995655</v>
+        <v>199.9584575688297</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0439123054440127</v>
+        <v>0.04071459157096483</v>
       </c>
       <c r="L17" t="n">
         <v>109.609711216533</v>
@@ -1921,7 +1921,7 @@
         <v>200</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="O17" t="n">
         <v>196.7571923388938</v>
@@ -1930,16 +1930,16 @@
         <v>200</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="R17" t="n">
         <v>197.0125798901019</v>
       </c>
       <c r="S17" t="n">
-        <v>198.9692946971688</v>
+        <v>199.0485797204635</v>
       </c>
       <c r="T17" t="n">
-        <v>0.04797756857827003</v>
+        <v>0.04428698637994159</v>
       </c>
       <c r="U17" t="n">
         <v>192.256373806382</v>
@@ -1981,7 +1981,7 @@
         <v>2026</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.02469487618589014</v>
+        <v>0.03213318165902102</v>
       </c>
       <c r="I18" t="n">
         <v>199.6410247115898</v>
@@ -1999,7 +1999,7 @@
         <v>200</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0005610538594717875</v>
+        <v>0.0005621916357963347</v>
       </c>
       <c r="L18" t="n">
         <v>79.54507935933471</v>
@@ -2022,7 +2022,7 @@
         <v>200</v>
       </c>
       <c r="T18" t="n">
-        <v>4.242192837297683e-263</v>
+        <v>3.915870311351707e-263</v>
       </c>
       <c r="U18" t="n">
         <v>196.0211023092105</v>
@@ -2064,25 +2064,25 @@
         <v>2026</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.246564725076</v>
+        <v>199.30683954707</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09538539145820128</v>
+        <v>0.1010139478438304</v>
       </c>
       <c r="I19" t="n">
         <v>196.278530387405</v>
       </c>
       <c r="J19" t="n">
-        <v>199.8967026227874</v>
+        <v>199.9046485748806</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04645743202683102</v>
+        <v>0.04327476996875143</v>
       </c>
       <c r="L19" t="n">
         <v>109.7635513825217</v>
@@ -2091,7 +2091,7 @@
         <v>200</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="O19" t="n">
         <v>196.7189002085085</v>
@@ -2100,16 +2100,16 @@
         <v>200</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.09615384615384616</v>
       </c>
       <c r="R19" t="n">
         <v>196.7488584326798</v>
       </c>
       <c r="S19" t="n">
-        <v>199.0659579938217</v>
+        <v>199.1378073789123</v>
       </c>
       <c r="T19" t="n">
-        <v>0.04869846746450934</v>
+        <v>0.04495243150570093</v>
       </c>
       <c r="U19" t="n">
         <v>197.8046914283761</v>
@@ -2151,7 +2151,7 @@
         <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07101922894124693</v>
+        <v>0.07124381545859265</v>
       </c>
       <c r="I20" t="n">
         <v>200</v>
@@ -2169,7 +2169,7 @@
         <v>200</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00135199373175945</v>
+        <v>0.001318309886591289</v>
       </c>
       <c r="L20" t="n">
         <v>109.609711216533</v>
@@ -2192,7 +2192,7 @@
         <v>200</v>
       </c>
       <c r="T20" t="n">
-        <v>6250</v>
+        <v>5769.23076923077</v>
       </c>
       <c r="U20" t="n">
         <v>200</v>
@@ -2234,7 +2234,7 @@
         <v>2026</v>
       </c>
       <c r="E21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05715685033181415</v>
+        <v>0.05733506266469365</v>
       </c>
       <c r="I21" t="n">
         <v>200</v>
@@ -2252,7 +2252,7 @@
         <v>200</v>
       </c>
       <c r="K21" t="n">
-        <v>0.006040243875664572</v>
+        <v>0.006075711302686262</v>
       </c>
       <c r="L21" t="n">
         <v>79.54507935933471</v>
@@ -2275,7 +2275,7 @@
         <v>200</v>
       </c>
       <c r="T21" t="n">
-        <v>14583.33333340942</v>
+        <v>13461.5384616087</v>
       </c>
       <c r="U21" t="n">
         <v>200</v>
@@ -2317,7 +2317,7 @@
         <v>2026</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0639970336351797</v>
+        <v>0.06419987238281549</v>
       </c>
       <c r="I22" t="n">
         <v>200</v>
@@ -2335,7 +2335,7 @@
         <v>200</v>
       </c>
       <c r="K22" t="n">
-        <v>0.000397037299094625</v>
+        <v>0.0004004337771155077</v>
       </c>
       <c r="L22" t="n">
         <v>109.7635513825217</v>
@@ -2358,7 +2358,7 @@
         <v>200</v>
       </c>
       <c r="T22" t="n">
-        <v>2.679548501589419e-17</v>
+        <v>2.473430849578971e-17</v>
       </c>
       <c r="U22" t="n">
         <v>200</v>
@@ -2400,52 +2400,52 @@
         <v>2026</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F23" t="n">
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>189.5869565095285</v>
+        <v>191.6695652076228</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1272192625621998</v>
+        <v>0.1549098148173384</v>
       </c>
       <c r="I23" t="n">
         <v>149.2565324185079</v>
       </c>
       <c r="J23" t="n">
-        <v>199.4157035257112</v>
+        <v>199.4606494083488</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3874155932337184</v>
+        <v>0.838262376823547</v>
       </c>
       <c r="L23" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M23" t="n">
-        <v>194.2857142857143</v>
+        <v>195.2380952380952</v>
       </c>
       <c r="N23" t="n">
-        <v>1.875</v>
+        <v>4.316793663519504</v>
       </c>
       <c r="O23" t="n">
         <v>169.6992056798271</v>
       </c>
       <c r="P23" t="n">
-        <v>194.2857142857143</v>
+        <v>195.2380952380952</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.875</v>
+        <v>5.307692307692307</v>
       </c>
       <c r="R23" t="n">
         <v>186.3774873978808</v>
       </c>
       <c r="S23" t="n">
-        <v>191.4105963705904</v>
+        <v>192.0713197266988</v>
       </c>
       <c r="T23" t="n">
-        <v>0.338078850963736</v>
+        <v>0.7520862116405661</v>
       </c>
       <c r="U23" t="n">
         <v>159.9263814945425</v>
@@ -2487,52 +2487,52 @@
         <v>2026</v>
       </c>
       <c r="E24" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>191.1105522650305</v>
+        <v>193.3329141987729</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06057232076800143</v>
+        <v>0.0736243714974817</v>
       </c>
       <c r="I24" t="n">
         <v>156.2502876793226</v>
       </c>
       <c r="J24" t="n">
-        <v>198.8307920869546</v>
+        <v>198.9207311571889</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1836614891690675</v>
+        <v>0.7476191834856146</v>
       </c>
       <c r="L24" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M24" t="n">
-        <v>169.1274787406131</v>
+        <v>179.4183191604088</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4258575985829036</v>
+        <v>1.044049313435188</v>
       </c>
       <c r="O24" t="n">
         <v>159.6122718089852</v>
       </c>
       <c r="P24" t="n">
-        <v>183.3333333333333</v>
+        <v>187.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.7083333333333334</v>
+        <v>2.211538461538462</v>
       </c>
       <c r="R24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="S24" t="n">
-        <v>194.1183840753929</v>
+        <v>194.5708160695934</v>
       </c>
       <c r="T24" t="n">
-        <v>0.168721598493243</v>
+        <v>0.3302519970580709</v>
       </c>
       <c r="U24" t="n">
         <v>166.4426133688291</v>
@@ -2574,7 +2574,7 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2583,16 +2583,16 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>0.07062044496379477</v>
+        <v>0.0851379480990028</v>
       </c>
       <c r="I25" t="n">
         <v>155.3955473497874</v>
       </c>
       <c r="J25" t="n">
-        <v>199.9318612064084</v>
+        <v>199.9371026520693</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0701348939381</v>
+        <v>0.3177389752069076</v>
       </c>
       <c r="L25" t="n">
         <v>109.7635513825217</v>
@@ -2601,7 +2601,7 @@
         <v>200</v>
       </c>
       <c r="N25" t="n">
-        <v>1.229166666666667</v>
+        <v>3.153846153846154</v>
       </c>
       <c r="O25" t="n">
         <v>177.0659734750362</v>
@@ -2610,23 +2610,23 @@
         <v>200</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.229166666666667</v>
+        <v>3.153846153846154</v>
       </c>
       <c r="R25" t="n">
         <v>183.340259481936</v>
       </c>
       <c r="S25" t="n">
-        <v>199.6423641372105</v>
+        <v>199.6698745881943</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2384298444055527</v>
+        <v>0.4625315179892543</v>
       </c>
       <c r="U25" t="n">
         <v>180.6321027113416</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2637,7 +2637,7 @@
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
         <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02200870226558647</v>
+        <v>0.02031572516823366</v>
       </c>
       <c r="I26" t="n">
         <v>97.19414576199205</v>
@@ -2679,7 +2679,7 @@
         <v>200</v>
       </c>
       <c r="K26" t="n">
-        <v>0.105833757744135</v>
+        <v>0.1448044608516833</v>
       </c>
       <c r="L26" t="n">
         <v>109.609711216533</v>
@@ -2688,7 +2688,7 @@
         <v>200</v>
       </c>
       <c r="N26" t="n">
-        <v>70.3125</v>
+        <v>72.86538461538461</v>
       </c>
       <c r="O26" t="n">
         <v>198.3074653131699</v>
@@ -2697,7 +2697,7 @@
         <v>200</v>
       </c>
       <c r="Q26" t="n">
-        <v>70.3125</v>
+        <v>72.86538461538461</v>
       </c>
       <c r="R26" t="n">
         <v>199.6509594119097</v>
@@ -2706,7 +2706,7 @@
         <v>200</v>
       </c>
       <c r="T26" t="n">
-        <v>1.138951792336027</v>
+        <v>1.285590062997845</v>
       </c>
       <c r="U26" t="n">
         <v>183.6686755299509</v>
@@ -2748,7 +2748,7 @@
         <v>2026</v>
       </c>
       <c r="E27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01541049055402086</v>
+        <v>0.01422506820371157</v>
       </c>
       <c r="I27" t="n">
         <v>129.0985231723771</v>
@@ -2766,7 +2766,7 @@
         <v>200</v>
       </c>
       <c r="K27" t="n">
-        <v>0.01137759494141414</v>
+        <v>0.01233773058711022</v>
       </c>
       <c r="L27" t="n">
         <v>79.54507935933471</v>
@@ -2775,7 +2775,7 @@
         <v>200</v>
       </c>
       <c r="N27" t="n">
-        <v>34.4375</v>
+        <v>36.05769230769231</v>
       </c>
       <c r="O27" t="n">
         <v>198.6114841856233</v>
@@ -2784,7 +2784,7 @@
         <v>200</v>
       </c>
       <c r="Q27" t="n">
-        <v>34.4375</v>
+        <v>36.05769230769231</v>
       </c>
       <c r="R27" t="n">
         <v>199.779644487174</v>
@@ -2793,7 +2793,7 @@
         <v>200</v>
       </c>
       <c r="T27" t="n">
-        <v>0.7753725409691095</v>
+        <v>0.8885456236906393</v>
       </c>
       <c r="U27" t="n">
         <v>192.722098187243</v>
@@ -2835,7 +2835,7 @@
         <v>2026</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0155484488781284</v>
+        <v>0.0143524143490416</v>
       </c>
       <c r="I28" t="n">
         <v>127.1718885128103</v>
@@ -2853,7 +2853,7 @@
         <v>200</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05058959153596346</v>
+        <v>0.2261063548282595</v>
       </c>
       <c r="L28" t="n">
         <v>109.7635513825217</v>
@@ -2862,7 +2862,7 @@
         <v>200</v>
       </c>
       <c r="N28" t="n">
-        <v>35.875</v>
+        <v>36.80769230769231</v>
       </c>
       <c r="O28" t="n">
         <v>197.4940180993655</v>
@@ -2871,7 +2871,7 @@
         <v>200</v>
       </c>
       <c r="Q28" t="n">
-        <v>35.875</v>
+        <v>36.80769230769231</v>
       </c>
       <c r="R28" t="n">
         <v>199.5411797194807</v>
@@ -2880,7 +2880,7 @@
         <v>200</v>
       </c>
       <c r="T28" t="n">
-        <v>0.83269649664334</v>
+        <v>0.8966237872700616</v>
       </c>
       <c r="U28" t="n">
         <v>184.9627687949149</v>
@@ -2922,25 +2922,25 @@
         <v>2026</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>197.0275577348071</v>
+        <v>197.2752612569065</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1473758985359336</v>
+        <v>0.165481408153559</v>
       </c>
       <c r="I29" t="n">
         <v>191.5075017030775</v>
       </c>
       <c r="J29" t="n">
-        <v>199.6578908654198</v>
+        <v>199.6842069526952</v>
       </c>
       <c r="K29" t="n">
-        <v>0.06570026843773663</v>
+        <v>0.06251244142477602</v>
       </c>
       <c r="L29" t="n">
         <v>109.609711216533</v>
@@ -2949,7 +2949,7 @@
         <v>200</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="O29" t="n">
         <v>198.5277121400952</v>
@@ -2958,16 +2958,16 @@
         <v>200</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="R29" t="n">
         <v>199.9388941772115</v>
       </c>
       <c r="S29" t="n">
-        <v>199.999961272195</v>
+        <v>199.999964251257</v>
       </c>
       <c r="T29" t="n">
-        <v>0.07295291457808649</v>
+        <v>0.06751301021021251</v>
       </c>
       <c r="U29" t="n">
         <v>192.5799615112869</v>
@@ -3009,7 +3009,7 @@
         <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3018,7 +3018,7 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1007596403583528</v>
+        <v>0.1198547547246342</v>
       </c>
       <c r="I30" t="n">
         <v>196.0386411854094</v>
@@ -3027,7 +3027,7 @@
         <v>200</v>
       </c>
       <c r="K30" t="n">
-        <v>0.005811931459301625</v>
+        <v>0.006022060414032323</v>
       </c>
       <c r="L30" t="n">
         <v>79.54507935933471</v>
@@ -3036,7 +3036,7 @@
         <v>200</v>
       </c>
       <c r="N30" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="O30" t="n">
         <v>198.9477887234591</v>
@@ -3045,7 +3045,7 @@
         <v>200</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="R30" t="n">
         <v>199.7754683359127</v>
@@ -3054,7 +3054,7 @@
         <v>200</v>
       </c>
       <c r="T30" t="n">
-        <v>0.020527641695696</v>
+        <v>0.01909230307143704</v>
       </c>
       <c r="U30" t="n">
         <v>198.9226798174336</v>
@@ -3096,25 +3096,25 @@
         <v>2026</v>
       </c>
       <c r="E31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>197.3364790654304</v>
+        <v>197.5495607401959</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1431302305581424</v>
+        <v>0.1596547285707901</v>
       </c>
       <c r="I31" t="n">
         <v>194.2466814459454</v>
       </c>
       <c r="J31" t="n">
-        <v>199.8899201942293</v>
+        <v>199.8983878715963</v>
       </c>
       <c r="K31" t="n">
-        <v>0.04713093038733673</v>
+        <v>0.04410647872176808</v>
       </c>
       <c r="L31" t="n">
         <v>109.7635513825217</v>
@@ -3123,7 +3123,7 @@
         <v>200</v>
       </c>
       <c r="N31" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="O31" t="n">
         <v>199.0633013569061</v>
@@ -3132,16 +3132,16 @@
         <v>200</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="R31" t="n">
         <v>199.9196066031173</v>
       </c>
       <c r="S31" t="n">
-        <v>199.9999999917521</v>
+        <v>199.9999999923865</v>
       </c>
       <c r="T31" t="n">
-        <v>0.05472020386558352</v>
+        <v>0.05052019072418547</v>
       </c>
       <c r="U31" t="n">
         <v>194.1597056483905</v>
@@ -3183,52 +3183,52 @@
         <v>2026</v>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F32" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>144.1198765122525</v>
+        <v>136.4384553168091</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7441079019883944</v>
+        <v>0.9088263617437347</v>
       </c>
       <c r="I32" t="n">
         <v>164.6748490827784</v>
       </c>
       <c r="J32" t="n">
-        <v>166.1972827302878</v>
+        <v>159.6862497058564</v>
       </c>
       <c r="K32" t="n">
-        <v>1.216894351016665</v>
+        <v>1.377016198743123</v>
       </c>
       <c r="L32" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M32" t="n">
-        <v>157.9374441348126</v>
+        <v>157.5789375132153</v>
       </c>
       <c r="N32" t="n">
-        <v>10.04166666666667</v>
+        <v>12.25</v>
       </c>
       <c r="O32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="P32" t="n">
-        <v>157.9374441348126</v>
+        <v>157.5789375132153</v>
       </c>
       <c r="Q32" t="n">
-        <v>10.04166666666667</v>
+        <v>12.25</v>
       </c>
       <c r="R32" t="n">
         <v>195.3761640213164</v>
       </c>
       <c r="S32" t="n">
-        <v>143.3697981039369</v>
+        <v>144.7850261687545</v>
       </c>
       <c r="T32" t="n">
-        <v>2.141585587987389</v>
+        <v>5.942491840375366</v>
       </c>
       <c r="U32" t="n">
         <v>173.3959783787531</v>
@@ -3244,11 +3244,11 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>144.1198765122525</v>
+        <v>136.4384553168091</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=144.12% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=136.44% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -3272,52 +3272,52 @@
         <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G33" t="n">
-        <v>158.0334561427051</v>
+        <v>139.8117872004429</v>
       </c>
       <c r="H33" t="n">
-        <v>0.301546770546361</v>
+        <v>0.2855099710301251</v>
       </c>
       <c r="I33" t="n">
         <v>170.4028696730483</v>
       </c>
       <c r="J33" t="n">
-        <v>181.5351440239996</v>
+        <v>172.4959078110981</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4630544675113303</v>
+        <v>0.6838980996468932</v>
       </c>
       <c r="L33" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M33" t="n">
-        <v>187.8183831672204</v>
+        <v>181.6029900332226</v>
       </c>
       <c r="N33" t="n">
-        <v>4.083333333333333</v>
+        <v>4.807692307692307</v>
       </c>
       <c r="O33" t="n">
         <v>180.7526372107734</v>
       </c>
       <c r="P33" t="n">
-        <v>187.8183831672204</v>
+        <v>181.6029900332226</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.083333333333333</v>
+        <v>4.807692307692307</v>
       </c>
       <c r="R33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="S33" t="n">
-        <v>176.8750401881282</v>
+        <v>172.0138066156621</v>
       </c>
       <c r="T33" t="n">
-        <v>0.6516481255066526</v>
+        <v>1.228747777109315</v>
       </c>
       <c r="U33" t="n">
         <v>182.3083787234438</v>
@@ -3329,13 +3329,15 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>139.8117872004429</v>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=139.81% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -3359,52 +3361,52 @@
         <v>2026</v>
       </c>
       <c r="E34" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G34" t="n">
-        <v>156.0829422059128</v>
+        <v>150.568521206798</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6589674712418576</v>
+        <v>0.836651906100444</v>
       </c>
       <c r="I34" t="n">
         <v>169.6571057340244</v>
       </c>
       <c r="J34" t="n">
-        <v>171.1311227876345</v>
+        <v>169.7651776711998</v>
       </c>
       <c r="K34" t="n">
-        <v>3.137910561965469</v>
+        <v>4.2457171071596</v>
       </c>
       <c r="L34" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M34" t="n">
-        <v>168.4256150656863</v>
+        <v>167.6757509073452</v>
       </c>
       <c r="N34" t="n">
-        <v>6.5</v>
+        <v>7.942307692307693</v>
       </c>
       <c r="O34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="P34" t="n">
-        <v>168.4256150656863</v>
+        <v>167.6757509073452</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.5</v>
+        <v>7.942307692307693</v>
       </c>
       <c r="R34" t="n">
         <v>195.2398047728465</v>
       </c>
       <c r="S34" t="n">
-        <v>153.1386443458626</v>
+        <v>153.4535494003401</v>
       </c>
       <c r="T34" t="n">
-        <v>1.117764354865418</v>
+        <v>2.609194376670224</v>
       </c>
       <c r="U34" t="n">
         <v>176.7243686471345</v>
@@ -3420,11 +3422,11 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>156.0829422059128</v>
+        <v>150.568521206798</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=156.08% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=150.57% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -3448,52 +3450,52 @@
         <v>2026</v>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
-        <v>116.8979864259819</v>
+        <v>120.0269946697649</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6414754500263838</v>
+        <v>0.6288707011427206</v>
       </c>
       <c r="I35" t="n">
         <v>48.55849570822402</v>
       </c>
       <c r="J35" t="n">
-        <v>129.7312553309233</v>
+        <v>132.6935847973162</v>
       </c>
       <c r="K35" t="n">
-        <v>1.152761421673629</v>
+        <v>1.41605812453869</v>
       </c>
       <c r="L35" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M35" t="n">
-        <v>190.8516231199793</v>
+        <v>191.1576938126877</v>
       </c>
       <c r="N35" t="n">
-        <v>31.76489407303251</v>
+        <v>32.21614184248983</v>
       </c>
       <c r="O35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="P35" t="n">
-        <v>198.0457667956422</v>
+        <v>198.1187828016984</v>
       </c>
       <c r="Q35" t="n">
-        <v>170.9807379841873</v>
+        <v>173.9018700236352</v>
       </c>
       <c r="R35" t="n">
         <v>185.853149170162</v>
       </c>
       <c r="S35" t="n">
-        <v>138.5481828361519</v>
+        <v>142.2217601484261</v>
       </c>
       <c r="T35" t="n">
-        <v>2.967085931556756</v>
+        <v>3.827236981373604</v>
       </c>
       <c r="U35" t="n">
         <v>110.5529101365675</v>
@@ -3509,11 +3511,11 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>116.8979864259819</v>
+        <v>120.0269946697649</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=116.90% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=120.03% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3539,7 @@
         <v>2026</v>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
         <v>9</v>
@@ -3546,43 +3548,43 @@
         <v>165.4537784983441</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4506368854945325</v>
+        <v>0.4159725096872607</v>
       </c>
       <c r="I36" t="n">
         <v>58.86670393327421</v>
       </c>
       <c r="J36" t="n">
-        <v>166.4007305232537</v>
+        <v>168.9852897137726</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7167570211664328</v>
+        <v>0.8438138868550287</v>
       </c>
       <c r="L36" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M36" t="n">
-        <v>186.7457909399486</v>
+        <v>187.7653454830295</v>
       </c>
       <c r="N36" t="n">
-        <v>9.734355160027052</v>
+        <v>10.03105728252018</v>
       </c>
       <c r="O36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="P36" t="n">
-        <v>198.2277240316573</v>
+        <v>198.364052952299</v>
       </c>
       <c r="Q36" t="n">
-        <v>83.80329933474678</v>
+        <v>84.7415070782278</v>
       </c>
       <c r="R36" t="n">
         <v>187.2910306593169</v>
       </c>
       <c r="S36" t="n">
-        <v>161.2464665195107</v>
+        <v>164.2275075564714</v>
       </c>
       <c r="T36" t="n">
-        <v>1.706659111411458</v>
+        <v>2.165195990873503</v>
       </c>
       <c r="U36" t="n">
         <v>118.8153464644226</v>
@@ -3624,52 +3626,52 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
-        <v>159.8648785235238</v>
+        <v>161.9002846937967</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5375794385995696</v>
+        <v>0.5332963051073031</v>
       </c>
       <c r="I37" t="n">
         <v>60.32903496111531</v>
       </c>
       <c r="J37" t="n">
-        <v>169.9169994755493</v>
+        <v>168.8038084510468</v>
       </c>
       <c r="K37" t="n">
-        <v>1.062051652510472</v>
+        <v>1.191727828613862</v>
       </c>
       <c r="L37" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M37" t="n">
-        <v>184.68147581926</v>
+        <v>184.8161119307371</v>
       </c>
       <c r="N37" t="n">
-        <v>9.933022199180121</v>
+        <v>10.19318387103714</v>
       </c>
       <c r="O37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="P37" t="n">
-        <v>197.8759239898324</v>
+        <v>197.9055351879389</v>
       </c>
       <c r="Q37" t="n">
-        <v>88.56837843626886</v>
+        <v>90.56059711647093</v>
       </c>
       <c r="R37" t="n">
         <v>185.3862117422507</v>
       </c>
       <c r="S37" t="n">
-        <v>156.7412318015016</v>
+        <v>158.2676147173262</v>
       </c>
       <c r="T37" t="n">
-        <v>1.775045998738149</v>
+        <v>2.210830069810609</v>
       </c>
       <c r="U37" t="n">
         <v>110.8838400280787</v>
@@ -3681,13 +3683,15 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>161.9002846937967</v>
+      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=161.90% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -3711,52 +3715,52 @@
         <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>193.6603031715468</v>
+        <v>186.7585467679683</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5502117871569219</v>
+        <v>0.5553684594761084</v>
       </c>
       <c r="I38" t="n">
         <v>164.4263244057969</v>
       </c>
       <c r="J38" t="n">
-        <v>194.8852119657672</v>
+        <v>191.4574463290842</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7201488391456481</v>
+        <v>0.8441273509148057</v>
       </c>
       <c r="L38" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M38" t="n">
-        <v>186.1363636363636</v>
+        <v>186.9731760776537</v>
       </c>
       <c r="N38" t="n">
-        <v>13.52083333333333</v>
+        <v>17.11538461538462</v>
       </c>
       <c r="O38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="P38" t="n">
-        <v>186.1363636363636</v>
+        <v>186.9731760776537</v>
       </c>
       <c r="Q38" t="n">
-        <v>13.52083333333333</v>
+        <v>17.11538461538462</v>
       </c>
       <c r="R38" t="n">
         <v>199.036270909302</v>
       </c>
       <c r="S38" t="n">
-        <v>187.7048504927184</v>
+        <v>186.3039188319287</v>
       </c>
       <c r="T38" t="n">
-        <v>0.6418559263963389</v>
+        <v>0.9283347032724557</v>
       </c>
       <c r="U38" t="n">
         <v>129.2920232398837</v>
@@ -3774,7 +3778,7 @@
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3798,52 +3802,52 @@
         <v>2026</v>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>198.8219130250654</v>
+        <v>198.9125351000604</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1730604370946455</v>
+        <v>0.1704836994124694</v>
       </c>
       <c r="I39" t="n">
         <v>170.2041702191862</v>
       </c>
       <c r="J39" t="n">
-        <v>199.3241476838446</v>
+        <v>199.3761363235489</v>
       </c>
       <c r="K39" t="n">
-        <v>0.09970820878019504</v>
+        <v>0.09436105974426881</v>
       </c>
       <c r="L39" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M39" t="n">
-        <v>186.0869565217391</v>
+        <v>187.2</v>
       </c>
       <c r="N39" t="n">
-        <v>5.854166666666667</v>
+        <v>7.25</v>
       </c>
       <c r="O39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="P39" t="n">
-        <v>186.0869565217391</v>
+        <v>187.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.854166666666667</v>
+        <v>7.25</v>
       </c>
       <c r="R39" t="n">
         <v>199.0467638312102</v>
       </c>
       <c r="S39" t="n">
-        <v>195.3930047151476</v>
+        <v>195.7473889678286</v>
       </c>
       <c r="T39" t="n">
-        <v>0.3098871835001967</v>
+        <v>0.4596834347927579</v>
       </c>
       <c r="U39" t="n">
         <v>146.152525200624</v>
@@ -3885,52 +3889,52 @@
         <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>198.2981578758505</v>
+        <v>194.1141677438596</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2474889189401752</v>
+        <v>0.2682565987196245</v>
       </c>
       <c r="I40" t="n">
         <v>165.7522199768573</v>
       </c>
       <c r="J40" t="n">
-        <v>199.6742990291648</v>
+        <v>199.4838010220985</v>
       </c>
       <c r="K40" t="n">
-        <v>0.09354414265114504</v>
+        <v>0.1245454299554858</v>
       </c>
       <c r="L40" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M40" t="n">
-        <v>189.1666666666667</v>
+        <v>189.6153846153846</v>
       </c>
       <c r="N40" t="n">
-        <v>8.041666666666666</v>
+        <v>10.21153846153846</v>
       </c>
       <c r="O40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="P40" t="n">
-        <v>189.1666666666667</v>
+        <v>189.6153846153846</v>
       </c>
       <c r="Q40" t="n">
-        <v>8.041666666666666</v>
+        <v>10.21153846153846</v>
       </c>
       <c r="R40" t="n">
         <v>198.942356787496</v>
       </c>
       <c r="S40" t="n">
-        <v>195.5475972749778</v>
+        <v>191.6029876294868</v>
       </c>
       <c r="T40" t="n">
-        <v>0.360091758570227</v>
+        <v>0.4760050468291805</v>
       </c>
       <c r="U40" t="n">
         <v>124.2002492905602</v>
@@ -3948,7 +3952,7 @@
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3972,52 +3976,52 @@
         <v>2026</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F41" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G41" t="n">
-        <v>82.36181669230595</v>
+        <v>77.92724717992357</v>
       </c>
       <c r="H41" t="n">
-        <v>2.315633934912618</v>
+        <v>2.212301818876929</v>
       </c>
       <c r="I41" t="n">
         <v>127.4617865350128</v>
       </c>
       <c r="J41" t="n">
-        <v>80.67815950615892</v>
+        <v>81.89642293849408</v>
       </c>
       <c r="K41" t="n">
-        <v>1.807472114623043</v>
+        <v>2.227550347391977</v>
       </c>
       <c r="L41" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M41" t="n">
-        <v>183.2156609274762</v>
+        <v>184.0199928479197</v>
       </c>
       <c r="N41" t="n">
-        <v>76.875</v>
+        <v>90.84615384615384</v>
       </c>
       <c r="O41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="P41" t="n">
-        <v>183.2156609274762</v>
+        <v>184.0199928479197</v>
       </c>
       <c r="Q41" t="n">
-        <v>76.875</v>
+        <v>90.84615384615384</v>
       </c>
       <c r="R41" t="n">
         <v>198.8825072752037</v>
       </c>
       <c r="S41" t="n">
-        <v>67.99944625466701</v>
+        <v>72.68033743905205</v>
       </c>
       <c r="T41" t="n">
-        <v>1.790465524326272</v>
+        <v>2.739741236221613</v>
       </c>
       <c r="U41" t="n">
         <v>124.7888620818299</v>
@@ -4033,11 +4037,11 @@
         </is>
       </c>
       <c r="X41" t="n">
-        <v>67.99944625466701</v>
+        <v>72.68033743905205</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=68.00% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=72.68% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4061,52 +4065,52 @@
         <v>2026</v>
       </c>
       <c r="E42" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F42" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G42" t="n">
-        <v>102.7675015291024</v>
+        <v>102.8181551117132</v>
       </c>
       <c r="H42" t="n">
-        <v>1.330768077642003</v>
+        <v>1.305219418515306</v>
       </c>
       <c r="I42" t="n">
         <v>139.5371944473096</v>
       </c>
       <c r="J42" t="n">
-        <v>156.8485070497925</v>
+        <v>157.4561336663125</v>
       </c>
       <c r="K42" t="n">
-        <v>1.673525259402368</v>
+        <v>1.649802586809004</v>
       </c>
       <c r="L42" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M42" t="n">
-        <v>181.200311890131</v>
+        <v>182.4002878985824</v>
       </c>
       <c r="N42" t="n">
-        <v>34.08333333333334</v>
+        <v>40.15384615384615</v>
       </c>
       <c r="O42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="P42" t="n">
-        <v>181.200311890131</v>
+        <v>182.4002878985824</v>
       </c>
       <c r="Q42" t="n">
-        <v>34.08333333333334</v>
+        <v>40.15384615384615</v>
       </c>
       <c r="R42" t="n">
         <v>198.6803521667581</v>
       </c>
       <c r="S42" t="n">
-        <v>84.50088578046086</v>
+        <v>89.21287175816121</v>
       </c>
       <c r="T42" t="n">
-        <v>0.7585201957721628</v>
+        <v>1.067278521000874</v>
       </c>
       <c r="U42" t="n">
         <v>125.9010082864909</v>
@@ -4122,11 +4126,11 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>84.50088578046086</v>
+        <v>89.21287175816121</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=84.50% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=89.21% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4150,59 +4154,59 @@
         <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F43" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>87.28106962397432</v>
+        <v>86.37455469393578</v>
       </c>
       <c r="H43" t="n">
-        <v>1.335705207861408</v>
+        <v>1.385679333576383</v>
       </c>
       <c r="I43" t="n">
         <v>137.8269504556986</v>
       </c>
       <c r="J43" t="n">
-        <v>125.1681580974914</v>
+        <v>125.130614858072</v>
       </c>
       <c r="K43" t="n">
-        <v>1.402398755290558</v>
+        <v>1.515851310470872</v>
       </c>
       <c r="L43" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M43" t="n">
-        <v>186.1328320895093</v>
+        <v>186.4977222744996</v>
       </c>
       <c r="N43" t="n">
-        <v>44.16666666666666</v>
+        <v>51.96153846153846</v>
       </c>
       <c r="O43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="P43" t="n">
-        <v>186.1328320895093</v>
+        <v>186.4977222744996</v>
       </c>
       <c r="Q43" t="n">
-        <v>44.16666666666666</v>
+        <v>51.96153846153846</v>
       </c>
       <c r="R43" t="n">
         <v>198.9631246433146</v>
       </c>
       <c r="S43" t="n">
-        <v>79.0378561004004</v>
+        <v>82.34334736233528</v>
       </c>
       <c r="T43" t="n">
-        <v>1.086405372344756</v>
+        <v>1.602581000227404</v>
       </c>
       <c r="U43" t="n">
         <v>126.6160396504699</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
@@ -4211,11 +4215,11 @@
         </is>
       </c>
       <c r="X43" t="n">
-        <v>79.0378561004004</v>
+        <v>86.37455469393578</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=79.04% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=86.37% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4239,59 +4243,59 @@
         <v>2026</v>
       </c>
       <c r="E44" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F44" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G44" t="n">
-        <v>101.4106959347236</v>
+        <v>103.0105577142707</v>
       </c>
       <c r="H44" t="n">
-        <v>3.596832160579731</v>
+        <v>3.857363668221427</v>
       </c>
       <c r="I44" t="n">
         <v>101.902133963665</v>
       </c>
       <c r="J44" t="n">
-        <v>102.2728260688832</v>
+        <v>100.4112462101342</v>
       </c>
       <c r="K44" t="n">
-        <v>1.69776768391928</v>
+        <v>1.70774239004787</v>
       </c>
       <c r="L44" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M44" t="n">
-        <v>186.1511073484419</v>
+        <v>186.7796297381574</v>
       </c>
       <c r="N44" t="n">
-        <v>83.15822230584824</v>
+        <v>89.76791078069188</v>
       </c>
       <c r="O44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="P44" t="n">
-        <v>186.3314880385136</v>
+        <v>187.0172162311941</v>
       </c>
       <c r="Q44" t="n">
-        <v>91.20833333333333</v>
+        <v>101.9423076923077</v>
       </c>
       <c r="R44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="S44" t="n">
-        <v>94.32385183734597</v>
+        <v>101.2048277356274</v>
       </c>
       <c r="T44" t="n">
-        <v>5.012388893725952</v>
+        <v>8.886579865047516</v>
       </c>
       <c r="U44" t="n">
         <v>121.0188473841644</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
@@ -4300,11 +4304,11 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>94.32385183734597</v>
+        <v>100.4112462101342</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=94.32% sobre 24 sem</t>
+          <t>DeepAR: menor SMAPE real=100.41% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4328,52 +4332,52 @@
         <v>2026</v>
       </c>
       <c r="E45" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F45" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G45" t="n">
-        <v>123.6540232660805</v>
+        <v>125.5252502727978</v>
       </c>
       <c r="H45" t="n">
-        <v>3.300247891535429</v>
+        <v>3.570361775059859</v>
       </c>
       <c r="I45" t="n">
         <v>133.2410714461222</v>
       </c>
       <c r="J45" t="n">
-        <v>127.8483953239954</v>
+        <v>129.9289777485386</v>
       </c>
       <c r="K45" t="n">
-        <v>1.331772445537866</v>
+        <v>1.389499155522514</v>
       </c>
       <c r="L45" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M45" t="n">
-        <v>184.2343130466408</v>
+        <v>184.8553422205679</v>
       </c>
       <c r="N45" t="n">
-        <v>41.54166666666666</v>
+        <v>44.86538461538461</v>
       </c>
       <c r="O45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="P45" t="n">
-        <v>184.2343130466408</v>
+        <v>184.8553422205679</v>
       </c>
       <c r="Q45" t="n">
-        <v>41.54166666666666</v>
+        <v>44.86538461538461</v>
       </c>
       <c r="R45" t="n">
         <v>195.8311934408034</v>
       </c>
       <c r="S45" t="n">
-        <v>103.3194889096851</v>
+        <v>108.7931937538279</v>
       </c>
       <c r="T45" t="n">
-        <v>2.169692890302565</v>
+        <v>3.422300329439217</v>
       </c>
       <c r="U45" t="n">
         <v>112.5504951429215</v>
@@ -4389,11 +4393,11 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>103.3194889096851</v>
+        <v>108.7931937538279</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=103.32% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=108.79% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4417,59 +4421,59 @@
         <v>2026</v>
       </c>
       <c r="E46" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F46" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G46" t="n">
-        <v>133.1211168205784</v>
+        <v>134.4608149355389</v>
       </c>
       <c r="H46" t="n">
-        <v>2.731181544234872</v>
+        <v>2.989627752045402</v>
       </c>
       <c r="I46" t="n">
         <v>129.1401202444324</v>
       </c>
       <c r="J46" t="n">
-        <v>146.232019798444</v>
+        <v>142.0150170963277</v>
       </c>
       <c r="K46" t="n">
-        <v>1.101723379072723</v>
+        <v>1.064136701870199</v>
       </c>
       <c r="L46" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M46" t="n">
-        <v>187.5288824711572</v>
+        <v>188.2191225161923</v>
       </c>
       <c r="N46" t="n">
-        <v>45.5644927119441</v>
+        <v>50.70255772644789</v>
       </c>
       <c r="O46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="P46" t="n">
-        <v>187.7190314249972</v>
+        <v>188.4486636457789</v>
       </c>
       <c r="Q46" t="n">
-        <v>49.91666666666666</v>
+        <v>57.30769230769231</v>
       </c>
       <c r="R46" t="n">
         <v>196.1388328305384</v>
       </c>
       <c r="S46" t="n">
-        <v>125.2530483618128</v>
+        <v>130.2447330072169</v>
       </c>
       <c r="T46" t="n">
-        <v>2.773539326140427</v>
+        <v>5.535956264534023</v>
       </c>
       <c r="U46" t="n">
         <v>125.7491255686458</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -4478,11 +4482,11 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>125.2530483618128</v>
+        <v>134.4608149355389</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=125.25% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=134.46% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4506,52 +4510,52 @@
         <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G47" t="n">
-        <v>196.5209543145911</v>
+        <v>196.7528906936184</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2128632997858552</v>
+        <v>0.3503353536484817</v>
       </c>
       <c r="I47" t="n">
         <v>52.02932925897922</v>
       </c>
       <c r="J47" t="n">
-        <v>190.661990295025</v>
+        <v>184.9000553356195</v>
       </c>
       <c r="K47" t="n">
-        <v>1.402523974264165</v>
+        <v>1.571310252876007</v>
       </c>
       <c r="L47" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M47" t="n">
-        <v>198.0477819087835</v>
+        <v>197.3418108488528</v>
       </c>
       <c r="N47" t="n">
-        <v>30.30731738479767</v>
+        <v>33.3350964253559</v>
       </c>
       <c r="O47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="P47" t="n">
-        <v>198.8491442958136</v>
+        <v>198.6941826951429</v>
       </c>
       <c r="Q47" t="n">
-        <v>63.56306315862759</v>
+        <v>78.65883520826061</v>
       </c>
       <c r="R47" t="n">
         <v>193.8459595711977</v>
       </c>
       <c r="S47" t="n">
-        <v>185.7524464670526</v>
+        <v>184.0090106039409</v>
       </c>
       <c r="T47" t="n">
-        <v>2.17706222844933</v>
+        <v>3.428651107244254</v>
       </c>
       <c r="U47" t="n">
         <v>130.8486591703272</v>
@@ -4569,7 +4573,7 @@
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4593,52 +4597,52 @@
         <v>2026</v>
       </c>
       <c r="E48" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G48" t="n">
-        <v>197.4116289114259</v>
+        <v>197.6704660202833</v>
       </c>
       <c r="H48" t="n">
-        <v>0.09806399196555902</v>
+        <v>0.1674436848912853</v>
       </c>
       <c r="I48" t="n">
         <v>75.82494372432545</v>
       </c>
       <c r="J48" t="n">
-        <v>198.8386638909737</v>
+        <v>193.5901427785547</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4766963579860826</v>
+        <v>0.6733722969208772</v>
       </c>
       <c r="L48" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M48" t="n">
-        <v>197.7975219007006</v>
+        <v>196.7233124918204</v>
       </c>
       <c r="N48" t="n">
-        <v>14.21611750782219</v>
+        <v>14.820582969364</v>
       </c>
       <c r="O48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="P48" t="n">
-        <v>198.1592979330603</v>
+        <v>198.022320718163</v>
       </c>
       <c r="Q48" t="n">
-        <v>26.69742465512154</v>
+        <v>33.60628094632519</v>
       </c>
       <c r="R48" t="n">
         <v>192.3368460426438</v>
       </c>
       <c r="S48" t="n">
-        <v>192.960503700666</v>
+        <v>191.8157157323924</v>
       </c>
       <c r="T48" t="n">
-        <v>1.916144240073933</v>
+        <v>3.127699672131663</v>
       </c>
       <c r="U48" t="n">
         <v>148.2729860112375</v>
@@ -4656,7 +4660,7 @@
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4680,52 +4684,52 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.103198347700101</v>
+        <v>0.1721830901847086</v>
       </c>
       <c r="I49" t="n">
         <v>67.54170898302603</v>
       </c>
       <c r="J49" t="n">
-        <v>193.285313573381</v>
+        <v>188.5364639501912</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9947434210124114</v>
+        <v>1.241250903265522</v>
       </c>
       <c r="L49" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M49" t="n">
-        <v>198.7623048616662</v>
+        <v>197.9461764628585</v>
       </c>
       <c r="N49" t="n">
-        <v>16.99260096397655</v>
+        <v>18.18137305728497</v>
       </c>
       <c r="O49" t="n">
         <v>179.6516960231333</v>
       </c>
       <c r="P49" t="n">
-        <v>199.527175157881</v>
+        <v>199.2925955034458</v>
       </c>
       <c r="Q49" t="n">
-        <v>34.85190379153376</v>
+        <v>40.95455768647587</v>
       </c>
       <c r="R49" t="n">
         <v>193.5695579772771</v>
       </c>
       <c r="S49" t="n">
-        <v>191.1619594493655</v>
+        <v>188.78130964667</v>
       </c>
       <c r="T49" t="n">
-        <v>1.287354175399031</v>
+        <v>1.811429776081504</v>
       </c>
       <c r="U49" t="n">
         <v>141.2583029624075</v>
@@ -4743,7 +4747,7 @@
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4767,52 +4771,52 @@
         <v>2026</v>
       </c>
       <c r="E50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G50" t="n">
-        <v>190.2245178657064</v>
+        <v>187.3936004904889</v>
       </c>
       <c r="H50" t="n">
-        <v>4.532822588444636</v>
+        <v>5.208788529216767</v>
       </c>
       <c r="I50" t="n">
         <v>162.6912701840232</v>
       </c>
       <c r="J50" t="n">
-        <v>196.8963895312021</v>
+        <v>193.8662174422948</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3344503561427851</v>
+        <v>0.4434513820849675</v>
       </c>
       <c r="L50" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M50" t="n">
-        <v>192.2542620549439</v>
+        <v>191.0040394407015</v>
       </c>
       <c r="N50" t="n">
-        <v>9.146953662236532</v>
+        <v>12.53571605682373</v>
       </c>
       <c r="O50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="P50" t="n">
-        <v>193.6879643864485</v>
+        <v>192.412989113812</v>
       </c>
       <c r="Q50" t="n">
-        <v>14.58561396653528</v>
+        <v>17.22534489261614</v>
       </c>
       <c r="R50" t="n">
         <v>160.5521309789579</v>
       </c>
       <c r="S50" t="n">
-        <v>190.9473551075631</v>
+        <v>191.1162051189995</v>
       </c>
       <c r="T50" t="n">
-        <v>17.2298443262551</v>
+        <v>24.59129532093463</v>
       </c>
       <c r="U50" t="n">
         <v>135.4400555181058</v>
@@ -4824,13 +4828,15 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>193.8662174422948</v>
+      </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=193.87% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -4854,52 +4860,52 @@
         <v>2026</v>
       </c>
       <c r="E51" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>190.2043219320878</v>
+        <v>188.6384797133506</v>
       </c>
       <c r="H51" t="n">
-        <v>1.662514124286943</v>
+        <v>1.903489031688147</v>
       </c>
       <c r="I51" t="n">
         <v>169.9274838481079</v>
       </c>
       <c r="J51" t="n">
-        <v>185.4056327404524</v>
+        <v>178.9137103796107</v>
       </c>
       <c r="K51" t="n">
-        <v>0.2217234068381974</v>
+        <v>0.2427665114409492</v>
       </c>
       <c r="L51" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M51" t="n">
-        <v>196.0740124018415</v>
+        <v>196.1122293407287</v>
       </c>
       <c r="N51" t="n">
-        <v>13.87524560256816</v>
+        <v>17.6295960754129</v>
       </c>
       <c r="O51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="P51" t="n">
-        <v>193.1635287487645</v>
+        <v>193.2719749453459</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.310507974087312</v>
+        <v>6.58219201990204</v>
       </c>
       <c r="R51" t="n">
         <v>165.5121650610737</v>
       </c>
       <c r="S51" t="n">
-        <v>190.1106722061027</v>
+        <v>190.5740611048891</v>
       </c>
       <c r="T51" t="n">
-        <v>7.645007009384247</v>
+        <v>11.55415004784484</v>
       </c>
       <c r="U51" t="n">
         <v>151.1230387281904</v>
@@ -4917,7 +4923,7 @@
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4941,52 +4947,52 @@
         <v>2026</v>
       </c>
       <c r="E52" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G52" t="n">
-        <v>189.4221899554474</v>
+        <v>185.8425679938319</v>
       </c>
       <c r="H52" t="n">
-        <v>2.594455221952179</v>
+        <v>2.98718902787148</v>
       </c>
       <c r="I52" t="n">
         <v>174.432365021141</v>
       </c>
       <c r="J52" t="n">
-        <v>199.1917030038023</v>
+        <v>197.6004713705168</v>
       </c>
       <c r="K52" t="n">
-        <v>0.177983292756472</v>
+        <v>0.2735075320235206</v>
       </c>
       <c r="L52" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M52" t="n">
-        <v>196.692358582482</v>
+        <v>196.3981217470596</v>
       </c>
       <c r="N52" t="n">
-        <v>21.74160851094635</v>
+        <v>26.6248126355684</v>
       </c>
       <c r="O52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="P52" t="n">
-        <v>192.5677751534704</v>
+        <v>190.2706087569731</v>
       </c>
       <c r="Q52" t="n">
-        <v>7.788443947555142</v>
+        <v>9.21501289688549</v>
       </c>
       <c r="R52" t="n">
         <v>154.7555469695623</v>
       </c>
       <c r="S52" t="n">
-        <v>191.5720783747983</v>
+        <v>191.7742099589465</v>
       </c>
       <c r="T52" t="n">
-        <v>13.39175311243195</v>
+        <v>20.05581811117946</v>
       </c>
       <c r="U52" t="n">
         <v>133.8716916594558</v>
@@ -5004,7 +5010,7 @@
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5028,59 +5034,59 @@
         <v>2026</v>
       </c>
       <c r="E53" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F53" t="n">
-        <v>2840</v>
+        <v>3167</v>
       </c>
       <c r="G53" t="n">
-        <v>19.81317872296284</v>
+        <v>20.09590459559316</v>
       </c>
       <c r="H53" t="n">
-        <v>24.63728416607406</v>
+        <v>26.06827811607847</v>
       </c>
       <c r="I53" t="n">
         <v>35.23746831954708</v>
       </c>
       <c r="J53" t="n">
-        <v>18.21180301884046</v>
+        <v>21.82929250468235</v>
       </c>
       <c r="K53" t="n">
-        <v>20.51335326459974</v>
+        <v>25.13835366588721</v>
       </c>
       <c r="L53" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M53" t="n">
-        <v>163.498571035511</v>
+        <v>164.5356140391471</v>
       </c>
       <c r="N53" t="n">
-        <v>1112.854166666667</v>
+        <v>1223.115384615385</v>
       </c>
       <c r="O53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="P53" t="n">
-        <v>163.498571035511</v>
+        <v>164.5356140391471</v>
       </c>
       <c r="Q53" t="n">
-        <v>1112.854166666667</v>
+        <v>1223.115384615385</v>
       </c>
       <c r="R53" t="n">
         <v>188.2648408233968</v>
       </c>
       <c r="S53" t="n">
-        <v>45.99685526730337</v>
+        <v>52.86613593151077</v>
       </c>
       <c r="T53" t="n">
-        <v>95.88333984517892</v>
+        <v>141.2650529879882</v>
       </c>
       <c r="U53" t="n">
         <v>92.2349408254034</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
@@ -5089,11 +5095,11 @@
         </is>
       </c>
       <c r="X53" t="n">
-        <v>18.21180301884046</v>
+        <v>20.09590459559316</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=18.21% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=20.10% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5117,52 +5123,52 @@
         <v>2026</v>
       </c>
       <c r="E54" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F54" t="n">
-        <v>1332</v>
+        <v>1472</v>
       </c>
       <c r="G54" t="n">
-        <v>20.15918071164578</v>
+        <v>18.73958210756178</v>
       </c>
       <c r="H54" t="n">
-        <v>11.48924610389167</v>
+        <v>10.69622688969862</v>
       </c>
       <c r="I54" t="n">
         <v>38.4591918317379</v>
       </c>
       <c r="J54" t="n">
-        <v>23.61771749479679</v>
+        <v>24.99748527673886</v>
       </c>
       <c r="K54" t="n">
-        <v>14.39206329784811</v>
+        <v>16.11825956854353</v>
       </c>
       <c r="L54" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M54" t="n">
-        <v>163.381789446615</v>
+        <v>164.4694964886822</v>
       </c>
       <c r="N54" t="n">
-        <v>510.5</v>
+        <v>556.8269230769231</v>
       </c>
       <c r="O54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="P54" t="n">
-        <v>163.381789446615</v>
+        <v>164.4694964886822</v>
       </c>
       <c r="Q54" t="n">
-        <v>510.5</v>
+        <v>556.8269230769231</v>
       </c>
       <c r="R54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="S54" t="n">
-        <v>45.7020281333458</v>
+        <v>52.7013059681811</v>
       </c>
       <c r="T54" t="n">
-        <v>42.92606372582961</v>
+        <v>63.00118284664776</v>
       </c>
       <c r="U54" t="n">
         <v>91.67135817890519</v>
@@ -5178,11 +5184,11 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>20.15918071164578</v>
+        <v>18.73958210756178</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=20.16% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=18.74% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5206,52 +5212,52 @@
         <v>2026</v>
       </c>
       <c r="E55" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F55" t="n">
-        <v>1503</v>
+        <v>1690</v>
       </c>
       <c r="G55" t="n">
-        <v>23.01187674672067</v>
+        <v>21.72360139831728</v>
       </c>
       <c r="H55" t="n">
-        <v>13.8414317572904</v>
+        <v>13.22536243480747</v>
       </c>
       <c r="I55" t="n">
         <v>38.25160771522186</v>
       </c>
       <c r="J55" t="n">
-        <v>26.02651666734207</v>
+        <v>26.16584507117277</v>
       </c>
       <c r="K55" t="n">
-        <v>17.51608646817878</v>
+        <v>18.47461648062351</v>
       </c>
       <c r="L55" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M55" t="n">
-        <v>163.6985215778323</v>
+        <v>164.6853792291117</v>
       </c>
       <c r="N55" t="n">
-        <v>602.5625</v>
+        <v>666.4807692307693</v>
       </c>
       <c r="O55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="P55" t="n">
-        <v>163.6985215778323</v>
+        <v>164.6853792291117</v>
       </c>
       <c r="Q55" t="n">
-        <v>602.5625</v>
+        <v>666.4807692307693</v>
       </c>
       <c r="R55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="S55" t="n">
-        <v>43.6062374418027</v>
+        <v>50.45851269062578</v>
       </c>
       <c r="T55" t="n">
-        <v>49.23042089827342</v>
+        <v>73.8401566078978</v>
       </c>
       <c r="U55" t="n">
         <v>92.1901984902002</v>
@@ -5267,11 +5273,11 @@
         </is>
       </c>
       <c r="X55" t="n">
-        <v>23.01187674672067</v>
+        <v>21.72360139831728</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=23.01% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=21.72% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5295,52 +5301,52 @@
         <v>2026</v>
       </c>
       <c r="E56" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F56" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G56" t="n">
-        <v>72.02356238360656</v>
+        <v>75.15141959765678</v>
       </c>
       <c r="H56" t="n">
-        <v>3.287071266976904</v>
+        <v>3.663066571838782</v>
       </c>
       <c r="I56" t="n">
         <v>154.1439500713238</v>
       </c>
       <c r="J56" t="n">
-        <v>68.30227160802244</v>
+        <v>69.90930581618821</v>
       </c>
       <c r="K56" t="n">
-        <v>2.246097620761395</v>
+        <v>2.311390036345996</v>
       </c>
       <c r="L56" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M56" t="n">
-        <v>169.4835575273476</v>
+        <v>170.9999889298593</v>
       </c>
       <c r="N56" t="n">
-        <v>57.35198327273171</v>
+        <v>63.55748541917569</v>
       </c>
       <c r="O56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="P56" t="n">
-        <v>169.5174488102849</v>
+        <v>171.0772515772597</v>
       </c>
       <c r="Q56" t="n">
-        <v>57.8125</v>
+        <v>65.57692307692308</v>
       </c>
       <c r="R56" t="n">
         <v>197.7368060568652</v>
       </c>
       <c r="S56" t="n">
-        <v>57.20235627657991</v>
+        <v>60.29853061336017</v>
       </c>
       <c r="T56" t="n">
-        <v>1.76394664475274</v>
+        <v>1.876042993102666</v>
       </c>
       <c r="U56" t="n">
         <v>104.7066447751141</v>
@@ -5356,11 +5362,11 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>57.20235627657991</v>
+        <v>60.29853061336017</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=57.20% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=60.30% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5384,52 +5390,52 @@
         <v>2026</v>
       </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F57" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G57" t="n">
-        <v>94.75567260792225</v>
+        <v>95.70003000461385</v>
       </c>
       <c r="H57" t="n">
-        <v>1.675103479712558</v>
+        <v>1.739251349080757</v>
       </c>
       <c r="I57" t="n">
         <v>164.0555422208552</v>
       </c>
       <c r="J57" t="n">
-        <v>130.8385995272074</v>
+        <v>130.4479548242629</v>
       </c>
       <c r="K57" t="n">
-        <v>1.519977565318321</v>
+        <v>1.557985936312652</v>
       </c>
       <c r="L57" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M57" t="n">
-        <v>168.3523102925899</v>
+        <v>169.926070178636</v>
       </c>
       <c r="N57" t="n">
-        <v>24.60416666666667</v>
+        <v>28.29105662783227</v>
       </c>
       <c r="O57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="P57" t="n">
-        <v>168.3523102925899</v>
+        <v>169.926070178636</v>
       </c>
       <c r="Q57" t="n">
-        <v>24.60416666666667</v>
+        <v>28.44230769230769</v>
       </c>
       <c r="R57" t="n">
         <v>197.2831175654684</v>
       </c>
       <c r="S57" t="n">
-        <v>101.7234545524474</v>
+        <v>106.6582394576391</v>
       </c>
       <c r="T57" t="n">
-        <v>0.9429043330170425</v>
+        <v>1.034083610053474</v>
       </c>
       <c r="U57" t="n">
         <v>124.2225772452616</v>
@@ -5445,11 +5451,11 @@
         </is>
       </c>
       <c r="X57" t="n">
-        <v>94.75567260792225</v>
+        <v>95.70003000461385</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=94.76% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=95.70% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5473,52 +5479,52 @@
         <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F58" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G58" t="n">
-        <v>88.8688213896983</v>
+        <v>91.29340382256389</v>
       </c>
       <c r="H58" t="n">
-        <v>1.97475055418743</v>
+        <v>2.251105847677055</v>
       </c>
       <c r="I58" t="n">
         <v>158.4722608607674</v>
       </c>
       <c r="J58" t="n">
-        <v>120.6941795478983</v>
+        <v>125.4554034373361</v>
       </c>
       <c r="K58" t="n">
-        <v>1.842030318086942</v>
+        <v>1.849110789028315</v>
       </c>
       <c r="L58" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M58" t="n">
-        <v>171.0700060037982</v>
+        <v>172.5722834767986</v>
       </c>
       <c r="N58" t="n">
-        <v>33.64583333333334</v>
+        <v>37.53846153846154</v>
       </c>
       <c r="O58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="P58" t="n">
-        <v>171.0700060037982</v>
+        <v>172.5722834767986</v>
       </c>
       <c r="Q58" t="n">
-        <v>33.64583333333334</v>
+        <v>37.53846153846154</v>
       </c>
       <c r="R58" t="n">
         <v>197.6615055783608</v>
       </c>
       <c r="S58" t="n">
-        <v>89.73059687062958</v>
+        <v>87.35952124159834</v>
       </c>
       <c r="T58" t="n">
-        <v>1.172426225870094</v>
+        <v>1.166134199350967</v>
       </c>
       <c r="U58" t="n">
         <v>111.9755139895278</v>
@@ -5534,11 +5540,11 @@
         </is>
       </c>
       <c r="X58" t="n">
-        <v>89.73059687062958</v>
+        <v>87.35952124159834</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=89.73% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=87.36% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5568,7 @@
         <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F59" t="n">
         <v>6</v>
@@ -5571,43 +5577,43 @@
         <v>199.5468394226922</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2653151645328648</v>
+        <v>0.2449063057226444</v>
       </c>
       <c r="I59" t="n">
         <v>163.442478475025</v>
       </c>
       <c r="J59" t="n">
-        <v>193.3342294751162</v>
+        <v>193.8469810539535</v>
       </c>
       <c r="K59" t="n">
-        <v>0.258391598481908</v>
+        <v>0.2418557896529395</v>
       </c>
       <c r="L59" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M59" t="n">
-        <v>174.9064171122995</v>
+        <v>176.9975490196078</v>
       </c>
       <c r="N59" t="n">
-        <v>5.875</v>
+        <v>10.55769230769231</v>
       </c>
       <c r="O59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="P59" t="n">
-        <v>174.9064171122995</v>
+        <v>176.9975490196078</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.875</v>
+        <v>10.55769230769231</v>
       </c>
       <c r="R59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="S59" t="n">
-        <v>173.6670553170678</v>
+        <v>175.6926664465242</v>
       </c>
       <c r="T59" t="n">
-        <v>0.450879453393054</v>
+        <v>0.6390549945212811</v>
       </c>
       <c r="U59" t="n">
         <v>167.6265476269683</v>
@@ -5649,7 +5655,7 @@
         <v>2026</v>
       </c>
       <c r="E60" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -5658,43 +5664,43 @@
         <v>197.8217646398928</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1784006183325819</v>
+        <v>0.1646774938454602</v>
       </c>
       <c r="I60" t="n">
         <v>179.6544870721095</v>
       </c>
       <c r="J60" t="n">
-        <v>198.7452026030459</v>
+        <v>198.8417254797347</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1741067871157174</v>
+        <v>0.1612453958722502</v>
       </c>
       <c r="L60" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M60" t="n">
-        <v>170.1587301587302</v>
+        <v>173.1428571428572</v>
       </c>
       <c r="N60" t="n">
-        <v>3.333333333333333</v>
+        <v>5.673076923076923</v>
       </c>
       <c r="O60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="P60" t="n">
-        <v>170.1587301587302</v>
+        <v>173.1428571428572</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.333333333333333</v>
+        <v>5.673076923076923</v>
       </c>
       <c r="R60" t="n">
         <v>199.0965028052728</v>
       </c>
       <c r="S60" t="n">
-        <v>186.6263689202685</v>
+        <v>187.6551097725555</v>
       </c>
       <c r="T60" t="n">
-        <v>0.2999967515724015</v>
+        <v>0.3705474387374383</v>
       </c>
       <c r="U60" t="n">
         <v>167.0169829765832</v>
@@ -5736,7 +5742,7 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -5745,43 +5751,43 @@
         <v>199.9531681019307</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1007173132369165</v>
+        <v>0.09296982760330753</v>
       </c>
       <c r="I61" t="n">
         <v>178.3754768379913</v>
       </c>
       <c r="J61" t="n">
-        <v>197.3048991849245</v>
+        <v>197.512214632238</v>
       </c>
       <c r="K61" t="n">
-        <v>0.1602251162734526</v>
+        <v>0.153430299764158</v>
       </c>
       <c r="L61" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M61" t="n">
-        <v>183.75</v>
+        <v>185.5555555555555</v>
       </c>
       <c r="N61" t="n">
-        <v>2.729166666666667</v>
+        <v>5.057692307692307</v>
       </c>
       <c r="O61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="P61" t="n">
-        <v>183.75</v>
+        <v>185.5555555555555</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.729166666666667</v>
+        <v>5.057692307692307</v>
       </c>
       <c r="R61" t="n">
         <v>199.3694289811982</v>
       </c>
       <c r="S61" t="n">
-        <v>191.0007172947431</v>
+        <v>191.6929698105321</v>
       </c>
       <c r="T61" t="n">
-        <v>0.2421981990418275</v>
+        <v>0.3417249318550903</v>
       </c>
       <c r="U61" t="n">
         <v>167.1297521794813</v>
@@ -5823,52 +5829,52 @@
         <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F62" t="n">
         <v>21</v>
       </c>
       <c r="G62" t="n">
-        <v>115.0714960980425</v>
+        <v>121.6044579366546</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7444208963099056</v>
+        <v>0.808461210422098</v>
       </c>
       <c r="I62" t="n">
         <v>51.86246745886869</v>
       </c>
       <c r="J62" t="n">
-        <v>134.4105482127552</v>
+        <v>139.4558906579279</v>
       </c>
       <c r="K62" t="n">
-        <v>3.425978484552677</v>
+        <v>4.069888424207752</v>
       </c>
       <c r="L62" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="M62" t="n">
-        <v>179.7158878848481</v>
+        <v>181.2762042013983</v>
       </c>
       <c r="N62" t="n">
-        <v>42.43720076707844</v>
+        <v>51.13178595466775</v>
       </c>
       <c r="O62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="P62" t="n">
-        <v>179.9230212454476</v>
+        <v>181.467404226567</v>
       </c>
       <c r="Q62" t="n">
-        <v>60.90831139371448</v>
+        <v>75.08417009920558</v>
       </c>
       <c r="R62" t="n">
         <v>188.4656733609786</v>
       </c>
       <c r="S62" t="n">
-        <v>123.840234425149</v>
+        <v>129.6986779309068</v>
       </c>
       <c r="T62" t="n">
-        <v>2.617745701031933</v>
+        <v>4.324530451610826</v>
       </c>
       <c r="U62" t="n">
         <v>127.8730185036105</v>
@@ -5884,11 +5890,11 @@
         </is>
       </c>
       <c r="X62" t="n">
-        <v>115.0714960980425</v>
+        <v>121.6044579366546</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=115.07% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=121.60% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -5912,52 +5918,52 @@
         <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F63" t="n">
         <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>147.8188112287161</v>
+        <v>151.8327488265072</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5000845178023875</v>
+        <v>0.5314209835917494</v>
       </c>
       <c r="I63" t="n">
         <v>69.84803023883232</v>
       </c>
       <c r="J63" t="n">
-        <v>164.0184235376574</v>
+        <v>166.7862371116838</v>
       </c>
       <c r="K63" t="n">
-        <v>0.4507962089061189</v>
+        <v>0.5116838462098096</v>
       </c>
       <c r="L63" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M63" t="n">
-        <v>180.5376455904877</v>
+        <v>182.0347497758348</v>
       </c>
       <c r="N63" t="n">
-        <v>13.25352849882985</v>
+        <v>15.1677508887776</v>
       </c>
       <c r="O63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="P63" t="n">
-        <v>181.0126881707742</v>
+        <v>182.4732506191762</v>
       </c>
       <c r="Q63" t="n">
-        <v>21.65221409322612</v>
+        <v>26.8344783570363</v>
       </c>
       <c r="R63" t="n">
         <v>186.3893216158546</v>
       </c>
       <c r="S63" t="n">
-        <v>140.7102637875787</v>
+        <v>145.2710127269957</v>
       </c>
       <c r="T63" t="n">
-        <v>1.379688051367461</v>
+        <v>2.104858798994898</v>
       </c>
       <c r="U63" t="n">
         <v>131.8859677830883</v>
@@ -5999,52 +6005,52 @@
         <v>2026</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F64" t="n">
         <v>12</v>
       </c>
       <c r="G64" t="n">
-        <v>141.6564464705618</v>
+        <v>146.1444121266724</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7300548706756037</v>
+        <v>0.8390743959406475</v>
       </c>
       <c r="I64" t="n">
         <v>72.92360982323459</v>
       </c>
       <c r="J64" t="n">
-        <v>155.9307174498431</v>
+        <v>159.3206622613936</v>
       </c>
       <c r="K64" t="n">
-        <v>1.211972614781416</v>
+        <v>2.050984692736824</v>
       </c>
       <c r="L64" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="M64" t="n">
-        <v>180.3182275636854</v>
+        <v>181.8322100587866</v>
       </c>
       <c r="N64" t="n">
-        <v>25.96941433467142</v>
+        <v>31.39477888154723</v>
       </c>
       <c r="O64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="P64" t="n">
-        <v>180.521209708531</v>
+        <v>182.0195781924902</v>
       </c>
       <c r="Q64" t="n">
-        <v>39.99123758256633</v>
+        <v>49.51562916668028</v>
       </c>
       <c r="R64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="S64" t="n">
-        <v>143.5126733326317</v>
+        <v>147.8578523070447</v>
       </c>
       <c r="T64" t="n">
-        <v>1.867934673595985</v>
+        <v>3.052893810965289</v>
       </c>
       <c r="U64" t="n">
         <v>132.574641557417</v>
@@ -6060,11 +6066,11 @@
         </is>
       </c>
       <c r="X64" t="n">
-        <v>141.6564464705618</v>
+        <v>146.1444121266724</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=141.66% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=146.14% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6088,52 +6094,52 @@
         <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F65" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G65" t="n">
-        <v>155.480822424112</v>
+        <v>150.9338289242287</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7502048770932279</v>
+        <v>0.8811472161839162</v>
       </c>
       <c r="I65" t="n">
         <v>124.1398173354868</v>
       </c>
       <c r="J65" t="n">
-        <v>170.5715077099328</v>
+        <v>159.1362720494756</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6796958122893066</v>
+        <v>0.6961974997610457</v>
       </c>
       <c r="L65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="M65" t="n">
-        <v>190.7006764318506</v>
+        <v>190.7194605391035</v>
       </c>
       <c r="N65" t="n">
-        <v>32.87690244111926</v>
+        <v>41.64065176267066</v>
       </c>
       <c r="O65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="P65" t="n">
-        <v>190.761948677814</v>
+        <v>190.927725291808</v>
       </c>
       <c r="Q65" t="n">
-        <v>33.625</v>
+        <v>45.19230769230769</v>
       </c>
       <c r="R65" t="n">
         <v>191.9303948964172</v>
       </c>
       <c r="S65" t="n">
-        <v>162.284479679222</v>
+        <v>162.7562716199893</v>
       </c>
       <c r="T65" t="n">
-        <v>4.020766697853392</v>
+        <v>6.581622894105985</v>
       </c>
       <c r="U65" t="n">
         <v>113.9712651292745</v>
@@ -6149,11 +6155,11 @@
         </is>
       </c>
       <c r="X65" t="n">
-        <v>155.480822424112</v>
+        <v>150.9338289242287</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=155.48% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=150.93% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6177,70 +6183,72 @@
         <v>2026</v>
       </c>
       <c r="E66" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F66" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G66" t="n">
-        <v>182.2476695665705</v>
+        <v>180.1220212764491</v>
       </c>
       <c r="H66" t="n">
-        <v>0.3695273264813482</v>
+        <v>0.5174825916730073</v>
       </c>
       <c r="I66" t="n">
         <v>146.9871894171194</v>
       </c>
       <c r="J66" t="n">
-        <v>180.3459413036325</v>
+        <v>171.7530356338314</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4064358027291891</v>
+        <v>0.4975427705603367</v>
       </c>
       <c r="L66" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="M66" t="n">
-        <v>192.2395607922245</v>
+        <v>191.8776960511818</v>
       </c>
       <c r="N66" t="n">
-        <v>14.89583333333333</v>
+        <v>19.4398982130394</v>
       </c>
       <c r="O66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="P66" t="n">
-        <v>192.2395607922245</v>
+        <v>191.9387057888072</v>
       </c>
       <c r="Q66" t="n">
-        <v>14.89583333333333</v>
+        <v>19.73076923076923</v>
       </c>
       <c r="R66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="S66" t="n">
-        <v>175.4247667889375</v>
+        <v>173.5926484386023</v>
       </c>
       <c r="T66" t="n">
-        <v>1.806412889004299</v>
+        <v>2.781624413232052</v>
       </c>
       <c r="U66" t="n">
         <v>118.44057480835</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>171.7530356338314</v>
+      </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=171.75% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6264,52 +6272,52 @@
         <v>2026</v>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G67" t="n">
-        <v>187.7521498383148</v>
+        <v>177.6001138412982</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5389679906118942</v>
+        <v>0.5310402008178121</v>
       </c>
       <c r="I67" t="n">
         <v>137.6516466078508</v>
       </c>
       <c r="J67" t="n">
-        <v>196.4080267258852</v>
+        <v>183.7604374326015</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5502692552689088</v>
+        <v>0.5406099533335619</v>
       </c>
       <c r="L67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="M67" t="n">
-        <v>192.8522685320083</v>
+        <v>192.7117313666085</v>
       </c>
       <c r="N67" t="n">
-        <v>14.26230507406671</v>
+        <v>16.43981187413353</v>
       </c>
       <c r="O67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="P67" t="n">
-        <v>194.0260697900837</v>
+        <v>194.196348065024</v>
       </c>
       <c r="Q67" t="n">
-        <v>19.85416666666667</v>
+        <v>26.5</v>
       </c>
       <c r="R67" t="n">
         <v>191.2393501485975</v>
       </c>
       <c r="S67" t="n">
-        <v>181.0806839434517</v>
+        <v>181.3259710545283</v>
       </c>
       <c r="T67" t="n">
-        <v>2.223232977114444</v>
+        <v>3.854970419694336</v>
       </c>
       <c r="U67" t="n">
         <v>116.630186356802</v>
@@ -6321,13 +6329,15 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>177.6001138412982</v>
+      </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=177.60% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6361,7 @@
         <v>2026</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -6360,16 +6370,16 @@
         <v>199.988140539529</v>
       </c>
       <c r="H68" t="n">
-        <v>0.04856558864475128</v>
+        <v>0.04482977413361657</v>
       </c>
       <c r="I68" t="n">
         <v>183.5383709430125</v>
       </c>
       <c r="J68" t="n">
-        <v>199.8280527126044</v>
+        <v>199.8412794270195</v>
       </c>
       <c r="K68" t="n">
-        <v>0.05587964844368295</v>
+        <v>0.05254346953207076</v>
       </c>
       <c r="L68" t="n">
         <v>198.3312090033645</v>
@@ -6378,7 +6388,7 @@
         <v>200</v>
       </c>
       <c r="N68" t="n">
-        <v>6.712081579052339</v>
+        <v>8.849613765279083</v>
       </c>
       <c r="O68" t="n">
         <v>188.2784643365136</v>
@@ -6387,16 +6397,16 @@
         <v>200</v>
       </c>
       <c r="Q68" t="n">
-        <v>7.166666666666667</v>
+        <v>9.26923076923077</v>
       </c>
       <c r="R68" t="n">
         <v>199.7672857698158</v>
       </c>
       <c r="S68" t="n">
-        <v>197.3740131705127</v>
+        <v>197.5760121573963</v>
       </c>
       <c r="T68" t="n">
-        <v>0.6442582695936658</v>
+        <v>0.7060823159264591</v>
       </c>
       <c r="U68" t="n">
         <v>177.2448922419183</v>
@@ -6438,7 +6448,7 @@
         <v>2026</v>
       </c>
       <c r="E69" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -6447,16 +6457,16 @@
         <v>198.1317768745953</v>
       </c>
       <c r="H69" t="n">
-        <v>0.06429198833683604</v>
+        <v>0.05934645077246404</v>
       </c>
       <c r="I69" t="n">
         <v>171.5447439761989</v>
       </c>
       <c r="J69" t="n">
-        <v>199.5149630806197</v>
+        <v>199.5522736128797</v>
       </c>
       <c r="K69" t="n">
-        <v>0.06857957821459099</v>
+        <v>0.06626069061720037</v>
       </c>
       <c r="L69" t="n">
         <v>194.4182830751776</v>
@@ -6465,7 +6475,7 @@
         <v>200</v>
       </c>
       <c r="N69" t="n">
-        <v>3.416666666666667</v>
+        <v>4.25</v>
       </c>
       <c r="O69" t="n">
         <v>190.8574288418282</v>
@@ -6474,16 +6484,16 @@
         <v>200</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.416666666666667</v>
+        <v>4.25</v>
       </c>
       <c r="R69" t="n">
         <v>199.6130972886749</v>
       </c>
       <c r="S69" t="n">
-        <v>198.6768525364572</v>
+        <v>198.7786331105758</v>
       </c>
       <c r="T69" t="n">
-        <v>0.3002826763129219</v>
+        <v>0.3453066502488701</v>
       </c>
       <c r="U69" t="n">
         <v>185.6695408532579</v>
@@ -6525,7 +6535,7 @@
         <v>2026</v>
       </c>
       <c r="E70" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -6534,7 +6544,7 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01408360079746666</v>
+        <v>0.01300024688996922</v>
       </c>
       <c r="I70" t="n">
         <v>188.453973372859</v>
@@ -6543,7 +6553,7 @@
         <v>200</v>
       </c>
       <c r="K70" t="n">
-        <v>0.01614480047598248</v>
+        <v>0.01611028223724515</v>
       </c>
       <c r="L70" t="n">
         <v>198.9765474653765</v>
@@ -6552,7 +6562,7 @@
         <v>200</v>
       </c>
       <c r="N70" t="n">
-        <v>3.687813358363893</v>
+        <v>4.961827715412824</v>
       </c>
       <c r="O70" t="n">
         <v>192.937344462188</v>
@@ -6561,7 +6571,7 @@
         <v>200</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.875</v>
+        <v>5.134615384615385</v>
       </c>
       <c r="R70" t="n">
         <v>199.6974055100667</v>
@@ -6570,7 +6580,7 @@
         <v>200</v>
       </c>
       <c r="T70" t="n">
-        <v>0.3188993582383924</v>
+        <v>0.3664860990972112</v>
       </c>
       <c r="U70" t="n">
         <v>184.4638384017739</v>
@@ -6612,59 +6622,59 @@
         <v>2026</v>
       </c>
       <c r="E71" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F71" t="n">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G71" t="n">
-        <v>61.34695045948616</v>
+        <v>61.42327963804853</v>
       </c>
       <c r="H71" t="n">
-        <v>3.084299467974718</v>
+        <v>3.115210034521734</v>
       </c>
       <c r="I71" t="n">
         <v>143.4057585362926</v>
       </c>
       <c r="J71" t="n">
-        <v>173.5415322252807</v>
+        <v>173.2999901984479</v>
       </c>
       <c r="K71" t="n">
-        <v>4.554704402073362</v>
+        <v>4.703881357592056</v>
       </c>
       <c r="L71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="M71" t="n">
-        <v>69.44887372191104</v>
+        <v>67.03669362173159</v>
       </c>
       <c r="N71" t="n">
-        <v>4.261547569775879</v>
+        <v>4.16481419340312</v>
       </c>
       <c r="O71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="P71" t="n">
-        <v>190.1539581976679</v>
+        <v>190.9113460286165</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.853391764773163</v>
+        <v>5.018515475175227</v>
       </c>
       <c r="R71" t="n">
         <v>185.267595267154</v>
       </c>
       <c r="S71" t="n">
-        <v>54.91812707291811</v>
+        <v>59.79657500626929</v>
       </c>
       <c r="T71" t="n">
-        <v>4.826720185282983</v>
+        <v>5.964030506842874</v>
       </c>
       <c r="U71" t="n">
         <v>93.16202342284906</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -6673,11 +6683,11 @@
         </is>
       </c>
       <c r="X71" t="n">
-        <v>54.91812707291811</v>
+        <v>61.42327963804853</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=54.92% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=61.42% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6701,59 +6711,59 @@
         <v>2026</v>
       </c>
       <c r="E72" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F72" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G72" t="n">
-        <v>87.20988140011258</v>
+        <v>84.07539050911866</v>
       </c>
       <c r="H72" t="n">
-        <v>1.642466111479539</v>
+        <v>1.602741103507269</v>
       </c>
       <c r="I72" t="n">
         <v>151.0433307550491</v>
       </c>
       <c r="J72" t="n">
-        <v>86.79876133578003</v>
+        <v>84.07765725354294</v>
       </c>
       <c r="K72" t="n">
-        <v>1.307239309458101</v>
+        <v>1.367494685518548</v>
       </c>
       <c r="L72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="M72" t="n">
-        <v>90.88895020884301</v>
+        <v>87.90553164133496</v>
       </c>
       <c r="N72" t="n">
-        <v>2.438331418698073</v>
+        <v>2.415561923845612</v>
       </c>
       <c r="O72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="P72" t="n">
-        <v>168.3172643464729</v>
+        <v>171.1975130422481</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.110864049449704</v>
+        <v>2.179259122568957</v>
       </c>
       <c r="R72" t="n">
         <v>161.2927483340683</v>
       </c>
       <c r="S72" t="n">
-        <v>82.50956190575791</v>
+        <v>85.73646487878931</v>
       </c>
       <c r="T72" t="n">
-        <v>2.228309830326239</v>
+        <v>2.828564867761933</v>
       </c>
       <c r="U72" t="n">
         <v>104.036396201453</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -6762,11 +6772,11 @@
         </is>
       </c>
       <c r="X72" t="n">
-        <v>82.50956190575791</v>
+        <v>84.07765725354294</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=82.51% sobre 24 sem</t>
+          <t>DeepAR: menor SMAPE real=84.08% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6790,52 +6800,52 @@
         <v>2026</v>
       </c>
       <c r="E73" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G73" t="n">
-        <v>71.70774255746809</v>
+        <v>71.82079597245757</v>
       </c>
       <c r="H73" t="n">
-        <v>1.938968631695724</v>
+        <v>1.977763974231611</v>
       </c>
       <c r="I73" t="n">
         <v>148.5993365374143</v>
       </c>
       <c r="J73" t="n">
-        <v>153.5954395736106</v>
+        <v>147.0918094181974</v>
       </c>
       <c r="K73" t="n">
-        <v>2.355923158194214</v>
+        <v>2.362989944339627</v>
       </c>
       <c r="L73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="M73" t="n">
-        <v>88.73030972106281</v>
+        <v>86.13938208574584</v>
       </c>
       <c r="N73" t="n">
-        <v>1.997552126646042</v>
+        <v>2.002529465235197</v>
       </c>
       <c r="O73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="P73" t="n">
-        <v>172.1718058275552</v>
+        <v>174.3124361485125</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.507643182936564</v>
+        <v>2.622439861172213</v>
       </c>
       <c r="R73" t="n">
         <v>173.6314937555617</v>
       </c>
       <c r="S73" t="n">
-        <v>58.77174837866832</v>
+        <v>62.86539382703211</v>
       </c>
       <c r="T73" t="n">
-        <v>2.143140475575205</v>
+        <v>2.667844818908352</v>
       </c>
       <c r="U73" t="n">
         <v>104.3951484726403</v>
@@ -6851,11 +6861,11 @@
         </is>
       </c>
       <c r="X73" t="n">
-        <v>58.77174837866832</v>
+        <v>62.86539382703211</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=58.77% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=62.87% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6879,52 +6889,52 @@
         <v>2026</v>
       </c>
       <c r="E74" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F74" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G74" t="n">
-        <v>173.3426311603178</v>
+        <v>174.4718442606345</v>
       </c>
       <c r="H74" t="n">
-        <v>5.508267258971564</v>
+        <v>6.258269259578741</v>
       </c>
       <c r="I74" t="n">
         <v>148.9425712788151</v>
       </c>
       <c r="J74" t="n">
-        <v>188.8350419277548</v>
+        <v>189.2587566906077</v>
       </c>
       <c r="K74" t="n">
-        <v>0.434158698718744</v>
+        <v>0.4390523964915655</v>
       </c>
       <c r="L74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="M74" t="n">
-        <v>191.2067195412283</v>
+        <v>191.7085025444234</v>
       </c>
       <c r="N74" t="n">
-        <v>35.33999170262691</v>
+        <v>38.4139073690108</v>
       </c>
       <c r="O74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="P74" t="n">
-        <v>191.2067195412283</v>
+        <v>191.7140640228413</v>
       </c>
       <c r="Q74" t="n">
-        <v>35.54166666666666</v>
+        <v>38.71153846153846</v>
       </c>
       <c r="R74" t="n">
         <v>193.1141809259393</v>
       </c>
       <c r="S74" t="n">
-        <v>161.7645862384469</v>
+        <v>163.1582599134988</v>
       </c>
       <c r="T74" t="n">
-        <v>1.568910235668429</v>
+        <v>2.043127757499643</v>
       </c>
       <c r="U74" t="n">
         <v>113.155914904339</v>
@@ -6940,11 +6950,11 @@
         </is>
       </c>
       <c r="X74" t="n">
-        <v>161.7645862384469</v>
+        <v>163.1582599134988</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=161.76% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=163.16% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -6968,52 +6978,52 @@
         <v>2026</v>
       </c>
       <c r="E75" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F75" t="n">
         <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>172.1257922122402</v>
+        <v>174.2699620420679</v>
       </c>
       <c r="H75" t="n">
-        <v>1.922071693781937</v>
+        <v>2.142589026981875</v>
       </c>
       <c r="I75" t="n">
         <v>157.2380343536269</v>
       </c>
       <c r="J75" t="n">
-        <v>197.3088606057077</v>
+        <v>197.5158713283456</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2817551987303564</v>
+        <v>0.260182167677241</v>
       </c>
       <c r="L75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="M75" t="n">
-        <v>190.6795156378952</v>
+        <v>191.3964759734417</v>
       </c>
       <c r="N75" t="n">
-        <v>15.24813829311545</v>
+        <v>16.20981996287579</v>
       </c>
       <c r="O75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="P75" t="n">
-        <v>190.6795156378952</v>
+        <v>191.3964759734417</v>
       </c>
       <c r="Q75" t="n">
-        <v>15.5</v>
+        <v>16.44230769230769</v>
       </c>
       <c r="R75" t="n">
         <v>193.2892416279341</v>
       </c>
       <c r="S75" t="n">
-        <v>167.3559759268335</v>
+        <v>169.8670547016924</v>
       </c>
       <c r="T75" t="n">
-        <v>0.7985252001300038</v>
+        <v>0.9626258278621391</v>
       </c>
       <c r="U75" t="n">
         <v>110.9447640026735</v>
@@ -7055,52 +7065,52 @@
         <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>179.2568497322164</v>
+        <v>179.2253712539902</v>
       </c>
       <c r="H76" t="n">
-        <v>3.192081591173338</v>
+        <v>3.56168156738758</v>
       </c>
       <c r="I76" t="n">
         <v>154.9841830576604</v>
       </c>
       <c r="J76" t="n">
-        <v>196.0505085236394</v>
+        <v>196.2482320486948</v>
       </c>
       <c r="K76" t="n">
-        <v>0.2052074704385354</v>
+        <v>0.2278723959063293</v>
       </c>
       <c r="L76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="M76" t="n">
-        <v>190.863599677159</v>
+        <v>191.2067962153635</v>
       </c>
       <c r="N76" t="n">
-        <v>18.71047097254399</v>
+        <v>20.1666718255868</v>
       </c>
       <c r="O76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="P76" t="n">
-        <v>190.863599677159</v>
+        <v>191.3315200778003</v>
       </c>
       <c r="Q76" t="n">
-        <v>20.85416666666667</v>
+        <v>23.01923076923077</v>
       </c>
       <c r="R76" t="n">
         <v>192.8448970866968</v>
       </c>
       <c r="S76" t="n">
-        <v>175.7063738678908</v>
+        <v>174.7180212472131</v>
       </c>
       <c r="T76" t="n">
-        <v>0.877827446481018</v>
+        <v>1.080921636694278</v>
       </c>
       <c r="U76" t="n">
         <v>118.0223455785753</v>
@@ -7118,7 +7128,7 @@
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -7142,52 +7152,52 @@
         <v>2026</v>
       </c>
       <c r="E77" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F77" t="n">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="G77" t="n">
-        <v>46.47505719782153</v>
+        <v>45.07314790540139</v>
       </c>
       <c r="H77" t="n">
-        <v>6.28277908356672</v>
+        <v>5.9559345125117</v>
       </c>
       <c r="I77" t="n">
         <v>77.76772218573589</v>
       </c>
       <c r="J77" t="n">
-        <v>44.06413052616614</v>
+        <v>48.91910741895335</v>
       </c>
       <c r="K77" t="n">
-        <v>7.367943329729475</v>
+        <v>8.212790663504016</v>
       </c>
       <c r="L77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="M77" t="n">
-        <v>55.06794886135159</v>
+        <v>59.40091192585066</v>
       </c>
       <c r="N77" t="n">
-        <v>11.70833333333333</v>
+        <v>12.5</v>
       </c>
       <c r="O77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="P77" t="n">
-        <v>55.06794886135159</v>
+        <v>59.40091192585066</v>
       </c>
       <c r="Q77" t="n">
-        <v>11.70833333333333</v>
+        <v>12.5</v>
       </c>
       <c r="R77" t="n">
         <v>138.4032392925817</v>
       </c>
       <c r="S77" t="n">
-        <v>32.24270743084072</v>
+        <v>33.73237849708716</v>
       </c>
       <c r="T77" t="n">
-        <v>5.932864951354129</v>
+        <v>5.898095795965104</v>
       </c>
       <c r="U77" t="n">
         <v>118.3894561520081</v>
@@ -7203,11 +7213,11 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>32.24270743084072</v>
+        <v>33.73237849708716</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=32.24% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=33.73% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7231,52 +7241,52 @@
         <v>2026</v>
       </c>
       <c r="E78" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G78" t="n">
-        <v>49.66723387575536</v>
+        <v>46.68643158087417</v>
       </c>
       <c r="H78" t="n">
-        <v>3.409834025958952</v>
+        <v>3.17139220478416</v>
       </c>
       <c r="I78" t="n">
         <v>103.5437500854655</v>
       </c>
       <c r="J78" t="n">
-        <v>53.38814440168505</v>
+        <v>55.22945859981466</v>
       </c>
       <c r="K78" t="n">
-        <v>3.997693569883748</v>
+        <v>3.993802203932325</v>
       </c>
       <c r="L78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="M78" t="n">
-        <v>117.0607914055987</v>
+        <v>110.8945250546275</v>
       </c>
       <c r="N78" t="n">
-        <v>5.690818513743579</v>
+        <v>5.324883351245751</v>
       </c>
       <c r="O78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="P78" t="n">
-        <v>52.91358782520027</v>
+        <v>55.29074480395132</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.404478823137183</v>
+        <v>4.416331334856955</v>
       </c>
       <c r="R78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="S78" t="n">
-        <v>31.481531192365</v>
+        <v>33.76738924721007</v>
       </c>
       <c r="T78" t="n">
-        <v>2.921953121524437</v>
+        <v>2.900697323286576</v>
       </c>
       <c r="U78" t="n">
         <v>124.390269119479</v>
@@ -7292,11 +7302,11 @@
         </is>
       </c>
       <c r="X78" t="n">
-        <v>31.481531192365</v>
+        <v>33.76738924721007</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=31.48% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=33.77% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7320,52 +7330,52 @@
         <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F79" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G79" t="n">
-        <v>50.335930401087</v>
+        <v>48.60323352904944</v>
       </c>
       <c r="H79" t="n">
-        <v>3.4517723720998</v>
+        <v>3.286245827177914</v>
       </c>
       <c r="I79" t="n">
         <v>102.5016657415887</v>
       </c>
       <c r="J79" t="n">
-        <v>49.71125144661219</v>
+        <v>53.41466540703234</v>
       </c>
       <c r="K79" t="n">
-        <v>4.416549243131193</v>
+        <v>4.80042473164641</v>
       </c>
       <c r="L79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="M79" t="n">
-        <v>57.69992528257627</v>
+        <v>62.22131467786915</v>
       </c>
       <c r="N79" t="n">
-        <v>6.6875</v>
+        <v>7.288461538461538</v>
       </c>
       <c r="O79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="P79" t="n">
-        <v>57.69992528257627</v>
+        <v>62.22131467786915</v>
       </c>
       <c r="Q79" t="n">
-        <v>6.6875</v>
+        <v>7.288461538461538</v>
       </c>
       <c r="R79" t="n">
         <v>148.0195847609927</v>
       </c>
       <c r="S79" t="n">
-        <v>34.0863393255216</v>
+        <v>36.04795612140367</v>
       </c>
       <c r="T79" t="n">
-        <v>3.187340837450748</v>
+        <v>3.257588844669878</v>
       </c>
       <c r="U79" t="n">
         <v>120.3982350383182</v>
@@ -7381,11 +7391,11 @@
         </is>
       </c>
       <c r="X79" t="n">
-        <v>34.0863393255216</v>
+        <v>36.04795612140367</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=34.09% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=36.05% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7409,52 +7419,52 @@
         <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F80" t="n">
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="G80" t="n">
-        <v>144.6360358455763</v>
+        <v>143.5582136650195</v>
       </c>
       <c r="H80" t="n">
-        <v>28.39113287792135</v>
+        <v>29.25013720036457</v>
       </c>
       <c r="I80" t="n">
         <v>180.9937478063148</v>
       </c>
       <c r="J80" t="n">
-        <v>152.7039681099278</v>
+        <v>155.1167720404115</v>
       </c>
       <c r="K80" t="n">
-        <v>27.64499574860297</v>
+        <v>29.20862733339917</v>
       </c>
       <c r="L80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="M80" t="n">
-        <v>120.3882102704755</v>
+        <v>121.8065814559429</v>
       </c>
       <c r="N80" t="n">
-        <v>21.3492732445399</v>
+        <v>22.8612208366394</v>
       </c>
       <c r="O80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="P80" t="n">
-        <v>160.5027082559168</v>
+        <v>163.5409614670002</v>
       </c>
       <c r="Q80" t="n">
-        <v>30.35191477596914</v>
+        <v>31.86330594704844</v>
       </c>
       <c r="R80" t="n">
         <v>172.7461511452186</v>
       </c>
       <c r="S80" t="n">
-        <v>54.17209463992535</v>
+        <v>53.61240802508001</v>
       </c>
       <c r="T80" t="n">
-        <v>28.95510697940467</v>
+        <v>28.18228627350842</v>
       </c>
       <c r="U80" t="n">
         <v>175.912448276349</v>
@@ -7470,11 +7480,11 @@
         </is>
       </c>
       <c r="X80" t="n">
-        <v>54.17209463992535</v>
+        <v>53.61240802508001</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=54.17% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=53.61% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7498,52 +7508,52 @@
         <v>2026</v>
       </c>
       <c r="E81" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F81" t="n">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="G81" t="n">
-        <v>132.1254209199005</v>
+        <v>131.6290115636485</v>
       </c>
       <c r="H81" t="n">
-        <v>12.61055894746372</v>
+        <v>12.89128020151289</v>
       </c>
       <c r="I81" t="n">
         <v>185.5191244575439</v>
       </c>
       <c r="J81" t="n">
-        <v>117.5102746798739</v>
+        <v>113.5248773576872</v>
       </c>
       <c r="K81" t="n">
-        <v>9.366696817338918</v>
+        <v>10.23591089824205</v>
       </c>
       <c r="L81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="M81" t="n">
-        <v>162.1923398856764</v>
+        <v>160.6879071728418</v>
       </c>
       <c r="N81" t="n">
-        <v>13.02483438452085</v>
+        <v>13.36833044198843</v>
       </c>
       <c r="O81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="P81" t="n">
-        <v>146.8494116843916</v>
+        <v>149.7346987873689</v>
       </c>
       <c r="Q81" t="n">
-        <v>13.4559246932461</v>
+        <v>13.97074602195977</v>
       </c>
       <c r="R81" t="n">
         <v>163.1536185700502</v>
       </c>
       <c r="S81" t="n">
-        <v>55.18680741715015</v>
+        <v>55.98270195837857</v>
       </c>
       <c r="T81" t="n">
-        <v>8.657222666661834</v>
+        <v>8.787075583211861</v>
       </c>
       <c r="U81" t="n">
         <v>172.1596497720207</v>
@@ -7559,11 +7569,11 @@
         </is>
       </c>
       <c r="X81" t="n">
-        <v>55.18680741715015</v>
+        <v>55.98270195837857</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=55.19% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=55.98% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7587,52 +7597,52 @@
         <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F82" t="n">
-        <v>424</v>
+        <v>482</v>
       </c>
       <c r="G82" t="n">
-        <v>130.4082911873624</v>
+        <v>130.2538719970943</v>
       </c>
       <c r="H82" t="n">
-        <v>14.77151678933826</v>
+        <v>15.38036762375736</v>
       </c>
       <c r="I82" t="n">
         <v>186.2973802760101</v>
       </c>
       <c r="J82" t="n">
-        <v>147.141676840363</v>
+        <v>147.761699642381</v>
       </c>
       <c r="K82" t="n">
-        <v>15.06512782755899</v>
+        <v>15.85623120177246</v>
       </c>
       <c r="L82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="M82" t="n">
-        <v>158.9308837266639</v>
+        <v>162.0900465169206</v>
       </c>
       <c r="N82" t="n">
-        <v>14.28263561303417</v>
+        <v>15.4147405658777</v>
       </c>
       <c r="O82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="P82" t="n">
-        <v>150.7562222351752</v>
+        <v>154.1395095724688</v>
       </c>
       <c r="Q82" t="n">
-        <v>16.07901112328347</v>
+        <v>17.04319178960882</v>
       </c>
       <c r="R82" t="n">
         <v>166.6060177059153</v>
       </c>
       <c r="S82" t="n">
-        <v>37.63301310609035</v>
+        <v>40.7500349637836</v>
       </c>
       <c r="T82" t="n">
-        <v>9.210726229697036</v>
+        <v>9.748616504925208</v>
       </c>
       <c r="U82" t="n">
         <v>176.1888335684919</v>
@@ -7648,11 +7658,11 @@
         </is>
       </c>
       <c r="X82" t="n">
-        <v>37.63301310609035</v>
+        <v>40.7500349637836</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=37.63% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=40.75% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7676,52 +7686,52 @@
         <v>2026</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F83" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="G83" t="n">
-        <v>38.55088026874415</v>
+        <v>43.1997975360161</v>
       </c>
       <c r="H83" t="n">
-        <v>5.82105084784645</v>
+        <v>6.048264925018194</v>
       </c>
       <c r="I83" t="n">
         <v>88.04980557911651</v>
       </c>
       <c r="J83" t="n">
-        <v>48.81168296710427</v>
+        <v>50.07649051829125</v>
       </c>
       <c r="K83" t="n">
-        <v>7.729765190223816</v>
+        <v>7.637246332998242</v>
       </c>
       <c r="L83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="M83" t="n">
-        <v>98.48174674508603</v>
+        <v>92.30002957030169</v>
       </c>
       <c r="N83" t="n">
-        <v>33.48056145320806</v>
+        <v>31.07821057219206</v>
       </c>
       <c r="O83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="P83" t="n">
-        <v>90.07823790274031</v>
+        <v>98.53375806406798</v>
       </c>
       <c r="Q83" t="n">
-        <v>25.75172869289571</v>
+        <v>24.77082648574989</v>
       </c>
       <c r="R83" t="n">
         <v>103.1343264142703</v>
       </c>
       <c r="S83" t="n">
-        <v>52.87979117452389</v>
+        <v>52.93333819357255</v>
       </c>
       <c r="T83" t="n">
-        <v>11.57357328125053</v>
+        <v>11.37971859865602</v>
       </c>
       <c r="U83" t="n">
         <v>103.3034448942146</v>
@@ -7737,11 +7747,11 @@
         </is>
       </c>
       <c r="X83" t="n">
-        <v>38.55088026874415</v>
+        <v>43.1997975360161</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=38.55% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=43.20% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7765,52 +7775,52 @@
         <v>2026</v>
       </c>
       <c r="E84" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F84" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G84" t="n">
-        <v>35.98096847304528</v>
+        <v>40.28371767364471</v>
       </c>
       <c r="H84" t="n">
-        <v>2.43602600495171</v>
+        <v>2.490847406123287</v>
       </c>
       <c r="I84" t="n">
         <v>100.4914466151705</v>
       </c>
       <c r="J84" t="n">
-        <v>48.13170036163415</v>
+        <v>50.45190516411535</v>
       </c>
       <c r="K84" t="n">
-        <v>3.402200816679951</v>
+        <v>3.435796323442797</v>
       </c>
       <c r="L84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="M84" t="n">
-        <v>75.24862404261012</v>
+        <v>72.53719142394779</v>
       </c>
       <c r="N84" t="n">
-        <v>8.419301408575459</v>
+        <v>7.96397053099273</v>
       </c>
       <c r="O84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="P84" t="n">
-        <v>86.62199055701288</v>
+        <v>91.01392829545925</v>
       </c>
       <c r="Q84" t="n">
-        <v>11.78239945745356</v>
+        <v>11.19769136149799</v>
       </c>
       <c r="R84" t="n">
         <v>98.74789164115032</v>
       </c>
       <c r="S84" t="n">
-        <v>53.84857939311091</v>
+        <v>55.35222777066018</v>
       </c>
       <c r="T84" t="n">
-        <v>5.086121349145057</v>
+        <v>5.146215844761524</v>
       </c>
       <c r="U84" t="n">
         <v>110.607240444147</v>
@@ -7826,11 +7836,11 @@
         </is>
       </c>
       <c r="X84" t="n">
-        <v>35.98096847304528</v>
+        <v>40.28371767364471</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=35.98% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=40.28% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7854,52 +7864,52 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F85" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="G85" t="n">
-        <v>48.22410033751445</v>
+        <v>52.76186105573009</v>
       </c>
       <c r="H85" t="n">
-        <v>3.974672465078696</v>
+        <v>4.117499428134585</v>
       </c>
       <c r="I85" t="n">
         <v>109.9471447641292</v>
       </c>
       <c r="J85" t="n">
-        <v>51.89351382674426</v>
+        <v>50.75761225595868</v>
       </c>
       <c r="K85" t="n">
-        <v>4.30813663569926</v>
+        <v>4.204387319908268</v>
       </c>
       <c r="L85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="M85" t="n">
-        <v>92.30664048160357</v>
+        <v>87.58282274969386</v>
       </c>
       <c r="N85" t="n">
-        <v>16.22673645999537</v>
+        <v>15.15160288614957</v>
       </c>
       <c r="O85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="P85" t="n">
-        <v>97.41973716461989</v>
+        <v>105.3105266134953</v>
       </c>
       <c r="Q85" t="n">
-        <v>15.41689418699289</v>
+        <v>14.84636386491651</v>
       </c>
       <c r="R85" t="n">
         <v>106.9882513320439</v>
       </c>
       <c r="S85" t="n">
-        <v>43.15264064001872</v>
+        <v>42.65874933717573</v>
       </c>
       <c r="T85" t="n">
-        <v>4.338974668943958</v>
+        <v>4.227487013689769</v>
       </c>
       <c r="U85" t="n">
         <v>107.8756984639591</v>
@@ -7915,11 +7925,11 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>43.15264064001872</v>
+        <v>42.65874933717573</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=43.15% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=42.66% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -7943,52 +7953,52 @@
         <v>2026</v>
       </c>
       <c r="E86" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F86" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G86" t="n">
-        <v>119.6206339741325</v>
+        <v>119.187088797981</v>
       </c>
       <c r="H86" t="n">
-        <v>3.890290018699859</v>
+        <v>4.100360487593037</v>
       </c>
       <c r="I86" t="n">
         <v>160.3842205944857</v>
       </c>
       <c r="J86" t="n">
-        <v>131.2996698967427</v>
+        <v>127.8983281168288</v>
       </c>
       <c r="K86" t="n">
-        <v>1.592519190019324</v>
+        <v>1.868879119234964</v>
       </c>
       <c r="L86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="M86" t="n">
-        <v>143.9765512792932</v>
+        <v>140.7985337554678</v>
       </c>
       <c r="N86" t="n">
-        <v>2.822131001700958</v>
+        <v>3.01021462564285</v>
       </c>
       <c r="O86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="P86" t="n">
-        <v>174.2219484859416</v>
+        <v>172.7754875759728</v>
       </c>
       <c r="Q86" t="n">
-        <v>24.16666666666667</v>
+        <v>23.67307692307692</v>
       </c>
       <c r="R86" t="n">
         <v>188.4995472315167</v>
       </c>
       <c r="S86" t="n">
-        <v>86.77624301918637</v>
+        <v>87.65363536216613</v>
       </c>
       <c r="T86" t="n">
-        <v>1.001154152655852</v>
+        <v>1.307092869748586</v>
       </c>
       <c r="U86" t="n">
         <v>113.2748521774272</v>
@@ -8004,11 +8014,11 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>86.77624301918637</v>
+        <v>87.65363536216613</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=86.78% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=87.65% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8032,52 +8042,52 @@
         <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F87" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G87" t="n">
-        <v>124.0748652164507</v>
+        <v>123.9503694107824</v>
       </c>
       <c r="H87" t="n">
-        <v>1.378238515867345</v>
+        <v>1.456561855382656</v>
       </c>
       <c r="I87" t="n">
         <v>171.410316416684</v>
       </c>
       <c r="J87" t="n">
-        <v>152.1191024197826</v>
+        <v>151.8452170739236</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8877626768742942</v>
+        <v>0.9569466966124592</v>
       </c>
       <c r="L87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="M87" t="n">
-        <v>167.7190918164549</v>
+        <v>168.0044364020023</v>
       </c>
       <c r="N87" t="n">
-        <v>10.45833333333333</v>
+        <v>10.26923076923077</v>
       </c>
       <c r="O87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="P87" t="n">
-        <v>167.7190918164549</v>
+        <v>168.0044364020023</v>
       </c>
       <c r="Q87" t="n">
-        <v>10.45833333333333</v>
+        <v>10.26923076923077</v>
       </c>
       <c r="R87" t="n">
         <v>191.241827101395</v>
       </c>
       <c r="S87" t="n">
-        <v>117.016074579642</v>
+        <v>117.1224183786047</v>
       </c>
       <c r="T87" t="n">
-        <v>0.6133114361700361</v>
+        <v>0.7576229918228641</v>
       </c>
       <c r="U87" t="n">
         <v>108.9238350712686</v>
@@ -8093,11 +8103,11 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>117.016074579642</v>
+        <v>117.1224183786047</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=117.02% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=117.12% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8121,52 +8131,52 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F88" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G88" t="n">
-        <v>137.2772444978907</v>
+        <v>133.1340630323003</v>
       </c>
       <c r="H88" t="n">
-        <v>2.055451826229087</v>
+        <v>2.051713009899168</v>
       </c>
       <c r="I88" t="n">
         <v>169.0038464611843</v>
       </c>
       <c r="J88" t="n">
-        <v>178.8431439589145</v>
+        <v>180.4350145751346</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9167893191839737</v>
+        <v>0.9615121828108862</v>
       </c>
       <c r="L88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="M88" t="n">
-        <v>170.8399756459885</v>
+        <v>165.0245602125755</v>
       </c>
       <c r="N88" t="n">
-        <v>2.104949722687403</v>
+        <v>2.075674739021522</v>
       </c>
       <c r="O88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="P88" t="n">
-        <v>182.0372258426758</v>
+        <v>179.8964312818334</v>
       </c>
       <c r="Q88" t="n">
-        <v>14.125</v>
+        <v>13.84615384615385</v>
       </c>
       <c r="R88" t="n">
         <v>190.1751472740156</v>
       </c>
       <c r="S88" t="n">
-        <v>122.629638513054</v>
+        <v>123.5071248811116</v>
       </c>
       <c r="T88" t="n">
-        <v>0.7384892654011512</v>
+        <v>1.131116051777212</v>
       </c>
       <c r="U88" t="n">
         <v>121.3094122928426</v>
@@ -8182,11 +8192,11 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>122.629638513054</v>
+        <v>123.5071248811116</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=122.63% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=123.51% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8220,7 @@
         <v>2026</v>
       </c>
       <c r="E89" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -8219,7 +8229,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1035679512288425</v>
+        <v>0.1039132270690247</v>
       </c>
       <c r="I89" t="n">
         <v>200</v>
@@ -8228,7 +8238,7 @@
         <v>200</v>
       </c>
       <c r="K89" t="n">
-        <v>0.007116236184866621</v>
+        <v>0.007230453015671066</v>
       </c>
       <c r="L89" t="n">
         <v>200</v>
@@ -8293,7 +8303,7 @@
         <v>2026</v>
       </c>
       <c r="E90" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -8302,7 +8312,7 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09100131122582784</v>
+        <v>0.09129889207558607</v>
       </c>
       <c r="I90" t="n">
         <v>200</v>
@@ -8311,7 +8321,7 @@
         <v>200</v>
       </c>
       <c r="K90" t="n">
-        <v>0.003352477918869271</v>
+        <v>0.003387767147173362</v>
       </c>
       <c r="L90" t="n">
         <v>200</v>
@@ -8376,7 +8386,7 @@
         <v>2026</v>
       </c>
       <c r="E91" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -8385,7 +8395,7 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09345947579812951</v>
+        <v>0.09375575732311482</v>
       </c>
       <c r="I91" t="n">
         <v>200</v>
@@ -8394,7 +8404,7 @@
         <v>200</v>
       </c>
       <c r="K91" t="n">
-        <v>0.01358042405695121</v>
+        <v>0.01353305780754677</v>
       </c>
       <c r="L91" t="n">
         <v>200</v>
@@ -8417,7 +8427,7 @@
         <v>200</v>
       </c>
       <c r="T91" t="n">
-        <v>2.710778893187692e-17</v>
+        <v>2.502257439865562e-17</v>
       </c>
       <c r="U91" t="n">
         <v>200</v>
@@ -8459,52 +8469,52 @@
         <v>2026</v>
       </c>
       <c r="E92" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F92" t="n">
-        <v>426</v>
+        <v>497</v>
       </c>
       <c r="G92" t="n">
-        <v>50.81720714933605</v>
+        <v>48.98239479605041</v>
       </c>
       <c r="H92" t="n">
-        <v>8.229198781425604</v>
+        <v>8.327145552672791</v>
       </c>
       <c r="I92" t="n">
         <v>49.15109590531281</v>
       </c>
       <c r="J92" t="n">
-        <v>54.05813673509176</v>
+        <v>51.27271043422916</v>
       </c>
       <c r="K92" t="n">
-        <v>8.667249683706071</v>
+        <v>8.504691706163086</v>
       </c>
       <c r="L92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="M92" t="n">
-        <v>145.1299702704904</v>
+        <v>143.8102183858536</v>
       </c>
       <c r="N92" t="n">
-        <v>93.65849896561129</v>
+        <v>95.98543158524623</v>
       </c>
       <c r="O92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="P92" t="n">
-        <v>93.23088683705704</v>
+        <v>88.12288395195948</v>
       </c>
       <c r="Q92" t="n">
-        <v>33.51436772257085</v>
+        <v>31.66390403140978</v>
       </c>
       <c r="R92" t="n">
         <v>92.01416331532587</v>
       </c>
       <c r="S92" t="n">
-        <v>35.61339068746875</v>
+        <v>37.67464475879304</v>
       </c>
       <c r="T92" t="n">
-        <v>5.493510551764362</v>
+        <v>7.406895854835166</v>
       </c>
       <c r="U92" t="n">
         <v>95.83480509856771</v>
@@ -8520,11 +8530,11 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>35.61339068746875</v>
+        <v>37.67464475879304</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=35.61% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=37.67% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8548,52 +8558,52 @@
         <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F93" t="n">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="G93" t="n">
-        <v>47.29273134308652</v>
+        <v>46.33071747502665</v>
       </c>
       <c r="H93" t="n">
-        <v>3.728743913484136</v>
+        <v>3.862865777081154</v>
       </c>
       <c r="I93" t="n">
         <v>60.93105560683724</v>
       </c>
       <c r="J93" t="n">
-        <v>55.49201589625309</v>
+        <v>57.67261314686925</v>
       </c>
       <c r="K93" t="n">
-        <v>5.141016757035305</v>
+        <v>6.51001922416303</v>
       </c>
       <c r="L93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="M93" t="n">
-        <v>139.8022773934235</v>
+        <v>139.1563622088194</v>
       </c>
       <c r="N93" t="n">
-        <v>41.66525063954594</v>
+        <v>43.02895105926984</v>
       </c>
       <c r="O93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="P93" t="n">
-        <v>99.63567471335472</v>
+        <v>95.74384653120181</v>
       </c>
       <c r="Q93" t="n">
-        <v>17.93644890212915</v>
+        <v>17.24488657444334</v>
       </c>
       <c r="R93" t="n">
         <v>96.01849856237216</v>
       </c>
       <c r="S93" t="n">
-        <v>34.94100165608</v>
+        <v>36.62559731227307</v>
       </c>
       <c r="T93" t="n">
-        <v>2.318161172800703</v>
+        <v>2.9917584455536</v>
       </c>
       <c r="U93" t="n">
         <v>99.35850993844542</v>
@@ -8609,11 +8619,11 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>34.94100165608</v>
+        <v>36.62559731227307</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=34.94% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=36.63% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8637,52 +8647,52 @@
         <v>2026</v>
       </c>
       <c r="E94" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F94" t="n">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="G94" t="n">
-        <v>53.25947624904145</v>
+        <v>50.85788690564483</v>
       </c>
       <c r="H94" t="n">
-        <v>4.3901691327336</v>
+        <v>4.370402940003936</v>
       </c>
       <c r="I94" t="n">
         <v>64.07712599234655</v>
       </c>
       <c r="J94" t="n">
-        <v>61.85939605120323</v>
+        <v>67.50136305395694</v>
       </c>
       <c r="K94" t="n">
-        <v>4.965759876091769</v>
+        <v>5.808354629419098</v>
       </c>
       <c r="L94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="M94" t="n">
-        <v>144.8736097808937</v>
+        <v>142.4143174612214</v>
       </c>
       <c r="N94" t="n">
-        <v>45.68054826102104</v>
+        <v>46.01139013859893</v>
       </c>
       <c r="O94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="P94" t="n">
-        <v>100.0062163492703</v>
+        <v>94.85079297405257</v>
       </c>
       <c r="Q94" t="n">
-        <v>19.46287869400934</v>
+        <v>18.52912014414084</v>
       </c>
       <c r="R94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="S94" t="n">
-        <v>38.00214671634703</v>
+        <v>39.84205949425877</v>
       </c>
       <c r="T94" t="n">
-        <v>3.145750961099421</v>
+        <v>4.219821617011154</v>
       </c>
       <c r="U94" t="n">
         <v>93.11495456228404</v>
@@ -8698,11 +8708,11 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>38.00214671634703</v>
+        <v>39.84205949425877</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=38.00% sobre 24 sem</t>
+          <t>NBGLM: menor SMAPE real=39.84% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8726,25 +8736,25 @@
         <v>2026</v>
       </c>
       <c r="E95" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F95" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G95" t="n">
-        <v>148.4660272027334</v>
+        <v>144.6453651559676</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6267581054027628</v>
+        <v>0.6583240568762944</v>
       </c>
       <c r="I95" t="n">
         <v>152.3875262412586</v>
       </c>
       <c r="J95" t="n">
-        <v>199.301491897467</v>
+        <v>199.3241646511038</v>
       </c>
       <c r="K95" t="n">
-        <v>0.4984347198135324</v>
+        <v>0.5753658334003174</v>
       </c>
       <c r="L95" t="n">
         <v>128.1095321097334</v>
@@ -8753,25 +8763,25 @@
         <v>200</v>
       </c>
       <c r="N95" t="n">
-        <v>0.5</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="O95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="P95" t="n">
-        <v>168.2373082435138</v>
+        <v>170.6805922247819</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.169917931694554</v>
+        <v>3.041462706179588</v>
       </c>
       <c r="R95" t="n">
         <v>118.2821915164861</v>
       </c>
       <c r="S95" t="n">
-        <v>157.8434525212073</v>
+        <v>151.5302584151449</v>
       </c>
       <c r="T95" t="n">
-        <v>1.532090325210222</v>
+        <v>1.552458663105297</v>
       </c>
       <c r="U95" t="n">
         <v>128.8999217807187</v>
@@ -8787,11 +8797,11 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>148.4660272027334</v>
+        <v>144.6453651559676</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=148.47% sobre 24 sem</t>
+          <t>Prophet: menor SMAPE real=144.65% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8815,52 +8825,52 @@
         <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="n">
-        <v>185.5000821403173</v>
+        <v>185.4949802057396</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2811483352958202</v>
+        <v>0.2981965736936112</v>
       </c>
       <c r="I96" t="n">
         <v>158.9896824444987</v>
       </c>
       <c r="J96" t="n">
-        <v>199.4072912825802</v>
+        <v>199.4502738784551</v>
       </c>
       <c r="K96" t="n">
-        <v>0.125414931048193</v>
+        <v>0.1542300177840033</v>
       </c>
       <c r="L96" t="n">
         <v>189.1617640516506</v>
       </c>
       <c r="M96" t="n">
-        <v>200</v>
+        <v>195.7774133191963</v>
       </c>
       <c r="N96" t="n">
-        <v>1.481632344945054</v>
+        <v>1.776959200108318</v>
       </c>
       <c r="O96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="P96" t="n">
-        <v>189.4889548982903</v>
+        <v>182.6873255227291</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.123775857105041</v>
+        <v>2.906151396101761</v>
       </c>
       <c r="R96" t="n">
         <v>124.4459476108536</v>
       </c>
       <c r="S96" t="n">
-        <v>184.9394139173172</v>
+        <v>180.5351894338612</v>
       </c>
       <c r="T96" t="n">
-        <v>0.9436462249325906</v>
+        <v>0.9586028878180607</v>
       </c>
       <c r="U96" t="n">
         <v>151.8363274594118</v>
@@ -8878,7 +8888,7 @@
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -8902,70 +8912,72 @@
         <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G97" t="n">
-        <v>170.4249265108153</v>
+        <v>171.9346393710365</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4048010743517452</v>
+        <v>0.4505051113538389</v>
       </c>
       <c r="I97" t="n">
         <v>157.2976315063829</v>
       </c>
       <c r="J97" t="n">
-        <v>199.4090022955906</v>
+        <v>199.4351970061328</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3774483945165135</v>
+        <v>0.4253306195534445</v>
       </c>
       <c r="L97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="M97" t="n">
-        <v>154.6893586856203</v>
+        <v>148.8155072683896</v>
       </c>
       <c r="N97" t="n">
-        <v>1.575165877739588</v>
+        <v>1.556585907936096</v>
       </c>
       <c r="O97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="P97" t="n">
-        <v>169.0263878187246</v>
+        <v>170.2653323059756</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.04563638965791</v>
+        <v>1.965202821222686</v>
       </c>
       <c r="R97" t="n">
         <v>128.4785456608675</v>
       </c>
       <c r="S97" t="n">
-        <v>157.9595871373196</v>
+        <v>153.558624927868</v>
       </c>
       <c r="T97" t="n">
-        <v>0.8237589857741744</v>
+        <v>0.8518205666403911</v>
       </c>
       <c r="U97" t="n">
         <v>136.0400571203446</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="X97" t="n">
+        <v>153.558624927868</v>
+      </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=153.56% sobre 26 sem</t>
         </is>
       </c>
     </row>
@@ -8989,7 +9001,7 @@
         <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8998,7 +9010,7 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.06050305315781612</v>
+        <v>0.05584897214567642</v>
       </c>
       <c r="I98" t="n">
         <v>198.585723184526</v>
@@ -9007,7 +9019,7 @@
         <v>200</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0005236563068297292</v>
+        <v>0.0005257727496187077</v>
       </c>
       <c r="L98" t="n">
         <v>199.9898962083731</v>
@@ -9016,7 +9028,7 @@
         <v>200</v>
       </c>
       <c r="N98" t="n">
-        <v>0.5</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="O98" t="n">
         <v>199.2030987655621</v>
@@ -9032,7 +9044,7 @@
         <v>200</v>
       </c>
       <c r="T98" t="n">
-        <v>0.042972898000321</v>
+        <v>0.05238370102220309</v>
       </c>
       <c r="U98" t="n">
         <v>199.9999998548883</v>
@@ -9074,7 +9086,7 @@
         <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -9083,7 +9095,7 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.03485912018033694</v>
+        <v>0.0321776493972341</v>
       </c>
       <c r="I99" t="n">
         <v>198.7380283178126</v>
@@ -9092,7 +9104,7 @@
         <v>200</v>
       </c>
       <c r="K99" t="n">
-        <v>0.0016373444565096</v>
+        <v>0.001656036062763181</v>
       </c>
       <c r="L99" t="n">
         <v>199.9983019911245</v>
@@ -9101,7 +9113,7 @@
         <v>200</v>
       </c>
       <c r="N99" t="n">
-        <v>0.3171048613027408</v>
+        <v>0.4409654044720926</v>
       </c>
       <c r="O99" t="n">
         <v>198.5022493653877</v>
@@ -9117,7 +9129,7 @@
         <v>200</v>
       </c>
       <c r="T99" t="n">
-        <v>0.03506900760664092</v>
+        <v>0.04163218264949037</v>
       </c>
       <c r="U99" t="n">
         <v>200</v>
@@ -9159,7 +9171,7 @@
         <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -9168,7 +9180,7 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.05177206683268074</v>
+        <v>0.05279450630904018</v>
       </c>
       <c r="I100" t="n">
         <v>200</v>
@@ -9177,7 +9189,7 @@
         <v>200</v>
       </c>
       <c r="K100" t="n">
-        <v>0.002396106685502108</v>
+        <v>0.002392263610996015</v>
       </c>
       <c r="L100" t="n">
         <v>200</v>
@@ -9186,7 +9198,7 @@
         <v>200</v>
       </c>
       <c r="N100" t="n">
-        <v>0.125</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="O100" t="n">
         <v>200</v>
@@ -9202,7 +9214,7 @@
         <v>200</v>
       </c>
       <c r="T100" t="n">
-        <v>0.01616425401782888</v>
+        <v>0.0202913101091679</v>
       </c>
       <c r="U100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y100"/>
+  <dimension ref="A1:AD100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,85 +471,110 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>mase_real_prophet</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>cv_smape_prophet</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>smape_real_deepar</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mae_real_deepar</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>mase_real_deepar</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>cv_smape_deepar</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>smape_real_ensemble</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mae_real_ensemble</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mase_real_ensemble</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cv_smape_ensemble</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>smape_real_stacking</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mae_real_stacking</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mase_real_stacking</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>cv_smape_stacking</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>smape_real_nbglm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mae_real_nbglm</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mase_real_nbglm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>cv_smape_nbglm</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>motor_productivo</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>criterio_seleccion</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>smape_ganador</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>justificacion</t>
         </is>
@@ -587,56 +612,71 @@
         <v>0.2006674831338297</v>
       </c>
       <c r="I2" t="n">
+        <v>0.01004121885892502</v>
+      </c>
+      <c r="J2" t="n">
         <v>185.8333489727328</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>197.4073596888732</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.1951254343367843</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
+        <v>0.009763899763529472</v>
+      </c>
+      <c r="N2" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>155.6923076923077</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.75</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
+        <v>0.03752931978107897</v>
+      </c>
+      <c r="R2" t="n">
         <v>197.8088169752323</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>155.6923076923077</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0.75</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
+        <v>0.03752931978107897</v>
+      </c>
+      <c r="V2" t="n">
         <v>199.5572761277739</v>
       </c>
-      <c r="S2" t="n">
+      <c r="W2" t="n">
         <v>184.0794920386864</v>
       </c>
-      <c r="T2" t="n">
+      <c r="X2" t="n">
         <v>0.1760121898273306</v>
       </c>
-      <c r="U2" t="n">
+      <c r="Y2" t="n">
+        <v>0.008807490343197154</v>
+      </c>
+      <c r="Z2" t="n">
         <v>194.9779461019607</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>NBGLM: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
@@ -674,56 +714,71 @@
         <v>0.1229909956009693</v>
       </c>
       <c r="I3" t="n">
+        <v>0.01348308276543685</v>
+      </c>
+      <c r="J3" t="n">
         <v>157.2321783542833</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>197.2796288638902</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.1214219715065594</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
+        <v>0.01331107601305208</v>
+      </c>
+      <c r="N3" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>183.3333333333333</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.3269230769230769</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
+        <v>0.03583946029989196</v>
+      </c>
+      <c r="R3" t="n">
         <v>197.8854209931308</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>183.3333333333333</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0.3269230769230769</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
+        <v>0.03583946029989196</v>
+      </c>
+      <c r="V3" t="n">
         <v>199.636475467609</v>
       </c>
-      <c r="S3" t="n">
+      <c r="W3" t="n">
         <v>187.0830627946073</v>
       </c>
-      <c r="T3" t="n">
+      <c r="X3" t="n">
         <v>0.09806476296935614</v>
       </c>
-      <c r="U3" t="n">
+      <c r="Y3" t="n">
+        <v>0.01075050501890852</v>
+      </c>
+      <c r="Z3" t="n">
         <v>198.5158836242873</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>NBGLM: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
@@ -761,56 +816,71 @@
         <v>0.0872286621725092</v>
       </c>
       <c r="I4" t="n">
+        <v>0.00757686533528853</v>
+      </c>
+      <c r="J4" t="n">
         <v>158.5580779411727</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>191.1760450805634</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.1792257312452026</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
+        <v>0.01556792453812835</v>
+      </c>
+      <c r="N4" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>160</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.5</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
+        <v>0.04343105320304018</v>
+      </c>
+      <c r="R4" t="n">
         <v>197.7265973322816</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>160</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0.5</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
+        <v>0.04343105320304018</v>
+      </c>
+      <c r="V4" t="n">
         <v>199.5859359679221</v>
       </c>
-      <c r="S4" t="n">
+      <c r="W4" t="n">
         <v>192.0311816113775</v>
       </c>
-      <c r="T4" t="n">
+      <c r="X4" t="n">
         <v>0.1242171289414107</v>
       </c>
-      <c r="U4" t="n">
+      <c r="Y4" t="n">
+        <v>0.01078976147156662</v>
+      </c>
+      <c r="Z4" t="n">
         <v>196.9436529554095</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -848,56 +918,71 @@
         <v>0.194717393070758</v>
       </c>
       <c r="I5" t="n">
+        <v>0.240577474064257</v>
+      </c>
+      <c r="J5" t="n">
         <v>175.1088701866436</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>199.1789075403633</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.2029091662089284</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
+        <v>0.250698583733039</v>
+      </c>
+      <c r="N5" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M5" t="n">
-        <v>200</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
+        <v>200</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.3076923076923077</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
+        <v>0.3801603801603802</v>
+      </c>
+      <c r="R5" t="n">
         <v>187.2707284786031</v>
       </c>
-      <c r="P5" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
+        <v>200</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.3076923076923077</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
+        <v>0.3801603801603802</v>
+      </c>
+      <c r="V5" t="n">
         <v>193.7972259177366</v>
       </c>
-      <c r="S5" t="n">
+      <c r="W5" t="n">
         <v>199.4340125103117</v>
       </c>
-      <c r="T5" t="n">
+      <c r="X5" t="n">
         <v>0.2029541892643015</v>
       </c>
-      <c r="U5" t="n">
+      <c r="Y5" t="n">
+        <v>0.2507542106740405</v>
+      </c>
+      <c r="Z5" t="n">
         <v>187.0400639517023</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
@@ -935,56 +1020,71 @@
         <v>0.08444375875288576</v>
       </c>
       <c r="I6" t="n">
+        <v>0.05749362298068818</v>
+      </c>
+      <c r="J6" t="n">
         <v>191.646475967384</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>199.9795881412977</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.0776408859315368</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
+        <v>0.05286187978317399</v>
+      </c>
+      <c r="N6" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M6" t="n">
-        <v>200</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
+        <v>200</v>
+      </c>
+      <c r="P6" t="n">
         <v>0.1346153846153846</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
+        <v>0.09165302782324058</v>
+      </c>
+      <c r="R6" t="n">
         <v>192.53013744135</v>
       </c>
-      <c r="P6" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
+        <v>200</v>
+      </c>
+      <c r="T6" t="n">
         <v>0.1346153846153846</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
+        <v>0.09165302782324058</v>
+      </c>
+      <c r="V6" t="n">
         <v>193.2139428195562</v>
       </c>
-      <c r="S6" t="n">
+      <c r="W6" t="n">
         <v>198.5786411733137</v>
       </c>
-      <c r="T6" t="n">
+      <c r="X6" t="n">
         <v>0.08214655428525444</v>
       </c>
-      <c r="U6" t="n">
+      <c r="Y6" t="n">
+        <v>0.05592956887506685</v>
+      </c>
+      <c r="Z6" t="n">
         <v>198.9985835834048</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -1022,56 +1122,71 @@
         <v>0.134291957686018</v>
       </c>
       <c r="I7" t="n">
+        <v>0.07972806393232978</v>
+      </c>
+      <c r="J7" t="n">
         <v>186.9197740801393</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>199.9807829565354</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.1157850864840191</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
+        <v>0.06874068214264582</v>
+      </c>
+      <c r="N7" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M7" t="n">
-        <v>200</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
+        <v>200</v>
+      </c>
+      <c r="P7" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
+        <v>0.1027543884686742</v>
+      </c>
+      <c r="R7" t="n">
         <v>185.3187572725189</v>
       </c>
-      <c r="P7" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
+        <v>200</v>
+      </c>
+      <c r="T7" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
+        <v>0.1027543884686742</v>
+      </c>
+      <c r="V7" t="n">
         <v>190.8625800946274</v>
       </c>
-      <c r="S7" t="n">
+      <c r="W7" t="n">
         <v>199.8339639128756</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>0.127880876000855</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
+        <v>0.0759218558817692</v>
+      </c>
+      <c r="Z7" t="n">
         <v>197.3279694158802</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
@@ -1109,58 +1224,73 @@
         <v>4.842719830400823</v>
       </c>
       <c r="I8" t="n">
+        <v>0.3045735742390455</v>
+      </c>
+      <c r="J8" t="n">
         <v>154.5040916050135</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>66.09321580505865</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>6.379512625221059</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
+        <v>0.4012272091333999</v>
+      </c>
+      <c r="N8" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>94.35475689730009</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>14.71153846153846</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
+        <v>0.9252539912917271</v>
+      </c>
+      <c r="R8" t="n">
         <v>165.4966466258163</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>94.35475689730009</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>14.71153846153846</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
+        <v>0.9252539912917271</v>
+      </c>
+      <c r="V8" t="n">
         <v>172.894287988784</v>
       </c>
-      <c r="S8" t="n">
+      <c r="W8" t="n">
         <v>60.16199655312483</v>
       </c>
-      <c r="T8" t="n">
+      <c r="X8" t="n">
         <v>3.27268470603121</v>
       </c>
-      <c r="U8" t="n">
+      <c r="Y8" t="n">
+        <v>0.2058292267944157</v>
+      </c>
+      <c r="Z8" t="n">
         <v>111.5676388698673</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X8" t="n">
+      <c r="AC8" t="n">
         <v>60.16199655312483</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=60.16% sobre 26 sem</t>
         </is>
@@ -1198,58 +1328,73 @@
         <v>2.184156444835504</v>
       </c>
       <c r="I9" t="n">
+        <v>0.2712184952841915</v>
+      </c>
+      <c r="J9" t="n">
         <v>164.086229256472</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>81.59982771449211</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>3.552656265560343</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
+        <v>0.4411525048425727</v>
+      </c>
+      <c r="N9" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>103.0533505779254</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>7.346153846153846</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
+        <v>0.9122115757738575</v>
+      </c>
+      <c r="R9" t="n">
         <v>169.8771678897395</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>103.0533505779254</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>7.346153846153846</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
+        <v>0.9122115757738575</v>
+      </c>
+      <c r="V9" t="n">
         <v>176.8647517474977</v>
       </c>
-      <c r="S9" t="n">
+      <c r="W9" t="n">
         <v>57.53807472706776</v>
       </c>
-      <c r="T9" t="n">
+      <c r="X9" t="n">
         <v>1.39801286411231</v>
       </c>
-      <c r="U9" t="n">
+      <c r="Y9" t="n">
+        <v>0.1735988034598134</v>
+      </c>
+      <c r="Z9" t="n">
         <v>121.2492629006552</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X9" t="n">
+      <c r="AC9" t="n">
         <v>57.53807472706776</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=57.54% sobre 26 sem</t>
         </is>
@@ -1287,58 +1432,73 @@
         <v>2.459546181486654</v>
       </c>
       <c r="I10" t="n">
+        <v>0.2983528347519823</v>
+      </c>
+      <c r="J10" t="n">
         <v>164.4874496413386</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>80.62136290545641</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>1.954195725687168</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
+        <v>0.2370517938665254</v>
+      </c>
+      <c r="N10" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>98.21286575944892</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>8</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
+        <v>0.9704321455648218</v>
+      </c>
+      <c r="R10" t="n">
         <v>162.692005533007</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>98.21286575944892</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>8</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
+        <v>0.9704321455648218</v>
+      </c>
+      <c r="V10" t="n">
         <v>168.5443712458804</v>
       </c>
-      <c r="S10" t="n">
+      <c r="W10" t="n">
         <v>65.3176995141846</v>
       </c>
-      <c r="T10" t="n">
+      <c r="X10" t="n">
         <v>1.888960773953696</v>
       </c>
-      <c r="U10" t="n">
+      <c r="Y10" t="n">
+        <v>0.2291385320944589</v>
+      </c>
+      <c r="Z10" t="n">
         <v>114.746491150853</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X10" t="n">
+      <c r="AC10" t="n">
         <v>65.3176995141846</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=65.32% sobre 26 sem</t>
         </is>
@@ -1376,58 +1536,73 @@
         <v>0.6173266662411392</v>
       </c>
       <c r="I11" t="n">
+        <v>0.03931234491485861</v>
+      </c>
+      <c r="J11" t="n">
         <v>123.2554563734294</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>198.496465086452</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0.6359759888102187</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
+        <v>0.04049996346652139</v>
+      </c>
+      <c r="N11" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>181.3852359729555</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>23.063540985444</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
+        <v>1.468723008028274</v>
+      </c>
+      <c r="R11" t="n">
         <v>192.5936095855003</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>166.0092425476692</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>0.9921050187942237</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
+        <v>0.06317882706749285</v>
+      </c>
+      <c r="V11" t="n">
         <v>177.781032308345</v>
       </c>
-      <c r="S11" t="n">
+      <c r="W11" t="n">
         <v>123.5450259718557</v>
       </c>
-      <c r="T11" t="n">
+      <c r="X11" t="n">
         <v>0.7176289557794688</v>
       </c>
-      <c r="U11" t="n">
+      <c r="Y11" t="n">
+        <v>0.04569975439789652</v>
+      </c>
+      <c r="Z11" t="n">
         <v>147.9725418621825</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X11" t="n">
+      <c r="AC11" t="n">
         <v>123.5450259718557</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=123.55% sobre 26 sem</t>
         </is>
@@ -1465,56 +1640,71 @@
         <v>0.351300905032329</v>
       </c>
       <c r="I12" t="n">
+        <v>0.04415408075818747</v>
+      </c>
+      <c r="J12" t="n">
         <v>147.3485671696691</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>199.6235849176428</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.4164095901696</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>0.05233741903152867</v>
+      </c>
+      <c r="N12" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>187.6610978466063</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>10.67195884484822</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
+        <v>1.341330255440468</v>
+      </c>
+      <c r="R12" t="n">
         <v>191.4723960783834</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>183.7041303456979</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>9.46877517918894</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
+        <v>1.190105285679678</v>
+      </c>
+      <c r="V12" t="n">
         <v>189.6908701459495</v>
       </c>
-      <c r="S12" t="n">
+      <c r="W12" t="n">
         <v>163.8231047633718</v>
       </c>
-      <c r="T12" t="n">
+      <c r="X12" t="n">
         <v>0.5920824067350805</v>
       </c>
-      <c r="U12" t="n">
+      <c r="Y12" t="n">
+        <v>0.07441727028877682</v>
+      </c>
+      <c r="Z12" t="n">
         <v>169.7722333133142</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
@@ -1552,56 +1742,71 @@
         <v>0.2736267513739156</v>
       </c>
       <c r="I13" t="n">
+        <v>0.02957128012146336</v>
+      </c>
+      <c r="J13" t="n">
         <v>157.1522264328246</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>199.8277670092382</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.2703163975234029</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0.02921352489276897</v>
+      </c>
+      <c r="N13" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>183.5601864370778</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>12.43617814849466</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
+        <v>1.343997638472912</v>
+      </c>
+      <c r="R13" t="n">
         <v>193.9340304002594</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>192.8768953963663</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>5.005018829816438</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
+        <v>0.540900380122006</v>
+      </c>
+      <c r="V13" t="n">
         <v>188.2053733911598</v>
       </c>
-      <c r="S13" t="n">
+      <c r="W13" t="n">
         <v>156.1223227898773</v>
       </c>
-      <c r="T13" t="n">
+      <c r="X13" t="n">
         <v>0.4111642329034779</v>
       </c>
-      <c r="U13" t="n">
+      <c r="Y13" t="n">
+        <v>0.04443517545731608</v>
+      </c>
+      <c r="Z13" t="n">
         <v>173.7069303697712</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -1639,58 +1844,73 @@
         <v>2.736183592451876</v>
       </c>
       <c r="I14" t="n">
+        <v>0.06445187703972029</v>
+      </c>
+      <c r="J14" t="n">
         <v>66.61025297793201</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>72.37581760472351</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>3.007663214842723</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
+        <v>0.07084668595875386</v>
+      </c>
+      <c r="N14" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>159.5399375746496</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>34.0281274780627</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
+        <v>0.8015458809701924</v>
+      </c>
+      <c r="R14" t="n">
         <v>128.1619574474296</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>180.7733847934277</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>91.01923076923077</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
+        <v>2.143993658163699</v>
+      </c>
+      <c r="V14" t="n">
         <v>186.0423288913966</v>
       </c>
-      <c r="S14" t="n">
+      <c r="W14" t="n">
         <v>87.66138746028537</v>
       </c>
-      <c r="T14" t="n">
+      <c r="X14" t="n">
         <v>11.71729553707351</v>
       </c>
-      <c r="U14" t="n">
+      <c r="Y14" t="n">
+        <v>0.2760054892796115</v>
+      </c>
+      <c r="Z14" t="n">
         <v>130.2296761771863</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X14" t="n">
+      <c r="AC14" t="n">
         <v>70.1958408791165</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=70.20% sobre 26 sem</t>
         </is>
@@ -1728,58 +1948,73 @@
         <v>1.268116397136053</v>
       </c>
       <c r="I15" t="n">
+        <v>0.04373286421850815</v>
+      </c>
+      <c r="J15" t="n">
         <v>82.6747998505866</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>81.22456724195349</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>1.379338892325262</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>0.04756853600000902</v>
+      </c>
+      <c r="N15" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>168.0571596557481</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>23.13369034589022</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
+        <v>0.7977994299692716</v>
+      </c>
+      <c r="R15" t="n">
         <v>129.025548034421</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>178.2169897626607</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>43.94230769230769</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
+        <v>1.515415288451176</v>
+      </c>
+      <c r="V15" t="n">
         <v>186.4460938550808</v>
       </c>
-      <c r="S15" t="n">
+      <c r="W15" t="n">
         <v>89.94521924807745</v>
       </c>
-      <c r="T15" t="n">
+      <c r="X15" t="n">
         <v>5.524349859202757</v>
       </c>
-      <c r="U15" t="n">
+      <c r="Y15" t="n">
+        <v>0.1905153524027247</v>
+      </c>
+      <c r="Z15" t="n">
         <v>131.9030800529592</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X15" t="n">
+      <c r="AC15" t="n">
         <v>68.83481220671345</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=68.83% sobre 26 sem</t>
         </is>
@@ -1817,58 +2052,73 @@
         <v>1.918207186286123</v>
       </c>
       <c r="I16" t="n">
+        <v>0.06076284890235194</v>
+      </c>
+      <c r="J16" t="n">
         <v>90.20708978859948</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>115.8528555849145</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1.837330136736047</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
+        <v>0.05820091504212382</v>
+      </c>
+      <c r="N16" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>170.0377875017184</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>24.2248835744896</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
+        <v>0.7673691094671028</v>
+      </c>
+      <c r="R16" t="n">
         <v>142.9387914444607</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>181.9337683311368</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>47.13461538461539</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
+        <v>1.493078293711832</v>
+      </c>
+      <c r="V16" t="n">
         <v>186.1307414343702</v>
       </c>
-      <c r="S16" t="n">
+      <c r="W16" t="n">
         <v>109.723969075079</v>
       </c>
-      <c r="T16" t="n">
+      <c r="X16" t="n">
         <v>5.827568191103187</v>
       </c>
-      <c r="U16" t="n">
+      <c r="Y16" t="n">
+        <v>0.1845992695657315</v>
+      </c>
+      <c r="Z16" t="n">
         <v>133.2708900338696</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X16" t="n">
+      <c r="AC16" t="n">
         <v>111.1712374987075</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=111.17% sobre 26 sem</t>
         </is>
@@ -1906,56 +2156,71 @@
         <v>0.1178858876047085</v>
       </c>
       <c r="I17" t="n">
+        <v>0.05539424968209503</v>
+      </c>
+      <c r="J17" t="n">
         <v>194.5446671655584</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>199.9584575688297</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>0.04071459157096483</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>0.01913167298488802</v>
+      </c>
+      <c r="N17" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M17" t="n">
-        <v>200</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
+        <v>200</v>
+      </c>
+      <c r="P17" t="n">
         <v>0.09615384615384616</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
+        <v>0.04518242403704959</v>
+      </c>
+      <c r="R17" t="n">
         <v>196.7571923388938</v>
       </c>
-      <c r="P17" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
+        <v>200</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.09615384615384616</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
+        <v>0.04518242403704959</v>
+      </c>
+      <c r="V17" t="n">
         <v>197.0125798901019</v>
       </c>
-      <c r="S17" t="n">
+      <c r="W17" t="n">
         <v>199.0485797204635</v>
       </c>
-      <c r="T17" t="n">
+      <c r="X17" t="n">
         <v>0.04428698637994159</v>
       </c>
-      <c r="U17" t="n">
+      <c r="Y17" t="n">
+        <v>0.02081033133859223</v>
+      </c>
+      <c r="Z17" t="n">
         <v>192.256373806382</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -1993,52 +2258,67 @@
         <v>0.03213318165902102</v>
       </c>
       <c r="I18" t="n">
+        <v>0.03427539376962242</v>
+      </c>
+      <c r="J18" t="n">
         <v>199.6410247115898</v>
       </c>
-      <c r="J18" t="n">
-        <v>200</v>
-      </c>
       <c r="K18" t="n">
+        <v>200</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.0005621916357963347</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
+        <v>0.000599671078182757</v>
+      </c>
+      <c r="N18" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="n">
-        <v>196.9959839919002</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
+        <v>196.9959839919002</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
         <v>196.686324272832</v>
       </c>
-      <c r="S18" t="n">
-        <v>200</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
+        <v>200</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.915870311351707e-263</v>
       </c>
-      <c r="U18" t="n">
+      <c r="Y18" t="n">
+        <v>4.176928332108487e-263</v>
+      </c>
+      <c r="Z18" t="n">
         <v>196.0211023092105</v>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2076,56 +2356,71 @@
         <v>0.1010139478438304</v>
       </c>
       <c r="I19" t="n">
+        <v>0.08395964496110579</v>
+      </c>
+      <c r="J19" t="n">
         <v>196.278530387405</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>199.9046485748806</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>0.04327476996875143</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
+        <v>0.03596863997402716</v>
+      </c>
+      <c r="N19" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M19" t="n">
-        <v>200</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>200</v>
+      </c>
+      <c r="P19" t="n">
         <v>0.09615384615384616</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
+        <v>0.07992007992007992</v>
+      </c>
+      <c r="R19" t="n">
         <v>196.7189002085085</v>
       </c>
-      <c r="P19" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
+        <v>200</v>
+      </c>
+      <c r="T19" t="n">
         <v>0.09615384615384616</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
+        <v>0.07992007992007992</v>
+      </c>
+      <c r="V19" t="n">
         <v>196.7488584326798</v>
       </c>
-      <c r="S19" t="n">
+      <c r="W19" t="n">
         <v>199.1378073789123</v>
       </c>
-      <c r="T19" t="n">
+      <c r="X19" t="n">
         <v>0.04495243150570093</v>
       </c>
-      <c r="U19" t="n">
+      <c r="Y19" t="n">
+        <v>0.03736305995279039</v>
+      </c>
+      <c r="Z19" t="n">
         <v>197.8046914283761</v>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -2162,53 +2457,58 @@
       <c r="H20" t="n">
         <v>0.07124381545859265</v>
       </c>
-      <c r="I20" t="n">
-        <v>200</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>200</v>
       </c>
       <c r="K20" t="n">
+        <v>200</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.001318309886591289</v>
-      </c>
-      <c r="L20" t="n">
-        <v>109.609711216533</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>109.609711216533</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="n">
-        <v>200</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>200</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="n">
-        <v>200</v>
-      </c>
-      <c r="S20" t="n">
-        <v>200</v>
-      </c>
-      <c r="T20" t="n">
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>200</v>
+      </c>
+      <c r="W20" t="n">
+        <v>200</v>
+      </c>
+      <c r="X20" t="n">
         <v>5769.23076923077</v>
       </c>
-      <c r="U20" t="n">
-        <v>200</v>
-      </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2246,52 +2546,67 @@
         <v>0.05733506266469365</v>
       </c>
       <c r="I21" t="n">
-        <v>200</v>
+        <v>0.08993735319951945</v>
       </c>
       <c r="J21" t="n">
         <v>200</v>
       </c>
       <c r="K21" t="n">
+        <v>200</v>
+      </c>
+      <c r="L21" t="n">
         <v>0.006075711302686262</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
+        <v>0.009530527533625509</v>
+      </c>
+      <c r="N21" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="n">
-        <v>200</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
+        <v>200</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="n">
-        <v>200</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>200</v>
+      </c>
+      <c r="X21" t="n">
         <v>13461.5384616087</v>
       </c>
-      <c r="U21" t="n">
-        <v>200</v>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="n">
+        <v>21116.13876330776</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2329,52 +2644,67 @@
         <v>0.06419987238281549</v>
       </c>
       <c r="I22" t="n">
-        <v>200</v>
+        <v>0.06893946027684884</v>
       </c>
       <c r="J22" t="n">
         <v>200</v>
       </c>
       <c r="K22" t="n">
+        <v>200</v>
+      </c>
+      <c r="L22" t="n">
         <v>0.0004004337771155077</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
+        <v>0.0004299960022716861</v>
+      </c>
+      <c r="N22" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="n">
-        <v>200</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>200</v>
       </c>
-      <c r="S22" t="n">
-        <v>200</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>200</v>
+      </c>
+      <c r="W22" t="n">
+        <v>200</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.473430849578971e-17</v>
       </c>
-      <c r="U22" t="n">
-        <v>200</v>
-      </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="n">
+        <v>2.656033127064667e-17</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2412,56 +2742,71 @@
         <v>0.1549098148173384</v>
       </c>
       <c r="I23" t="n">
+        <v>0.003745175335565753</v>
+      </c>
+      <c r="J23" t="n">
         <v>149.2565324185079</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>199.4606494083488</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>0.838262376823547</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
+        <v>0.0202662406001462</v>
+      </c>
+      <c r="N23" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>195.2380952380952</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>4.316793663519504</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
+        <v>0.1043649117804655</v>
+      </c>
+      <c r="R23" t="n">
         <v>169.6992056798271</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>195.2380952380952</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>5.307692307692307</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
+        <v>0.128321361322268</v>
+      </c>
+      <c r="V23" t="n">
         <v>186.3774873978808</v>
       </c>
-      <c r="S23" t="n">
+      <c r="W23" t="n">
         <v>192.0713197266988</v>
       </c>
-      <c r="T23" t="n">
+      <c r="X23" t="n">
         <v>0.7520862116405661</v>
       </c>
-      <c r="U23" t="n">
+      <c r="Y23" t="n">
+        <v>0.01818280354525394</v>
+      </c>
+      <c r="Z23" t="n">
         <v>159.9263814945425</v>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -2499,56 +2844,71 @@
         <v>0.0736243714974817</v>
       </c>
       <c r="I24" t="n">
+        <v>0.003276289650840515</v>
+      </c>
+      <c r="J24" t="n">
         <v>156.2502876793226</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>198.9207311571889</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>0.7476191834856146</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
+        <v>0.03326910564808742</v>
+      </c>
+      <c r="N24" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>179.4183191604088</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>1.044049313435188</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
+        <v>0.04646026704203311</v>
+      </c>
+      <c r="R24" t="n">
         <v>159.6122718089852</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>187.5</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>2.211538461538462</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
+        <v>0.09841361530973547</v>
+      </c>
+      <c r="V24" t="n">
         <v>185.3144083651474</v>
       </c>
-      <c r="S24" t="n">
+      <c r="W24" t="n">
         <v>194.5708160695934</v>
       </c>
-      <c r="T24" t="n">
+      <c r="X24" t="n">
         <v>0.3302519970580709</v>
       </c>
-      <c r="U24" t="n">
+      <c r="Y24" t="n">
+        <v>0.0146962368319542</v>
+      </c>
+      <c r="Z24" t="n">
         <v>166.4426133688291</v>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -2586,56 +2946,71 @@
         <v>0.0851379480990028</v>
       </c>
       <c r="I25" t="n">
+        <v>0.003055989163396623</v>
+      </c>
+      <c r="J25" t="n">
         <v>155.3955473497874</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>199.9371026520693</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>0.3177389752069076</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
+        <v>0.0114051006243646</v>
+      </c>
+      <c r="N25" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M25" t="n">
-        <v>200</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
+        <v>200</v>
+      </c>
+      <c r="P25" t="n">
         <v>3.153846153846154</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
+        <v>0.1132059191509556</v>
+      </c>
+      <c r="R25" t="n">
         <v>177.0659734750362</v>
       </c>
-      <c r="P25" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
+        <v>200</v>
+      </c>
+      <c r="T25" t="n">
         <v>3.153846153846154</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
+        <v>0.1132059191509556</v>
+      </c>
+      <c r="V25" t="n">
         <v>183.340259481936</v>
       </c>
-      <c r="S25" t="n">
+      <c r="W25" t="n">
         <v>199.6698745881943</v>
       </c>
-      <c r="T25" t="n">
+      <c r="X25" t="n">
         <v>0.4625315179892543</v>
       </c>
-      <c r="U25" t="n">
+      <c r="Y25" t="n">
+        <v>0.01660236519983863</v>
+      </c>
+      <c r="Z25" t="n">
         <v>180.6321027113416</v>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -2673,56 +3048,71 @@
         <v>0.02031572516823366</v>
       </c>
       <c r="I26" t="n">
+        <v>0.0005919176958786099</v>
+      </c>
+      <c r="J26" t="n">
         <v>97.19414576199205</v>
       </c>
-      <c r="J26" t="n">
-        <v>200</v>
-      </c>
       <c r="K26" t="n">
+        <v>200</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.1448044608516833</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
+        <v>0.004219013700495189</v>
+      </c>
+      <c r="N26" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M26" t="n">
-        <v>200</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
+        <v>200</v>
+      </c>
+      <c r="P26" t="n">
         <v>72.86538461538461</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
+        <v>2.12300128170109</v>
+      </c>
+      <c r="R26" t="n">
         <v>198.3074653131699</v>
       </c>
-      <c r="P26" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
+        <v>200</v>
+      </c>
+      <c r="T26" t="n">
         <v>72.86538461538461</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
+        <v>2.12300128170109</v>
+      </c>
+      <c r="V26" t="n">
         <v>199.6509594119097</v>
       </c>
-      <c r="S26" t="n">
-        <v>200</v>
-      </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
+        <v>200</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.285590062997845</v>
       </c>
-      <c r="U26" t="n">
+      <c r="Y26" t="n">
+        <v>0.0374568715432314</v>
+      </c>
+      <c r="Z26" t="n">
         <v>183.6686755299509</v>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2760,56 +3150,71 @@
         <v>0.01422506820371157</v>
       </c>
       <c r="I27" t="n">
+        <v>0.0007615897315020412</v>
+      </c>
+      <c r="J27" t="n">
         <v>129.0985231723771</v>
       </c>
-      <c r="J27" t="n">
-        <v>200</v>
-      </c>
       <c r="K27" t="n">
+        <v>200</v>
+      </c>
+      <c r="L27" t="n">
         <v>0.01233773058711022</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
+        <v>0.0006605443847875641</v>
+      </c>
+      <c r="N27" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M27" t="n">
-        <v>200</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
+        <v>200</v>
+      </c>
+      <c r="P27" t="n">
         <v>36.05769230769231</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
+        <v>1.930477085236998</v>
+      </c>
+      <c r="R27" t="n">
         <v>198.6114841856233</v>
       </c>
-      <c r="P27" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
+        <v>200</v>
+      </c>
+      <c r="T27" t="n">
         <v>36.05769230769231</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
+        <v>1.930477085236998</v>
+      </c>
+      <c r="V27" t="n">
         <v>199.779644487174</v>
       </c>
-      <c r="S27" t="n">
-        <v>200</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
+        <v>200</v>
+      </c>
+      <c r="X27" t="n">
         <v>0.8885456236906393</v>
       </c>
-      <c r="U27" t="n">
+      <c r="Y27" t="n">
+        <v>0.04757145718270111</v>
+      </c>
+      <c r="Z27" t="n">
         <v>192.722098187243</v>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2847,56 +3252,71 @@
         <v>0.0143524143490416</v>
       </c>
       <c r="I28" t="n">
+        <v>0.00073484361467093</v>
+      </c>
+      <c r="J28" t="n">
         <v>127.1718885128103</v>
       </c>
-      <c r="J28" t="n">
-        <v>200</v>
-      </c>
       <c r="K28" t="n">
+        <v>200</v>
+      </c>
+      <c r="L28" t="n">
         <v>0.2261063548282595</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0.01157664536720688</v>
+      </c>
+      <c r="N28" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M28" t="n">
-        <v>200</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
+        <v>200</v>
+      </c>
+      <c r="P28" t="n">
         <v>36.80769230769231</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
+        <v>1.884553846153846</v>
+      </c>
+      <c r="R28" t="n">
         <v>197.4940180993655</v>
       </c>
-      <c r="P28" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
+        <v>200</v>
+      </c>
+      <c r="T28" t="n">
         <v>36.80769230769231</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
+        <v>1.884553846153846</v>
+      </c>
+      <c r="V28" t="n">
         <v>199.5411797194807</v>
       </c>
-      <c r="S28" t="n">
-        <v>200</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="W28" t="n">
+        <v>200</v>
+      </c>
+      <c r="X28" t="n">
         <v>0.8966237872700616</v>
       </c>
-      <c r="U28" t="n">
+      <c r="Y28" t="n">
+        <v>0.04590713790822715</v>
+      </c>
+      <c r="Z28" t="n">
         <v>184.9627687949149</v>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -2934,56 +3354,71 @@
         <v>0.165481408153559</v>
       </c>
       <c r="I29" t="n">
+        <v>0.01967089547144833</v>
+      </c>
+      <c r="J29" t="n">
         <v>191.5075017030775</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>199.6842069526952</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>0.06251244142477602</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0.007430899426422113</v>
+      </c>
+      <c r="N29" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M29" t="n">
-        <v>200</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
+        <v>200</v>
+      </c>
+      <c r="P29" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
+        <v>0.04571951080123443</v>
+      </c>
+      <c r="R29" t="n">
         <v>198.5277121400952</v>
       </c>
-      <c r="P29" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
+        <v>200</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.3846153846153846</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
+        <v>0.04571951080123443</v>
+      </c>
+      <c r="V29" t="n">
         <v>199.9388941772115</v>
       </c>
-      <c r="S29" t="n">
+      <c r="W29" t="n">
         <v>199.999964251257</v>
       </c>
-      <c r="T29" t="n">
+      <c r="X29" t="n">
         <v>0.06751301021021251</v>
       </c>
-      <c r="U29" t="n">
+      <c r="Y29" t="n">
+        <v>0.008025320678777119</v>
+      </c>
+      <c r="Z29" t="n">
         <v>192.5799615112869</v>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -3021,56 +3456,71 @@
         <v>0.1198547547246342</v>
       </c>
       <c r="I30" t="n">
+        <v>0.02464879274542605</v>
+      </c>
+      <c r="J30" t="n">
         <v>196.0386411854094</v>
       </c>
-      <c r="J30" t="n">
-        <v>200</v>
-      </c>
       <c r="K30" t="n">
+        <v>200</v>
+      </c>
+      <c r="L30" t="n">
         <v>0.006022060414032323</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
+        <v>0.001238470008027213</v>
+      </c>
+      <c r="N30" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M30" t="n">
-        <v>200</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
+        <v>200</v>
+      </c>
+      <c r="P30" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
+        <v>0.04745896776745107</v>
+      </c>
+      <c r="R30" t="n">
         <v>198.9477887234591</v>
       </c>
-      <c r="P30" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
+        <v>200</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
+        <v>0.04745896776745107</v>
+      </c>
+      <c r="V30" t="n">
         <v>199.7754683359127</v>
       </c>
-      <c r="S30" t="n">
-        <v>200</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="W30" t="n">
+        <v>200</v>
+      </c>
+      <c r="X30" t="n">
         <v>0.01909230307143704</v>
       </c>
-      <c r="U30" t="n">
+      <c r="Y30" t="n">
+        <v>0.003926437649652862</v>
+      </c>
+      <c r="Z30" t="n">
         <v>198.9226798174336</v>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -3108,56 +3558,71 @@
         <v>0.1596547285707901</v>
       </c>
       <c r="I31" t="n">
+        <v>0.02395195177808384</v>
+      </c>
+      <c r="J31" t="n">
         <v>194.2466814459454</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>199.8983878715963</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>0.04410647872176808</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
+        <v>0.006617005715408244</v>
+      </c>
+      <c r="N31" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M31" t="n">
-        <v>200</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
+        <v>200</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
+        <v>0.02308052940964333</v>
+      </c>
+      <c r="R31" t="n">
         <v>199.0633013569061</v>
       </c>
-      <c r="P31" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
+        <v>200</v>
+      </c>
+      <c r="T31" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
+        <v>0.02308052940964333</v>
+      </c>
+      <c r="V31" t="n">
         <v>199.9196066031173</v>
       </c>
-      <c r="S31" t="n">
+      <c r="W31" t="n">
         <v>199.9999999923865</v>
       </c>
-      <c r="T31" t="n">
+      <c r="X31" t="n">
         <v>0.05052019072418547</v>
       </c>
-      <c r="U31" t="n">
+      <c r="Y31" t="n">
+        <v>0.007579212860637294</v>
+      </c>
+      <c r="Z31" t="n">
         <v>194.1597056483905</v>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -3195,58 +3660,73 @@
         <v>0.9088263617437347</v>
       </c>
       <c r="I32" t="n">
+        <v>0.04065200388006641</v>
+      </c>
+      <c r="J32" t="n">
         <v>164.6748490827784</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>159.6862497058564</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>1.377016198743123</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
+        <v>0.06159423869133344</v>
+      </c>
+      <c r="N32" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>157.5789375132153</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>12.25</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="R32" t="n">
         <v>170.2678863343212</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>157.5789375132153</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="T32" t="n">
         <v>12.25</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="V32" t="n">
         <v>195.3761640213164</v>
       </c>
-      <c r="S32" t="n">
+      <c r="W32" t="n">
         <v>144.7850261687545</v>
       </c>
-      <c r="T32" t="n">
+      <c r="X32" t="n">
         <v>5.942491840375366</v>
       </c>
-      <c r="U32" t="n">
+      <c r="Y32" t="n">
+        <v>0.2658089724517916</v>
+      </c>
+      <c r="Z32" t="n">
         <v>173.3959783787531</v>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X32" t="n">
+      <c r="AC32" t="n">
         <v>136.4384553168091</v>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AD32" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=136.44% sobre 26 sem</t>
         </is>
@@ -3284,58 +3764,73 @@
         <v>0.2855099710301251</v>
       </c>
       <c r="I33" t="n">
+        <v>0.01575499064142784</v>
+      </c>
+      <c r="J33" t="n">
         <v>170.4028696730483</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>172.4959078110981</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>0.6838980996468932</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
+        <v>0.03773881563838694</v>
+      </c>
+      <c r="N33" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>181.6029900332226</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>4.807692307692307</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
+        <v>0.2652977303779166</v>
+      </c>
+      <c r="R33" t="n">
         <v>180.7526372107734</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>181.6029900332226</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
         <v>4.807692307692307</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
+        <v>0.2652977303779166</v>
+      </c>
+      <c r="V33" t="n">
         <v>196.5601753860276</v>
       </c>
-      <c r="S33" t="n">
+      <c r="W33" t="n">
         <v>172.0138066156621</v>
       </c>
-      <c r="T33" t="n">
+      <c r="X33" t="n">
         <v>1.228747777109315</v>
       </c>
-      <c r="U33" t="n">
+      <c r="Y33" t="n">
+        <v>0.06780467126659438</v>
+      </c>
+      <c r="Z33" t="n">
         <v>182.3083787234438</v>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X33" t="n">
+      <c r="AC33" t="n">
         <v>139.8117872004429</v>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AD33" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=139.81% sobre 26 sem</t>
         </is>
@@ -3373,58 +3868,73 @@
         <v>0.836651906100444</v>
       </c>
       <c r="I34" t="n">
+        <v>0.0386388526413829</v>
+      </c>
+      <c r="J34" t="n">
         <v>169.6571057340244</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>169.7651776711998</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4.2457171071596</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
+        <v>0.1960787233787086</v>
+      </c>
+      <c r="N34" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>167.6757509073452</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>7.942307692307693</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
+        <v>0.3667972956470575</v>
+      </c>
+      <c r="R34" t="n">
         <v>184.4689912561869</v>
       </c>
-      <c r="P34" t="n">
+      <c r="S34" t="n">
         <v>167.6757509073452</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="T34" t="n">
         <v>7.942307692307693</v>
       </c>
-      <c r="R34" t="n">
+      <c r="U34" t="n">
+        <v>0.3667972956470575</v>
+      </c>
+      <c r="V34" t="n">
         <v>195.2398047728465</v>
       </c>
-      <c r="S34" t="n">
+      <c r="W34" t="n">
         <v>153.4535494003401</v>
       </c>
-      <c r="T34" t="n">
+      <c r="X34" t="n">
         <v>2.609194376670224</v>
       </c>
-      <c r="U34" t="n">
+      <c r="Y34" t="n">
+        <v>0.1204996681389049</v>
+      </c>
+      <c r="Z34" t="n">
         <v>176.7243686471345</v>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X34" t="n">
+      <c r="AC34" t="n">
         <v>150.568521206798</v>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AD34" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=150.57% sobre 26 sem</t>
         </is>
@@ -3462,58 +3972,73 @@
         <v>0.6288707011427206</v>
       </c>
       <c r="I35" t="n">
+        <v>0.01052008073426058</v>
+      </c>
+      <c r="J35" t="n">
         <v>48.55849570822402</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>132.6935847973162</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>1.41605812453869</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
+        <v>0.0236885670893607</v>
+      </c>
+      <c r="N35" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>191.1576938126877</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>32.21614184248983</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
+        <v>0.5389286104656147</v>
+      </c>
+      <c r="R35" t="n">
         <v>189.0070522024178</v>
       </c>
-      <c r="P35" t="n">
+      <c r="S35" t="n">
         <v>198.1187828016984</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="T35" t="n">
         <v>173.9018700236352</v>
       </c>
-      <c r="R35" t="n">
+      <c r="U35" t="n">
+        <v>2.909122191832468</v>
+      </c>
+      <c r="V35" t="n">
         <v>185.853149170162</v>
       </c>
-      <c r="S35" t="n">
+      <c r="W35" t="n">
         <v>142.2217601484261</v>
       </c>
-      <c r="T35" t="n">
+      <c r="X35" t="n">
         <v>3.827236981373604</v>
       </c>
-      <c r="U35" t="n">
+      <c r="Y35" t="n">
+        <v>0.06402403858223395</v>
+      </c>
+      <c r="Z35" t="n">
         <v>110.5529101365675</v>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X35" t="n">
+      <c r="AC35" t="n">
         <v>120.0269946697649</v>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AD35" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=120.03% sobre 26 sem</t>
         </is>
@@ -3551,56 +4076,71 @@
         <v>0.4159725096872607</v>
       </c>
       <c r="I36" t="n">
+        <v>0.01052096135788203</v>
+      </c>
+      <c r="J36" t="n">
         <v>58.86670393327421</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>168.9852897137726</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>0.8438138868550287</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
+        <v>0.02134211538046231</v>
+      </c>
+      <c r="N36" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>187.7653454830295</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>10.03105728252018</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
+        <v>0.2537099533991825</v>
+      </c>
+      <c r="R36" t="n">
         <v>185.6171222178218</v>
       </c>
-      <c r="P36" t="n">
+      <c r="S36" t="n">
         <v>198.364052952299</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="T36" t="n">
         <v>84.7415070782278</v>
       </c>
-      <c r="R36" t="n">
+      <c r="U36" t="n">
+        <v>2.143319812285243</v>
+      </c>
+      <c r="V36" t="n">
         <v>187.2910306593169</v>
       </c>
-      <c r="S36" t="n">
+      <c r="W36" t="n">
         <v>164.2275075564714</v>
       </c>
-      <c r="T36" t="n">
+      <c r="X36" t="n">
         <v>2.165195990873503</v>
       </c>
-      <c r="U36" t="n">
+      <c r="Y36" t="n">
+        <v>0.05476309809354418</v>
+      </c>
+      <c r="Z36" t="n">
         <v>118.8153464644226</v>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
@@ -3638,58 +4178,73 @@
         <v>0.5332963051073031</v>
       </c>
       <c r="I37" t="n">
+        <v>0.0127211940092685</v>
+      </c>
+      <c r="J37" t="n">
         <v>60.32903496111531</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>168.8038084510468</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>1.191727828613862</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
+        <v>0.02842735036574252</v>
+      </c>
+      <c r="N37" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>184.8161119307371</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>10.19318387103714</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
+        <v>0.243147136692649</v>
+      </c>
+      <c r="R37" t="n">
         <v>181.1462848359585</v>
       </c>
-      <c r="P37" t="n">
+      <c r="S37" t="n">
         <v>197.9055351879389</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="T37" t="n">
         <v>90.56059711647093</v>
       </c>
-      <c r="R37" t="n">
+      <c r="U37" t="n">
+        <v>2.160222965133857</v>
+      </c>
+      <c r="V37" t="n">
         <v>185.3862117422507</v>
       </c>
-      <c r="S37" t="n">
+      <c r="W37" t="n">
         <v>158.2676147173262</v>
       </c>
-      <c r="T37" t="n">
+      <c r="X37" t="n">
         <v>2.210830069810609</v>
       </c>
-      <c r="U37" t="n">
+      <c r="Y37" t="n">
+        <v>0.05273690811326089</v>
+      </c>
+      <c r="Z37" t="n">
         <v>110.8838400280787</v>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X37" t="n">
+      <c r="AC37" t="n">
         <v>161.9002846937967</v>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=161.90% sobre 26 sem</t>
         </is>
@@ -3727,56 +4282,71 @@
         <v>0.5553684594761084</v>
       </c>
       <c r="I38" t="n">
+        <v>0.03093974704602275</v>
+      </c>
+      <c r="J38" t="n">
         <v>164.4263244057969</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>191.4574463290842</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>0.8441273509148057</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0.04702659336572734</v>
+      </c>
+      <c r="N38" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>186.9731760776537</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>17.11538461538462</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
+        <v>0.9535033211913436</v>
+      </c>
+      <c r="R38" t="n">
         <v>190.3086393348001</v>
       </c>
-      <c r="P38" t="n">
+      <c r="S38" t="n">
         <v>186.9731760776537</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="T38" t="n">
         <v>17.11538461538462</v>
       </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
+        <v>0.9535033211913436</v>
+      </c>
+      <c r="V38" t="n">
         <v>199.036270909302</v>
       </c>
-      <c r="S38" t="n">
+      <c r="W38" t="n">
         <v>186.3039188319287</v>
       </c>
-      <c r="T38" t="n">
+      <c r="X38" t="n">
         <v>0.9283347032724557</v>
       </c>
-      <c r="U38" t="n">
+      <c r="Y38" t="n">
+        <v>0.05171781076726773</v>
+      </c>
+      <c r="Z38" t="n">
         <v>129.2920232398837</v>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr">
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
         </is>
@@ -3814,56 +4384,71 @@
         <v>0.1704836994124694</v>
       </c>
       <c r="I39" t="n">
+        <v>0.009255986394976282</v>
+      </c>
+      <c r="J39" t="n">
         <v>170.2041702191862</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>199.3761363235489</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>0.09436105974426881</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
+        <v>0.005123097916214119</v>
+      </c>
+      <c r="N39" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>187.2</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>7.25</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
+        <v>0.3936206311503224</v>
+      </c>
+      <c r="R39" t="n">
         <v>190.9487472471646</v>
       </c>
-      <c r="P39" t="n">
+      <c r="S39" t="n">
         <v>187.2</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="T39" t="n">
         <v>7.25</v>
       </c>
-      <c r="R39" t="n">
+      <c r="U39" t="n">
+        <v>0.3936206311503224</v>
+      </c>
+      <c r="V39" t="n">
         <v>199.0467638312102</v>
       </c>
-      <c r="S39" t="n">
+      <c r="W39" t="n">
         <v>195.7473889678286</v>
       </c>
-      <c r="T39" t="n">
+      <c r="X39" t="n">
         <v>0.4596834347927579</v>
       </c>
-      <c r="U39" t="n">
+      <c r="Y39" t="n">
+        <v>0.02495736327344461</v>
+      </c>
+      <c r="Z39" t="n">
         <v>146.152525200624</v>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr">
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -3901,56 +4486,71 @@
         <v>0.2682565987196245</v>
       </c>
       <c r="I40" t="n">
+        <v>0.01032749176976418</v>
+      </c>
+      <c r="J40" t="n">
         <v>165.7522199768573</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>199.4838010220985</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>0.1245454299554858</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
+        <v>0.004794819247564419</v>
+      </c>
+      <c r="N40" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>189.6153846153846</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>10.21153846153846</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
+        <v>0.3931294884134153</v>
+      </c>
+      <c r="R40" t="n">
         <v>189.6576328974018</v>
       </c>
-      <c r="P40" t="n">
+      <c r="S40" t="n">
         <v>189.6153846153846</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="T40" t="n">
         <v>10.21153846153846</v>
       </c>
-      <c r="R40" t="n">
+      <c r="U40" t="n">
+        <v>0.3931294884134153</v>
+      </c>
+      <c r="V40" t="n">
         <v>198.942356787496</v>
       </c>
-      <c r="S40" t="n">
+      <c r="W40" t="n">
         <v>191.6029876294868</v>
       </c>
-      <c r="T40" t="n">
+      <c r="X40" t="n">
         <v>0.4760050468291805</v>
       </c>
-      <c r="U40" t="n">
+      <c r="Y40" t="n">
+        <v>0.01832550709640733</v>
+      </c>
+      <c r="Z40" t="n">
         <v>124.2002492905602</v>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr">
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
@@ -3988,58 +4588,73 @@
         <v>2.212301818876929</v>
       </c>
       <c r="I41" t="n">
+        <v>0.01117130204731844</v>
+      </c>
+      <c r="J41" t="n">
         <v>127.4617865350128</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>81.89642293849408</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>2.227550347391977</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
+        <v>0.01124830144964467</v>
+      </c>
+      <c r="N41" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>184.0199928479197</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>90.84615384615384</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
+        <v>0.4587393165764976</v>
+      </c>
+      <c r="R41" t="n">
         <v>183.1586103963582</v>
       </c>
-      <c r="P41" t="n">
+      <c r="S41" t="n">
         <v>184.0199928479197</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="T41" t="n">
         <v>90.84615384615384</v>
       </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
+        <v>0.4587393165764976</v>
+      </c>
+      <c r="V41" t="n">
         <v>198.8825072752037</v>
       </c>
-      <c r="S41" t="n">
+      <c r="W41" t="n">
         <v>72.68033743905205</v>
       </c>
-      <c r="T41" t="n">
+      <c r="X41" t="n">
         <v>2.739741236221613</v>
       </c>
-      <c r="U41" t="n">
+      <c r="Y41" t="n">
+        <v>0.0138346750972987</v>
+      </c>
+      <c r="Z41" t="n">
         <v>124.7888620818299</v>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X41" t="n">
+      <c r="AC41" t="n">
         <v>72.68033743905205</v>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=72.68% sobre 26 sem</t>
         </is>
@@ -4077,58 +4692,73 @@
         <v>1.305219418515306</v>
       </c>
       <c r="I42" t="n">
+        <v>0.01343682325070448</v>
+      </c>
+      <c r="J42" t="n">
         <v>139.5371944473096</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>157.4561336663125</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1.649802586809004</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
+        <v>0.01698419855163046</v>
+      </c>
+      <c r="N42" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>182.4002878985824</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>40.15384615384615</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
+        <v>0.4133712124961642</v>
+      </c>
+      <c r="R42" t="n">
         <v>178.6003071053324</v>
       </c>
-      <c r="P42" t="n">
+      <c r="S42" t="n">
         <v>182.4002878985824</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="T42" t="n">
         <v>40.15384615384615</v>
       </c>
-      <c r="R42" t="n">
+      <c r="U42" t="n">
+        <v>0.4133712124961642</v>
+      </c>
+      <c r="V42" t="n">
         <v>198.6803521667581</v>
       </c>
-      <c r="S42" t="n">
+      <c r="W42" t="n">
         <v>89.21287175816121</v>
       </c>
-      <c r="T42" t="n">
+      <c r="X42" t="n">
         <v>1.067278521000874</v>
       </c>
-      <c r="U42" t="n">
+      <c r="Y42" t="n">
+        <v>0.01098729657445244</v>
+      </c>
+      <c r="Z42" t="n">
         <v>125.9010082864909</v>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X42" t="n">
+      <c r="AC42" t="n">
         <v>89.21287175816121</v>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="AD42" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=89.21% sobre 26 sem</t>
         </is>
@@ -4166,58 +4796,73 @@
         <v>1.385679333576383</v>
       </c>
       <c r="I43" t="n">
+        <v>0.01040470673075164</v>
+      </c>
+      <c r="J43" t="n">
         <v>137.8269504556986</v>
       </c>
-      <c r="J43" t="n">
+      <c r="K43" t="n">
         <v>125.130614858072</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1.515851310470872</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
+        <v>0.01138213434429169</v>
+      </c>
+      <c r="N43" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>186.4977222744996</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>51.96153846153846</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
+        <v>0.3901657157400171</v>
+      </c>
+      <c r="R43" t="n">
         <v>183.3878591635464</v>
       </c>
-      <c r="P43" t="n">
+      <c r="S43" t="n">
         <v>186.4977222744996</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="T43" t="n">
         <v>51.96153846153846</v>
       </c>
-      <c r="R43" t="n">
+      <c r="U43" t="n">
+        <v>0.3901657157400171</v>
+      </c>
+      <c r="V43" t="n">
         <v>198.9631246433146</v>
       </c>
-      <c r="S43" t="n">
+      <c r="W43" t="n">
         <v>82.34334736233528</v>
       </c>
-      <c r="T43" t="n">
+      <c r="X43" t="n">
         <v>1.602581000227404</v>
       </c>
-      <c r="U43" t="n">
+      <c r="Y43" t="n">
+        <v>0.01203336509075649</v>
+      </c>
+      <c r="Z43" t="n">
         <v>126.6160396504699</v>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X43" t="n">
+      <c r="AC43" t="n">
         <v>86.37455469393578</v>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="AD43" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=86.37% sobre 26 sem</t>
         </is>
@@ -4255,58 +4900,73 @@
         <v>3.857363668221427</v>
       </c>
       <c r="I44" t="n">
+        <v>0.08070853758538359</v>
+      </c>
+      <c r="J44" t="n">
         <v>101.902133963665</v>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>100.4112462101342</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1.70774239004787</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
+        <v>0.03573150024946505</v>
+      </c>
+      <c r="N44" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>186.7796297381574</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>89.76791078069188</v>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
+        <v>1.878235350452556</v>
+      </c>
+      <c r="R44" t="n">
         <v>175.3243009167544</v>
       </c>
-      <c r="P44" t="n">
+      <c r="S44" t="n">
         <v>187.0172162311941</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="T44" t="n">
         <v>101.9423076923077</v>
       </c>
-      <c r="R44" t="n">
+      <c r="U44" t="n">
+        <v>2.132963152970999</v>
+      </c>
+      <c r="V44" t="n">
         <v>196.0447922196767</v>
       </c>
-      <c r="S44" t="n">
+      <c r="W44" t="n">
         <v>101.2048277356274</v>
       </c>
-      <c r="T44" t="n">
+      <c r="X44" t="n">
         <v>8.886579865047516</v>
       </c>
-      <c r="U44" t="n">
+      <c r="Y44" t="n">
+        <v>0.1859360243765663</v>
+      </c>
+      <c r="Z44" t="n">
         <v>121.0188473841644</v>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X44" t="n">
+      <c r="AC44" t="n">
         <v>100.4112462101342</v>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="AD44" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=100.41% sobre 26 sem</t>
         </is>
@@ -4344,58 +5004,73 @@
         <v>3.570361775059859</v>
       </c>
       <c r="I45" t="n">
+        <v>0.1216607143029661</v>
+      </c>
+      <c r="J45" t="n">
         <v>133.2410714461222</v>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>129.9289777485386</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>1.389499155522514</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
+        <v>0.04734743155864174</v>
+      </c>
+      <c r="N45" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>184.8553422205679</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>44.86538461538461</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
+        <v>1.528795983060705</v>
+      </c>
+      <c r="R45" t="n">
         <v>177.4357058560748</v>
       </c>
-      <c r="P45" t="n">
+      <c r="S45" t="n">
         <v>184.8553422205679</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="T45" t="n">
         <v>44.86538461538461</v>
       </c>
-      <c r="R45" t="n">
+      <c r="U45" t="n">
+        <v>1.528795983060705</v>
+      </c>
+      <c r="V45" t="n">
         <v>195.8311934408034</v>
       </c>
-      <c r="S45" t="n">
+      <c r="W45" t="n">
         <v>108.7931937538279</v>
       </c>
-      <c r="T45" t="n">
+      <c r="X45" t="n">
         <v>3.422300329439217</v>
       </c>
-      <c r="U45" t="n">
+      <c r="Y45" t="n">
+        <v>0.1166154941348684</v>
+      </c>
+      <c r="Z45" t="n">
         <v>112.5504951429215</v>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X45" t="n">
+      <c r="AC45" t="n">
         <v>108.7931937538279</v>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="AD45" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=108.79% sobre 26 sem</t>
         </is>
@@ -4433,58 +5108,73 @@
         <v>2.989627752045402</v>
       </c>
       <c r="I46" t="n">
+        <v>0.07982318570333988</v>
+      </c>
+      <c r="J46" t="n">
         <v>129.1401202444324</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>142.0150170963277</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>1.064136701870199</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
+        <v>0.02841249433445671</v>
+      </c>
+      <c r="N46" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>188.2191225161923</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>50.70255772644789</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
+        <v>1.353760406546794</v>
+      </c>
+      <c r="R46" t="n">
         <v>173.6962919474645</v>
       </c>
-      <c r="P46" t="n">
+      <c r="S46" t="n">
         <v>188.4486636457789</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="T46" t="n">
         <v>57.30769230769231</v>
       </c>
-      <c r="R46" t="n">
+      <c r="U46" t="n">
+        <v>1.530117775424409</v>
+      </c>
+      <c r="V46" t="n">
         <v>196.1388328305384</v>
       </c>
-      <c r="S46" t="n">
+      <c r="W46" t="n">
         <v>130.2447330072169</v>
       </c>
-      <c r="T46" t="n">
+      <c r="X46" t="n">
         <v>5.535956264534023</v>
       </c>
-      <c r="U46" t="n">
+      <c r="Y46" t="n">
+        <v>0.1478102632165947</v>
+      </c>
+      <c r="Z46" t="n">
         <v>125.7491255686458</v>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X46" t="n">
+      <c r="AC46" t="n">
         <v>134.4608149355389</v>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="AD46" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=134.46% sobre 26 sem</t>
         </is>
@@ -4522,56 +5212,71 @@
         <v>0.3503353536484817</v>
       </c>
       <c r="I47" t="n">
+        <v>0.006384243346669371</v>
+      </c>
+      <c r="J47" t="n">
         <v>52.02932925897922</v>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>184.9000553356195</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1.571310252876007</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
+        <v>0.02863435540548532</v>
+      </c>
+      <c r="N47" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>197.3418108488528</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>33.3350964253559</v>
       </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
+        <v>0.6074732833777841</v>
+      </c>
+      <c r="R47" t="n">
         <v>176.1972572849119</v>
       </c>
-      <c r="P47" t="n">
+      <c r="S47" t="n">
         <v>198.6941826951429</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="T47" t="n">
         <v>78.65883520826061</v>
       </c>
-      <c r="R47" t="n">
+      <c r="U47" t="n">
+        <v>1.433418409262152</v>
+      </c>
+      <c r="V47" t="n">
         <v>193.8459595711977</v>
       </c>
-      <c r="S47" t="n">
+      <c r="W47" t="n">
         <v>184.0090106039409</v>
       </c>
-      <c r="T47" t="n">
+      <c r="X47" t="n">
         <v>3.428651107244254</v>
       </c>
-      <c r="U47" t="n">
+      <c r="Y47" t="n">
+        <v>0.06248111357164927</v>
+      </c>
+      <c r="Z47" t="n">
         <v>130.8486591703272</v>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
-      <c r="Y47" t="inlineStr">
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
@@ -4609,56 +5314,71 @@
         <v>0.1674436848912853</v>
       </c>
       <c r="I48" t="n">
+        <v>0.006083330967894107</v>
+      </c>
+      <c r="J48" t="n">
         <v>75.82494372432545</v>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>193.5901427785547</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>0.6733722969208772</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
+        <v>0.02446402531955957</v>
+      </c>
+      <c r="N48" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>196.7233124918204</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>14.820582969364</v>
       </c>
-      <c r="O48" t="n">
+      <c r="Q48" t="n">
+        <v>0.5384407981603634</v>
+      </c>
+      <c r="R48" t="n">
         <v>183.163735304357</v>
       </c>
-      <c r="P48" t="n">
+      <c r="S48" t="n">
         <v>198.022320718163</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="T48" t="n">
         <v>33.60628094632519</v>
       </c>
-      <c r="R48" t="n">
+      <c r="U48" t="n">
+        <v>1.220936637468672</v>
+      </c>
+      <c r="V48" t="n">
         <v>192.3368460426438</v>
       </c>
-      <c r="S48" t="n">
+      <c r="W48" t="n">
         <v>191.8157157323924</v>
       </c>
-      <c r="T48" t="n">
+      <c r="X48" t="n">
         <v>3.127699672131663</v>
       </c>
-      <c r="U48" t="n">
+      <c r="Y48" t="n">
+        <v>0.1136312324116862</v>
+      </c>
+      <c r="Z48" t="n">
         <v>148.2729860112375</v>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
-      <c r="Y48" t="inlineStr">
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -4696,56 +5416,71 @@
         <v>0.1721830901847086</v>
       </c>
       <c r="I49" t="n">
+        <v>0.004913375143490882</v>
+      </c>
+      <c r="J49" t="n">
         <v>67.54170898302603</v>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>188.5364639501912</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>1.241250903265522</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
+        <v>0.03542003647627671</v>
+      </c>
+      <c r="N49" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>197.9461764628585</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>18.18137305728497</v>
       </c>
-      <c r="O49" t="n">
+      <c r="Q49" t="n">
+        <v>0.5188192775397886</v>
+      </c>
+      <c r="R49" t="n">
         <v>179.6516960231333</v>
       </c>
-      <c r="P49" t="n">
+      <c r="S49" t="n">
         <v>199.2925955034458</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="T49" t="n">
         <v>40.95455768647587</v>
       </c>
-      <c r="R49" t="n">
+      <c r="U49" t="n">
+        <v>1.16866938288499</v>
+      </c>
+      <c r="V49" t="n">
         <v>193.5695579772771</v>
       </c>
-      <c r="S49" t="n">
+      <c r="W49" t="n">
         <v>188.78130964667</v>
       </c>
-      <c r="T49" t="n">
+      <c r="X49" t="n">
         <v>1.811429776081504</v>
       </c>
-      <c r="U49" t="n">
+      <c r="Y49" t="n">
+        <v>0.05169052330533985</v>
+      </c>
+      <c r="Z49" t="n">
         <v>141.2583029624075</v>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr">
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -4783,58 +5518,73 @@
         <v>5.208788529216767</v>
       </c>
       <c r="I50" t="n">
+        <v>0.2262231717357988</v>
+      </c>
+      <c r="J50" t="n">
         <v>162.6912701840232</v>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>193.8662174422948</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>0.4434513820849675</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
+        <v>0.01925956056829392</v>
+      </c>
+      <c r="N50" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>191.0040394407015</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>12.53571605682373</v>
       </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
+        <v>0.5444393510021165</v>
+      </c>
+      <c r="R50" t="n">
         <v>176.9763205357646</v>
       </c>
-      <c r="P50" t="n">
+      <c r="S50" t="n">
         <v>192.412989113812</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="T50" t="n">
         <v>17.22534489261614</v>
       </c>
-      <c r="R50" t="n">
+      <c r="U50" t="n">
+        <v>0.7481148704719277</v>
+      </c>
+      <c r="V50" t="n">
         <v>160.5521309789579</v>
       </c>
-      <c r="S50" t="n">
+      <c r="W50" t="n">
         <v>191.1162051189995</v>
       </c>
-      <c r="T50" t="n">
+      <c r="X50" t="n">
         <v>24.59129532093463</v>
       </c>
-      <c r="U50" t="n">
+      <c r="Y50" t="n">
+        <v>1.068025855415185</v>
+      </c>
+      <c r="Z50" t="n">
         <v>135.4400555181058</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X50" t="n">
+      <c r="AC50" t="n">
         <v>193.8662174422948</v>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="AD50" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=193.87% sobre 26 sem</t>
         </is>
@@ -4872,56 +5622,71 @@
         <v>1.903489031688147</v>
       </c>
       <c r="I51" t="n">
+        <v>0.1592461412131261</v>
+      </c>
+      <c r="J51" t="n">
         <v>169.9274838481079</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>178.9137103796107</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>0.2427665114409492</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
+        <v>0.02030987808133431</v>
+      </c>
+      <c r="N51" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>196.1122293407287</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>17.6295960754129</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
+        <v>1.474894312191406</v>
+      </c>
+      <c r="R51" t="n">
         <v>191.5443980495646</v>
       </c>
-      <c r="P51" t="n">
+      <c r="S51" t="n">
         <v>193.2719749453459</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="T51" t="n">
         <v>6.58219201990204</v>
       </c>
-      <c r="R51" t="n">
+      <c r="U51" t="n">
+        <v>0.5506670448022621</v>
+      </c>
+      <c r="V51" t="n">
         <v>165.5121650610737</v>
       </c>
-      <c r="S51" t="n">
+      <c r="W51" t="n">
         <v>190.5740611048891</v>
       </c>
-      <c r="T51" t="n">
+      <c r="X51" t="n">
         <v>11.55415004784484</v>
       </c>
-      <c r="U51" t="n">
+      <c r="Y51" t="n">
+        <v>0.9666217033491109</v>
+      </c>
+      <c r="Z51" t="n">
         <v>151.1230387281904</v>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="AA51" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
-      <c r="Y51" t="inlineStr">
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -4959,56 +5724,71 @@
         <v>2.98718902787148</v>
       </c>
       <c r="I52" t="n">
+        <v>0.1855036850220985</v>
+      </c>
+      <c r="J52" t="n">
         <v>174.432365021141</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>197.6004713705168</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>0.2735075320235206</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
+        <v>0.01698474873811888</v>
+      </c>
+      <c r="N52" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>196.3981217470596</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>26.6248126355684</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
+        <v>1.653394147755072</v>
+      </c>
+      <c r="R52" t="n">
         <v>190.0491824654319</v>
       </c>
-      <c r="P52" t="n">
+      <c r="S52" t="n">
         <v>190.2706087569731</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="T52" t="n">
         <v>9.21501289688549</v>
       </c>
-      <c r="R52" t="n">
+      <c r="U52" t="n">
+        <v>0.572249976131061</v>
+      </c>
+      <c r="V52" t="n">
         <v>154.7555469695623</v>
       </c>
-      <c r="S52" t="n">
+      <c r="W52" t="n">
         <v>191.7742099589465</v>
       </c>
-      <c r="T52" t="n">
+      <c r="X52" t="n">
         <v>20.05581811117946</v>
       </c>
-      <c r="U52" t="n">
+      <c r="Y52" t="n">
+        <v>1.245461245017937</v>
+      </c>
+      <c r="Z52" t="n">
         <v>133.8716916594558</v>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="AA52" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr">
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
@@ -5046,58 +5826,73 @@
         <v>26.06827811607847</v>
       </c>
       <c r="I53" t="n">
+        <v>0.02933397449545533</v>
+      </c>
+      <c r="J53" t="n">
         <v>35.23746831954708</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>21.82929250468235</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>25.13835366588721</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
+        <v>0.02828755401524011</v>
+      </c>
+      <c r="N53" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>164.5356140391471</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>1223.115384615385</v>
       </c>
-      <c r="O53" t="n">
+      <c r="Q53" t="n">
+        <v>1.376340828402367</v>
+      </c>
+      <c r="R53" t="n">
         <v>169.178554981669</v>
       </c>
-      <c r="P53" t="n">
+      <c r="S53" t="n">
         <v>164.5356140391471</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="T53" t="n">
         <v>1223.115384615385</v>
       </c>
-      <c r="R53" t="n">
+      <c r="U53" t="n">
+        <v>1.376340828402367</v>
+      </c>
+      <c r="V53" t="n">
         <v>188.2648408233968</v>
       </c>
-      <c r="S53" t="n">
+      <c r="W53" t="n">
         <v>52.86613593151077</v>
       </c>
-      <c r="T53" t="n">
+      <c r="X53" t="n">
         <v>141.2650529879882</v>
       </c>
-      <c r="U53" t="n">
+      <c r="Y53" t="n">
+        <v>0.1589619936919779</v>
+      </c>
+      <c r="Z53" t="n">
         <v>92.2349408254034</v>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X53" t="n">
+      <c r="AC53" t="n">
         <v>20.09590459559316</v>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=20.10% sobre 26 sem</t>
         </is>
@@ -5135,58 +5930,73 @@
         <v>10.69622688969862</v>
       </c>
       <c r="I54" t="n">
+        <v>0.02115734280744945</v>
+      </c>
+      <c r="J54" t="n">
         <v>38.4591918317379</v>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>24.99748527673886</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>16.11825956854353</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
+        <v>0.03188222787977308</v>
+      </c>
+      <c r="N54" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>164.4694964886822</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>556.8269230769231</v>
       </c>
-      <c r="O54" t="n">
+      <c r="Q54" t="n">
+        <v>1.101414378868668</v>
+      </c>
+      <c r="R54" t="n">
         <v>163.7593826553296</v>
       </c>
-      <c r="P54" t="n">
+      <c r="S54" t="n">
         <v>164.4694964886822</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="T54" t="n">
         <v>556.8269230769231</v>
       </c>
-      <c r="R54" t="n">
+      <c r="U54" t="n">
+        <v>1.101414378868668</v>
+      </c>
+      <c r="V54" t="n">
         <v>187.9362468841497</v>
       </c>
-      <c r="S54" t="n">
+      <c r="W54" t="n">
         <v>52.7013059681811</v>
       </c>
-      <c r="T54" t="n">
+      <c r="X54" t="n">
         <v>63.00118284664776</v>
       </c>
-      <c r="U54" t="n">
+      <c r="Y54" t="n">
+        <v>0.1246175531340929</v>
+      </c>
+      <c r="Z54" t="n">
         <v>91.67135817890519</v>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X54" t="n">
+      <c r="AC54" t="n">
         <v>18.73958210756178</v>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="AD54" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=18.74% sobre 26 sem</t>
         </is>
@@ -5224,58 +6034,73 @@
         <v>13.22536243480747</v>
       </c>
       <c r="I55" t="n">
+        <v>0.02094546991961748</v>
+      </c>
+      <c r="J55" t="n">
         <v>38.25160771522186</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>26.16584507117277</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>18.47461648062351</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
+        <v>0.02925889749175726</v>
+      </c>
+      <c r="N55" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>164.6853792291117</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>666.4807692307693</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
+        <v>1.05552894846846</v>
+      </c>
+      <c r="R55" t="n">
         <v>170.8273891473021</v>
       </c>
-      <c r="P55" t="n">
+      <c r="S55" t="n">
         <v>164.6853792291117</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="T55" t="n">
         <v>666.4807692307693</v>
       </c>
-      <c r="R55" t="n">
+      <c r="U55" t="n">
+        <v>1.05552894846846</v>
+      </c>
+      <c r="V55" t="n">
         <v>188.8384134033935</v>
       </c>
-      <c r="S55" t="n">
+      <c r="W55" t="n">
         <v>50.45851269062578</v>
       </c>
-      <c r="T55" t="n">
+      <c r="X55" t="n">
         <v>73.8401566078978</v>
       </c>
-      <c r="U55" t="n">
+      <c r="Y55" t="n">
+        <v>0.1169432434622789</v>
+      </c>
+      <c r="Z55" t="n">
         <v>92.1901984902002</v>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X55" t="n">
+      <c r="AC55" t="n">
         <v>21.72360139831728</v>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="AD55" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=21.72% sobre 26 sem</t>
         </is>
@@ -5313,58 +6138,73 @@
         <v>3.663066571838782</v>
       </c>
       <c r="I56" t="n">
+        <v>0.09285339852569789</v>
+      </c>
+      <c r="J56" t="n">
         <v>154.1439500713238</v>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>69.90930581618821</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>2.311390036345996</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
+        <v>0.05859036847518367</v>
+      </c>
+      <c r="N56" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>170.9999889298593</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>63.55748541917569</v>
       </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
+        <v>1.611089617723085</v>
+      </c>
+      <c r="R56" t="n">
         <v>179.6737627262154</v>
       </c>
-      <c r="P56" t="n">
+      <c r="S56" t="n">
         <v>171.0772515772597</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="T56" t="n">
         <v>65.57692307692308</v>
       </c>
-      <c r="R56" t="n">
+      <c r="U56" t="n">
+        <v>1.662279418933411</v>
+      </c>
+      <c r="V56" t="n">
         <v>197.7368060568652</v>
       </c>
-      <c r="S56" t="n">
+      <c r="W56" t="n">
         <v>60.29853061336017</v>
       </c>
-      <c r="T56" t="n">
+      <c r="X56" t="n">
         <v>1.876042993102666</v>
       </c>
-      <c r="U56" t="n">
+      <c r="Y56" t="n">
+        <v>0.04755495546521333</v>
+      </c>
+      <c r="Z56" t="n">
         <v>104.7066447751141</v>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X56" t="n">
+      <c r="AC56" t="n">
         <v>60.29853061336017</v>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="AD56" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=60.30% sobre 26 sem</t>
         </is>
@@ -5402,58 +6242,73 @@
         <v>1.739251349080757</v>
       </c>
       <c r="I57" t="n">
+        <v>0.09088184711068618</v>
+      </c>
+      <c r="J57" t="n">
         <v>164.0555422208552</v>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>130.4479548242629</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>1.557985936312652</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
+        <v>0.0814101077106546</v>
+      </c>
+      <c r="N57" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>169.926070178636</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>28.29105662783227</v>
       </c>
-      <c r="O57" t="n">
+      <c r="Q57" t="n">
+        <v>1.478304722551654</v>
+      </c>
+      <c r="R57" t="n">
         <v>187.7358722188936</v>
       </c>
-      <c r="P57" t="n">
+      <c r="S57" t="n">
         <v>169.926070178636</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="T57" t="n">
         <v>28.44230769230769</v>
       </c>
-      <c r="R57" t="n">
+      <c r="U57" t="n">
+        <v>1.486208109330252</v>
+      </c>
+      <c r="V57" t="n">
         <v>197.2831175654684</v>
       </c>
-      <c r="S57" t="n">
+      <c r="W57" t="n">
         <v>106.6582394576391</v>
       </c>
-      <c r="T57" t="n">
+      <c r="X57" t="n">
         <v>1.034083610053474</v>
       </c>
-      <c r="U57" t="n">
+      <c r="Y57" t="n">
+        <v>0.05403441463375435</v>
+      </c>
+      <c r="Z57" t="n">
         <v>124.2225772452616</v>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="AA57" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X57" t="n">
+      <c r="AC57" t="n">
         <v>95.70003000461385</v>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="AD57" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=95.70% sobre 26 sem</t>
         </is>
@@ -5491,58 +6346,73 @@
         <v>2.251105847677055</v>
       </c>
       <c r="I58" t="n">
+        <v>0.09251912037717154</v>
+      </c>
+      <c r="J58" t="n">
         <v>158.4722608607674</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>125.4554034373361</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>1.849110789028315</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
+        <v>0.07599736096699983</v>
+      </c>
+      <c r="N58" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>172.5722834767986</v>
       </c>
-      <c r="N58" t="n">
+      <c r="P58" t="n">
         <v>37.53846153846154</v>
       </c>
-      <c r="O58" t="n">
+      <c r="Q58" t="n">
+        <v>1.542808591357268</v>
+      </c>
+      <c r="R58" t="n">
         <v>183.1273067581348</v>
       </c>
-      <c r="P58" t="n">
+      <c r="S58" t="n">
         <v>172.5722834767986</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="T58" t="n">
         <v>37.53846153846154</v>
       </c>
-      <c r="R58" t="n">
+      <c r="U58" t="n">
+        <v>1.542808591357268</v>
+      </c>
+      <c r="V58" t="n">
         <v>197.6615055783608</v>
       </c>
-      <c r="S58" t="n">
+      <c r="W58" t="n">
         <v>87.35952124159834</v>
       </c>
-      <c r="T58" t="n">
+      <c r="X58" t="n">
         <v>1.166134199350967</v>
       </c>
-      <c r="U58" t="n">
+      <c r="Y58" t="n">
+        <v>0.04792742663656684</v>
+      </c>
+      <c r="Z58" t="n">
         <v>111.9755139895278</v>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X58" t="n">
+      <c r="AC58" t="n">
         <v>87.35952124159834</v>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=87.36% sobre 26 sem</t>
         </is>
@@ -5580,56 +6450,71 @@
         <v>0.2449063057226444</v>
       </c>
       <c r="I59" t="n">
+        <v>0.003284577444729514</v>
+      </c>
+      <c r="J59" t="n">
         <v>163.442478475025</v>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>193.8469810539535</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>0.2418557896529395</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
+        <v>0.003243665242621149</v>
+      </c>
+      <c r="N59" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>176.9975490196078</v>
       </c>
-      <c r="N59" t="n">
+      <c r="P59" t="n">
         <v>10.55769230769231</v>
       </c>
-      <c r="O59" t="n">
+      <c r="Q59" t="n">
+        <v>0.1415952027854794</v>
+      </c>
+      <c r="R59" t="n">
         <v>198.2516520479188</v>
       </c>
-      <c r="P59" t="n">
+      <c r="S59" t="n">
         <v>176.9975490196078</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="T59" t="n">
         <v>10.55769230769231</v>
       </c>
-      <c r="R59" t="n">
+      <c r="U59" t="n">
+        <v>0.1415952027854794</v>
+      </c>
+      <c r="V59" t="n">
         <v>199.2894660635261</v>
       </c>
-      <c r="S59" t="n">
+      <c r="W59" t="n">
         <v>175.6926664465242</v>
       </c>
-      <c r="T59" t="n">
+      <c r="X59" t="n">
         <v>0.6390549945212811</v>
       </c>
-      <c r="U59" t="n">
+      <c r="Y59" t="n">
+        <v>0.008570729180503351</v>
+      </c>
+      <c r="Z59" t="n">
         <v>167.6265476269683</v>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr">
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
@@ -5667,56 +6552,71 @@
         <v>0.1646774938454602</v>
       </c>
       <c r="I60" t="n">
+        <v>0.004169710241378959</v>
+      </c>
+      <c r="J60" t="n">
         <v>179.6544870721095</v>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>198.8417254797347</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>0.1612453958722502</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
+        <v>0.004082807934730184</v>
+      </c>
+      <c r="N60" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>173.1428571428572</v>
       </c>
-      <c r="N60" t="n">
+      <c r="P60" t="n">
         <v>5.673076923076923</v>
       </c>
-      <c r="O60" t="n">
+      <c r="Q60" t="n">
+        <v>0.1436449292122658</v>
+      </c>
+      <c r="R60" t="n">
         <v>197.6157031839507</v>
       </c>
-      <c r="P60" t="n">
+      <c r="S60" t="n">
         <v>173.1428571428572</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="T60" t="n">
         <v>5.673076923076923</v>
       </c>
-      <c r="R60" t="n">
+      <c r="U60" t="n">
+        <v>0.1436449292122658</v>
+      </c>
+      <c r="V60" t="n">
         <v>199.0965028052728</v>
       </c>
-      <c r="S60" t="n">
+      <c r="W60" t="n">
         <v>187.6551097725555</v>
       </c>
-      <c r="T60" t="n">
+      <c r="X60" t="n">
         <v>0.3705474387374383</v>
       </c>
-      <c r="U60" t="n">
+      <c r="Y60" t="n">
+        <v>0.009382432378222842</v>
+      </c>
+      <c r="Z60" t="n">
         <v>167.0169829765832</v>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr">
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -5754,56 +6654,71 @@
         <v>0.09296982760330753</v>
       </c>
       <c r="I61" t="n">
+        <v>0.002097162331387171</v>
+      </c>
+      <c r="J61" t="n">
         <v>178.3754768379913</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>197.512214632238</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>0.153430299764158</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
+        <v>0.003460996470078286</v>
+      </c>
+      <c r="N61" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>185.5555555555555</v>
       </c>
-      <c r="N61" t="n">
+      <c r="P61" t="n">
         <v>5.057692307692307</v>
       </c>
-      <c r="O61" t="n">
+      <c r="Q61" t="n">
+        <v>0.1140886464444902</v>
+      </c>
+      <c r="R61" t="n">
         <v>198.3770115307477</v>
       </c>
-      <c r="P61" t="n">
+      <c r="S61" t="n">
         <v>185.5555555555555</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="T61" t="n">
         <v>5.057692307692307</v>
       </c>
-      <c r="R61" t="n">
+      <c r="U61" t="n">
+        <v>0.1140886464444902</v>
+      </c>
+      <c r="V61" t="n">
         <v>199.3694289811982</v>
       </c>
-      <c r="S61" t="n">
+      <c r="W61" t="n">
         <v>191.6929698105321</v>
       </c>
-      <c r="T61" t="n">
+      <c r="X61" t="n">
         <v>0.3417249318550903</v>
       </c>
-      <c r="U61" t="n">
+      <c r="Y61" t="n">
+        <v>0.007708443408545673</v>
+      </c>
+      <c r="Z61" t="n">
         <v>167.1297521794813</v>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
-      <c r="Y61" t="inlineStr">
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
@@ -5841,58 +6756,73 @@
         <v>0.808461210422098</v>
       </c>
       <c r="I62" t="n">
+        <v>0.02428039299249848</v>
+      </c>
+      <c r="J62" t="n">
         <v>51.86246745886869</v>
       </c>
-      <c r="J62" t="n">
+      <c r="K62" t="n">
         <v>139.4558906579279</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>4.069888424207752</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
+        <v>0.1222303421629733</v>
+      </c>
+      <c r="N62" t="n">
         <v>109.609711216533</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>181.2762042013983</v>
       </c>
-      <c r="N62" t="n">
+      <c r="P62" t="n">
         <v>51.13178595466775</v>
       </c>
-      <c r="O62" t="n">
+      <c r="Q62" t="n">
+        <v>1.535633177427844</v>
+      </c>
+      <c r="R62" t="n">
         <v>187.6026725565334</v>
       </c>
-      <c r="P62" t="n">
+      <c r="S62" t="n">
         <v>181.467404226567</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="T62" t="n">
         <v>75.08417009920558</v>
       </c>
-      <c r="R62" t="n">
+      <c r="U62" t="n">
+        <v>2.254991499929215</v>
+      </c>
+      <c r="V62" t="n">
         <v>188.4656733609786</v>
       </c>
-      <c r="S62" t="n">
+      <c r="W62" t="n">
         <v>129.6986779309068</v>
       </c>
-      <c r="T62" t="n">
+      <c r="X62" t="n">
         <v>4.324530451610826</v>
       </c>
-      <c r="U62" t="n">
+      <c r="Y62" t="n">
+        <v>0.1298779675753603</v>
+      </c>
+      <c r="Z62" t="n">
         <v>127.8730185036105</v>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X62" t="n">
+      <c r="AC62" t="n">
         <v>121.6044579366546</v>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=121.60% sobre 26 sem</t>
         </is>
@@ -5930,56 +6860,71 @@
         <v>0.5314209835917494</v>
       </c>
       <c r="I63" t="n">
+        <v>0.03465553591794576</v>
+      </c>
+      <c r="J63" t="n">
         <v>69.84803023883232</v>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>166.7862371116838</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>0.5116838462098096</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
+        <v>0.03336841874610537</v>
+      </c>
+      <c r="N63" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>182.0347497758348</v>
       </c>
-      <c r="N63" t="n">
+      <c r="P63" t="n">
         <v>15.1677508887776</v>
       </c>
-      <c r="O63" t="n">
+      <c r="Q63" t="n">
+        <v>0.9891339483205281</v>
+      </c>
+      <c r="R63" t="n">
         <v>179.6068984245533</v>
       </c>
-      <c r="P63" t="n">
+      <c r="S63" t="n">
         <v>182.4732506191762</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="T63" t="n">
         <v>26.8344783570363</v>
       </c>
-      <c r="R63" t="n">
+      <c r="U63" t="n">
+        <v>1.749955792592544</v>
+      </c>
+      <c r="V63" t="n">
         <v>186.3893216158546</v>
       </c>
-      <c r="S63" t="n">
+      <c r="W63" t="n">
         <v>145.2710127269957</v>
       </c>
-      <c r="T63" t="n">
+      <c r="X63" t="n">
         <v>2.104858798994898</v>
       </c>
-      <c r="U63" t="n">
+      <c r="Y63" t="n">
+        <v>0.1372640749293596</v>
+      </c>
+      <c r="Z63" t="n">
         <v>131.8859677830883</v>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
-      <c r="Y63" t="inlineStr">
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
@@ -6017,58 +6962,73 @@
         <v>0.8390743959406475</v>
       </c>
       <c r="I64" t="n">
+        <v>0.03769532594426607</v>
+      </c>
+      <c r="J64" t="n">
         <v>72.92360982323459</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>159.3206622613936</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>2.050984692736824</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
+        <v>0.09214026416899954</v>
+      </c>
+      <c r="N64" t="n">
         <v>109.7635513825217</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>181.8322100587866</v>
       </c>
-      <c r="N64" t="n">
+      <c r="P64" t="n">
         <v>31.39477888154723</v>
       </c>
-      <c r="O64" t="n">
+      <c r="Q64" t="n">
+        <v>1.410407025423995</v>
+      </c>
+      <c r="R64" t="n">
         <v>188.9515900641726</v>
       </c>
-      <c r="P64" t="n">
+      <c r="S64" t="n">
         <v>182.0195781924902</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="T64" t="n">
         <v>49.51562916668028</v>
       </c>
-      <c r="R64" t="n">
+      <c r="U64" t="n">
+        <v>2.224484252890312</v>
+      </c>
+      <c r="V64" t="n">
         <v>191.0006997623111</v>
       </c>
-      <c r="S64" t="n">
+      <c r="W64" t="n">
         <v>147.8578523070447</v>
       </c>
-      <c r="T64" t="n">
+      <c r="X64" t="n">
         <v>3.052893810965289</v>
       </c>
-      <c r="U64" t="n">
+      <c r="Y64" t="n">
+        <v>0.1371509222952257</v>
+      </c>
+      <c r="Z64" t="n">
         <v>132.574641557417</v>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X64" t="n">
+      <c r="AC64" t="n">
         <v>146.1444121266724</v>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=146.14% sobre 26 sem</t>
         </is>
@@ -6106,58 +7066,73 @@
         <v>0.8811472161839162</v>
       </c>
       <c r="I65" t="n">
+        <v>0.02301772319827373</v>
+      </c>
+      <c r="J65" t="n">
         <v>124.1398173354868</v>
       </c>
-      <c r="J65" t="n">
+      <c r="K65" t="n">
         <v>159.1362720494756</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>0.6961974997610457</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
+        <v>0.01818638366722732</v>
+      </c>
+      <c r="N65" t="n">
         <v>137.6406301580537</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>190.7194605391035</v>
       </c>
-      <c r="N65" t="n">
+      <c r="P65" t="n">
         <v>41.64065176267066</v>
       </c>
-      <c r="O65" t="n">
+      <c r="Q65" t="n">
+        <v>1.087755801147315</v>
+      </c>
+      <c r="R65" t="n">
         <v>183.1533465531335</v>
       </c>
-      <c r="P65" t="n">
+      <c r="S65" t="n">
         <v>190.927725291808</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="T65" t="n">
         <v>45.19230769230769</v>
       </c>
-      <c r="R65" t="n">
+      <c r="U65" t="n">
+        <v>1.180533751962323</v>
+      </c>
+      <c r="V65" t="n">
         <v>191.9303948964172</v>
       </c>
-      <c r="S65" t="n">
+      <c r="W65" t="n">
         <v>162.7562716199893</v>
       </c>
-      <c r="T65" t="n">
+      <c r="X65" t="n">
         <v>6.581622894105985</v>
       </c>
-      <c r="U65" t="n">
+      <c r="Y65" t="n">
+        <v>0.1719281082541972</v>
+      </c>
+      <c r="Z65" t="n">
         <v>113.9712651292745</v>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X65" t="n">
+      <c r="AC65" t="n">
         <v>150.9338289242287</v>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="AD65" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=150.93% sobre 26 sem</t>
         </is>
@@ -6195,58 +7170,73 @@
         <v>0.5174825916730073</v>
       </c>
       <c r="I66" t="n">
+        <v>0.02444919966563743</v>
+      </c>
+      <c r="J66" t="n">
         <v>146.9871894171194</v>
       </c>
-      <c r="J66" t="n">
+      <c r="K66" t="n">
         <v>171.7530356338314</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>0.4975427705603367</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
+        <v>0.02350711451045441</v>
+      </c>
+      <c r="N66" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>191.8776960511818</v>
       </c>
-      <c r="N66" t="n">
+      <c r="P66" t="n">
         <v>19.4398982130394</v>
       </c>
-      <c r="O66" t="n">
+      <c r="Q66" t="n">
+        <v>0.918465588095764</v>
+      </c>
+      <c r="R66" t="n">
         <v>185.4205866195275</v>
       </c>
-      <c r="P66" t="n">
+      <c r="S66" t="n">
         <v>191.9387057888072</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="T66" t="n">
         <v>19.73076923076923</v>
       </c>
-      <c r="R66" t="n">
+      <c r="U66" t="n">
+        <v>0.9322082022510193</v>
+      </c>
+      <c r="V66" t="n">
         <v>192.190104304547</v>
       </c>
-      <c r="S66" t="n">
+      <c r="W66" t="n">
         <v>173.5926484386023</v>
       </c>
-      <c r="T66" t="n">
+      <c r="X66" t="n">
         <v>2.781624413232052</v>
       </c>
-      <c r="U66" t="n">
+      <c r="Y66" t="n">
+        <v>0.1314217942173714</v>
+      </c>
+      <c r="Z66" t="n">
         <v>118.44057480835</v>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X66" t="n">
+      <c r="AC66" t="n">
         <v>171.7530356338314</v>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="AD66" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=171.75% sobre 26 sem</t>
         </is>
@@ -6284,58 +7274,73 @@
         <v>0.5310402008178121</v>
       </c>
       <c r="I67" t="n">
+        <v>0.01945424891376072</v>
+      </c>
+      <c r="J67" t="n">
         <v>137.6516466078508</v>
       </c>
-      <c r="J67" t="n">
+      <c r="K67" t="n">
         <v>183.7604374326015</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>0.5406099533335619</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
+        <v>0.01980482942950656</v>
+      </c>
+      <c r="N67" t="n">
         <v>151.2037021887013</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>192.7117313666085</v>
       </c>
-      <c r="N67" t="n">
+      <c r="P67" t="n">
         <v>16.43981187413353</v>
       </c>
-      <c r="O67" t="n">
+      <c r="Q67" t="n">
+        <v>0.6022598511416978</v>
+      </c>
+      <c r="R67" t="n">
         <v>175.6951253506204</v>
       </c>
-      <c r="P67" t="n">
+      <c r="S67" t="n">
         <v>194.196348065024</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="T67" t="n">
         <v>26.5</v>
       </c>
-      <c r="R67" t="n">
+      <c r="U67" t="n">
+        <v>0.9708070978820835</v>
+      </c>
+      <c r="V67" t="n">
         <v>191.2393501485975</v>
       </c>
-      <c r="S67" t="n">
+      <c r="W67" t="n">
         <v>181.3259710545283</v>
       </c>
-      <c r="T67" t="n">
+      <c r="X67" t="n">
         <v>3.854970419694336</v>
       </c>
-      <c r="U67" t="n">
+      <c r="Y67" t="n">
+        <v>0.1412238734175372</v>
+      </c>
+      <c r="Z67" t="n">
         <v>116.630186356802</v>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X67" t="n">
+      <c r="AC67" t="n">
         <v>177.6001138412982</v>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=177.60% sobre 26 sem</t>
         </is>
@@ -6373,56 +7378,71 @@
         <v>0.04482977413361657</v>
       </c>
       <c r="I68" t="n">
+        <v>0.002330332638524578</v>
+      </c>
+      <c r="J68" t="n">
         <v>183.5383709430125</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>199.8412794270195</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>0.05254346953207076</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
+        <v>0.002731304459106992</v>
+      </c>
+      <c r="N68" t="n">
         <v>198.3312090033645</v>
       </c>
-      <c r="M68" t="n">
-        <v>200</v>
-      </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
+        <v>200</v>
+      </c>
+      <c r="P68" t="n">
         <v>8.849613765279083</v>
       </c>
-      <c r="O68" t="n">
+      <c r="Q68" t="n">
+        <v>0.4600189091763006</v>
+      </c>
+      <c r="R68" t="n">
         <v>188.2784643365136</v>
       </c>
-      <c r="P68" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q68" t="n">
+      <c r="S68" t="n">
+        <v>200</v>
+      </c>
+      <c r="T68" t="n">
         <v>9.26923076923077</v>
       </c>
-      <c r="R68" t="n">
+      <c r="U68" t="n">
+        <v>0.4818313590243415</v>
+      </c>
+      <c r="V68" t="n">
         <v>199.7672857698158</v>
       </c>
-      <c r="S68" t="n">
+      <c r="W68" t="n">
         <v>197.5760121573963</v>
       </c>
-      <c r="T68" t="n">
+      <c r="X68" t="n">
         <v>0.7060823159264591</v>
       </c>
-      <c r="U68" t="n">
+      <c r="Y68" t="n">
+        <v>0.0367034342261967</v>
+      </c>
+      <c r="Z68" t="n">
         <v>177.2448922419183</v>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr">
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -6460,56 +7480,71 @@
         <v>0.05934645077246404</v>
       </c>
       <c r="I69" t="n">
+        <v>0.007104700429176391</v>
+      </c>
+      <c r="J69" t="n">
         <v>171.5447439761989</v>
       </c>
-      <c r="J69" t="n">
+      <c r="K69" t="n">
         <v>199.5522736128797</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>0.06626069061720037</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
+        <v>0.007932443321176251</v>
+      </c>
+      <c r="N69" t="n">
         <v>194.4182830751776</v>
       </c>
-      <c r="M69" t="n">
-        <v>200</v>
-      </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
+        <v>200</v>
+      </c>
+      <c r="P69" t="n">
         <v>4.25</v>
       </c>
-      <c r="O69" t="n">
+      <c r="Q69" t="n">
+        <v>0.508791619902731</v>
+      </c>
+      <c r="R69" t="n">
         <v>190.8574288418282</v>
       </c>
-      <c r="P69" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q69" t="n">
+      <c r="S69" t="n">
+        <v>200</v>
+      </c>
+      <c r="T69" t="n">
         <v>4.25</v>
       </c>
-      <c r="R69" t="n">
+      <c r="U69" t="n">
+        <v>0.508791619902731</v>
+      </c>
+      <c r="V69" t="n">
         <v>199.6130972886749</v>
       </c>
-      <c r="S69" t="n">
+      <c r="W69" t="n">
         <v>198.7786331105758</v>
       </c>
-      <c r="T69" t="n">
+      <c r="X69" t="n">
         <v>0.3453066502488701</v>
       </c>
-      <c r="U69" t="n">
+      <c r="Y69" t="n">
+        <v>0.04133861881019021</v>
+      </c>
+      <c r="Z69" t="n">
         <v>185.6695408532579</v>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="AA69" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr">
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
@@ -6547,56 +7582,71 @@
         <v>0.01300024688996922</v>
       </c>
       <c r="I70" t="n">
+        <v>0.001071909045295066</v>
+      </c>
+      <c r="J70" t="n">
         <v>188.453973372859</v>
       </c>
-      <c r="J70" t="n">
-        <v>200</v>
-      </c>
       <c r="K70" t="n">
+        <v>200</v>
+      </c>
+      <c r="L70" t="n">
         <v>0.01611028223724515</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
+        <v>0.001328340715258554</v>
+      </c>
+      <c r="N70" t="n">
         <v>198.9765474653765</v>
       </c>
-      <c r="M70" t="n">
-        <v>200</v>
-      </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
+        <v>200</v>
+      </c>
+      <c r="P70" t="n">
         <v>4.961827715412824</v>
       </c>
-      <c r="O70" t="n">
+      <c r="Q70" t="n">
+        <v>0.4091174617191712</v>
+      </c>
+      <c r="R70" t="n">
         <v>192.937344462188</v>
       </c>
-      <c r="P70" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q70" t="n">
+      <c r="S70" t="n">
+        <v>200</v>
+      </c>
+      <c r="T70" t="n">
         <v>5.134615384615385</v>
       </c>
-      <c r="R70" t="n">
+      <c r="U70" t="n">
+        <v>0.423364319267437</v>
+      </c>
+      <c r="V70" t="n">
         <v>199.6974055100667</v>
       </c>
-      <c r="S70" t="n">
-        <v>200</v>
-      </c>
-      <c r="T70" t="n">
+      <c r="W70" t="n">
+        <v>200</v>
+      </c>
+      <c r="X70" t="n">
         <v>0.3664860990972112</v>
       </c>
-      <c r="U70" t="n">
+      <c r="Y70" t="n">
+        <v>0.03021786954679401</v>
+      </c>
+      <c r="Z70" t="n">
         <v>184.4638384017739</v>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr">
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr">
         <is>
           <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -6634,58 +7684,73 @@
         <v>3.115210034521734</v>
       </c>
       <c r="I71" t="n">
+        <v>0.07109815355873011</v>
+      </c>
+      <c r="J71" t="n">
         <v>143.4057585362926</v>
       </c>
-      <c r="J71" t="n">
+      <c r="K71" t="n">
         <v>173.2999901984479</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>4.703881357592056</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
+        <v>0.1073562537928435</v>
+      </c>
+      <c r="N71" t="n">
         <v>171.2174826415851</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>67.03669362173159</v>
       </c>
-      <c r="N71" t="n">
+      <c r="P71" t="n">
         <v>4.16481419340312</v>
       </c>
-      <c r="O71" t="n">
+      <c r="Q71" t="n">
+        <v>0.09505317323222298</v>
+      </c>
+      <c r="R71" t="n">
         <v>65.78436567943845</v>
       </c>
-      <c r="P71" t="n">
+      <c r="S71" t="n">
         <v>190.9113460286165</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="T71" t="n">
         <v>5.018515475175227</v>
       </c>
-      <c r="R71" t="n">
+      <c r="U71" t="n">
+        <v>0.1145371194676608</v>
+      </c>
+      <c r="V71" t="n">
         <v>185.267595267154</v>
       </c>
-      <c r="S71" t="n">
+      <c r="W71" t="n">
         <v>59.79657500626929</v>
       </c>
-      <c r="T71" t="n">
+      <c r="X71" t="n">
         <v>5.964030506842874</v>
       </c>
-      <c r="U71" t="n">
+      <c r="Y71" t="n">
+        <v>0.1361165225154924</v>
+      </c>
+      <c r="Z71" t="n">
         <v>93.16202342284906</v>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X71" t="n">
+      <c r="AC71" t="n">
         <v>61.42327963804853</v>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="AD71" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=61.42% sobre 26 sem</t>
         </is>
@@ -6723,58 +7788,73 @@
         <v>1.602741103507269</v>
       </c>
       <c r="I72" t="n">
+        <v>0.07262491548036337</v>
+      </c>
+      <c r="J72" t="n">
         <v>151.0433307550491</v>
       </c>
-      <c r="J72" t="n">
+      <c r="K72" t="n">
         <v>84.07765725354294</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>1.367494685518548</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
+        <v>0.06196520806654424</v>
+      </c>
+      <c r="N72" t="n">
         <v>171.9287045593839</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>87.90553164133496</v>
       </c>
-      <c r="N72" t="n">
+      <c r="P72" t="n">
         <v>2.415561923845612</v>
       </c>
-      <c r="O72" t="n">
+      <c r="Q72" t="n">
+        <v>0.1094562185826389</v>
+      </c>
+      <c r="R72" t="n">
         <v>96.15548417978732</v>
       </c>
-      <c r="P72" t="n">
+      <c r="S72" t="n">
         <v>171.1975130422481</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="T72" t="n">
         <v>2.179259122568957</v>
       </c>
-      <c r="R72" t="n">
+      <c r="U72" t="n">
+        <v>0.09874864333362593</v>
+      </c>
+      <c r="V72" t="n">
         <v>161.2927483340683</v>
       </c>
-      <c r="S72" t="n">
+      <c r="W72" t="n">
         <v>85.73646487878931</v>
       </c>
-      <c r="T72" t="n">
+      <c r="X72" t="n">
         <v>2.828564867761933</v>
       </c>
-      <c r="U72" t="n">
+      <c r="Y72" t="n">
+        <v>0.1281705972364512</v>
+      </c>
+      <c r="Z72" t="n">
         <v>104.036396201453</v>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="AB72" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X72" t="n">
+      <c r="AC72" t="n">
         <v>84.07765725354294</v>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="AD72" t="inlineStr">
         <is>
           <t>DeepAR: menor SMAPE real=84.08% sobre 26 sem</t>
         </is>
@@ -6812,58 +7892,73 @@
         <v>1.977763974231611</v>
       </c>
       <c r="I73" t="n">
+        <v>0.0886392817582795</v>
+      </c>
+      <c r="J73" t="n">
         <v>148.5993365374143</v>
       </c>
-      <c r="J73" t="n">
+      <c r="K73" t="n">
         <v>147.0918094181974</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>2.362989944339627</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
+        <v>0.1059043112309076</v>
+      </c>
+      <c r="N73" t="n">
         <v>191.7880460732582</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>86.13938208574584</v>
       </c>
-      <c r="N73" t="n">
+      <c r="P73" t="n">
         <v>2.002529465235197</v>
       </c>
-      <c r="O73" t="n">
+      <c r="Q73" t="n">
+        <v>0.08974921973042897</v>
+      </c>
+      <c r="R73" t="n">
         <v>105.84208545642</v>
       </c>
-      <c r="P73" t="n">
+      <c r="S73" t="n">
         <v>174.3124361485125</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="T73" t="n">
         <v>2.622439861172213</v>
       </c>
-      <c r="R73" t="n">
+      <c r="U73" t="n">
+        <v>0.1175323187079983</v>
+      </c>
+      <c r="V73" t="n">
         <v>173.6314937555617</v>
       </c>
-      <c r="S73" t="n">
+      <c r="W73" t="n">
         <v>62.86539382703211</v>
       </c>
-      <c r="T73" t="n">
+      <c r="X73" t="n">
         <v>2.667844818908352</v>
       </c>
-      <c r="U73" t="n">
+      <c r="Y73" t="n">
+        <v>0.119567274797013</v>
+      </c>
+      <c r="Z73" t="n">
         <v>104.3951484726403</v>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="AB73" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X73" t="n">
+      <c r="AC73" t="n">
         <v>62.86539382703211</v>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="AD73" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=62.87% sobre 26 sem</t>
         </is>
@@ -6901,58 +7996,73 @@
         <v>6.258269259578741</v>
       </c>
       <c r="I74" t="n">
+        <v>0.1930633532310033</v>
+      </c>
+      <c r="J74" t="n">
         <v>148.9425712788151</v>
       </c>
-      <c r="J74" t="n">
+      <c r="K74" t="n">
         <v>189.2587566906077</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>0.4390523964915655</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
+        <v>0.01354446803020351</v>
+      </c>
+      <c r="N74" t="n">
         <v>144.0733541161664</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>191.7085025444234</v>
       </c>
-      <c r="N74" t="n">
+      <c r="P74" t="n">
         <v>38.4139073690108</v>
       </c>
-      <c r="O74" t="n">
+      <c r="Q74" t="n">
+        <v>1.185042934356836</v>
+      </c>
+      <c r="R74" t="n">
         <v>166.1309749781026</v>
       </c>
-      <c r="P74" t="n">
+      <c r="S74" t="n">
         <v>191.7140640228413</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="T74" t="n">
         <v>38.71153846153846</v>
       </c>
-      <c r="R74" t="n">
+      <c r="U74" t="n">
+        <v>1.194224651276613</v>
+      </c>
+      <c r="V74" t="n">
         <v>193.1141809259393</v>
       </c>
-      <c r="S74" t="n">
+      <c r="W74" t="n">
         <v>163.1582599134988</v>
       </c>
-      <c r="T74" t="n">
+      <c r="X74" t="n">
         <v>2.043127757499643</v>
       </c>
-      <c r="U74" t="n">
+      <c r="Y74" t="n">
+        <v>0.06302910270894493</v>
+      </c>
+      <c r="Z74" t="n">
         <v>113.155914904339</v>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X74" t="n">
+      <c r="AC74" t="n">
         <v>163.1582599134988</v>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=163.16% sobre 26 sem</t>
         </is>
@@ -6990,56 +8100,71 @@
         <v>2.142589026981875</v>
       </c>
       <c r="I75" t="n">
+        <v>0.1289745087724228</v>
+      </c>
+      <c r="J75" t="n">
         <v>157.2380343536269</v>
       </c>
-      <c r="J75" t="n">
+      <c r="K75" t="n">
         <v>197.5158713283456</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>0.260182167677241</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
+        <v>0.01566183101142158</v>
+      </c>
+      <c r="N75" t="n">
         <v>158.6014909691414</v>
       </c>
-      <c r="M75" t="n">
+      <c r="O75" t="n">
         <v>191.3964759734417</v>
       </c>
-      <c r="N75" t="n">
+      <c r="P75" t="n">
         <v>16.20981996287579</v>
       </c>
-      <c r="O75" t="n">
+      <c r="Q75" t="n">
+        <v>0.9757604191347355</v>
+      </c>
+      <c r="R75" t="n">
         <v>163.9609846286252</v>
       </c>
-      <c r="P75" t="n">
+      <c r="S75" t="n">
         <v>191.3964759734417</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="T75" t="n">
         <v>16.44230769230769</v>
       </c>
-      <c r="R75" t="n">
+      <c r="U75" t="n">
+        <v>0.9897551658274006</v>
+      </c>
+      <c r="V75" t="n">
         <v>193.2892416279341</v>
       </c>
-      <c r="S75" t="n">
+      <c r="W75" t="n">
         <v>169.8670547016924</v>
       </c>
-      <c r="T75" t="n">
+      <c r="X75" t="n">
         <v>0.9626258278621391</v>
       </c>
-      <c r="U75" t="n">
+      <c r="Y75" t="n">
+        <v>0.05794587376145307</v>
+      </c>
+      <c r="Z75" t="n">
         <v>110.9447640026735</v>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr">
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
@@ -7077,56 +8202,71 @@
         <v>3.56168156738758</v>
       </c>
       <c r="I76" t="n">
+        <v>0.1637319496572368</v>
+      </c>
+      <c r="J76" t="n">
         <v>154.9841830576604</v>
       </c>
-      <c r="J76" t="n">
+      <c r="K76" t="n">
         <v>196.2482320486948</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>0.2278723959063293</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
+        <v>0.01047538668151492</v>
+      </c>
+      <c r="N76" t="n">
         <v>166.7038660732646</v>
       </c>
-      <c r="M76" t="n">
+      <c r="O76" t="n">
         <v>191.2067962153635</v>
       </c>
-      <c r="N76" t="n">
+      <c r="P76" t="n">
         <v>20.1666718255868</v>
       </c>
-      <c r="O76" t="n">
+      <c r="Q76" t="n">
+        <v>0.9270701025984448</v>
+      </c>
+      <c r="R76" t="n">
         <v>168.5329779328607</v>
       </c>
-      <c r="P76" t="n">
+      <c r="S76" t="n">
         <v>191.3315200778003</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="T76" t="n">
         <v>23.01923076923077</v>
       </c>
-      <c r="R76" t="n">
+      <c r="U76" t="n">
+        <v>1.05820339694783</v>
+      </c>
+      <c r="V76" t="n">
         <v>192.8448970866968</v>
       </c>
-      <c r="S76" t="n">
+      <c r="W76" t="n">
         <v>174.7180212472131</v>
       </c>
-      <c r="T76" t="n">
+      <c r="X76" t="n">
         <v>1.080921636694278</v>
       </c>
-      <c r="U76" t="n">
+      <c r="Y76" t="n">
+        <v>0.04969040708837363</v>
+      </c>
+      <c r="Z76" t="n">
         <v>118.0223455785753</v>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr">
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
@@ -7164,58 +8304,73 @@
         <v>5.9559345125117</v>
       </c>
       <c r="I77" t="n">
+        <v>0.1646707312946037</v>
+      </c>
+      <c r="J77" t="n">
         <v>77.76772218573589</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
         <v>48.91910741895335</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>8.212790663504016</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
+        <v>0.2270686895041719</v>
+      </c>
+      <c r="N77" t="n">
         <v>110.3330967959057</v>
       </c>
-      <c r="M77" t="n">
+      <c r="O77" t="n">
         <v>59.40091192585066</v>
       </c>
-      <c r="N77" t="n">
+      <c r="P77" t="n">
         <v>12.5</v>
       </c>
-      <c r="O77" t="n">
+      <c r="Q77" t="n">
+        <v>0.3456022118541558</v>
+      </c>
+      <c r="R77" t="n">
         <v>117.4841503463031</v>
       </c>
-      <c r="P77" t="n">
+      <c r="S77" t="n">
         <v>59.40091192585066</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="T77" t="n">
         <v>12.5</v>
       </c>
-      <c r="R77" t="n">
+      <c r="U77" t="n">
+        <v>0.3456022118541558</v>
+      </c>
+      <c r="V77" t="n">
         <v>138.4032392925817</v>
       </c>
-      <c r="S77" t="n">
+      <c r="W77" t="n">
         <v>33.73237849708716</v>
       </c>
-      <c r="T77" t="n">
+      <c r="X77" t="n">
         <v>5.898095795965104</v>
       </c>
-      <c r="U77" t="n">
+      <c r="Y77" t="n">
+        <v>0.163071596225059</v>
+      </c>
+      <c r="Z77" t="n">
         <v>118.3894561520081</v>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X77" t="n">
+      <c r="AC77" t="n">
         <v>33.73237849708716</v>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="AD77" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=33.73% sobre 26 sem</t>
         </is>
@@ -7253,58 +8408,73 @@
         <v>3.17139220478416</v>
       </c>
       <c r="I78" t="n">
+        <v>0.1693384791474939</v>
+      </c>
+      <c r="J78" t="n">
         <v>103.5437500854655</v>
       </c>
-      <c r="J78" t="n">
+      <c r="K78" t="n">
         <v>55.22945859981466</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>3.993802203932325</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
+        <v>0.2132515777170606</v>
+      </c>
+      <c r="N78" t="n">
         <v>115.3631910942854</v>
       </c>
-      <c r="M78" t="n">
+      <c r="O78" t="n">
         <v>110.8945250546275</v>
       </c>
-      <c r="N78" t="n">
+      <c r="P78" t="n">
         <v>5.324883351245751</v>
       </c>
-      <c r="O78" t="n">
+      <c r="Q78" t="n">
+        <v>0.2843254918068814</v>
+      </c>
+      <c r="R78" t="n">
         <v>128.5059105773902</v>
       </c>
-      <c r="P78" t="n">
+      <c r="S78" t="n">
         <v>55.29074480395132</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="T78" t="n">
         <v>4.416331334856955</v>
       </c>
-      <c r="R78" t="n">
+      <c r="U78" t="n">
+        <v>0.2358127861094987</v>
+      </c>
+      <c r="V78" t="n">
         <v>82.9912432467173</v>
       </c>
-      <c r="S78" t="n">
+      <c r="W78" t="n">
         <v>33.76738924721007</v>
       </c>
-      <c r="T78" t="n">
+      <c r="X78" t="n">
         <v>2.900697323286576</v>
       </c>
-      <c r="U78" t="n">
+      <c r="Y78" t="n">
+        <v>0.1548845558904897</v>
+      </c>
+      <c r="Z78" t="n">
         <v>124.390269119479</v>
       </c>
-      <c r="V78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
+      <c r="AB78" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X78" t="n">
+      <c r="AC78" t="n">
         <v>33.76738924721007</v>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="AD78" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=33.77% sobre 26 sem</t>
         </is>
@@ -7342,58 +8512,73 @@
         <v>3.286245827177914</v>
       </c>
       <c r="I79" t="n">
+        <v>0.1477379410925727</v>
+      </c>
+      <c r="J79" t="n">
         <v>102.5016657415887</v>
       </c>
-      <c r="J79" t="n">
+      <c r="K79" t="n">
         <v>53.41466540703234</v>
       </c>
-      <c r="K79" t="n">
+      <c r="L79" t="n">
         <v>4.80042473164641</v>
       </c>
-      <c r="L79" t="n">
+      <c r="M79" t="n">
+        <v>0.2158100469411142</v>
+      </c>
+      <c r="N79" t="n">
         <v>114.5134591086363</v>
       </c>
-      <c r="M79" t="n">
+      <c r="O79" t="n">
         <v>62.22131467786915</v>
       </c>
-      <c r="N79" t="n">
+      <c r="P79" t="n">
         <v>7.288461538461538</v>
       </c>
-      <c r="O79" t="n">
+      <c r="Q79" t="n">
+        <v>0.327663345364947</v>
+      </c>
+      <c r="R79" t="n">
         <v>131.5261264594907</v>
       </c>
-      <c r="P79" t="n">
+      <c r="S79" t="n">
         <v>62.22131467786915</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="T79" t="n">
         <v>7.288461538461538</v>
       </c>
-      <c r="R79" t="n">
+      <c r="U79" t="n">
+        <v>0.327663345364947</v>
+      </c>
+      <c r="V79" t="n">
         <v>148.0195847609927</v>
       </c>
-      <c r="S79" t="n">
+      <c r="W79" t="n">
         <v>36.04795612140367</v>
       </c>
-      <c r="T79" t="n">
+      <c r="X79" t="n">
         <v>3.257588844669878</v>
       </c>
-      <c r="U79" t="n">
+      <c r="Y79" t="n">
+        <v>0.1464496249359878</v>
+      </c>
+      <c r="Z79" t="n">
         <v>120.3982350383182</v>
       </c>
-      <c r="V79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
+      <c r="AB79" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X79" t="n">
+      <c r="AC79" t="n">
         <v>36.04795612140367</v>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="AD79" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=36.05% sobre 26 sem</t>
         </is>
@@ -7431,58 +8616,73 @@
         <v>29.25013720036457</v>
       </c>
       <c r="I80" t="n">
+        <v>0.9623734221793813</v>
+      </c>
+      <c r="J80" t="n">
         <v>180.9937478063148</v>
       </c>
-      <c r="J80" t="n">
+      <c r="K80" t="n">
         <v>155.1167720404115</v>
       </c>
-      <c r="K80" t="n">
+      <c r="L80" t="n">
         <v>29.20862733339917</v>
       </c>
-      <c r="L80" t="n">
+      <c r="M80" t="n">
+        <v>0.9610076852444719</v>
+      </c>
+      <c r="N80" t="n">
         <v>195.3549053278383</v>
       </c>
-      <c r="M80" t="n">
+      <c r="O80" t="n">
         <v>121.8065814559429</v>
       </c>
-      <c r="N80" t="n">
+      <c r="P80" t="n">
         <v>22.8612208366394</v>
       </c>
-      <c r="O80" t="n">
+      <c r="Q80" t="n">
+        <v>0.752168483212483</v>
+      </c>
+      <c r="R80" t="n">
         <v>171.1146914183623</v>
       </c>
-      <c r="P80" t="n">
+      <c r="S80" t="n">
         <v>163.5409614670002</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="T80" t="n">
         <v>31.86330594704844</v>
       </c>
-      <c r="R80" t="n">
+      <c r="U80" t="n">
+        <v>1.048350596653866</v>
+      </c>
+      <c r="V80" t="n">
         <v>172.7461511452186</v>
       </c>
-      <c r="S80" t="n">
+      <c r="W80" t="n">
         <v>53.61240802508001</v>
       </c>
-      <c r="T80" t="n">
+      <c r="X80" t="n">
         <v>28.18228627350842</v>
       </c>
-      <c r="U80" t="n">
+      <c r="Y80" t="n">
+        <v>0.9272395237016958</v>
+      </c>
+      <c r="Z80" t="n">
         <v>175.912448276349</v>
       </c>
-      <c r="V80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
+      <c r="AB80" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X80" t="n">
+      <c r="AC80" t="n">
         <v>53.61240802508001</v>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="AD80" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=53.61% sobre 26 sem</t>
         </is>
@@ -7520,58 +8720,73 @@
         <v>12.89128020151289</v>
       </c>
       <c r="I81" t="n">
+        <v>0.8019458912294177</v>
+      </c>
+      <c r="J81" t="n">
         <v>185.5191244575439</v>
       </c>
-      <c r="J81" t="n">
+      <c r="K81" t="n">
         <v>113.5248773576872</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>10.23591089824205</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
+        <v>0.6367596204194119</v>
+      </c>
+      <c r="N81" t="n">
         <v>199.4307199889832</v>
       </c>
-      <c r="M81" t="n">
+      <c r="O81" t="n">
         <v>160.6879071728418</v>
       </c>
-      <c r="N81" t="n">
+      <c r="P81" t="n">
         <v>13.36833044198843</v>
       </c>
-      <c r="O81" t="n">
+      <c r="Q81" t="n">
+        <v>0.8316224225187205</v>
+      </c>
+      <c r="R81" t="n">
         <v>169.7911563334158</v>
       </c>
-      <c r="P81" t="n">
+      <c r="S81" t="n">
         <v>149.7346987873689</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="T81" t="n">
         <v>13.97074602195977</v>
       </c>
-      <c r="R81" t="n">
+      <c r="U81" t="n">
+        <v>0.8690977307595501</v>
+      </c>
+      <c r="V81" t="n">
         <v>163.1536185700502</v>
       </c>
-      <c r="S81" t="n">
+      <c r="W81" t="n">
         <v>55.98270195837857</v>
       </c>
-      <c r="T81" t="n">
+      <c r="X81" t="n">
         <v>8.787075583211861</v>
       </c>
-      <c r="U81" t="n">
+      <c r="Y81" t="n">
+        <v>0.5466298963117798</v>
+      </c>
+      <c r="Z81" t="n">
         <v>172.1596497720207</v>
       </c>
-      <c r="V81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X81" t="n">
+      <c r="AC81" t="n">
         <v>55.98270195837857</v>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="AD81" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=55.98% sobre 26 sem</t>
         </is>
@@ -7609,58 +8824,73 @@
         <v>15.38036762375736</v>
       </c>
       <c r="I82" t="n">
+        <v>0.76011083237102</v>
+      </c>
+      <c r="J82" t="n">
         <v>186.2973802760101</v>
       </c>
-      <c r="J82" t="n">
+      <c r="K82" t="n">
         <v>147.761699642381</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>15.85623120177246</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
+        <v>0.7836284146049711</v>
+      </c>
+      <c r="N82" t="n">
         <v>183.0162368876618</v>
       </c>
-      <c r="M82" t="n">
+      <c r="O82" t="n">
         <v>162.0900465169206</v>
       </c>
-      <c r="N82" t="n">
+      <c r="P82" t="n">
         <v>15.4147405658777</v>
       </c>
-      <c r="O82" t="n">
+      <c r="Q82" t="n">
+        <v>0.7618095723677007</v>
+      </c>
+      <c r="R82" t="n">
         <v>164.8878431370165</v>
       </c>
-      <c r="P82" t="n">
+      <c r="S82" t="n">
         <v>154.1395095724688</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="T82" t="n">
         <v>17.04319178960882</v>
       </c>
-      <c r="R82" t="n">
+      <c r="U82" t="n">
+        <v>0.8422890150849146</v>
+      </c>
+      <c r="V82" t="n">
         <v>166.6060177059153</v>
       </c>
-      <c r="S82" t="n">
+      <c r="W82" t="n">
         <v>40.7500349637836</v>
       </c>
-      <c r="T82" t="n">
+      <c r="X82" t="n">
         <v>9.748616504925208</v>
       </c>
-      <c r="U82" t="n">
+      <c r="Y82" t="n">
+        <v>0.4817849083515161</v>
+      </c>
+      <c r="Z82" t="n">
         <v>176.1888335684919</v>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
+      <c r="AB82" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X82" t="n">
+      <c r="AC82" t="n">
         <v>40.7500349637836</v>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="AD82" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=40.75% sobre 26 sem</t>
         </is>
@@ -7698,58 +8928,73 @@
         <v>6.048264925018194</v>
       </c>
       <c r="I83" t="n">
+        <v>0.1546500020779722</v>
+      </c>
+      <c r="J83" t="n">
         <v>88.04980557911651</v>
       </c>
-      <c r="J83" t="n">
+      <c r="K83" t="n">
         <v>50.07649051829125</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>7.637246332998242</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
+        <v>0.1952791711194117</v>
+      </c>
+      <c r="N83" t="n">
         <v>194.0620340843763</v>
       </c>
-      <c r="M83" t="n">
+      <c r="O83" t="n">
         <v>92.30002957030169</v>
       </c>
-      <c r="N83" t="n">
+      <c r="P83" t="n">
         <v>31.07821057219206</v>
       </c>
-      <c r="O83" t="n">
+      <c r="Q83" t="n">
+        <v>0.7946486123133407</v>
+      </c>
+      <c r="R83" t="n">
         <v>149.7627223031833</v>
       </c>
-      <c r="P83" t="n">
+      <c r="S83" t="n">
         <v>98.53375806406798</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="T83" t="n">
         <v>24.77082648574989</v>
       </c>
-      <c r="R83" t="n">
+      <c r="U83" t="n">
+        <v>0.6333731103028337</v>
+      </c>
+      <c r="V83" t="n">
         <v>103.1343264142703</v>
       </c>
-      <c r="S83" t="n">
+      <c r="W83" t="n">
         <v>52.93333819357255</v>
       </c>
-      <c r="T83" t="n">
+      <c r="X83" t="n">
         <v>11.37971859865602</v>
       </c>
-      <c r="U83" t="n">
+      <c r="Y83" t="n">
+        <v>0.2909716301693909</v>
+      </c>
+      <c r="Z83" t="n">
         <v>103.3034448942146</v>
       </c>
-      <c r="V83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
+      <c r="AB83" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X83" t="n">
+      <c r="AC83" t="n">
         <v>43.1997975360161</v>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="AD83" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=43.20% sobre 26 sem</t>
         </is>
@@ -7787,58 +9032,73 @@
         <v>2.490847406123287</v>
       </c>
       <c r="I84" t="n">
+        <v>0.1239227565235466</v>
+      </c>
+      <c r="J84" t="n">
         <v>100.4914466151705</v>
       </c>
-      <c r="J84" t="n">
+      <c r="K84" t="n">
         <v>50.45190516411535</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>3.435796323442797</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
+        <v>0.1709351404697909</v>
+      </c>
+      <c r="N84" t="n">
         <v>161.0256208848398</v>
       </c>
-      <c r="M84" t="n">
+      <c r="O84" t="n">
         <v>72.53719142394779</v>
       </c>
-      <c r="N84" t="n">
+      <c r="P84" t="n">
         <v>7.96397053099273</v>
       </c>
-      <c r="O84" t="n">
+      <c r="Q84" t="n">
+        <v>0.3962174393528721</v>
+      </c>
+      <c r="R84" t="n">
         <v>93.7212443502728</v>
       </c>
-      <c r="P84" t="n">
+      <c r="S84" t="n">
         <v>91.01392829545925</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="T84" t="n">
         <v>11.19769136149799</v>
       </c>
-      <c r="R84" t="n">
+      <c r="U84" t="n">
+        <v>0.5570990727113425</v>
+      </c>
+      <c r="V84" t="n">
         <v>98.74789164115032</v>
       </c>
-      <c r="S84" t="n">
+      <c r="W84" t="n">
         <v>55.35222777066018</v>
       </c>
-      <c r="T84" t="n">
+      <c r="X84" t="n">
         <v>5.146215844761524</v>
       </c>
-      <c r="U84" t="n">
+      <c r="Y84" t="n">
+        <v>0.2560306390428618</v>
+      </c>
+      <c r="Z84" t="n">
         <v>110.607240444147</v>
       </c>
-      <c r="V84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
+      <c r="AB84" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X84" t="n">
+      <c r="AC84" t="n">
         <v>40.28371767364471</v>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="AD84" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=40.28% sobre 26 sem</t>
         </is>
@@ -7876,58 +9136,73 @@
         <v>4.117499428134585</v>
       </c>
       <c r="I85" t="n">
+        <v>0.1789730802775152</v>
+      </c>
+      <c r="J85" t="n">
         <v>109.9471447641292</v>
       </c>
-      <c r="J85" t="n">
+      <c r="K85" t="n">
         <v>50.75761225595868</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>4.204387319908268</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
+        <v>0.1827497884230706</v>
+      </c>
+      <c r="N85" t="n">
         <v>191.126671844217</v>
       </c>
-      <c r="M85" t="n">
+      <c r="O85" t="n">
         <v>87.58282274969386</v>
       </c>
-      <c r="N85" t="n">
+      <c r="P85" t="n">
         <v>15.15160288614957</v>
       </c>
-      <c r="O85" t="n">
+      <c r="Q85" t="n">
+        <v>0.658586379186072</v>
+      </c>
+      <c r="R85" t="n">
         <v>122.1180851534335</v>
       </c>
-      <c r="P85" t="n">
+      <c r="S85" t="n">
         <v>105.3105266134953</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="T85" t="n">
         <v>14.84636386491651</v>
       </c>
-      <c r="R85" t="n">
+      <c r="U85" t="n">
+        <v>0.6453187227347572</v>
+      </c>
+      <c r="V85" t="n">
         <v>106.9882513320439</v>
       </c>
-      <c r="S85" t="n">
+      <c r="W85" t="n">
         <v>42.65874933717573</v>
       </c>
-      <c r="T85" t="n">
+      <c r="X85" t="n">
         <v>4.227487013689769</v>
       </c>
-      <c r="U85" t="n">
+      <c r="Y85" t="n">
+        <v>0.1837538500924648</v>
+      </c>
+      <c r="Z85" t="n">
         <v>107.8756984639591</v>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X85" t="n">
+      <c r="AC85" t="n">
         <v>42.65874933717573</v>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="AD85" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=42.66% sobre 26 sem</t>
         </is>
@@ -7965,58 +9240,73 @@
         <v>4.100360487593037</v>
       </c>
       <c r="I86" t="n">
+        <v>0.1753461654456464</v>
+      </c>
+      <c r="J86" t="n">
         <v>160.3842205944857</v>
       </c>
-      <c r="J86" t="n">
+      <c r="K86" t="n">
         <v>127.8983281168288</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>1.868879119234964</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
+        <v>0.07991999440801663</v>
+      </c>
+      <c r="N86" t="n">
         <v>143.9950818237897</v>
       </c>
-      <c r="M86" t="n">
+      <c r="O86" t="n">
         <v>140.7985337554678</v>
       </c>
-      <c r="N86" t="n">
+      <c r="P86" t="n">
         <v>3.01021462564285</v>
       </c>
-      <c r="O86" t="n">
+      <c r="Q86" t="n">
+        <v>0.1287276066023937</v>
+      </c>
+      <c r="R86" t="n">
         <v>178.0725595254285</v>
       </c>
-      <c r="P86" t="n">
+      <c r="S86" t="n">
         <v>172.7754875759728</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="T86" t="n">
         <v>23.67307692307692</v>
       </c>
-      <c r="R86" t="n">
+      <c r="U86" t="n">
+        <v>1.012345932832369</v>
+      </c>
+      <c r="V86" t="n">
         <v>188.4995472315167</v>
       </c>
-      <c r="S86" t="n">
+      <c r="W86" t="n">
         <v>87.65363536216613</v>
       </c>
-      <c r="T86" t="n">
+      <c r="X86" t="n">
         <v>1.307092869748586</v>
       </c>
-      <c r="U86" t="n">
+      <c r="Y86" t="n">
+        <v>0.05589599336089104</v>
+      </c>
+      <c r="Z86" t="n">
         <v>113.2748521774272</v>
       </c>
-      <c r="V86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
+      <c r="AB86" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X86" t="n">
+      <c r="AC86" t="n">
         <v>87.65363536216613</v>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="AD86" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=87.65% sobre 26 sem</t>
         </is>
@@ -8054,58 +9344,73 @@
         <v>1.456561855382656</v>
       </c>
       <c r="I87" t="n">
+        <v>0.1019020099961631</v>
+      </c>
+      <c r="J87" t="n">
         <v>171.410316416684</v>
       </c>
-      <c r="J87" t="n">
+      <c r="K87" t="n">
         <v>151.8452170739236</v>
       </c>
-      <c r="K87" t="n">
+      <c r="L87" t="n">
         <v>0.9569466966124592</v>
       </c>
-      <c r="L87" t="n">
+      <c r="M87" t="n">
+        <v>0.06694861016965171</v>
+      </c>
+      <c r="N87" t="n">
         <v>150.2517475184781</v>
       </c>
-      <c r="M87" t="n">
+      <c r="O87" t="n">
         <v>168.0044364020023</v>
       </c>
-      <c r="N87" t="n">
+      <c r="P87" t="n">
         <v>10.26923076923077</v>
       </c>
-      <c r="O87" t="n">
+      <c r="Q87" t="n">
+        <v>0.7184420302041641</v>
+      </c>
+      <c r="R87" t="n">
         <v>166.9678403273574</v>
       </c>
-      <c r="P87" t="n">
+      <c r="S87" t="n">
         <v>168.0044364020023</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="T87" t="n">
         <v>10.26923076923077</v>
       </c>
-      <c r="R87" t="n">
+      <c r="U87" t="n">
+        <v>0.7184420302041641</v>
+      </c>
+      <c r="V87" t="n">
         <v>191.241827101395</v>
       </c>
-      <c r="S87" t="n">
+      <c r="W87" t="n">
         <v>117.1224183786047</v>
       </c>
-      <c r="T87" t="n">
+      <c r="X87" t="n">
         <v>0.7576229918228641</v>
       </c>
-      <c r="U87" t="n">
+      <c r="Y87" t="n">
+        <v>0.05300379479302941</v>
+      </c>
+      <c r="Z87" t="n">
         <v>108.9238350712686</v>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
+      <c r="AB87" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X87" t="n">
+      <c r="AC87" t="n">
         <v>117.1224183786047</v>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="AD87" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=117.12% sobre 26 sem</t>
         </is>
@@ -8143,58 +9448,73 @@
         <v>2.051713009899168</v>
       </c>
       <c r="I88" t="n">
+        <v>0.1134914715933853</v>
+      </c>
+      <c r="J88" t="n">
         <v>169.0038464611843</v>
       </c>
-      <c r="J88" t="n">
+      <c r="K88" t="n">
         <v>180.4350145751346</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L88" t="n">
         <v>0.9615121828108862</v>
       </c>
-      <c r="L88" t="n">
+      <c r="M88" t="n">
+        <v>0.05318649930846735</v>
+      </c>
+      <c r="N88" t="n">
         <v>118.6804789630648</v>
       </c>
-      <c r="M88" t="n">
+      <c r="O88" t="n">
         <v>165.0245602125755</v>
       </c>
-      <c r="N88" t="n">
+      <c r="P88" t="n">
         <v>2.075674739021522</v>
       </c>
-      <c r="O88" t="n">
+      <c r="Q88" t="n">
+        <v>0.1148169259268603</v>
+      </c>
+      <c r="R88" t="n">
         <v>181.2811328411623</v>
       </c>
-      <c r="P88" t="n">
+      <c r="S88" t="n">
         <v>179.8964312818334</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="T88" t="n">
         <v>13.84615384615385</v>
       </c>
-      <c r="R88" t="n">
+      <c r="U88" t="n">
+        <v>0.7659065221727279</v>
+      </c>
+      <c r="V88" t="n">
         <v>190.1751472740156</v>
       </c>
-      <c r="S88" t="n">
+      <c r="W88" t="n">
         <v>123.5071248811116</v>
       </c>
-      <c r="T88" t="n">
+      <c r="X88" t="n">
         <v>1.131116051777212</v>
       </c>
-      <c r="U88" t="n">
+      <c r="Y88" t="n">
+        <v>0.06256821721153119</v>
+      </c>
+      <c r="Z88" t="n">
         <v>121.3094122928426</v>
       </c>
-      <c r="V88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
+      <c r="AB88" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X88" t="n">
+      <c r="AC88" t="n">
         <v>123.5071248811116</v>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="AD88" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=123.51% sobre 26 sem</t>
         </is>
@@ -8231,53 +9551,58 @@
       <c r="H89" t="n">
         <v>0.1039132270690247</v>
       </c>
-      <c r="I89" t="n">
-        <v>200</v>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>200</v>
       </c>
       <c r="K89" t="n">
+        <v>200</v>
+      </c>
+      <c r="L89" t="n">
         <v>0.007230453015671066</v>
-      </c>
-      <c r="L89" t="n">
-        <v>200</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
+        <v>200</v>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="n">
         <v>0</v>
       </c>
-      <c r="O89" t="n">
-        <v>200</v>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>200</v>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="n">
         <v>0</v>
       </c>
-      <c r="R89" t="n">
-        <v>200</v>
-      </c>
-      <c r="S89" t="n">
-        <v>200</v>
-      </c>
-      <c r="T89" t="n">
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="n">
+        <v>200</v>
+      </c>
+      <c r="W89" t="n">
+        <v>200</v>
+      </c>
+      <c r="X89" t="n">
         <v>7.21227621483376</v>
       </c>
-      <c r="U89" t="n">
-        <v>200</v>
-      </c>
-      <c r="V89" t="inlineStr">
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA89" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr">
+      <c r="AB89" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr">
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -8315,52 +9640,67 @@
         <v>0.09129889207558607</v>
       </c>
       <c r="I90" t="n">
-        <v>200</v>
+        <v>0.01557337178261596</v>
       </c>
       <c r="J90" t="n">
         <v>200</v>
       </c>
       <c r="K90" t="n">
+        <v>200</v>
+      </c>
+      <c r="L90" t="n">
         <v>0.003387767147173362</v>
       </c>
-      <c r="L90" t="n">
-        <v>200</v>
-      </c>
-      <c r="M90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>0.0005778707287289317</v>
+      </c>
       <c r="N90" t="n">
+        <v>200</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
         <v>0</v>
       </c>
-      <c r="O90" t="n">
-        <v>200</v>
-      </c>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>200</v>
       </c>
-      <c r="S90" t="n">
-        <v>200</v>
-      </c>
+      <c r="S90" t="inlineStr"/>
       <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>200</v>
+      </c>
+      <c r="W90" t="n">
+        <v>200</v>
+      </c>
+      <c r="X90" t="n">
         <v>3.199488491048593</v>
       </c>
-      <c r="U90" t="n">
-        <v>200</v>
-      </c>
-      <c r="V90" t="inlineStr">
+      <c r="Y90" t="n">
+        <v>0.5457549664901652</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA90" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
+      <c r="AB90" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr">
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -8398,52 +9738,67 @@
         <v>0.09375575732311482</v>
       </c>
       <c r="I91" t="n">
-        <v>200</v>
+        <v>0.0127450477244676</v>
       </c>
       <c r="J91" t="n">
         <v>200</v>
       </c>
       <c r="K91" t="n">
+        <v>200</v>
+      </c>
+      <c r="L91" t="n">
         <v>0.01353305780754677</v>
       </c>
-      <c r="L91" t="n">
-        <v>200</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0.001839668011221312</v>
+      </c>
       <c r="N91" t="n">
+        <v>200</v>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="n">
         <v>0</v>
       </c>
-      <c r="O91" t="n">
-        <v>200</v>
-      </c>
-      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>200</v>
       </c>
-      <c r="S91" t="n">
-        <v>200</v>
-      </c>
+      <c r="S91" t="inlineStr"/>
       <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>200</v>
+      </c>
+      <c r="W91" t="n">
+        <v>200</v>
+      </c>
+      <c r="X91" t="n">
         <v>2.502257439865562e-17</v>
       </c>
-      <c r="U91" t="n">
-        <v>200</v>
-      </c>
-      <c r="V91" t="inlineStr">
+      <c r="Y91" t="n">
+        <v>3.401539425475701e-18</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA91" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
+      <c r="AB91" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr">
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr">
         <is>
           <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -8481,58 +9836,73 @@
         <v>8.327145552672791</v>
       </c>
       <c r="I92" t="n">
+        <v>0.06902975433540473</v>
+      </c>
+      <c r="J92" t="n">
         <v>49.15109590531281</v>
       </c>
-      <c r="J92" t="n">
+      <c r="K92" t="n">
         <v>51.27271043422916</v>
       </c>
-      <c r="K92" t="n">
+      <c r="L92" t="n">
         <v>8.504691706163086</v>
       </c>
-      <c r="L92" t="n">
+      <c r="M92" t="n">
+        <v>0.07050156328615584</v>
+      </c>
+      <c r="N92" t="n">
         <v>104.6459551741298</v>
       </c>
-      <c r="M92" t="n">
+      <c r="O92" t="n">
         <v>143.8102183858536</v>
       </c>
-      <c r="N92" t="n">
+      <c r="P92" t="n">
         <v>95.98543158524623</v>
       </c>
-      <c r="O92" t="n">
+      <c r="Q92" t="n">
+        <v>0.7956929202445158</v>
+      </c>
+      <c r="R92" t="n">
         <v>118.9713689353267</v>
       </c>
-      <c r="P92" t="n">
+      <c r="S92" t="n">
         <v>88.12288395195948</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="T92" t="n">
         <v>31.66390403140978</v>
       </c>
-      <c r="R92" t="n">
+      <c r="U92" t="n">
+        <v>0.262485086007231</v>
+      </c>
+      <c r="V92" t="n">
         <v>92.01416331532587</v>
       </c>
-      <c r="S92" t="n">
+      <c r="W92" t="n">
         <v>37.67464475879304</v>
       </c>
-      <c r="T92" t="n">
+      <c r="X92" t="n">
         <v>7.406895854835166</v>
       </c>
-      <c r="U92" t="n">
+      <c r="Y92" t="n">
+        <v>0.06140113656150596</v>
+      </c>
+      <c r="Z92" t="n">
         <v>95.83480509856771</v>
       </c>
-      <c r="V92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr">
+      <c r="AB92" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X92" t="n">
+      <c r="AC92" t="n">
         <v>37.67464475879304</v>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="AD92" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=37.67% sobre 26 sem</t>
         </is>
@@ -8570,58 +9940,73 @@
         <v>3.862865777081154</v>
       </c>
       <c r="I93" t="n">
+        <v>0.06613434533550744</v>
+      </c>
+      <c r="J93" t="n">
         <v>60.93105560683724</v>
       </c>
-      <c r="J93" t="n">
+      <c r="K93" t="n">
         <v>57.67261314686925</v>
       </c>
-      <c r="K93" t="n">
+      <c r="L93" t="n">
         <v>6.51001922416303</v>
       </c>
-      <c r="L93" t="n">
+      <c r="M93" t="n">
+        <v>0.1114550399514296</v>
+      </c>
+      <c r="N93" t="n">
         <v>89.5280086489867</v>
       </c>
-      <c r="M93" t="n">
+      <c r="O93" t="n">
         <v>139.1563622088194</v>
       </c>
-      <c r="N93" t="n">
+      <c r="P93" t="n">
         <v>43.02895105926984</v>
       </c>
-      <c r="O93" t="n">
+      <c r="Q93" t="n">
+        <v>0.7366788475183966</v>
+      </c>
+      <c r="R93" t="n">
         <v>121.8694023763068</v>
       </c>
-      <c r="P93" t="n">
+      <c r="S93" t="n">
         <v>95.74384653120181</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="T93" t="n">
         <v>17.24488657444334</v>
       </c>
-      <c r="R93" t="n">
+      <c r="U93" t="n">
+        <v>0.2952417582698555</v>
+      </c>
+      <c r="V93" t="n">
         <v>96.01849856237216</v>
       </c>
-      <c r="S93" t="n">
+      <c r="W93" t="n">
         <v>36.62559731227307</v>
       </c>
-      <c r="T93" t="n">
+      <c r="X93" t="n">
         <v>2.9917584455536</v>
       </c>
-      <c r="U93" t="n">
+      <c r="Y93" t="n">
+        <v>0.05122051803419571</v>
+      </c>
+      <c r="Z93" t="n">
         <v>99.35850993844542</v>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
+      <c r="AB93" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X93" t="n">
+      <c r="AC93" t="n">
         <v>36.62559731227307</v>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="AD93" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=36.63% sobre 26 sem</t>
         </is>
@@ -8659,58 +10044,73 @@
         <v>4.370402940003936</v>
       </c>
       <c r="I94" t="n">
+        <v>0.05855750704690615</v>
+      </c>
+      <c r="J94" t="n">
         <v>64.07712599234655</v>
       </c>
-      <c r="J94" t="n">
+      <c r="K94" t="n">
         <v>67.50136305395694</v>
       </c>
-      <c r="K94" t="n">
+      <c r="L94" t="n">
         <v>5.808354629419098</v>
       </c>
-      <c r="L94" t="n">
+      <c r="M94" t="n">
+        <v>0.07782412098204208</v>
+      </c>
+      <c r="N94" t="n">
         <v>91.94886769427217</v>
       </c>
-      <c r="M94" t="n">
+      <c r="O94" t="n">
         <v>142.4143174612214</v>
       </c>
-      <c r="N94" t="n">
+      <c r="P94" t="n">
         <v>46.01139013859893</v>
       </c>
-      <c r="O94" t="n">
+      <c r="Q94" t="n">
+        <v>0.6164905934912556</v>
+      </c>
+      <c r="R94" t="n">
         <v>120.3184691119026</v>
       </c>
-      <c r="P94" t="n">
+      <c r="S94" t="n">
         <v>94.85079297405257</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="T94" t="n">
         <v>18.52912014414084</v>
       </c>
-      <c r="R94" t="n">
+      <c r="U94" t="n">
+        <v>0.2482652282428953</v>
+      </c>
+      <c r="V94" t="n">
         <v>95.82311990464228</v>
       </c>
-      <c r="S94" t="n">
+      <c r="W94" t="n">
         <v>39.84205949425877</v>
       </c>
-      <c r="T94" t="n">
+      <c r="X94" t="n">
         <v>4.219821617011154</v>
       </c>
-      <c r="U94" t="n">
+      <c r="Y94" t="n">
+        <v>0.0565399203384654</v>
+      </c>
+      <c r="Z94" t="n">
         <v>93.11495456228404</v>
       </c>
-      <c r="V94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
+      <c r="AB94" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X94" t="n">
+      <c r="AC94" t="n">
         <v>39.84205949425877</v>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="AD94" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=39.84% sobre 26 sem</t>
         </is>
@@ -8748,58 +10148,73 @@
         <v>0.6583240568762944</v>
       </c>
       <c r="I95" t="n">
+        <v>0.009399593887221766</v>
+      </c>
+      <c r="J95" t="n">
         <v>152.3875262412586</v>
       </c>
-      <c r="J95" t="n">
+      <c r="K95" t="n">
         <v>199.3241646511038</v>
       </c>
-      <c r="K95" t="n">
+      <c r="L95" t="n">
         <v>0.5753658334003174</v>
       </c>
-      <c r="L95" t="n">
+      <c r="M95" t="n">
+        <v>0.008215110953422346</v>
+      </c>
+      <c r="N95" t="n">
         <v>128.1095321097334</v>
       </c>
-      <c r="M95" t="n">
-        <v>200</v>
-      </c>
-      <c r="N95" t="n">
+      <c r="O95" t="n">
+        <v>200</v>
+      </c>
+      <c r="P95" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="O95" t="n">
+      <c r="Q95" t="n">
+        <v>0.008237345378162798</v>
+      </c>
+      <c r="R95" t="n">
         <v>189.619699057401</v>
       </c>
-      <c r="P95" t="n">
+      <c r="S95" t="n">
         <v>170.6805922247819</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="T95" t="n">
         <v>3.041462706179588</v>
       </c>
-      <c r="R95" t="n">
+      <c r="U95" t="n">
+        <v>0.04342620319371177</v>
+      </c>
+      <c r="V95" t="n">
         <v>118.2821915164861</v>
       </c>
-      <c r="S95" t="n">
+      <c r="W95" t="n">
         <v>151.5302584151449</v>
       </c>
-      <c r="T95" t="n">
+      <c r="X95" t="n">
         <v>1.552458663105297</v>
       </c>
-      <c r="U95" t="n">
+      <c r="Y95" t="n">
+        <v>0.02216610620175331</v>
+      </c>
+      <c r="Z95" t="n">
         <v>128.8999217807187</v>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>Prophet</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="AB95" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X95" t="n">
+      <c r="AC95" t="n">
         <v>144.6453651559676</v>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="AD95" t="inlineStr">
         <is>
           <t>Prophet: menor SMAPE real=144.65% sobre 26 sem</t>
         </is>
@@ -8837,56 +10252,71 @@
         <v>0.2981965736936112</v>
       </c>
       <c r="I96" t="n">
+        <v>0.009060283287310634</v>
+      </c>
+      <c r="J96" t="n">
         <v>158.9896824444987</v>
       </c>
-      <c r="J96" t="n">
+      <c r="K96" t="n">
         <v>199.4502738784551</v>
       </c>
-      <c r="K96" t="n">
+      <c r="L96" t="n">
         <v>0.1542300177840033</v>
       </c>
-      <c r="L96" t="n">
+      <c r="M96" t="n">
+        <v>0.004686062067117457</v>
+      </c>
+      <c r="N96" t="n">
         <v>189.1617640516506</v>
       </c>
-      <c r="M96" t="n">
+      <c r="O96" t="n">
         <v>195.7774133191963</v>
       </c>
-      <c r="N96" t="n">
+      <c r="P96" t="n">
         <v>1.776959200108318</v>
       </c>
-      <c r="O96" t="n">
+      <c r="Q96" t="n">
+        <v>0.05399040486466595</v>
+      </c>
+      <c r="R96" t="n">
         <v>127.6499599586913</v>
       </c>
-      <c r="P96" t="n">
+      <c r="S96" t="n">
         <v>182.6873255227291</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="T96" t="n">
         <v>2.906151396101761</v>
       </c>
-      <c r="R96" t="n">
+      <c r="U96" t="n">
+        <v>0.08829932080825706</v>
+      </c>
+      <c r="V96" t="n">
         <v>124.4459476108536</v>
       </c>
-      <c r="S96" t="n">
+      <c r="W96" t="n">
         <v>180.5351894338612</v>
       </c>
-      <c r="T96" t="n">
+      <c r="X96" t="n">
         <v>0.9586028878180607</v>
       </c>
-      <c r="U96" t="n">
+      <c r="Y96" t="n">
+        <v>0.02912579985774586</v>
+      </c>
+      <c r="Z96" t="n">
         <v>151.8363274594118</v>
       </c>
-      <c r="V96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
+      <c r="AB96" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr">
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
@@ -8924,58 +10354,73 @@
         <v>0.4505051113538389</v>
       </c>
       <c r="I97" t="n">
+        <v>0.01203151691146957</v>
+      </c>
+      <c r="J97" t="n">
         <v>157.2976315063829</v>
       </c>
-      <c r="J97" t="n">
+      <c r="K97" t="n">
         <v>199.4351970061328</v>
       </c>
-      <c r="K97" t="n">
+      <c r="L97" t="n">
         <v>0.4253306195534445</v>
       </c>
-      <c r="L97" t="n">
+      <c r="M97" t="n">
+        <v>0.01135918863771509</v>
+      </c>
+      <c r="N97" t="n">
         <v>187.1093440450062</v>
       </c>
-      <c r="M97" t="n">
+      <c r="O97" t="n">
         <v>148.8155072683896</v>
       </c>
-      <c r="N97" t="n">
+      <c r="P97" t="n">
         <v>1.556585907936096</v>
       </c>
-      <c r="O97" t="n">
+      <c r="Q97" t="n">
+        <v>0.04157131451673767</v>
+      </c>
+      <c r="R97" t="n">
         <v>126.5693936023772</v>
       </c>
-      <c r="P97" t="n">
+      <c r="S97" t="n">
         <v>170.2653323059756</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="T97" t="n">
         <v>1.965202821222686</v>
       </c>
-      <c r="R97" t="n">
+      <c r="U97" t="n">
+        <v>0.05248413476809043</v>
+      </c>
+      <c r="V97" t="n">
         <v>128.4785456608675</v>
       </c>
-      <c r="S97" t="n">
+      <c r="W97" t="n">
         <v>153.558624927868</v>
       </c>
-      <c r="T97" t="n">
+      <c r="X97" t="n">
         <v>0.8518205666403911</v>
       </c>
-      <c r="U97" t="n">
+      <c r="Y97" t="n">
+        <v>0.02274933911908906</v>
+      </c>
+      <c r="Z97" t="n">
         <v>136.0400571203446</v>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>NBGLM</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>smape_real</t>
         </is>
       </c>
-      <c r="X97" t="n">
+      <c r="AC97" t="n">
         <v>153.558624927868</v>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>NBGLM: menor SMAPE real=153.56% sobre 26 sem</t>
         </is>
@@ -9013,54 +10458,69 @@
         <v>0.05584897214567642</v>
       </c>
       <c r="I98" t="n">
+        <v>0.04195227954604801</v>
+      </c>
+      <c r="J98" t="n">
         <v>198.585723184526</v>
       </c>
-      <c r="J98" t="n">
-        <v>200</v>
-      </c>
       <c r="K98" t="n">
+        <v>200</v>
+      </c>
+      <c r="L98" t="n">
         <v>0.0005257727496187077</v>
       </c>
-      <c r="L98" t="n">
+      <c r="M98" t="n">
+        <v>0.0003949466663802499</v>
+      </c>
+      <c r="N98" t="n">
         <v>199.9898962083731</v>
       </c>
-      <c r="M98" t="n">
-        <v>200</v>
-      </c>
-      <c r="N98" t="n">
+      <c r="O98" t="n">
+        <v>200</v>
+      </c>
+      <c r="P98" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="O98" t="n">
+      <c r="Q98" t="n">
+        <v>0.5200433369447454</v>
+      </c>
+      <c r="R98" t="n">
         <v>199.2030987655621</v>
       </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="n">
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="n">
         <v>0</v>
       </c>
-      <c r="R98" t="n">
-        <v>200</v>
-      </c>
-      <c r="S98" t="n">
-        <v>200</v>
-      </c>
-      <c r="T98" t="n">
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>200</v>
+      </c>
+      <c r="W98" t="n">
+        <v>200</v>
+      </c>
+      <c r="X98" t="n">
         <v>0.05238370102220309</v>
       </c>
-      <c r="U98" t="n">
+      <c r="Y98" t="n">
+        <v>0.03934925898381453</v>
+      </c>
+      <c r="Z98" t="n">
         <v>199.9999998548883</v>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
+      <c r="AB98" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr">
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -9098,54 +10558,69 @@
         <v>0.0321776493972341</v>
       </c>
       <c r="I99" t="n">
+        <v>0.04974322612132808</v>
+      </c>
+      <c r="J99" t="n">
         <v>198.7380283178126</v>
       </c>
-      <c r="J99" t="n">
-        <v>200</v>
-      </c>
       <c r="K99" t="n">
+        <v>200</v>
+      </c>
+      <c r="L99" t="n">
         <v>0.001656036062763181</v>
       </c>
-      <c r="L99" t="n">
+      <c r="M99" t="n">
+        <v>0.00256005574919912</v>
+      </c>
+      <c r="N99" t="n">
         <v>199.9983019911245</v>
       </c>
-      <c r="M99" t="n">
-        <v>200</v>
-      </c>
-      <c r="N99" t="n">
+      <c r="O99" t="n">
+        <v>200</v>
+      </c>
+      <c r="P99" t="n">
         <v>0.4409654044720926</v>
       </c>
-      <c r="O99" t="n">
+      <c r="Q99" t="n">
+        <v>0.6816856494254572</v>
+      </c>
+      <c r="R99" t="n">
         <v>198.5022493653877</v>
       </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="n">
         <v>0</v>
       </c>
-      <c r="R99" t="n">
-        <v>200</v>
-      </c>
-      <c r="S99" t="n">
-        <v>200</v>
-      </c>
-      <c r="T99" t="n">
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>200</v>
+      </c>
+      <c r="W99" t="n">
+        <v>200</v>
+      </c>
+      <c r="X99" t="n">
         <v>0.04163218264949037</v>
       </c>
-      <c r="U99" t="n">
-        <v>200</v>
-      </c>
-      <c r="V99" t="inlineStr">
+      <c r="Y99" t="n">
+        <v>0.06435892969969527</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA99" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W99" t="inlineStr">
+      <c r="AB99" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr">
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
@@ -9183,54 +10658,69 @@
         <v>0.05279450630904018</v>
       </c>
       <c r="I100" t="n">
-        <v>200</v>
+        <v>0.07068720509997012</v>
       </c>
       <c r="J100" t="n">
         <v>200</v>
       </c>
       <c r="K100" t="n">
+        <v>200</v>
+      </c>
+      <c r="L100" t="n">
         <v>0.002392263610996015</v>
       </c>
-      <c r="L100" t="n">
-        <v>200</v>
-      </c>
       <c r="M100" t="n">
-        <v>200</v>
+        <v>0.003203030776228975</v>
       </c>
       <c r="N100" t="n">
+        <v>200</v>
+      </c>
+      <c r="O100" t="n">
+        <v>200</v>
+      </c>
+      <c r="P100" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="O100" t="n">
-        <v>200</v>
-      </c>
-      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
+        <v>0.2317347924042485</v>
+      </c>
+      <c r="R100" t="n">
+        <v>200</v>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="n">
         <v>0</v>
       </c>
-      <c r="R100" t="n">
+      <c r="U100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="n">
-        <v>200</v>
-      </c>
-      <c r="T100" t="n">
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>200</v>
+      </c>
+      <c r="X100" t="n">
         <v>0.0202913101091679</v>
       </c>
-      <c r="U100" t="n">
-        <v>200</v>
-      </c>
-      <c r="V100" t="inlineStr">
+      <c r="Y100" t="n">
+        <v>0.02716828131771434</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA100" t="inlineStr">
         <is>
           <t>DeepAR</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
+      <c r="AB100" t="inlineStr">
         <is>
           <t>mae_real_casi_cero</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr">
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr">
         <is>
           <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -600,67 +600,67 @@
         <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2006674831338297</v>
+        <v>0.5072451520493191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01004121885892502</v>
+        <v>0.02538208735821456</v>
       </c>
       <c r="J2" t="n">
         <v>185.8333489727328</v>
       </c>
       <c r="K2" t="n">
-        <v>197.4073596888732</v>
+        <v>185.2980944031261</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1951254343367843</v>
+        <v>0.3423955968242271</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009763899763529472</v>
+        <v>0.01713316512646641</v>
       </c>
       <c r="N2" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O2" t="n">
-        <v>155.6923076923077</v>
+        <v>142.4564622417932</v>
       </c>
       <c r="P2" t="n">
-        <v>0.75</v>
+        <v>1.366666666666667</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03752931978107897</v>
+        <v>0.06838676048996611</v>
       </c>
       <c r="R2" t="n">
         <v>197.8088169752323</v>
       </c>
       <c r="S2" t="n">
-        <v>155.6923076923077</v>
+        <v>142.4564622417932</v>
       </c>
       <c r="T2" t="n">
-        <v>0.75</v>
+        <v>1.366666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03752931978107897</v>
+        <v>0.06838676048996611</v>
       </c>
       <c r="V2" t="n">
         <v>199.5572761277739</v>
       </c>
       <c r="W2" t="n">
-        <v>184.0794920386864</v>
+        <v>166.8873519190716</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1760121898273306</v>
+        <v>0.2244707512531855</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008807490343197154</v>
+        <v>0.01123231280703977</v>
       </c>
       <c r="Z2" t="n">
         <v>194.9779461019607</v>
@@ -672,13 +672,15 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>166.8873519190716</v>
+      </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>NBGLM: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=166.89% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -702,74 +704,74 @@
         <v>2026</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>199.7803928247721</v>
+        <v>199.8117652783761</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1229909956009693</v>
+        <v>0.23992552952084</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01348308276543685</v>
+        <v>0.02630221632294238</v>
       </c>
       <c r="J3" t="n">
         <v>157.2321783542833</v>
       </c>
       <c r="K3" t="n">
-        <v>197.2796288638902</v>
+        <v>184.4705655017831</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1214219715065594</v>
+        <v>0.1781083907603099</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01331107601305208</v>
+        <v>0.019525414540356</v>
       </c>
       <c r="N3" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O3" t="n">
-        <v>183.3333333333333</v>
+        <v>165.1021493126756</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03583946029989196</v>
+        <v>0.08221993833504626</v>
       </c>
       <c r="R3" t="n">
         <v>197.8854209931308</v>
       </c>
       <c r="S3" t="n">
-        <v>183.3333333333333</v>
+        <v>165.1021493126756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03583946029989196</v>
+        <v>0.08221993833504626</v>
       </c>
       <c r="V3" t="n">
         <v>199.636475467609</v>
       </c>
       <c r="W3" t="n">
-        <v>187.0830627946073</v>
+        <v>185.2923057680258</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09806476296935614</v>
+        <v>1.952122269565353</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01075050501890852</v>
+        <v>0.2140044968348451</v>
       </c>
       <c r="Z3" t="n">
         <v>198.5158836242873</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -780,7 +782,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>NBGLM: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -804,74 +806,74 @@
         <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0872286621725092</v>
+        <v>0.2755981738828413</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00757686533528853</v>
+        <v>0.02393903790513279</v>
       </c>
       <c r="J4" t="n">
         <v>158.5580779411727</v>
       </c>
       <c r="K4" t="n">
-        <v>191.1760450805634</v>
+        <v>181.5672899011693</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1792257312452026</v>
+        <v>0.3068804105213799</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01556792453812835</v>
+        <v>0.02665627887264973</v>
       </c>
       <c r="N4" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O4" t="n">
-        <v>160</v>
+        <v>150.6293706293706</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04343105320304018</v>
+        <v>0.06514657980456026</v>
       </c>
       <c r="R4" t="n">
         <v>197.7265973322816</v>
       </c>
       <c r="S4" t="n">
-        <v>160</v>
+        <v>150.6293706293706</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0.04343105320304018</v>
+        <v>0.06514657980456026</v>
       </c>
       <c r="V4" t="n">
         <v>199.5859359679221</v>
       </c>
       <c r="W4" t="n">
-        <v>192.0311816113775</v>
+        <v>176.562581332529</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1242171289414107</v>
+        <v>0.1817109824281797</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01078976147156662</v>
+        <v>0.01578379869082994</v>
       </c>
       <c r="Z4" t="n">
         <v>196.9436529554095</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -882,7 +884,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>NBGLM: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -906,31 +908,31 @@
         <v>2026</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>199.1344570193647</v>
+        <v>199.3652684808674</v>
       </c>
       <c r="H5" t="n">
-        <v>0.194717393070758</v>
+        <v>0.1710356971411547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.240577474064257</v>
+        <v>0.2113182358500753</v>
       </c>
       <c r="J5" t="n">
         <v>175.1088701866436</v>
       </c>
       <c r="K5" t="n">
-        <v>199.1789075403633</v>
+        <v>199.2883865349815</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2029091662089284</v>
+        <v>0.1778404880304248</v>
       </c>
       <c r="M5" t="n">
-        <v>0.250698583733039</v>
+        <v>0.21972569949705</v>
       </c>
       <c r="N5" t="n">
         <v>109.609711216533</v>
@@ -939,10 +941,10 @@
         <v>200</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3801603801603802</v>
+        <v>0.3294723294723295</v>
       </c>
       <c r="R5" t="n">
         <v>187.2707284786031</v>
@@ -951,22 +953,22 @@
         <v>200</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3801603801603802</v>
+        <v>0.3294723294723295</v>
       </c>
       <c r="V5" t="n">
         <v>193.7972259177366</v>
       </c>
       <c r="W5" t="n">
-        <v>199.4340125103117</v>
+        <v>199.5094775089368</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2029541892643015</v>
+        <v>0.1773081327790403</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2507542106740405</v>
+        <v>0.2190679632791232</v>
       </c>
       <c r="Z5" t="n">
         <v>187.0400639517023</v>
@@ -1008,31 +1010,31 @@
         <v>2026</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>199.5546454208607</v>
+        <v>199.60071658422</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08444375875288576</v>
+        <v>0.07333931411793927</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05749362298068818</v>
+        <v>0.04993315003774589</v>
       </c>
       <c r="J6" t="n">
         <v>191.646475967384</v>
       </c>
       <c r="K6" t="n">
-        <v>199.9795881412977</v>
+        <v>199.982309722458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0776408859315368</v>
+        <v>0.0674159383528599</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05286187978317399</v>
+        <v>0.04590021334662802</v>
       </c>
       <c r="N6" t="n">
         <v>79.54507935933471</v>
@@ -1041,10 +1043,10 @@
         <v>200</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.09165302782324058</v>
+        <v>0.07943262411347518</v>
       </c>
       <c r="R6" t="n">
         <v>192.53013744135</v>
@@ -1053,22 +1055,22 @@
         <v>200</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1346153846153846</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09165302782324058</v>
+        <v>0.07943262411347518</v>
       </c>
       <c r="V6" t="n">
         <v>193.2139428195562</v>
       </c>
       <c r="W6" t="n">
-        <v>198.5786411733137</v>
+        <v>199.0159823507556</v>
       </c>
       <c r="X6" t="n">
-        <v>0.08214655428525444</v>
+        <v>0.07119368038055386</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.05592956887506685</v>
+        <v>0.04847229302505795</v>
       </c>
       <c r="Z6" t="n">
         <v>198.9985835834048</v>
@@ -1110,31 +1112,31 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>198.6610533081308</v>
+        <v>198.8457356104576</v>
       </c>
       <c r="H7" t="n">
-        <v>0.134291957686018</v>
+        <v>0.1218664864738857</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07972806393232978</v>
+        <v>0.07235116080082271</v>
       </c>
       <c r="J7" t="n">
         <v>186.9197740801393</v>
       </c>
       <c r="K7" t="n">
-        <v>199.9807829565354</v>
+        <v>199.9833452289974</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1157850864840191</v>
+        <v>0.1004020992957013</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06874068214264582</v>
+        <v>0.05960792537036072</v>
       </c>
       <c r="N7" t="n">
         <v>109.7635513825217</v>
@@ -1143,10 +1145,10 @@
         <v>200</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1730769230769231</v>
+        <v>0.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1027543884686742</v>
+        <v>0.08905380333951762</v>
       </c>
       <c r="R7" t="n">
         <v>185.3187572725189</v>
@@ -1155,22 +1157,22 @@
         <v>200</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1730769230769231</v>
+        <v>0.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1027543884686742</v>
+        <v>0.08905380333951762</v>
       </c>
       <c r="V7" t="n">
         <v>190.8625800946274</v>
       </c>
       <c r="W7" t="n">
-        <v>199.8339639128756</v>
+        <v>199.8561020578255</v>
       </c>
       <c r="X7" t="n">
-        <v>0.127880876000855</v>
+        <v>0.110837566833549</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0759218558817692</v>
+        <v>0.06580337919617009</v>
       </c>
       <c r="Z7" t="n">
         <v>197.3279694158802</v>
@@ -1212,67 +1214,67 @@
         <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F8" t="n">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G8" t="n">
-        <v>97.22491608385673</v>
+        <v>92.27883215001214</v>
       </c>
       <c r="H8" t="n">
-        <v>4.842719830400823</v>
+        <v>4.580452151583914</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3045735742390455</v>
+        <v>0.2880787516719443</v>
       </c>
       <c r="J8" t="n">
         <v>154.5040916050135</v>
       </c>
       <c r="K8" t="n">
-        <v>66.09321580505865</v>
+        <v>75.36878373383229</v>
       </c>
       <c r="L8" t="n">
-        <v>6.379512625221059</v>
+        <v>7.945027821912805</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4012272091333999</v>
+        <v>0.4996872843970318</v>
       </c>
       <c r="N8" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O8" t="n">
-        <v>94.35475689730009</v>
+        <v>100.6652716966206</v>
       </c>
       <c r="P8" t="n">
-        <v>14.71153846153846</v>
+        <v>19.20543948854522</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9252539912917271</v>
+        <v>1.207889276009134</v>
       </c>
       <c r="R8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="S8" t="n">
-        <v>94.35475689730009</v>
+        <v>100.9187941761143</v>
       </c>
       <c r="T8" t="n">
-        <v>14.71153846153846</v>
+        <v>20.13333333333333</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9252539912917271</v>
+        <v>1.266247379454926</v>
       </c>
       <c r="V8" t="n">
         <v>172.894287988784</v>
       </c>
       <c r="W8" t="n">
-        <v>60.16199655312483</v>
+        <v>68.51901851641311</v>
       </c>
       <c r="X8" t="n">
-        <v>3.27268470603121</v>
+        <v>4.860772940984292</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2058292267944157</v>
+        <v>0.3057089899990121</v>
       </c>
       <c r="Z8" t="n">
         <v>111.5676388698673</v>
@@ -1288,11 +1290,11 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>60.16199655312483</v>
+        <v>68.51901851641311</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=60.16% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=68.52% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -1316,67 +1318,67 @@
         <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F9" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G9" t="n">
-        <v>91.2579130376192</v>
+        <v>88.28084364582529</v>
       </c>
       <c r="H9" t="n">
-        <v>2.184156444835504</v>
+        <v>2.008305808530846</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2712184952841915</v>
+        <v>0.2493821725765894</v>
       </c>
       <c r="J9" t="n">
         <v>164.086229256472</v>
       </c>
       <c r="K9" t="n">
-        <v>81.59982771449211</v>
+        <v>94.10648776806431</v>
       </c>
       <c r="L9" t="n">
-        <v>3.552656265560343</v>
+        <v>5.749642108989677</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4411525048425727</v>
+        <v>0.7139640958000375</v>
       </c>
       <c r="N9" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O9" t="n">
-        <v>103.0533505779254</v>
+        <v>109.3048230261212</v>
       </c>
       <c r="P9" t="n">
-        <v>7.346153846153846</v>
+        <v>9.816666666666666</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9122115757738575</v>
+        <v>1.218988487905834</v>
       </c>
       <c r="R9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="S9" t="n">
-        <v>103.0533505779254</v>
+        <v>109.3048230261212</v>
       </c>
       <c r="T9" t="n">
-        <v>7.346153846153846</v>
+        <v>9.816666666666666</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9122115757738575</v>
+        <v>1.218988487905834</v>
       </c>
       <c r="V9" t="n">
         <v>176.8647517474977</v>
       </c>
       <c r="W9" t="n">
-        <v>57.53807472706776</v>
+        <v>69.2678850224322</v>
       </c>
       <c r="X9" t="n">
-        <v>1.39801286411231</v>
+        <v>2.265436255273298</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1735988034598134</v>
+        <v>0.2813114480742939</v>
       </c>
       <c r="Z9" t="n">
         <v>121.2492629006552</v>
@@ -1392,11 +1394,11 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>57.53807472706776</v>
+        <v>69.2678850224322</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=57.54% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=69.27% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -1420,67 +1422,67 @@
         <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G10" t="n">
-        <v>90.90668407086</v>
+        <v>88.19035827372585</v>
       </c>
       <c r="H10" t="n">
-        <v>2.459546181486654</v>
+        <v>2.421405704540458</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2983528347519823</v>
+        <v>0.2937262416425119</v>
       </c>
       <c r="J10" t="n">
         <v>164.4874496413386</v>
       </c>
       <c r="K10" t="n">
-        <v>80.62136290545641</v>
+        <v>92.59928882647066</v>
       </c>
       <c r="L10" t="n">
-        <v>1.954195725687168</v>
+        <v>2.109625130989282</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2370517938665254</v>
+        <v>0.2559060052754246</v>
       </c>
       <c r="N10" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O10" t="n">
-        <v>98.21286575944892</v>
+        <v>103.7999683567414</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>10.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9704321455648218</v>
+        <v>1.32221379833207</v>
       </c>
       <c r="R10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="S10" t="n">
-        <v>98.21286575944892</v>
+        <v>103.7999683567414</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>10.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9704321455648218</v>
+        <v>1.32221379833207</v>
       </c>
       <c r="V10" t="n">
         <v>168.5443712458804</v>
       </c>
       <c r="W10" t="n">
-        <v>65.3176995141846</v>
+        <v>72.49824933557935</v>
       </c>
       <c r="X10" t="n">
-        <v>1.888960773953696</v>
+        <v>2.77295675433941</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2291385320944589</v>
+        <v>0.3363707965840073</v>
       </c>
       <c r="Z10" t="n">
         <v>114.746491150853</v>
@@ -1496,11 +1498,11 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>65.3176995141846</v>
+        <v>72.49824933557935</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=65.32% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=72.50% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -1524,67 +1526,67 @@
         <v>2026</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>181.515507584439</v>
+        <v>183.1228547510095</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6173266662411392</v>
+        <v>0.6350164440756541</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03931234491485861</v>
+        <v>0.04043885813019091</v>
       </c>
       <c r="J11" t="n">
         <v>123.2554563734294</v>
       </c>
       <c r="K11" t="n">
-        <v>198.496465086452</v>
+        <v>197.4346585076968</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6359759888102187</v>
+        <v>0.6552399939771771</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04049996346652139</v>
+        <v>0.04172672598461626</v>
       </c>
       <c r="N11" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O11" t="n">
-        <v>181.3852359729555</v>
+        <v>179.4915595150547</v>
       </c>
       <c r="P11" t="n">
-        <v>23.063540985444</v>
+        <v>20.7384021873848</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.468723008028274</v>
+        <v>1.320654467654355</v>
       </c>
       <c r="R11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="S11" t="n">
-        <v>166.0092425476692</v>
+        <v>169.2464575431293</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9921050187942237</v>
+        <v>0.9598243496216606</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06317882706749285</v>
+        <v>0.06112314266247391</v>
       </c>
       <c r="V11" t="n">
         <v>177.781032308345</v>
       </c>
       <c r="W11" t="n">
-        <v>123.5450259718557</v>
+        <v>123.7678316346247</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7176289557794688</v>
+        <v>0.8267959529168735</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.04569975439789652</v>
+        <v>0.05265168257381084</v>
       </c>
       <c r="Z11" t="n">
         <v>147.9725418621825</v>
@@ -1600,11 +1602,11 @@
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>123.5450259718557</v>
+        <v>123.7678316346247</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=123.55% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=123.77% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -1628,85 +1630,87 @@
         <v>2026</v>
       </c>
       <c r="E12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>192.5956874696411</v>
+        <v>193.2127135138377</v>
       </c>
       <c r="H12" t="n">
-        <v>0.351300905032329</v>
+        <v>0.3377941176946851</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04415408075818747</v>
+        <v>0.04245644841410025</v>
       </c>
       <c r="J12" t="n">
         <v>147.3485671696691</v>
       </c>
       <c r="K12" t="n">
-        <v>199.6235849176428</v>
+        <v>193.6955061779731</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4164095901696</v>
+        <v>0.4970911410202871</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05233741903152867</v>
+        <v>0.06247806957049956</v>
       </c>
       <c r="N12" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O12" t="n">
-        <v>187.6610978466063</v>
+        <v>186.8820423761497</v>
       </c>
       <c r="P12" t="n">
-        <v>10.67195884484822</v>
+        <v>9.665697665535125</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.341330255440468</v>
+        <v>1.214855951677628</v>
       </c>
       <c r="R12" t="n">
         <v>191.4723960783834</v>
       </c>
       <c r="S12" t="n">
-        <v>183.7041303456979</v>
+        <v>185.5844229981174</v>
       </c>
       <c r="T12" t="n">
-        <v>9.46877517918894</v>
+        <v>8.362726471706072</v>
       </c>
       <c r="U12" t="n">
-        <v>1.190105285679678</v>
+        <v>1.051088951667692</v>
       </c>
       <c r="V12" t="n">
         <v>189.6908701459495</v>
       </c>
       <c r="W12" t="n">
-        <v>163.8231047633718</v>
+        <v>162.4467540726264</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5920824067350805</v>
+        <v>0.6511809055943154</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.07441727028877682</v>
+        <v>0.08184520415953689</v>
       </c>
       <c r="Z12" t="n">
         <v>169.7722333133142</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>162.4467540726264</v>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=162.45% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -1730,67 +1734,67 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>196.5301539342985</v>
+        <v>197.0258462293987</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2736267513739156</v>
+        <v>0.3038098511907269</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02957128012146336</v>
+        <v>0.03283321593415488</v>
       </c>
       <c r="J13" t="n">
         <v>157.1522264328246</v>
       </c>
       <c r="K13" t="n">
-        <v>199.8277670092382</v>
+        <v>199.7826415765892</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2703163975234029</v>
+        <v>0.3009092622820653</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02921352489276897</v>
+        <v>0.03251974465729851</v>
       </c>
       <c r="N13" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O13" t="n">
-        <v>183.5601864370778</v>
+        <v>179.8421375938333</v>
       </c>
       <c r="P13" t="n">
-        <v>12.43617814849466</v>
+        <v>11.21135439536204</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.343997638472912</v>
+        <v>1.21162897889762</v>
       </c>
       <c r="R13" t="n">
         <v>193.9340304002594</v>
       </c>
       <c r="S13" t="n">
-        <v>192.8768953963663</v>
+        <v>193.4962957966822</v>
       </c>
       <c r="T13" t="n">
-        <v>5.005018829816438</v>
+        <v>4.404349652507579</v>
       </c>
       <c r="U13" t="n">
-        <v>0.540900380122006</v>
+        <v>0.4759851026012919</v>
       </c>
       <c r="V13" t="n">
         <v>188.2053733911598</v>
       </c>
       <c r="W13" t="n">
-        <v>156.1223227898773</v>
+        <v>151.0374606732225</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4111642329034779</v>
+        <v>0.4643319378183132</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04443517545731608</v>
+        <v>0.05018109425932462</v>
       </c>
       <c r="Z13" t="n">
         <v>173.7069303697712</v>
@@ -1808,7 +1812,7 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1832,67 +1836,67 @@
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
-        <v>122</v>
+        <v>181</v>
       </c>
       <c r="G14" t="n">
-        <v>70.1958408791165</v>
+        <v>73.51977150703368</v>
       </c>
       <c r="H14" t="n">
-        <v>2.736183592451876</v>
+        <v>3.702156604902078</v>
       </c>
       <c r="I14" t="n">
-        <v>0.06445187703972029</v>
+        <v>0.08720574998665183</v>
       </c>
       <c r="J14" t="n">
         <v>66.61025297793201</v>
       </c>
       <c r="K14" t="n">
-        <v>72.37581760472351</v>
+        <v>73.36927836706568</v>
       </c>
       <c r="L14" t="n">
-        <v>3.007663214842723</v>
+        <v>5.301703827430049</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07084668595875386</v>
+        <v>0.1248837117981314</v>
       </c>
       <c r="N14" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O14" t="n">
-        <v>159.5399375746496</v>
+        <v>153.5517342731258</v>
       </c>
       <c r="P14" t="n">
-        <v>34.0281274780627</v>
+        <v>34.61700716363286</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8015458809701924</v>
+        <v>0.8154171727907629</v>
       </c>
       <c r="R14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="S14" t="n">
-        <v>180.7733847934277</v>
+        <v>181.0872230382438</v>
       </c>
       <c r="T14" t="n">
-        <v>91.01923076923077</v>
+        <v>122.2166666666667</v>
       </c>
       <c r="U14" t="n">
-        <v>2.143993658163699</v>
+        <v>2.878861489387805</v>
       </c>
       <c r="V14" t="n">
         <v>186.0423288913966</v>
       </c>
       <c r="W14" t="n">
-        <v>87.66138746028537</v>
+        <v>96.33854616271445</v>
       </c>
       <c r="X14" t="n">
-        <v>11.71729553707351</v>
+        <v>22.74901767455469</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2760054892796115</v>
+        <v>0.5358620284032021</v>
       </c>
       <c r="Z14" t="n">
         <v>130.2296761771863</v>
@@ -1908,11 +1912,11 @@
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>70.1958408791165</v>
+        <v>73.51977150703368</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=70.20% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=73.52% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -1936,67 +1940,67 @@
         <v>2026</v>
       </c>
       <c r="E15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>68.83481220671345</v>
+        <v>72.76882002827271</v>
       </c>
       <c r="H15" t="n">
-        <v>1.268116397136053</v>
+        <v>1.732657682219908</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04373286421850815</v>
+        <v>0.05975325555667321</v>
       </c>
       <c r="J15" t="n">
         <v>82.6747998505866</v>
       </c>
       <c r="K15" t="n">
-        <v>81.22456724195349</v>
+        <v>76.92729274465719</v>
       </c>
       <c r="L15" t="n">
-        <v>1.379338892325262</v>
+        <v>1.718379949755973</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04756853600000902</v>
+        <v>0.05926086689534555</v>
       </c>
       <c r="N15" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O15" t="n">
-        <v>168.0571596557481</v>
+        <v>163.8675828819894</v>
       </c>
       <c r="P15" t="n">
-        <v>23.13369034589022</v>
+        <v>23.84006586211239</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7977994299692716</v>
+        <v>0.822159831433987</v>
       </c>
       <c r="R15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="S15" t="n">
-        <v>178.2169897626607</v>
+        <v>178.8256680643568</v>
       </c>
       <c r="T15" t="n">
-        <v>43.94230769230769</v>
+        <v>58.78333333333333</v>
       </c>
       <c r="U15" t="n">
-        <v>1.515415288451176</v>
+        <v>2.027229945755649</v>
       </c>
       <c r="V15" t="n">
         <v>186.4460938550808</v>
       </c>
       <c r="W15" t="n">
-        <v>89.94521924807745</v>
+        <v>99.01160339376972</v>
       </c>
       <c r="X15" t="n">
-        <v>5.524349859202757</v>
+        <v>11.55202776329354</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1905153524027247</v>
+        <v>0.3983887147595572</v>
       </c>
       <c r="Z15" t="n">
         <v>131.9030800529592</v>
@@ -2012,11 +2016,11 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>68.83481220671345</v>
+        <v>72.76882002827271</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=68.83% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=72.77% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -2040,67 +2044,67 @@
         <v>2026</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="G16" t="n">
-        <v>111.1712374987075</v>
+        <v>110.31830830747</v>
       </c>
       <c r="H16" t="n">
-        <v>1.918207186286123</v>
+        <v>2.446385065587029</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06076284890235194</v>
+        <v>0.07749388447711833</v>
       </c>
       <c r="J16" t="n">
         <v>90.20708978859948</v>
       </c>
       <c r="K16" t="n">
-        <v>115.8528555849145</v>
+        <v>112.5622406395385</v>
       </c>
       <c r="L16" t="n">
-        <v>1.837330136736047</v>
+        <v>3.469407999521305</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05820091504212382</v>
+        <v>0.1099000752174636</v>
       </c>
       <c r="N16" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O16" t="n">
-        <v>170.0377875017184</v>
+        <v>165.1964090265081</v>
       </c>
       <c r="P16" t="n">
-        <v>24.2248835744896</v>
+        <v>25.16707906345231</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7673691094671028</v>
+        <v>0.7972149376662779</v>
       </c>
       <c r="R16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="S16" t="n">
-        <v>181.9337683311368</v>
+        <v>182.098489126943</v>
       </c>
       <c r="T16" t="n">
-        <v>47.13461538461539</v>
+        <v>63.48333333333333</v>
       </c>
       <c r="U16" t="n">
-        <v>1.493078293711832</v>
+        <v>2.010954926417211</v>
       </c>
       <c r="V16" t="n">
         <v>186.1307414343702</v>
       </c>
       <c r="W16" t="n">
-        <v>109.723969075079</v>
+        <v>115.175173488451</v>
       </c>
       <c r="X16" t="n">
-        <v>5.827568191103187</v>
+        <v>11.41341266330384</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1845992695657315</v>
+        <v>0.361541482108219</v>
       </c>
       <c r="Z16" t="n">
         <v>133.2708900338696</v>
@@ -2116,11 +2120,11 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>111.1712374987075</v>
+        <v>110.31830830747</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=111.17% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=110.32% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -2144,31 +2148,31 @@
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>199.0757688868626</v>
+        <v>199.1989997019476</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1178858876047085</v>
+        <v>0.1150468576285209</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05539424968209503</v>
+        <v>0.05406019741721982</v>
       </c>
       <c r="J17" t="n">
         <v>194.5446671655584</v>
       </c>
       <c r="K17" t="n">
-        <v>199.9584575688297</v>
+        <v>199.9639965596524</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04071459157096483</v>
+        <v>0.03560876259773929</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01913167298488802</v>
+        <v>0.01673245819570716</v>
       </c>
       <c r="N17" t="n">
         <v>109.609711216533</v>
@@ -2177,10 +2181,10 @@
         <v>200</v>
       </c>
       <c r="P17" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.04518242403704959</v>
+        <v>0.03915810083210965</v>
       </c>
       <c r="R17" t="n">
         <v>196.7571923388938</v>
@@ -2189,22 +2193,22 @@
         <v>200</v>
       </c>
       <c r="T17" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U17" t="n">
-        <v>0.04518242403704959</v>
+        <v>0.03915810083210965</v>
       </c>
       <c r="V17" t="n">
         <v>197.0125798901019</v>
       </c>
       <c r="W17" t="n">
-        <v>199.0485797204635</v>
+        <v>199.175435757735</v>
       </c>
       <c r="X17" t="n">
-        <v>0.04428698637994159</v>
+        <v>0.03848235094654683</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.02081033133859223</v>
+        <v>0.01808274934345813</v>
       </c>
       <c r="Z17" t="n">
         <v>192.256373806382</v>
@@ -2246,7 +2250,7 @@
         <v>2026</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2255,10 +2259,10 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03213318165902102</v>
+        <v>0.0338663207647142</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03427539376962242</v>
+        <v>0.03612407548236182</v>
       </c>
       <c r="J18" t="n">
         <v>199.6410247115898</v>
@@ -2267,10 +2271,10 @@
         <v>200</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0005621916357963347</v>
+        <v>0.0005702780614168433</v>
       </c>
       <c r="M18" t="n">
-        <v>0.000599671078182757</v>
+        <v>0.0006082965988446329</v>
       </c>
       <c r="N18" t="n">
         <v>79.54507935933471</v>
@@ -2299,10 +2303,10 @@
         <v>200</v>
       </c>
       <c r="X18" t="n">
-        <v>3.915870311351707e-263</v>
+        <v>2.219757347666035e-19</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.176928332108487e-263</v>
+        <v>2.36774117084377e-19</v>
       </c>
       <c r="Z18" t="n">
         <v>196.0211023092105</v>
@@ -2344,31 +2348,31 @@
         <v>2026</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.30683954707</v>
+        <v>199.4024478854051</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1010139478438304</v>
+        <v>0.0962407870067717</v>
       </c>
       <c r="I19" t="n">
-        <v>0.08395964496110579</v>
+        <v>0.07999234244718686</v>
       </c>
       <c r="J19" t="n">
         <v>196.278530387405</v>
       </c>
       <c r="K19" t="n">
-        <v>199.9046485748806</v>
+        <v>199.9173620982299</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04327476996875143</v>
+        <v>0.03828893595064166</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03596863997402716</v>
+        <v>0.03182457014079307</v>
       </c>
       <c r="N19" t="n">
         <v>109.7635513825217</v>
@@ -2377,10 +2381,10 @@
         <v>200</v>
       </c>
       <c r="P19" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.07992007992007992</v>
+        <v>0.06926406926406926</v>
       </c>
       <c r="R19" t="n">
         <v>196.7189002085085</v>
@@ -2389,22 +2393,22 @@
         <v>200</v>
       </c>
       <c r="T19" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07992007992007992</v>
+        <v>0.06926406926406926</v>
       </c>
       <c r="V19" t="n">
         <v>196.7488584326798</v>
       </c>
       <c r="W19" t="n">
-        <v>199.1378073789123</v>
+        <v>199.2527663950573</v>
       </c>
       <c r="X19" t="n">
-        <v>0.04495243150570093</v>
+        <v>0.03895957101369892</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.03736305995279039</v>
+        <v>0.03238198110229521</v>
       </c>
       <c r="Z19" t="n">
         <v>197.8046914283761</v>
@@ -2446,7 +2450,7 @@
         <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2455,7 +2459,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07124381545859265</v>
+        <v>0.07171241224355712</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
@@ -2465,7 +2469,7 @@
         <v>200</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001318309886591289</v>
+        <v>0.001366867765529553</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
@@ -2491,7 +2495,7 @@
         <v>200</v>
       </c>
       <c r="X20" t="n">
-        <v>5769.23076923077</v>
+        <v>5000</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
@@ -2534,7 +2538,7 @@
         <v>2026</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2543,10 +2547,10 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05733506266469365</v>
+        <v>0.0577058978768387</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08993735319951945</v>
+        <v>0.09051905549308033</v>
       </c>
       <c r="J21" t="n">
         <v>200</v>
@@ -2555,10 +2559,10 @@
         <v>200</v>
       </c>
       <c r="L21" t="n">
-        <v>0.006075711302686262</v>
+        <v>0.00608844158616144</v>
       </c>
       <c r="M21" t="n">
-        <v>0.009530527533625509</v>
+        <v>0.009550496605743435</v>
       </c>
       <c r="N21" t="n">
         <v>79.54507935933471</v>
@@ -2587,10 +2591,10 @@
         <v>200</v>
       </c>
       <c r="X21" t="n">
-        <v>13461.5384616087</v>
+        <v>11666.66666672754</v>
       </c>
       <c r="Y21" t="n">
-        <v>21116.13876330776</v>
+        <v>18300.65359486673</v>
       </c>
       <c r="Z21" t="n">
         <v>200</v>
@@ -2632,7 +2636,7 @@
         <v>2026</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2641,10 +2645,10 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06419987238281549</v>
+        <v>0.06462246577622624</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06893946027684884</v>
+        <v>0.06939325184024293</v>
       </c>
       <c r="J22" t="n">
         <v>200</v>
@@ -2653,10 +2657,10 @@
         <v>200</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0004004337771155077</v>
+        <v>0.00039442201699259</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0004299960022716861</v>
+        <v>0.0004235404209316402</v>
       </c>
       <c r="N22" t="n">
         <v>109.7635513825217</v>
@@ -2685,10 +2689,10 @@
         <v>200</v>
       </c>
       <c r="X22" t="n">
-        <v>2.473430849578971e-17</v>
+        <v>8.711041683575902e-16</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.656033127064667e-17</v>
+        <v>9.354138720618418e-16</v>
       </c>
       <c r="Z22" t="n">
         <v>200</v>
@@ -2730,67 +2734,67 @@
         <v>2026</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>191.6695652076228</v>
+        <v>182.5487674821857</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1549098148173384</v>
+        <v>0.2533462861681124</v>
       </c>
       <c r="I23" t="n">
-        <v>0.003745175335565753</v>
+        <v>0.006125023539875793</v>
       </c>
       <c r="J23" t="n">
         <v>149.2565324185079</v>
       </c>
       <c r="K23" t="n">
-        <v>199.4606494083488</v>
+        <v>196.8096497945818</v>
       </c>
       <c r="L23" t="n">
-        <v>0.838262376823547</v>
+        <v>1.258395964919489</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0202662406001462</v>
+        <v>0.03042359540452074</v>
       </c>
       <c r="N23" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O23" t="n">
-        <v>195.2380952380952</v>
+        <v>186.4285714285714</v>
       </c>
       <c r="P23" t="n">
-        <v>4.316793663519504</v>
+        <v>7.928549876008182</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1043649117804655</v>
+        <v>0.1916844938291492</v>
       </c>
       <c r="R23" t="n">
         <v>169.6992056798271</v>
       </c>
       <c r="S23" t="n">
-        <v>195.2380952380952</v>
+        <v>186.4285714285714</v>
       </c>
       <c r="T23" t="n">
-        <v>5.307692307692307</v>
+        <v>15.26666666666667</v>
       </c>
       <c r="U23" t="n">
-        <v>0.128321361322268</v>
+        <v>0.369094389039992</v>
       </c>
       <c r="V23" t="n">
         <v>186.3774873978808</v>
       </c>
       <c r="W23" t="n">
-        <v>192.0713197266988</v>
+        <v>192.0231043563226</v>
       </c>
       <c r="X23" t="n">
-        <v>0.7520862116405661</v>
+        <v>3.582459466670285</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.01818280354525394</v>
+        <v>0.08661128961427102</v>
       </c>
       <c r="Z23" t="n">
         <v>159.9263814945425</v>
@@ -2808,7 +2812,7 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2832,67 +2836,67 @@
         <v>2026</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>193.3329141987729</v>
+        <v>187.0869559636593</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0736243714974817</v>
+        <v>0.1382318691869096</v>
       </c>
       <c r="I24" t="n">
-        <v>0.003276289650840515</v>
+        <v>0.006151327790267151</v>
       </c>
       <c r="J24" t="n">
         <v>156.2502876793226</v>
       </c>
       <c r="K24" t="n">
-        <v>198.9207311571889</v>
+        <v>197.9839364257978</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7476191834856146</v>
+        <v>2.107750666107081</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03326910564808742</v>
+        <v>0.09379505119653261</v>
       </c>
       <c r="N24" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O24" t="n">
-        <v>179.4183191604088</v>
+        <v>171.6509914962452</v>
       </c>
       <c r="P24" t="n">
-        <v>1.044049313435188</v>
+        <v>2.020837509632111</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.04646026704203311</v>
+        <v>0.08992740969020656</v>
       </c>
       <c r="R24" t="n">
         <v>159.6122718089852</v>
       </c>
       <c r="S24" t="n">
-        <v>187.5</v>
+        <v>178.3333333333333</v>
       </c>
       <c r="T24" t="n">
-        <v>2.211538461538462</v>
+        <v>6.233333333333333</v>
       </c>
       <c r="U24" t="n">
-        <v>0.09841361530973547</v>
+        <v>0.2773837667454689</v>
       </c>
       <c r="V24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="W24" t="n">
-        <v>194.5708160695934</v>
+        <v>192.6107016410813</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3302519970580709</v>
+        <v>1.150307104863834</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.0146962368319542</v>
+        <v>0.05118874614885649</v>
       </c>
       <c r="Z24" t="n">
         <v>166.4426133688291</v>
@@ -2910,7 +2914,7 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2938,7 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2943,22 +2947,22 @@
         <v>200</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0851379480990028</v>
+        <v>0.1400345713133921</v>
       </c>
       <c r="I25" t="n">
-        <v>0.003055989163396623</v>
+        <v>0.005026479284384237</v>
       </c>
       <c r="J25" t="n">
         <v>155.3955473497874</v>
       </c>
       <c r="K25" t="n">
-        <v>199.9371026520693</v>
+        <v>199.9454889651267</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3177389752069076</v>
+        <v>0.8448776191837108</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0114051006243646</v>
+        <v>0.03032651016699803</v>
       </c>
       <c r="N25" t="n">
         <v>109.7635513825217</v>
@@ -2967,10 +2971,10 @@
         <v>200</v>
       </c>
       <c r="P25" t="n">
-        <v>3.153846153846154</v>
+        <v>8.029075112468957</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1132059191509556</v>
+        <v>0.2882001162075229</v>
       </c>
       <c r="R25" t="n">
         <v>177.0659734750362</v>
@@ -2979,22 +2983,22 @@
         <v>200</v>
       </c>
       <c r="T25" t="n">
-        <v>3.153846153846154</v>
+        <v>9.133333333333333</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1132059191509556</v>
+        <v>0.327836978874556</v>
       </c>
       <c r="V25" t="n">
         <v>183.340259481936</v>
       </c>
       <c r="W25" t="n">
-        <v>199.6698745881943</v>
+        <v>199.7138913097684</v>
       </c>
       <c r="X25" t="n">
-        <v>0.4625315179892543</v>
+        <v>2.09079770088027</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.01660236519983863</v>
+        <v>0.07504826295924694</v>
       </c>
       <c r="Z25" t="n">
         <v>180.6321027113416</v>
@@ -3036,67 +3040,67 @@
         <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02031572516823366</v>
+        <v>0.05094029514580251</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0005919176958786099</v>
+        <v>0.001484193248352618</v>
       </c>
       <c r="J26" t="n">
         <v>97.19414576199205</v>
       </c>
       <c r="K26" t="n">
-        <v>200</v>
+        <v>194.9373081954851</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1448044608516833</v>
+        <v>0.1855918596837396</v>
       </c>
       <c r="M26" t="n">
-        <v>0.004219013700495189</v>
+        <v>0.005407392797850923</v>
       </c>
       <c r="N26" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O26" t="n">
-        <v>200</v>
+        <v>199.9275362318841</v>
       </c>
       <c r="P26" t="n">
-        <v>72.86538461538461</v>
+        <v>86.10241296238631</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12300128170109</v>
+        <v>2.50867451042189</v>
       </c>
       <c r="R26" t="n">
         <v>198.3074653131699</v>
       </c>
       <c r="S26" t="n">
-        <v>200</v>
+        <v>199.9275362318841</v>
       </c>
       <c r="T26" t="n">
-        <v>72.86538461538461</v>
+        <v>87.46666666666667</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12300128170109</v>
+        <v>2.54842332088986</v>
       </c>
       <c r="V26" t="n">
         <v>199.6509594119097</v>
       </c>
       <c r="W26" t="n">
-        <v>200</v>
+        <v>197.2926384996639</v>
       </c>
       <c r="X26" t="n">
-        <v>1.285590062997845</v>
+        <v>1.591280551137813</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.0374568715432314</v>
+        <v>0.04636345045653284</v>
       </c>
       <c r="Z26" t="n">
         <v>183.6686755299509</v>
@@ -3114,7 +3118,7 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="E27" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3147,10 +3151,10 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01422506820371157</v>
+        <v>0.01232839244321669</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0007615897315020412</v>
+        <v>0.0006600444339684358</v>
       </c>
       <c r="J27" t="n">
         <v>129.0985231723771</v>
@@ -3159,10 +3163,10 @@
         <v>200</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01233773058711022</v>
+        <v>0.1149934630296452</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0006605443847875641</v>
+        <v>0.006156584937173573</v>
       </c>
       <c r="N27" t="n">
         <v>79.54507935933471</v>
@@ -3171,10 +3175,10 @@
         <v>200</v>
       </c>
       <c r="P27" t="n">
-        <v>36.05769230769231</v>
+        <v>40.4888699881782</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.930477085236998</v>
+        <v>2.16771597728242</v>
       </c>
       <c r="R27" t="n">
         <v>198.6114841856233</v>
@@ -3183,10 +3187,10 @@
         <v>200</v>
       </c>
       <c r="T27" t="n">
-        <v>36.05769230769231</v>
+        <v>42.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.930477085236998</v>
+        <v>2.280742847582399</v>
       </c>
       <c r="V27" t="n">
         <v>199.779644487174</v>
@@ -3195,17 +3199,17 @@
         <v>200</v>
       </c>
       <c r="X27" t="n">
-        <v>0.8885456236906393</v>
+        <v>1.071897421311159</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.04757145718270111</v>
+        <v>0.0573878492252921</v>
       </c>
       <c r="Z27" t="n">
         <v>192.722098187243</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -3216,7 +3220,7 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3240,67 +3244,67 @@
         <v>2026</v>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0143524143490416</v>
+        <v>0.04577209243583606</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00073484361467093</v>
+        <v>0.002343531132714806</v>
       </c>
       <c r="J28" t="n">
         <v>127.1718885128103</v>
       </c>
       <c r="K28" t="n">
-        <v>200</v>
+        <v>196.0543300200681</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2261063548282595</v>
+        <v>0.466428794628377</v>
       </c>
       <c r="M28" t="n">
-        <v>0.01157664536720688</v>
+        <v>0.0238811542849729</v>
       </c>
       <c r="N28" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O28" t="n">
-        <v>200</v>
+        <v>199.8625429553265</v>
       </c>
       <c r="P28" t="n">
-        <v>36.80769230769231</v>
+        <v>43.33434520066904</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.884553846153846</v>
+        <v>2.218718474274255</v>
       </c>
       <c r="R28" t="n">
         <v>197.4940180993655</v>
       </c>
       <c r="S28" t="n">
-        <v>200</v>
+        <v>199.8625429553265</v>
       </c>
       <c r="T28" t="n">
-        <v>36.80769230769231</v>
+        <v>44.86666666666667</v>
       </c>
       <c r="U28" t="n">
-        <v>1.884553846153846</v>
+        <v>2.297173333333333</v>
       </c>
       <c r="V28" t="n">
         <v>199.5411797194807</v>
       </c>
       <c r="W28" t="n">
-        <v>200</v>
+        <v>196.64626555975</v>
       </c>
       <c r="X28" t="n">
-        <v>0.8966237872700616</v>
+        <v>1.116591091954148</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.04590713790822715</v>
+        <v>0.05716946390805237</v>
       </c>
       <c r="Z28" t="n">
         <v>184.9627687949149</v>
@@ -3318,7 +3322,7 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3342,31 +3346,31 @@
         <v>2026</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>197.2752612569065</v>
+        <v>197.3842508066303</v>
       </c>
       <c r="H29" t="n">
-        <v>0.165481408153559</v>
+        <v>0.149771458699966</v>
       </c>
       <c r="I29" t="n">
-        <v>0.01967089547144833</v>
+        <v>0.0178034423417493</v>
       </c>
       <c r="J29" t="n">
         <v>191.5075017030775</v>
       </c>
       <c r="K29" t="n">
-        <v>199.6842069526952</v>
+        <v>199.7263126923358</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06251244142477602</v>
+        <v>0.05795993941483705</v>
       </c>
       <c r="M29" t="n">
-        <v>0.007430899426422113</v>
+        <v>0.006889740197900392</v>
       </c>
       <c r="N29" t="n">
         <v>109.609711216533</v>
@@ -3375,10 +3379,10 @@
         <v>200</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.04571951080123443</v>
+        <v>0.0871718672610203</v>
       </c>
       <c r="R29" t="n">
         <v>198.5277121400952</v>
@@ -3387,22 +3391,22 @@
         <v>200</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="U29" t="n">
-        <v>0.04571951080123443</v>
+        <v>0.0871718672610203</v>
       </c>
       <c r="V29" t="n">
         <v>199.9388941772115</v>
       </c>
       <c r="W29" t="n">
-        <v>199.999964251257</v>
+        <v>199.999969017756</v>
       </c>
       <c r="X29" t="n">
-        <v>0.06751301021021251</v>
+        <v>0.09732881366899378</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.008025320678777119</v>
+        <v>0.01156954694430832</v>
       </c>
       <c r="Z29" t="n">
         <v>192.5799615112869</v>
@@ -3444,7 +3448,7 @@
         <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3453,10 +3457,10 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1198547547246342</v>
+        <v>0.1139970950750777</v>
       </c>
       <c r="I30" t="n">
-        <v>0.02464879274542605</v>
+        <v>0.02344413266325505</v>
       </c>
       <c r="J30" t="n">
         <v>196.0386411854094</v>
@@ -3465,10 +3469,10 @@
         <v>200</v>
       </c>
       <c r="L30" t="n">
-        <v>0.006022060414032323</v>
+        <v>0.006130680813965784</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001238470008027213</v>
+        <v>0.001260808393617642</v>
       </c>
       <c r="N30" t="n">
         <v>79.54507935933471</v>
@@ -3477,10 +3481,10 @@
         <v>200</v>
       </c>
       <c r="P30" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.04745896776745107</v>
+        <v>0.08226221079691518</v>
       </c>
       <c r="R30" t="n">
         <v>198.9477887234591</v>
@@ -3489,10 +3493,10 @@
         <v>200</v>
       </c>
       <c r="T30" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.4</v>
       </c>
       <c r="U30" t="n">
-        <v>0.04745896776745107</v>
+        <v>0.08226221079691518</v>
       </c>
       <c r="V30" t="n">
         <v>199.7754683359127</v>
@@ -3501,10 +3505,10 @@
         <v>200</v>
       </c>
       <c r="X30" t="n">
-        <v>0.01909230307143704</v>
+        <v>0.03861961598056001</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.003926437649652862</v>
+        <v>0.007942337476721854</v>
       </c>
       <c r="Z30" t="n">
         <v>198.9226798174336</v>
@@ -3546,31 +3550,31 @@
         <v>2026</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>197.5495607401959</v>
+        <v>197.6438084040346</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1596547285707901</v>
+        <v>0.1449540930155994</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02395195177808384</v>
+        <v>0.02174651184481565</v>
       </c>
       <c r="J31" t="n">
         <v>194.2466814459454</v>
       </c>
       <c r="K31" t="n">
-        <v>199.8983878715963</v>
+        <v>199.9119361553834</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04410647872176808</v>
+        <v>0.03921319648113078</v>
       </c>
       <c r="M31" t="n">
-        <v>0.006617005715408244</v>
+        <v>0.005882898675087599</v>
       </c>
       <c r="N31" t="n">
         <v>109.7635513825217</v>
@@ -3579,10 +3583,10 @@
         <v>200</v>
       </c>
       <c r="P31" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.02308052940964333</v>
+        <v>0.05000781372089388</v>
       </c>
       <c r="R31" t="n">
         <v>199.0633013569061</v>
@@ -3591,22 +3595,22 @@
         <v>200</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U31" t="n">
-        <v>0.02308052940964333</v>
+        <v>0.05000781372089388</v>
       </c>
       <c r="V31" t="n">
         <v>199.9196066031173</v>
       </c>
       <c r="W31" t="n">
-        <v>199.9999999923865</v>
+        <v>199.9999999934016</v>
       </c>
       <c r="X31" t="n">
-        <v>0.05052019072418547</v>
+        <v>0.06886750441279872</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.007579212860637294</v>
+        <v>0.01033173999629423</v>
       </c>
       <c r="Z31" t="n">
         <v>194.1597056483905</v>
@@ -3648,67 +3652,67 @@
         <v>2026</v>
       </c>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G32" t="n">
-        <v>136.4384553168091</v>
+        <v>122.4271857349756</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9088263617437347</v>
+        <v>1.132317772431623</v>
       </c>
       <c r="I32" t="n">
-        <v>0.04065200388006641</v>
+        <v>0.05064882403943519</v>
       </c>
       <c r="J32" t="n">
         <v>164.6748490827784</v>
       </c>
       <c r="K32" t="n">
-        <v>159.6862497058564</v>
+        <v>147.203167680811</v>
       </c>
       <c r="L32" t="n">
-        <v>1.377016198743123</v>
+        <v>2.136834004651067</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06159423869133344</v>
+        <v>0.09558105695951097</v>
       </c>
       <c r="N32" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O32" t="n">
-        <v>157.5789375132153</v>
+        <v>157.3546675582937</v>
       </c>
       <c r="P32" t="n">
-        <v>12.25</v>
+        <v>20.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.547945205479452</v>
+        <v>0.914733016494269</v>
       </c>
       <c r="R32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="S32" t="n">
-        <v>157.5789375132153</v>
+        <v>157.3546675582937</v>
       </c>
       <c r="T32" t="n">
-        <v>12.25</v>
+        <v>20.45</v>
       </c>
       <c r="U32" t="n">
-        <v>0.547945205479452</v>
+        <v>0.914733016494269</v>
       </c>
       <c r="V32" t="n">
         <v>195.3761640213164</v>
       </c>
       <c r="W32" t="n">
-        <v>144.7850261687545</v>
+        <v>149.514771523089</v>
       </c>
       <c r="X32" t="n">
-        <v>5.942491840375366</v>
+        <v>26.16782352234143</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.2658089724517916</v>
+        <v>1.170492525461177</v>
       </c>
       <c r="Z32" t="n">
         <v>173.3959783787531</v>
@@ -3724,11 +3728,11 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>136.4384553168091</v>
+        <v>122.4271857349756</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=136.44% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=122.43% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -3752,67 +3756,67 @@
         <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G33" t="n">
-        <v>139.8117872004429</v>
+        <v>123.2888303517377</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2855099710301251</v>
+        <v>0.4556641525522134</v>
       </c>
       <c r="I33" t="n">
-        <v>0.01575499064142784</v>
+        <v>0.02514442642122923</v>
       </c>
       <c r="J33" t="n">
         <v>170.4028696730483</v>
       </c>
       <c r="K33" t="n">
-        <v>172.4959078110981</v>
+        <v>168.3864603919355</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6838980996468932</v>
+        <v>2.458028500591371</v>
       </c>
       <c r="M33" t="n">
-        <v>0.03773881563838694</v>
+        <v>0.1356387515415138</v>
       </c>
       <c r="N33" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O33" t="n">
-        <v>181.6029900332226</v>
+        <v>178.6452278811728</v>
       </c>
       <c r="P33" t="n">
-        <v>4.807692307692307</v>
+        <v>8.433333333333334</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2652977303779166</v>
+        <v>0.4653675921135828</v>
       </c>
       <c r="R33" t="n">
         <v>180.7526372107734</v>
       </c>
       <c r="S33" t="n">
-        <v>181.6029900332226</v>
+        <v>178.6452278811728</v>
       </c>
       <c r="T33" t="n">
-        <v>4.807692307692307</v>
+        <v>8.433333333333334</v>
       </c>
       <c r="U33" t="n">
-        <v>0.2652977303779166</v>
+        <v>0.4653675921135828</v>
       </c>
       <c r="V33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="W33" t="n">
-        <v>172.0138066156621</v>
+        <v>170.5104647616149</v>
       </c>
       <c r="X33" t="n">
-        <v>1.228747777109315</v>
+        <v>4.302459658811338</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.06780467126659438</v>
+        <v>0.2374180187652402</v>
       </c>
       <c r="Z33" t="n">
         <v>182.3083787234438</v>
@@ -3828,11 +3832,11 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>139.8117872004429</v>
+        <v>123.2888303517377</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=139.81% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=123.29% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -3856,67 +3860,67 @@
         <v>2026</v>
       </c>
       <c r="E34" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F34" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="G34" t="n">
-        <v>150.568521206798</v>
+        <v>135.6931738222306</v>
       </c>
       <c r="H34" t="n">
-        <v>0.836651906100444</v>
+        <v>0.9697079095547546</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0386388526413829</v>
+        <v>0.044783739508951</v>
       </c>
       <c r="J34" t="n">
         <v>169.6571057340244</v>
       </c>
       <c r="K34" t="n">
-        <v>169.7651776711998</v>
+        <v>170.4581422708645</v>
       </c>
       <c r="L34" t="n">
-        <v>4.2457171071596</v>
+        <v>14.27976610502534</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1960787233787086</v>
+        <v>0.6594783018629109</v>
       </c>
       <c r="N34" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O34" t="n">
-        <v>167.6757509073452</v>
+        <v>164.5890108415669</v>
       </c>
       <c r="P34" t="n">
-        <v>7.942307692307693</v>
+        <v>12.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.3667972956470575</v>
+        <v>0.5749747438302786</v>
       </c>
       <c r="R34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="S34" t="n">
-        <v>167.6757509073452</v>
+        <v>164.5890108415669</v>
       </c>
       <c r="T34" t="n">
-        <v>7.942307692307693</v>
+        <v>12.45</v>
       </c>
       <c r="U34" t="n">
-        <v>0.3667972956470575</v>
+        <v>0.5749747438302786</v>
       </c>
       <c r="V34" t="n">
         <v>195.2398047728465</v>
       </c>
       <c r="W34" t="n">
-        <v>153.4535494003401</v>
+        <v>155.3949822801956</v>
       </c>
       <c r="X34" t="n">
-        <v>2.609194376670224</v>
+        <v>9.975811480521559</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1204996681389049</v>
+        <v>0.4607100120893201</v>
       </c>
       <c r="Z34" t="n">
         <v>176.7243686471345</v>
@@ -3932,11 +3936,11 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>150.568521206798</v>
+        <v>135.6931738222306</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=150.57% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=135.69% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -3960,67 +3964,67 @@
         <v>2026</v>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G35" t="n">
-        <v>120.0269946697649</v>
+        <v>128.206206655399</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6288707011427206</v>
+        <v>0.6116602248966727</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01052008073426058</v>
+        <v>0.01023217481138247</v>
       </c>
       <c r="J35" t="n">
         <v>48.55849570822402</v>
       </c>
       <c r="K35" t="n">
-        <v>132.6935847973162</v>
+        <v>139.1871116092317</v>
       </c>
       <c r="L35" t="n">
-        <v>1.41605812453869</v>
+        <v>2.830757297351863</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0236885670893607</v>
+        <v>0.0473544009175909</v>
       </c>
       <c r="N35" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O35" t="n">
-        <v>191.1576938126877</v>
+        <v>191.6790647796566</v>
       </c>
       <c r="P35" t="n">
-        <v>32.21614184248983</v>
+        <v>33.28102958205857</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5389286104656147</v>
+        <v>0.5567426141595871</v>
       </c>
       <c r="R35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="S35" t="n">
-        <v>198.1187828016984</v>
+        <v>197.983406206727</v>
       </c>
       <c r="T35" t="n">
-        <v>173.9018700236352</v>
+        <v>168.8323159287893</v>
       </c>
       <c r="U35" t="n">
-        <v>2.909122191832468</v>
+        <v>2.824316017419236</v>
       </c>
       <c r="V35" t="n">
         <v>185.853149170162</v>
       </c>
       <c r="W35" t="n">
-        <v>142.2217601484261</v>
+        <v>148.8351407346903</v>
       </c>
       <c r="X35" t="n">
-        <v>3.827236981373604</v>
+        <v>6.78678751889074</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.06402403858223395</v>
+        <v>0.1135329607425917</v>
       </c>
       <c r="Z35" t="n">
         <v>110.5529101365675</v>
@@ -4036,11 +4040,11 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>120.0269946697649</v>
+        <v>128.206206655399</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=120.03% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=128.21% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4064,67 +4068,67 @@
         <v>2026</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
-        <v>165.4537784983441</v>
+        <v>168.4577977593577</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4159725096872607</v>
+        <v>0.4271761750622927</v>
       </c>
       <c r="I36" t="n">
-        <v>0.01052096135788203</v>
+        <v>0.0108043294356571</v>
       </c>
       <c r="J36" t="n">
         <v>58.86670393327421</v>
       </c>
       <c r="K36" t="n">
-        <v>168.9852897137726</v>
+        <v>169.2080576338946</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8438138868550287</v>
+        <v>1.457062808901235</v>
       </c>
       <c r="M36" t="n">
-        <v>0.02134211538046231</v>
+        <v>0.03685267932725222</v>
       </c>
       <c r="N36" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O36" t="n">
-        <v>187.7653454830295</v>
+        <v>187.6622286247015</v>
       </c>
       <c r="P36" t="n">
-        <v>10.03105728252018</v>
+        <v>10.57220473225772</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2537099533991825</v>
+        <v>0.2673968949037677</v>
       </c>
       <c r="R36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="S36" t="n">
-        <v>198.364052952299</v>
+        <v>197.789638432785</v>
       </c>
       <c r="T36" t="n">
-        <v>84.7415070782278</v>
+        <v>82.07154641761467</v>
       </c>
       <c r="U36" t="n">
-        <v>2.143319812285243</v>
+        <v>2.075789982108496</v>
       </c>
       <c r="V36" t="n">
         <v>187.2910306593169</v>
       </c>
       <c r="W36" t="n">
-        <v>164.2275075564714</v>
+        <v>167.120508356944</v>
       </c>
       <c r="X36" t="n">
-        <v>2.165195990873503</v>
+        <v>3.786276551701051</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.05476309809354418</v>
+        <v>0.09576418720710847</v>
       </c>
       <c r="Z36" t="n">
         <v>118.8153464644226</v>
@@ -4136,13 +4140,15 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC36" t="n">
+        <v>168.4577977593577</v>
+      </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=168.46% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4172,7 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F37" t="n">
         <v>10</v>
@@ -4175,58 +4181,58 @@
         <v>161.9002846937967</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5332963051073031</v>
+        <v>0.462190131092996</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0127211940092685</v>
+        <v>0.0110250348080327</v>
       </c>
       <c r="J37" t="n">
         <v>60.32903496111531</v>
       </c>
       <c r="K37" t="n">
-        <v>168.8038084510468</v>
+        <v>172.9633006575739</v>
       </c>
       <c r="L37" t="n">
-        <v>1.191727828613862</v>
+        <v>1.653101623635907</v>
       </c>
       <c r="M37" t="n">
-        <v>0.02842735036574252</v>
+        <v>0.03943291237894075</v>
       </c>
       <c r="N37" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O37" t="n">
-        <v>184.8161119307371</v>
+        <v>186.8406303399722</v>
       </c>
       <c r="P37" t="n">
-        <v>10.19318387103714</v>
+        <v>10.78681930444123</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.243147136692649</v>
+        <v>0.2573076539262911</v>
       </c>
       <c r="R37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="S37" t="n">
-        <v>197.9055351879389</v>
+        <v>198.1847971628804</v>
       </c>
       <c r="T37" t="n">
-        <v>90.56059711647093</v>
+        <v>88.28279771360384</v>
       </c>
       <c r="U37" t="n">
-        <v>2.160222965133857</v>
+        <v>2.105888577588761</v>
       </c>
       <c r="V37" t="n">
         <v>185.3862117422507</v>
       </c>
       <c r="W37" t="n">
-        <v>158.2676147173262</v>
+        <v>163.8319327550161</v>
       </c>
       <c r="X37" t="n">
-        <v>2.210830069810609</v>
+        <v>3.711324481089274</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.05273690811326089</v>
+        <v>0.08852954408859991</v>
       </c>
       <c r="Z37" t="n">
         <v>110.8838400280787</v>
@@ -4246,7 +4252,7 @@
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=161.90% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=161.90% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4270,67 +4276,67 @@
         <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>186.7585467679683</v>
+        <v>181.9284170935218</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5553684594761084</v>
+        <v>0.5674918975368912</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03093974704602275</v>
+        <v>0.03161514749509144</v>
       </c>
       <c r="J38" t="n">
         <v>164.4263244057969</v>
       </c>
       <c r="K38" t="n">
-        <v>191.4574463290842</v>
+        <v>189.9116176993802</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8441273509148057</v>
+        <v>1.37971911857156</v>
       </c>
       <c r="M38" t="n">
-        <v>0.04702659336572734</v>
+        <v>0.07686457485078332</v>
       </c>
       <c r="N38" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O38" t="n">
-        <v>186.9731760776537</v>
+        <v>188.4967526006332</v>
       </c>
       <c r="P38" t="n">
-        <v>17.11538461538462</v>
+        <v>24</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9535033211913436</v>
+        <v>1.337047353760446</v>
       </c>
       <c r="R38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="S38" t="n">
-        <v>186.9731760776537</v>
+        <v>188.4967526006332</v>
       </c>
       <c r="T38" t="n">
-        <v>17.11538461538462</v>
+        <v>24</v>
       </c>
       <c r="U38" t="n">
-        <v>0.9535033211913436</v>
+        <v>1.337047353760446</v>
       </c>
       <c r="V38" t="n">
         <v>199.036270909302</v>
       </c>
       <c r="W38" t="n">
-        <v>186.3039188319287</v>
+        <v>186.7438171931493</v>
       </c>
       <c r="X38" t="n">
-        <v>0.9283347032724557</v>
+        <v>3.339096834991882</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.05171781076726773</v>
+        <v>0.1860221077989906</v>
       </c>
       <c r="Z38" t="n">
         <v>129.2920232398837</v>
@@ -4348,7 +4354,7 @@
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4372,67 +4378,67 @@
         <v>2026</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F39" t="n">
         <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>198.9125351000604</v>
+        <v>199.0575304200523</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1704836994124694</v>
+        <v>0.1555366685566097</v>
       </c>
       <c r="I39" t="n">
-        <v>0.009255986394976282</v>
+        <v>0.00844447470955465</v>
       </c>
       <c r="J39" t="n">
         <v>170.2041702191862</v>
       </c>
       <c r="K39" t="n">
-        <v>199.3761363235489</v>
+        <v>199.4593181470757</v>
       </c>
       <c r="L39" t="n">
-        <v>0.09436105974426881</v>
+        <v>0.08698373878303987</v>
       </c>
       <c r="M39" t="n">
-        <v>0.005123097916214119</v>
+        <v>0.004722564711668266</v>
       </c>
       <c r="N39" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O39" t="n">
-        <v>187.2</v>
+        <v>188.9655172413793</v>
       </c>
       <c r="P39" t="n">
-        <v>7.25</v>
+        <v>10.63333333333333</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.3936206311503224</v>
+        <v>0.5773102590204728</v>
       </c>
       <c r="R39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="S39" t="n">
-        <v>187.2</v>
+        <v>188.9655172413793</v>
       </c>
       <c r="T39" t="n">
-        <v>7.25</v>
+        <v>10.63333333333333</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3936206311503224</v>
+        <v>0.5773102590204728</v>
       </c>
       <c r="V39" t="n">
         <v>199.0467638312102</v>
       </c>
       <c r="W39" t="n">
-        <v>195.7473889678286</v>
+        <v>196.3144037721181</v>
       </c>
       <c r="X39" t="n">
-        <v>0.4596834347927579</v>
+        <v>1.219729573806344</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.02495736327344461</v>
+        <v>0.06622216892060233</v>
       </c>
       <c r="Z39" t="n">
         <v>146.152525200624</v>
@@ -4474,67 +4480,67 @@
         <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>194.1141677438596</v>
+        <v>191.484685334018</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2682565987196245</v>
+        <v>0.2821475542940849</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01032749176976418</v>
+        <v>0.01086227350506583</v>
       </c>
       <c r="J40" t="n">
         <v>165.7522199768573</v>
       </c>
       <c r="K40" t="n">
-        <v>199.4838010220985</v>
+        <v>199.42957101869</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1245454299554858</v>
+        <v>0.1778563782821241</v>
       </c>
       <c r="M40" t="n">
-        <v>0.004794819247564419</v>
+        <v>0.006847213793344529</v>
       </c>
       <c r="N40" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O40" t="n">
-        <v>189.6153846153846</v>
+        <v>190.4968553459119</v>
       </c>
       <c r="P40" t="n">
-        <v>10.21153846153846</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3931294884134153</v>
+        <v>0.5261469361565607</v>
       </c>
       <c r="R40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="S40" t="n">
-        <v>189.6153846153846</v>
+        <v>190.4968553459119</v>
       </c>
       <c r="T40" t="n">
-        <v>10.21153846153846</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="U40" t="n">
-        <v>0.3931294884134153</v>
+        <v>0.5261469361565607</v>
       </c>
       <c r="V40" t="n">
         <v>198.942356787496</v>
       </c>
       <c r="W40" t="n">
-        <v>191.6029876294868</v>
+        <v>189.6416443324678</v>
       </c>
       <c r="X40" t="n">
-        <v>0.4760050468291805</v>
+        <v>1.620404119185325</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.01832550709640733</v>
+        <v>0.06238321921791434</v>
       </c>
       <c r="Z40" t="n">
         <v>124.2002492905602</v>
@@ -4552,7 +4558,7 @@
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4576,74 +4582,74 @@
         <v>2026</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="G41" t="n">
-        <v>77.92724717992357</v>
+        <v>75.94982401573796</v>
       </c>
       <c r="H41" t="n">
-        <v>2.212301818876929</v>
+        <v>2.509249036474215</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01117130204731844</v>
+        <v>0.01267077514433651</v>
       </c>
       <c r="J41" t="n">
         <v>127.4617865350128</v>
       </c>
       <c r="K41" t="n">
-        <v>81.89642293849408</v>
+        <v>80.53135851469673</v>
       </c>
       <c r="L41" t="n">
-        <v>2.227550347391977</v>
+        <v>2.995365591472618</v>
       </c>
       <c r="M41" t="n">
-        <v>0.01124830144964467</v>
+        <v>0.01512548309591513</v>
       </c>
       <c r="N41" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O41" t="n">
-        <v>184.0199928479197</v>
+        <v>184.9224967591002</v>
       </c>
       <c r="P41" t="n">
-        <v>90.84615384615384</v>
+        <v>143.0833333333333</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4587393165764976</v>
+        <v>0.7225176605492523</v>
       </c>
       <c r="R41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="S41" t="n">
-        <v>184.0199928479197</v>
+        <v>184.9224967591002</v>
       </c>
       <c r="T41" t="n">
-        <v>90.84615384615384</v>
+        <v>143.0833333333333</v>
       </c>
       <c r="U41" t="n">
-        <v>0.4587393165764976</v>
+        <v>0.7225176605492523</v>
       </c>
       <c r="V41" t="n">
         <v>198.8825072752037</v>
       </c>
       <c r="W41" t="n">
-        <v>72.68033743905205</v>
+        <v>81.08729520360787</v>
       </c>
       <c r="X41" t="n">
-        <v>2.739741236221613</v>
+        <v>7.091758973772515</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.0138346750972987</v>
+        <v>0.03581074737036191</v>
       </c>
       <c r="Z41" t="n">
         <v>124.7888620818299</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
@@ -4652,11 +4658,11 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>72.68033743905205</v>
+        <v>75.94982401573796</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=72.68% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=75.95% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4680,67 +4686,67 @@
         <v>2026</v>
       </c>
       <c r="E42" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F42" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G42" t="n">
-        <v>102.8181551117132</v>
+        <v>96.20590361230173</v>
       </c>
       <c r="H42" t="n">
-        <v>1.305219418515306</v>
+        <v>1.434857888355854</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01343682325070448</v>
+        <v>0.01477141050938982</v>
       </c>
       <c r="J42" t="n">
         <v>139.5371944473096</v>
       </c>
       <c r="K42" t="n">
-        <v>157.4561336663125</v>
+        <v>155.7418456955398</v>
       </c>
       <c r="L42" t="n">
-        <v>1.649802586809004</v>
+        <v>1.930294394398277</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01698419855163046</v>
+        <v>0.01987177345925391</v>
       </c>
       <c r="N42" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O42" t="n">
-        <v>182.4002878985824</v>
+        <v>183.260562191004</v>
       </c>
       <c r="P42" t="n">
-        <v>40.15384615384615</v>
+        <v>60.50599734144464</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.4133712124961642</v>
+        <v>0.6228902055482655</v>
       </c>
       <c r="R42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="S42" t="n">
-        <v>182.4002878985824</v>
+        <v>183.2778706175911</v>
       </c>
       <c r="T42" t="n">
-        <v>40.15384615384615</v>
+        <v>62.73333333333333</v>
       </c>
       <c r="U42" t="n">
-        <v>0.4133712124961642</v>
+        <v>0.6458199287950929</v>
       </c>
       <c r="V42" t="n">
         <v>198.6803521667581</v>
       </c>
       <c r="W42" t="n">
-        <v>89.21287175816121</v>
+        <v>90.86697592286167</v>
       </c>
       <c r="X42" t="n">
-        <v>1.067278521000874</v>
+        <v>2.08702081704121</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.01098729657445244</v>
+        <v>0.02148522266932143</v>
       </c>
       <c r="Z42" t="n">
         <v>125.9010082864909</v>
@@ -4756,11 +4762,11 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>89.21287175816121</v>
+        <v>90.86697592286167</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=89.21% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=90.87% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4784,67 +4790,67 @@
         <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F43" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G43" t="n">
-        <v>86.37455469393578</v>
+        <v>83.4495100316808</v>
       </c>
       <c r="H43" t="n">
-        <v>1.385679333576383</v>
+        <v>1.486748173543052</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01040470673075164</v>
+        <v>0.01116360643719118</v>
       </c>
       <c r="J43" t="n">
         <v>137.8269504556986</v>
       </c>
       <c r="K43" t="n">
-        <v>125.130614858072</v>
+        <v>130.7211233694397</v>
       </c>
       <c r="L43" t="n">
-        <v>1.515851310470872</v>
+        <v>1.794886661910823</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01138213434429169</v>
+        <v>0.01347733842859571</v>
       </c>
       <c r="N43" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O43" t="n">
-        <v>186.4977222744996</v>
+        <v>187.2518083194242</v>
       </c>
       <c r="P43" t="n">
-        <v>51.96153846153846</v>
+        <v>78.44234551334827</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.3901657157400171</v>
+        <v>0.5890032279201128</v>
       </c>
       <c r="R43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="S43" t="n">
-        <v>186.4977222744996</v>
+        <v>187.2578670760399</v>
       </c>
       <c r="T43" t="n">
-        <v>51.96153846153846</v>
+        <v>81.45</v>
       </c>
       <c r="U43" t="n">
-        <v>0.3901657157400171</v>
+        <v>0.6115869254053548</v>
       </c>
       <c r="V43" t="n">
         <v>198.9631246433146</v>
       </c>
       <c r="W43" t="n">
-        <v>82.34334736233528</v>
+        <v>91.01274318253468</v>
       </c>
       <c r="X43" t="n">
-        <v>1.602581000227404</v>
+        <v>4.360115194213262</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.01203336509075649</v>
+        <v>0.03273897416871774</v>
       </c>
       <c r="Z43" t="n">
         <v>126.6160396504699</v>
@@ -4860,11 +4866,11 @@
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>86.37455469393578</v>
+        <v>83.4495100316808</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=86.37% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=83.45% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4888,67 +4894,67 @@
         <v>2026</v>
       </c>
       <c r="E44" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="G44" t="n">
-        <v>103.0105577142707</v>
+        <v>98.47151054424607</v>
       </c>
       <c r="H44" t="n">
-        <v>3.857363668221427</v>
+        <v>4.017906093573102</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08070853758538359</v>
+        <v>0.08406760493941366</v>
       </c>
       <c r="J44" t="n">
         <v>101.902133963665</v>
       </c>
       <c r="K44" t="n">
-        <v>100.4112462101342</v>
+        <v>98.09760383854663</v>
       </c>
       <c r="L44" t="n">
-        <v>1.70774239004787</v>
+        <v>1.995254153813774</v>
       </c>
       <c r="M44" t="n">
-        <v>0.03573150024946505</v>
+        <v>0.04174717727346723</v>
       </c>
       <c r="N44" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O44" t="n">
-        <v>186.7796297381574</v>
+        <v>186.8078753071063</v>
       </c>
       <c r="P44" t="n">
-        <v>89.76791078069188</v>
+        <v>101.7924516165815</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.878235350452556</v>
+        <v>2.129827678652157</v>
       </c>
       <c r="R44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="S44" t="n">
-        <v>187.0172162311941</v>
+        <v>187.588295223341</v>
       </c>
       <c r="T44" t="n">
-        <v>101.9423076923077</v>
+        <v>140.5166666666667</v>
       </c>
       <c r="U44" t="n">
-        <v>2.132963152970999</v>
+        <v>2.940063641515191</v>
       </c>
       <c r="V44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="W44" t="n">
-        <v>101.2048277356274</v>
+        <v>110.8339792344407</v>
       </c>
       <c r="X44" t="n">
-        <v>8.886579865047516</v>
+        <v>18.16852661292504</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1859360243765663</v>
+        <v>0.3801444040889246</v>
       </c>
       <c r="Z44" t="n">
         <v>121.0188473841644</v>
@@ -4964,11 +4970,11 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>100.4112462101342</v>
+        <v>98.09760383854663</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=100.41% sobre 26 sem</t>
+          <t>DeepAR: menor SMAPE real=98.10% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -4992,67 +4998,67 @@
         <v>2026</v>
       </c>
       <c r="E45" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G45" t="n">
-        <v>125.5252502727978</v>
+        <v>125.6352641194155</v>
       </c>
       <c r="H45" t="n">
-        <v>3.570361775059859</v>
+        <v>4.174806737513546</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1216607143029661</v>
+        <v>0.1422572842087461</v>
       </c>
       <c r="J45" t="n">
         <v>133.2410714461222</v>
       </c>
       <c r="K45" t="n">
-        <v>129.9289777485386</v>
+        <v>125.8561656686459</v>
       </c>
       <c r="L45" t="n">
-        <v>1.389499155522514</v>
+        <v>1.436951799944003</v>
       </c>
       <c r="M45" t="n">
-        <v>0.04734743155864174</v>
+        <v>0.04896438888106495</v>
       </c>
       <c r="N45" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O45" t="n">
-        <v>184.8553422205679</v>
+        <v>185.7061596829474</v>
       </c>
       <c r="P45" t="n">
-        <v>44.86538461538461</v>
+        <v>55.61887342091581</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.528795983060705</v>
+        <v>1.895223032125765</v>
       </c>
       <c r="R45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="S45" t="n">
-        <v>184.8553422205679</v>
+        <v>185.7183105546389</v>
       </c>
       <c r="T45" t="n">
-        <v>44.86538461538461</v>
+        <v>61.31666666666667</v>
       </c>
       <c r="U45" t="n">
-        <v>1.528795983060705</v>
+        <v>2.089376353246016</v>
       </c>
       <c r="V45" t="n">
         <v>195.8311934408034</v>
       </c>
       <c r="W45" t="n">
-        <v>108.7931937538279</v>
+        <v>116.8108862461247</v>
       </c>
       <c r="X45" t="n">
-        <v>3.422300329439217</v>
+        <v>6.698293822804751</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1166154941348684</v>
+        <v>0.2282455567349079</v>
       </c>
       <c r="Z45" t="n">
         <v>112.5504951429215</v>
@@ -5068,11 +5074,11 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>108.7931937538279</v>
+        <v>116.8108862461247</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=108.79% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=116.81% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5096,67 +5102,67 @@
         <v>2026</v>
       </c>
       <c r="E46" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G46" t="n">
-        <v>134.4608149355389</v>
+        <v>128.0344004160513</v>
       </c>
       <c r="H46" t="n">
-        <v>2.989627752045402</v>
+        <v>3.220915073690542</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07982318570333988</v>
+        <v>0.08599856684029816</v>
       </c>
       <c r="J46" t="n">
         <v>129.1401202444324</v>
       </c>
       <c r="K46" t="n">
-        <v>142.0150170963277</v>
+        <v>138.8108877847343</v>
       </c>
       <c r="L46" t="n">
-        <v>1.064136701870199</v>
+        <v>1.272332175143986</v>
       </c>
       <c r="M46" t="n">
-        <v>0.02841249433445671</v>
+        <v>0.03397132215653529</v>
       </c>
       <c r="N46" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O46" t="n">
-        <v>188.2191225161923</v>
+        <v>188.2918837662258</v>
       </c>
       <c r="P46" t="n">
-        <v>50.70255772644789</v>
+        <v>59.68078838856012</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.353760406546794</v>
+        <v>1.593479539786336</v>
       </c>
       <c r="R46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="S46" t="n">
-        <v>188.4486636457789</v>
+        <v>188.8267987558104</v>
       </c>
       <c r="T46" t="n">
-        <v>57.30769230769231</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="U46" t="n">
-        <v>1.530117775424409</v>
+        <v>2.119983312473926</v>
       </c>
       <c r="V46" t="n">
         <v>196.1388328305384</v>
       </c>
       <c r="W46" t="n">
-        <v>130.2447330072169</v>
+        <v>136.8734725362575</v>
       </c>
       <c r="X46" t="n">
-        <v>5.535956264534023</v>
+        <v>12.9946526042741</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1478102632165947</v>
+        <v>0.346957766655629</v>
       </c>
       <c r="Z46" t="n">
         <v>125.7491255686458</v>
@@ -5172,11 +5178,11 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>134.4608149355389</v>
+        <v>128.0344004160513</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=134.46% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=128.03% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5200,85 +5206,87 @@
         <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G47" t="n">
-        <v>196.7528906936184</v>
+        <v>197.4364926528566</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3503353536484817</v>
+        <v>0.6369573064953509</v>
       </c>
       <c r="I47" t="n">
-        <v>0.006384243346669371</v>
+        <v>0.01160742244182872</v>
       </c>
       <c r="J47" t="n">
         <v>52.02932925897922</v>
       </c>
       <c r="K47" t="n">
-        <v>184.9000553356195</v>
+        <v>180.1798683655593</v>
       </c>
       <c r="L47" t="n">
-        <v>1.571310252876007</v>
+        <v>3.409523834340176</v>
       </c>
       <c r="M47" t="n">
-        <v>0.02863435540548532</v>
+        <v>0.06213255278979819</v>
       </c>
       <c r="N47" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O47" t="n">
-        <v>197.3418108488528</v>
+        <v>196.3603122729191</v>
       </c>
       <c r="P47" t="n">
-        <v>33.3350964253559</v>
+        <v>42.33628413852398</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.6074732833777841</v>
+        <v>0.7715040389708242</v>
       </c>
       <c r="R47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="S47" t="n">
-        <v>198.6941826951429</v>
+        <v>198.2307854609157</v>
       </c>
       <c r="T47" t="n">
-        <v>78.65883520826061</v>
+        <v>105.7600687886773</v>
       </c>
       <c r="U47" t="n">
-        <v>1.433418409262152</v>
+        <v>1.927290547401865</v>
       </c>
       <c r="V47" t="n">
         <v>193.8459595711977</v>
       </c>
       <c r="W47" t="n">
-        <v>184.0090106039409</v>
+        <v>182.5544195123821</v>
       </c>
       <c r="X47" t="n">
-        <v>3.428651107244254</v>
+        <v>7.486138477694856</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.06248111357164927</v>
+        <v>0.1364216579078789</v>
       </c>
       <c r="Z47" t="n">
         <v>130.8486591703272</v>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC47" t="n">
+        <v>180.1798683655593</v>
+      </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=180.18% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5302,85 +5310,87 @@
         <v>2026</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
-        <v>197.6704660202833</v>
+        <v>198.3360471573452</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1674436848912853</v>
+        <v>0.3451178602391139</v>
       </c>
       <c r="I48" t="n">
-        <v>0.006083330967894107</v>
+        <v>0.01253834187971349</v>
       </c>
       <c r="J48" t="n">
         <v>75.82494372432545</v>
       </c>
       <c r="K48" t="n">
-        <v>193.5901427785547</v>
+        <v>184.5453577696137</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6733722969208772</v>
+        <v>1.33804197106262</v>
       </c>
       <c r="M48" t="n">
-        <v>0.02446402531955957</v>
+        <v>0.04861187905767922</v>
       </c>
       <c r="N48" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O48" t="n">
-        <v>196.7233124918204</v>
+        <v>194.3060832548155</v>
       </c>
       <c r="P48" t="n">
-        <v>14.820582969364</v>
+        <v>16.18379468811215</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5384407981603634</v>
+        <v>0.5879671094681982</v>
       </c>
       <c r="R48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="S48" t="n">
-        <v>198.022320718163</v>
+        <v>197.4134559091565</v>
       </c>
       <c r="T48" t="n">
-        <v>33.60628094632519</v>
+        <v>44.83206660190069</v>
       </c>
       <c r="U48" t="n">
-        <v>1.220936637468672</v>
+        <v>1.628776261649435</v>
       </c>
       <c r="V48" t="n">
         <v>192.3368460426438</v>
       </c>
       <c r="W48" t="n">
-        <v>191.8157157323924</v>
+        <v>190.3155545241084</v>
       </c>
       <c r="X48" t="n">
-        <v>3.127699672131663</v>
+        <v>6.479984524027412</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1136312324116862</v>
+        <v>0.2354217810727489</v>
       </c>
       <c r="Z48" t="n">
         <v>148.2729860112375</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC48" t="n">
+        <v>184.5453577696137</v>
+      </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=184.55% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5404,67 +5414,67 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1721830901847086</v>
+        <v>0.2825586781600808</v>
       </c>
       <c r="I49" t="n">
-        <v>0.004913375143490882</v>
+        <v>0.008063026307403767</v>
       </c>
       <c r="J49" t="n">
         <v>67.54170898302603</v>
       </c>
       <c r="K49" t="n">
-        <v>188.5364639501912</v>
+        <v>185.4380858106232</v>
       </c>
       <c r="L49" t="n">
-        <v>1.241250903265522</v>
+        <v>2.498396514648</v>
       </c>
       <c r="M49" t="n">
-        <v>0.03542003647627671</v>
+        <v>0.07129364051073302</v>
       </c>
       <c r="N49" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O49" t="n">
-        <v>197.9461764628585</v>
+        <v>197.0233242641232</v>
       </c>
       <c r="P49" t="n">
-        <v>18.18137305728497</v>
+        <v>21.51664874945378</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.5188192775397886</v>
+        <v>0.6139939004659539</v>
       </c>
       <c r="R49" t="n">
         <v>179.6516960231333</v>
       </c>
       <c r="S49" t="n">
-        <v>199.2925955034458</v>
+        <v>198.8887153465189</v>
       </c>
       <c r="T49" t="n">
-        <v>40.95455768647587</v>
+        <v>56.03326440617489</v>
       </c>
       <c r="U49" t="n">
-        <v>1.16866938288499</v>
+        <v>1.598951721952556</v>
       </c>
       <c r="V49" t="n">
         <v>193.5695579772771</v>
       </c>
       <c r="W49" t="n">
-        <v>188.78130964667</v>
+        <v>187.1159543060611</v>
       </c>
       <c r="X49" t="n">
-        <v>1.811429776081504</v>
+        <v>3.806267332840057</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.05169052330533985</v>
+        <v>0.1086147268154823</v>
       </c>
       <c r="Z49" t="n">
         <v>141.2583029624075</v>
@@ -5482,7 +5492,7 @@
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5506,74 +5516,74 @@
         <v>2026</v>
       </c>
       <c r="E50" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G50" t="n">
-        <v>187.3936004904889</v>
+        <v>181.6093242162106</v>
       </c>
       <c r="H50" t="n">
-        <v>5.208788529216767</v>
+        <v>5.695770875531969</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2262231717357988</v>
+        <v>0.2473733279275557</v>
       </c>
       <c r="J50" t="n">
         <v>162.6912701840232</v>
       </c>
       <c r="K50" t="n">
-        <v>193.8662174422948</v>
+        <v>191.9366713895737</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4434513820849675</v>
+        <v>0.6046137871938644</v>
       </c>
       <c r="M50" t="n">
-        <v>0.01925956056829392</v>
+        <v>0.02625901355890833</v>
       </c>
       <c r="N50" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O50" t="n">
-        <v>191.0040394407015</v>
+        <v>186.1286318640659</v>
       </c>
       <c r="P50" t="n">
-        <v>12.53571605682373</v>
+        <v>15.78147665659587</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5444393510021165</v>
+        <v>0.6854061522951517</v>
       </c>
       <c r="R50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="S50" t="n">
-        <v>192.412989113812</v>
+        <v>189.8841877001909</v>
       </c>
       <c r="T50" t="n">
-        <v>17.22534489261614</v>
+        <v>19.57917005013473</v>
       </c>
       <c r="U50" t="n">
-        <v>0.7481148704719277</v>
+        <v>0.8503439761187723</v>
       </c>
       <c r="V50" t="n">
         <v>160.5521309789579</v>
       </c>
       <c r="W50" t="n">
-        <v>191.1162051189995</v>
+        <v>191.1823462858561</v>
       </c>
       <c r="X50" t="n">
-        <v>24.59129532093463</v>
+        <v>31.87616557327694</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.068025855415185</v>
+        <v>1.384415442921909</v>
       </c>
       <c r="Z50" t="n">
         <v>135.4400555181058</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
@@ -5582,11 +5592,11 @@
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>193.8662174422948</v>
+        <v>181.6093242162106</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=193.87% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=181.61% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5610,67 +5620,67 @@
         <v>2026</v>
       </c>
       <c r="E51" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>188.6384797133506</v>
+        <v>183.4879098173768</v>
       </c>
       <c r="H51" t="n">
-        <v>1.903489031688147</v>
+        <v>2.111044521326194</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1592461412131261</v>
+        <v>0.1766102606076816</v>
       </c>
       <c r="J51" t="n">
         <v>169.9274838481079</v>
       </c>
       <c r="K51" t="n">
-        <v>178.9137103796107</v>
+        <v>172.3082229992432</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2427665114409492</v>
+        <v>0.3449617018585135</v>
       </c>
       <c r="M51" t="n">
-        <v>0.02030987808133431</v>
+        <v>0.02885954107051616</v>
       </c>
       <c r="N51" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O51" t="n">
-        <v>196.1122293407287</v>
+        <v>192.198574523709</v>
       </c>
       <c r="P51" t="n">
-        <v>17.6295960754129</v>
+        <v>22.53175402442044</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.474894312191406</v>
+        <v>1.885009487010338</v>
       </c>
       <c r="R51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="S51" t="n">
-        <v>193.2719749453459</v>
+        <v>189.3725933315535</v>
       </c>
       <c r="T51" t="n">
-        <v>6.58219201990204</v>
+        <v>8.076082774173011</v>
       </c>
       <c r="U51" t="n">
-        <v>0.5506670448022621</v>
+        <v>0.6756461405844087</v>
       </c>
       <c r="V51" t="n">
         <v>165.5121650610737</v>
       </c>
       <c r="W51" t="n">
-        <v>190.5740611048891</v>
+        <v>191.0961530583145</v>
       </c>
       <c r="X51" t="n">
-        <v>11.55415004784484</v>
+        <v>17.35802982679935</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.9666217033491109</v>
+        <v>1.45217504433354</v>
       </c>
       <c r="Z51" t="n">
         <v>151.1230387281904</v>
@@ -5688,7 +5698,7 @@
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -5712,85 +5722,87 @@
         <v>2026</v>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F52" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G52" t="n">
-        <v>185.8425679938319</v>
+        <v>179.8956291501944</v>
       </c>
       <c r="H52" t="n">
-        <v>2.98718902787148</v>
+        <v>3.205054604669189</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1855036850220985</v>
+        <v>0.1990330823780595</v>
       </c>
       <c r="J52" t="n">
         <v>174.432365021141</v>
       </c>
       <c r="K52" t="n">
-        <v>197.6004713705168</v>
+        <v>195.1242849844105</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2735075320235206</v>
+        <v>0.3635914258970534</v>
       </c>
       <c r="M52" t="n">
-        <v>0.01698474873811888</v>
+        <v>0.02257893582128024</v>
       </c>
       <c r="N52" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O52" t="n">
-        <v>196.3981217470596</v>
+        <v>196.2047085093486</v>
       </c>
       <c r="P52" t="n">
-        <v>26.6248126355684</v>
+        <v>31.19829930124861</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.653394147755072</v>
+        <v>1.937406515893568</v>
       </c>
       <c r="R52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="S52" t="n">
-        <v>190.2706087569731</v>
+        <v>189.4513429810953</v>
       </c>
       <c r="T52" t="n">
-        <v>9.21501289688549</v>
+        <v>10.50655857373429</v>
       </c>
       <c r="U52" t="n">
-        <v>0.572249976131061</v>
+        <v>0.6524546368319374</v>
       </c>
       <c r="V52" t="n">
         <v>154.7555469695623</v>
       </c>
       <c r="W52" t="n">
-        <v>191.7742099589465</v>
+        <v>191.9112853316146</v>
       </c>
       <c r="X52" t="n">
-        <v>20.05581811117946</v>
+        <v>25.03129298284138</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.245461245017937</v>
+        <v>1.554436979334221</v>
       </c>
       <c r="Z52" t="n">
         <v>133.8716916594558</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>179.8956291501944</v>
+      </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=179.90% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5814,67 +5826,67 @@
         <v>2026</v>
       </c>
       <c r="E53" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" t="n">
-        <v>3167</v>
+        <v>3878</v>
       </c>
       <c r="G53" t="n">
-        <v>20.09590459559316</v>
+        <v>22.34651210656633</v>
       </c>
       <c r="H53" t="n">
-        <v>26.06827811607847</v>
+        <v>33.31859414632342</v>
       </c>
       <c r="I53" t="n">
-        <v>0.02933397449545533</v>
+        <v>0.03749257187454415</v>
       </c>
       <c r="J53" t="n">
         <v>35.23746831954708</v>
       </c>
       <c r="K53" t="n">
-        <v>21.82929250468235</v>
+        <v>28.21900210882411</v>
       </c>
       <c r="L53" t="n">
-        <v>25.13835366588721</v>
+        <v>34.11616154524422</v>
       </c>
       <c r="M53" t="n">
-        <v>0.02828755401524011</v>
+        <v>0.03839005431025284</v>
       </c>
       <c r="N53" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O53" t="n">
-        <v>164.5356140391471</v>
+        <v>165.7517623458724</v>
       </c>
       <c r="P53" t="n">
-        <v>1223.115384615385</v>
+        <v>1482.410777604546</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.376340828402367</v>
+        <v>1.668119380513247</v>
       </c>
       <c r="R53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="S53" t="n">
-        <v>164.5356140391471</v>
+        <v>165.9235835561136</v>
       </c>
       <c r="T53" t="n">
-        <v>1223.115384615385</v>
+        <v>1578.883333333333</v>
       </c>
       <c r="U53" t="n">
-        <v>1.376340828402367</v>
+        <v>1.776677509157509</v>
       </c>
       <c r="V53" t="n">
         <v>188.2648408233968</v>
       </c>
       <c r="W53" t="n">
-        <v>52.86613593151077</v>
+        <v>66.5088389137223</v>
       </c>
       <c r="X53" t="n">
-        <v>141.2650529879882</v>
+        <v>290.2219395031086</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.1589619936919779</v>
+        <v>0.3265794132430585</v>
       </c>
       <c r="Z53" t="n">
         <v>92.2349408254034</v>
@@ -5890,11 +5902,11 @@
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>20.09590459559316</v>
+        <v>22.34651210656633</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=20.10% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=22.35% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -5918,67 +5930,67 @@
         <v>2026</v>
       </c>
       <c r="E54" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F54" t="n">
-        <v>1472</v>
+        <v>1793</v>
       </c>
       <c r="G54" t="n">
-        <v>18.73958210756178</v>
+        <v>17.79050811290443</v>
       </c>
       <c r="H54" t="n">
-        <v>10.69622688969862</v>
+        <v>10.54307531656366</v>
       </c>
       <c r="I54" t="n">
-        <v>0.02115734280744945</v>
+        <v>0.02085440604594179</v>
       </c>
       <c r="J54" t="n">
         <v>38.4591918317379</v>
       </c>
       <c r="K54" t="n">
-        <v>24.99748527673886</v>
+        <v>29.33637308392764</v>
       </c>
       <c r="L54" t="n">
-        <v>16.11825956854353</v>
+        <v>22.61307561621521</v>
       </c>
       <c r="M54" t="n">
-        <v>0.03188222787977308</v>
+        <v>0.04472909911847635</v>
       </c>
       <c r="N54" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O54" t="n">
-        <v>164.4694964886822</v>
+        <v>165.2785945174107</v>
       </c>
       <c r="P54" t="n">
-        <v>556.8269230769231</v>
+        <v>633.6555268756704</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.101414378868668</v>
+        <v>1.253382836975451</v>
       </c>
       <c r="R54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="S54" t="n">
-        <v>164.4694964886822</v>
+        <v>165.8297134659983</v>
       </c>
       <c r="T54" t="n">
-        <v>556.8269230769231</v>
+        <v>714.9833333333333</v>
       </c>
       <c r="U54" t="n">
-        <v>1.101414378868668</v>
+        <v>1.414250804600543</v>
       </c>
       <c r="V54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="W54" t="n">
-        <v>52.7013059681811</v>
+        <v>66.31045525836954</v>
       </c>
       <c r="X54" t="n">
-        <v>63.00118284664776</v>
+        <v>129.7378537080727</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1246175531340929</v>
+        <v>0.2566239735105099</v>
       </c>
       <c r="Z54" t="n">
         <v>91.67135817890519</v>
@@ -5994,11 +6006,11 @@
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>18.73958210756178</v>
+        <v>17.79050811290443</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=18.74% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=17.79% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6022,67 +6034,67 @@
         <v>2026</v>
       </c>
       <c r="E55" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F55" t="n">
-        <v>1690</v>
+        <v>2079</v>
       </c>
       <c r="G55" t="n">
-        <v>21.72360139831728</v>
+        <v>21.53694792260096</v>
       </c>
       <c r="H55" t="n">
-        <v>13.22536243480747</v>
+        <v>14.33813548159063</v>
       </c>
       <c r="I55" t="n">
-        <v>0.02094546991961748</v>
+        <v>0.02270780758663031</v>
       </c>
       <c r="J55" t="n">
         <v>38.25160771522186</v>
       </c>
       <c r="K55" t="n">
-        <v>26.16584507117277</v>
+        <v>30.17748998611819</v>
       </c>
       <c r="L55" t="n">
-        <v>18.47461648062351</v>
+        <v>26.47224732773434</v>
       </c>
       <c r="M55" t="n">
-        <v>0.02925889749175726</v>
+        <v>0.04192502571032985</v>
       </c>
       <c r="N55" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O55" t="n">
-        <v>164.6853792291117</v>
+        <v>165.9721223123166</v>
       </c>
       <c r="P55" t="n">
-        <v>666.4807692307693</v>
+        <v>822.3178682226661</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.05552894846846</v>
+        <v>1.3023336228496</v>
       </c>
       <c r="R55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="S55" t="n">
-        <v>164.6853792291117</v>
+        <v>166.0862873260907</v>
       </c>
       <c r="T55" t="n">
-        <v>666.4807692307693</v>
+        <v>864.1</v>
       </c>
       <c r="U55" t="n">
-        <v>1.05552894846846</v>
+        <v>1.368505449038376</v>
       </c>
       <c r="V55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="W55" t="n">
-        <v>50.45851269062578</v>
+        <v>64.36158086853793</v>
       </c>
       <c r="X55" t="n">
-        <v>73.8401566078978</v>
+        <v>154.3932353666919</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.1169432434622789</v>
+        <v>0.2445179769632939</v>
       </c>
       <c r="Z55" t="n">
         <v>92.1901984902002</v>
@@ -6098,11 +6110,11 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>21.72360139831728</v>
+        <v>21.53694792260096</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=21.72% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=21.54% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6126,67 +6138,67 @@
         <v>2026</v>
       </c>
       <c r="E56" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="G56" t="n">
-        <v>75.15141959765678</v>
+        <v>78.5538480505229</v>
       </c>
       <c r="H56" t="n">
-        <v>3.663066571838782</v>
+        <v>4.067269629281515</v>
       </c>
       <c r="I56" t="n">
-        <v>0.09285339852569789</v>
+        <v>0.1030993568892653</v>
       </c>
       <c r="J56" t="n">
         <v>154.1439500713238</v>
       </c>
       <c r="K56" t="n">
-        <v>69.90930581618821</v>
+        <v>76.25300836710791</v>
       </c>
       <c r="L56" t="n">
-        <v>2.311390036345996</v>
+        <v>2.409234264790217</v>
       </c>
       <c r="M56" t="n">
-        <v>0.05859036847518367</v>
+        <v>0.06107057705425138</v>
       </c>
       <c r="N56" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O56" t="n">
-        <v>170.9999889298593</v>
+        <v>172.8259293765196</v>
       </c>
       <c r="P56" t="n">
-        <v>63.55748541917569</v>
+        <v>70.36836257459157</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.611089617723085</v>
+        <v>1.783735426478874</v>
       </c>
       <c r="R56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="S56" t="n">
-        <v>171.0772515772597</v>
+        <v>173.2900008669255</v>
       </c>
       <c r="T56" t="n">
-        <v>65.57692307692308</v>
+        <v>83.83333333333333</v>
       </c>
       <c r="U56" t="n">
-        <v>1.662279418933411</v>
+        <v>2.125052809463456</v>
       </c>
       <c r="V56" t="n">
         <v>197.7368060568652</v>
       </c>
       <c r="W56" t="n">
-        <v>60.29853061336017</v>
+        <v>60.08762800466895</v>
       </c>
       <c r="X56" t="n">
-        <v>1.876042993102666</v>
+        <v>2.000377583772848</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.04755495546521333</v>
+        <v>0.05070665611591503</v>
       </c>
       <c r="Z56" t="n">
         <v>104.7066447751141</v>
@@ -6202,11 +6214,11 @@
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>60.29853061336017</v>
+        <v>60.08762800466895</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=60.30% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=60.09% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6230,67 +6242,67 @@
         <v>2026</v>
       </c>
       <c r="E57" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F57" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G57" t="n">
-        <v>95.70003000461385</v>
+        <v>100.2985096506785</v>
       </c>
       <c r="H57" t="n">
-        <v>1.739251349080757</v>
+        <v>1.945993378968185</v>
       </c>
       <c r="I57" t="n">
-        <v>0.09088184711068618</v>
+        <v>0.1016848271178673</v>
       </c>
       <c r="J57" t="n">
         <v>164.0555422208552</v>
       </c>
       <c r="K57" t="n">
-        <v>130.4479548242629</v>
+        <v>133.1646447608327</v>
       </c>
       <c r="L57" t="n">
-        <v>1.557985936312652</v>
+        <v>1.499200354839822</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0814101077106546</v>
+        <v>0.07833835949522255</v>
       </c>
       <c r="N57" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O57" t="n">
-        <v>169.926070178636</v>
+        <v>173.2853535587645</v>
       </c>
       <c r="P57" t="n">
-        <v>28.29105662783227</v>
+        <v>32.67215808699144</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.478304722551654</v>
+        <v>1.707232297164804</v>
       </c>
       <c r="R57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="S57" t="n">
-        <v>169.926070178636</v>
+        <v>173.4749001434029</v>
       </c>
       <c r="T57" t="n">
-        <v>28.44230769230769</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="U57" t="n">
-        <v>1.486208109330252</v>
+        <v>1.915959068147181</v>
       </c>
       <c r="V57" t="n">
         <v>197.2831175654684</v>
       </c>
       <c r="W57" t="n">
-        <v>106.6582394576391</v>
+        <v>105.6158970996608</v>
       </c>
       <c r="X57" t="n">
-        <v>1.034083610053474</v>
+        <v>1.056349174846893</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.05403441463375435</v>
+        <v>0.05519786674575532</v>
       </c>
       <c r="Z57" t="n">
         <v>124.2225772452616</v>
@@ -6306,11 +6318,11 @@
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>95.70003000461385</v>
+        <v>100.2985096506785</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=95.70% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=100.30% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6334,67 +6346,67 @@
         <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F58" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G58" t="n">
-        <v>91.29340382256389</v>
+        <v>91.80424842220479</v>
       </c>
       <c r="H58" t="n">
-        <v>2.251105847677055</v>
+        <v>2.486029720446764</v>
       </c>
       <c r="I58" t="n">
-        <v>0.09251912037717154</v>
+        <v>0.1021743527540411</v>
       </c>
       <c r="J58" t="n">
         <v>158.4722608607674</v>
       </c>
       <c r="K58" t="n">
-        <v>125.4554034373361</v>
+        <v>134.4011905309047</v>
       </c>
       <c r="L58" t="n">
-        <v>1.849110789028315</v>
+        <v>1.963797120224555</v>
       </c>
       <c r="M58" t="n">
-        <v>0.07599736096699983</v>
+        <v>0.08071090142202128</v>
       </c>
       <c r="N58" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O58" t="n">
-        <v>172.5722834767986</v>
+        <v>173.7396733637671</v>
       </c>
       <c r="P58" t="n">
-        <v>37.53846153846154</v>
+        <v>42.86137514228709</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.542808591357268</v>
+        <v>1.761577195675812</v>
       </c>
       <c r="R58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="S58" t="n">
-        <v>172.5722834767986</v>
+        <v>173.988426541041</v>
       </c>
       <c r="T58" t="n">
-        <v>37.53846153846154</v>
+        <v>47.51666666666667</v>
       </c>
       <c r="U58" t="n">
-        <v>1.542808591357268</v>
+        <v>1.952906926962925</v>
       </c>
       <c r="V58" t="n">
         <v>197.6615055783608</v>
       </c>
       <c r="W58" t="n">
-        <v>87.35952124159834</v>
+        <v>85.12382338909936</v>
       </c>
       <c r="X58" t="n">
-        <v>1.166134199350967</v>
+        <v>1.284006266668031</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.04792742663656684</v>
+        <v>0.05277189896400845</v>
       </c>
       <c r="Z58" t="n">
         <v>111.9755139895278</v>
@@ -6410,11 +6422,11 @@
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>87.35952124159834</v>
+        <v>85.12382338909936</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=87.36% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=85.12% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6438,85 +6450,87 @@
         <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F59" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G59" t="n">
-        <v>199.5468394226922</v>
+        <v>199.5971905979486</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2449063057226444</v>
+        <v>0.3789187982929585</v>
       </c>
       <c r="I59" t="n">
-        <v>0.003284577444729514</v>
+        <v>0.00508189503159039</v>
       </c>
       <c r="J59" t="n">
         <v>163.442478475025</v>
       </c>
       <c r="K59" t="n">
-        <v>193.8469810539535</v>
+        <v>193.6239631122541</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2418557896529395</v>
+        <v>0.3692266830685438</v>
       </c>
       <c r="M59" t="n">
-        <v>0.003243665242621149</v>
+        <v>0.00495190857426379</v>
       </c>
       <c r="N59" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O59" t="n">
-        <v>176.9975490196078</v>
+        <v>180.0693359196252</v>
       </c>
       <c r="P59" t="n">
-        <v>10.55769230769231</v>
+        <v>38.93333333333333</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.1415952027854794</v>
+        <v>0.5221570271025425</v>
       </c>
       <c r="R59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="S59" t="n">
-        <v>176.9975490196078</v>
+        <v>180.0693359196252</v>
       </c>
       <c r="T59" t="n">
-        <v>10.55769230769231</v>
+        <v>38.93333333333333</v>
       </c>
       <c r="U59" t="n">
-        <v>0.1415952027854794</v>
+        <v>0.5221570271025425</v>
       </c>
       <c r="V59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="W59" t="n">
-        <v>175.6926664465242</v>
+        <v>173.3128205112955</v>
       </c>
       <c r="X59" t="n">
-        <v>0.6390549945212811</v>
+        <v>1.359807121174114</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.008570729180503351</v>
+        <v>0.01823714496126222</v>
       </c>
       <c r="Z59" t="n">
         <v>167.6265476269683</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>173.3128205112955</v>
+      </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=173.31% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6540,67 +6554,67 @@
         <v>2026</v>
       </c>
       <c r="E60" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F60" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G60" t="n">
-        <v>197.8217646398928</v>
+        <v>198.0292156265697</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1646774938454602</v>
+        <v>0.3093871613327322</v>
       </c>
       <c r="I60" t="n">
-        <v>0.004169710241378959</v>
+        <v>0.007833825892267313</v>
       </c>
       <c r="J60" t="n">
         <v>179.6544870721095</v>
       </c>
       <c r="K60" t="n">
-        <v>198.8417254797347</v>
+        <v>196.702728441294</v>
       </c>
       <c r="L60" t="n">
-        <v>0.1612453958722502</v>
+        <v>0.2820001549430792</v>
       </c>
       <c r="M60" t="n">
-        <v>0.004082807934730184</v>
+        <v>0.007140374234988555</v>
       </c>
       <c r="N60" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O60" t="n">
-        <v>173.1428571428572</v>
+        <v>177.1128125605738</v>
       </c>
       <c r="P60" t="n">
-        <v>5.673076923076923</v>
+        <v>19.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.1436449292122658</v>
+        <v>0.483620826080076</v>
       </c>
       <c r="R60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="S60" t="n">
-        <v>173.1428571428572</v>
+        <v>177.1128125605738</v>
       </c>
       <c r="T60" t="n">
-        <v>5.673076923076923</v>
+        <v>19.1</v>
       </c>
       <c r="U60" t="n">
-        <v>0.1436449292122658</v>
+        <v>0.483620826080076</v>
       </c>
       <c r="V60" t="n">
         <v>199.0965028052728</v>
       </c>
       <c r="W60" t="n">
-        <v>187.6551097725555</v>
+        <v>179.0063969665014</v>
       </c>
       <c r="X60" t="n">
-        <v>0.3705474387374383</v>
+        <v>0.555374994757333</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.009382432378222842</v>
+        <v>0.01406235150517064</v>
       </c>
       <c r="Z60" t="n">
         <v>167.0169829765832</v>
@@ -6618,7 +6632,7 @@
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6656,7 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -6651,58 +6665,58 @@
         <v>199.9531681019307</v>
       </c>
       <c r="H61" t="n">
-        <v>0.09296982760330753</v>
+        <v>0.0805738505895332</v>
       </c>
       <c r="I61" t="n">
-        <v>0.002097162331387171</v>
+        <v>0.001817540687202215</v>
       </c>
       <c r="J61" t="n">
         <v>178.3754768379913</v>
       </c>
       <c r="K61" t="n">
-        <v>197.512214632238</v>
+        <v>197.8439193479396</v>
       </c>
       <c r="L61" t="n">
-        <v>0.153430299764158</v>
+        <v>0.1444126059750072</v>
       </c>
       <c r="M61" t="n">
-        <v>0.003460996470078286</v>
+        <v>0.003257580284224045</v>
       </c>
       <c r="N61" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O61" t="n">
-        <v>185.5555555555555</v>
+        <v>188.1818181818182</v>
       </c>
       <c r="P61" t="n">
-        <v>5.057692307692307</v>
+        <v>19.98333333333333</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1140886464444902</v>
+        <v>0.4507730626439213</v>
       </c>
       <c r="R61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="S61" t="n">
-        <v>185.5555555555555</v>
+        <v>188.1818181818182</v>
       </c>
       <c r="T61" t="n">
-        <v>5.057692307692307</v>
+        <v>19.98333333333333</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1140886464444902</v>
+        <v>0.4507730626439213</v>
       </c>
       <c r="V61" t="n">
         <v>199.3694289811982</v>
       </c>
       <c r="W61" t="n">
-        <v>191.6929698105321</v>
+        <v>192.8005738357945</v>
       </c>
       <c r="X61" t="n">
-        <v>0.3417249318550903</v>
+        <v>0.7061909943580195</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.007708443408545673</v>
+        <v>0.01592986875754732</v>
       </c>
       <c r="Z61" t="n">
         <v>167.1297521794813</v>
@@ -6744,67 +6758,67 @@
         <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F62" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="G62" t="n">
-        <v>121.6044579366546</v>
+        <v>114.0814773305413</v>
       </c>
       <c r="H62" t="n">
-        <v>0.808461210422098</v>
+        <v>0.9539496620132599</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02428039299249848</v>
+        <v>0.02864982560715562</v>
       </c>
       <c r="J62" t="n">
         <v>51.86246745886869</v>
       </c>
       <c r="K62" t="n">
-        <v>139.4558906579279</v>
+        <v>138.5434288302061</v>
       </c>
       <c r="L62" t="n">
-        <v>4.069888424207752</v>
+        <v>5.143253855969866</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1222303421629733</v>
+        <v>0.1544665634829054</v>
       </c>
       <c r="N62" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O62" t="n">
-        <v>181.2762042013983</v>
+        <v>182.7789372555233</v>
       </c>
       <c r="P62" t="n">
-        <v>51.13178595466775</v>
+        <v>65.25866986829126</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.535633177427844</v>
+        <v>1.9599037407652</v>
       </c>
       <c r="R62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="S62" t="n">
-        <v>181.467404226567</v>
+        <v>183.2056271741027</v>
       </c>
       <c r="T62" t="n">
-        <v>75.08417009920558</v>
+        <v>97.39562605025814</v>
       </c>
       <c r="U62" t="n">
-        <v>2.254991499929215</v>
+        <v>2.925068074714463</v>
       </c>
       <c r="V62" t="n">
         <v>188.4656733609786</v>
       </c>
       <c r="W62" t="n">
-        <v>129.6986779309068</v>
+        <v>135.8519961168652</v>
       </c>
       <c r="X62" t="n">
-        <v>4.324530451610826</v>
+        <v>9.46436992033137</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.1298779675753603</v>
+        <v>0.2842419872835324</v>
       </c>
       <c r="Z62" t="n">
         <v>127.8730185036105</v>
@@ -6820,11 +6834,11 @@
         </is>
       </c>
       <c r="AC62" t="n">
-        <v>121.6044579366546</v>
+        <v>114.0814773305413</v>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=121.60% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=114.08% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6848,85 +6862,87 @@
         <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G63" t="n">
-        <v>151.8327488265072</v>
+        <v>145.6703907877284</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5314209835917494</v>
+        <v>0.6572830526929875</v>
       </c>
       <c r="I63" t="n">
-        <v>0.03465553591794576</v>
+        <v>0.04286337413119136</v>
       </c>
       <c r="J63" t="n">
         <v>69.84803023883232</v>
       </c>
       <c r="K63" t="n">
-        <v>166.7862371116838</v>
+        <v>160.5300534379983</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5116838462098096</v>
+        <v>0.8949442505513538</v>
       </c>
       <c r="M63" t="n">
-        <v>0.03336841874610537</v>
+        <v>0.05836196457640783</v>
       </c>
       <c r="N63" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O63" t="n">
-        <v>182.0347497758348</v>
+        <v>182.3612136565039</v>
       </c>
       <c r="P63" t="n">
-        <v>15.1677508887776</v>
+        <v>19.08095021402942</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9891339483205281</v>
+        <v>1.244325263600859</v>
       </c>
       <c r="R63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="S63" t="n">
-        <v>182.4732506191762</v>
+        <v>183.8520986065637</v>
       </c>
       <c r="T63" t="n">
-        <v>26.8344783570363</v>
+        <v>36.48551160183993</v>
       </c>
       <c r="U63" t="n">
-        <v>1.749955792592544</v>
+        <v>2.379328247929239</v>
       </c>
       <c r="V63" t="n">
         <v>186.3893216158546</v>
       </c>
       <c r="W63" t="n">
-        <v>145.2710127269957</v>
+        <v>148.7792654729243</v>
       </c>
       <c r="X63" t="n">
-        <v>2.104858798994898</v>
+        <v>4.435610872164337</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.1372640749293596</v>
+        <v>0.2892593191547968</v>
       </c>
       <c r="Z63" t="n">
         <v>131.8859677830883</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>145.6703907877284</v>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=145.67% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -6950,67 +6966,67 @@
         <v>2026</v>
       </c>
       <c r="E64" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F64" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G64" t="n">
-        <v>146.1444121266724</v>
+        <v>135.4248706491216</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8390743959406475</v>
+        <v>0.8779678022912319</v>
       </c>
       <c r="I64" t="n">
-        <v>0.03769532594426607</v>
+        <v>0.03944260799286736</v>
       </c>
       <c r="J64" t="n">
         <v>72.92360982323459</v>
       </c>
       <c r="K64" t="n">
-        <v>159.3206622613936</v>
+        <v>160.2316722114404</v>
       </c>
       <c r="L64" t="n">
-        <v>2.050984692736824</v>
+        <v>3.436662129766569</v>
       </c>
       <c r="M64" t="n">
-        <v>0.09214026416899954</v>
+        <v>0.1543916722624319</v>
       </c>
       <c r="N64" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O64" t="n">
-        <v>181.8322100587866</v>
+        <v>183.5148640295954</v>
       </c>
       <c r="P64" t="n">
-        <v>31.39477888154723</v>
+        <v>39.503279554723</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.410407025423995</v>
+        <v>1.774680535941508</v>
       </c>
       <c r="R64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="S64" t="n">
-        <v>182.0195781924902</v>
+        <v>183.8609121554279</v>
       </c>
       <c r="T64" t="n">
-        <v>49.51562916668028</v>
+        <v>63.45549192010526</v>
       </c>
       <c r="U64" t="n">
-        <v>2.224484252890312</v>
+        <v>2.850731070396418</v>
       </c>
       <c r="V64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="W64" t="n">
-        <v>147.8578523070447</v>
+        <v>152.6880272401768</v>
       </c>
       <c r="X64" t="n">
-        <v>3.052893810965289</v>
+        <v>6.439831266841253</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.1371509222952257</v>
+        <v>0.2893087189932895</v>
       </c>
       <c r="Z64" t="n">
         <v>132.574641557417</v>
@@ -7026,11 +7042,11 @@
         </is>
       </c>
       <c r="AC64" t="n">
-        <v>146.1444121266724</v>
+        <v>135.4248706491216</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=146.14% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=135.42% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7054,67 +7070,67 @@
         <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F65" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G65" t="n">
-        <v>150.9338289242287</v>
+        <v>142.2404520386731</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8811472161839162</v>
+        <v>0.9302240774001294</v>
       </c>
       <c r="I65" t="n">
-        <v>0.02301772319827373</v>
+        <v>0.02429973100147277</v>
       </c>
       <c r="J65" t="n">
         <v>124.1398173354868</v>
       </c>
       <c r="K65" t="n">
-        <v>159.1362720494756</v>
+        <v>151.7073283857741</v>
       </c>
       <c r="L65" t="n">
-        <v>0.6961974997610457</v>
+        <v>1.071747818441324</v>
       </c>
       <c r="M65" t="n">
-        <v>0.01818638366722732</v>
+        <v>0.02799667770622234</v>
       </c>
       <c r="N65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="O65" t="n">
-        <v>190.7194605391035</v>
+        <v>191.3946073876266</v>
       </c>
       <c r="P65" t="n">
-        <v>41.64065176267066</v>
+        <v>57.64655096611156</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.087755801147315</v>
+        <v>1.50586908646169</v>
       </c>
       <c r="R65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="S65" t="n">
-        <v>190.927725291808</v>
+        <v>191.8218723809736</v>
       </c>
       <c r="T65" t="n">
-        <v>45.19230769230769</v>
+        <v>74.69815431704413</v>
       </c>
       <c r="U65" t="n">
-        <v>1.180533751962323</v>
+        <v>1.951298725016663</v>
       </c>
       <c r="V65" t="n">
         <v>191.9303948964172</v>
       </c>
       <c r="W65" t="n">
-        <v>162.7562716199893</v>
+        <v>166.2596534933332</v>
       </c>
       <c r="X65" t="n">
-        <v>6.581622894105985</v>
+        <v>14.1171104545942</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.1719281082541972</v>
+        <v>0.3687734975893995</v>
       </c>
       <c r="Z65" t="n">
         <v>113.9712651292745</v>
@@ -7130,11 +7146,11 @@
         </is>
       </c>
       <c r="AC65" t="n">
-        <v>150.9338289242287</v>
+        <v>142.2404520386731</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=150.93% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=142.24% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7158,67 +7174,67 @@
         <v>2026</v>
       </c>
       <c r="E66" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F66" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G66" t="n">
-        <v>180.1220212764491</v>
+        <v>179.0102200549941</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5174825916730073</v>
+        <v>0.5707652943023513</v>
       </c>
       <c r="I66" t="n">
-        <v>0.02444919966563743</v>
+        <v>0.0269666165918725</v>
       </c>
       <c r="J66" t="n">
         <v>146.9871894171194</v>
       </c>
       <c r="K66" t="n">
-        <v>171.7530356338314</v>
+        <v>159.7628188702215</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4975427705603367</v>
+        <v>0.5972460506798528</v>
       </c>
       <c r="M66" t="n">
-        <v>0.02350711451045441</v>
+        <v>0.02821773751920167</v>
       </c>
       <c r="N66" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O66" t="n">
-        <v>191.8776960511818</v>
+        <v>192.3239464940251</v>
       </c>
       <c r="P66" t="n">
-        <v>19.4398982130394</v>
+        <v>27.74886181250367</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.918465588095764</v>
+        <v>1.311034368817536</v>
       </c>
       <c r="R66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="S66" t="n">
-        <v>191.9387057888072</v>
+        <v>192.564066052336</v>
       </c>
       <c r="T66" t="n">
-        <v>19.73076923076923</v>
+        <v>32.496373557589</v>
       </c>
       <c r="U66" t="n">
-        <v>0.9322082022510193</v>
+        <v>1.535337300816253</v>
       </c>
       <c r="V66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="W66" t="n">
-        <v>173.5926484386023</v>
+        <v>175.0461202354696</v>
       </c>
       <c r="X66" t="n">
-        <v>2.781624413232052</v>
+        <v>5.914462434333503</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.1314217942173714</v>
+        <v>0.2794371739239216</v>
       </c>
       <c r="Z66" t="n">
         <v>118.44057480835</v>
@@ -7234,11 +7250,11 @@
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>171.7530356338314</v>
+        <v>159.7628188702215</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=171.75% sobre 26 sem</t>
+          <t>DeepAR: menor SMAPE real=159.76% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7262,67 +7278,67 @@
         <v>2026</v>
       </c>
       <c r="E67" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G67" t="n">
-        <v>177.6001138412982</v>
+        <v>178.8082242945412</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5310402008178121</v>
+        <v>0.5883220185903816</v>
       </c>
       <c r="I67" t="n">
-        <v>0.01945424891376072</v>
+        <v>0.02155272420708896</v>
       </c>
       <c r="J67" t="n">
         <v>137.6516466078508</v>
       </c>
       <c r="K67" t="n">
-        <v>183.7604374326015</v>
+        <v>182.131586053904</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5406099533335619</v>
+        <v>0.6788572770473629</v>
       </c>
       <c r="M67" t="n">
-        <v>0.01980482942950656</v>
+        <v>0.02486941369835789</v>
       </c>
       <c r="N67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="O67" t="n">
-        <v>192.7117313666085</v>
+        <v>192.8902232559284</v>
       </c>
       <c r="P67" t="n">
-        <v>16.43981187413353</v>
+        <v>20.48462416805092</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.6022598511416978</v>
+        <v>0.7504384354638001</v>
       </c>
       <c r="R67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="S67" t="n">
-        <v>194.196348065024</v>
+        <v>194.743138152032</v>
       </c>
       <c r="T67" t="n">
-        <v>26.5</v>
+        <v>42.38960120891837</v>
       </c>
       <c r="U67" t="n">
-        <v>0.9708070978820835</v>
+        <v>1.552910404905997</v>
       </c>
       <c r="V67" t="n">
         <v>191.2393501485975</v>
       </c>
       <c r="W67" t="n">
-        <v>181.3259710545283</v>
+        <v>182.8543417202187</v>
       </c>
       <c r="X67" t="n">
-        <v>3.854970419694336</v>
+        <v>8.53304155574738</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.1412238734175372</v>
+        <v>0.3126014078808427</v>
       </c>
       <c r="Z67" t="n">
         <v>116.630186356802</v>
@@ -7338,11 +7354,11 @@
         </is>
       </c>
       <c r="AC67" t="n">
-        <v>177.6001138412982</v>
+        <v>178.8082242945412</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=177.60% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=178.81% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7382,7 @@
         <v>2026</v>
       </c>
       <c r="E68" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -7375,22 +7391,22 @@
         <v>199.988140539529</v>
       </c>
       <c r="H68" t="n">
-        <v>0.04482977413361657</v>
+        <v>0.03885247091580103</v>
       </c>
       <c r="I68" t="n">
-        <v>0.002330332638524578</v>
+        <v>0.002019621620054634</v>
       </c>
       <c r="J68" t="n">
         <v>183.5383709430125</v>
       </c>
       <c r="K68" t="n">
-        <v>199.8412794270195</v>
+        <v>199.8624421700836</v>
       </c>
       <c r="L68" t="n">
-        <v>0.05254346953207076</v>
+        <v>0.04797058629323744</v>
       </c>
       <c r="M68" t="n">
-        <v>0.002731304459106992</v>
+        <v>0.002493597728043531</v>
       </c>
       <c r="N68" t="n">
         <v>198.3312090033645</v>
@@ -7399,10 +7415,10 @@
         <v>200</v>
       </c>
       <c r="P68" t="n">
-        <v>8.849613765279083</v>
+        <v>14.65556081304576</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.4600189091763006</v>
+        <v>0.7618225243948412</v>
       </c>
       <c r="R68" t="n">
         <v>188.2784643365136</v>
@@ -7411,22 +7427,22 @@
         <v>200</v>
       </c>
       <c r="T68" t="n">
-        <v>9.26923076923077</v>
+        <v>15.88333333333333</v>
       </c>
       <c r="U68" t="n">
-        <v>0.4818313590243415</v>
+        <v>0.8256443578081004</v>
       </c>
       <c r="V68" t="n">
         <v>199.7672857698158</v>
       </c>
       <c r="W68" t="n">
-        <v>197.5760121573963</v>
+        <v>197.8992105364101</v>
       </c>
       <c r="X68" t="n">
-        <v>0.7060823159264591</v>
+        <v>0.8889352246395691</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.0367034342261967</v>
+        <v>0.04620845872070534</v>
       </c>
       <c r="Z68" t="n">
         <v>177.2448922419183</v>
@@ -7468,7 +7484,7 @@
         <v>2026</v>
       </c>
       <c r="E69" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -7477,22 +7493,22 @@
         <v>198.1317768745953</v>
       </c>
       <c r="H69" t="n">
-        <v>0.05934645077246404</v>
+        <v>0.05143359066946884</v>
       </c>
       <c r="I69" t="n">
-        <v>0.007104700429176391</v>
+        <v>0.006157407038619538</v>
       </c>
       <c r="J69" t="n">
         <v>171.5447439761989</v>
       </c>
       <c r="K69" t="n">
-        <v>199.5522736128797</v>
+        <v>199.6119704644958</v>
       </c>
       <c r="L69" t="n">
-        <v>0.06626069061720037</v>
+        <v>0.06330304403561769</v>
       </c>
       <c r="M69" t="n">
-        <v>0.007932443321176251</v>
+        <v>0.007578366663448433</v>
       </c>
       <c r="N69" t="n">
         <v>194.4182830751776</v>
@@ -7501,10 +7517,10 @@
         <v>200</v>
       </c>
       <c r="P69" t="n">
-        <v>4.25</v>
+        <v>6.425606072522023</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.508791619902731</v>
+        <v>0.7692457699988954</v>
       </c>
       <c r="R69" t="n">
         <v>190.8574288418282</v>
@@ -7513,22 +7529,22 @@
         <v>200</v>
       </c>
       <c r="T69" t="n">
-        <v>4.25</v>
+        <v>6.583333333333333</v>
       </c>
       <c r="U69" t="n">
-        <v>0.508791619902731</v>
+        <v>0.7881281955356029</v>
       </c>
       <c r="V69" t="n">
         <v>199.6130972886749</v>
       </c>
       <c r="W69" t="n">
-        <v>198.7786331105758</v>
+        <v>198.9414820291657</v>
       </c>
       <c r="X69" t="n">
-        <v>0.3453066502488701</v>
+        <v>0.5946076275643608</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.04133861881019021</v>
+        <v>0.07118385365529198</v>
       </c>
       <c r="Z69" t="n">
         <v>185.6695408532579</v>
@@ -7570,7 +7586,7 @@
         <v>2026</v>
       </c>
       <c r="E70" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -7579,10 +7595,10 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01300024688996922</v>
+        <v>0.01126688063797333</v>
       </c>
       <c r="I70" t="n">
-        <v>0.001071909045295066</v>
+        <v>0.0009289878392557239</v>
       </c>
       <c r="J70" t="n">
         <v>188.453973372859</v>
@@ -7591,10 +7607,10 @@
         <v>200</v>
       </c>
       <c r="L70" t="n">
-        <v>0.01611028223724515</v>
+        <v>0.01610996399576582</v>
       </c>
       <c r="M70" t="n">
-        <v>0.001328340715258554</v>
+        <v>0.001328314475301484</v>
       </c>
       <c r="N70" t="n">
         <v>198.9765474653765</v>
@@ -7603,10 +7619,10 @@
         <v>200</v>
       </c>
       <c r="P70" t="n">
-        <v>4.961827715412824</v>
+        <v>8.336310348202737</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.4091174617191712</v>
+        <v>0.687353597378221</v>
       </c>
       <c r="R70" t="n">
         <v>192.937344462188</v>
@@ -7615,10 +7631,10 @@
         <v>200</v>
       </c>
       <c r="T70" t="n">
-        <v>5.134615384615385</v>
+        <v>9.4</v>
       </c>
       <c r="U70" t="n">
-        <v>0.423364319267437</v>
+        <v>0.775057974748776</v>
       </c>
       <c r="V70" t="n">
         <v>199.6974055100667</v>
@@ -7627,10 +7643,10 @@
         <v>200</v>
       </c>
       <c r="X70" t="n">
-        <v>0.3664860990972112</v>
+        <v>0.5361441192751984</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.03021786954679401</v>
+        <v>0.04420667821903208</v>
       </c>
       <c r="Z70" t="n">
         <v>184.4638384017739</v>
@@ -7672,67 +7688,67 @@
         <v>2026</v>
       </c>
       <c r="E71" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F71" t="n">
-        <v>133</v>
+        <v>196</v>
       </c>
       <c r="G71" t="n">
-        <v>61.42327963804853</v>
+        <v>63.86911921407565</v>
       </c>
       <c r="H71" t="n">
-        <v>3.115210034521734</v>
+        <v>3.930401904317618</v>
       </c>
       <c r="I71" t="n">
-        <v>0.07109815355873011</v>
+        <v>0.08970320300846145</v>
       </c>
       <c r="J71" t="n">
         <v>143.4057585362926</v>
       </c>
       <c r="K71" t="n">
-        <v>173.2999901984479</v>
+        <v>170.7957427044227</v>
       </c>
       <c r="L71" t="n">
-        <v>4.703881357592056</v>
+        <v>5.917055135514486</v>
       </c>
       <c r="M71" t="n">
-        <v>0.1073562537928435</v>
+        <v>0.1350444079141742</v>
       </c>
       <c r="N71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="O71" t="n">
-        <v>67.03669362173159</v>
+        <v>64.12956415789046</v>
       </c>
       <c r="P71" t="n">
-        <v>4.16481419340312</v>
+        <v>4.418139860418601</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.09505317323222298</v>
+        <v>0.1008348017498005</v>
       </c>
       <c r="R71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="S71" t="n">
-        <v>190.9113460286165</v>
+        <v>192.1231665581343</v>
       </c>
       <c r="T71" t="n">
-        <v>5.018515475175227</v>
+        <v>6.449380078485197</v>
       </c>
       <c r="U71" t="n">
-        <v>0.1145371194676608</v>
+        <v>0.147193611376882</v>
       </c>
       <c r="V71" t="n">
         <v>185.267595267154</v>
       </c>
       <c r="W71" t="n">
-        <v>59.79657500626929</v>
+        <v>65.4660703942622</v>
       </c>
       <c r="X71" t="n">
-        <v>5.964030506842874</v>
+        <v>9.874659219574868</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.1361165225154924</v>
+        <v>0.2253684437817529</v>
       </c>
       <c r="Z71" t="n">
         <v>93.16202342284906</v>
@@ -7748,11 +7764,11 @@
         </is>
       </c>
       <c r="AC71" t="n">
-        <v>61.42327963804853</v>
+        <v>63.86911921407565</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=61.42% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=63.87% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7776,67 +7792,67 @@
         <v>2026</v>
       </c>
       <c r="E72" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F72" t="n">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="G72" t="n">
-        <v>84.07539050911866</v>
+        <v>84.2300798330179</v>
       </c>
       <c r="H72" t="n">
-        <v>1.602741103507269</v>
+        <v>2.063904478594651</v>
       </c>
       <c r="I72" t="n">
-        <v>0.07262491548036337</v>
+        <v>0.09352158498304845</v>
       </c>
       <c r="J72" t="n">
         <v>151.0433307550491</v>
       </c>
       <c r="K72" t="n">
-        <v>84.07765725354294</v>
+        <v>76.94964840030202</v>
       </c>
       <c r="L72" t="n">
-        <v>1.367494685518548</v>
+        <v>1.530896185171238</v>
       </c>
       <c r="M72" t="n">
-        <v>0.06196520806654424</v>
+        <v>0.0693694108262243</v>
       </c>
       <c r="N72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="O72" t="n">
-        <v>87.90553164133496</v>
+        <v>82.55723414430395</v>
       </c>
       <c r="P72" t="n">
-        <v>2.415561923845612</v>
+        <v>2.5233391310531</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.1094562185826389</v>
+        <v>0.1143399209766344</v>
       </c>
       <c r="R72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="S72" t="n">
-        <v>171.1975130422481</v>
+        <v>175.6286648819022</v>
       </c>
       <c r="T72" t="n">
-        <v>2.179259122568957</v>
+        <v>2.95535790622643</v>
       </c>
       <c r="U72" t="n">
-        <v>0.09874864333362593</v>
+        <v>0.1339159628989603</v>
       </c>
       <c r="V72" t="n">
         <v>161.2927483340683</v>
       </c>
       <c r="W72" t="n">
-        <v>85.73646487878931</v>
+        <v>87.91613783087769</v>
       </c>
       <c r="X72" t="n">
-        <v>2.828564867761933</v>
+        <v>4.724833537931276</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.1281705972364512</v>
+        <v>0.2140961104698397</v>
       </c>
       <c r="Z72" t="n">
         <v>104.036396201453</v>
@@ -7852,11 +7868,11 @@
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>84.07765725354294</v>
+        <v>76.94964840030202</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=84.08% sobre 26 sem</t>
+          <t>DeepAR: menor SMAPE real=76.95% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7880,67 +7896,67 @@
         <v>2026</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F73" t="n">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="G73" t="n">
-        <v>71.82079597245757</v>
+        <v>73.34183447667557</v>
       </c>
       <c r="H73" t="n">
-        <v>1.977763974231611</v>
+        <v>2.345163339846095</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0886392817582795</v>
+        <v>0.1051053597690127</v>
       </c>
       <c r="J73" t="n">
         <v>148.5993365374143</v>
       </c>
       <c r="K73" t="n">
-        <v>147.0918094181974</v>
+        <v>135.079608707855</v>
       </c>
       <c r="L73" t="n">
-        <v>2.362989944339627</v>
+        <v>2.49182844205712</v>
       </c>
       <c r="M73" t="n">
-        <v>0.1059043112309076</v>
+        <v>0.1116785856384143</v>
       </c>
       <c r="N73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="O73" t="n">
-        <v>86.13938208574584</v>
+        <v>91.98855490686815</v>
       </c>
       <c r="P73" t="n">
-        <v>2.002529465235197</v>
+        <v>2.564648282527924</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.08974921973042897</v>
+        <v>0.1149422199452291</v>
       </c>
       <c r="R73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="S73" t="n">
-        <v>174.3124361485125</v>
+        <v>177.7374446620441</v>
       </c>
       <c r="T73" t="n">
-        <v>2.622439861172213</v>
+        <v>3.306114546349251</v>
       </c>
       <c r="U73" t="n">
-        <v>0.1175323187079983</v>
+        <v>0.1481732009568292</v>
       </c>
       <c r="V73" t="n">
         <v>173.6314937555617</v>
       </c>
       <c r="W73" t="n">
-        <v>62.86539382703211</v>
+        <v>68.71046704826695</v>
       </c>
       <c r="X73" t="n">
-        <v>2.667844818908352</v>
+        <v>4.902334720420154</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.119567274797013</v>
+        <v>0.2197124804670097</v>
       </c>
       <c r="Z73" t="n">
         <v>104.3951484726403</v>
@@ -7956,11 +7972,11 @@
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>62.86539382703211</v>
+        <v>68.71046704826695</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=62.87% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=68.71% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -7984,67 +8000,67 @@
         <v>2026</v>
       </c>
       <c r="E74" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G74" t="n">
-        <v>174.4718442606345</v>
+        <v>175.5501426823518</v>
       </c>
       <c r="H74" t="n">
-        <v>6.258269259578741</v>
+        <v>8.845154474561605</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1930633532310033</v>
+        <v>0.272867003939045</v>
       </c>
       <c r="J74" t="n">
         <v>148.9425712788151</v>
       </c>
       <c r="K74" t="n">
-        <v>189.2587566906077</v>
+        <v>190.4324624461753</v>
       </c>
       <c r="L74" t="n">
-        <v>0.4390523964915655</v>
+        <v>0.5817667011906837</v>
       </c>
       <c r="M74" t="n">
-        <v>0.01354446803020351</v>
+        <v>0.01794710733452413</v>
       </c>
       <c r="N74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="O74" t="n">
-        <v>191.7085025444234</v>
+        <v>192.0388761917751</v>
       </c>
       <c r="P74" t="n">
-        <v>38.4139073690108</v>
+        <v>44.0625374726764</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.185042934356836</v>
+        <v>1.359299333968616</v>
       </c>
       <c r="R74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="S74" t="n">
-        <v>191.7140640228413</v>
+        <v>192.2280762126967</v>
       </c>
       <c r="T74" t="n">
-        <v>38.71153846153846</v>
+        <v>50.7</v>
       </c>
       <c r="U74" t="n">
-        <v>1.194224651276613</v>
+        <v>1.564060541791189</v>
       </c>
       <c r="V74" t="n">
         <v>193.1141809259393</v>
       </c>
       <c r="W74" t="n">
-        <v>163.1582599134988</v>
+        <v>165.1498296698461</v>
       </c>
       <c r="X74" t="n">
-        <v>2.043127757499643</v>
+        <v>4.445256260689707</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.06302910270894493</v>
+        <v>0.1371331344279096</v>
       </c>
       <c r="Z74" t="n">
         <v>113.155914904339</v>
@@ -8060,11 +8076,11 @@
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>163.1582599134988</v>
+        <v>165.1498296698461</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=163.16% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=165.15% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8088,67 +8104,67 @@
         <v>2026</v>
       </c>
       <c r="E75" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>174.2699620420679</v>
+        <v>174.9146593701546</v>
       </c>
       <c r="H75" t="n">
-        <v>2.142589026981875</v>
+        <v>2.877833751567339</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1289745087724228</v>
+        <v>0.1732330324495012</v>
       </c>
       <c r="J75" t="n">
         <v>157.2380343536269</v>
       </c>
       <c r="K75" t="n">
-        <v>197.5158713283456</v>
+        <v>197.7573242429261</v>
       </c>
       <c r="L75" t="n">
-        <v>0.260182167677241</v>
+        <v>0.2925073377788802</v>
       </c>
       <c r="M75" t="n">
-        <v>0.01566183101142158</v>
+        <v>0.01760766517856314</v>
       </c>
       <c r="N75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="O75" t="n">
-        <v>191.3964759734417</v>
+        <v>191.8733040331857</v>
       </c>
       <c r="P75" t="n">
-        <v>16.20981996287579</v>
+        <v>18.28361475170498</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.9757604191347355</v>
+        <v>1.100593815001052</v>
       </c>
       <c r="R75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="S75" t="n">
-        <v>191.3964759734417</v>
+        <v>192.0144757786478</v>
       </c>
       <c r="T75" t="n">
-        <v>16.44230769230769</v>
+        <v>21.43333333333333</v>
       </c>
       <c r="U75" t="n">
-        <v>0.9897551658274006</v>
+        <v>1.290193127664911</v>
       </c>
       <c r="V75" t="n">
         <v>193.2892416279341</v>
       </c>
       <c r="W75" t="n">
-        <v>169.8670547016924</v>
+        <v>170.9367193902676</v>
       </c>
       <c r="X75" t="n">
-        <v>0.9626258278621391</v>
+        <v>1.882139849337658</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.05794587376145307</v>
+        <v>0.1132966049262699</v>
       </c>
       <c r="Z75" t="n">
         <v>110.9447640026735</v>
@@ -8166,7 +8182,7 @@
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 8 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -8190,85 +8206,87 @@
         <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G76" t="n">
-        <v>179.2253712539902</v>
+        <v>179.2850643951095</v>
       </c>
       <c r="H76" t="n">
-        <v>3.56168156738758</v>
+        <v>4.871315095367873</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1637319496572368</v>
+        <v>0.223936335371027</v>
       </c>
       <c r="J76" t="n">
         <v>154.9841830576604</v>
       </c>
       <c r="K76" t="n">
-        <v>196.2482320486948</v>
+        <v>196.6399996091033</v>
       </c>
       <c r="L76" t="n">
-        <v>0.2278723959063293</v>
+        <v>0.3308675294953379</v>
       </c>
       <c r="M76" t="n">
-        <v>0.01047538668151492</v>
+        <v>0.01521011484535384</v>
       </c>
       <c r="N76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="O76" t="n">
-        <v>191.2067962153635</v>
+        <v>191.3471645075774</v>
       </c>
       <c r="P76" t="n">
-        <v>20.1666718255868</v>
+        <v>22.81962161012898</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.9270701025984448</v>
+        <v>1.049027282752661</v>
       </c>
       <c r="R76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="S76" t="n">
-        <v>191.3315200778003</v>
+        <v>191.8273248164073</v>
       </c>
       <c r="T76" t="n">
-        <v>23.01923076923077</v>
+        <v>29.91666666666667</v>
       </c>
       <c r="U76" t="n">
-        <v>1.05820339694783</v>
+        <v>1.375281329310923</v>
       </c>
       <c r="V76" t="n">
         <v>192.8448970866968</v>
       </c>
       <c r="W76" t="n">
-        <v>174.7180212472131</v>
+        <v>174.724326480066</v>
       </c>
       <c r="X76" t="n">
-        <v>1.080921636694278</v>
+        <v>2.262001641210584</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.04969040708837363</v>
+        <v>0.1039851350649888</v>
       </c>
       <c r="Z76" t="n">
         <v>118.0223455785753</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>174.724326480066</v>
+      </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=174.72% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8292,74 +8310,74 @@
         <v>2026</v>
       </c>
       <c r="E77" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F77" t="n">
-        <v>426</v>
+        <v>454</v>
       </c>
       <c r="G77" t="n">
-        <v>45.07314790540139</v>
+        <v>44.06787720600779</v>
       </c>
       <c r="H77" t="n">
-        <v>5.9559345125117</v>
+        <v>5.464696874230028</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1646707312946037</v>
+        <v>0.1510889061477111</v>
       </c>
       <c r="J77" t="n">
         <v>77.76772218573589</v>
       </c>
       <c r="K77" t="n">
-        <v>48.91910741895335</v>
+        <v>60.79172681990623</v>
       </c>
       <c r="L77" t="n">
-        <v>8.212790663504016</v>
+        <v>11.07972940847461</v>
       </c>
       <c r="M77" t="n">
-        <v>0.2270686895041719</v>
+        <v>0.3063343192251491</v>
       </c>
       <c r="N77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="O77" t="n">
-        <v>59.40091192585066</v>
+        <v>69.57263625479605</v>
       </c>
       <c r="P77" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.3456022118541558</v>
+        <v>0.414722654224987</v>
       </c>
       <c r="R77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="S77" t="n">
-        <v>59.40091192585066</v>
+        <v>69.57263625479605</v>
       </c>
       <c r="T77" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="U77" t="n">
-        <v>0.3456022118541558</v>
+        <v>0.414722654224987</v>
       </c>
       <c r="V77" t="n">
         <v>138.4032392925817</v>
       </c>
       <c r="W77" t="n">
-        <v>33.73237849708716</v>
+        <v>42.01107382340651</v>
       </c>
       <c r="X77" t="n">
-        <v>5.898095795965104</v>
+        <v>6.64316396424577</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.163071596225059</v>
+        <v>0.1836713727802528</v>
       </c>
       <c r="Z77" t="n">
         <v>118.3894561520081</v>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
@@ -8368,11 +8386,11 @@
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>33.73237849708716</v>
+        <v>44.06787720600779</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=33.73% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=44.07% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8396,67 +8414,67 @@
         <v>2026</v>
       </c>
       <c r="E78" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F78" t="n">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="G78" t="n">
-        <v>46.68643158087417</v>
+        <v>46.76775401331676</v>
       </c>
       <c r="H78" t="n">
-        <v>3.17139220478416</v>
+        <v>2.942152392863164</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1693384791474939</v>
+        <v>0.1570980753739717</v>
       </c>
       <c r="J78" t="n">
         <v>103.5437500854655</v>
       </c>
       <c r="K78" t="n">
-        <v>55.22945859981466</v>
+        <v>62.71186936371598</v>
       </c>
       <c r="L78" t="n">
-        <v>3.993802203932325</v>
+        <v>4.695318087252637</v>
       </c>
       <c r="M78" t="n">
-        <v>0.2132515777170606</v>
+        <v>0.2507094590223334</v>
       </c>
       <c r="N78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="O78" t="n">
-        <v>110.8945250546275</v>
+        <v>106.0980075956651</v>
       </c>
       <c r="P78" t="n">
-        <v>5.324883351245751</v>
+        <v>4.914375861734152</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.2843254918068814</v>
+        <v>0.2624061865100832</v>
       </c>
       <c r="R78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="S78" t="n">
-        <v>55.29074480395132</v>
+        <v>59.71744169672258</v>
       </c>
       <c r="T78" t="n">
-        <v>4.416331334856955</v>
+        <v>4.502415400067723</v>
       </c>
       <c r="U78" t="n">
-        <v>0.2358127861094987</v>
+        <v>0.2404092988522729</v>
       </c>
       <c r="V78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="W78" t="n">
-        <v>33.76738924721007</v>
+        <v>38.66884599042365</v>
       </c>
       <c r="X78" t="n">
-        <v>2.900697323286576</v>
+        <v>2.955632096327329</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.1548845558904897</v>
+        <v>0.1578178326088345</v>
       </c>
       <c r="Z78" t="n">
         <v>124.390269119479</v>
@@ -8472,11 +8490,11 @@
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>33.76738924721007</v>
+        <v>38.66884599042365</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=33.77% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=38.67% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8500,67 +8518,67 @@
         <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F79" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G79" t="n">
-        <v>48.60323352904944</v>
+        <v>50.64369544820199</v>
       </c>
       <c r="H79" t="n">
-        <v>3.286245827177914</v>
+        <v>3.132500146257386</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1477379410925727</v>
+        <v>0.1408260813153082</v>
       </c>
       <c r="J79" t="n">
         <v>102.5016657415887</v>
       </c>
       <c r="K79" t="n">
-        <v>53.41466540703234</v>
+        <v>64.93379962831473</v>
       </c>
       <c r="L79" t="n">
-        <v>4.80042473164641</v>
+        <v>6.210467202274184</v>
       </c>
       <c r="M79" t="n">
-        <v>0.2158100469411142</v>
+        <v>0.2792005485709103</v>
       </c>
       <c r="N79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="O79" t="n">
-        <v>62.22131467786915</v>
+        <v>72.37494476991608</v>
       </c>
       <c r="P79" t="n">
-        <v>7.288461538461538</v>
+        <v>8.483333333333333</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.327663345364947</v>
+        <v>0.3813805376041959</v>
       </c>
       <c r="R79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="S79" t="n">
-        <v>62.22131467786915</v>
+        <v>72.37494476991608</v>
       </c>
       <c r="T79" t="n">
-        <v>7.288461538461538</v>
+        <v>8.483333333333333</v>
       </c>
       <c r="U79" t="n">
-        <v>0.327663345364947</v>
+        <v>0.3813805376041959</v>
       </c>
       <c r="V79" t="n">
         <v>148.0195847609927</v>
       </c>
       <c r="W79" t="n">
-        <v>36.04795612140367</v>
+        <v>48.20324713186123</v>
       </c>
       <c r="X79" t="n">
-        <v>3.257588844669878</v>
+        <v>4.128318268512884</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.1464496249359878</v>
+        <v>0.1855945273846759</v>
       </c>
       <c r="Z79" t="n">
         <v>120.3982350383182</v>
@@ -8576,11 +8594,11 @@
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>36.04795612140367</v>
+        <v>48.20324713186123</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=36.05% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=48.20% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8604,67 +8622,67 @@
         <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F80" t="n">
-        <v>890</v>
+        <v>1005</v>
       </c>
       <c r="G80" t="n">
-        <v>143.5582136650195</v>
+        <v>131.6224629997963</v>
       </c>
       <c r="H80" t="n">
-        <v>29.25013720036457</v>
+        <v>27.05441498034019</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9623734221793813</v>
+        <v>0.8901308650739113</v>
       </c>
       <c r="J80" t="n">
         <v>180.9937478063148</v>
       </c>
       <c r="K80" t="n">
-        <v>155.1167720404115</v>
+        <v>152.474693069763</v>
       </c>
       <c r="L80" t="n">
-        <v>29.20862733339917</v>
+        <v>28.22984007888106</v>
       </c>
       <c r="M80" t="n">
-        <v>0.9610076852444719</v>
+        <v>0.9288041152829466</v>
       </c>
       <c r="N80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="O80" t="n">
-        <v>121.8065814559429</v>
+        <v>127.9110003655342</v>
       </c>
       <c r="P80" t="n">
-        <v>22.8612208366394</v>
+        <v>23.27241895198822</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.752168483212483</v>
+        <v>0.7656975184696927</v>
       </c>
       <c r="R80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="S80" t="n">
-        <v>163.5409614670002</v>
+        <v>168.3914484230634</v>
       </c>
       <c r="T80" t="n">
-        <v>31.86330594704844</v>
+        <v>31.44763533020268</v>
       </c>
       <c r="U80" t="n">
-        <v>1.048350596653866</v>
+        <v>1.034674409383596</v>
       </c>
       <c r="V80" t="n">
         <v>172.7461511452186</v>
       </c>
       <c r="W80" t="n">
-        <v>53.61240802508001</v>
+        <v>54.81188710756886</v>
       </c>
       <c r="X80" t="n">
-        <v>28.18228627350842</v>
+        <v>26.25624373632104</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.9272395237016958</v>
+        <v>0.8638698329860922</v>
       </c>
       <c r="Z80" t="n">
         <v>175.912448276349</v>
@@ -8680,11 +8698,11 @@
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>53.61240802508001</v>
+        <v>54.81188710756886</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=53.61% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=54.81% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8708,67 +8726,67 @@
         <v>2026</v>
       </c>
       <c r="E81" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F81" t="n">
-        <v>408</v>
+        <v>460</v>
       </c>
       <c r="G81" t="n">
-        <v>131.6290115636485</v>
+        <v>121.0006886478078</v>
       </c>
       <c r="H81" t="n">
-        <v>12.89128020151289</v>
+        <v>11.9446466786775</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8019458912294177</v>
+        <v>0.7430573361541213</v>
       </c>
       <c r="J81" t="n">
         <v>185.5191244575439</v>
       </c>
       <c r="K81" t="n">
-        <v>113.5248773576872</v>
+        <v>107.1807386438778</v>
       </c>
       <c r="L81" t="n">
-        <v>10.23591089824205</v>
+        <v>9.757829421331051</v>
       </c>
       <c r="M81" t="n">
-        <v>0.6367596204194119</v>
+        <v>0.6070189375633624</v>
       </c>
       <c r="N81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="O81" t="n">
-        <v>160.6879071728418</v>
+        <v>158.7014436592695</v>
       </c>
       <c r="P81" t="n">
-        <v>13.36833044198843</v>
+        <v>13.05160442590713</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8316224225187205</v>
+        <v>0.8119194044110193</v>
       </c>
       <c r="R81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="S81" t="n">
-        <v>149.7346987873689</v>
+        <v>152.9040114241883</v>
       </c>
       <c r="T81" t="n">
-        <v>13.97074602195977</v>
+        <v>13.72569787553653</v>
       </c>
       <c r="U81" t="n">
-        <v>0.8690977307595501</v>
+        <v>0.8538536781049161</v>
       </c>
       <c r="V81" t="n">
         <v>163.1536185700502</v>
       </c>
       <c r="W81" t="n">
-        <v>55.98270195837857</v>
+        <v>59.45563258226454</v>
       </c>
       <c r="X81" t="n">
-        <v>8.787075583211861</v>
+        <v>8.624026131743031</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.5466298963117798</v>
+        <v>0.5364868511193177</v>
       </c>
       <c r="Z81" t="n">
         <v>172.1596497720207</v>
@@ -8784,11 +8802,11 @@
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>55.98270195837857</v>
+        <v>59.45563258226454</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=55.98% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=59.46% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8812,67 +8830,67 @@
         <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F82" t="n">
-        <v>482</v>
+        <v>545</v>
       </c>
       <c r="G82" t="n">
-        <v>130.2538719970943</v>
+        <v>118.5148674970889</v>
       </c>
       <c r="H82" t="n">
-        <v>15.38036762375736</v>
+        <v>14.13067712384159</v>
       </c>
       <c r="I82" t="n">
-        <v>0.76011083237102</v>
+        <v>0.6983500663520168</v>
       </c>
       <c r="J82" t="n">
         <v>186.2973802760101</v>
       </c>
       <c r="K82" t="n">
-        <v>147.761699642381</v>
+        <v>146.9740155456509</v>
       </c>
       <c r="L82" t="n">
-        <v>15.85623120177246</v>
+        <v>15.45664292371725</v>
       </c>
       <c r="M82" t="n">
-        <v>0.7836284146049711</v>
+        <v>0.763880422484868</v>
       </c>
       <c r="N82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="O82" t="n">
-        <v>162.0900465169206</v>
+        <v>164.7829457759922</v>
       </c>
       <c r="P82" t="n">
-        <v>15.4147405658777</v>
+        <v>15.37333707312743</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.7618095723677007</v>
+        <v>0.7597633765869927</v>
       </c>
       <c r="R82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="S82" t="n">
-        <v>154.1395095724688</v>
+        <v>158.7269467661581</v>
       </c>
       <c r="T82" t="n">
-        <v>17.04319178960882</v>
+        <v>16.81347917984981</v>
       </c>
       <c r="U82" t="n">
-        <v>0.8422890150849146</v>
+        <v>0.8309364227879444</v>
       </c>
       <c r="V82" t="n">
         <v>166.6060177059153</v>
       </c>
       <c r="W82" t="n">
-        <v>40.7500349637836</v>
+        <v>49.13487795057277</v>
       </c>
       <c r="X82" t="n">
-        <v>9.748616504925208</v>
+        <v>9.88834149188437</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.4817849083515161</v>
+        <v>0.488690235892355</v>
       </c>
       <c r="Z82" t="n">
         <v>176.1888335684919</v>
@@ -8888,11 +8906,11 @@
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>40.7500349637836</v>
+        <v>49.13487795057277</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=40.75% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=49.13% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -8916,67 +8934,67 @@
         <v>2026</v>
       </c>
       <c r="E83" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>438</v>
+        <v>517</v>
       </c>
       <c r="G83" t="n">
-        <v>43.1997975360161</v>
+        <v>51.02863183184109</v>
       </c>
       <c r="H83" t="n">
-        <v>6.048264925018194</v>
+        <v>7.052280333443618</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1546500020779722</v>
+        <v>0.1803219901479791</v>
       </c>
       <c r="J83" t="n">
         <v>88.04980557911651</v>
       </c>
       <c r="K83" t="n">
-        <v>50.07649051829125</v>
+        <v>50.31163205003056</v>
       </c>
       <c r="L83" t="n">
-        <v>7.637246332998242</v>
+        <v>7.661759227942159</v>
       </c>
       <c r="M83" t="n">
-        <v>0.1952791711194117</v>
+        <v>0.1959059490964036</v>
       </c>
       <c r="N83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="O83" t="n">
-        <v>92.30002957030169</v>
+        <v>88.95299588907891</v>
       </c>
       <c r="P83" t="n">
-        <v>31.07821057219206</v>
+        <v>29.65877688393252</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.7946486123133407</v>
+        <v>0.7583546626335124</v>
       </c>
       <c r="R83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="S83" t="n">
-        <v>98.53375806406798</v>
+        <v>96.91457721417946</v>
       </c>
       <c r="T83" t="n">
-        <v>24.77082648574989</v>
+        <v>22.72224518269569</v>
       </c>
       <c r="U83" t="n">
-        <v>0.6333731103028337</v>
+        <v>0.580992285933889</v>
       </c>
       <c r="V83" t="n">
         <v>103.1343264142703</v>
       </c>
       <c r="W83" t="n">
-        <v>52.93333819357255</v>
+        <v>53.85416383210703</v>
       </c>
       <c r="X83" t="n">
-        <v>11.37971859865602</v>
+        <v>12.0151604806659</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.2909716301693909</v>
+        <v>0.3072194449710817</v>
       </c>
       <c r="Z83" t="n">
         <v>103.3034448942146</v>
@@ -8992,11 +9010,11 @@
         </is>
       </c>
       <c r="AC83" t="n">
-        <v>43.1997975360161</v>
+        <v>51.02863183184109</v>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=43.20% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=51.03% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9020,67 +9038,67 @@
         <v>2026</v>
       </c>
       <c r="E84" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F84" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="G84" t="n">
-        <v>40.28371767364471</v>
+        <v>48.50722597157945</v>
       </c>
       <c r="H84" t="n">
-        <v>2.490847406123287</v>
+        <v>2.938329021180119</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1239227565235466</v>
+        <v>0.1461855234417969</v>
       </c>
       <c r="J84" t="n">
         <v>100.4914466151705</v>
       </c>
       <c r="K84" t="n">
-        <v>50.45190516411535</v>
+        <v>48.44075332352193</v>
       </c>
       <c r="L84" t="n">
-        <v>3.435796323442797</v>
+        <v>3.466984031116273</v>
       </c>
       <c r="M84" t="n">
-        <v>0.1709351404697909</v>
+        <v>0.1724867677172275</v>
       </c>
       <c r="N84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="O84" t="n">
-        <v>72.53719142394779</v>
+        <v>68.3318816586695</v>
       </c>
       <c r="P84" t="n">
-        <v>7.96397053099273</v>
+        <v>7.426679536194794</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.3962174393528721</v>
+        <v>0.3694865440892932</v>
       </c>
       <c r="R84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="S84" t="n">
-        <v>91.01392829545925</v>
+        <v>86.97211525948009</v>
       </c>
       <c r="T84" t="n">
-        <v>11.19769136149799</v>
+        <v>10.12669274718141</v>
       </c>
       <c r="U84" t="n">
-        <v>0.5570990727113425</v>
+        <v>0.5038155595612642</v>
       </c>
       <c r="V84" t="n">
         <v>98.74789164115032</v>
       </c>
       <c r="W84" t="n">
-        <v>55.35222777066018</v>
+        <v>57.23119043438312</v>
       </c>
       <c r="X84" t="n">
-        <v>5.146215844761524</v>
+        <v>5.616704349781711</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.2560306390428618</v>
+        <v>0.2794380273523239</v>
       </c>
       <c r="Z84" t="n">
         <v>110.607240444147</v>
@@ -9096,11 +9114,11 @@
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>40.28371767364471</v>
+        <v>48.50722597157945</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=40.28% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=48.51% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9124,67 +9142,67 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F85" t="n">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="G85" t="n">
-        <v>52.76186105573009</v>
+        <v>58.99109895409914</v>
       </c>
       <c r="H85" t="n">
-        <v>4.117499428134585</v>
+        <v>4.602364883946806</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1789730802775152</v>
+        <v>0.2000484600465876</v>
       </c>
       <c r="J85" t="n">
         <v>109.9471447641292</v>
       </c>
       <c r="K85" t="n">
-        <v>50.75761225595868</v>
+        <v>53.05256417977209</v>
       </c>
       <c r="L85" t="n">
-        <v>4.204387319908268</v>
+        <v>5.120832214469105</v>
       </c>
       <c r="M85" t="n">
-        <v>0.1827497884230706</v>
+        <v>0.2225843940002871</v>
       </c>
       <c r="N85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="O85" t="n">
-        <v>87.58282274969386</v>
+        <v>83.59158083265145</v>
       </c>
       <c r="P85" t="n">
-        <v>15.15160288614957</v>
+        <v>14.28470782949307</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.658586379186072</v>
+        <v>0.6209055291276532</v>
       </c>
       <c r="R85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="S85" t="n">
-        <v>105.3105266134953</v>
+        <v>104.6846217735562</v>
       </c>
       <c r="T85" t="n">
-        <v>14.84636386491651</v>
+        <v>13.73058450796558</v>
       </c>
       <c r="U85" t="n">
-        <v>0.6453187227347572</v>
+        <v>0.5968197558474579</v>
       </c>
       <c r="V85" t="n">
         <v>106.9882513320439</v>
       </c>
       <c r="W85" t="n">
-        <v>42.65874933717573</v>
+        <v>45.16982604300648</v>
       </c>
       <c r="X85" t="n">
-        <v>4.227487013689769</v>
+        <v>4.927689121257922</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.1837538500924648</v>
+        <v>0.21418914952493</v>
       </c>
       <c r="Z85" t="n">
         <v>107.8756984639591</v>
@@ -9200,11 +9218,11 @@
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>42.65874933717573</v>
+        <v>45.16982604300648</v>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=42.66% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=45.17% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9228,67 +9246,67 @@
         <v>2026</v>
       </c>
       <c r="E86" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F86" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G86" t="n">
-        <v>119.187088797981</v>
+        <v>123.301086111422</v>
       </c>
       <c r="H86" t="n">
-        <v>4.100360487593037</v>
+        <v>5.996981232960371</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1753461654456464</v>
+        <v>0.2564524915872403</v>
       </c>
       <c r="J86" t="n">
         <v>160.3842205944857</v>
       </c>
       <c r="K86" t="n">
-        <v>127.8983281168288</v>
+        <v>132.9116328362832</v>
       </c>
       <c r="L86" t="n">
-        <v>1.868879119234964</v>
+        <v>4.520642627545026</v>
       </c>
       <c r="M86" t="n">
-        <v>0.07991999440801663</v>
+        <v>0.1933189417097967</v>
       </c>
       <c r="N86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="O86" t="n">
-        <v>140.7985337554678</v>
+        <v>138.5203739979674</v>
       </c>
       <c r="P86" t="n">
-        <v>3.01021462564285</v>
+        <v>3.717853485544523</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.1287276066023937</v>
+        <v>0.1589887899738404</v>
       </c>
       <c r="R86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="S86" t="n">
-        <v>172.7754875759728</v>
+        <v>173.8897661590264</v>
       </c>
       <c r="T86" t="n">
-        <v>23.67307692307692</v>
+        <v>28.88333333333333</v>
       </c>
       <c r="U86" t="n">
-        <v>1.012345932832369</v>
+        <v>1.235155240767963</v>
       </c>
       <c r="V86" t="n">
         <v>188.4995472315167</v>
       </c>
       <c r="W86" t="n">
-        <v>87.65363536216613</v>
+        <v>95.88396977701767</v>
       </c>
       <c r="X86" t="n">
-        <v>1.307092869748586</v>
+        <v>3.497229831366464</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.05589599336089104</v>
+        <v>0.1495541288303179</v>
       </c>
       <c r="Z86" t="n">
         <v>113.2748521774272</v>
@@ -9304,11 +9322,11 @@
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>87.65363536216613</v>
+        <v>95.88396977701767</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=87.65% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=95.88% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9332,74 +9350,74 @@
         <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F87" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G87" t="n">
-        <v>123.9503694107824</v>
+        <v>127.1359430438049</v>
       </c>
       <c r="H87" t="n">
-        <v>1.456561855382656</v>
+        <v>2.106495564834618</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1019020099961631</v>
+        <v>0.1473717929049143</v>
       </c>
       <c r="J87" t="n">
         <v>171.410316416684</v>
       </c>
       <c r="K87" t="n">
-        <v>151.8452170739236</v>
+        <v>154.5788759945366</v>
       </c>
       <c r="L87" t="n">
-        <v>0.9569466966124592</v>
+        <v>3.01489895316687</v>
       </c>
       <c r="M87" t="n">
-        <v>0.06694861016965171</v>
+        <v>0.210924281813161</v>
       </c>
       <c r="N87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="O87" t="n">
-        <v>168.0044364020023</v>
+        <v>170.49225333327</v>
       </c>
       <c r="P87" t="n">
-        <v>10.26923076923077</v>
+        <v>12.80341693714172</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.7184420302041641</v>
+        <v>0.8957353344742783</v>
       </c>
       <c r="R87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="S87" t="n">
-        <v>168.0044364020023</v>
+        <v>170.5857762963043</v>
       </c>
       <c r="T87" t="n">
-        <v>10.26923076923077</v>
+        <v>13.26666666666667</v>
       </c>
       <c r="U87" t="n">
-        <v>0.7184420302041641</v>
+        <v>0.9281445853374145</v>
       </c>
       <c r="V87" t="n">
         <v>191.241827101395</v>
       </c>
       <c r="W87" t="n">
-        <v>117.1224183786047</v>
+        <v>123.3429179529025</v>
       </c>
       <c r="X87" t="n">
-        <v>0.7576229918228641</v>
+        <v>2.148143063855119</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.05300379479302941</v>
+        <v>0.1502854788879838</v>
       </c>
       <c r="Z87" t="n">
         <v>108.9238350712686</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
@@ -9408,11 +9426,11 @@
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>117.1224183786047</v>
+        <v>127.1359430438049</v>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=117.12% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=127.14% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9436,74 +9454,74 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F88" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G88" t="n">
-        <v>133.1340630323003</v>
+        <v>133.5528783141412</v>
       </c>
       <c r="H88" t="n">
-        <v>2.051713009899168</v>
+        <v>2.706558296192459</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1134914715933853</v>
+        <v>0.1497145470668257</v>
       </c>
       <c r="J88" t="n">
         <v>169.0038464611843</v>
       </c>
       <c r="K88" t="n">
-        <v>180.4350145751346</v>
+        <v>183.0002012052401</v>
       </c>
       <c r="L88" t="n">
-        <v>0.9615121828108862</v>
+        <v>1.033555717685064</v>
       </c>
       <c r="M88" t="n">
-        <v>0.05318649930846735</v>
+        <v>0.05717162137583758</v>
       </c>
       <c r="N88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="O88" t="n">
-        <v>165.0245602125755</v>
+        <v>166.3099100017029</v>
       </c>
       <c r="P88" t="n">
-        <v>2.075674739021522</v>
+        <v>1.9910009821256</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.1148169259268603</v>
+        <v>0.1101331571789442</v>
       </c>
       <c r="R88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="S88" t="n">
-        <v>179.8964312818334</v>
+        <v>179.1829677169829</v>
       </c>
       <c r="T88" t="n">
-        <v>13.84615384615385</v>
+        <v>16</v>
       </c>
       <c r="U88" t="n">
-        <v>0.7659065221727279</v>
+        <v>0.88504753673293</v>
       </c>
       <c r="V88" t="n">
         <v>190.1751472740156</v>
       </c>
       <c r="W88" t="n">
-        <v>123.5071248811116</v>
+        <v>129.3590645685444</v>
       </c>
       <c r="X88" t="n">
-        <v>1.131116051777212</v>
+        <v>3.591105399479158</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.06256821721153119</v>
+        <v>0.1986436867473346</v>
       </c>
       <c r="Z88" t="n">
         <v>121.3094122928426</v>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
@@ -9512,11 +9530,11 @@
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>123.5071248811116</v>
+        <v>133.5528783141412</v>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=123.51% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=133.55% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9558,7 @@
         <v>2026</v>
       </c>
       <c r="E89" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -9549,7 +9567,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1039132270690247</v>
+        <v>0.1046335363502783</v>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
@@ -9559,7 +9577,7 @@
         <v>200</v>
       </c>
       <c r="L89" t="n">
-        <v>0.007230453015671066</v>
+        <v>0.007315806193424531</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
@@ -9585,7 +9603,7 @@
         <v>200</v>
       </c>
       <c r="X89" t="n">
-        <v>7.21227621483376</v>
+        <v>7.212276214833761</v>
       </c>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
@@ -9628,7 +9646,7 @@
         <v>2026</v>
       </c>
       <c r="E90" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -9637,10 +9655,10 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09129889207558607</v>
+        <v>0.09192167342417998</v>
       </c>
       <c r="I90" t="n">
-        <v>0.01557337178261596</v>
+        <v>0.01567960314271727</v>
       </c>
       <c r="J90" t="n">
         <v>200</v>
@@ -9649,10 +9667,10 @@
         <v>200</v>
       </c>
       <c r="L90" t="n">
-        <v>0.003387767147173362</v>
+        <v>0.00337484183522561</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0005778707287289317</v>
+        <v>0.0005756659846866712</v>
       </c>
       <c r="N90" t="n">
         <v>200</v>
@@ -9681,10 +9699,10 @@
         <v>200</v>
       </c>
       <c r="X90" t="n">
-        <v>3.199488491048593</v>
+        <v>3.199488491048594</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.5457549664901652</v>
+        <v>0.5457549664901653</v>
       </c>
       <c r="Z90" t="n">
         <v>200</v>
@@ -9726,7 +9744,7 @@
         <v>2026</v>
       </c>
       <c r="E91" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -9735,10 +9753,10 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09375575732311482</v>
+        <v>0.09437379485105826</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0127450477244676</v>
+        <v>0.0128290630213843</v>
       </c>
       <c r="J91" t="n">
         <v>200</v>
@@ -9747,10 +9765,10 @@
         <v>200</v>
       </c>
       <c r="L91" t="n">
-        <v>0.01353305780754677</v>
+        <v>0.01324307176903409</v>
       </c>
       <c r="M91" t="n">
-        <v>0.001839668011221312</v>
+        <v>0.00180024764914652</v>
       </c>
       <c r="N91" t="n">
         <v>200</v>
@@ -9779,10 +9797,10 @@
         <v>200</v>
       </c>
       <c r="X91" t="n">
-        <v>2.502257439865562e-17</v>
+        <v>2.168623114550154e-17</v>
       </c>
       <c r="Y91" t="n">
-        <v>3.401539425475701e-18</v>
+        <v>2.948000835412274e-18</v>
       </c>
       <c r="Z91" t="n">
         <v>200</v>
@@ -9824,74 +9842,74 @@
         <v>2026</v>
       </c>
       <c r="E92" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F92" t="n">
-        <v>497</v>
+        <v>658</v>
       </c>
       <c r="G92" t="n">
-        <v>48.98239479605041</v>
+        <v>44.8147114175882</v>
       </c>
       <c r="H92" t="n">
-        <v>8.327145552672791</v>
+        <v>8.16451841578726</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06902975433540473</v>
+        <v>0.06768161994331701</v>
       </c>
       <c r="J92" t="n">
         <v>49.15109590531281</v>
       </c>
       <c r="K92" t="n">
-        <v>51.27271043422916</v>
+        <v>47.96484795715127</v>
       </c>
       <c r="L92" t="n">
-        <v>8.504691706163086</v>
+        <v>8.800377035330758</v>
       </c>
       <c r="M92" t="n">
-        <v>0.07050156328615584</v>
+        <v>0.07295271362379779</v>
       </c>
       <c r="N92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="O92" t="n">
-        <v>143.8102183858536</v>
+        <v>141.9480576296123</v>
       </c>
       <c r="P92" t="n">
-        <v>95.98543158524623</v>
+        <v>102.688934953488</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.7956929202445158</v>
+        <v>0.8512631258773166</v>
       </c>
       <c r="R92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="S92" t="n">
-        <v>88.12288395195948</v>
+        <v>85.35510875281915</v>
       </c>
       <c r="T92" t="n">
-        <v>31.66390403140978</v>
+        <v>34.08913721062245</v>
       </c>
       <c r="U92" t="n">
-        <v>0.262485086007231</v>
+        <v>0.2825896043572661</v>
       </c>
       <c r="V92" t="n">
         <v>92.01416331532587</v>
       </c>
       <c r="W92" t="n">
-        <v>37.67464475879304</v>
+        <v>46.56001376738867</v>
       </c>
       <c r="X92" t="n">
-        <v>7.406895854835166</v>
+        <v>18.26791375477017</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.06140113656150596</v>
+        <v>0.1514359981743551</v>
       </c>
       <c r="Z92" t="n">
         <v>95.83480509856771</v>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
@@ -9900,11 +9918,11 @@
         </is>
       </c>
       <c r="AC92" t="n">
-        <v>37.67464475879304</v>
+        <v>44.8147114175882</v>
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=37.67% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=44.81% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -9928,74 +9946,74 @@
         <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F93" t="n">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G93" t="n">
-        <v>46.33071747502665</v>
+        <v>42.40547593859543</v>
       </c>
       <c r="H93" t="n">
-        <v>3.862865777081154</v>
+        <v>3.735237768442399</v>
       </c>
       <c r="I93" t="n">
-        <v>0.06613434533550744</v>
+        <v>0.06394928499821131</v>
       </c>
       <c r="J93" t="n">
         <v>60.93105560683724</v>
       </c>
       <c r="K93" t="n">
-        <v>57.67261314686925</v>
+        <v>63.82707453463673</v>
       </c>
       <c r="L93" t="n">
-        <v>6.51001922416303</v>
+        <v>10.52412469171541</v>
       </c>
       <c r="M93" t="n">
-        <v>0.1114550399514296</v>
+        <v>0.1801786903509139</v>
       </c>
       <c r="N93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="O93" t="n">
-        <v>139.1563622088194</v>
+        <v>138.6160653578765</v>
       </c>
       <c r="P93" t="n">
-        <v>43.02895105926984</v>
+        <v>46.60846914201453</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.7366788475183966</v>
+        <v>0.7979621275183055</v>
       </c>
       <c r="R93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="S93" t="n">
-        <v>95.74384653120181</v>
+        <v>93.80035718981365</v>
       </c>
       <c r="T93" t="n">
-        <v>17.24488657444334</v>
+        <v>18.79890339507979</v>
       </c>
       <c r="U93" t="n">
-        <v>0.2952417582698555</v>
+        <v>0.321847364315742</v>
       </c>
       <c r="V93" t="n">
         <v>96.01849856237216</v>
       </c>
       <c r="W93" t="n">
-        <v>36.62559731227307</v>
+        <v>45.66091742819074</v>
       </c>
       <c r="X93" t="n">
-        <v>2.9917584455536</v>
+        <v>7.852568814286215</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.05122051803419571</v>
+        <v>0.1344402129672885</v>
       </c>
       <c r="Z93" t="n">
         <v>99.35850993844542</v>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
@@ -10004,11 +10022,11 @@
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>36.62559731227307</v>
+        <v>42.40547593859543</v>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=36.63% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=42.41% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -10032,74 +10050,74 @@
         <v>2026</v>
       </c>
       <c r="E94" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F94" t="n">
-        <v>261</v>
+        <v>355</v>
       </c>
       <c r="G94" t="n">
-        <v>50.85788690564483</v>
+        <v>47.60497596594993</v>
       </c>
       <c r="H94" t="n">
-        <v>4.370402940003936</v>
+        <v>4.626567631499932</v>
       </c>
       <c r="I94" t="n">
-        <v>0.05855750704690615</v>
+        <v>0.06198976854163958</v>
       </c>
       <c r="J94" t="n">
         <v>64.07712599234655</v>
       </c>
       <c r="K94" t="n">
-        <v>67.50136305395694</v>
+        <v>71.83030663782192</v>
       </c>
       <c r="L94" t="n">
-        <v>5.808354629419098</v>
+        <v>7.176601563223335</v>
       </c>
       <c r="M94" t="n">
-        <v>0.07782412098204208</v>
+        <v>0.09615678517068489</v>
       </c>
       <c r="N94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="O94" t="n">
-        <v>142.4143174612214</v>
+        <v>138.4285659846822</v>
       </c>
       <c r="P94" t="n">
-        <v>46.01139013859893</v>
+        <v>47.51795838081418</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.6164905934912556</v>
+        <v>0.6366765767223772</v>
       </c>
       <c r="R94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="S94" t="n">
-        <v>94.85079297405257</v>
+        <v>92.16441284077607</v>
       </c>
       <c r="T94" t="n">
-        <v>18.52912014414084</v>
+        <v>19.79456233909</v>
       </c>
       <c r="U94" t="n">
-        <v>0.2482652282428953</v>
+        <v>0.2652204475362726</v>
       </c>
       <c r="V94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="W94" t="n">
-        <v>39.84205949425877</v>
+        <v>48.27835983968884</v>
       </c>
       <c r="X94" t="n">
-        <v>4.219821617011154</v>
+        <v>10.03168973088775</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.0565399203384654</v>
+        <v>0.13441111727522</v>
       </c>
       <c r="Z94" t="n">
         <v>93.11495456228404</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
@@ -10108,11 +10126,11 @@
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>39.84205949425877</v>
+        <v>47.60497596594993</v>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=39.84% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=47.60% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -10136,31 +10154,31 @@
         <v>2026</v>
       </c>
       <c r="E95" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F95" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>144.6453651559676</v>
+        <v>139.6518920842648</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6583240568762944</v>
+        <v>0.6920073517632495</v>
       </c>
       <c r="I95" t="n">
-        <v>0.009399593887221766</v>
+        <v>0.009880526171882913</v>
       </c>
       <c r="J95" t="n">
         <v>152.3875262412586</v>
       </c>
       <c r="K95" t="n">
-        <v>199.3241646511038</v>
+        <v>199.3733198561377</v>
       </c>
       <c r="L95" t="n">
-        <v>0.5753658334003174</v>
+        <v>0.6652266326922892</v>
       </c>
       <c r="M95" t="n">
-        <v>0.008215110953422346</v>
+        <v>0.009498149315613625</v>
       </c>
       <c r="N95" t="n">
         <v>128.1095321097334</v>
@@ -10169,34 +10187,34 @@
         <v>200</v>
       </c>
       <c r="P95" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.008237345378162798</v>
+        <v>0.009518710214765899</v>
       </c>
       <c r="R95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="S95" t="n">
-        <v>170.6805922247819</v>
+        <v>173.7136344084252</v>
       </c>
       <c r="T95" t="n">
-        <v>3.041462706179588</v>
+        <v>2.802601012022309</v>
       </c>
       <c r="U95" t="n">
-        <v>0.04342620319371177</v>
+        <v>0.04001572032157501</v>
       </c>
       <c r="V95" t="n">
         <v>118.2821915164861</v>
       </c>
       <c r="W95" t="n">
-        <v>151.5302584151449</v>
+        <v>150.7403026179851</v>
       </c>
       <c r="X95" t="n">
-        <v>1.552458663105297</v>
+        <v>2.026063216588837</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.02216610620175331</v>
+        <v>0.02892826295325843</v>
       </c>
       <c r="Z95" t="n">
         <v>128.8999217807187</v>
@@ -10212,11 +10230,11 @@
         </is>
       </c>
       <c r="AC95" t="n">
-        <v>144.6453651559676</v>
+        <v>139.6518920842648</v>
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=144.65% sobre 26 sem</t>
+          <t>Prophet: menor SMAPE real=139.65% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -10240,67 +10258,67 @@
         <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G96" t="n">
-        <v>185.4949802057396</v>
+        <v>187.1999330460831</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2981965736936112</v>
+        <v>0.3633763130695801</v>
       </c>
       <c r="I96" t="n">
-        <v>0.009060283287310634</v>
+        <v>0.01104067795122157</v>
       </c>
       <c r="J96" t="n">
         <v>158.9896824444987</v>
       </c>
       <c r="K96" t="n">
-        <v>199.4502738784551</v>
+        <v>199.5213512926411</v>
       </c>
       <c r="L96" t="n">
-        <v>0.1542300177840033</v>
+        <v>0.233681801781556</v>
       </c>
       <c r="M96" t="n">
-        <v>0.004686062067117457</v>
+        <v>0.007100092724088296</v>
       </c>
       <c r="N96" t="n">
         <v>189.1617640516506</v>
       </c>
       <c r="O96" t="n">
-        <v>195.7774133191963</v>
+        <v>186.2454672519581</v>
       </c>
       <c r="P96" t="n">
-        <v>1.776959200108318</v>
+        <v>2.008256972093726</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.05399040486466595</v>
+        <v>0.06101806219806232</v>
       </c>
       <c r="R96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="S96" t="n">
-        <v>182.6873255227291</v>
+        <v>180.9325446207748</v>
       </c>
       <c r="T96" t="n">
-        <v>2.906151396101761</v>
+        <v>2.683217129863186</v>
       </c>
       <c r="U96" t="n">
-        <v>0.08829932080825706</v>
+        <v>0.08152577682835355</v>
       </c>
       <c r="V96" t="n">
         <v>124.4459476108536</v>
       </c>
       <c r="W96" t="n">
-        <v>180.5351894338612</v>
+        <v>176.9802125669613</v>
       </c>
       <c r="X96" t="n">
-        <v>0.9586028878180607</v>
+        <v>1.090996869122955</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.02912579985774586</v>
+        <v>0.03314840468280911</v>
       </c>
       <c r="Z96" t="n">
         <v>151.8363274594118</v>
@@ -10318,7 +10336,7 @@
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -10342,67 +10360,67 @@
         <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F97" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G97" t="n">
-        <v>171.9346393710365</v>
+        <v>173.4553670502901</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4505051113538389</v>
+        <v>0.4569409088175804</v>
       </c>
       <c r="I97" t="n">
-        <v>0.01203151691146957</v>
+        <v>0.01220339599579584</v>
       </c>
       <c r="J97" t="n">
         <v>157.2976315063829</v>
       </c>
       <c r="K97" t="n">
-        <v>199.4351970061328</v>
+        <v>199.4509302749238</v>
       </c>
       <c r="L97" t="n">
-        <v>0.4253306195534445</v>
+        <v>0.4352984025939205</v>
       </c>
       <c r="M97" t="n">
-        <v>0.01135918863771509</v>
+        <v>0.01162539549574817</v>
       </c>
       <c r="N97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="O97" t="n">
-        <v>148.8155072683896</v>
+        <v>156.9933999861937</v>
       </c>
       <c r="P97" t="n">
-        <v>1.556585907936096</v>
+        <v>1.911514888207118</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.04157131451673767</v>
+        <v>0.05105030581090617</v>
       </c>
       <c r="R97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="S97" t="n">
-        <v>170.2653323059756</v>
+        <v>172.4679002833108</v>
       </c>
       <c r="T97" t="n">
-        <v>1.965202821222686</v>
+        <v>1.769842445059661</v>
       </c>
       <c r="U97" t="n">
-        <v>0.05248413476809043</v>
+        <v>0.04726669858279849</v>
       </c>
       <c r="V97" t="n">
         <v>128.4785456608675</v>
       </c>
       <c r="W97" t="n">
-        <v>153.558624927868</v>
+        <v>153.0029045246747</v>
       </c>
       <c r="X97" t="n">
-        <v>0.8518205666403911</v>
+        <v>1.063882494691097</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.02274933911908906</v>
+        <v>0.02841281908705985</v>
       </c>
       <c r="Z97" t="n">
         <v>136.0400571203446</v>
@@ -10418,11 +10436,11 @@
         </is>
       </c>
       <c r="AC97" t="n">
-        <v>153.558624927868</v>
+        <v>153.0029045246747</v>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=153.56% sobre 26 sem</t>
+          <t>NBGLM: menor SMAPE real=153.00% sobre 30 sem</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10464,7 @@
         <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -10455,10 +10473,10 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.05584897214567642</v>
+        <v>0.0484024425262529</v>
       </c>
       <c r="I98" t="n">
-        <v>0.04195227954604801</v>
+        <v>0.03635864227324161</v>
       </c>
       <c r="J98" t="n">
         <v>198.585723184526</v>
@@ -10467,10 +10485,10 @@
         <v>200</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0005257727496187077</v>
+        <v>0.0005431090563802467</v>
       </c>
       <c r="M98" t="n">
-        <v>0.0003949466663802499</v>
+        <v>0.0004079692442292933</v>
       </c>
       <c r="N98" t="n">
         <v>199.9898962083731</v>
@@ -10479,10 +10497,10 @@
         <v>200</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.9</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.5200433369447454</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="R98" t="n">
         <v>199.2030987655621</v>
@@ -10501,10 +10519,10 @@
         <v>200</v>
       </c>
       <c r="X98" t="n">
-        <v>0.05238370102220309</v>
+        <v>0.09609024543466431</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.03934925898381453</v>
+        <v>0.07218046605420793</v>
       </c>
       <c r="Z98" t="n">
         <v>199.9999998548883</v>
@@ -10546,7 +10564,7 @@
         <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -10555,10 +10573,10 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0321776493972341</v>
+        <v>0.02788729614426955</v>
       </c>
       <c r="I99" t="n">
-        <v>0.04974322612132808</v>
+        <v>0.04311079597181767</v>
       </c>
       <c r="J99" t="n">
         <v>198.7380283178126</v>
@@ -10567,10 +10585,10 @@
         <v>200</v>
       </c>
       <c r="L99" t="n">
-        <v>0.001656036062763181</v>
+        <v>0.00166805595446163</v>
       </c>
       <c r="M99" t="n">
-        <v>0.00256005574919912</v>
+        <v>0.00257863722428851</v>
       </c>
       <c r="N99" t="n">
         <v>199.9983019911245</v>
@@ -10579,10 +10597,10 @@
         <v>200</v>
       </c>
       <c r="P99" t="n">
-        <v>0.4409654044720926</v>
+        <v>0.5103918545549554</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.6816856494254572</v>
+        <v>0.7890115625970325</v>
       </c>
       <c r="R99" t="n">
         <v>198.5022493653877</v>
@@ -10601,10 +10619,10 @@
         <v>200</v>
       </c>
       <c r="X99" t="n">
-        <v>0.04163218264949037</v>
+        <v>0.08281289059030879</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.06435892969969527</v>
+        <v>0.128019927482603</v>
       </c>
       <c r="Z99" t="n">
         <v>200</v>
@@ -10646,7 +10664,7 @@
         <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -10655,10 +10673,10 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.05279450630904018</v>
+        <v>0.0463232786624037</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07068720509997012</v>
+        <v>0.06202279988271626</v>
       </c>
       <c r="J100" t="n">
         <v>200</v>
@@ -10667,10 +10685,10 @@
         <v>200</v>
       </c>
       <c r="L100" t="n">
-        <v>0.002392263610996015</v>
+        <v>0.002423718137088566</v>
       </c>
       <c r="M100" t="n">
-        <v>0.003203030776228975</v>
+        <v>0.003245145622880089</v>
       </c>
       <c r="N100" t="n">
         <v>200</v>
@@ -10679,10 +10697,10 @@
         <v>200</v>
       </c>
       <c r="P100" t="n">
-        <v>0.1730769230769231</v>
+        <v>0.2704078702567994</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.2317347924042485</v>
+        <v>0.3620523785865097</v>
       </c>
       <c r="R100" t="n">
         <v>200</v>
@@ -10701,10 +10719,10 @@
         <v>200</v>
       </c>
       <c r="X100" t="n">
-        <v>0.0202913101091679</v>
+        <v>0.05609176635205636</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.02716828131771434</v>
+        <v>0.07510194658015916</v>
       </c>
       <c r="Z100" t="n">
         <v>200</v>

--- a/reports/ProdDetails/produccion_dengue.xlsx
+++ b/reports/ProdDetails/produccion_dengue.xlsx
@@ -600,67 +600,67 @@
         <v>2026</v>
       </c>
       <c r="E2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="G2" t="n">
         <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5072451520493191</v>
+        <v>1.725542330046237</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02538208735821456</v>
+        <v>0.08634457320012444</v>
       </c>
       <c r="J2" t="n">
         <v>185.8333489727328</v>
       </c>
       <c r="K2" t="n">
-        <v>185.2980944031261</v>
+        <v>179.494566733362</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3423955968242271</v>
+        <v>1.102412815272061</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01713316512646641</v>
+        <v>0.05516373743347297</v>
       </c>
       <c r="N2" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O2" t="n">
-        <v>142.4564622417932</v>
+        <v>130.762597309224</v>
       </c>
       <c r="P2" t="n">
-        <v>1.366666666666667</v>
+        <v>2.234375</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.06838676048996611</v>
+        <v>0.1118060985144644</v>
       </c>
       <c r="R2" t="n">
         <v>197.8088169752323</v>
       </c>
       <c r="S2" t="n">
-        <v>142.4564622417932</v>
+        <v>130.762597309224</v>
       </c>
       <c r="T2" t="n">
-        <v>1.366666666666667</v>
+        <v>2.234375</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06838676048996611</v>
+        <v>0.1118060985144644</v>
       </c>
       <c r="V2" t="n">
         <v>199.5572761277739</v>
       </c>
       <c r="W2" t="n">
-        <v>166.8873519190716</v>
+        <v>158.5599684099862</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2244707512531855</v>
+        <v>0.5309488839978331</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01123231280703977</v>
+        <v>0.02656820060661557</v>
       </c>
       <c r="Z2" t="n">
         <v>194.9779461019607</v>
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>166.8873519190716</v>
+        <v>158.5599684099862</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=166.89% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=158.56% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -704,67 +704,67 @@
         <v>2026</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>199.8117652783761</v>
+        <v>199.8281335150391</v>
       </c>
       <c r="H3" t="n">
-        <v>0.23992552952084</v>
+        <v>0.7561801839257876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02630221632294238</v>
+        <v>0.08289745079008291</v>
       </c>
       <c r="J3" t="n">
         <v>157.2321783542833</v>
       </c>
       <c r="K3" t="n">
-        <v>184.4705655017831</v>
+        <v>180.636290188897</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1781083907603099</v>
+        <v>0.5750590655641956</v>
       </c>
       <c r="M3" t="n">
-        <v>0.019525414540356</v>
+        <v>0.06304176121292998</v>
       </c>
       <c r="N3" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O3" t="n">
-        <v>165.1021493126756</v>
+        <v>148.635489278677</v>
       </c>
       <c r="P3" t="n">
-        <v>0.75</v>
+        <v>1.296875</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.08221993833504626</v>
+        <v>0.1421719767043508</v>
       </c>
       <c r="R3" t="n">
         <v>197.8854209931308</v>
       </c>
       <c r="S3" t="n">
-        <v>165.1021493126756</v>
+        <v>148.635489278677</v>
       </c>
       <c r="T3" t="n">
-        <v>0.75</v>
+        <v>1.296875</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08221993833504626</v>
+        <v>0.1421719767043508</v>
       </c>
       <c r="V3" t="n">
         <v>199.636475467609</v>
       </c>
       <c r="W3" t="n">
-        <v>185.2923057680258</v>
+        <v>185.3579915532606</v>
       </c>
       <c r="X3" t="n">
-        <v>1.952122269565353</v>
+        <v>20.27028248534635</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2140044968348451</v>
+        <v>2.22216183463886</v>
       </c>
       <c r="Z3" t="n">
         <v>198.5158836242873</v>
@@ -776,13 +776,15 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>180.636290188897</v>
+      </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=180.64% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -806,67 +808,67 @@
         <v>2026</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="G4" t="n">
         <v>200</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2755981738828413</v>
+        <v>0.9771232880151637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02393903790513279</v>
+        <v>0.08487498701543225</v>
       </c>
       <c r="J4" t="n">
         <v>158.5580779411727</v>
       </c>
       <c r="K4" t="n">
-        <v>181.5672899011693</v>
+        <v>181.1026385185562</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3068804105213799</v>
+        <v>0.95811177934586</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02665627887264973</v>
+        <v>0.08322360732645907</v>
       </c>
       <c r="N4" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O4" t="n">
-        <v>150.6293706293706</v>
+        <v>133.5088900669084</v>
       </c>
       <c r="P4" t="n">
-        <v>0.75</v>
+        <v>1.0625</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06514657980456026</v>
+        <v>0.09229098805646037</v>
       </c>
       <c r="R4" t="n">
         <v>197.7265973322816</v>
       </c>
       <c r="S4" t="n">
-        <v>150.6293706293706</v>
+        <v>133.5088900669084</v>
       </c>
       <c r="T4" t="n">
-        <v>0.75</v>
+        <v>1.0625</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06514657980456026</v>
+        <v>0.09229098805646037</v>
       </c>
       <c r="V4" t="n">
         <v>199.5859359679221</v>
       </c>
       <c r="W4" t="n">
-        <v>176.562581332529</v>
+        <v>168.6646361278689</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1817109824281797</v>
+        <v>0.4605265827804104</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01578379869082994</v>
+        <v>0.04000230903630058</v>
       </c>
       <c r="Z4" t="n">
         <v>196.9436529554095</v>
@@ -878,13 +880,15 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>168.6646361278689</v>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>NBGLM: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=168.66% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -908,31 +912,31 @@
         <v>2026</v>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>199.3652684808674</v>
+        <v>198.9886096531516</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1710356971411547</v>
+        <v>0.191401667221809</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2113182358500753</v>
+        <v>0.2364808243667138</v>
       </c>
       <c r="J5" t="n">
         <v>175.1088701866436</v>
       </c>
       <c r="K5" t="n">
-        <v>199.2883865349815</v>
+        <v>199.133448588981</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1778404880304248</v>
+        <v>0.1979928299731855</v>
       </c>
       <c r="M5" t="n">
-        <v>0.21972569949705</v>
+        <v>0.244624345912816</v>
       </c>
       <c r="N5" t="n">
         <v>109.609711216533</v>
@@ -941,10 +945,10 @@
         <v>200</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.28125</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3294723294723295</v>
+        <v>0.3474903474903475</v>
       </c>
       <c r="R5" t="n">
         <v>187.2707284786031</v>
@@ -953,22 +957,22 @@
         <v>200</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.28125</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3294723294723295</v>
+        <v>0.3474903474903475</v>
       </c>
       <c r="V5" t="n">
         <v>193.7972259177366</v>
       </c>
       <c r="W5" t="n">
-        <v>199.5094775089368</v>
+        <v>196.9187315615351</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1773081327790403</v>
+        <v>0.2088576837763497</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2190679632791232</v>
+        <v>0.258048103507459</v>
       </c>
       <c r="Z5" t="n">
         <v>187.0400639517023</v>
@@ -986,7 +990,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 5 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1010,31 +1014,31 @@
         <v>2026</v>
       </c>
       <c r="E6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>199.60071658422</v>
+        <v>199.6140260314126</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07333931411793927</v>
+        <v>0.06878063435478154</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04993315003774589</v>
+        <v>0.04682936807134062</v>
       </c>
       <c r="J6" t="n">
         <v>191.646475967384</v>
       </c>
       <c r="K6" t="n">
-        <v>199.982309722458</v>
+        <v>199.9834153648044</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0674159383528599</v>
+        <v>0.06325676484094528</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04590021334662802</v>
+        <v>0.04306843563638828</v>
       </c>
       <c r="N6" t="n">
         <v>79.54507935933471</v>
@@ -1043,10 +1047,10 @@
         <v>200</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.109375</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.07943262411347518</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="R6" t="n">
         <v>192.53013744135</v>
@@ -1055,22 +1059,22 @@
         <v>200</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.109375</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07943262411347518</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="V6" t="n">
         <v>193.2139428195562</v>
       </c>
       <c r="W6" t="n">
-        <v>199.0159823507556</v>
+        <v>199.1471847039882</v>
       </c>
       <c r="X6" t="n">
-        <v>0.07119368038055386</v>
+        <v>0.06674407537733093</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.04847229302505795</v>
+        <v>0.04544277472499127</v>
       </c>
       <c r="Z6" t="n">
         <v>198.9985835834048</v>
@@ -1112,31 +1116,31 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>198.8457356104576</v>
+        <v>198.5057824953416</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1218664864738857</v>
+        <v>0.1453313779293551</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07235116080082271</v>
+        <v>0.08628207966121269</v>
       </c>
       <c r="J7" t="n">
         <v>186.9197740801393</v>
       </c>
       <c r="K7" t="n">
-        <v>199.9833452289974</v>
+        <v>199.9813980617566</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1004020992957013</v>
+        <v>0.1253885532811225</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05960792537036072</v>
+        <v>0.07444218376615806</v>
       </c>
       <c r="N7" t="n">
         <v>109.7635513825217</v>
@@ -1145,10 +1149,10 @@
         <v>200</v>
       </c>
       <c r="P7" t="n">
-        <v>0.15</v>
+        <v>0.171875</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08905380333951762</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="R7" t="n">
         <v>185.3187572725189</v>
@@ -1157,22 +1161,22 @@
         <v>200</v>
       </c>
       <c r="T7" t="n">
-        <v>0.15</v>
+        <v>0.171875</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08905380333951762</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="V7" t="n">
         <v>190.8625800946274</v>
       </c>
       <c r="W7" t="n">
-        <v>199.8561020578255</v>
+        <v>199.0624941908825</v>
       </c>
       <c r="X7" t="n">
-        <v>0.110837566833549</v>
+        <v>0.159283523977287</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.06580337919617009</v>
+        <v>0.09456535746332438</v>
       </c>
       <c r="Z7" t="n">
         <v>197.3279694158802</v>
@@ -1190,7 +1194,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -1214,74 +1218,74 @@
         <v>2026</v>
       </c>
       <c r="E8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="G8" t="n">
-        <v>92.27883215001214</v>
+        <v>89.3084333102466</v>
       </c>
       <c r="H8" t="n">
-        <v>4.580452151583914</v>
+        <v>4.480605393977324</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2880787516719443</v>
+        <v>0.2817990813822217</v>
       </c>
       <c r="J8" t="n">
         <v>154.5040916050135</v>
       </c>
       <c r="K8" t="n">
-        <v>75.36878373383229</v>
+        <v>76.52700403802542</v>
       </c>
       <c r="L8" t="n">
-        <v>7.945027821912805</v>
+        <v>8.072967854729704</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4996872843970318</v>
+        <v>0.5077338273414909</v>
       </c>
       <c r="N8" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O8" t="n">
-        <v>100.6652716966206</v>
+        <v>105.1070548653255</v>
       </c>
       <c r="P8" t="n">
-        <v>19.20543948854522</v>
+        <v>22.77946467573016</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.207889276009134</v>
+        <v>1.432670734322652</v>
       </c>
       <c r="R8" t="n">
         <v>165.4966466258163</v>
       </c>
       <c r="S8" t="n">
-        <v>100.9187941761143</v>
+        <v>105.4629631656052</v>
       </c>
       <c r="T8" t="n">
-        <v>20.13333333333333</v>
+        <v>24.546875</v>
       </c>
       <c r="U8" t="n">
-        <v>1.266247379454926</v>
+        <v>1.543828616352201</v>
       </c>
       <c r="V8" t="n">
         <v>172.894287988784</v>
       </c>
       <c r="W8" t="n">
-        <v>68.51901851641311</v>
+        <v>74.84396075817462</v>
       </c>
       <c r="X8" t="n">
-        <v>4.860772940984292</v>
+        <v>9.407989752209376</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3057089899990121</v>
+        <v>0.5916974686924136</v>
       </c>
       <c r="Z8" t="n">
         <v>111.5676388698673</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1290,11 +1294,11 @@
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>68.51901851641311</v>
+        <v>76.52700403802542</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=68.52% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=76.53% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1318,67 +1322,67 @@
         <v>2026</v>
       </c>
       <c r="E9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>88.28084364582529</v>
+        <v>85.03757701120786</v>
       </c>
       <c r="H9" t="n">
-        <v>2.008305808530846</v>
+        <v>1.969948554697387</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2493821725765894</v>
+        <v>0.2446191453252478</v>
       </c>
       <c r="J9" t="n">
         <v>164.086229256472</v>
       </c>
       <c r="K9" t="n">
-        <v>94.10648776806431</v>
+        <v>97.79869222405507</v>
       </c>
       <c r="L9" t="n">
-        <v>5.749642108989677</v>
+        <v>7.048936882879026</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7139640958000375</v>
+        <v>0.8753045411413615</v>
       </c>
       <c r="N9" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O9" t="n">
-        <v>109.3048230261212</v>
+        <v>112.7187786473224</v>
       </c>
       <c r="P9" t="n">
-        <v>9.816666666666666</v>
+        <v>11.8125</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.218988487905834</v>
+        <v>1.466821885913853</v>
       </c>
       <c r="R9" t="n">
         <v>169.8771678897395</v>
       </c>
       <c r="S9" t="n">
-        <v>109.3048230261212</v>
+        <v>112.7187786473224</v>
       </c>
       <c r="T9" t="n">
-        <v>9.816666666666666</v>
+        <v>11.8125</v>
       </c>
       <c r="U9" t="n">
-        <v>1.218988487905834</v>
+        <v>1.466821885913853</v>
       </c>
       <c r="V9" t="n">
         <v>176.8647517474977</v>
       </c>
       <c r="W9" t="n">
-        <v>69.2678850224322</v>
+        <v>74.68426423326106</v>
       </c>
       <c r="X9" t="n">
-        <v>2.265436255273298</v>
+        <v>4.110976605877084</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2813114480742939</v>
+        <v>0.5104821551729402</v>
       </c>
       <c r="Z9" t="n">
         <v>121.2492629006552</v>
@@ -1394,11 +1398,11 @@
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>69.2678850224322</v>
+        <v>74.68426423326106</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=69.27% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=74.68% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1422,67 +1426,67 @@
         <v>2026</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G10" t="n">
-        <v>88.19035827372585</v>
+        <v>89.09365600951975</v>
       </c>
       <c r="H10" t="n">
-        <v>2.421405704540458</v>
+        <v>2.522993155458538</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2937262416425119</v>
+        <v>0.3060492076371236</v>
       </c>
       <c r="J10" t="n">
         <v>164.4874496413386</v>
       </c>
       <c r="K10" t="n">
-        <v>92.59928882647066</v>
+        <v>91.70798371873357</v>
       </c>
       <c r="L10" t="n">
-        <v>2.109625130989282</v>
+        <v>2.06014444738079</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2559060052754246</v>
+        <v>0.2499037995306492</v>
       </c>
       <c r="N10" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O10" t="n">
-        <v>103.7999683567414</v>
+        <v>108.7243006915879</v>
       </c>
       <c r="P10" t="n">
-        <v>10.9</v>
+        <v>13.28125</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.32221379833207</v>
+        <v>1.611068991660349</v>
       </c>
       <c r="R10" t="n">
         <v>162.692005533007</v>
       </c>
       <c r="S10" t="n">
-        <v>103.7999683567414</v>
+        <v>108.7243006915879</v>
       </c>
       <c r="T10" t="n">
-        <v>10.9</v>
+        <v>13.28125</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32221379833207</v>
+        <v>1.611068991660349</v>
       </c>
       <c r="V10" t="n">
         <v>168.5443712458804</v>
       </c>
       <c r="W10" t="n">
-        <v>72.49824933557935</v>
+        <v>79.1562812224054</v>
       </c>
       <c r="X10" t="n">
-        <v>2.77295675433941</v>
+        <v>5.074600960650059</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3363707965840073</v>
+        <v>0.6155694872661178</v>
       </c>
       <c r="Z10" t="n">
         <v>114.746491150853</v>
@@ -1498,11 +1502,11 @@
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>72.49824933557935</v>
+        <v>79.1562812224054</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=72.50% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=79.16% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1526,67 +1530,67 @@
         <v>2026</v>
       </c>
       <c r="E11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>183.1228547510095</v>
+        <v>184.4730263709287</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6350164440756541</v>
+        <v>0.8453279163209256</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04043885813019091</v>
+        <v>0.05383182750700422</v>
       </c>
       <c r="J11" t="n">
         <v>123.2554563734294</v>
       </c>
       <c r="K11" t="n">
-        <v>197.4346585076968</v>
+        <v>191.8267597638673</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6552399939771771</v>
+        <v>0.8066228153164969</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04172672598461626</v>
+        <v>0.0513670250549809</v>
       </c>
       <c r="N11" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O11" t="n">
-        <v>179.4915595150547</v>
+        <v>177.1213499347301</v>
       </c>
       <c r="P11" t="n">
-        <v>20.7384021873848</v>
+        <v>20.59850205067325</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.320654467654355</v>
+        <v>1.311745404221978</v>
       </c>
       <c r="R11" t="n">
         <v>192.5936095855003</v>
       </c>
       <c r="S11" t="n">
-        <v>169.2464575431293</v>
+        <v>171.9206786263354</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9598243496216606</v>
+        <v>1.149835327770307</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06112314266247391</v>
+        <v>0.07322334425601953</v>
       </c>
       <c r="V11" t="n">
         <v>177.781032308345</v>
       </c>
       <c r="W11" t="n">
-        <v>123.7678316346247</v>
+        <v>118.5084574088488</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8267959529168735</v>
+        <v>0.8576982749508867</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.05265168257381084</v>
+        <v>0.05461959163866343</v>
       </c>
       <c r="Z11" t="n">
         <v>147.9725418621825</v>
@@ -1602,11 +1606,11 @@
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>123.7678316346247</v>
+        <v>118.5084574088488</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=123.77% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=118.51% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1630,67 +1634,67 @@
         <v>2026</v>
       </c>
       <c r="E12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>193.2127135138377</v>
+        <v>194.1823258690038</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3377941176946851</v>
+        <v>0.4104319853387673</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04245644841410025</v>
+        <v>0.05158610970479401</v>
       </c>
       <c r="J12" t="n">
         <v>147.3485671696691</v>
       </c>
       <c r="K12" t="n">
-        <v>193.6955061779731</v>
+        <v>185.0725170127717</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4970911410202871</v>
+        <v>0.5387800051470371</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06247806957049956</v>
+        <v>0.06771783254008322</v>
       </c>
       <c r="N12" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O12" t="n">
-        <v>186.8820423761497</v>
+        <v>184.1791874549131</v>
       </c>
       <c r="P12" t="n">
-        <v>9.665697665535125</v>
+        <v>9.53034156143918</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.214855951677628</v>
+        <v>1.197843401280651</v>
       </c>
       <c r="R12" t="n">
         <v>191.4723960783834</v>
       </c>
       <c r="S12" t="n">
-        <v>185.5844229981174</v>
+        <v>180.708355256726</v>
       </c>
       <c r="T12" t="n">
-        <v>8.362726471706072</v>
+        <v>8.075087140455349</v>
       </c>
       <c r="U12" t="n">
-        <v>1.051088951667692</v>
+        <v>1.014936325587475</v>
       </c>
       <c r="V12" t="n">
         <v>189.6908701459495</v>
       </c>
       <c r="W12" t="n">
-        <v>162.4467540726264</v>
+        <v>156.6997471468527</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6511809055943154</v>
+        <v>0.7084654546651266</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.08184520415953689</v>
+        <v>0.08904514748344089</v>
       </c>
       <c r="Z12" t="n">
         <v>169.7722333133142</v>
@@ -1706,11 +1710,11 @@
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>162.4467540726264</v>
+        <v>156.6997471468527</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=162.45% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=156.70% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1734,85 +1738,87 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>197.0258462293987</v>
+        <v>197.2241231474388</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3038098511907269</v>
+        <v>0.4410717354913065</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03283321593415488</v>
+        <v>0.04766732703722325</v>
       </c>
       <c r="J13" t="n">
         <v>157.1522264328246</v>
       </c>
       <c r="K13" t="n">
-        <v>199.7826415765892</v>
+        <v>199.790051427191</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3009092622820653</v>
+        <v>0.4383387585233122</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03251974465729851</v>
+        <v>0.0473719698505437</v>
       </c>
       <c r="N13" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O13" t="n">
-        <v>179.8421375938333</v>
+        <v>177.9168383942311</v>
       </c>
       <c r="P13" t="n">
-        <v>11.21135439536204</v>
+        <v>11.24501974565191</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.21162897889762</v>
+        <v>1.215267247081598</v>
       </c>
       <c r="R13" t="n">
         <v>193.9340304002594</v>
       </c>
       <c r="S13" t="n">
-        <v>193.4962957966822</v>
+        <v>193.7672834718205</v>
       </c>
       <c r="T13" t="n">
-        <v>4.404349652507579</v>
+        <v>4.285327799225855</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4759851026012919</v>
+        <v>0.4631222207876641</v>
       </c>
       <c r="V13" t="n">
         <v>188.2053733911598</v>
       </c>
       <c r="W13" t="n">
-        <v>151.0374606732225</v>
+        <v>148.9148368047677</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4643319378183132</v>
+        <v>0.5552158067284312</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.05018109425932462</v>
+        <v>0.06000305915335966</v>
       </c>
       <c r="Z13" t="n">
         <v>173.7069303697712</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>148.9148368047677</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
+          <t>NBGLM: menor SMAPE real=148.91% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1836,67 +1842,67 @@
         <v>2026</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F14" t="n">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="G14" t="n">
-        <v>73.51977150703368</v>
+        <v>75.21371350770966</v>
       </c>
       <c r="H14" t="n">
-        <v>3.702156604902078</v>
+        <v>4.098358669021673</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08720574998665183</v>
+        <v>0.09653844490886532</v>
       </c>
       <c r="J14" t="n">
         <v>66.61025297793201</v>
       </c>
       <c r="K14" t="n">
-        <v>73.36927836706568</v>
+        <v>75.76674947089774</v>
       </c>
       <c r="L14" t="n">
-        <v>5.301703827430049</v>
+        <v>7.376788931345082</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1248837117981314</v>
+        <v>0.1737631548053313</v>
       </c>
       <c r="N14" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O14" t="n">
-        <v>153.5517342731258</v>
+        <v>150.7250686199016</v>
       </c>
       <c r="P14" t="n">
-        <v>34.61700716363286</v>
+        <v>34.66922552768253</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8154171727907629</v>
+        <v>0.8166471968243216</v>
       </c>
       <c r="R14" t="n">
         <v>128.1619574474296</v>
       </c>
       <c r="S14" t="n">
-        <v>181.0872230382438</v>
+        <v>181.1253274666046</v>
       </c>
       <c r="T14" t="n">
-        <v>122.2166666666667</v>
+        <v>133.28125</v>
       </c>
       <c r="U14" t="n">
-        <v>2.878861489387805</v>
+        <v>3.139492086860508</v>
       </c>
       <c r="V14" t="n">
         <v>186.0423288913966</v>
       </c>
       <c r="W14" t="n">
-        <v>96.33854616271445</v>
+        <v>99.47246716290033</v>
       </c>
       <c r="X14" t="n">
-        <v>22.74901767455469</v>
+        <v>26.46061990700224</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5358620284032021</v>
+        <v>0.623290273849151</v>
       </c>
       <c r="Z14" t="n">
         <v>130.2296761771863</v>
@@ -1912,11 +1918,11 @@
         </is>
       </c>
       <c r="AC14" t="n">
-        <v>73.51977150703368</v>
+        <v>75.21371350770966</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=73.52% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=75.21% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -1940,67 +1946,67 @@
         <v>2026</v>
       </c>
       <c r="E15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G15" t="n">
-        <v>72.76882002827271</v>
+        <v>74.91741109212454</v>
       </c>
       <c r="H15" t="n">
-        <v>1.732657682219908</v>
+        <v>1.908420619007908</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05975325555667321</v>
+        <v>0.06581469965325257</v>
       </c>
       <c r="J15" t="n">
         <v>82.6747998505866</v>
       </c>
       <c r="K15" t="n">
-        <v>76.92729274465719</v>
+        <v>76.64105206664335</v>
       </c>
       <c r="L15" t="n">
-        <v>1.718379949755973</v>
+        <v>2.07422008695318</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05926086689534555</v>
+        <v>0.07153253883231142</v>
       </c>
       <c r="N15" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O15" t="n">
-        <v>163.8675828819894</v>
+        <v>162.0902105632453</v>
       </c>
       <c r="P15" t="n">
-        <v>23.84006586211239</v>
+        <v>24.05135935499062</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.822159831433987</v>
+        <v>0.8294465991590686</v>
       </c>
       <c r="R15" t="n">
         <v>129.025548034421</v>
       </c>
       <c r="S15" t="n">
-        <v>178.8256680643568</v>
+        <v>179.0319592030568</v>
       </c>
       <c r="T15" t="n">
-        <v>58.78333333333333</v>
+        <v>63.375</v>
       </c>
       <c r="U15" t="n">
-        <v>2.027229945755649</v>
+        <v>2.185580342709344</v>
       </c>
       <c r="V15" t="n">
         <v>186.4460938550808</v>
       </c>
       <c r="W15" t="n">
-        <v>99.01160339376972</v>
+        <v>102.5259642435288</v>
       </c>
       <c r="X15" t="n">
-        <v>11.55202776329354</v>
+        <v>13.65237221627533</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3983887147595572</v>
+        <v>0.4708221908835118</v>
       </c>
       <c r="Z15" t="n">
         <v>131.9030800529592</v>
@@ -2016,11 +2022,11 @@
         </is>
       </c>
       <c r="AC15" t="n">
-        <v>72.76882002827271</v>
+        <v>74.91741109212454</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=72.77% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=74.92% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -2044,67 +2050,67 @@
         <v>2026</v>
       </c>
       <c r="E16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F16" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="G16" t="n">
-        <v>110.31830830747</v>
+        <v>110.9041825645268</v>
       </c>
       <c r="H16" t="n">
-        <v>2.446385065587029</v>
+        <v>2.691594028890769</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07749388447711833</v>
+        <v>0.08526134322362364</v>
       </c>
       <c r="J16" t="n">
         <v>90.20708978859948</v>
       </c>
       <c r="K16" t="n">
-        <v>112.5622406395385</v>
+        <v>113.0306585968643</v>
       </c>
       <c r="L16" t="n">
-        <v>3.469407999521305</v>
+        <v>4.869042529734196</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1099000752174636</v>
+        <v>0.1542361521990638</v>
       </c>
       <c r="N16" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O16" t="n">
-        <v>165.1964090265081</v>
+        <v>162.8861882092564</v>
       </c>
       <c r="P16" t="n">
-        <v>25.16707906345231</v>
+        <v>25.49252312012145</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7972149376662779</v>
+        <v>0.8075239950939284</v>
       </c>
       <c r="R16" t="n">
         <v>142.9387914444607</v>
       </c>
       <c r="S16" t="n">
-        <v>182.098489126943</v>
+        <v>182.0476906993662</v>
       </c>
       <c r="T16" t="n">
-        <v>63.48333333333333</v>
+        <v>69.953125</v>
       </c>
       <c r="U16" t="n">
-        <v>2.010954926417211</v>
+        <v>2.215897842011483</v>
       </c>
       <c r="V16" t="n">
         <v>186.1307414343702</v>
       </c>
       <c r="W16" t="n">
-        <v>115.175173488451</v>
+        <v>116.9062686313471</v>
       </c>
       <c r="X16" t="n">
-        <v>11.41341266330384</v>
+        <v>13.35413739453337</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.361541482108219</v>
+        <v>0.4230176169323577</v>
       </c>
       <c r="Z16" t="n">
         <v>133.2708900338696</v>
@@ -2120,11 +2126,11 @@
         </is>
       </c>
       <c r="AC16" t="n">
-        <v>110.31830830747</v>
+        <v>110.9041825645268</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=110.32% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=110.90% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -2148,31 +2154,31 @@
         <v>2026</v>
       </c>
       <c r="E17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>199.1989997019476</v>
+        <v>199.2490622205759</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1150468576285209</v>
+        <v>0.1127837429425722</v>
       </c>
       <c r="I17" t="n">
-        <v>0.05406019741721982</v>
+        <v>0.05299676614041574</v>
       </c>
       <c r="J17" t="n">
         <v>194.5446671655584</v>
       </c>
       <c r="K17" t="n">
-        <v>199.9639965596524</v>
+        <v>199.9662467746741</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03560876259773929</v>
+        <v>0.03356390997144428</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01673245819570716</v>
+        <v>0.01577158765177998</v>
       </c>
       <c r="N17" t="n">
         <v>109.609711216533</v>
@@ -2181,10 +2187,10 @@
         <v>200</v>
       </c>
       <c r="P17" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.03915810083210965</v>
+        <v>0.05873715124816447</v>
       </c>
       <c r="R17" t="n">
         <v>196.7571923388938</v>
@@ -2193,22 +2199,22 @@
         <v>200</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="U17" t="n">
-        <v>0.03915810083210965</v>
+        <v>0.05873715124816447</v>
       </c>
       <c r="V17" t="n">
         <v>197.0125798901019</v>
       </c>
       <c r="W17" t="n">
-        <v>199.175435757735</v>
+        <v>199.2269710228766</v>
       </c>
       <c r="X17" t="n">
-        <v>0.03848235094654683</v>
+        <v>0.04090431774394512</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.01808274934345813</v>
+        <v>0.01922082478423266</v>
       </c>
       <c r="Z17" t="n">
         <v>192.256373806382</v>
@@ -2250,7 +2256,7 @@
         <v>2026</v>
       </c>
       <c r="E18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -2259,10 +2265,10 @@
         <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0338663207647142</v>
+        <v>0.03174967571691957</v>
       </c>
       <c r="I18" t="n">
-        <v>0.03612407548236182</v>
+        <v>0.03386632076471421</v>
       </c>
       <c r="J18" t="n">
         <v>199.6410247115898</v>
@@ -2271,30 +2277,34 @@
         <v>200</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0005702780614168433</v>
+        <v>0.000576301963589675</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0006082965988446329</v>
+        <v>0.0006147220944956534</v>
       </c>
       <c r="N18" t="n">
         <v>79.54507935933471</v>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>200</v>
+      </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.046875</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R18" t="n">
         <v>196.9959839919002</v>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>200</v>
+      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.01795065592987011</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.01914736632519478</v>
       </c>
       <c r="V18" t="n">
         <v>196.686324272832</v>
@@ -2303,17 +2313,17 @@
         <v>200</v>
       </c>
       <c r="X18" t="n">
-        <v>2.219757347666035e-19</v>
+        <v>0.004915383697777253</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.36774117084377e-19</v>
+        <v>0.005243075944295737</v>
       </c>
       <c r="Z18" t="n">
         <v>196.0211023092105</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2324,7 +2334,7 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>NBGLM: serie casi-cero (total 0 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 0 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2348,31 +2358,31 @@
         <v>2026</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>199.4024478854051</v>
+        <v>199.4409996347338</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0962407870067717</v>
+        <v>0.09503151307568426</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07999234244718686</v>
+        <v>0.07898723164732198</v>
       </c>
       <c r="J19" t="n">
         <v>196.278530387405</v>
       </c>
       <c r="K19" t="n">
-        <v>199.9173620982299</v>
+        <v>199.9225269670905</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03828893595064166</v>
+        <v>0.03624356678081794</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03182457014079307</v>
+        <v>0.03012452303860193</v>
       </c>
       <c r="N19" t="n">
         <v>109.7635513825217</v>
@@ -2381,10 +2391,10 @@
         <v>200</v>
       </c>
       <c r="P19" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.078125</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.06926406926406926</v>
+        <v>0.06493506493506493</v>
       </c>
       <c r="R19" t="n">
         <v>196.7189002085085</v>
@@ -2393,22 +2403,22 @@
         <v>200</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.078125</v>
       </c>
       <c r="U19" t="n">
-        <v>0.06926406926406926</v>
+        <v>0.06493506493506493</v>
       </c>
       <c r="V19" t="n">
         <v>196.7488584326798</v>
       </c>
       <c r="W19" t="n">
-        <v>199.2527663950573</v>
+        <v>199.2994684953663</v>
       </c>
       <c r="X19" t="n">
-        <v>0.03895957101369892</v>
+        <v>0.03776800954372855</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.03238198110229521</v>
+        <v>0.03139159234803413</v>
       </c>
       <c r="Z19" t="n">
         <v>197.8046914283761</v>
@@ -2450,7 +2460,7 @@
         <v>2026</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2459,7 +2469,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>0.07171241224355712</v>
+        <v>0.07192011919331612</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
@@ -2469,7 +2479,7 @@
         <v>200</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001366867765529553</v>
+        <v>0.001357012247778247</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
@@ -2495,7 +2505,7 @@
         <v>200</v>
       </c>
       <c r="X20" t="n">
-        <v>5000</v>
+        <v>4687.5</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
@@ -2538,7 +2548,7 @@
         <v>2026</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2547,10 +2557,10 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0577058978768387</v>
+        <v>0.05787117644587096</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09051905549308033</v>
+        <v>0.09077831599352308</v>
       </c>
       <c r="J21" t="n">
         <v>200</v>
@@ -2559,10 +2569,10 @@
         <v>200</v>
       </c>
       <c r="L21" t="n">
-        <v>0.00608844158616144</v>
+        <v>0.006088256276343688</v>
       </c>
       <c r="M21" t="n">
-        <v>0.009550496605743435</v>
+        <v>0.009550205923676374</v>
       </c>
       <c r="N21" t="n">
         <v>79.54507935933471</v>
@@ -2591,10 +2601,10 @@
         <v>200</v>
       </c>
       <c r="X21" t="n">
-        <v>11666.66666672754</v>
+        <v>10937.50000005707</v>
       </c>
       <c r="Y21" t="n">
-        <v>18300.65359486673</v>
+        <v>17156.86274518756</v>
       </c>
       <c r="Z21" t="n">
         <v>200</v>
@@ -2636,7 +2646,7 @@
         <v>2026</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2645,10 +2655,10 @@
         <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06462246577622624</v>
+        <v>0.06481035465896406</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06939325184024293</v>
+        <v>0.06959501171432382</v>
       </c>
       <c r="J22" t="n">
         <v>200</v>
@@ -2657,10 +2667,10 @@
         <v>200</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00039442201699259</v>
+        <v>0.0003912268415505937</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0004235404209316402</v>
+        <v>0.0004201093600543289</v>
       </c>
       <c r="N22" t="n">
         <v>109.7635513825217</v>
@@ -2689,10 +2699,10 @@
         <v>200</v>
       </c>
       <c r="X22" t="n">
-        <v>8.711041683575902e-16</v>
+        <v>8.166601578352409e-16</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.354138720618418e-16</v>
+        <v>8.769505050579767e-16</v>
       </c>
       <c r="Z22" t="n">
         <v>200</v>
@@ -2734,67 +2744,67 @@
         <v>2026</v>
       </c>
       <c r="E23" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>182.5487674821857</v>
+        <v>177.7768609808887</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2533462861681124</v>
+        <v>0.3453943559054111</v>
       </c>
       <c r="I23" t="n">
-        <v>0.006125023539875793</v>
+        <v>0.008350422626906282</v>
       </c>
       <c r="J23" t="n">
         <v>149.2565324185079</v>
       </c>
       <c r="K23" t="n">
-        <v>196.8096497945818</v>
+        <v>193.1305877850569</v>
       </c>
       <c r="L23" t="n">
-        <v>1.258395964919489</v>
+        <v>1.305705946484624</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03042359540452074</v>
+        <v>0.03156738462338166</v>
       </c>
       <c r="N23" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O23" t="n">
-        <v>186.4285714285714</v>
+        <v>187.4467318709617</v>
       </c>
       <c r="P23" t="n">
-        <v>7.928549876008182</v>
+        <v>10.08317875737203</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1916844938291492</v>
+        <v>0.2437758539104753</v>
       </c>
       <c r="R23" t="n">
         <v>169.6992056798271</v>
       </c>
       <c r="S23" t="n">
-        <v>186.4285714285714</v>
+        <v>187.8137332280979</v>
       </c>
       <c r="T23" t="n">
-        <v>15.26666666666667</v>
+        <v>23.1875</v>
       </c>
       <c r="U23" t="n">
-        <v>0.369094389039992</v>
+        <v>0.5605923239649442</v>
       </c>
       <c r="V23" t="n">
         <v>186.3774873978808</v>
       </c>
       <c r="W23" t="n">
-        <v>192.0231043563226</v>
+        <v>192.3692718300408</v>
       </c>
       <c r="X23" t="n">
-        <v>3.582459466670285</v>
+        <v>7.470299724838054</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.08661128961427102</v>
+        <v>0.1806056143810953</v>
       </c>
       <c r="Z23" t="n">
         <v>159.9263814945425</v>
@@ -2812,7 +2822,7 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 3 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -2836,67 +2846,67 @@
         <v>2026</v>
       </c>
       <c r="E24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>187.0869559636593</v>
+        <v>188.9316765402794</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1382318691869096</v>
+        <v>0.1854517026294812</v>
       </c>
       <c r="I24" t="n">
-        <v>0.006151327790267151</v>
+        <v>0.008252613661720759</v>
       </c>
       <c r="J24" t="n">
         <v>156.2502876793226</v>
       </c>
       <c r="K24" t="n">
-        <v>197.9839364257978</v>
+        <v>198.1099403991855</v>
       </c>
       <c r="L24" t="n">
-        <v>2.107750666107081</v>
+        <v>2.346217693302085</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09379505119653261</v>
+        <v>0.1044068504876467</v>
       </c>
       <c r="N24" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O24" t="n">
-        <v>171.6509914962452</v>
+        <v>176.375826246871</v>
       </c>
       <c r="P24" t="n">
-        <v>2.020837509632111</v>
+        <v>2.547171544283628</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.08992740969020656</v>
+        <v>0.1133493108289196</v>
       </c>
       <c r="R24" t="n">
         <v>159.6122718089852</v>
       </c>
       <c r="S24" t="n">
-        <v>178.3333333333333</v>
+        <v>181.4285714285714</v>
       </c>
       <c r="T24" t="n">
-        <v>6.233333333333333</v>
+        <v>9.546875</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2773837667454689</v>
+        <v>0.4248366013071895</v>
       </c>
       <c r="V24" t="n">
         <v>185.3144083651474</v>
       </c>
       <c r="W24" t="n">
-        <v>192.6107016410813</v>
+        <v>193.0725327885137</v>
       </c>
       <c r="X24" t="n">
-        <v>1.150307104863834</v>
+        <v>1.929756116403934</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.05118874614885649</v>
+        <v>0.08587428135853968</v>
       </c>
       <c r="Z24" t="n">
         <v>166.4426133688291</v>
@@ -2938,67 +2948,67 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>200</v>
+        <v>187.4918388878622</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1400345713133921</v>
+        <v>0.1623953822127881</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005026479284384237</v>
+        <v>0.005829110746841525</v>
       </c>
       <c r="J25" t="n">
         <v>155.3955473497874</v>
       </c>
       <c r="K25" t="n">
-        <v>199.9454889651267</v>
+        <v>197.0177752371734</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8448776191837108</v>
+        <v>0.9297482311334753</v>
       </c>
       <c r="M25" t="n">
-        <v>0.03032651016699803</v>
+        <v>0.03337290341701762</v>
       </c>
       <c r="N25" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O25" t="n">
-        <v>200</v>
+        <v>199.5503034748231</v>
       </c>
       <c r="P25" t="n">
-        <v>8.029075112468957</v>
+        <v>10.84005369860009</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2882001162075229</v>
+        <v>0.3890989549693806</v>
       </c>
       <c r="R25" t="n">
         <v>177.0659734750362</v>
       </c>
       <c r="S25" t="n">
-        <v>200</v>
+        <v>199.7099319184056</v>
       </c>
       <c r="T25" t="n">
-        <v>9.133333333333333</v>
+        <v>13.11520821924202</v>
       </c>
       <c r="U25" t="n">
-        <v>0.327836978874556</v>
+        <v>0.470764624807341</v>
       </c>
       <c r="V25" t="n">
         <v>183.340259481936</v>
       </c>
       <c r="W25" t="n">
-        <v>199.7138913097684</v>
+        <v>199.5491282423042</v>
       </c>
       <c r="X25" t="n">
-        <v>2.09079770088027</v>
+        <v>5.138445710702859</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.07504826295924694</v>
+        <v>0.1844422464862496</v>
       </c>
       <c r="Z25" t="n">
         <v>180.6321027113416</v>
@@ -3016,7 +3026,7 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 1 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3050,7 @@
         <v>2026</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -3049,58 +3059,58 @@
         <v>200</v>
       </c>
       <c r="H26" t="n">
-        <v>0.05094029514580251</v>
+        <v>0.04775652669918985</v>
       </c>
       <c r="I26" t="n">
-        <v>0.001484193248352618</v>
+        <v>0.001391431170330579</v>
       </c>
       <c r="J26" t="n">
         <v>97.19414576199205</v>
       </c>
       <c r="K26" t="n">
-        <v>194.9373081954851</v>
+        <v>195.2537264332673</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1855918596837396</v>
+        <v>0.2112277865219744</v>
       </c>
       <c r="M26" t="n">
-        <v>0.005407392797850923</v>
+        <v>0.006154319556317202</v>
       </c>
       <c r="N26" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O26" t="n">
-        <v>199.9275362318841</v>
+        <v>199.9320652173913</v>
       </c>
       <c r="P26" t="n">
-        <v>86.10241296238631</v>
+        <v>98.66506638434961</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.50867451042189</v>
+        <v>2.874699193571144</v>
       </c>
       <c r="R26" t="n">
         <v>198.3074653131699</v>
       </c>
       <c r="S26" t="n">
-        <v>199.9275362318841</v>
+        <v>199.9320652173913</v>
       </c>
       <c r="T26" t="n">
-        <v>87.46666666666667</v>
+        <v>106.421875</v>
       </c>
       <c r="U26" t="n">
-        <v>2.54842332088986</v>
+        <v>3.10070108349267</v>
       </c>
       <c r="V26" t="n">
         <v>199.6509594119097</v>
       </c>
       <c r="W26" t="n">
-        <v>197.2926384996639</v>
+        <v>197.4618485934349</v>
       </c>
       <c r="X26" t="n">
-        <v>1.591280551137813</v>
+        <v>1.852581982165122</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.04636345045653284</v>
+        <v>0.05397671258243095</v>
       </c>
       <c r="Z26" t="n">
         <v>183.6686755299509</v>
@@ -3142,7 +3152,7 @@
         <v>2026</v>
       </c>
       <c r="E27" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -3151,10 +3161,10 @@
         <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>0.01232839244321669</v>
+        <v>0.01155786791551565</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0006600444339684358</v>
+        <v>0.0006187916568454085</v>
       </c>
       <c r="J27" t="n">
         <v>129.0985231723771</v>
@@ -3163,10 +3173,10 @@
         <v>200</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1149934630296452</v>
+        <v>0.1925674074180119</v>
       </c>
       <c r="M27" t="n">
-        <v>0.006156584937173573</v>
+        <v>0.01030978256211541</v>
       </c>
       <c r="N27" t="n">
         <v>79.54507935933471</v>
@@ -3175,10 +3185,10 @@
         <v>200</v>
       </c>
       <c r="P27" t="n">
-        <v>40.4888699881782</v>
+        <v>44.09752830198847</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16771597728242</v>
+        <v>2.36091836316485</v>
       </c>
       <c r="R27" t="n">
         <v>198.6114841856233</v>
@@ -3187,10 +3197,10 @@
         <v>200</v>
       </c>
       <c r="T27" t="n">
-        <v>42.6</v>
+        <v>51.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.280742847582399</v>
+        <v>2.77062071273214</v>
       </c>
       <c r="V27" t="n">
         <v>199.779644487174</v>
@@ -3199,10 +3209,10 @@
         <v>200</v>
       </c>
       <c r="X27" t="n">
-        <v>1.071897421311159</v>
+        <v>1.189343684900793</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.0573878492252921</v>
+        <v>0.06367575358344552</v>
       </c>
       <c r="Z27" t="n">
         <v>192.722098187243</v>
@@ -3244,7 +3254,7 @@
         <v>2026</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
@@ -3253,58 +3263,58 @@
         <v>200</v>
       </c>
       <c r="H28" t="n">
-        <v>0.04577209243583606</v>
+        <v>0.0429113366585963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.002343531132714806</v>
+        <v>0.002197060436920131</v>
       </c>
       <c r="J28" t="n">
         <v>127.1718885128103</v>
       </c>
       <c r="K28" t="n">
-        <v>196.0543300200681</v>
+        <v>196.3009343938139</v>
       </c>
       <c r="L28" t="n">
-        <v>0.466428794628377</v>
+        <v>0.4998517059216651</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0238811542849729</v>
+        <v>0.02559240734318925</v>
       </c>
       <c r="N28" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O28" t="n">
-        <v>199.8625429553265</v>
+        <v>199.8711340206186</v>
       </c>
       <c r="P28" t="n">
-        <v>43.33434520066904</v>
+        <v>49.13148076123822</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.218718474274255</v>
+        <v>2.515531814975397</v>
       </c>
       <c r="R28" t="n">
         <v>197.4940180993655</v>
       </c>
       <c r="S28" t="n">
-        <v>199.8625429553265</v>
+        <v>199.8711340206186</v>
       </c>
       <c r="T28" t="n">
-        <v>44.86666666666667</v>
+        <v>54.671875</v>
       </c>
       <c r="U28" t="n">
-        <v>2.297173333333333</v>
+        <v>2.7992</v>
       </c>
       <c r="V28" t="n">
         <v>199.5411797194807</v>
       </c>
       <c r="W28" t="n">
-        <v>196.64626555975</v>
+        <v>196.8558739622656</v>
       </c>
       <c r="X28" t="n">
-        <v>1.116591091954148</v>
+        <v>1.373690913977071</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.05716946390805237</v>
+        <v>0.07033297479562603</v>
       </c>
       <c r="Z28" t="n">
         <v>184.9627687949149</v>
@@ -3346,7 +3356,7 @@
         <v>2026</v>
       </c>
       <c r="E29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
         <v>1</v>
@@ -3355,22 +3365,22 @@
         <v>197.3842508066303</v>
       </c>
       <c r="H29" t="n">
-        <v>0.149771458699966</v>
+        <v>0.1404107425312182</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0178034423417493</v>
+        <v>0.01669072719538997</v>
       </c>
       <c r="J29" t="n">
         <v>191.5075017030775</v>
       </c>
       <c r="K29" t="n">
-        <v>199.7263126923358</v>
+        <v>199.7434181490648</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05795993941483705</v>
+        <v>0.05613511419535459</v>
       </c>
       <c r="M29" t="n">
-        <v>0.006889740197900392</v>
+        <v>0.006672821895435909</v>
       </c>
       <c r="N29" t="n">
         <v>109.609711216533</v>
@@ -3379,10 +3389,10 @@
         <v>200</v>
       </c>
       <c r="P29" t="n">
-        <v>0.7333333333333333</v>
+        <v>2.515625</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.0871718672610203</v>
+        <v>0.2990341753343239</v>
       </c>
       <c r="R29" t="n">
         <v>198.5277121400952</v>
@@ -3391,22 +3401,22 @@
         <v>200</v>
       </c>
       <c r="T29" t="n">
-        <v>0.7333333333333333</v>
+        <v>2.515625</v>
       </c>
       <c r="U29" t="n">
-        <v>0.0871718672610203</v>
+        <v>0.2990341753343239</v>
       </c>
       <c r="V29" t="n">
         <v>199.9388941772115</v>
       </c>
       <c r="W29" t="n">
-        <v>199.999969017756</v>
+        <v>199.9999709541463</v>
       </c>
       <c r="X29" t="n">
-        <v>0.09732881366899378</v>
+        <v>0.2210730053748357</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.01156954694430832</v>
+        <v>0.02627910910845001</v>
       </c>
       <c r="Z29" t="n">
         <v>192.5799615112869</v>
@@ -3448,7 +3458,7 @@
         <v>2026</v>
       </c>
       <c r="E30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3457,10 +3467,10 @@
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1139970950750777</v>
+        <v>0.1068722766328853</v>
       </c>
       <c r="I30" t="n">
-        <v>0.02344413266325505</v>
+        <v>0.02197887437180161</v>
       </c>
       <c r="J30" t="n">
         <v>196.0386411854094</v>
@@ -3469,10 +3479,10 @@
         <v>200</v>
       </c>
       <c r="L30" t="n">
-        <v>0.006130680813965784</v>
+        <v>0.006255837376740553</v>
       </c>
       <c r="M30" t="n">
-        <v>0.001260808393617642</v>
+        <v>0.001286547532491631</v>
       </c>
       <c r="N30" t="n">
         <v>79.54507935933471</v>
@@ -3481,10 +3491,10 @@
         <v>200</v>
       </c>
       <c r="P30" t="n">
-        <v>0.4</v>
+        <v>1.125</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.08226221079691518</v>
+        <v>0.2313624678663239</v>
       </c>
       <c r="R30" t="n">
         <v>198.9477887234591</v>
@@ -3493,10 +3503,10 @@
         <v>200</v>
       </c>
       <c r="T30" t="n">
-        <v>0.4</v>
+        <v>1.125</v>
       </c>
       <c r="U30" t="n">
-        <v>0.08226221079691518</v>
+        <v>0.2313624678663239</v>
       </c>
       <c r="V30" t="n">
         <v>199.7754683359127</v>
@@ -3505,10 +3515,10 @@
         <v>200</v>
       </c>
       <c r="X30" t="n">
-        <v>0.03861961598056001</v>
+        <v>0.1051921781979175</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.007942337476721854</v>
+        <v>0.02163335284275939</v>
       </c>
       <c r="Z30" t="n">
         <v>198.9226798174336</v>
@@ -3550,7 +3560,7 @@
         <v>2026</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
         <v>1</v>
@@ -3559,22 +3569,22 @@
         <v>197.6438084040346</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1449540930155994</v>
+        <v>0.1358944622021244</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02174651184481565</v>
+        <v>0.02038735485451468</v>
       </c>
       <c r="J31" t="n">
         <v>194.2466814459454</v>
       </c>
       <c r="K31" t="n">
-        <v>199.9119361553834</v>
+        <v>199.917440145672</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03921319648113078</v>
+        <v>0.03717228314210543</v>
       </c>
       <c r="M31" t="n">
-        <v>0.005882898675087599</v>
+        <v>0.005576713832852197</v>
       </c>
       <c r="N31" t="n">
         <v>109.7635513825217</v>
@@ -3583,10 +3593,10 @@
         <v>200</v>
       </c>
       <c r="P31" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.390625</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.05000781372089388</v>
+        <v>0.2086263478668542</v>
       </c>
       <c r="R31" t="n">
         <v>199.0633013569061</v>
@@ -3595,22 +3605,22 @@
         <v>200</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3333333333333333</v>
+        <v>1.390625</v>
       </c>
       <c r="U31" t="n">
-        <v>0.05000781372089388</v>
+        <v>0.2086263478668542</v>
       </c>
       <c r="V31" t="n">
         <v>199.9196066031173</v>
       </c>
       <c r="W31" t="n">
-        <v>199.9999999934016</v>
+        <v>199.9999999938141</v>
       </c>
       <c r="X31" t="n">
-        <v>0.06886750441279872</v>
+        <v>0.1602822088730292</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.01033173999629423</v>
+        <v>0.02404608853228754</v>
       </c>
       <c r="Z31" t="n">
         <v>194.1597056483905</v>
@@ -3652,67 +3662,67 @@
         <v>2026</v>
       </c>
       <c r="E32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F32" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="G32" t="n">
-        <v>122.4271857349756</v>
+        <v>117.2609403466935</v>
       </c>
       <c r="H32" t="n">
-        <v>1.132317772431623</v>
+        <v>1.347330425473971</v>
       </c>
       <c r="I32" t="n">
-        <v>0.05064882403943519</v>
+        <v>0.06026638749673898</v>
       </c>
       <c r="J32" t="n">
         <v>164.6748490827784</v>
       </c>
       <c r="K32" t="n">
-        <v>147.203167680811</v>
+        <v>142.2304483574256</v>
       </c>
       <c r="L32" t="n">
-        <v>2.136834004651067</v>
+        <v>2.374505157559204</v>
       </c>
       <c r="M32" t="n">
-        <v>0.09558105695951097</v>
+        <v>0.1062121401200651</v>
       </c>
       <c r="N32" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O32" t="n">
-        <v>157.3546675582937</v>
+        <v>158.8958750633478</v>
       </c>
       <c r="P32" t="n">
-        <v>20.45</v>
+        <v>29.015625</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.914733016494269</v>
+        <v>1.297875314509365</v>
       </c>
       <c r="R32" t="n">
         <v>170.2678863343212</v>
       </c>
       <c r="S32" t="n">
-        <v>157.3546675582937</v>
+        <v>158.8958750633478</v>
       </c>
       <c r="T32" t="n">
-        <v>20.45</v>
+        <v>29.015625</v>
       </c>
       <c r="U32" t="n">
-        <v>0.914733016494269</v>
+        <v>1.297875314509365</v>
       </c>
       <c r="V32" t="n">
         <v>195.3761640213164</v>
       </c>
       <c r="W32" t="n">
-        <v>149.514771523089</v>
+        <v>152.1129095661626</v>
       </c>
       <c r="X32" t="n">
-        <v>26.16782352234143</v>
+        <v>49.67891240947901</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.170492525461177</v>
+        <v>2.222148723935321</v>
       </c>
       <c r="Z32" t="n">
         <v>173.3959783787531</v>
@@ -3728,11 +3738,11 @@
         </is>
       </c>
       <c r="AC32" t="n">
-        <v>122.4271857349756</v>
+        <v>117.2609403466935</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=122.43% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=117.26% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -3756,67 +3766,67 @@
         <v>2026</v>
       </c>
       <c r="E33" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F33" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G33" t="n">
-        <v>123.2888303517377</v>
+        <v>117.0230588650137</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4556641525522134</v>
+        <v>0.5792190093625738</v>
       </c>
       <c r="I33" t="n">
-        <v>0.02514442642122923</v>
+        <v>0.0319624216237323</v>
       </c>
       <c r="J33" t="n">
         <v>170.4028696730483</v>
       </c>
       <c r="K33" t="n">
-        <v>168.3864603919355</v>
+        <v>167.5379951910371</v>
       </c>
       <c r="L33" t="n">
-        <v>2.458028500591371</v>
+        <v>3.793460215948032</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1356387515415138</v>
+        <v>0.2093304481985463</v>
       </c>
       <c r="N33" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O33" t="n">
-        <v>178.6452278811728</v>
+        <v>178.7263051637108</v>
       </c>
       <c r="P33" t="n">
-        <v>8.433333333333334</v>
+        <v>12</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4653675921135828</v>
+        <v>0.6621831350232799</v>
       </c>
       <c r="R33" t="n">
         <v>180.7526372107734</v>
       </c>
       <c r="S33" t="n">
-        <v>178.6452278811728</v>
+        <v>178.7263051637108</v>
       </c>
       <c r="T33" t="n">
-        <v>8.433333333333334</v>
+        <v>12</v>
       </c>
       <c r="U33" t="n">
-        <v>0.4653675921135828</v>
+        <v>0.6621831350232799</v>
       </c>
       <c r="V33" t="n">
         <v>196.5601753860276</v>
       </c>
       <c r="W33" t="n">
-        <v>170.5104647616149</v>
+        <v>171.0800912057028</v>
       </c>
       <c r="X33" t="n">
-        <v>4.302459658811338</v>
+        <v>8.161226949062694</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.2374180187652402</v>
+        <v>0.4503522372305677</v>
       </c>
       <c r="Z33" t="n">
         <v>182.3083787234438</v>
@@ -3832,11 +3842,11 @@
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>123.2888303517377</v>
+        <v>117.0230588650137</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=123.29% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=117.02% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -3860,67 +3870,67 @@
         <v>2026</v>
       </c>
       <c r="E34" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F34" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G34" t="n">
-        <v>135.6931738222306</v>
+        <v>129.160208321844</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9697079095547546</v>
+        <v>1.036536636975544</v>
       </c>
       <c r="I34" t="n">
-        <v>0.044783739508951</v>
+        <v>0.04787007127033831</v>
       </c>
       <c r="J34" t="n">
         <v>169.6571057340244</v>
       </c>
       <c r="K34" t="n">
-        <v>170.4581422708645</v>
+        <v>171.4606303997813</v>
       </c>
       <c r="L34" t="n">
-        <v>14.27976610502534</v>
+        <v>22.86947639373218</v>
       </c>
       <c r="M34" t="n">
-        <v>0.6594783018629109</v>
+        <v>1.056174404097892</v>
       </c>
       <c r="N34" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O34" t="n">
-        <v>164.5890108415669</v>
+        <v>165.6153690231507</v>
       </c>
       <c r="P34" t="n">
-        <v>12.45</v>
+        <v>17.421875</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.5749747438302786</v>
+        <v>0.804589406840814</v>
       </c>
       <c r="R34" t="n">
         <v>184.4689912561869</v>
       </c>
       <c r="S34" t="n">
-        <v>164.5890108415669</v>
+        <v>165.6153690231507</v>
       </c>
       <c r="T34" t="n">
-        <v>12.45</v>
+        <v>17.421875</v>
       </c>
       <c r="U34" t="n">
-        <v>0.5749747438302786</v>
+        <v>0.804589406840814</v>
       </c>
       <c r="V34" t="n">
         <v>195.2398047728465</v>
       </c>
       <c r="W34" t="n">
-        <v>155.3949822801956</v>
+        <v>157.3497684423348</v>
       </c>
       <c r="X34" t="n">
-        <v>9.975811480521559</v>
+        <v>19.23659843186786</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.4607100120893201</v>
+        <v>0.8883982534561575</v>
       </c>
       <c r="Z34" t="n">
         <v>176.7243686471345</v>
@@ -3936,11 +3946,11 @@
         </is>
       </c>
       <c r="AC34" t="n">
-        <v>135.6931738222306</v>
+        <v>129.160208321844</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=135.69% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=129.16% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -3964,67 +3974,67 @@
         <v>2026</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G35" t="n">
-        <v>128.206206655399</v>
+        <v>132.6933187394365</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6116602248966727</v>
+        <v>0.6359314608406307</v>
       </c>
       <c r="I35" t="n">
-        <v>0.01023217481138247</v>
+        <v>0.01063819684609764</v>
       </c>
       <c r="J35" t="n">
         <v>48.55849570822402</v>
       </c>
       <c r="K35" t="n">
-        <v>139.1871116092317</v>
+        <v>141.8013251717405</v>
       </c>
       <c r="L35" t="n">
-        <v>2.830757297351863</v>
+        <v>3.851210139237723</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0473544009175909</v>
+        <v>0.06442507420963309</v>
       </c>
       <c r="N35" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O35" t="n">
-        <v>191.6790647796566</v>
+        <v>191.5781352601809</v>
       </c>
       <c r="P35" t="n">
-        <v>33.28102958205857</v>
+        <v>33.59212094798215</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5567426141595871</v>
+        <v>0.5619467145880228</v>
       </c>
       <c r="R35" t="n">
         <v>189.0070522024178</v>
       </c>
       <c r="S35" t="n">
-        <v>197.983406206727</v>
+        <v>197.9379121901729</v>
       </c>
       <c r="T35" t="n">
-        <v>168.8323159287893</v>
+        <v>167.2646711832399</v>
       </c>
       <c r="U35" t="n">
-        <v>2.824316017419236</v>
+        <v>2.798091629391854</v>
       </c>
       <c r="V35" t="n">
         <v>185.853149170162</v>
       </c>
       <c r="W35" t="n">
-        <v>148.8351407346903</v>
+        <v>151.6616173413013</v>
       </c>
       <c r="X35" t="n">
-        <v>6.78678751889074</v>
+        <v>10.5466116406108</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1135329607425917</v>
+        <v>0.1764292814572353</v>
       </c>
       <c r="Z35" t="n">
         <v>110.5529101365675</v>
@@ -4040,11 +4050,11 @@
         </is>
       </c>
       <c r="AC35" t="n">
-        <v>128.206206655399</v>
+        <v>132.6933187394365</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=128.21% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=132.69% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4068,67 +4078,67 @@
         <v>2026</v>
       </c>
       <c r="E36" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>168.4577977593577</v>
+        <v>169.7720561860511</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4271761750622927</v>
+        <v>0.4317276641208993</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0108043294356571</v>
+        <v>0.01091944771725322</v>
       </c>
       <c r="J36" t="n">
         <v>58.86670393327421</v>
       </c>
       <c r="K36" t="n">
-        <v>169.2080576338946</v>
+        <v>170.4776304723652</v>
       </c>
       <c r="L36" t="n">
-        <v>1.457062808901235</v>
+        <v>2.165813951993467</v>
       </c>
       <c r="M36" t="n">
-        <v>0.03685267932725222</v>
+        <v>0.05477872784049237</v>
       </c>
       <c r="N36" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O36" t="n">
-        <v>187.6622286247015</v>
+        <v>187.6679274197503</v>
       </c>
       <c r="P36" t="n">
-        <v>10.57220473225772</v>
+        <v>10.81052205769364</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.2673968949037677</v>
+        <v>0.273424522483557</v>
       </c>
       <c r="R36" t="n">
         <v>185.6171222178218</v>
       </c>
       <c r="S36" t="n">
-        <v>197.789638432785</v>
+        <v>197.7492146021645</v>
       </c>
       <c r="T36" t="n">
-        <v>82.07154641761467</v>
+        <v>81.73894976651377</v>
       </c>
       <c r="U36" t="n">
-        <v>2.075789982108496</v>
+        <v>2.067377799975056</v>
       </c>
       <c r="V36" t="n">
         <v>187.2910306593169</v>
       </c>
       <c r="W36" t="n">
-        <v>167.120508356944</v>
+        <v>168.9182248715372</v>
       </c>
       <c r="X36" t="n">
-        <v>3.786276551701051</v>
+        <v>6.07637294579545</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.09576418720710847</v>
+        <v>0.153686321740005</v>
       </c>
       <c r="Z36" t="n">
         <v>118.8153464644226</v>
@@ -4144,11 +4154,11 @@
         </is>
       </c>
       <c r="AC36" t="n">
-        <v>168.4577977593577</v>
+        <v>169.7720561860511</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=168.46% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=169.77% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4172,67 +4182,67 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" t="n">
-        <v>161.9002846937967</v>
+        <v>163.3113852606931</v>
       </c>
       <c r="H37" t="n">
-        <v>0.462190131092996</v>
+        <v>0.4645532478996838</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0110250348080327</v>
+        <v>0.01108140434796115</v>
       </c>
       <c r="J37" t="n">
         <v>60.32903496111531</v>
       </c>
       <c r="K37" t="n">
-        <v>172.9633006575739</v>
+        <v>173.5795493207705</v>
       </c>
       <c r="L37" t="n">
-        <v>1.653101623635907</v>
+        <v>2.34427299960588</v>
       </c>
       <c r="M37" t="n">
-        <v>0.03943291237894075</v>
+        <v>0.05592004173491476</v>
       </c>
       <c r="N37" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O37" t="n">
-        <v>186.8406303399722</v>
+        <v>186.8355206782766</v>
       </c>
       <c r="P37" t="n">
-        <v>10.78681930444123</v>
+        <v>10.97614870862924</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2573076539262911</v>
+        <v>0.261823897634093</v>
       </c>
       <c r="R37" t="n">
         <v>181.1462848359585</v>
       </c>
       <c r="S37" t="n">
-        <v>198.1847971628804</v>
+        <v>198.0933293074135</v>
       </c>
       <c r="T37" t="n">
-        <v>88.28279771360384</v>
+        <v>87.28074785650358</v>
       </c>
       <c r="U37" t="n">
-        <v>2.105888577588761</v>
+        <v>2.081985785619168</v>
       </c>
       <c r="V37" t="n">
         <v>185.3862117422507</v>
       </c>
       <c r="W37" t="n">
-        <v>163.8319327550161</v>
+        <v>165.6511166098396</v>
       </c>
       <c r="X37" t="n">
-        <v>3.711324481089274</v>
+        <v>5.497411848994725</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.08852954408859991</v>
+        <v>0.1311346844337169</v>
       </c>
       <c r="Z37" t="n">
         <v>110.8838400280787</v>
@@ -4248,11 +4258,11 @@
         </is>
       </c>
       <c r="AC37" t="n">
-        <v>161.9002846937967</v>
+        <v>163.3113852606931</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=161.90% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=163.31% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4276,67 +4286,67 @@
         <v>2026</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
-        <v>181.9284170935218</v>
+        <v>180.4649390578837</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5674918975368912</v>
+        <v>0.6530102236952079</v>
       </c>
       <c r="I38" t="n">
-        <v>0.03161514749509144</v>
+        <v>0.0363793996487581</v>
       </c>
       <c r="J38" t="n">
         <v>164.4263244057969</v>
       </c>
       <c r="K38" t="n">
-        <v>189.9116176993802</v>
+        <v>187.4627465382147</v>
       </c>
       <c r="L38" t="n">
-        <v>1.37971911857156</v>
+        <v>1.890527785990071</v>
       </c>
       <c r="M38" t="n">
-        <v>0.07686457485078332</v>
+        <v>0.1053218822278591</v>
       </c>
       <c r="N38" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O38" t="n">
-        <v>188.4967526006332</v>
+        <v>188.6837906694766</v>
       </c>
       <c r="P38" t="n">
-        <v>24</v>
+        <v>27.53125</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.337047353760446</v>
+        <v>1.533774373259053</v>
       </c>
       <c r="R38" t="n">
         <v>190.3086393348001</v>
       </c>
       <c r="S38" t="n">
-        <v>188.4967526006332</v>
+        <v>188.6837906694766</v>
       </c>
       <c r="T38" t="n">
-        <v>24</v>
+        <v>27.53125</v>
       </c>
       <c r="U38" t="n">
-        <v>1.337047353760446</v>
+        <v>1.533774373259053</v>
       </c>
       <c r="V38" t="n">
         <v>199.036270909302</v>
       </c>
       <c r="W38" t="n">
-        <v>186.7438171931493</v>
+        <v>186.9094758694109</v>
       </c>
       <c r="X38" t="n">
-        <v>3.339096834991882</v>
+        <v>6.800053487843204</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1860221077989906</v>
+        <v>0.3788330633895935</v>
       </c>
       <c r="Z38" t="n">
         <v>129.2920232398837</v>
@@ -4348,13 +4358,15 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC38" t="n">
+        <v>180.4649390578837</v>
+      </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 6 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=180.46% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4378,67 +4390,67 @@
         <v>2026</v>
       </c>
       <c r="E39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>199.0575304200523</v>
+        <v>199.116434768799</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1555366685566097</v>
+        <v>0.1771998595823088</v>
       </c>
       <c r="I39" t="n">
-        <v>0.00844447470955465</v>
+        <v>0.009620623526694745</v>
       </c>
       <c r="J39" t="n">
         <v>170.2041702191862</v>
       </c>
       <c r="K39" t="n">
-        <v>199.4593181470757</v>
+        <v>199.0916868047874</v>
       </c>
       <c r="L39" t="n">
-        <v>0.08698373878303987</v>
+        <v>0.1146091595807947</v>
       </c>
       <c r="M39" t="n">
-        <v>0.004722564711668266</v>
+        <v>0.006222417893765574</v>
       </c>
       <c r="N39" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O39" t="n">
-        <v>188.9655172413793</v>
+        <v>189.2400218698742</v>
       </c>
       <c r="P39" t="n">
-        <v>10.63333333333333</v>
+        <v>11.90625</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.5773102590204728</v>
+        <v>0.6464200882253139</v>
       </c>
       <c r="R39" t="n">
         <v>190.9487472471646</v>
       </c>
       <c r="S39" t="n">
-        <v>188.9655172413793</v>
+        <v>189.2400218698742</v>
       </c>
       <c r="T39" t="n">
-        <v>10.63333333333333</v>
+        <v>11.90625</v>
       </c>
       <c r="U39" t="n">
-        <v>0.5773102590204728</v>
+        <v>0.6464200882253139</v>
       </c>
       <c r="V39" t="n">
         <v>199.0467638312102</v>
       </c>
       <c r="W39" t="n">
-        <v>196.3144037721181</v>
+        <v>195.80011873161</v>
       </c>
       <c r="X39" t="n">
-        <v>1.219729573806344</v>
+        <v>1.879897655140335</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.06622216892060233</v>
+        <v>0.102064345036462</v>
       </c>
       <c r="Z39" t="n">
         <v>146.152525200624</v>
@@ -4456,7 +4468,7 @@
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 3 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4480,67 +4492,67 @@
         <v>2026</v>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>191.484685334018</v>
+        <v>190.992014377814</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2821475542940849</v>
+        <v>0.3580378953758061</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01086227350506583</v>
+        <v>0.01378394207414075</v>
       </c>
       <c r="J40" t="n">
         <v>165.7522199768573</v>
       </c>
       <c r="K40" t="n">
-        <v>199.42957101869</v>
+        <v>193.8939272873753</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1778563782821241</v>
+        <v>0.2465188128420891</v>
       </c>
       <c r="M40" t="n">
-        <v>0.006847213793344529</v>
+        <v>0.00949061839623057</v>
       </c>
       <c r="N40" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O40" t="n">
-        <v>190.4968553459119</v>
+        <v>190.5094065379552</v>
       </c>
       <c r="P40" t="n">
-        <v>13.66666666666667</v>
+        <v>15.90625</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.5261469361565607</v>
+        <v>0.6123676612127045</v>
       </c>
       <c r="R40" t="n">
         <v>189.6576328974018</v>
       </c>
       <c r="S40" t="n">
-        <v>190.4968553459119</v>
+        <v>190.5094065379552</v>
       </c>
       <c r="T40" t="n">
-        <v>13.66666666666667</v>
+        <v>15.90625</v>
       </c>
       <c r="U40" t="n">
-        <v>0.5261469361565607</v>
+        <v>0.6123676612127045</v>
       </c>
       <c r="V40" t="n">
         <v>198.942356787496</v>
       </c>
       <c r="W40" t="n">
-        <v>189.6416443324678</v>
+        <v>189.2214783528398</v>
       </c>
       <c r="X40" t="n">
-        <v>1.620404119185325</v>
+        <v>3.328579716241676</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.06238321921791434</v>
+        <v>0.1281455136185438</v>
       </c>
       <c r="Z40" t="n">
         <v>124.2002492905602</v>
@@ -4558,7 +4570,7 @@
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 4 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -4582,67 +4594,67 @@
         <v>2026</v>
       </c>
       <c r="E41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F41" t="n">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="G41" t="n">
-        <v>75.94982401573796</v>
+        <v>73.97942797267486</v>
       </c>
       <c r="H41" t="n">
-        <v>2.509249036474215</v>
+        <v>2.564216624419759</v>
       </c>
       <c r="I41" t="n">
-        <v>0.01267077514433651</v>
+        <v>0.01294834103634664</v>
       </c>
       <c r="J41" t="n">
         <v>127.4617865350128</v>
       </c>
       <c r="K41" t="n">
-        <v>80.53135851469673</v>
+        <v>82.6844374440045</v>
       </c>
       <c r="L41" t="n">
-        <v>2.995365591472618</v>
+        <v>4.327159565188543</v>
       </c>
       <c r="M41" t="n">
-        <v>0.01512548309591513</v>
+        <v>0.02185054774045437</v>
       </c>
       <c r="N41" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O41" t="n">
-        <v>184.9224967591002</v>
+        <v>185.580754576068</v>
       </c>
       <c r="P41" t="n">
-        <v>143.0833333333333</v>
+        <v>183.0625</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.7225176605492523</v>
+        <v>0.9243975951144845</v>
       </c>
       <c r="R41" t="n">
         <v>183.1586103963582</v>
       </c>
       <c r="S41" t="n">
-        <v>184.9224967591002</v>
+        <v>185.580754576068</v>
       </c>
       <c r="T41" t="n">
-        <v>143.0833333333333</v>
+        <v>183.0625</v>
       </c>
       <c r="U41" t="n">
-        <v>0.7225176605492523</v>
+        <v>0.9243975951144845</v>
       </c>
       <c r="V41" t="n">
         <v>198.8825072752037</v>
       </c>
       <c r="W41" t="n">
-        <v>81.08729520360787</v>
+        <v>86.41224974787254</v>
       </c>
       <c r="X41" t="n">
-        <v>7.091758973772515</v>
+        <v>12.0767995003465</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.03581074737036191</v>
+        <v>0.06098334948337378</v>
       </c>
       <c r="Z41" t="n">
         <v>124.7888620818299</v>
@@ -4658,11 +4670,11 @@
         </is>
       </c>
       <c r="AC41" t="n">
-        <v>75.94982401573796</v>
+        <v>73.97942797267486</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=75.95% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=73.98% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4686,74 +4698,74 @@
         <v>2026</v>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F42" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G42" t="n">
-        <v>96.20590361230173</v>
+        <v>93.55454584497669</v>
       </c>
       <c r="H42" t="n">
-        <v>1.434857888355854</v>
+        <v>1.457087769765574</v>
       </c>
       <c r="I42" t="n">
-        <v>0.01477141050938982</v>
+        <v>0.01500026014428592</v>
       </c>
       <c r="J42" t="n">
         <v>139.5371944473096</v>
       </c>
       <c r="K42" t="n">
-        <v>155.7418456955398</v>
+        <v>156.4122792151834</v>
       </c>
       <c r="L42" t="n">
-        <v>1.930294394398277</v>
+        <v>2.037016177010556</v>
       </c>
       <c r="M42" t="n">
-        <v>0.01987177345925391</v>
+        <v>0.02097044063323182</v>
       </c>
       <c r="N42" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O42" t="n">
-        <v>183.260562191004</v>
+        <v>183.9459105198269</v>
       </c>
       <c r="P42" t="n">
-        <v>60.50599734144464</v>
+        <v>73.95324624959355</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.6228902055482655</v>
+        <v>0.7613254021319629</v>
       </c>
       <c r="R42" t="n">
         <v>178.6003071053324</v>
       </c>
       <c r="S42" t="n">
-        <v>183.2778706175911</v>
+        <v>183.9947814082954</v>
       </c>
       <c r="T42" t="n">
-        <v>62.73333333333333</v>
+        <v>79.46875</v>
       </c>
       <c r="U42" t="n">
-        <v>0.6458199287950929</v>
+        <v>0.8181057778921631</v>
       </c>
       <c r="V42" t="n">
         <v>198.6803521667581</v>
       </c>
       <c r="W42" t="n">
-        <v>90.86697592286167</v>
+        <v>94.97570837545362</v>
       </c>
       <c r="X42" t="n">
-        <v>2.08702081704121</v>
+        <v>3.853029430890049</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.02148522266932143</v>
+        <v>0.03966572570727113</v>
       </c>
       <c r="Z42" t="n">
         <v>125.9010082864909</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
@@ -4762,11 +4774,11 @@
         </is>
       </c>
       <c r="AC42" t="n">
-        <v>90.86697592286167</v>
+        <v>93.55454584497669</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=90.87% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=93.55% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4790,67 +4802,67 @@
         <v>2026</v>
       </c>
       <c r="E43" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F43" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G43" t="n">
-        <v>83.4495100316808</v>
+        <v>80.56609614743942</v>
       </c>
       <c r="H43" t="n">
-        <v>1.486748173543052</v>
+        <v>1.495524492027962</v>
       </c>
       <c r="I43" t="n">
-        <v>0.01116360643719118</v>
+        <v>0.01122950553649829</v>
       </c>
       <c r="J43" t="n">
         <v>137.8269504556986</v>
       </c>
       <c r="K43" t="n">
-        <v>130.7211233694397</v>
+        <v>134.7096573919788</v>
       </c>
       <c r="L43" t="n">
-        <v>1.794886661910823</v>
+        <v>1.959261437128033</v>
       </c>
       <c r="M43" t="n">
-        <v>0.01347733842859571</v>
+        <v>0.01471158598401977</v>
       </c>
       <c r="N43" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O43" t="n">
-        <v>187.2518083194242</v>
+        <v>187.7797061309884</v>
       </c>
       <c r="P43" t="n">
-        <v>78.44234551334827</v>
+        <v>99.22426670367474</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5890032279201128</v>
+        <v>0.7450492842099613</v>
       </c>
       <c r="R43" t="n">
         <v>183.3878591635464</v>
       </c>
       <c r="S43" t="n">
-        <v>187.2578670760399</v>
+        <v>187.7997804715835</v>
       </c>
       <c r="T43" t="n">
-        <v>81.45</v>
+        <v>104.625</v>
       </c>
       <c r="U43" t="n">
-        <v>0.6115869254053548</v>
+        <v>0.7856019898162705</v>
       </c>
       <c r="V43" t="n">
         <v>198.9631246433146</v>
       </c>
       <c r="W43" t="n">
-        <v>91.01274318253468</v>
+        <v>96.13725845231659</v>
       </c>
       <c r="X43" t="n">
-        <v>4.360115194213262</v>
+        <v>7.951822962980351</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.03273897416871774</v>
+        <v>0.05970817627129343</v>
       </c>
       <c r="Z43" t="n">
         <v>126.6160396504699</v>
@@ -4866,11 +4878,11 @@
         </is>
       </c>
       <c r="AC43" t="n">
-        <v>83.4495100316808</v>
+        <v>80.56609614743942</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=83.45% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=80.57% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4894,67 +4906,67 @@
         <v>2026</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F44" t="n">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="G44" t="n">
-        <v>98.47151054424607</v>
+        <v>97.23977132324379</v>
       </c>
       <c r="H44" t="n">
-        <v>4.017906093573102</v>
+        <v>4.33342698474571</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08406760493941366</v>
+        <v>0.09066932359870715</v>
       </c>
       <c r="J44" t="n">
         <v>101.902133963665</v>
       </c>
       <c r="K44" t="n">
-        <v>98.09760383854663</v>
+        <v>98.19298430595107</v>
       </c>
       <c r="L44" t="n">
-        <v>1.995254153813774</v>
+        <v>2.51540602706301</v>
       </c>
       <c r="M44" t="n">
-        <v>0.04174717727346723</v>
+        <v>0.05263043864653872</v>
       </c>
       <c r="N44" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O44" t="n">
-        <v>186.8078753071063</v>
+        <v>186.0496228933664</v>
       </c>
       <c r="P44" t="n">
-        <v>101.7924516165815</v>
+        <v>106.0353716657421</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.129827678652157</v>
+        <v>2.218603304108636</v>
       </c>
       <c r="R44" t="n">
         <v>175.3243009167544</v>
       </c>
       <c r="S44" t="n">
-        <v>187.588295223341</v>
+        <v>187.4588604590726</v>
       </c>
       <c r="T44" t="n">
-        <v>140.5166666666667</v>
+        <v>152.984375</v>
       </c>
       <c r="U44" t="n">
-        <v>2.940063641515191</v>
+        <v>3.200928468680528</v>
       </c>
       <c r="V44" t="n">
         <v>196.0447922196767</v>
       </c>
       <c r="W44" t="n">
-        <v>110.8339792344407</v>
+        <v>113.4998918652504</v>
       </c>
       <c r="X44" t="n">
-        <v>18.16852661292504</v>
+        <v>21.73156362157868</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.3801444040889246</v>
+        <v>0.4546946749643768</v>
       </c>
       <c r="Z44" t="n">
         <v>121.0188473841644</v>
@@ -4970,11 +4982,11 @@
         </is>
       </c>
       <c r="AC44" t="n">
-        <v>98.09760383854663</v>
+        <v>98.19298430595107</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=98.10% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=98.19% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -4998,74 +5010,74 @@
         <v>2026</v>
       </c>
       <c r="E45" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F45" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
-        <v>125.6352641194155</v>
+        <v>123.6615696831511</v>
       </c>
       <c r="H45" t="n">
-        <v>4.174806737513546</v>
+        <v>4.44235986049962</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1422572842087461</v>
+        <v>0.1513742045958767</v>
       </c>
       <c r="J45" t="n">
         <v>133.2410714461222</v>
       </c>
       <c r="K45" t="n">
-        <v>125.8561656686459</v>
+        <v>126.0161733399299</v>
       </c>
       <c r="L45" t="n">
-        <v>1.436951799944003</v>
+        <v>1.766908034351987</v>
       </c>
       <c r="M45" t="n">
-        <v>0.04896438888106495</v>
+        <v>0.06020770642025724</v>
       </c>
       <c r="N45" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O45" t="n">
-        <v>185.7061596829474</v>
+        <v>185.408297304904</v>
       </c>
       <c r="P45" t="n">
-        <v>55.61887342091581</v>
+        <v>60.30235707933744</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.895223032125765</v>
+        <v>2.05481357314322</v>
       </c>
       <c r="R45" t="n">
         <v>177.4357058560748</v>
       </c>
       <c r="S45" t="n">
-        <v>185.7183105546389</v>
+        <v>185.4686552579178</v>
       </c>
       <c r="T45" t="n">
-        <v>61.31666666666667</v>
+        <v>66.46875</v>
       </c>
       <c r="U45" t="n">
-        <v>2.089376353246016</v>
+        <v>2.264934511766585</v>
       </c>
       <c r="V45" t="n">
         <v>195.8311934408034</v>
       </c>
       <c r="W45" t="n">
-        <v>116.8108862461247</v>
+        <v>118.6234488433119</v>
       </c>
       <c r="X45" t="n">
-        <v>6.698293822804751</v>
+        <v>8.375005187109451</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.2282455567349079</v>
+        <v>0.2853797955356218</v>
       </c>
       <c r="Z45" t="n">
         <v>112.5504951429215</v>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -5074,11 +5086,11 @@
         </is>
       </c>
       <c r="AC45" t="n">
-        <v>116.8108862461247</v>
+        <v>123.6615696831511</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=116.81% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=123.66% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5102,67 +5114,67 @@
         <v>2026</v>
       </c>
       <c r="E46" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F46" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G46" t="n">
-        <v>128.0344004160513</v>
+        <v>124.2286314426618</v>
       </c>
       <c r="H46" t="n">
-        <v>3.220915073690542</v>
+        <v>3.323649909340402</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08599856684029816</v>
+        <v>0.08874159123812504</v>
       </c>
       <c r="J46" t="n">
         <v>129.1401202444324</v>
       </c>
       <c r="K46" t="n">
-        <v>138.8108877847343</v>
+        <v>137.8933440857099</v>
       </c>
       <c r="L46" t="n">
-        <v>1.272332175143986</v>
+        <v>1.478871390086655</v>
       </c>
       <c r="M46" t="n">
-        <v>0.03397132215653529</v>
+        <v>0.03948592781207589</v>
       </c>
       <c r="N46" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O46" t="n">
-        <v>188.2918837662258</v>
+        <v>187.9130410895593</v>
       </c>
       <c r="P46" t="n">
-        <v>59.68078838856012</v>
+        <v>63.01301606104661</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.593479539786336</v>
+        <v>1.682450157658316</v>
       </c>
       <c r="R46" t="n">
         <v>173.6962919474645</v>
       </c>
       <c r="S46" t="n">
-        <v>188.8267987558104</v>
+        <v>188.8211846002213</v>
       </c>
       <c r="T46" t="n">
-        <v>79.40000000000001</v>
+        <v>86.703125</v>
       </c>
       <c r="U46" t="n">
-        <v>2.119983312473926</v>
+        <v>2.314977054651648</v>
       </c>
       <c r="V46" t="n">
         <v>196.1388328305384</v>
       </c>
       <c r="W46" t="n">
-        <v>136.8734725362575</v>
+        <v>138.8187505468746</v>
       </c>
       <c r="X46" t="n">
-        <v>12.9946526042741</v>
+        <v>15.62149985863151</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.346957766655629</v>
+        <v>0.4170946979359268</v>
       </c>
       <c r="Z46" t="n">
         <v>125.7491255686458</v>
@@ -5178,11 +5190,11 @@
         </is>
       </c>
       <c r="AC46" t="n">
-        <v>128.0344004160513</v>
+        <v>124.2286314426618</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=128.03% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=124.23% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5206,67 +5218,67 @@
         <v>2026</v>
       </c>
       <c r="E47" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F47" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G47" t="n">
-        <v>197.4364926528566</v>
+        <v>197.6806362097274</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6369573064953509</v>
+        <v>0.7533974748393915</v>
       </c>
       <c r="I47" t="n">
-        <v>0.01160742244182872</v>
+        <v>0.0137293389492372</v>
       </c>
       <c r="J47" t="n">
         <v>52.02932925897922</v>
       </c>
       <c r="K47" t="n">
-        <v>180.1798683655593</v>
+        <v>179.9453107710243</v>
       </c>
       <c r="L47" t="n">
-        <v>3.409523834340176</v>
+        <v>5.598316321632638</v>
       </c>
       <c r="M47" t="n">
-        <v>0.06213255278979819</v>
+        <v>0.1020194318292964</v>
       </c>
       <c r="N47" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O47" t="n">
-        <v>196.3603122729191</v>
+        <v>196.0902107040521</v>
       </c>
       <c r="P47" t="n">
-        <v>42.33628413852398</v>
+        <v>47.22420213766239</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.7715040389708242</v>
+        <v>0.8605777154927087</v>
       </c>
       <c r="R47" t="n">
         <v>176.1972572849119</v>
       </c>
       <c r="S47" t="n">
-        <v>198.2307854609157</v>
+        <v>198.1626280604777</v>
       </c>
       <c r="T47" t="n">
-        <v>105.7600687886773</v>
+        <v>120.5566048790589</v>
       </c>
       <c r="U47" t="n">
-        <v>1.927290547401865</v>
+        <v>2.19693129620153</v>
       </c>
       <c r="V47" t="n">
         <v>193.8459595711977</v>
       </c>
       <c r="W47" t="n">
-        <v>182.5544195123821</v>
+        <v>182.3991198672665</v>
       </c>
       <c r="X47" t="n">
-        <v>7.486138477694856</v>
+        <v>9.854914858240488</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1364216579078789</v>
+        <v>0.1795884256626968</v>
       </c>
       <c r="Z47" t="n">
         <v>130.8486591703272</v>
@@ -5282,11 +5294,11 @@
         </is>
       </c>
       <c r="AC47" t="n">
-        <v>180.1798683655593</v>
+        <v>179.9453107710243</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=180.18% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=179.95% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5310,67 +5322,67 @@
         <v>2026</v>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G48" t="n">
-        <v>198.3360471573452</v>
+        <v>198.4469773468555</v>
       </c>
       <c r="H48" t="n">
-        <v>0.3451178602391139</v>
+        <v>0.3547979939741693</v>
       </c>
       <c r="I48" t="n">
-        <v>0.01253834187971349</v>
+        <v>0.01289002702903431</v>
       </c>
       <c r="J48" t="n">
         <v>75.82494372432545</v>
       </c>
       <c r="K48" t="n">
-        <v>184.5453577696137</v>
+        <v>184.4822122372113</v>
       </c>
       <c r="L48" t="n">
-        <v>1.33804197106262</v>
+        <v>1.771714701815509</v>
       </c>
       <c r="M48" t="n">
-        <v>0.04861187905767922</v>
+        <v>0.06436747327213474</v>
       </c>
       <c r="N48" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O48" t="n">
-        <v>194.3060832548155</v>
+        <v>194.228971973746</v>
       </c>
       <c r="P48" t="n">
-        <v>16.18379468811215</v>
+        <v>16.83265144259446</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.5879671094681982</v>
+        <v>0.6115404702123327</v>
       </c>
       <c r="R48" t="n">
         <v>183.163735304357</v>
       </c>
       <c r="S48" t="n">
-        <v>197.4134559091565</v>
+        <v>197.4814314641825</v>
       </c>
       <c r="T48" t="n">
-        <v>44.83206660190069</v>
+        <v>51.14719891833802</v>
       </c>
       <c r="U48" t="n">
-        <v>1.628776261649435</v>
+        <v>1.858208861701654</v>
       </c>
       <c r="V48" t="n">
         <v>192.3368460426438</v>
       </c>
       <c r="W48" t="n">
-        <v>190.3155545241084</v>
+        <v>190.5705697921683</v>
       </c>
       <c r="X48" t="n">
-        <v>6.479984524027412</v>
+        <v>8.19300442332386</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2354217810727489</v>
+        <v>0.2976568364513664</v>
       </c>
       <c r="Z48" t="n">
         <v>148.2729860112375</v>
@@ -5386,11 +5398,11 @@
         </is>
       </c>
       <c r="AC48" t="n">
-        <v>184.5453577696137</v>
+        <v>184.4822122372113</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=184.55% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=184.48% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5414,85 +5426,87 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
         <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2825586781600808</v>
+        <v>0.3898987607750757</v>
       </c>
       <c r="I49" t="n">
-        <v>0.008063026307403767</v>
+        <v>0.01112605702229572</v>
       </c>
       <c r="J49" t="n">
         <v>67.54170898302603</v>
       </c>
       <c r="K49" t="n">
-        <v>185.4380858106232</v>
+        <v>183.7851048607569</v>
       </c>
       <c r="L49" t="n">
-        <v>2.498396514648</v>
+        <v>3.233840030780621</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07129364051073302</v>
+        <v>0.09228007935168527</v>
       </c>
       <c r="N49" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O49" t="n">
-        <v>197.0233242641232</v>
+        <v>196.379677223346</v>
       </c>
       <c r="P49" t="n">
-        <v>21.51664874945378</v>
+        <v>23.66259142527058</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.6139939004659539</v>
+        <v>0.6752300032179941</v>
       </c>
       <c r="R49" t="n">
         <v>179.6516960231333</v>
       </c>
       <c r="S49" t="n">
-        <v>198.8887153465189</v>
+        <v>198.690507734309</v>
       </c>
       <c r="T49" t="n">
-        <v>56.03326440617489</v>
+        <v>63.87458952195998</v>
       </c>
       <c r="U49" t="n">
-        <v>1.598951721952556</v>
+        <v>1.822709884700124</v>
       </c>
       <c r="V49" t="n">
         <v>193.5695579772771</v>
       </c>
       <c r="W49" t="n">
-        <v>187.1159543060611</v>
+        <v>186.2888716112597</v>
       </c>
       <c r="X49" t="n">
-        <v>3.806267332840057</v>
+        <v>5.277896557233818</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1086147268154823</v>
+        <v>0.1506087835130036</v>
       </c>
       <c r="Z49" t="n">
         <v>141.2583029624075</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC49" t="n">
+        <v>183.7851048607569</v>
+      </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=183.79% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5516,67 +5530,67 @@
         <v>2026</v>
       </c>
       <c r="E50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F50" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="G50" t="n">
-        <v>181.6093242162106</v>
+        <v>171.2930985561618</v>
       </c>
       <c r="H50" t="n">
-        <v>5.695770875531969</v>
+        <v>5.506505002681031</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2473733279275557</v>
+        <v>0.2391533117342468</v>
       </c>
       <c r="J50" t="n">
         <v>162.6912701840232</v>
       </c>
       <c r="K50" t="n">
-        <v>191.9366713895737</v>
+        <v>192.3467776640405</v>
       </c>
       <c r="L50" t="n">
-        <v>0.6046137871938644</v>
+        <v>1.687664144098375</v>
       </c>
       <c r="M50" t="n">
-        <v>0.02625901355890833</v>
+        <v>0.07329703123119977</v>
       </c>
       <c r="N50" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O50" t="n">
-        <v>186.1286318640659</v>
+        <v>172.5375097425694</v>
       </c>
       <c r="P50" t="n">
-        <v>15.78147665659587</v>
+        <v>16.23466664552689</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.6854061522951517</v>
+        <v>0.7050886708155</v>
       </c>
       <c r="R50" t="n">
         <v>176.9763205357646</v>
       </c>
       <c r="S50" t="n">
-        <v>189.8841877001909</v>
+        <v>180.2882425166753</v>
       </c>
       <c r="T50" t="n">
-        <v>19.57917005013473</v>
+        <v>18.8620500300316</v>
       </c>
       <c r="U50" t="n">
-        <v>0.8503439761187723</v>
+        <v>0.8191986983727079</v>
       </c>
       <c r="V50" t="n">
         <v>160.5521309789579</v>
       </c>
       <c r="W50" t="n">
-        <v>191.1823462858561</v>
+        <v>187.9582835119267</v>
       </c>
       <c r="X50" t="n">
-        <v>31.87616557327694</v>
+        <v>35.15234470259706</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.384415442921909</v>
+        <v>1.526703352990101</v>
       </c>
       <c r="Z50" t="n">
         <v>135.4400555181058</v>
@@ -5592,11 +5606,11 @@
         </is>
       </c>
       <c r="AC50" t="n">
-        <v>181.6093242162106</v>
+        <v>171.2930985561618</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=181.61% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=171.29% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5620,67 +5634,67 @@
         <v>2026</v>
       </c>
       <c r="E51" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G51" t="n">
-        <v>183.4879098173768</v>
+        <v>174.4865462700739</v>
       </c>
       <c r="H51" t="n">
-        <v>2.111044521326194</v>
+        <v>2.104730247733441</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1766102606076816</v>
+        <v>0.1760820076535167</v>
       </c>
       <c r="J51" t="n">
         <v>169.9274838481079</v>
       </c>
       <c r="K51" t="n">
-        <v>172.3082229992432</v>
+        <v>167.7560230281385</v>
       </c>
       <c r="L51" t="n">
-        <v>0.3449617018585135</v>
+        <v>0.5688430275534382</v>
       </c>
       <c r="M51" t="n">
-        <v>0.02885954107051616</v>
+        <v>0.04758948204368633</v>
       </c>
       <c r="N51" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O51" t="n">
-        <v>192.198574523709</v>
+        <v>190.9413348902396</v>
       </c>
       <c r="P51" t="n">
-        <v>22.53175402442044</v>
+        <v>25.35822030640537</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.885009487010338</v>
+        <v>2.121472025633913</v>
       </c>
       <c r="R51" t="n">
         <v>191.5443980495646</v>
       </c>
       <c r="S51" t="n">
-        <v>189.3725933315535</v>
+        <v>184.4596038471734</v>
       </c>
       <c r="T51" t="n">
-        <v>8.076082774173011</v>
+        <v>8.391394772656394</v>
       </c>
       <c r="U51" t="n">
-        <v>0.6756461405844087</v>
+        <v>0.7020251835947833</v>
       </c>
       <c r="V51" t="n">
         <v>165.5121650610737</v>
       </c>
       <c r="W51" t="n">
-        <v>191.0961530583145</v>
+        <v>190.1505370830066</v>
       </c>
       <c r="X51" t="n">
-        <v>17.35802982679935</v>
+        <v>21.00874918553261</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.45217504433354</v>
+        <v>1.757594703103382</v>
       </c>
       <c r="Z51" t="n">
         <v>151.1230387281904</v>
@@ -5692,13 +5706,15 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>167.7560230281385</v>
+      </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: menor SMAPE real=167.76% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5722,67 +5738,67 @@
         <v>2026</v>
       </c>
       <c r="E52" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F52" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G52" t="n">
-        <v>179.8956291501944</v>
+        <v>171.9928455041256</v>
       </c>
       <c r="H52" t="n">
-        <v>3.205054604669189</v>
+        <v>3.337980188772649</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1990330823780595</v>
+        <v>0.2072877276163881</v>
       </c>
       <c r="J52" t="n">
         <v>174.432365021141</v>
       </c>
       <c r="K52" t="n">
-        <v>195.1242849844105</v>
+        <v>195.3136714084257</v>
       </c>
       <c r="L52" t="n">
-        <v>0.3635914258970534</v>
+        <v>1.118487699559207</v>
       </c>
       <c r="M52" t="n">
-        <v>0.02257893582128024</v>
+        <v>0.0694578039702981</v>
       </c>
       <c r="N52" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O52" t="n">
-        <v>196.2047085093486</v>
+        <v>193.0045785737439</v>
       </c>
       <c r="P52" t="n">
-        <v>31.19829930124861</v>
+        <v>33.72763051890161</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.937406515893568</v>
+        <v>2.09447734640957</v>
       </c>
       <c r="R52" t="n">
         <v>190.0491824654319</v>
       </c>
       <c r="S52" t="n">
-        <v>189.4513429810953</v>
+        <v>178.5636777387527</v>
       </c>
       <c r="T52" t="n">
-        <v>10.50655857373429</v>
+        <v>10.04882463583072</v>
       </c>
       <c r="U52" t="n">
-        <v>0.6524546368319374</v>
+        <v>0.6240294747653465</v>
       </c>
       <c r="V52" t="n">
         <v>154.7555469695623</v>
       </c>
       <c r="W52" t="n">
-        <v>191.9112853316146</v>
+        <v>187.888629056777</v>
       </c>
       <c r="X52" t="n">
-        <v>25.03129298284138</v>
+        <v>26.28035703295192</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.554436979334221</v>
+        <v>1.632003541731926</v>
       </c>
       <c r="Z52" t="n">
         <v>133.8716916594558</v>
@@ -5798,11 +5814,11 @@
         </is>
       </c>
       <c r="AC52" t="n">
-        <v>179.8956291501944</v>
+        <v>171.9928455041256</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=179.90% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=171.99% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5826,67 +5842,67 @@
         <v>2026</v>
       </c>
       <c r="E53" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F53" t="n">
-        <v>3878</v>
+        <v>4404</v>
       </c>
       <c r="G53" t="n">
-        <v>22.34651210656633</v>
+        <v>23.14175963708643</v>
       </c>
       <c r="H53" t="n">
-        <v>33.31859414632342</v>
+        <v>38.30678709599061</v>
       </c>
       <c r="I53" t="n">
-        <v>0.03749257187454415</v>
+        <v>0.04310565932559822</v>
       </c>
       <c r="J53" t="n">
         <v>35.23746831954708</v>
       </c>
       <c r="K53" t="n">
-        <v>28.21900210882411</v>
+        <v>32.77357810109085</v>
       </c>
       <c r="L53" t="n">
-        <v>34.11616154524422</v>
+        <v>43.02335789261404</v>
       </c>
       <c r="M53" t="n">
-        <v>0.03839005431025284</v>
+        <v>0.04841309723300745</v>
       </c>
       <c r="N53" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O53" t="n">
-        <v>165.7517623458724</v>
+        <v>166.5077835010221</v>
       </c>
       <c r="P53" t="n">
-        <v>1482.410777604546</v>
+        <v>1653.974275134457</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.668119380513247</v>
+        <v>1.861175448063389</v>
       </c>
       <c r="R53" t="n">
         <v>169.178554981669</v>
       </c>
       <c r="S53" t="n">
-        <v>165.9235835561136</v>
+        <v>166.9741566956818</v>
       </c>
       <c r="T53" t="n">
-        <v>1578.883333333333</v>
+        <v>1837.171875</v>
       </c>
       <c r="U53" t="n">
-        <v>1.776677509157509</v>
+        <v>2.067323076923077</v>
       </c>
       <c r="V53" t="n">
         <v>188.2648408233968</v>
       </c>
       <c r="W53" t="n">
-        <v>66.5088389137223</v>
+        <v>72.28090248644145</v>
       </c>
       <c r="X53" t="n">
-        <v>290.2219395031086</v>
+        <v>400.0158107222369</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.3265794132430585</v>
+        <v>0.4501276815160117</v>
       </c>
       <c r="Z53" t="n">
         <v>92.2349408254034</v>
@@ -5902,11 +5918,11 @@
         </is>
       </c>
       <c r="AC53" t="n">
-        <v>22.34651210656633</v>
+        <v>23.14175963708643</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=22.35% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=23.14% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -5930,67 +5946,67 @@
         <v>2026</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F54" t="n">
-        <v>1793</v>
+        <v>2026</v>
       </c>
       <c r="G54" t="n">
-        <v>17.79050811290443</v>
+        <v>17.14143037623663</v>
       </c>
       <c r="H54" t="n">
-        <v>10.54307531656366</v>
+        <v>10.44615146886808</v>
       </c>
       <c r="I54" t="n">
-        <v>0.02085440604594179</v>
+        <v>0.02066268880835334</v>
       </c>
       <c r="J54" t="n">
         <v>38.4591918317379</v>
       </c>
       <c r="K54" t="n">
-        <v>29.33637308392764</v>
+        <v>29.95786837609862</v>
       </c>
       <c r="L54" t="n">
-        <v>22.61307561621521</v>
+        <v>24.76304569623144</v>
       </c>
       <c r="M54" t="n">
-        <v>0.04472909911847635</v>
+        <v>0.04898178134724167</v>
       </c>
       <c r="N54" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O54" t="n">
-        <v>165.2785945174107</v>
+        <v>165.6186481550991</v>
       </c>
       <c r="P54" t="n">
-        <v>633.6555268756704</v>
+        <v>679.0276123750535</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.253382836975451</v>
+        <v>1.343129696003271</v>
       </c>
       <c r="R54" t="n">
         <v>163.7593826553296</v>
       </c>
       <c r="S54" t="n">
-        <v>165.8297134659983</v>
+        <v>166.8813852647021</v>
       </c>
       <c r="T54" t="n">
-        <v>714.9833333333333</v>
+        <v>827.5</v>
       </c>
       <c r="U54" t="n">
-        <v>1.414250804600543</v>
+        <v>1.636810938446513</v>
       </c>
       <c r="V54" t="n">
         <v>187.9362468841497</v>
       </c>
       <c r="W54" t="n">
-        <v>66.31045525836954</v>
+        <v>72.16040260248478</v>
       </c>
       <c r="X54" t="n">
-        <v>129.7378537080727</v>
+        <v>180.1436393650845</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.2566239735105099</v>
+        <v>0.3563275884040293</v>
       </c>
       <c r="Z54" t="n">
         <v>91.67135817890519</v>
@@ -6006,11 +6022,11 @@
         </is>
       </c>
       <c r="AC54" t="n">
-        <v>17.79050811290443</v>
+        <v>17.14143037623663</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=17.79% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=17.14% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6034,67 +6050,67 @@
         <v>2026</v>
       </c>
       <c r="E55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F55" t="n">
-        <v>2079</v>
+        <v>2372</v>
       </c>
       <c r="G55" t="n">
-        <v>21.53694792260096</v>
+        <v>20.92198386139502</v>
       </c>
       <c r="H55" t="n">
-        <v>14.33813548159063</v>
+        <v>14.60387777653818</v>
       </c>
       <c r="I55" t="n">
-        <v>0.02270780758663031</v>
+        <v>0.02312867297104841</v>
       </c>
       <c r="J55" t="n">
         <v>38.25160771522186</v>
       </c>
       <c r="K55" t="n">
-        <v>30.17748998611819</v>
+        <v>29.97621694499686</v>
       </c>
       <c r="L55" t="n">
-        <v>26.47224732773434</v>
+        <v>27.6677141939641</v>
       </c>
       <c r="M55" t="n">
-        <v>0.04192502571032985</v>
+        <v>0.04381832847688494</v>
       </c>
       <c r="N55" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O55" t="n">
-        <v>165.9721223123166</v>
+        <v>166.8417490367129</v>
       </c>
       <c r="P55" t="n">
-        <v>822.3178682226661</v>
+        <v>934.8911671193673</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.3023336228496</v>
+        <v>1.480619901007639</v>
       </c>
       <c r="R55" t="n">
         <v>170.8273891473021</v>
       </c>
       <c r="S55" t="n">
-        <v>166.0862873260907</v>
+        <v>167.1304454732693</v>
       </c>
       <c r="T55" t="n">
-        <v>864.1</v>
+        <v>1009.859375</v>
       </c>
       <c r="U55" t="n">
-        <v>1.368505449038376</v>
+        <v>1.599349678798737</v>
       </c>
       <c r="V55" t="n">
         <v>188.8384134033935</v>
       </c>
       <c r="W55" t="n">
-        <v>64.36158086853793</v>
+        <v>70.17533513380856</v>
       </c>
       <c r="X55" t="n">
-        <v>154.3932353666919</v>
+        <v>212.9343393386995</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.2445179769632939</v>
+        <v>0.3372315746700578</v>
       </c>
       <c r="Z55" t="n">
         <v>92.1901984902002</v>
@@ -6110,11 +6126,11 @@
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>21.53694792260096</v>
+        <v>20.92198386139502</v>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=21.54% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=20.92% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6138,67 +6154,67 @@
         <v>2026</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F56" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G56" t="n">
-        <v>78.5538480505229</v>
+        <v>84.13837080041309</v>
       </c>
       <c r="H56" t="n">
-        <v>4.067269629281515</v>
+        <v>4.797222217665949</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1030993568892653</v>
+        <v>0.1216025910688453</v>
       </c>
       <c r="J56" t="n">
         <v>154.1439500713238</v>
       </c>
       <c r="K56" t="n">
-        <v>76.25300836710791</v>
+        <v>80.12707021439411</v>
       </c>
       <c r="L56" t="n">
-        <v>2.409234264790217</v>
+        <v>2.569834747871757</v>
       </c>
       <c r="M56" t="n">
-        <v>0.06107057705425138</v>
+        <v>0.06514156521854896</v>
       </c>
       <c r="N56" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O56" t="n">
-        <v>172.8259293765196</v>
+        <v>174.2106307285389</v>
       </c>
       <c r="P56" t="n">
-        <v>70.36836257459157</v>
+        <v>75.35645005951561</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.783735426478874</v>
+        <v>1.910176173878723</v>
       </c>
       <c r="R56" t="n">
         <v>179.6737627262154</v>
       </c>
       <c r="S56" t="n">
-        <v>173.2900008669255</v>
+        <v>174.8689598995419</v>
       </c>
       <c r="T56" t="n">
-        <v>83.83333333333333</v>
+        <v>102.609375</v>
       </c>
       <c r="U56" t="n">
-        <v>2.125052809463456</v>
+        <v>2.600998098859316</v>
       </c>
       <c r="V56" t="n">
         <v>197.7368060568652</v>
       </c>
       <c r="W56" t="n">
-        <v>60.08762800466895</v>
+        <v>67.2397715447118</v>
       </c>
       <c r="X56" t="n">
-        <v>2.000377583772848</v>
+        <v>3.119186977789615</v>
       </c>
       <c r="Y56" t="n">
-        <v>0.05070665611591503</v>
+        <v>0.07906684354346298</v>
       </c>
       <c r="Z56" t="n">
         <v>104.7066447751141</v>
@@ -6214,11 +6230,11 @@
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>60.08762800466895</v>
+        <v>67.2397715447118</v>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=60.09% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=67.24% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6242,74 +6258,74 @@
         <v>2026</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F57" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G57" t="n">
-        <v>100.2985096506785</v>
+        <v>104.2963219317266</v>
       </c>
       <c r="H57" t="n">
-        <v>1.945993378968185</v>
+        <v>2.251427608175669</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1016848271178673</v>
+        <v>0.1176448129680297</v>
       </c>
       <c r="J57" t="n">
         <v>164.0555422208552</v>
       </c>
       <c r="K57" t="n">
-        <v>133.1646447608327</v>
+        <v>137.1691869983401</v>
       </c>
       <c r="L57" t="n">
-        <v>1.499200354839822</v>
+        <v>1.46810334804045</v>
       </c>
       <c r="M57" t="n">
-        <v>0.07833835949522255</v>
+        <v>0.07671343425423648</v>
       </c>
       <c r="N57" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O57" t="n">
-        <v>173.2853535587645</v>
+        <v>174.6870071288088</v>
       </c>
       <c r="P57" t="n">
-        <v>32.67215808699144</v>
+        <v>36.1053231107882</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.707232297164804</v>
+        <v>1.886626942431781</v>
       </c>
       <c r="R57" t="n">
         <v>187.7358722188936</v>
       </c>
       <c r="S57" t="n">
-        <v>173.4749001434029</v>
+        <v>175.0274557265455</v>
       </c>
       <c r="T57" t="n">
-        <v>36.66666666666666</v>
+        <v>45.09375</v>
       </c>
       <c r="U57" t="n">
-        <v>1.915959068147181</v>
+        <v>2.356303069888962</v>
       </c>
       <c r="V57" t="n">
         <v>197.2831175654684</v>
       </c>
       <c r="W57" t="n">
-        <v>105.6158970996608</v>
+        <v>109.0144645185557</v>
       </c>
       <c r="X57" t="n">
-        <v>1.056349174846893</v>
+        <v>1.336265978279143</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.05519786674575532</v>
+        <v>0.06982447959655873</v>
       </c>
       <c r="Z57" t="n">
         <v>124.2225772452616</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>NBGLM</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
@@ -6318,11 +6334,11 @@
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>100.2985096506785</v>
+        <v>109.0144645185557</v>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=100.30% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=109.01% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6346,67 +6362,67 @@
         <v>2026</v>
       </c>
       <c r="E58" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F58" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G58" t="n">
-        <v>91.80424842220479</v>
+        <v>96.9461023687702</v>
       </c>
       <c r="H58" t="n">
-        <v>2.486029720446764</v>
+        <v>2.986071917598713</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1021743527540411</v>
+        <v>0.1227257916300524</v>
       </c>
       <c r="J58" t="n">
         <v>158.4722608607674</v>
       </c>
       <c r="K58" t="n">
-        <v>134.4011905309047</v>
+        <v>137.8864411066156</v>
       </c>
       <c r="L58" t="n">
-        <v>1.963797120224555</v>
+        <v>1.903149984720945</v>
       </c>
       <c r="M58" t="n">
-        <v>0.08071090142202128</v>
+        <v>0.0782183399833936</v>
       </c>
       <c r="N58" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O58" t="n">
-        <v>173.7396733637671</v>
+        <v>175.1534984994845</v>
       </c>
       <c r="P58" t="n">
-        <v>42.86137514228709</v>
+        <v>46.77552546707687</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.761577195675812</v>
+        <v>1.922446461528975</v>
       </c>
       <c r="R58" t="n">
         <v>183.1273067581348</v>
       </c>
       <c r="S58" t="n">
-        <v>173.988426541041</v>
+        <v>175.5349105795317</v>
       </c>
       <c r="T58" t="n">
-        <v>47.51666666666667</v>
+        <v>57.84375</v>
       </c>
       <c r="U58" t="n">
-        <v>1.952906926962925</v>
+        <v>2.377343950680709</v>
       </c>
       <c r="V58" t="n">
         <v>197.6615055783608</v>
       </c>
       <c r="W58" t="n">
-        <v>85.12382338909936</v>
+        <v>90.40881674383272</v>
       </c>
       <c r="X58" t="n">
-        <v>1.284006266668031</v>
+        <v>1.726994175567854</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.05277189896400845</v>
+        <v>0.07097844030075948</v>
       </c>
       <c r="Z58" t="n">
         <v>111.9755139895278</v>
@@ -6422,11 +6438,11 @@
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>85.12382338909936</v>
+        <v>90.40881674383272</v>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=85.12% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=90.41% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6450,67 +6466,67 @@
         <v>2026</v>
       </c>
       <c r="E59" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F59" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G59" t="n">
-        <v>199.5971905979486</v>
+        <v>199.6183910927934</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3789187982929585</v>
+        <v>0.4177363733996486</v>
       </c>
       <c r="I59" t="n">
-        <v>0.00508189503159039</v>
+        <v>0.005602499559425296</v>
       </c>
       <c r="J59" t="n">
         <v>163.442478475025</v>
       </c>
       <c r="K59" t="n">
-        <v>193.6239631122541</v>
+        <v>193.8057320100581</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3692266830685438</v>
+        <v>0.4093446064569507</v>
       </c>
       <c r="M59" t="n">
-        <v>0.00495190857426379</v>
+        <v>0.005489952810822474</v>
       </c>
       <c r="N59" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O59" t="n">
-        <v>180.0693359196252</v>
+        <v>181.3446228437309</v>
       </c>
       <c r="P59" t="n">
-        <v>38.93333333333333</v>
+        <v>65.52035332088174</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.5221570271025425</v>
+        <v>0.8787306396765363</v>
       </c>
       <c r="R59" t="n">
         <v>198.2516520479188</v>
       </c>
       <c r="S59" t="n">
-        <v>180.0693359196252</v>
+        <v>181.3667111748073</v>
       </c>
       <c r="T59" t="n">
-        <v>38.93333333333333</v>
+        <v>76.515625</v>
       </c>
       <c r="U59" t="n">
-        <v>0.5221570271025425</v>
+        <v>1.026194467728416</v>
       </c>
       <c r="V59" t="n">
         <v>199.2894660635261</v>
       </c>
       <c r="W59" t="n">
-        <v>173.3128205112955</v>
+        <v>173.3546117654647</v>
       </c>
       <c r="X59" t="n">
-        <v>1.359807121174114</v>
+        <v>1.999510201671832</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.01823714496126222</v>
+        <v>0.02681656599056942</v>
       </c>
       <c r="Z59" t="n">
         <v>167.6265476269683</v>
@@ -6526,11 +6542,11 @@
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>173.3128205112955</v>
+        <v>173.3546117654647</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=173.31% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=173.35% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6570,7 @@
         <v>2026</v>
       </c>
       <c r="E60" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F60" t="n">
         <v>9</v>
@@ -6563,58 +6579,58 @@
         <v>198.0292156265697</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3093871613327322</v>
+        <v>0.2900504637494364</v>
       </c>
       <c r="I60" t="n">
-        <v>0.007833825892267313</v>
+        <v>0.007344211774000606</v>
       </c>
       <c r="J60" t="n">
         <v>179.6544870721095</v>
       </c>
       <c r="K60" t="n">
-        <v>196.702728441294</v>
+        <v>196.9088079137131</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2820001549430792</v>
+        <v>0.265203613216266</v>
       </c>
       <c r="M60" t="n">
-        <v>0.007140374234988555</v>
+        <v>0.006715078036810026</v>
       </c>
       <c r="N60" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O60" t="n">
-        <v>177.1128125605738</v>
+        <v>178.8733654405296</v>
       </c>
       <c r="P60" t="n">
-        <v>19.1</v>
+        <v>29.65671401127989</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.483620826080076</v>
+        <v>0.7509217030866883</v>
       </c>
       <c r="R60" t="n">
         <v>197.6157031839507</v>
       </c>
       <c r="S60" t="n">
-        <v>177.1128125605738</v>
+        <v>178.8733654405296</v>
       </c>
       <c r="T60" t="n">
-        <v>19.1</v>
+        <v>38.34375</v>
       </c>
       <c r="U60" t="n">
-        <v>0.483620826080076</v>
+        <v>0.9708814685868018</v>
       </c>
       <c r="V60" t="n">
         <v>199.0965028052728</v>
       </c>
       <c r="W60" t="n">
-        <v>179.0063969665014</v>
+        <v>180.318497156095</v>
       </c>
       <c r="X60" t="n">
-        <v>0.555374994757333</v>
+        <v>0.7867699396364152</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.01406235150517064</v>
+        <v>0.0199213784367505</v>
       </c>
       <c r="Z60" t="n">
         <v>167.0169829765832</v>
@@ -6656,67 +6672,67 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61" t="n">
-        <v>199.9531681019307</v>
+        <v>199.9557698740456</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0805738505895332</v>
+        <v>0.1380379849276874</v>
       </c>
       <c r="I61" t="n">
-        <v>0.001817540687202215</v>
+        <v>0.003113785082254333</v>
       </c>
       <c r="J61" t="n">
         <v>178.3754768379913</v>
       </c>
       <c r="K61" t="n">
-        <v>197.8439193479396</v>
+        <v>197.53129366247</v>
       </c>
       <c r="L61" t="n">
-        <v>0.1444126059750072</v>
+        <v>0.1978118742010364</v>
       </c>
       <c r="M61" t="n">
-        <v>0.003257580284224045</v>
+        <v>0.004462131661097676</v>
       </c>
       <c r="N61" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O61" t="n">
-        <v>188.1818181818182</v>
+        <v>189.0011586762996</v>
       </c>
       <c r="P61" t="n">
-        <v>19.98333333333333</v>
+        <v>30.77498888126861</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4507730626439213</v>
+        <v>0.6942053039620723</v>
       </c>
       <c r="R61" t="n">
         <v>198.3770115307477</v>
       </c>
       <c r="S61" t="n">
-        <v>188.1818181818182</v>
+        <v>189.0865384615385</v>
       </c>
       <c r="T61" t="n">
-        <v>19.98333333333333</v>
+        <v>38.3125</v>
       </c>
       <c r="U61" t="n">
-        <v>0.4507730626439213</v>
+        <v>0.8642323417453829</v>
       </c>
       <c r="V61" t="n">
         <v>199.3694289811982</v>
       </c>
       <c r="W61" t="n">
-        <v>192.8005738357945</v>
+        <v>190.0027846868423</v>
       </c>
       <c r="X61" t="n">
-        <v>0.7061909943580195</v>
+        <v>0.922355550152536</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.01592986875754732</v>
+        <v>0.02080599013455601</v>
       </c>
       <c r="Z61" t="n">
         <v>167.1297521794813</v>
@@ -6734,7 +6750,7 @@
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>Prophet: serie casi-cero (total 2 casos), menor MAE real</t>
+          <t>Prophet: serie casi-cero (total 4 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -6758,67 +6774,67 @@
         <v>2026</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F62" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G62" t="n">
-        <v>114.0814773305413</v>
+        <v>112.0276469608052</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9539496620132599</v>
+        <v>1.048434624162874</v>
       </c>
       <c r="I62" t="n">
-        <v>0.02864982560715562</v>
+        <v>0.03148747815411729</v>
       </c>
       <c r="J62" t="n">
         <v>51.86246745886869</v>
       </c>
       <c r="K62" t="n">
-        <v>138.5434288302061</v>
+        <v>139.0458749392876</v>
       </c>
       <c r="L62" t="n">
-        <v>5.143253855969866</v>
+        <v>5.89739287299443</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1544665634829054</v>
+        <v>0.177115506274821</v>
       </c>
       <c r="N62" t="n">
         <v>109.609711216533</v>
       </c>
       <c r="O62" t="n">
-        <v>182.7789372555233</v>
+        <v>183.3545624929642</v>
       </c>
       <c r="P62" t="n">
-        <v>65.25866986829126</v>
+        <v>71.58449211546866</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.9599037407652</v>
+        <v>2.149886201496947</v>
       </c>
       <c r="R62" t="n">
         <v>187.6026725565334</v>
       </c>
       <c r="S62" t="n">
-        <v>183.2056271741027</v>
+        <v>183.9193664230324</v>
       </c>
       <c r="T62" t="n">
-        <v>97.39562605025814</v>
+        <v>107.0404853518796</v>
       </c>
       <c r="U62" t="n">
-        <v>2.925068074714463</v>
+        <v>3.214730672229137</v>
       </c>
       <c r="V62" t="n">
         <v>188.4656733609786</v>
       </c>
       <c r="W62" t="n">
-        <v>135.8519961168652</v>
+        <v>138.701881557224</v>
       </c>
       <c r="X62" t="n">
-        <v>9.46436992033137</v>
+        <v>12.96039795020545</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.2842419872835324</v>
+        <v>0.3892376672046686</v>
       </c>
       <c r="Z62" t="n">
         <v>127.8730185036105</v>
@@ -6834,11 +6850,11 @@
         </is>
       </c>
       <c r="AC62" t="n">
-        <v>114.0814773305413</v>
+        <v>112.0276469608052</v>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=114.08% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=112.03% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6862,67 +6878,67 @@
         <v>2026</v>
       </c>
       <c r="E63" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F63" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G63" t="n">
-        <v>145.6703907877284</v>
+        <v>137.4897340479839</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6572830526929875</v>
+        <v>0.6261928653586925</v>
       </c>
       <c r="I63" t="n">
-        <v>0.04286337413119136</v>
+        <v>0.040835890954714</v>
       </c>
       <c r="J63" t="n">
         <v>69.84803023883232</v>
       </c>
       <c r="K63" t="n">
-        <v>160.5300534379983</v>
+        <v>161.0056677453144</v>
       </c>
       <c r="L63" t="n">
-        <v>0.8949442505513538</v>
+        <v>1.542783037871672</v>
       </c>
       <c r="M63" t="n">
-        <v>0.05836196457640783</v>
+        <v>0.1006094501974598</v>
       </c>
       <c r="N63" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O63" t="n">
-        <v>182.3612136565039</v>
+        <v>182.9184438353458</v>
       </c>
       <c r="P63" t="n">
-        <v>19.08095021402942</v>
+        <v>20.62941223555889</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.244325263600859</v>
+        <v>1.345305057138546</v>
       </c>
       <c r="R63" t="n">
         <v>179.6068984245533</v>
       </c>
       <c r="S63" t="n">
-        <v>183.8520986065637</v>
+        <v>184.6139254837163</v>
       </c>
       <c r="T63" t="n">
-        <v>36.48551160183993</v>
+        <v>40.39541730357679</v>
       </c>
       <c r="U63" t="n">
-        <v>2.379328247929239</v>
+        <v>2.63430477626749</v>
       </c>
       <c r="V63" t="n">
         <v>186.3893216158546</v>
       </c>
       <c r="W63" t="n">
-        <v>148.7792654729243</v>
+        <v>151.3091756185055</v>
       </c>
       <c r="X63" t="n">
-        <v>4.435610872164337</v>
+        <v>6.364956692841541</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.2892593191547968</v>
+        <v>0.4150776730607893</v>
       </c>
       <c r="Z63" t="n">
         <v>131.8859677830883</v>
@@ -6938,11 +6954,11 @@
         </is>
       </c>
       <c r="AC63" t="n">
-        <v>145.6703907877284</v>
+        <v>137.4897340479839</v>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=145.67% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=137.49% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -6966,67 +6982,67 @@
         <v>2026</v>
       </c>
       <c r="E64" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F64" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G64" t="n">
-        <v>135.4248706491216</v>
+        <v>134.6943660914244</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8779678022912319</v>
+        <v>0.9726789437395068</v>
       </c>
       <c r="I64" t="n">
-        <v>0.03944260799286736</v>
+        <v>0.04369749571762491</v>
       </c>
       <c r="J64" t="n">
         <v>72.92360982323459</v>
       </c>
       <c r="K64" t="n">
-        <v>160.2316722114404</v>
+        <v>159.9991599553016</v>
       </c>
       <c r="L64" t="n">
-        <v>3.436662129766569</v>
+        <v>4.079641808887035</v>
       </c>
       <c r="M64" t="n">
-        <v>0.1543916722624319</v>
+        <v>0.183277464389141</v>
       </c>
       <c r="N64" t="n">
         <v>109.7635513825217</v>
       </c>
       <c r="O64" t="n">
-        <v>183.5148640295954</v>
+        <v>183.9600228832853</v>
       </c>
       <c r="P64" t="n">
-        <v>39.503279554723</v>
+        <v>43.26893782571533</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.774680535941508</v>
+        <v>1.943852324052914</v>
       </c>
       <c r="R64" t="n">
         <v>188.9515900641726</v>
       </c>
       <c r="S64" t="n">
-        <v>183.8609121554279</v>
+        <v>184.4702441233494</v>
       </c>
       <c r="T64" t="n">
-        <v>63.45549192010526</v>
+        <v>68.66139867509867</v>
       </c>
       <c r="U64" t="n">
-        <v>2.850731070396418</v>
+        <v>3.084605864948978</v>
       </c>
       <c r="V64" t="n">
         <v>191.0006997623111</v>
       </c>
       <c r="W64" t="n">
-        <v>152.6880272401768</v>
+        <v>154.3523621928871</v>
       </c>
       <c r="X64" t="n">
-        <v>6.439831266841253</v>
+        <v>8.483185927404698</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.2893087189932895</v>
+        <v>0.3811062047970663</v>
       </c>
       <c r="Z64" t="n">
         <v>132.574641557417</v>
@@ -7042,11 +7058,11 @@
         </is>
       </c>
       <c r="AC64" t="n">
-        <v>135.4248706491216</v>
+        <v>134.6943660914244</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=135.42% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=134.69% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -7070,67 +7086,67 @@
         <v>2026</v>
       </c>
       <c r="E65" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F65" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G65" t="n">
-        <v>142.2404520386731</v>
+        <v>144.1491826136094</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9302240774001294</v>
+        <v>1.030011444089569</v>
       </c>
       <c r="I65" t="n">
-        <v>0.02429973100147277</v>
+        <v>0.02690642139662549</v>
       </c>
       <c r="J65" t="n">
         <v>124.1398173354868</v>
       </c>
       <c r="K65" t="n">
-        <v>151.7073283857741</v>
+        <v>148.7937652662132</v>
       </c>
       <c r="L65" t="n">
-        <v>1.071747818441324</v>
+        <v>1.035276129991761</v>
       </c>
       <c r="M65" t="n">
-        <v>0.02799667770622234</v>
+        <v>0.02704394788549906</v>
       </c>
       <c r="N65" t="n">
         <v>137.6406301580537</v>
       </c>
       <c r="O65" t="n">
-        <v>191.3946073876266</v>
+        <v>191.5799950902491</v>
       </c>
       <c r="P65" t="n">
-        <v>57.64655096611156</v>
+        <v>64.46886170886663</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.50586908646169</v>
+        <v>1.68408455076223</v>
       </c>
       <c r="R65" t="n">
         <v>183.1533465531335</v>
       </c>
       <c r="S65" t="n">
-        <v>191.8218723809736</v>
+        <v>192.1645417453029</v>
       </c>
       <c r="T65" t="n">
-        <v>74.69815431704413</v>
+        <v>90.96701967222887</v>
       </c>
       <c r="U65" t="n">
-        <v>1.951298725016663</v>
+        <v>2.376281330213326</v>
       </c>
       <c r="V65" t="n">
         <v>191.9303948964172</v>
       </c>
       <c r="W65" t="n">
-        <v>166.2596534933332</v>
+        <v>167.7347244484208</v>
       </c>
       <c r="X65" t="n">
-        <v>14.1171104545942</v>
+        <v>18.80015544443618</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.3687734975893995</v>
+        <v>0.4911061014056798</v>
       </c>
       <c r="Z65" t="n">
         <v>113.9712651292745</v>
@@ -7146,11 +7162,11 @@
         </is>
       </c>
       <c r="AC65" t="n">
-        <v>142.2404520386731</v>
+        <v>144.1491826136094</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=142.24% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=144.15% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -7174,67 +7190,67 @@
         <v>2026</v>
       </c>
       <c r="E66" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G66" t="n">
-        <v>179.0102200549941</v>
+        <v>180.3220813015569</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5707652943023513</v>
+        <v>0.6289925812480679</v>
       </c>
       <c r="I66" t="n">
-        <v>0.0269666165918725</v>
+        <v>0.0297176474235024</v>
       </c>
       <c r="J66" t="n">
         <v>146.9871894171194</v>
       </c>
       <c r="K66" t="n">
-        <v>159.7628188702215</v>
+        <v>158.1636420050805</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5972460506798528</v>
+        <v>0.6231364507384278</v>
       </c>
       <c r="M66" t="n">
-        <v>0.02821773751920167</v>
+        <v>0.02944096622416904</v>
       </c>
       <c r="N66" t="n">
         <v>79.54507935933471</v>
       </c>
       <c r="O66" t="n">
-        <v>192.3239464940251</v>
+        <v>192.3988707469497</v>
       </c>
       <c r="P66" t="n">
-        <v>27.74886181250367</v>
+        <v>31.38577893091625</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.311034368817536</v>
+        <v>1.482865681070899</v>
       </c>
       <c r="R66" t="n">
         <v>185.4205866195275</v>
       </c>
       <c r="S66" t="n">
-        <v>192.564066052336</v>
+        <v>192.7973304425836</v>
       </c>
       <c r="T66" t="n">
-        <v>32.496373557589</v>
+        <v>39.51222521023968</v>
       </c>
       <c r="U66" t="n">
-        <v>1.535337300816253</v>
+        <v>1.866811171899705</v>
       </c>
       <c r="V66" t="n">
         <v>192.190104304547</v>
       </c>
       <c r="W66" t="n">
-        <v>175.0461202354696</v>
+        <v>175.8699762732591</v>
       </c>
       <c r="X66" t="n">
-        <v>5.914462434333503</v>
+        <v>8.243516248779105</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.2794371739239216</v>
+        <v>0.3894766277291177</v>
       </c>
       <c r="Z66" t="n">
         <v>118.44057480835</v>
@@ -7250,11 +7266,11 @@
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>159.7628188702215</v>
+        <v>158.1636420050805</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=159.76% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=158.16% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -7278,67 +7294,67 @@
         <v>2026</v>
       </c>
       <c r="E67" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F67" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G67" t="n">
-        <v>178.8082242945412</v>
+        <v>178.5278959125725</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5883220185903816</v>
+        <v>0.6154206092991575</v>
       </c>
       <c r="I67" t="n">
-        <v>0.02155272420708896</v>
+        <v>0.02254546021473731</v>
       </c>
       <c r="J67" t="n">
         <v>137.6516466078508</v>
       </c>
       <c r="K67" t="n">
-        <v>182.131586053904</v>
+        <v>178.7139699699126</v>
       </c>
       <c r="L67" t="n">
-        <v>0.6788572770473629</v>
+        <v>0.7490869786137782</v>
       </c>
       <c r="M67" t="n">
-        <v>0.02486941369835789</v>
+        <v>0.02744222474601133</v>
       </c>
       <c r="N67" t="n">
         <v>151.2037021887013</v>
       </c>
       <c r="O67" t="n">
-        <v>192.8902232559284</v>
+        <v>192.846406966684</v>
       </c>
       <c r="P67" t="n">
-        <v>20.48462416805092</v>
+        <v>22.19457422136068</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.7504384354638001</v>
+        <v>0.8130811391912328</v>
       </c>
       <c r="R67" t="n">
         <v>175.6951253506204</v>
       </c>
       <c r="S67" t="n">
-        <v>194.743138152032</v>
+        <v>194.9519237278529</v>
       </c>
       <c r="T67" t="n">
-        <v>42.38960120891837</v>
+        <v>51.62263821031726</v>
       </c>
       <c r="U67" t="n">
-        <v>1.552910404905997</v>
+        <v>1.891155607017919</v>
       </c>
       <c r="V67" t="n">
         <v>191.2393501485975</v>
       </c>
       <c r="W67" t="n">
-        <v>182.8543417202187</v>
+        <v>183.4673551627698</v>
       </c>
       <c r="X67" t="n">
-        <v>8.53304155574738</v>
+        <v>11.19616563142592</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.3126014078808427</v>
+        <v>0.4101629080774235</v>
       </c>
       <c r="Z67" t="n">
         <v>116.630186356802</v>
@@ -7354,11 +7370,11 @@
         </is>
       </c>
       <c r="AC67" t="n">
-        <v>178.8082242945412</v>
+        <v>178.5278959125725</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=178.81% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=178.53% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -7382,7 +7398,7 @@
         <v>2026</v>
       </c>
       <c r="E68" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F68" t="n">
         <v>1</v>
@@ -7391,22 +7407,22 @@
         <v>199.988140539529</v>
       </c>
       <c r="H68" t="n">
-        <v>0.03885247091580103</v>
+        <v>0.03642419148356346</v>
       </c>
       <c r="I68" t="n">
-        <v>0.002019621620054634</v>
+        <v>0.00189339526880122</v>
       </c>
       <c r="J68" t="n">
         <v>183.5383709430125</v>
       </c>
       <c r="K68" t="n">
-        <v>199.8624421700836</v>
+        <v>199.8710395344533</v>
       </c>
       <c r="L68" t="n">
-        <v>0.04797058629323744</v>
+        <v>0.04577832686448341</v>
       </c>
       <c r="M68" t="n">
-        <v>0.002493597728043531</v>
+        <v>0.002379640122910119</v>
       </c>
       <c r="N68" t="n">
         <v>198.3312090033645</v>
@@ -7415,10 +7431,10 @@
         <v>200</v>
       </c>
       <c r="P68" t="n">
-        <v>14.65556081304576</v>
+        <v>17.83418036821299</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.7618225243948412</v>
+        <v>0.9270529106283554</v>
       </c>
       <c r="R68" t="n">
         <v>188.2784643365136</v>
@@ -7427,22 +7443,22 @@
         <v>200</v>
       </c>
       <c r="T68" t="n">
-        <v>15.88333333333333</v>
+        <v>26.1875</v>
       </c>
       <c r="U68" t="n">
-        <v>0.8256443578081004</v>
+        <v>1.36127355425601</v>
       </c>
       <c r="V68" t="n">
         <v>199.7672857698158</v>
       </c>
       <c r="W68" t="n">
-        <v>197.8992105364101</v>
+        <v>198.0305098778845</v>
       </c>
       <c r="X68" t="n">
-        <v>0.8889352246395691</v>
+        <v>1.298351877930445</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.04620845872070534</v>
+        <v>0.06749067591581263</v>
       </c>
       <c r="Z68" t="n">
         <v>177.2448922419183</v>
@@ -7484,7 +7500,7 @@
         <v>2026</v>
       </c>
       <c r="E69" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F69" t="n">
         <v>1</v>
@@ -7493,22 +7509,22 @@
         <v>198.1317768745953</v>
       </c>
       <c r="H69" t="n">
-        <v>0.05143359066946884</v>
+        <v>0.04821899125262703</v>
       </c>
       <c r="I69" t="n">
-        <v>0.006157407038619538</v>
+        <v>0.005772569098705818</v>
       </c>
       <c r="J69" t="n">
         <v>171.5447439761989</v>
       </c>
       <c r="K69" t="n">
-        <v>199.6119704644958</v>
+        <v>199.6362223104648</v>
       </c>
       <c r="L69" t="n">
-        <v>0.06330304403561769</v>
+        <v>0.06269083348061995</v>
       </c>
       <c r="M69" t="n">
-        <v>0.007578366663448433</v>
+        <v>0.007505075463448703</v>
       </c>
       <c r="N69" t="n">
         <v>194.4182830751776</v>
@@ -7517,10 +7533,10 @@
         <v>200</v>
       </c>
       <c r="P69" t="n">
-        <v>6.425606072522023</v>
+        <v>8.230428209974432</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.7692457699988954</v>
+        <v>0.9853112709284767</v>
       </c>
       <c r="R69" t="n">
         <v>190.8574288418282</v>
@@ -7529,22 +7545,22 @@
         <v>200</v>
       </c>
       <c r="T69" t="n">
-        <v>6.583333333333333</v>
+        <v>10.484375</v>
       </c>
       <c r="U69" t="n">
-        <v>0.7881281955356029</v>
+        <v>1.255144032921811</v>
       </c>
       <c r="V69" t="n">
         <v>199.6130972886749</v>
       </c>
       <c r="W69" t="n">
-        <v>198.9414820291657</v>
+        <v>199.0076394023429</v>
       </c>
       <c r="X69" t="n">
-        <v>0.5946076275643608</v>
+        <v>1.159145564811344</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.07118385365529198</v>
+        <v>0.1387678940290423</v>
       </c>
       <c r="Z69" t="n">
         <v>185.6695408532579</v>
@@ -7586,7 +7602,7 @@
         <v>2026</v>
       </c>
       <c r="E70" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -7595,10 +7611,10 @@
         <v>200</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01126688063797333</v>
+        <v>0.01056270059809999</v>
       </c>
       <c r="I70" t="n">
-        <v>0.0009289878392557239</v>
+        <v>0.0008709260993022412</v>
       </c>
       <c r="J70" t="n">
         <v>188.453973372859</v>
@@ -7607,10 +7623,10 @@
         <v>200</v>
       </c>
       <c r="L70" t="n">
-        <v>0.01610996399576582</v>
+        <v>0.01645922608223998</v>
       </c>
       <c r="M70" t="n">
-        <v>0.001328314475301484</v>
+        <v>0.001357112173748207</v>
       </c>
       <c r="N70" t="n">
         <v>198.9765474653765</v>
@@ -7619,10 +7635,10 @@
         <v>200</v>
       </c>
       <c r="P70" t="n">
-        <v>8.336310348202737</v>
+        <v>10.70399287863541</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.687353597378221</v>
+        <v>0.8825760683234556</v>
       </c>
       <c r="R70" t="n">
         <v>192.937344462188</v>
@@ -7631,10 +7647,10 @@
         <v>200</v>
       </c>
       <c r="T70" t="n">
-        <v>9.4</v>
+        <v>15.796875</v>
       </c>
       <c r="U70" t="n">
-        <v>0.775057974748776</v>
+        <v>1.302499355836125</v>
       </c>
       <c r="V70" t="n">
         <v>199.6974055100667</v>
@@ -7643,10 +7659,10 @@
         <v>200</v>
       </c>
       <c r="X70" t="n">
-        <v>0.5361441192751984</v>
+        <v>0.825117734035586</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.04420667821903208</v>
+        <v>0.06803341275222559</v>
       </c>
       <c r="Z70" t="n">
         <v>184.4638384017739</v>
@@ -7688,67 +7704,67 @@
         <v>2026</v>
       </c>
       <c r="E71" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F71" t="n">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="G71" t="n">
-        <v>63.86911921407565</v>
+        <v>61.04993932989751</v>
       </c>
       <c r="H71" t="n">
-        <v>3.930401904317618</v>
+        <v>3.805666185679715</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08970320300846145</v>
+        <v>0.08685637111600519</v>
       </c>
       <c r="J71" t="n">
         <v>143.4057585362926</v>
       </c>
       <c r="K71" t="n">
-        <v>170.7957427044227</v>
+        <v>167.0816442932022</v>
       </c>
       <c r="L71" t="n">
-        <v>5.917055135514486</v>
+        <v>6.011680752119631</v>
       </c>
       <c r="M71" t="n">
-        <v>0.1350444079141742</v>
+        <v>0.1372040397031797</v>
       </c>
       <c r="N71" t="n">
         <v>171.2174826415851</v>
       </c>
       <c r="O71" t="n">
-        <v>64.12956415789046</v>
+        <v>60.94761255412936</v>
       </c>
       <c r="P71" t="n">
-        <v>4.418139860418601</v>
+        <v>4.226440964878675</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.1008348017498005</v>
+        <v>0.09645967539841495</v>
       </c>
       <c r="R71" t="n">
         <v>65.78436567943845</v>
       </c>
       <c r="S71" t="n">
-        <v>192.1231665581343</v>
+        <v>192.6154686482509</v>
       </c>
       <c r="T71" t="n">
-        <v>6.449380078485197</v>
+        <v>6.702543823579873</v>
       </c>
       <c r="U71" t="n">
-        <v>0.147193611376882</v>
+        <v>0.1529715443652778</v>
       </c>
       <c r="V71" t="n">
         <v>185.267595267154</v>
       </c>
       <c r="W71" t="n">
-        <v>65.4660703942622</v>
+        <v>71.06273666386187</v>
       </c>
       <c r="X71" t="n">
-        <v>9.874659219574868</v>
+        <v>13.87136594424831</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.2253684437817529</v>
+        <v>0.3165849156379331</v>
       </c>
       <c r="Z71" t="n">
         <v>93.16202342284906</v>
@@ -7764,11 +7780,11 @@
         </is>
       </c>
       <c r="AC71" t="n">
-        <v>63.86911921407565</v>
+        <v>61.04993932989751</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=63.87% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=61.05% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -7792,67 +7808,67 @@
         <v>2026</v>
       </c>
       <c r="E72" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F72" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G72" t="n">
-        <v>84.2300798330179</v>
+        <v>81.50883063783806</v>
       </c>
       <c r="H72" t="n">
-        <v>2.063904478594651</v>
+        <v>2.0523155346466</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09352158498304845</v>
+        <v>0.09299645583218805</v>
       </c>
       <c r="J72" t="n">
         <v>151.0433307550491</v>
       </c>
       <c r="K72" t="n">
-        <v>76.94964840030202</v>
+        <v>75.15156760460241</v>
       </c>
       <c r="L72" t="n">
-        <v>1.530896185171238</v>
+        <v>1.665200740553375</v>
       </c>
       <c r="M72" t="n">
-        <v>0.0693694108262243</v>
+        <v>0.07545514542297931</v>
       </c>
       <c r="N72" t="n">
         <v>171.9287045593839</v>
       </c>
       <c r="O72" t="n">
-        <v>82.55723414430395</v>
+        <v>79.34090449087651</v>
       </c>
       <c r="P72" t="n">
-        <v>2.5233391310531</v>
+        <v>2.462943702158797</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.1143399209766344</v>
+        <v>0.1116032263793281</v>
       </c>
       <c r="R72" t="n">
         <v>96.15548417978732</v>
       </c>
       <c r="S72" t="n">
-        <v>175.6286648819022</v>
+        <v>177.3694745331949</v>
       </c>
       <c r="T72" t="n">
-        <v>2.95535790622643</v>
+        <v>3.114398037087278</v>
       </c>
       <c r="U72" t="n">
-        <v>0.1339159628989603</v>
+        <v>0.1411225392053142</v>
       </c>
       <c r="V72" t="n">
         <v>161.2927483340683</v>
       </c>
       <c r="W72" t="n">
-        <v>87.91613783087769</v>
+        <v>91.60683915529806</v>
       </c>
       <c r="X72" t="n">
-        <v>4.724833537931276</v>
+        <v>6.357504425637281</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.2140961104698397</v>
+        <v>0.2880772325409133</v>
       </c>
       <c r="Z72" t="n">
         <v>104.036396201453</v>
@@ -7868,11 +7884,11 @@
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>76.94964840030202</v>
+        <v>75.15156760460241</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>DeepAR: menor SMAPE real=76.95% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=75.15% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -7896,74 +7912,74 @@
         <v>2026</v>
       </c>
       <c r="E73" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F73" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G73" t="n">
-        <v>73.34183447667557</v>
+        <v>70.43329294744777</v>
       </c>
       <c r="H73" t="n">
-        <v>2.345163339846095</v>
+        <v>2.281964126293627</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1051053597690127</v>
+        <v>0.102272902018762</v>
       </c>
       <c r="J73" t="n">
         <v>148.5993365374143</v>
       </c>
       <c r="K73" t="n">
-        <v>135.079608707855</v>
+        <v>129.4960666025278</v>
       </c>
       <c r="L73" t="n">
-        <v>2.49182844205712</v>
+        <v>2.513426591694166</v>
       </c>
       <c r="M73" t="n">
-        <v>0.1116785856384143</v>
+        <v>0.112646569935873</v>
       </c>
       <c r="N73" t="n">
         <v>191.7880460732582</v>
       </c>
       <c r="O73" t="n">
-        <v>91.98855490686815</v>
+        <v>93.78510137924692</v>
       </c>
       <c r="P73" t="n">
-        <v>2.564648282527924</v>
+        <v>2.642118889838457</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.1149422199452291</v>
+        <v>0.1184142919815555</v>
       </c>
       <c r="R73" t="n">
         <v>105.84208545642</v>
       </c>
       <c r="S73" t="n">
-        <v>177.7374446620441</v>
+        <v>179.1288543706664</v>
       </c>
       <c r="T73" t="n">
-        <v>3.306114546349251</v>
+        <v>3.411982387202423</v>
       </c>
       <c r="U73" t="n">
-        <v>0.1481732009568292</v>
+        <v>0.1529179781379237</v>
       </c>
       <c r="V73" t="n">
         <v>173.6314937555617</v>
       </c>
       <c r="W73" t="n">
-        <v>68.71046704826695</v>
+        <v>74.94278059027945</v>
       </c>
       <c r="X73" t="n">
-        <v>4.902334720420154</v>
+        <v>8.085636312797877</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.2197124804670097</v>
+        <v>0.3623814593971038</v>
       </c>
       <c r="Z73" t="n">
         <v>104.3951484726403</v>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
@@ -7972,11 +7988,11 @@
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>68.71046704826695</v>
+        <v>70.43329294744777</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=68.71% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=70.43% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8000,67 +8016,67 @@
         <v>2026</v>
       </c>
       <c r="E74" t="n">
+        <v>32</v>
+      </c>
+      <c r="F74" t="n">
         <v>30</v>
       </c>
-      <c r="F74" t="n">
-        <v>18</v>
-      </c>
       <c r="G74" t="n">
-        <v>175.5501426823518</v>
+        <v>175.082480035204</v>
       </c>
       <c r="H74" t="n">
-        <v>8.845154474561605</v>
+        <v>12.1064701823642</v>
       </c>
       <c r="I74" t="n">
-        <v>0.272867003939045</v>
+        <v>0.3734763769745054</v>
       </c>
       <c r="J74" t="n">
         <v>148.9425712788151</v>
       </c>
       <c r="K74" t="n">
-        <v>190.4324624461753</v>
+        <v>190.8597196377525</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5817667011906837</v>
+        <v>0.9179878550786635</v>
       </c>
       <c r="M74" t="n">
-        <v>0.01794710733452413</v>
+        <v>0.02831930141956737</v>
       </c>
       <c r="N74" t="n">
         <v>144.0733541161664</v>
       </c>
       <c r="O74" t="n">
-        <v>192.0388761917751</v>
+        <v>191.2584534189687</v>
       </c>
       <c r="P74" t="n">
-        <v>44.0625374726764</v>
+        <v>47.7858149109922</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.359299333968616</v>
+        <v>1.474159912418539</v>
       </c>
       <c r="R74" t="n">
         <v>166.1309749781026</v>
       </c>
       <c r="S74" t="n">
-        <v>192.2280762126967</v>
+        <v>191.8217565337915</v>
       </c>
       <c r="T74" t="n">
-        <v>50.7</v>
+        <v>57</v>
       </c>
       <c r="U74" t="n">
-        <v>1.564060541791189</v>
+        <v>1.758411260001928</v>
       </c>
       <c r="V74" t="n">
         <v>193.1141809259393</v>
       </c>
       <c r="W74" t="n">
-        <v>165.1498296698461</v>
+        <v>165.7944919001347</v>
       </c>
       <c r="X74" t="n">
-        <v>4.445256260689707</v>
+        <v>9.384091944303988</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.1371331344279096</v>
+        <v>0.2894928585922372</v>
       </c>
       <c r="Z74" t="n">
         <v>113.155914904339</v>
@@ -8076,11 +8092,11 @@
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>165.1498296698461</v>
+        <v>165.7944919001347</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=165.15% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=165.79% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8104,85 +8120,87 @@
         <v>2026</v>
       </c>
       <c r="E75" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G75" t="n">
-        <v>174.9146593701546</v>
+        <v>174.6651846049306</v>
       </c>
       <c r="H75" t="n">
-        <v>2.877833751567339</v>
+        <v>3.764294836038152</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1732330324495012</v>
+        <v>0.2265941210557202</v>
       </c>
       <c r="J75" t="n">
         <v>157.2380343536269</v>
       </c>
       <c r="K75" t="n">
-        <v>197.7573242429261</v>
+        <v>197.8186519076857</v>
       </c>
       <c r="L75" t="n">
-        <v>0.2925073377788802</v>
+        <v>0.3677336217372682</v>
       </c>
       <c r="M75" t="n">
-        <v>0.01760766517856314</v>
+        <v>0.02213595917154361</v>
       </c>
       <c r="N75" t="n">
         <v>158.6014909691414</v>
       </c>
       <c r="O75" t="n">
-        <v>191.8733040331857</v>
+        <v>191.5738865648715</v>
       </c>
       <c r="P75" t="n">
-        <v>18.28361475170498</v>
+        <v>19.81323583499699</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.100593815001052</v>
+        <v>1.19267032866799</v>
       </c>
       <c r="R75" t="n">
         <v>163.9609846286252</v>
       </c>
       <c r="S75" t="n">
-        <v>192.0144757786478</v>
+        <v>191.9077167198138</v>
       </c>
       <c r="T75" t="n">
-        <v>21.43333333333333</v>
+        <v>23.703125</v>
       </c>
       <c r="U75" t="n">
-        <v>1.290193127664911</v>
+        <v>1.426824680210685</v>
       </c>
       <c r="V75" t="n">
         <v>193.2892416279341</v>
       </c>
       <c r="W75" t="n">
-        <v>170.9367193902676</v>
+        <v>171.8351725729502</v>
       </c>
       <c r="X75" t="n">
-        <v>1.882139849337658</v>
+        <v>4.084616644927537</v>
       </c>
       <c r="Y75" t="n">
-        <v>0.1132966049262699</v>
+        <v>0.2458760960076772</v>
       </c>
       <c r="Z75" t="n">
         <v>110.9447640026735</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>DeepAR</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>mae_real_casi_cero</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr"/>
+          <t>smape_real</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>174.6651846049306</v>
+      </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 8 casos), menor MAE real</t>
+          <t>Prophet: menor SMAPE real=174.67% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8206,67 +8224,67 @@
         <v>2026</v>
       </c>
       <c r="E76" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G76" t="n">
-        <v>179.2850643951095</v>
+        <v>177.7064817183663</v>
       </c>
       <c r="H76" t="n">
-        <v>4.871315095367873</v>
+        <v>6.382422663460829</v>
       </c>
       <c r="I76" t="n">
-        <v>0.223936335371027</v>
+        <v>0.2934025646182252</v>
       </c>
       <c r="J76" t="n">
         <v>154.9841830576604</v>
       </c>
       <c r="K76" t="n">
-        <v>196.6399996091033</v>
+        <v>196.8124215958167</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3308675294953379</v>
+        <v>0.5910765546956146</v>
       </c>
       <c r="M76" t="n">
-        <v>0.01521011484535384</v>
+        <v>0.02717202952199349</v>
       </c>
       <c r="N76" t="n">
         <v>166.7038660732646</v>
       </c>
       <c r="O76" t="n">
-        <v>191.3471645075774</v>
+        <v>190.0211379564913</v>
       </c>
       <c r="P76" t="n">
-        <v>22.81962161012898</v>
+        <v>24.54331787140107</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.049027282752661</v>
+        <v>1.128266300653404</v>
       </c>
       <c r="R76" t="n">
         <v>168.5329779328607</v>
       </c>
       <c r="S76" t="n">
-        <v>191.8273248164073</v>
+        <v>191.3109969991908</v>
       </c>
       <c r="T76" t="n">
-        <v>29.91666666666667</v>
+        <v>34.140625</v>
       </c>
       <c r="U76" t="n">
-        <v>1.375281329310923</v>
+        <v>1.569458411147824</v>
       </c>
       <c r="V76" t="n">
         <v>192.8448970866968</v>
       </c>
       <c r="W76" t="n">
-        <v>174.724326480066</v>
+        <v>174.0296588981325</v>
       </c>
       <c r="X76" t="n">
-        <v>2.262001641210584</v>
+        <v>4.570307091560869</v>
       </c>
       <c r="Y76" t="n">
-        <v>0.1039851350649888</v>
+        <v>0.2100988750609795</v>
       </c>
       <c r="Z76" t="n">
         <v>118.0223455785753</v>
@@ -8282,11 +8300,11 @@
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>174.724326480066</v>
+        <v>174.0296588981325</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=174.72% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=174.03% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8310,67 +8328,67 @@
         <v>2026</v>
       </c>
       <c r="E77" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F77" t="n">
-        <v>454</v>
+        <v>482</v>
       </c>
       <c r="G77" t="n">
-        <v>44.06787720600779</v>
+        <v>42.90418713283447</v>
       </c>
       <c r="H77" t="n">
-        <v>5.464696874230028</v>
+        <v>5.390500899095483</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1510889061477111</v>
+        <v>0.1490375226983372</v>
       </c>
       <c r="J77" t="n">
         <v>77.76772218573589</v>
       </c>
       <c r="K77" t="n">
-        <v>60.79172681990623</v>
+        <v>64.1012348621156</v>
       </c>
       <c r="L77" t="n">
-        <v>11.07972940847461</v>
+        <v>12.67496252870285</v>
       </c>
       <c r="M77" t="n">
-        <v>0.3063343192251491</v>
+        <v>0.3504396068070599</v>
       </c>
       <c r="N77" t="n">
         <v>110.3330967959057</v>
       </c>
       <c r="O77" t="n">
-        <v>69.57263625479605</v>
+        <v>73.5558705878726</v>
       </c>
       <c r="P77" t="n">
-        <v>15</v>
+        <v>17.546875</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.414722654224987</v>
+        <v>0.4851391048902712</v>
       </c>
       <c r="R77" t="n">
         <v>117.4841503463031</v>
       </c>
       <c r="S77" t="n">
-        <v>69.57263625479605</v>
+        <v>73.5558705878726</v>
       </c>
       <c r="T77" t="n">
-        <v>15</v>
+        <v>17.546875</v>
       </c>
       <c r="U77" t="n">
-        <v>0.414722654224987</v>
+        <v>0.4851391048902712</v>
       </c>
       <c r="V77" t="n">
         <v>138.4032392925817</v>
       </c>
       <c r="W77" t="n">
-        <v>42.01107382340651</v>
+        <v>44.31486715005466</v>
       </c>
       <c r="X77" t="n">
-        <v>6.64316396424577</v>
+        <v>7.361365328176242</v>
       </c>
       <c r="Y77" t="n">
-        <v>0.1836713727802528</v>
+        <v>0.2035283311747362</v>
       </c>
       <c r="Z77" t="n">
         <v>118.3894561520081</v>
@@ -8386,11 +8404,11 @@
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>44.06787720600779</v>
+        <v>42.90418713283447</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=44.07% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=42.90% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8414,67 +8432,67 @@
         <v>2026</v>
       </c>
       <c r="E78" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F78" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G78" t="n">
-        <v>46.76775401331676</v>
+        <v>44.73986115423827</v>
       </c>
       <c r="H78" t="n">
-        <v>2.942152392863164</v>
+        <v>2.821864190083981</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1570980753739717</v>
+        <v>0.1506752112175662</v>
       </c>
       <c r="J78" t="n">
         <v>103.5437500854655</v>
       </c>
       <c r="K78" t="n">
-        <v>62.71186936371598</v>
+        <v>62.48501119498336</v>
       </c>
       <c r="L78" t="n">
-        <v>4.695318087252637</v>
+        <v>4.759934651212013</v>
       </c>
       <c r="M78" t="n">
-        <v>0.2507094590223334</v>
+        <v>0.2541597010491981</v>
       </c>
       <c r="N78" t="n">
         <v>115.3631910942854</v>
       </c>
       <c r="O78" t="n">
-        <v>106.0980075956651</v>
+        <v>105.8217066656347</v>
       </c>
       <c r="P78" t="n">
-        <v>4.914375861734152</v>
+        <v>4.937555626267567</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.2624061865100832</v>
+        <v>0.2636438845996365</v>
       </c>
       <c r="R78" t="n">
         <v>128.5059105773902</v>
       </c>
       <c r="S78" t="n">
-        <v>59.71744169672258</v>
+        <v>58.45812598312033</v>
       </c>
       <c r="T78" t="n">
-        <v>4.502415400067723</v>
+        <v>4.410122753192395</v>
       </c>
       <c r="U78" t="n">
-        <v>0.2404092988522729</v>
+        <v>0.235481274991084</v>
       </c>
       <c r="V78" t="n">
         <v>82.9912432467173</v>
       </c>
       <c r="W78" t="n">
-        <v>38.66884599042365</v>
+        <v>40.00768563873216</v>
       </c>
       <c r="X78" t="n">
-        <v>2.955632096327329</v>
+        <v>3.136279762923714</v>
       </c>
       <c r="Y78" t="n">
-        <v>0.1578178326088345</v>
+        <v>0.1674636282555629</v>
       </c>
       <c r="Z78" t="n">
         <v>124.390269119479</v>
@@ -8490,11 +8508,11 @@
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>38.66884599042365</v>
+        <v>40.00768563873216</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=38.67% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=40.01% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8518,74 +8536,74 @@
         <v>2026</v>
       </c>
       <c r="E79" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F79" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="G79" t="n">
-        <v>50.64369544820199</v>
+        <v>50.6975623721255</v>
       </c>
       <c r="H79" t="n">
-        <v>3.132500146257386</v>
+        <v>3.233425470158111</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1408260813153082</v>
+        <v>0.1453633254355993</v>
       </c>
       <c r="J79" t="n">
         <v>102.5016657415887</v>
       </c>
       <c r="K79" t="n">
-        <v>64.93379962831473</v>
+        <v>69.91554069396271</v>
       </c>
       <c r="L79" t="n">
-        <v>6.210467202274184</v>
+        <v>7.966684079353604</v>
       </c>
       <c r="M79" t="n">
-        <v>0.2792005485709103</v>
+        <v>0.3581538220557957</v>
       </c>
       <c r="N79" t="n">
         <v>114.5134591086363</v>
       </c>
       <c r="O79" t="n">
-        <v>72.37494476991608</v>
+        <v>76.66108065593039</v>
       </c>
       <c r="P79" t="n">
-        <v>8.483333333333333</v>
+        <v>9.890625</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.3813805376041959</v>
+        <v>0.4446473728575443</v>
       </c>
       <c r="R79" t="n">
         <v>131.5261264594907</v>
       </c>
       <c r="S79" t="n">
-        <v>72.37494476991608</v>
+        <v>76.66108065593039</v>
       </c>
       <c r="T79" t="n">
-        <v>8.483333333333333</v>
+        <v>9.890625</v>
       </c>
       <c r="U79" t="n">
-        <v>0.3813805376041959</v>
+        <v>0.4446473728575443</v>
       </c>
       <c r="V79" t="n">
         <v>148.0195847609927</v>
       </c>
       <c r="W79" t="n">
-        <v>48.20324713186123</v>
+        <v>51.54765843112494</v>
       </c>
       <c r="X79" t="n">
-        <v>4.128318268512884</v>
+        <v>4.724136012620699</v>
       </c>
       <c r="Y79" t="n">
-        <v>0.1855945273846759</v>
+        <v>0.2123803770776375</v>
       </c>
       <c r="Z79" t="n">
         <v>120.3982350383182</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>NBGLM</t>
+          <t>Prophet</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
@@ -8594,11 +8612,11 @@
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>48.20324713186123</v>
+        <v>50.6975623721255</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=48.20% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=50.70% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8622,67 +8640,67 @@
         <v>2026</v>
       </c>
       <c r="E80" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F80" t="n">
-        <v>1005</v>
+        <v>1057</v>
       </c>
       <c r="G80" t="n">
-        <v>131.6224629997963</v>
+        <v>126.5102992597685</v>
       </c>
       <c r="H80" t="n">
-        <v>27.05441498034019</v>
+        <v>26.33108905478766</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8901308650739113</v>
+        <v>0.8663323563162708</v>
       </c>
       <c r="J80" t="n">
         <v>180.9937478063148</v>
       </c>
       <c r="K80" t="n">
-        <v>152.474693069763</v>
+        <v>155.1441581976109</v>
       </c>
       <c r="L80" t="n">
-        <v>28.22984007888106</v>
+        <v>28.0695708416215</v>
       </c>
       <c r="M80" t="n">
-        <v>0.9288041152829466</v>
+        <v>0.9235310167919885</v>
       </c>
       <c r="N80" t="n">
         <v>195.3549053278383</v>
       </c>
       <c r="O80" t="n">
-        <v>127.9110003655342</v>
+        <v>131.1155601605765</v>
       </c>
       <c r="P80" t="n">
-        <v>23.27241895198822</v>
+        <v>23.36110059916973</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.7656975184696927</v>
+        <v>0.768615277784733</v>
       </c>
       <c r="R80" t="n">
         <v>171.1146914183623</v>
       </c>
       <c r="S80" t="n">
-        <v>168.3914484230634</v>
+        <v>170.1180143846592</v>
       </c>
       <c r="T80" t="n">
-        <v>31.44763533020268</v>
+        <v>31.09569639899149</v>
       </c>
       <c r="U80" t="n">
-        <v>1.034674409383596</v>
+        <v>1.023095090240312</v>
       </c>
       <c r="V80" t="n">
         <v>172.7461511452186</v>
       </c>
       <c r="W80" t="n">
-        <v>54.81188710756886</v>
+        <v>55.51697718804227</v>
       </c>
       <c r="X80" t="n">
-        <v>26.25624373632104</v>
+        <v>25.48111739829556</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.8638698329860922</v>
+        <v>0.8383670128988874</v>
       </c>
       <c r="Z80" t="n">
         <v>175.912448276349</v>
@@ -8698,11 +8716,11 @@
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>54.81188710756886</v>
+        <v>55.51697718804227</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=54.81% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=55.52% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8726,67 +8744,67 @@
         <v>2026</v>
       </c>
       <c r="E81" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F81" t="n">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G81" t="n">
-        <v>121.0006886478078</v>
+        <v>117.6182078814882</v>
       </c>
       <c r="H81" t="n">
-        <v>11.9446466786775</v>
+        <v>11.80890883013778</v>
       </c>
       <c r="I81" t="n">
-        <v>0.7430573361541213</v>
+        <v>0.7346133020303444</v>
       </c>
       <c r="J81" t="n">
         <v>185.5191244575439</v>
       </c>
       <c r="K81" t="n">
-        <v>107.1807386438778</v>
+        <v>106.6755122354775</v>
       </c>
       <c r="L81" t="n">
-        <v>9.757829421331051</v>
+        <v>9.591669583527487</v>
       </c>
       <c r="M81" t="n">
-        <v>0.6070189375633624</v>
+        <v>0.5966824002194393</v>
       </c>
       <c r="N81" t="n">
         <v>199.4307199889832</v>
       </c>
       <c r="O81" t="n">
-        <v>158.7014436592695</v>
+        <v>158.9414113537469</v>
       </c>
       <c r="P81" t="n">
-        <v>13.05160442590713</v>
+        <v>12.78429606929421</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8119194044110193</v>
+        <v>0.7952905797383648</v>
       </c>
       <c r="R81" t="n">
         <v>169.7911563334158</v>
       </c>
       <c r="S81" t="n">
-        <v>152.9040114241883</v>
+        <v>153.3122146935787</v>
       </c>
       <c r="T81" t="n">
-        <v>13.72569787553653</v>
+        <v>13.43440265608159</v>
       </c>
       <c r="U81" t="n">
-        <v>0.8538536781049161</v>
+        <v>0.835732669118606</v>
       </c>
       <c r="V81" t="n">
         <v>163.1536185700502</v>
       </c>
       <c r="W81" t="n">
-        <v>59.45563258226454</v>
+        <v>61.06825885254703</v>
       </c>
       <c r="X81" t="n">
-        <v>8.624026131743031</v>
+        <v>8.490070115620881</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.5364868511193177</v>
+        <v>0.5281536619359802</v>
       </c>
       <c r="Z81" t="n">
         <v>172.1596497720207</v>
@@ -8802,11 +8820,11 @@
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>59.45563258226454</v>
+        <v>61.06825885254703</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=59.46% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=61.07% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8830,67 +8848,67 @@
         <v>2026</v>
       </c>
       <c r="E82" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F82" t="n">
-        <v>545</v>
+        <v>577</v>
       </c>
       <c r="G82" t="n">
-        <v>118.5148674970889</v>
+        <v>113.6913834891232</v>
       </c>
       <c r="H82" t="n">
-        <v>14.13067712384159</v>
+        <v>13.75816944320324</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6983500663520168</v>
+        <v>0.6799404203590791</v>
       </c>
       <c r="J82" t="n">
         <v>186.2973802760101</v>
       </c>
       <c r="K82" t="n">
-        <v>146.9740155456509</v>
+        <v>150.1497972539359</v>
       </c>
       <c r="L82" t="n">
-        <v>15.45664292371725</v>
+        <v>15.48483350062877</v>
       </c>
       <c r="M82" t="n">
-        <v>0.763880422484868</v>
+        <v>0.765273624741499</v>
       </c>
       <c r="N82" t="n">
         <v>183.0162368876618</v>
       </c>
       <c r="O82" t="n">
-        <v>164.7829457759922</v>
+        <v>165.5803756114567</v>
       </c>
       <c r="P82" t="n">
-        <v>15.37333707312743</v>
+        <v>15.33344404678792</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.7597633765869927</v>
+        <v>0.7577918293393257</v>
       </c>
       <c r="R82" t="n">
         <v>164.8878431370165</v>
       </c>
       <c r="S82" t="n">
-        <v>158.7269467661581</v>
+        <v>160.161799923148</v>
       </c>
       <c r="T82" t="n">
-        <v>16.81347917984981</v>
+        <v>16.71866595662715</v>
       </c>
       <c r="U82" t="n">
-        <v>0.8309364227879444</v>
+        <v>0.8262506727599516</v>
       </c>
       <c r="V82" t="n">
         <v>166.6060177059153</v>
       </c>
       <c r="W82" t="n">
-        <v>49.13487795057277</v>
+        <v>53.0875359438832</v>
       </c>
       <c r="X82" t="n">
-        <v>9.88834149188437</v>
+        <v>10.00681239928802</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.488690235892355</v>
+        <v>0.4945451687679019</v>
       </c>
       <c r="Z82" t="n">
         <v>176.1888335684919</v>
@@ -8906,11 +8924,11 @@
         </is>
       </c>
       <c r="AC82" t="n">
-        <v>49.13487795057277</v>
+        <v>53.0875359438832</v>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=49.13% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=53.09% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -8934,67 +8952,67 @@
         <v>2026</v>
       </c>
       <c r="E83" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F83" t="n">
-        <v>517</v>
+        <v>568</v>
       </c>
       <c r="G83" t="n">
-        <v>51.02863183184109</v>
+        <v>52.52556307122652</v>
       </c>
       <c r="H83" t="n">
-        <v>7.052280333443618</v>
+        <v>7.480870822943811</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1803219901479791</v>
+        <v>0.1912807561599696</v>
       </c>
       <c r="J83" t="n">
         <v>88.04980557911651</v>
       </c>
       <c r="K83" t="n">
-        <v>50.31163205003056</v>
+        <v>52.45767451233978</v>
       </c>
       <c r="L83" t="n">
-        <v>7.661759227942159</v>
+        <v>8.132669860598325</v>
       </c>
       <c r="M83" t="n">
-        <v>0.1959059490964036</v>
+        <v>0.2079468122566092</v>
       </c>
       <c r="N83" t="n">
         <v>194.0620340843763</v>
       </c>
       <c r="O83" t="n">
-        <v>88.95299588907891</v>
+        <v>87.08672830074077</v>
       </c>
       <c r="P83" t="n">
-        <v>29.65877688393252</v>
+        <v>29.13947193700469</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.7583546626335124</v>
+        <v>0.7450763899194166</v>
       </c>
       <c r="R83" t="n">
         <v>149.7627223031833</v>
       </c>
       <c r="S83" t="n">
-        <v>96.91457721417946</v>
+        <v>91.80819916945056</v>
       </c>
       <c r="T83" t="n">
-        <v>22.72224518269569</v>
+        <v>21.54199156037157</v>
       </c>
       <c r="U83" t="n">
-        <v>0.580992285933889</v>
+        <v>0.5508140071369478</v>
       </c>
       <c r="V83" t="n">
         <v>103.1343264142703</v>
       </c>
       <c r="W83" t="n">
-        <v>53.85416383210703</v>
+        <v>56.18793692851995</v>
       </c>
       <c r="X83" t="n">
-        <v>12.0151604806659</v>
+        <v>14.02910668794631</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.3072194449710817</v>
+        <v>0.3587146736031018</v>
       </c>
       <c r="Z83" t="n">
         <v>103.3034448942146</v>
@@ -9010,11 +9028,11 @@
         </is>
       </c>
       <c r="AC83" t="n">
-        <v>51.02863183184109</v>
+        <v>52.52556307122652</v>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=51.03% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=52.53% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9038,74 +9056,74 @@
         <v>2026</v>
       </c>
       <c r="E84" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F84" t="n">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="G84" t="n">
-        <v>48.50722597157945</v>
+        <v>51.62695131164382</v>
       </c>
       <c r="H84" t="n">
-        <v>2.938329021180119</v>
+        <v>3.378683688080732</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1461855234417969</v>
+        <v>0.1680937158249121</v>
       </c>
       <c r="J84" t="n">
         <v>100.4914466151705</v>
       </c>
       <c r="K84" t="n">
-        <v>48.44075332352193</v>
+        <v>47.53352019198421</v>
       </c>
       <c r="L84" t="n">
-        <v>3.466984031116273</v>
+        <v>3.552606807801132</v>
       </c>
       <c r="M84" t="n">
-        <v>0.1724867677172275</v>
+        <v>0.1767466073532901</v>
       </c>
       <c r="N84" t="n">
         <v>161.0256208848398</v>
       </c>
       <c r="O84" t="n">
-        <v>68.3318816586695</v>
+        <v>65.08926116149618</v>
       </c>
       <c r="P84" t="n">
-        <v>7.426679536194794</v>
+        <v>7.114489602688762</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.3694865440892932</v>
+        <v>0.3539547066014309</v>
       </c>
       <c r="R84" t="n">
         <v>93.7212443502728</v>
       </c>
       <c r="S84" t="n">
-        <v>86.97211525948009</v>
+        <v>84.03421546683751</v>
       </c>
       <c r="T84" t="n">
-        <v>10.12669274718141</v>
+        <v>9.813002901629179</v>
       </c>
       <c r="U84" t="n">
-        <v>0.5038155595612642</v>
+        <v>0.4882090995835413</v>
       </c>
       <c r="V84" t="n">
         <v>98.74789164115032</v>
       </c>
       <c r="W84" t="n">
-        <v>57.23119043438312</v>
+        <v>58.50110893202083</v>
       </c>
       <c r="X84" t="n">
-        <v>5.616704349781711</v>
+        <v>6.511660155341346</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.2794380273523239</v>
+        <v>0.3239631918080271</v>
       </c>
       <c r="Z84" t="n">
         <v>110.607240444147</v>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Prophet</t>
+          <t>DeepAR</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
@@ -9114,11 +9132,11 @@
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>48.50722597157945</v>
+        <v>47.53352019198421</v>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=48.51% sobre 30 sem</t>
+          <t>DeepAR: menor SMAPE real=47.53% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9142,67 +9160,67 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F85" t="n">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="G85" t="n">
-        <v>58.99109895409914</v>
+        <v>58.35535983346691</v>
       </c>
       <c r="H85" t="n">
-        <v>4.602364883946806</v>
+        <v>4.570460483149619</v>
       </c>
       <c r="I85" t="n">
-        <v>0.2000484600465876</v>
+        <v>0.1986616890257916</v>
       </c>
       <c r="J85" t="n">
         <v>109.9471447641292</v>
       </c>
       <c r="K85" t="n">
-        <v>53.05256417977209</v>
+        <v>56.25089073006766</v>
       </c>
       <c r="L85" t="n">
-        <v>5.120832214469105</v>
+        <v>6.227651313290661</v>
       </c>
       <c r="M85" t="n">
-        <v>0.2225843940002871</v>
+        <v>0.2706938902815826</v>
       </c>
       <c r="N85" t="n">
         <v>191.126671844217</v>
       </c>
       <c r="O85" t="n">
-        <v>83.59158083265145</v>
+        <v>82.96199500841203</v>
       </c>
       <c r="P85" t="n">
-        <v>14.28470782949307</v>
+        <v>14.15374989988948</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.6209055291276532</v>
+        <v>0.6152132529155979</v>
       </c>
       <c r="R85" t="n">
         <v>122.1180851534335</v>
       </c>
       <c r="S85" t="n">
-        <v>104.6846217735562</v>
+        <v>98.90275280448843</v>
       </c>
       <c r="T85" t="n">
-        <v>13.73058450796558</v>
+        <v>12.95739913762972</v>
       </c>
       <c r="U85" t="n">
-        <v>0.5968197558474579</v>
+        <v>0.5632121331216395</v>
       </c>
       <c r="V85" t="n">
         <v>106.9882513320439</v>
       </c>
       <c r="W85" t="n">
-        <v>45.16982604300648</v>
+        <v>49.73700094049354</v>
       </c>
       <c r="X85" t="n">
-        <v>4.927689121257922</v>
+        <v>6.541317105824335</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.21418914952493</v>
+        <v>0.2843278285606883</v>
       </c>
       <c r="Z85" t="n">
         <v>107.8756984639591</v>
@@ -9218,11 +9236,11 @@
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>45.16982604300648</v>
+        <v>49.73700094049354</v>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=45.17% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=49.74% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9246,67 +9264,67 @@
         <v>2026</v>
       </c>
       <c r="E86" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F86" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G86" t="n">
-        <v>123.301086111422</v>
+        <v>127.5252511541862</v>
       </c>
       <c r="H86" t="n">
-        <v>5.996981232960371</v>
+        <v>8.384262050715126</v>
       </c>
       <c r="I86" t="n">
-        <v>0.2564524915872403</v>
+        <v>0.3585412075676654</v>
       </c>
       <c r="J86" t="n">
         <v>160.3842205944857</v>
       </c>
       <c r="K86" t="n">
-        <v>132.9116328362832</v>
+        <v>136.0893225913666</v>
       </c>
       <c r="L86" t="n">
-        <v>4.520642627545026</v>
+        <v>5.846447599301512</v>
       </c>
       <c r="M86" t="n">
-        <v>0.1933189417097967</v>
+        <v>0.2500151318691011</v>
       </c>
       <c r="N86" t="n">
         <v>143.9950818237897</v>
       </c>
       <c r="O86" t="n">
-        <v>138.5203739979674</v>
+        <v>140.5290240841805</v>
       </c>
       <c r="P86" t="n">
-        <v>3.717853485544523</v>
+        <v>4.225549134425819</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.1589887899738404</v>
+        <v>0.1806996823488256</v>
       </c>
       <c r="R86" t="n">
         <v>178.0725595254285</v>
       </c>
       <c r="S86" t="n">
-        <v>173.8897661590264</v>
+        <v>175.3004168360341</v>
       </c>
       <c r="T86" t="n">
-        <v>28.88333333333333</v>
+        <v>37.140625</v>
       </c>
       <c r="U86" t="n">
-        <v>1.235155240767963</v>
+        <v>1.588266737939329</v>
       </c>
       <c r="V86" t="n">
         <v>188.4995472315167</v>
       </c>
       <c r="W86" t="n">
-        <v>95.88396977701767</v>
+        <v>101.8365964608055</v>
       </c>
       <c r="X86" t="n">
-        <v>3.497229831366464</v>
+        <v>6.393515742841513</v>
       </c>
       <c r="Y86" t="n">
-        <v>0.1495541288303179</v>
+        <v>0.2734097337577555</v>
       </c>
       <c r="Z86" t="n">
         <v>113.2748521774272</v>
@@ -9322,11 +9340,11 @@
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>95.88396977701767</v>
+        <v>101.8365964608055</v>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=95.88% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=101.84% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9350,67 +9368,67 @@
         <v>2026</v>
       </c>
       <c r="E87" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F87" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G87" t="n">
-        <v>127.1359430438049</v>
+        <v>130.8587080274083</v>
       </c>
       <c r="H87" t="n">
-        <v>2.106495564834618</v>
+        <v>2.903068594503345</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1473717929049143</v>
+        <v>0.2031005575516114</v>
       </c>
       <c r="J87" t="n">
         <v>171.410316416684</v>
       </c>
       <c r="K87" t="n">
-        <v>154.5788759945366</v>
+        <v>157.1061034890354</v>
       </c>
       <c r="L87" t="n">
-        <v>3.01489895316687</v>
+        <v>5.726332084084365</v>
       </c>
       <c r="M87" t="n">
-        <v>0.210924281813161</v>
+        <v>0.4006178983181017</v>
       </c>
       <c r="N87" t="n">
         <v>150.2517475184781</v>
       </c>
       <c r="O87" t="n">
-        <v>170.49225333327</v>
+        <v>172.0221077216994</v>
       </c>
       <c r="P87" t="n">
-        <v>12.80341693714172</v>
+        <v>14.55549038057714</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.8957353344742783</v>
+        <v>1.018311526406796</v>
       </c>
       <c r="R87" t="n">
         <v>166.9678403273574</v>
       </c>
       <c r="S87" t="n">
-        <v>170.5857762963043</v>
+        <v>172.1766405253101</v>
       </c>
       <c r="T87" t="n">
-        <v>13.26666666666667</v>
+        <v>16.296875</v>
       </c>
       <c r="U87" t="n">
-        <v>0.9281445853374145</v>
+        <v>1.140139921294272</v>
       </c>
       <c r="V87" t="n">
         <v>191.241827101395</v>
       </c>
       <c r="W87" t="n">
-        <v>123.3429179529025</v>
+        <v>127.7568541268455</v>
       </c>
       <c r="X87" t="n">
-        <v>2.148143063855119</v>
+        <v>4.433965946860839</v>
       </c>
       <c r="Y87" t="n">
-        <v>0.1502854788879838</v>
+        <v>0.3102031270213093</v>
       </c>
       <c r="Z87" t="n">
         <v>108.9238350712686</v>
@@ -9426,11 +9444,11 @@
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>127.1359430438049</v>
+        <v>130.8587080274083</v>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=127.14% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=130.86% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9454,67 +9472,67 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F88" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G88" t="n">
-        <v>133.5528783141412</v>
+        <v>137.0075349669297</v>
       </c>
       <c r="H88" t="n">
-        <v>2.706558296192459</v>
+        <v>3.625445764103078</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1497145470668257</v>
+        <v>0.2005432401923915</v>
       </c>
       <c r="J88" t="n">
         <v>169.0038464611843</v>
       </c>
       <c r="K88" t="n">
-        <v>183.0002012052401</v>
+        <v>183.9931937917177</v>
       </c>
       <c r="L88" t="n">
-        <v>1.033555717685064</v>
+        <v>1.000085253608984</v>
       </c>
       <c r="M88" t="n">
-        <v>0.05717162137583758</v>
+        <v>0.05532018688934742</v>
       </c>
       <c r="N88" t="n">
         <v>118.6804789630648</v>
       </c>
       <c r="O88" t="n">
-        <v>166.3099100017029</v>
+        <v>165.7955665327881</v>
       </c>
       <c r="P88" t="n">
-        <v>1.9910009821256</v>
+        <v>1.901194104924798</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.1101331571789442</v>
+        <v>0.1051654474634288</v>
       </c>
       <c r="R88" t="n">
         <v>181.2811328411623</v>
       </c>
       <c r="S88" t="n">
-        <v>179.1829677169829</v>
+        <v>180.3015504828466</v>
       </c>
       <c r="T88" t="n">
-        <v>16</v>
+        <v>21.390625</v>
       </c>
       <c r="U88" t="n">
-        <v>0.88504753673293</v>
+        <v>1.183232497839239</v>
       </c>
       <c r="V88" t="n">
         <v>190.1751472740156</v>
       </c>
       <c r="W88" t="n">
-        <v>129.3590645685444</v>
+        <v>133.4892045233175</v>
       </c>
       <c r="X88" t="n">
-        <v>3.591105399479158</v>
+        <v>6.482650465163747</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.1986436867473346</v>
+        <v>0.3585908641058598</v>
       </c>
       <c r="Z88" t="n">
         <v>121.3094122928426</v>
@@ -9530,11 +9548,11 @@
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>133.5528783141412</v>
+        <v>137.0075349669297</v>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=133.55% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=137.01% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9576,7 @@
         <v>2026</v>
       </c>
       <c r="E89" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -9567,7 +9585,7 @@
         <v>200</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1046335363502783</v>
+        <v>0.1049542097975099</v>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
@@ -9577,7 +9595,7 @@
         <v>200</v>
       </c>
       <c r="L89" t="n">
-        <v>0.007315806193424531</v>
+        <v>0.007386427217432228</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
@@ -9603,7 +9621,7 @@
         <v>200</v>
       </c>
       <c r="X89" t="n">
-        <v>7.212276214833761</v>
+        <v>7.21227621483376</v>
       </c>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="n">
@@ -9646,7 +9664,7 @@
         <v>2026</v>
       </c>
       <c r="E90" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -9655,10 +9673,10 @@
         <v>200</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09192167342417998</v>
+        <v>0.09219600477250796</v>
       </c>
       <c r="I90" t="n">
-        <v>0.01567960314271727</v>
+        <v>0.01572639740255999</v>
       </c>
       <c r="J90" t="n">
         <v>200</v>
@@ -9667,10 +9685,10 @@
         <v>200</v>
       </c>
       <c r="L90" t="n">
-        <v>0.00337484183522561</v>
+        <v>0.003374272658009103</v>
       </c>
       <c r="M90" t="n">
-        <v>0.0005756659846866712</v>
+        <v>0.0005755688968885464</v>
       </c>
       <c r="N90" t="n">
         <v>200</v>
@@ -9699,10 +9717,10 @@
         <v>200</v>
       </c>
       <c r="X90" t="n">
-        <v>3.199488491048594</v>
+        <v>3.199488491048593</v>
       </c>
       <c r="Y90" t="n">
-        <v>0.5457549664901653</v>
+        <v>0.5457549664901652</v>
       </c>
       <c r="Z90" t="n">
         <v>200</v>
@@ -9744,7 +9762,7 @@
         <v>2026</v>
       </c>
       <c r="E91" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -9753,10 +9771,10 @@
         <v>200</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09437379485105826</v>
+        <v>0.09464873649391999</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0128290630213843</v>
+        <v>0.01286643826595344</v>
       </c>
       <c r="J91" t="n">
         <v>200</v>
@@ -9765,10 +9783,10 @@
         <v>200</v>
       </c>
       <c r="L91" t="n">
-        <v>0.01324307176903409</v>
+        <v>0.01340366834135284</v>
       </c>
       <c r="M91" t="n">
-        <v>0.00180024764914652</v>
+        <v>0.001822078958892484</v>
       </c>
       <c r="N91" t="n">
         <v>200</v>
@@ -9797,10 +9815,10 @@
         <v>200</v>
       </c>
       <c r="X91" t="n">
-        <v>2.168623114550154e-17</v>
+        <v>2.033084169890769e-17</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.948000835412274e-18</v>
+        <v>2.763750783199007e-18</v>
       </c>
       <c r="Z91" t="n">
         <v>200</v>
@@ -9842,67 +9860,67 @@
         <v>2026</v>
       </c>
       <c r="E92" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F92" t="n">
-        <v>658</v>
+        <v>794</v>
       </c>
       <c r="G92" t="n">
-        <v>44.8147114175882</v>
+        <v>43.44768168096165</v>
       </c>
       <c r="H92" t="n">
-        <v>8.16451841578726</v>
+        <v>8.516976612509247</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06768161994331701</v>
+        <v>0.07060340179272989</v>
       </c>
       <c r="J92" t="n">
         <v>49.15109590531281</v>
       </c>
       <c r="K92" t="n">
-        <v>47.96484795715127</v>
+        <v>46.29142966394662</v>
       </c>
       <c r="L92" t="n">
-        <v>8.800377035330758</v>
+        <v>9.028304867313881</v>
       </c>
       <c r="M92" t="n">
-        <v>0.07295271362379779</v>
+        <v>0.07484217288069121</v>
       </c>
       <c r="N92" t="n">
         <v>104.6459551741298</v>
       </c>
       <c r="O92" t="n">
-        <v>141.9480576296123</v>
+        <v>139.3837241005544</v>
       </c>
       <c r="P92" t="n">
-        <v>102.688934953488</v>
+        <v>104.9309467603154</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.8512631258773166</v>
+        <v>0.8698487892674197</v>
       </c>
       <c r="R92" t="n">
         <v>118.9713689353267</v>
       </c>
       <c r="S92" t="n">
-        <v>85.35510875281915</v>
+        <v>86.15812744724073</v>
       </c>
       <c r="T92" t="n">
-        <v>34.08913721062245</v>
+        <v>40.15523805578477</v>
       </c>
       <c r="U92" t="n">
-        <v>0.2825896043572661</v>
+        <v>0.3328759177724244</v>
       </c>
       <c r="V92" t="n">
         <v>92.01416331532587</v>
       </c>
       <c r="W92" t="n">
-        <v>46.56001376738867</v>
+        <v>50.41443200535857</v>
       </c>
       <c r="X92" t="n">
-        <v>18.26791375477017</v>
+        <v>27.2045993632667</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.1514359981743551</v>
+        <v>0.2255186725103711</v>
       </c>
       <c r="Z92" t="n">
         <v>95.83480509856771</v>
@@ -9918,11 +9936,11 @@
         </is>
       </c>
       <c r="AC92" t="n">
-        <v>44.8147114175882</v>
+        <v>43.44768168096165</v>
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=44.81% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=43.45% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -9946,67 +9964,67 @@
         <v>2026</v>
       </c>
       <c r="E93" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F93" t="n">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="G93" t="n">
-        <v>42.40547593859543</v>
+        <v>40.16729015872674</v>
       </c>
       <c r="H93" t="n">
-        <v>3.735237768442399</v>
+        <v>3.617832009159766</v>
       </c>
       <c r="I93" t="n">
-        <v>0.06394928499821131</v>
+        <v>0.06193923508272031</v>
       </c>
       <c r="J93" t="n">
         <v>60.93105560683724</v>
       </c>
       <c r="K93" t="n">
-        <v>63.82707453463673</v>
+        <v>63.64418311143931</v>
       </c>
       <c r="L93" t="n">
-        <v>10.52412469171541</v>
+        <v>11.50221183857543</v>
       </c>
       <c r="M93" t="n">
-        <v>0.1801786903509139</v>
+        <v>0.1969240697846095</v>
       </c>
       <c r="N93" t="n">
         <v>89.5280086489867</v>
       </c>
       <c r="O93" t="n">
-        <v>138.6160653578765</v>
+        <v>136.5197813644439</v>
       </c>
       <c r="P93" t="n">
-        <v>46.60846914201453</v>
+        <v>47.83790019556624</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.7979621275183055</v>
+        <v>0.8190106501835749</v>
       </c>
       <c r="R93" t="n">
         <v>121.8694023763068</v>
       </c>
       <c r="S93" t="n">
-        <v>93.80035718981365</v>
+        <v>94.53863770585374</v>
       </c>
       <c r="T93" t="n">
-        <v>18.79890339507979</v>
+        <v>21.81291218134708</v>
       </c>
       <c r="U93" t="n">
-        <v>0.321847364315742</v>
+        <v>0.3734488201824978</v>
       </c>
       <c r="V93" t="n">
         <v>96.01849856237216</v>
       </c>
       <c r="W93" t="n">
-        <v>45.66091742819074</v>
+        <v>49.76203146735596</v>
       </c>
       <c r="X93" t="n">
-        <v>7.852568814286215</v>
+        <v>12.07659151073413</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.1344402129672885</v>
+        <v>0.2067577595331936</v>
       </c>
       <c r="Z93" t="n">
         <v>99.35850993844542</v>
@@ -10022,11 +10040,11 @@
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>42.40547593859543</v>
+        <v>40.16729015872674</v>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=42.41% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=40.17% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -10050,67 +10068,67 @@
         <v>2026</v>
       </c>
       <c r="E94" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F94" t="n">
-        <v>355</v>
+        <v>431</v>
       </c>
       <c r="G94" t="n">
-        <v>47.60497596594993</v>
+        <v>45.91779586034249</v>
       </c>
       <c r="H94" t="n">
-        <v>4.626567631499932</v>
+        <v>4.773811534244039</v>
       </c>
       <c r="I94" t="n">
-        <v>0.06198976854163958</v>
+        <v>0.06396263831838933</v>
       </c>
       <c r="J94" t="n">
         <v>64.07712599234655</v>
       </c>
       <c r="K94" t="n">
-        <v>71.83030663782192</v>
+        <v>73.71671526516033</v>
       </c>
       <c r="L94" t="n">
-        <v>7.176601563223335</v>
+        <v>8.313729180897738</v>
       </c>
       <c r="M94" t="n">
-        <v>0.09615678517068489</v>
+        <v>0.1113927621273406</v>
       </c>
       <c r="N94" t="n">
         <v>91.94886769427217</v>
       </c>
       <c r="O94" t="n">
-        <v>138.4285659846822</v>
+        <v>134.8238861050864</v>
       </c>
       <c r="P94" t="n">
-        <v>47.51795838081418</v>
+        <v>47.7732385182485</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.6366765767223772</v>
+        <v>0.6400969863852749</v>
       </c>
       <c r="R94" t="n">
         <v>120.3184691119026</v>
       </c>
       <c r="S94" t="n">
-        <v>92.16441284077607</v>
+        <v>92.3294023998548</v>
       </c>
       <c r="T94" t="n">
-        <v>19.79456233909</v>
+        <v>22.83818491885877</v>
       </c>
       <c r="U94" t="n">
-        <v>0.2652204475362726</v>
+        <v>0.306000886573496</v>
       </c>
       <c r="V94" t="n">
         <v>95.82311990464228</v>
       </c>
       <c r="W94" t="n">
-        <v>48.27835983968884</v>
+        <v>51.91622679743573</v>
       </c>
       <c r="X94" t="n">
-        <v>10.03168973088775</v>
+        <v>14.85231251753937</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.13441111727522</v>
+        <v>0.1990009632630992</v>
       </c>
       <c r="Z94" t="n">
         <v>93.11495456228404</v>
@@ -10126,11 +10144,11 @@
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>47.60497596594993</v>
+        <v>45.91779586034249</v>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=47.60% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=45.92% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -10154,31 +10172,31 @@
         <v>2026</v>
       </c>
       <c r="E95" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G95" t="n">
-        <v>139.6518920842648</v>
+        <v>138.7444850449937</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6920073517632495</v>
+        <v>0.8177615567993096</v>
       </c>
       <c r="I95" t="n">
-        <v>0.009880526171882913</v>
+        <v>0.01167605292592268</v>
       </c>
       <c r="J95" t="n">
         <v>152.3875262412586</v>
       </c>
       <c r="K95" t="n">
-        <v>199.3733198561377</v>
+        <v>199.4010591254942</v>
       </c>
       <c r="L95" t="n">
-        <v>0.6652266326922892</v>
+        <v>0.8422991112235738</v>
       </c>
       <c r="M95" t="n">
-        <v>0.009498149315613625</v>
+        <v>0.01202640173083811</v>
       </c>
       <c r="N95" t="n">
         <v>128.1095321097334</v>
@@ -10187,34 +10205,34 @@
         <v>200</v>
       </c>
       <c r="P95" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.84375</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.009518710214765899</v>
+        <v>0.01204711761556309</v>
       </c>
       <c r="R95" t="n">
         <v>189.619699057401</v>
       </c>
       <c r="S95" t="n">
-        <v>173.7136344084252</v>
+        <v>175.4095289627203</v>
       </c>
       <c r="T95" t="n">
-        <v>2.802601012022309</v>
+        <v>2.846188448770915</v>
       </c>
       <c r="U95" t="n">
-        <v>0.04001572032157501</v>
+        <v>0.04063806459069663</v>
       </c>
       <c r="V95" t="n">
         <v>118.2821915164861</v>
       </c>
       <c r="W95" t="n">
-        <v>150.7403026179851</v>
+        <v>147.9652568600357</v>
       </c>
       <c r="X95" t="n">
-        <v>2.026063216588837</v>
+        <v>2.394133154737051</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.02892826295325843</v>
+        <v>0.03418358957325791</v>
       </c>
       <c r="Z95" t="n">
         <v>128.8999217807187</v>
@@ -10230,11 +10248,11 @@
         </is>
       </c>
       <c r="AC95" t="n">
-        <v>139.6518920842648</v>
+        <v>138.7444850449937</v>
       </c>
       <c r="AD95" t="inlineStr">
         <is>
-          <t>Prophet: menor SMAPE real=139.65% sobre 30 sem</t>
+          <t>Prophet: menor SMAPE real=138.74% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -10258,67 +10276,67 @@
         <v>2026</v>
       </c>
       <c r="E96" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>187.1999330460831</v>
+        <v>187.1939399887914</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3633763130695801</v>
+        <v>0.4010795377122749</v>
       </c>
       <c r="I96" t="n">
-        <v>0.01104067795122157</v>
+        <v>0.01218623737826889</v>
       </c>
       <c r="J96" t="n">
         <v>158.9896824444987</v>
       </c>
       <c r="K96" t="n">
-        <v>199.5213512926411</v>
+        <v>199.5392659333326</v>
       </c>
       <c r="L96" t="n">
-        <v>0.233681801781556</v>
+        <v>0.2815466724663037</v>
       </c>
       <c r="M96" t="n">
-        <v>0.007100092724088296</v>
+        <v>0.00855439946726331</v>
       </c>
       <c r="N96" t="n">
         <v>189.1617640516506</v>
       </c>
       <c r="O96" t="n">
-        <v>186.2454672519581</v>
+        <v>177.1382946326388</v>
       </c>
       <c r="P96" t="n">
-        <v>2.008256972093726</v>
+        <v>2.002272480508249</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.06101806219806232</v>
+        <v>0.06083623184225594</v>
       </c>
       <c r="R96" t="n">
         <v>127.6499599586913</v>
       </c>
       <c r="S96" t="n">
-        <v>180.9325446207748</v>
+        <v>173.9313737757035</v>
       </c>
       <c r="T96" t="n">
-        <v>2.683217129863186</v>
+        <v>2.594704863987745</v>
       </c>
       <c r="U96" t="n">
-        <v>0.08152577682835355</v>
+        <v>0.07883645617889086</v>
       </c>
       <c r="V96" t="n">
         <v>124.4459476108536</v>
       </c>
       <c r="W96" t="n">
-        <v>176.9802125669613</v>
+        <v>174.2696067855812</v>
       </c>
       <c r="X96" t="n">
-        <v>1.090996869122955</v>
+        <v>1.279969003772953</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.03314840468280911</v>
+        <v>0.03889005708387248</v>
       </c>
       <c r="Z96" t="n">
         <v>151.8363274594118</v>
@@ -10336,7 +10354,7 @@
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr">
         <is>
-          <t>DeepAR: serie casi-cero (total 7 casos), menor MAE real</t>
+          <t>DeepAR: serie casi-cero (total 9 casos), menor MAE real</t>
         </is>
       </c>
     </row>
@@ -10360,67 +10378,67 @@
         <v>2026</v>
       </c>
       <c r="E97" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F97" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G97" t="n">
-        <v>173.4553670502901</v>
+        <v>174.5278837220783</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4569409088175804</v>
+        <v>0.581122551121958</v>
       </c>
       <c r="I97" t="n">
-        <v>0.01220339599579584</v>
+        <v>0.01551988118502976</v>
       </c>
       <c r="J97" t="n">
         <v>157.2976315063829</v>
       </c>
       <c r="K97" t="n">
-        <v>199.4509302749238</v>
+        <v>199.4618982132517</v>
       </c>
       <c r="L97" t="n">
-        <v>0.4352984025939205</v>
+        <v>0.564202898170945</v>
       </c>
       <c r="M97" t="n">
-        <v>0.01162539549574817</v>
+        <v>0.01506801263684714</v>
       </c>
       <c r="N97" t="n">
         <v>187.1093440450062</v>
       </c>
       <c r="O97" t="n">
-        <v>156.9933999861937</v>
+        <v>144.9181935094623</v>
       </c>
       <c r="P97" t="n">
-        <v>1.911514888207118</v>
+        <v>1.830292822793126</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.05105030581090617</v>
+        <v>0.0488811303032716</v>
       </c>
       <c r="R97" t="n">
         <v>126.5693936023772</v>
       </c>
       <c r="S97" t="n">
-        <v>172.4679002833108</v>
+        <v>174.3666657810135</v>
       </c>
       <c r="T97" t="n">
-        <v>1.769842445059661</v>
+        <v>1.815477292243432</v>
       </c>
       <c r="U97" t="n">
-        <v>0.04726669858279849</v>
+        <v>0.04848545597712388</v>
       </c>
       <c r="V97" t="n">
         <v>128.4785456608675</v>
       </c>
       <c r="W97" t="n">
-        <v>153.0029045246747</v>
+        <v>146.2756857328174</v>
       </c>
       <c r="X97" t="n">
-        <v>1.063882494691097</v>
+        <v>1.085326251723157</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.02841281908705985</v>
+        <v>0.02898551164675431</v>
       </c>
       <c r="Z97" t="n">
         <v>136.0400571203446</v>
@@ -10436,11 +10454,11 @@
         </is>
       </c>
       <c r="AC97" t="n">
-        <v>153.0029045246747</v>
+        <v>146.2756857328174</v>
       </c>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>NBGLM: menor SMAPE real=153.00% sobre 30 sem</t>
+          <t>NBGLM: menor SMAPE real=146.28% sobre 32 sem</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10482,7 @@
         <v>2026</v>
       </c>
       <c r="E98" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -10473,10 +10491,10 @@
         <v>200</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0484024425262529</v>
+        <v>0.04537728986836209</v>
       </c>
       <c r="I98" t="n">
-        <v>0.03635864227324161</v>
+        <v>0.03408622713116401</v>
       </c>
       <c r="J98" t="n">
         <v>198.585723184526</v>
@@ -10485,10 +10503,10 @@
         <v>200</v>
       </c>
       <c r="L98" t="n">
-        <v>0.0005431090563802467</v>
+        <v>0.0005406130549963625</v>
       </c>
       <c r="M98" t="n">
-        <v>0.0004079692442292933</v>
+        <v>0.000406094313612291</v>
       </c>
       <c r="N98" t="n">
         <v>199.9898962083731</v>
@@ -10497,10 +10515,10 @@
         <v>200</v>
       </c>
       <c r="P98" t="n">
-        <v>0.9</v>
+        <v>1.215525293323572</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.676056338028169</v>
+        <v>0.9130706428721664</v>
       </c>
       <c r="R98" t="n">
         <v>199.2030987655621</v>
@@ -10519,10 +10537,10 @@
         <v>200</v>
       </c>
       <c r="X98" t="n">
-        <v>0.09609024543466431</v>
+        <v>0.1472951036823441</v>
       </c>
       <c r="Y98" t="n">
-        <v>0.07218046605420793</v>
+        <v>0.11064420933885</v>
       </c>
       <c r="Z98" t="n">
         <v>199.9999998548883</v>
@@ -10564,7 +10582,7 @@
         <v>2026</v>
       </c>
       <c r="E99" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -10573,10 +10591,10 @@
         <v>200</v>
       </c>
       <c r="H99" t="n">
-        <v>0.02788729614426955</v>
+        <v>0.02614434013525271</v>
       </c>
       <c r="I99" t="n">
-        <v>0.04311079597181767</v>
+        <v>0.04041637122357906</v>
       </c>
       <c r="J99" t="n">
         <v>198.7380283178126</v>
@@ -10585,10 +10603,10 @@
         <v>200</v>
       </c>
       <c r="L99" t="n">
-        <v>0.00166805595446163</v>
+        <v>0.001670516963400413</v>
       </c>
       <c r="M99" t="n">
-        <v>0.00257863722428851</v>
+        <v>0.002582441682551363</v>
       </c>
       <c r="N99" t="n">
         <v>199.9983019911245</v>
@@ -10597,10 +10615,10 @@
         <v>200</v>
       </c>
       <c r="P99" t="n">
-        <v>0.5103918545549554</v>
+        <v>0.6582368534582161</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.7890115625970325</v>
+        <v>1.017564217906421</v>
       </c>
       <c r="R99" t="n">
         <v>198.5022493653877</v>
@@ -10619,10 +10637,10 @@
         <v>200</v>
       </c>
       <c r="X99" t="n">
-        <v>0.08281289059030879</v>
+        <v>0.1337533440853979</v>
       </c>
       <c r="Y99" t="n">
-        <v>0.128019927482603</v>
+        <v>0.2067684546247697</v>
       </c>
       <c r="Z99" t="n">
         <v>200</v>
@@ -10664,7 +10682,7 @@
         <v>2026</v>
       </c>
       <c r="E100" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -10673,10 +10691,10 @@
         <v>200</v>
       </c>
       <c r="H100" t="n">
-        <v>0.0463232786624037</v>
+        <v>0.04342807374600348</v>
       </c>
       <c r="I100" t="n">
-        <v>0.06202279988271626</v>
+        <v>0.0581463748900465</v>
       </c>
       <c r="J100" t="n">
         <v>200</v>
@@ -10685,10 +10703,10 @@
         <v>200</v>
       </c>
       <c r="L100" t="n">
-        <v>0.002423718137088566</v>
+        <v>0.002439463363407116</v>
       </c>
       <c r="M100" t="n">
-        <v>0.003245145622880089</v>
+        <v>0.003266227097448858</v>
       </c>
       <c r="N100" t="n">
         <v>200</v>
@@ -10697,10 +10715,10 @@
         <v>200</v>
       </c>
       <c r="P100" t="n">
-        <v>0.2704078702567994</v>
+        <v>0.440405014597148</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.3620523785865097</v>
+        <v>0.5896636178706585</v>
       </c>
       <c r="R100" t="n">
         <v>200</v>
@@ -10719,10 +10737,10 @@
         <v>200</v>
       </c>
       <c r="X100" t="n">
-        <v>0.05609176635205636</v>
+        <v>0.1054354194749046</v>
       </c>
       <c r="Y100" t="n">
-        <v>0.07510194658015916</v>
+        <v>0.1411687624768598</v>
       </c>
       <c r="Z100" t="n">
         <v>200</v>
